--- a/king_index/output/index.xlsx
+++ b/king_index/output/index.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -754,6 +754,22 @@
         <v>0.4222338098520577</v>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2021-03-26</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>25645315345</v>
+      </c>
+      <c r="C21" t="n">
+        <v>61399844931</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0.4176772005502575</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/king_index/output/index.xlsx
+++ b/king_index/output/index.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -770,6 +770,38 @@
         <v>0.4176772005502575</v>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2021-03-29</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>25840927972</v>
+      </c>
+      <c r="C22" t="n">
+        <v>63142726153</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0.4092463146013892</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2021-03-30</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>25574432328</v>
+      </c>
+      <c r="C23" t="n">
+        <v>62988936235</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0.4060146726813508</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/king_index/output/index.xlsx
+++ b/king_index/output/index.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:D24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -802,6 +802,22 @@
         <v>0.4060146726813508</v>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2021-03-31</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>25156623964</v>
+      </c>
+      <c r="C24" t="n">
+        <v>59075210254</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0.4258406166619887</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/king_index/output/index.xlsx
+++ b/king_index/output/index.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D24"/>
+  <dimension ref="A1:D25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -818,6 +818,22 @@
         <v>0.4258406166619887</v>
       </c>
     </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2021-04-01</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>24301307181</v>
+      </c>
+      <c r="C25" t="n">
+        <v>57851462635</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0.4200638337240201</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/king_index/output/index.xlsx
+++ b/king_index/output/index.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D25"/>
+  <dimension ref="A1:D26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -834,6 +834,22 @@
         <v>0.4200638337240201</v>
       </c>
     </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2021-04-02</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>23672531991</v>
+      </c>
+      <c r="C26" t="n">
+        <v>57863093037</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0.4091127996884443</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/king_index/output/index.xlsx
+++ b/king_index/output/index.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D26"/>
+  <dimension ref="A1:D27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -850,6 +850,22 @@
         <v>0.4091127996884443</v>
       </c>
     </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2021-04-06</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>21461794855</v>
+      </c>
+      <c r="C27" t="n">
+        <v>54114680064</v>
+      </c>
+      <c r="D27" t="n">
+        <v>0.3965983875284433</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/king_index/output/index.xlsx
+++ b/king_index/output/index.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D27"/>
+  <dimension ref="A1:D28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -866,6 +866,22 @@
         <v>0.3965983875284433</v>
       </c>
     </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2021-04-07</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>28017074765</v>
+      </c>
+      <c r="C28" t="n">
+        <v>64888959803</v>
+      </c>
+      <c r="D28" t="n">
+        <v>0.431769515955543</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/king_index/output/index.xlsx
+++ b/king_index/output/index.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D28"/>
+  <dimension ref="A1:D29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -882,6 +882,22 @@
         <v>0.431769515955543</v>
       </c>
     </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2021-04-08</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>31420565576</v>
+      </c>
+      <c r="C29" t="n">
+        <v>70318042166</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0.446835045575151</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/king_index/output/index.xlsx
+++ b/king_index/output/index.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D29"/>
+  <dimension ref="A1:D30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -460,10 +460,10 @@
         <v>27735524005</v>
       </c>
       <c r="C2" t="n">
-        <v>65960353205</v>
+        <v>65960299305</v>
       </c>
       <c r="D2" t="n">
-        <v>0.4204878030109996</v>
+        <v>0.4204881466160594</v>
       </c>
     </row>
     <row r="3">
@@ -476,10 +476,10 @@
         <v>30275962974</v>
       </c>
       <c r="C3" t="n">
-        <v>69588818844</v>
+        <v>69588729144</v>
       </c>
       <c r="D3" t="n">
-        <v>0.4350693613850642</v>
+        <v>0.4350699221902721</v>
       </c>
     </row>
     <row r="4">
@@ -489,13 +489,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>31392686674</v>
+        <v>31328612952</v>
       </c>
       <c r="C4" t="n">
-        <v>70191553922</v>
+        <v>70191438422</v>
       </c>
       <c r="D4" t="n">
-        <v>0.4472430786884268</v>
+        <v>0.4463309722141371</v>
       </c>
     </row>
     <row r="5">
@@ -505,13 +505,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>35807358233</v>
+        <v>35737177720</v>
       </c>
       <c r="C5" t="n">
-        <v>78683618027</v>
+        <v>78683500727</v>
       </c>
       <c r="D5" t="n">
-        <v>0.4550802203924181</v>
+        <v>0.454188964519939</v>
       </c>
     </row>
     <row r="6">
@@ -524,10 +524,10 @@
         <v>32013254979</v>
       </c>
       <c r="C6" t="n">
-        <v>73603004552</v>
+        <v>73602803152</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4349449478843335</v>
+        <v>0.4349461380280339</v>
       </c>
     </row>
     <row r="7">
@@ -540,10 +540,10 @@
         <v>33926652652</v>
       </c>
       <c r="C7" t="n">
-        <v>78914242339</v>
+        <v>78913752639</v>
       </c>
       <c r="D7" t="n">
-        <v>0.4299179925755075</v>
+        <v>0.4299206604354676</v>
       </c>
     </row>
     <row r="8">
@@ -556,10 +556,10 @@
         <v>35544287853</v>
       </c>
       <c r="C8" t="n">
-        <v>82998411331</v>
+        <v>82986392531</v>
       </c>
       <c r="D8" t="n">
-        <v>0.4282526289719978</v>
+        <v>0.4283146521849621</v>
       </c>
     </row>
     <row r="9">
@@ -569,13 +569,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>26853700349</v>
+        <v>26768080114</v>
       </c>
       <c r="C9" t="n">
-        <v>62383122535</v>
+        <v>62242276864</v>
       </c>
       <c r="D9" t="n">
-        <v>0.4304641905979258</v>
+        <v>0.4300626754462811</v>
       </c>
     </row>
     <row r="10">
@@ -588,10 +588,10 @@
         <v>30414794010</v>
       </c>
       <c r="C10" t="n">
-        <v>66747690761</v>
+        <v>66703023106</v>
       </c>
       <c r="D10" t="n">
-        <v>0.4556681087126246</v>
+        <v>0.4559732466947838</v>
       </c>
     </row>
     <row r="11">
@@ -604,10 +604,10 @@
         <v>33515365360</v>
       </c>
       <c r="C11" t="n">
-        <v>72364022977</v>
+        <v>72307731035</v>
       </c>
       <c r="D11" t="n">
-        <v>0.4631495594247495</v>
+        <v>0.4635101237484156</v>
       </c>
     </row>
     <row r="12">
@@ -620,10 +620,10 @@
         <v>34294525399</v>
       </c>
       <c r="C12" t="n">
-        <v>71847327222</v>
+        <v>71819039829</v>
       </c>
       <c r="D12" t="n">
-        <v>0.4773249990641106</v>
+        <v>0.4775130032461409</v>
       </c>
     </row>
     <row r="13">
@@ -636,10 +636,10 @@
         <v>29706651386</v>
       </c>
       <c r="C13" t="n">
-        <v>67180156615</v>
+        <v>67143243915</v>
       </c>
       <c r="D13" t="n">
-        <v>0.4421938394136922</v>
+        <v>0.4424369400979068</v>
       </c>
     </row>
     <row r="14">
@@ -652,10 +652,10 @@
         <v>27229816586</v>
       </c>
       <c r="C14" t="n">
-        <v>62653031351</v>
+        <v>62598212217</v>
       </c>
       <c r="D14" t="n">
-        <v>0.434612914951407</v>
+        <v>0.4349935185306316</v>
       </c>
     </row>
     <row r="15">
@@ -668,10 +668,10 @@
         <v>26457202635</v>
       </c>
       <c r="C15" t="n">
-        <v>62936194829</v>
+        <v>62902087938</v>
       </c>
       <c r="D15" t="n">
-        <v>0.4203813514128906</v>
+        <v>0.420609291397096</v>
       </c>
     </row>
     <row r="16">
@@ -684,10 +684,10 @@
         <v>28142140366</v>
       </c>
       <c r="C16" t="n">
-        <v>66054136669</v>
+        <v>66028104022</v>
       </c>
       <c r="D16" t="n">
-        <v>0.4260466003366515</v>
+        <v>0.426214576093587</v>
       </c>
     </row>
     <row r="17">
@@ -700,10 +700,10 @@
         <v>28955693616</v>
       </c>
       <c r="C17" t="n">
-        <v>67523746492</v>
+        <v>67503414654</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4288223790934139</v>
+        <v>0.4289515391838655</v>
       </c>
     </row>
     <row r="18">
@@ -716,10 +716,10 @@
         <v>29065050246</v>
       </c>
       <c r="C18" t="n">
-        <v>70407865486</v>
+        <v>70391613937</v>
       </c>
       <c r="D18" t="n">
-        <v>0.4128097059238266</v>
+        <v>0.4129050126910432</v>
       </c>
     </row>
     <row r="19">
@@ -732,10 +732,10 @@
         <v>28264580783</v>
       </c>
       <c r="C19" t="n">
-        <v>67418126725</v>
+        <v>67388687603</v>
       </c>
       <c r="D19" t="n">
-        <v>0.4192430456914331</v>
+        <v>0.4194261943415815</v>
       </c>
     </row>
     <row r="20">
@@ -748,10 +748,10 @@
         <v>25646340206</v>
       </c>
       <c r="C20" t="n">
-        <v>60739665104</v>
+        <v>60699839691</v>
       </c>
       <c r="D20" t="n">
-        <v>0.4222338098520577</v>
+        <v>0.4225108391810563</v>
       </c>
     </row>
     <row r="21">
@@ -764,10 +764,10 @@
         <v>25645315345</v>
       </c>
       <c r="C21" t="n">
-        <v>61399844931</v>
+        <v>61377161981</v>
       </c>
       <c r="D21" t="n">
-        <v>0.4176772005502575</v>
+        <v>0.4178315600994846</v>
       </c>
     </row>
     <row r="22">
@@ -780,10 +780,10 @@
         <v>25840927972</v>
       </c>
       <c r="C22" t="n">
-        <v>63142726153</v>
+        <v>63118193430</v>
       </c>
       <c r="D22" t="n">
-        <v>0.4092463146013892</v>
+        <v>0.4094053800931165</v>
       </c>
     </row>
     <row r="23">
@@ -796,10 +796,10 @@
         <v>25574432328</v>
       </c>
       <c r="C23" t="n">
-        <v>62988936235</v>
+        <v>62974799316</v>
       </c>
       <c r="D23" t="n">
-        <v>0.4060146726813508</v>
+        <v>0.4061058170216718</v>
       </c>
     </row>
     <row r="24">
@@ -812,10 +812,10 @@
         <v>25156623964</v>
       </c>
       <c r="C24" t="n">
-        <v>59075210254</v>
+        <v>59063876194</v>
       </c>
       <c r="D24" t="n">
-        <v>0.4258406166619887</v>
+        <v>0.4259223333289381</v>
       </c>
     </row>
     <row r="25">
@@ -825,13 +825,13 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>24301307181</v>
+        <v>24247693731</v>
       </c>
       <c r="C25" t="n">
-        <v>57851462635</v>
+        <v>57835629725</v>
       </c>
       <c r="D25" t="n">
-        <v>0.4200638337240201</v>
+        <v>0.4192518322406837</v>
       </c>
     </row>
     <row r="26">
@@ -841,13 +841,13 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>23672531991</v>
+        <v>23620032307</v>
       </c>
       <c r="C26" t="n">
-        <v>57863093037</v>
+        <v>57817527627</v>
       </c>
       <c r="D26" t="n">
-        <v>0.4091127996884443</v>
+        <v>0.4085271936804466</v>
       </c>
     </row>
     <row r="27">
@@ -860,10 +860,10 @@
         <v>21461794855</v>
       </c>
       <c r="C27" t="n">
-        <v>54114680064</v>
+        <v>54090962340</v>
       </c>
       <c r="D27" t="n">
-        <v>0.3965983875284433</v>
+        <v>0.3967722873942864</v>
       </c>
     </row>
     <row r="28">
@@ -876,10 +876,10 @@
         <v>28017074765</v>
       </c>
       <c r="C28" t="n">
-        <v>64888959803</v>
+        <v>64860913169</v>
       </c>
       <c r="D28" t="n">
-        <v>0.431769515955543</v>
+        <v>0.4319562182542728</v>
       </c>
     </row>
     <row r="29">
@@ -892,10 +892,26 @@
         <v>31420565576</v>
       </c>
       <c r="C29" t="n">
-        <v>70318042166</v>
+        <v>70274068859</v>
       </c>
       <c r="D29" t="n">
-        <v>0.446835045575151</v>
+        <v>0.4471146482074799</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2021-04-09</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>27209131167</v>
+      </c>
+      <c r="C30" t="n">
+        <v>60980906468</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0.4461909922785112</v>
       </c>
     </row>
   </sheetData>

--- a/king_index/output/index.xlsx
+++ b/king_index/output/index.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D30"/>
+  <dimension ref="A1:D31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -914,6 +914,22 @@
         <v>0.4461909922785112</v>
       </c>
     </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2021-04-12</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>29278689529</v>
+      </c>
+      <c r="C31" t="n">
+        <v>66777782156</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0.4384495648657793</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/king_index/output/index.xlsx
+++ b/king_index/output/index.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D31"/>
+  <dimension ref="A1:D32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -930,6 +930,22 @@
         <v>0.4384495648657793</v>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2021-04-13</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>26344677943</v>
+      </c>
+      <c r="C32" t="n">
+        <v>60183313808</v>
+      </c>
+      <c r="D32" t="n">
+        <v>0.4377405675441234</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/king_index/output/index.xlsx
+++ b/king_index/output/index.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D32"/>
+  <dimension ref="A1:D33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -946,6 +946,22 @@
         <v>0.4377405675441234</v>
       </c>
     </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2021-04-14</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>24787762777</v>
+      </c>
+      <c r="C33" t="n">
+        <v>56224723922</v>
+      </c>
+      <c r="D33" t="n">
+        <v>0.4408694440436527</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/king_index/output/index.xlsx
+++ b/king_index/output/index.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D33"/>
+  <dimension ref="A1:D27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -453,513 +453,417 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2021-03-01</t>
+          <t>2021-03-10</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>27735524005</v>
+        <v>26768080114</v>
       </c>
       <c r="C2" t="n">
-        <v>65960299305</v>
+        <v>62242276864</v>
       </c>
       <c r="D2" t="n">
-        <v>0.4204881466160594</v>
+        <v>0.4300626754462811</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2021-03-02</t>
+          <t>2021-03-11</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>30275962974</v>
+        <v>30414794010</v>
       </c>
       <c r="C3" t="n">
-        <v>69588729144</v>
+        <v>66703023106</v>
       </c>
       <c r="D3" t="n">
-        <v>0.4350699221902721</v>
+        <v>0.4559732466947838</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2021-03-03</t>
+          <t>2021-03-12</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>31328612952</v>
+        <v>33515365360</v>
       </c>
       <c r="C4" t="n">
-        <v>70191438422</v>
+        <v>72307731035</v>
       </c>
       <c r="D4" t="n">
-        <v>0.4463309722141371</v>
+        <v>0.4635101237484156</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2021-03-04</t>
+          <t>2021-03-15</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>35737177720</v>
+        <v>34294525399</v>
       </c>
       <c r="C5" t="n">
-        <v>78683500727</v>
+        <v>71819039829</v>
       </c>
       <c r="D5" t="n">
-        <v>0.454188964519939</v>
+        <v>0.4775130032461409</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2021-03-05</t>
+          <t>2021-03-16</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>32013254979</v>
+        <v>29706651386</v>
       </c>
       <c r="C6" t="n">
-        <v>73602803152</v>
+        <v>67143243915</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4349461380280339</v>
+        <v>0.4424369400979068</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2021-03-08</t>
+          <t>2021-03-17</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>33926652652</v>
+        <v>27229816586</v>
       </c>
       <c r="C7" t="n">
-        <v>78913752639</v>
+        <v>62598212217</v>
       </c>
       <c r="D7" t="n">
-        <v>0.4299206604354676</v>
+        <v>0.4349935185306316</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2021-03-09</t>
+          <t>2021-03-18</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>35544287853</v>
+        <v>26457202635</v>
       </c>
       <c r="C8" t="n">
-        <v>82986392531</v>
+        <v>62902087938</v>
       </c>
       <c r="D8" t="n">
-        <v>0.4283146521849621</v>
+        <v>0.420609291397096</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2021-03-10</t>
+          <t>2021-03-19</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>26768080114</v>
+        <v>28142140366</v>
       </c>
       <c r="C9" t="n">
-        <v>62242276864</v>
+        <v>66028104022</v>
       </c>
       <c r="D9" t="n">
-        <v>0.4300626754462811</v>
+        <v>0.426214576093587</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2021-03-11</t>
+          <t>2021-03-22</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>30414794010</v>
+        <v>28955693616</v>
       </c>
       <c r="C10" t="n">
-        <v>66703023106</v>
+        <v>67503414654</v>
       </c>
       <c r="D10" t="n">
-        <v>0.4559732466947838</v>
+        <v>0.4289515391838655</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2021-03-12</t>
+          <t>2021-03-23</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>33515365360</v>
+        <v>29065050246</v>
       </c>
       <c r="C11" t="n">
-        <v>72307731035</v>
+        <v>70391613937</v>
       </c>
       <c r="D11" t="n">
-        <v>0.4635101237484156</v>
+        <v>0.4129050126910432</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2021-03-15</t>
+          <t>2021-03-24</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>34294525399</v>
+        <v>28264580783</v>
       </c>
       <c r="C12" t="n">
-        <v>71819039829</v>
+        <v>67388687603</v>
       </c>
       <c r="D12" t="n">
-        <v>0.4775130032461409</v>
+        <v>0.4194261943415815</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2021-03-16</t>
+          <t>2021-03-25</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>29706651386</v>
+        <v>25646340206</v>
       </c>
       <c r="C13" t="n">
-        <v>67143243915</v>
+        <v>60699839691</v>
       </c>
       <c r="D13" t="n">
-        <v>0.4424369400979068</v>
+        <v>0.4225108391810563</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2021-03-17</t>
+          <t>2021-03-26</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>27229816586</v>
+        <v>25645315345</v>
       </c>
       <c r="C14" t="n">
-        <v>62598212217</v>
+        <v>61377161981</v>
       </c>
       <c r="D14" t="n">
-        <v>0.4349935185306316</v>
+        <v>0.4178315600994846</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2021-03-18</t>
+          <t>2021-03-29</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>26457202635</v>
+        <v>25840927972</v>
       </c>
       <c r="C15" t="n">
-        <v>62902087938</v>
+        <v>63118193430</v>
       </c>
       <c r="D15" t="n">
-        <v>0.420609291397096</v>
+        <v>0.4094053800931165</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2021-03-19</t>
+          <t>2021-03-30</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>28142140366</v>
+        <v>25574432328</v>
       </c>
       <c r="C16" t="n">
-        <v>66028104022</v>
+        <v>62974799316</v>
       </c>
       <c r="D16" t="n">
-        <v>0.426214576093587</v>
+        <v>0.4061058170216718</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2021-03-22</t>
+          <t>2021-03-31</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>28955693616</v>
+        <v>25156623964</v>
       </c>
       <c r="C17" t="n">
-        <v>67503414654</v>
+        <v>59063876194</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4289515391838655</v>
+        <v>0.4259223333289381</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2021-03-23</t>
+          <t>2021-04-01</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>29065050246</v>
+        <v>24247693731</v>
       </c>
       <c r="C18" t="n">
-        <v>70391613937</v>
+        <v>57835629725</v>
       </c>
       <c r="D18" t="n">
-        <v>0.4129050126910432</v>
+        <v>0.4192518322406837</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2021-03-24</t>
+          <t>2021-04-02</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>28264580783</v>
+        <v>23620032307</v>
       </c>
       <c r="C19" t="n">
-        <v>67388687603</v>
+        <v>57817527627</v>
       </c>
       <c r="D19" t="n">
-        <v>0.4194261943415815</v>
+        <v>0.4085271936804466</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2021-03-25</t>
+          <t>2021-04-06</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>25646340206</v>
+        <v>21461794855</v>
       </c>
       <c r="C20" t="n">
-        <v>60699839691</v>
+        <v>54090962340</v>
       </c>
       <c r="D20" t="n">
-        <v>0.4225108391810563</v>
+        <v>0.3967722873942864</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2021-03-26</t>
+          <t>2021-04-07</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>25645315345</v>
+        <v>28017074765</v>
       </c>
       <c r="C21" t="n">
-        <v>61377161981</v>
+        <v>64860913169</v>
       </c>
       <c r="D21" t="n">
-        <v>0.4178315600994846</v>
+        <v>0.4319562182542728</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2021-03-29</t>
+          <t>2021-04-08</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>25840927972</v>
+        <v>31420565576</v>
       </c>
       <c r="C22" t="n">
-        <v>63118193430</v>
+        <v>70274068859</v>
       </c>
       <c r="D22" t="n">
-        <v>0.4094053800931165</v>
+        <v>0.4471146482074799</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2021-03-30</t>
+          <t>2021-04-09</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>25574432328</v>
+        <v>27209131167</v>
       </c>
       <c r="C23" t="n">
-        <v>62974799316</v>
+        <v>60980906468</v>
       </c>
       <c r="D23" t="n">
-        <v>0.4061058170216718</v>
+        <v>0.4461909922785112</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2021-03-31</t>
+          <t>2021-04-12</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>25156623964</v>
+        <v>29278689529</v>
       </c>
       <c r="C24" t="n">
-        <v>59063876194</v>
+        <v>66777782156</v>
       </c>
       <c r="D24" t="n">
-        <v>0.4259223333289381</v>
+        <v>0.4384495648657793</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2021-04-01</t>
+          <t>2021-04-13</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>24247693731</v>
+        <v>26344677943</v>
       </c>
       <c r="C25" t="n">
-        <v>57835629725</v>
+        <v>60183313808</v>
       </c>
       <c r="D25" t="n">
-        <v>0.4192518322406837</v>
+        <v>0.4377405675441234</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2021-04-02</t>
+          <t>2021-04-14</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>23620032307</v>
+        <v>24787762777</v>
       </c>
       <c r="C26" t="n">
-        <v>57817527627</v>
+        <v>56224723922</v>
       </c>
       <c r="D26" t="n">
-        <v>0.4085271936804466</v>
+        <v>0.4408694440436527</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2021-04-06</t>
+          <t>2021-04-15</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>21461794855</v>
+        <v>23506917907</v>
       </c>
       <c r="C27" t="n">
-        <v>54090962340</v>
+        <v>56824659508</v>
       </c>
       <c r="D27" t="n">
-        <v>0.3967722873942864</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>2021-04-07</t>
-        </is>
-      </c>
-      <c r="B28" t="n">
-        <v>28017074765</v>
-      </c>
-      <c r="C28" t="n">
-        <v>64860913169</v>
-      </c>
-      <c r="D28" t="n">
-        <v>0.4319562182542728</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>2021-04-08</t>
-        </is>
-      </c>
-      <c r="B29" t="n">
-        <v>31420565576</v>
-      </c>
-      <c r="C29" t="n">
-        <v>70274068859</v>
-      </c>
-      <c r="D29" t="n">
-        <v>0.4471146482074799</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>2021-04-09</t>
-        </is>
-      </c>
-      <c r="B30" t="n">
-        <v>27209131167</v>
-      </c>
-      <c r="C30" t="n">
-        <v>60980906468</v>
-      </c>
-      <c r="D30" t="n">
-        <v>0.4461909922785112</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>2021-04-12</t>
-        </is>
-      </c>
-      <c r="B31" t="n">
-        <v>29278689529</v>
-      </c>
-      <c r="C31" t="n">
-        <v>66777782156</v>
-      </c>
-      <c r="D31" t="n">
-        <v>0.4384495648657793</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>2021-04-13</t>
-        </is>
-      </c>
-      <c r="B32" t="n">
-        <v>26344677943</v>
-      </c>
-      <c r="C32" t="n">
-        <v>60183313808</v>
-      </c>
-      <c r="D32" t="n">
-        <v>0.4377405675441234</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>2021-04-14</t>
-        </is>
-      </c>
-      <c r="B33" t="n">
-        <v>24787762777</v>
-      </c>
-      <c r="C33" t="n">
-        <v>56224723922</v>
-      </c>
-      <c r="D33" t="n">
-        <v>0.4408694440436527</v>
+        <v>0.4136745932228701</v>
       </c>
     </row>
   </sheetData>

--- a/king_index/output/index.xlsx
+++ b/king_index/output/index.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D27"/>
+  <dimension ref="A1:D28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -866,6 +866,22 @@
         <v>0.4136745932228701</v>
       </c>
     </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2021-04-16</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>22971891384</v>
+      </c>
+      <c r="C28" t="n">
+        <v>60847922090</v>
+      </c>
+      <c r="D28" t="n">
+        <v>0.3775295950126668</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/king_index/output/index.xlsx
+++ b/king_index/output/index.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D28"/>
+  <dimension ref="A1:D30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -882,6 +882,38 @@
         <v>0.3775295950126668</v>
       </c>
     </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2021-04-19</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>26281421095</v>
+      </c>
+      <c r="C29" t="n">
+        <v>68848421506</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0.3817287385842191</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2021-04-20</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>26246288235</v>
+      </c>
+      <c r="C30" t="n">
+        <v>66273319567</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0.396030988133406</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/king_index/output/index.xlsx
+++ b/king_index/output/index.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D30"/>
+  <dimension ref="A1:D31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -914,6 +914,22 @@
         <v>0.396030988133406</v>
       </c>
     </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2021-04-21</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>23805100513</v>
+      </c>
+      <c r="C31" t="n">
+        <v>58839709989</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0.4045754222352613</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/king_index/output/index.xlsx
+++ b/king_index/output/index.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D31"/>
+  <dimension ref="A1:D32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -930,6 +930,22 @@
         <v>0.4045754222352613</v>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2021-04-22</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>23209117307</v>
+      </c>
+      <c r="C32" t="n">
+        <v>57465747375</v>
+      </c>
+      <c r="D32" t="n">
+        <v>0.4038774116265463</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/king_index/output/index.xlsx
+++ b/king_index/output/index.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D32"/>
+  <dimension ref="A1:D28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -453,497 +453,433 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2021-03-10</t>
+          <t>2021-03-17</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>26768080114</v>
+        <v>27229816586</v>
       </c>
       <c r="C2" t="n">
-        <v>62242276864</v>
+        <v>62598212217</v>
       </c>
       <c r="D2" t="n">
-        <v>0.4300626754462811</v>
+        <v>0.4349935185306316</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2021-03-11</t>
+          <t>2021-03-18</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>30414794010</v>
+        <v>26457202635</v>
       </c>
       <c r="C3" t="n">
-        <v>66703023106</v>
+        <v>62902087938</v>
       </c>
       <c r="D3" t="n">
-        <v>0.4559732466947838</v>
+        <v>0.420609291397096</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2021-03-12</t>
+          <t>2021-03-19</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>33515365360</v>
+        <v>28142140366</v>
       </c>
       <c r="C4" t="n">
-        <v>72307731035</v>
+        <v>66028104022</v>
       </c>
       <c r="D4" t="n">
-        <v>0.4635101237484156</v>
+        <v>0.426214576093587</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2021-03-15</t>
+          <t>2021-03-22</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>34294525399</v>
+        <v>28955693616</v>
       </c>
       <c r="C5" t="n">
-        <v>71819039829</v>
+        <v>67503414654</v>
       </c>
       <c r="D5" t="n">
-        <v>0.4775130032461409</v>
+        <v>0.4289515391838655</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2021-03-16</t>
+          <t>2021-03-23</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>29706651386</v>
+        <v>29065050246</v>
       </c>
       <c r="C6" t="n">
-        <v>67143243915</v>
+        <v>70391613937</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4424369400979068</v>
+        <v>0.4129050126910432</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2021-03-17</t>
+          <t>2021-03-24</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>27229816586</v>
+        <v>28264580783</v>
       </c>
       <c r="C7" t="n">
-        <v>62598212217</v>
+        <v>67388687603</v>
       </c>
       <c r="D7" t="n">
-        <v>0.4349935185306316</v>
+        <v>0.4194261943415815</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2021-03-18</t>
+          <t>2021-03-25</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>26457202635</v>
+        <v>25646340206</v>
       </c>
       <c r="C8" t="n">
-        <v>62902087938</v>
+        <v>60699839691</v>
       </c>
       <c r="D8" t="n">
-        <v>0.420609291397096</v>
+        <v>0.4225108391810563</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2021-03-19</t>
+          <t>2021-03-26</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>28142140366</v>
+        <v>25645315345</v>
       </c>
       <c r="C9" t="n">
-        <v>66028104022</v>
+        <v>61377161981</v>
       </c>
       <c r="D9" t="n">
-        <v>0.426214576093587</v>
+        <v>0.4178315600994846</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2021-03-22</t>
+          <t>2021-03-29</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>28955693616</v>
+        <v>25840927972</v>
       </c>
       <c r="C10" t="n">
-        <v>67503414654</v>
+        <v>63118193430</v>
       </c>
       <c r="D10" t="n">
-        <v>0.4289515391838655</v>
+        <v>0.4094053800931165</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2021-03-23</t>
+          <t>2021-03-30</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>29065050246</v>
+        <v>25574432328</v>
       </c>
       <c r="C11" t="n">
-        <v>70391613937</v>
+        <v>62974799316</v>
       </c>
       <c r="D11" t="n">
-        <v>0.4129050126910432</v>
+        <v>0.4061058170216718</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2021-03-24</t>
+          <t>2021-03-31</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>28264580783</v>
+        <v>25156623964</v>
       </c>
       <c r="C12" t="n">
-        <v>67388687603</v>
+        <v>59063876194</v>
       </c>
       <c r="D12" t="n">
-        <v>0.4194261943415815</v>
+        <v>0.4259223333289381</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2021-03-25</t>
+          <t>2021-04-01</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>25646340206</v>
+        <v>24247693731</v>
       </c>
       <c r="C13" t="n">
-        <v>60699839691</v>
+        <v>57835629725</v>
       </c>
       <c r="D13" t="n">
-        <v>0.4225108391810563</v>
+        <v>0.4192518322406837</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2021-03-26</t>
+          <t>2021-04-02</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>25645315345</v>
+        <v>23620032307</v>
       </c>
       <c r="C14" t="n">
-        <v>61377161981</v>
+        <v>57817527627</v>
       </c>
       <c r="D14" t="n">
-        <v>0.4178315600994846</v>
+        <v>0.4085271936804466</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2021-03-29</t>
+          <t>2021-04-06</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>25840927972</v>
+        <v>21461794855</v>
       </c>
       <c r="C15" t="n">
-        <v>63118193430</v>
+        <v>54090962340</v>
       </c>
       <c r="D15" t="n">
-        <v>0.4094053800931165</v>
+        <v>0.3967722873942864</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2021-03-30</t>
+          <t>2021-04-07</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>25574432328</v>
+        <v>28017074765</v>
       </c>
       <c r="C16" t="n">
-        <v>62974799316</v>
+        <v>64860913169</v>
       </c>
       <c r="D16" t="n">
-        <v>0.4061058170216718</v>
+        <v>0.4319562182542728</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2021-03-31</t>
+          <t>2021-04-08</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>25156623964</v>
+        <v>31420565576</v>
       </c>
       <c r="C17" t="n">
-        <v>59063876194</v>
+        <v>70274068859</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4259223333289381</v>
+        <v>0.4471146482074799</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2021-04-01</t>
+          <t>2021-04-09</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>24247693731</v>
+        <v>27209131167</v>
       </c>
       <c r="C18" t="n">
-        <v>57835629725</v>
+        <v>60980906468</v>
       </c>
       <c r="D18" t="n">
-        <v>0.4192518322406837</v>
+        <v>0.4461909922785112</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2021-04-02</t>
+          <t>2021-04-12</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>23620032307</v>
+        <v>29278689529</v>
       </c>
       <c r="C19" t="n">
-        <v>57817527627</v>
+        <v>66777782156</v>
       </c>
       <c r="D19" t="n">
-        <v>0.4085271936804466</v>
+        <v>0.4384495648657793</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2021-04-06</t>
+          <t>2021-04-13</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>21461794855</v>
+        <v>26344677943</v>
       </c>
       <c r="C20" t="n">
-        <v>54090962340</v>
+        <v>60183313808</v>
       </c>
       <c r="D20" t="n">
-        <v>0.3967722873942864</v>
+        <v>0.4377405675441234</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2021-04-07</t>
+          <t>2021-04-14</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>28017074765</v>
+        <v>24787762777</v>
       </c>
       <c r="C21" t="n">
-        <v>64860913169</v>
+        <v>56224723922</v>
       </c>
       <c r="D21" t="n">
-        <v>0.4319562182542728</v>
+        <v>0.4408694440436527</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2021-04-08</t>
+          <t>2021-04-15</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>31420565576</v>
+        <v>23506917907</v>
       </c>
       <c r="C22" t="n">
-        <v>70274068859</v>
+        <v>56824659508</v>
       </c>
       <c r="D22" t="n">
-        <v>0.4471146482074799</v>
+        <v>0.4136745932228701</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2021-04-09</t>
+          <t>2021-04-16</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>27209131167</v>
+        <v>22971891384</v>
       </c>
       <c r="C23" t="n">
-        <v>60980906468</v>
+        <v>60847922090</v>
       </c>
       <c r="D23" t="n">
-        <v>0.4461909922785112</v>
+        <v>0.3775295950126668</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2021-04-12</t>
+          <t>2021-04-19</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>29278689529</v>
+        <v>26281421095</v>
       </c>
       <c r="C24" t="n">
-        <v>66777782156</v>
+        <v>68848421506</v>
       </c>
       <c r="D24" t="n">
-        <v>0.4384495648657793</v>
+        <v>0.3817287385842191</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2021-04-13</t>
+          <t>2021-04-20</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>26344677943</v>
+        <v>26246288235</v>
       </c>
       <c r="C25" t="n">
-        <v>60183313808</v>
+        <v>66273319567</v>
       </c>
       <c r="D25" t="n">
-        <v>0.4377405675441234</v>
+        <v>0.396030988133406</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2021-04-14</t>
+          <t>2021-04-21</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>24787762777</v>
+        <v>23805100513</v>
       </c>
       <c r="C26" t="n">
-        <v>56224723922</v>
+        <v>58839709989</v>
       </c>
       <c r="D26" t="n">
-        <v>0.4408694440436527</v>
+        <v>0.4045754222352613</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2021-04-15</t>
+          <t>2021-04-22</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>23506917907</v>
+        <v>23209117307</v>
       </c>
       <c r="C27" t="n">
-        <v>56824659508</v>
+        <v>57465747375</v>
       </c>
       <c r="D27" t="n">
-        <v>0.4136745932228701</v>
+        <v>0.4038774116265463</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2021-04-16</t>
+          <t>2021-04-23</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>22971891384</v>
+        <v>23040127385</v>
       </c>
       <c r="C28" t="n">
-        <v>60847922090</v>
+        <v>58897298710</v>
       </c>
       <c r="D28" t="n">
-        <v>0.3775295950126668</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>2021-04-19</t>
-        </is>
-      </c>
-      <c r="B29" t="n">
-        <v>26281421095</v>
-      </c>
-      <c r="C29" t="n">
-        <v>68848421506</v>
-      </c>
-      <c r="D29" t="n">
-        <v>0.3817287385842191</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>2021-04-20</t>
-        </is>
-      </c>
-      <c r="B30" t="n">
-        <v>26246288235</v>
-      </c>
-      <c r="C30" t="n">
-        <v>66273319567</v>
-      </c>
-      <c r="D30" t="n">
-        <v>0.396030988133406</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>2021-04-21</t>
-        </is>
-      </c>
-      <c r="B31" t="n">
-        <v>23805100513</v>
-      </c>
-      <c r="C31" t="n">
-        <v>58839709989</v>
-      </c>
-      <c r="D31" t="n">
-        <v>0.4045754222352613</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>2021-04-22</t>
-        </is>
-      </c>
-      <c r="B32" t="n">
-        <v>23209117307</v>
-      </c>
-      <c r="C32" t="n">
-        <v>57465747375</v>
-      </c>
-      <c r="D32" t="n">
-        <v>0.4038774116265463</v>
+        <v>0.3911915807623972</v>
       </c>
     </row>
   </sheetData>

--- a/king_index/output/index.xlsx
+++ b/king_index/output/index.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D28"/>
+  <dimension ref="A1:D23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -453,433 +453,353 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2021-03-17</t>
+          <t>2021-03-25</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>27229816586</v>
+        <v>25646340206</v>
       </c>
       <c r="C2" t="n">
-        <v>62598212217</v>
+        <v>60650573117</v>
       </c>
       <c r="D2" t="n">
-        <v>0.4349935185306316</v>
+        <v>0.4228540455261004</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2021-03-18</t>
+          <t>2021-03-26</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>26457202635</v>
+        <v>25622313889</v>
       </c>
       <c r="C3" t="n">
-        <v>62902087938</v>
+        <v>61294951175</v>
       </c>
       <c r="D3" t="n">
-        <v>0.420609291397096</v>
+        <v>0.4180167109660806</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2021-03-19</t>
+          <t>2021-03-29</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>28142140366</v>
+        <v>25819724731</v>
       </c>
       <c r="C4" t="n">
-        <v>66028104022</v>
+        <v>63039626762</v>
       </c>
       <c r="D4" t="n">
-        <v>0.426214576093587</v>
+        <v>0.4095792766743348</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2021-03-22</t>
+          <t>2021-03-30</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>28955693616</v>
+        <v>25557342000</v>
       </c>
       <c r="C5" t="n">
-        <v>67503414654</v>
+        <v>62900933835</v>
       </c>
       <c r="D5" t="n">
-        <v>0.4289515391838655</v>
+        <v>0.4063110106924854</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2021-03-23</t>
+          <t>2021-03-31</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>29065050246</v>
+        <v>25131445563</v>
       </c>
       <c r="C6" t="n">
-        <v>70391613937</v>
+        <v>58986173387</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4129050126910432</v>
+        <v>0.4260565505430589</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2021-03-24</t>
+          <t>2021-04-01</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>28264580783</v>
+        <v>24246862283</v>
       </c>
       <c r="C7" t="n">
-        <v>67388687603</v>
+        <v>57781184827</v>
       </c>
       <c r="D7" t="n">
-        <v>0.4194261943415815</v>
+        <v>0.4196324868656885</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2021-03-25</t>
+          <t>2021-04-02</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>25646340206</v>
+        <v>23614423639</v>
       </c>
       <c r="C8" t="n">
-        <v>60699839691</v>
+        <v>57759419275</v>
       </c>
       <c r="D8" t="n">
-        <v>0.4225108391810563</v>
+        <v>0.4088410848898723</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2021-03-26</t>
+          <t>2021-04-06</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>25645315345</v>
+        <v>21461794855</v>
       </c>
       <c r="C9" t="n">
-        <v>61377161981</v>
+        <v>54050852058</v>
       </c>
       <c r="D9" t="n">
-        <v>0.4178315600994846</v>
+        <v>0.3970667258301521</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2021-03-29</t>
+          <t>2021-04-07</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>25840927972</v>
+        <v>28017074765</v>
       </c>
       <c r="C10" t="n">
-        <v>63118193430</v>
+        <v>64809152710</v>
       </c>
       <c r="D10" t="n">
-        <v>0.4094053800931165</v>
+        <v>0.4323012042815518</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2021-03-30</t>
+          <t>2021-04-08</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>25574432328</v>
+        <v>31420565576</v>
       </c>
       <c r="C11" t="n">
-        <v>62974799316</v>
+        <v>70235765909</v>
       </c>
       <c r="D11" t="n">
-        <v>0.4061058170216718</v>
+        <v>0.4473584813855326</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2021-03-31</t>
+          <t>2021-04-09</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>25156623964</v>
+        <v>27209131167</v>
       </c>
       <c r="C12" t="n">
-        <v>59063876194</v>
+        <v>60941010440</v>
       </c>
       <c r="D12" t="n">
-        <v>0.4259223333289381</v>
+        <v>0.4464830985004586</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2021-04-01</t>
+          <t>2021-04-12</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>24247693731</v>
+        <v>29275293774</v>
       </c>
       <c r="C13" t="n">
-        <v>57835629725</v>
+        <v>66718307842</v>
       </c>
       <c r="D13" t="n">
-        <v>0.4192518322406837</v>
+        <v>0.4387895125177447</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2021-04-02</t>
+          <t>2021-04-13</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>23620032307</v>
+        <v>26344677943</v>
       </c>
       <c r="C14" t="n">
-        <v>57817527627</v>
+        <v>60133323390</v>
       </c>
       <c r="D14" t="n">
-        <v>0.4085271936804466</v>
+        <v>0.4381044728251465</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2021-04-06</t>
+          <t>2021-04-14</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>21461794855</v>
+        <v>24781421162</v>
       </c>
       <c r="C15" t="n">
-        <v>54090962340</v>
+        <v>56170980073</v>
       </c>
       <c r="D15" t="n">
-        <v>0.3967722873942864</v>
+        <v>0.4411783652304799</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2021-04-07</t>
+          <t>2021-04-15</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>28017074765</v>
+        <v>23433331402</v>
       </c>
       <c r="C16" t="n">
-        <v>64860913169</v>
+        <v>56751073003</v>
       </c>
       <c r="D16" t="n">
-        <v>0.4319562182542728</v>
+        <v>0.412914332047277</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2021-04-08</t>
+          <t>2021-04-16</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>31420565576</v>
+        <v>22954113918</v>
       </c>
       <c r="C17" t="n">
-        <v>70274068859</v>
+        <v>60774922264</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4471146482074799</v>
+        <v>0.3776905516767211</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2021-04-09</t>
+          <t>2021-04-19</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>27209131167</v>
+        <v>26230121790</v>
       </c>
       <c r="C18" t="n">
-        <v>60980906468</v>
+        <v>68737193244</v>
       </c>
       <c r="D18" t="n">
-        <v>0.4461909922785112</v>
+        <v>0.3816001287234637</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2021-04-12</t>
+          <t>2021-04-20</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>29278689529</v>
+        <v>26219403332</v>
       </c>
       <c r="C19" t="n">
-        <v>66777782156</v>
+        <v>66189842295</v>
       </c>
       <c r="D19" t="n">
-        <v>0.4384495648657793</v>
+        <v>0.3961242756123113</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2021-04-13</t>
+          <t>2021-04-21</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>26344677943</v>
+        <v>23695744997</v>
       </c>
       <c r="C20" t="n">
-        <v>60183313808</v>
+        <v>58680000024</v>
       </c>
       <c r="D20" t="n">
-        <v>0.4377405675441234</v>
+        <v>0.4038129684272067</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2021-04-14</t>
+          <t>2021-04-22</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>24787762777</v>
+        <v>23178816248</v>
       </c>
       <c r="C21" t="n">
-        <v>56224723922</v>
+        <v>57382777987</v>
       </c>
       <c r="D21" t="n">
-        <v>0.4408694440436527</v>
+        <v>0.4039333239190883</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2021-04-15</t>
+          <t>2021-04-23</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>23506917907</v>
+        <v>23008974358</v>
       </c>
       <c r="C22" t="n">
-        <v>56824659508</v>
+        <v>58814975695</v>
       </c>
       <c r="D22" t="n">
-        <v>0.4136745932228701</v>
+        <v>0.3912094510982863</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2021-04-16</t>
+          <t>2021-04-26</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>22971891384</v>
+        <v>25964986812</v>
       </c>
       <c r="C23" t="n">
-        <v>60847922090</v>
+        <v>65042511497</v>
       </c>
       <c r="D23" t="n">
-        <v>0.3775295950126668</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>2021-04-19</t>
-        </is>
-      </c>
-      <c r="B24" t="n">
-        <v>26281421095</v>
-      </c>
-      <c r="C24" t="n">
-        <v>68848421506</v>
-      </c>
-      <c r="D24" t="n">
-        <v>0.3817287385842191</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>2021-04-20</t>
-        </is>
-      </c>
-      <c r="B25" t="n">
-        <v>26246288235</v>
-      </c>
-      <c r="C25" t="n">
-        <v>66273319567</v>
-      </c>
-      <c r="D25" t="n">
-        <v>0.396030988133406</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>2021-04-21</t>
-        </is>
-      </c>
-      <c r="B26" t="n">
-        <v>23805100513</v>
-      </c>
-      <c r="C26" t="n">
-        <v>58839709989</v>
-      </c>
-      <c r="D26" t="n">
-        <v>0.4045754222352613</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>2021-04-22</t>
-        </is>
-      </c>
-      <c r="B27" t="n">
-        <v>23209117307</v>
-      </c>
-      <c r="C27" t="n">
-        <v>57465747375</v>
-      </c>
-      <c r="D27" t="n">
-        <v>0.4038774116265463</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>2021-04-23</t>
-        </is>
-      </c>
-      <c r="B28" t="n">
-        <v>23040127385</v>
-      </c>
-      <c r="C28" t="n">
-        <v>58897298710</v>
-      </c>
-      <c r="D28" t="n">
-        <v>0.3911915807623972</v>
+        <v>0.3992002494122264</v>
       </c>
     </row>
   </sheetData>

--- a/king_index/output/index.xlsx
+++ b/king_index/output/index.xlsx
@@ -453,353 +453,353 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2021-03-25</t>
+          <t>2021-03-26</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>25646340206</v>
+        <v>25622313889</v>
       </c>
       <c r="C2" t="n">
-        <v>60650573117</v>
+        <v>61294951175</v>
       </c>
       <c r="D2" t="n">
-        <v>0.4228540455261004</v>
+        <v>0.4180167109660806</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2021-03-26</t>
+          <t>2021-03-29</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>25622313889</v>
+        <v>25819724731</v>
       </c>
       <c r="C3" t="n">
-        <v>61294951175</v>
+        <v>63039626762</v>
       </c>
       <c r="D3" t="n">
-        <v>0.4180167109660806</v>
+        <v>0.4095792766743348</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2021-03-29</t>
+          <t>2021-03-30</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>25819724731</v>
+        <v>25557342000</v>
       </c>
       <c r="C4" t="n">
-        <v>63039626762</v>
+        <v>62900933835</v>
       </c>
       <c r="D4" t="n">
-        <v>0.4095792766743348</v>
+        <v>0.4063110106924854</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2021-03-30</t>
+          <t>2021-03-31</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>25557342000</v>
+        <v>25131445563</v>
       </c>
       <c r="C5" t="n">
-        <v>62900933835</v>
+        <v>58986173387</v>
       </c>
       <c r="D5" t="n">
-        <v>0.4063110106924854</v>
+        <v>0.4260565505430589</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2021-03-31</t>
+          <t>2021-04-01</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>25131445563</v>
+        <v>24246862283</v>
       </c>
       <c r="C6" t="n">
-        <v>58986173387</v>
+        <v>57781184827</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4260565505430589</v>
+        <v>0.4196324868656885</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2021-04-01</t>
+          <t>2021-04-02</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>24246862283</v>
+        <v>23614423639</v>
       </c>
       <c r="C7" t="n">
-        <v>57781184827</v>
+        <v>57759419275</v>
       </c>
       <c r="D7" t="n">
-        <v>0.4196324868656885</v>
+        <v>0.4088410848898723</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2021-04-02</t>
+          <t>2021-04-06</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>23614423639</v>
+        <v>21461794855</v>
       </c>
       <c r="C8" t="n">
-        <v>57759419275</v>
+        <v>54050852058</v>
       </c>
       <c r="D8" t="n">
-        <v>0.4088410848898723</v>
+        <v>0.3970667258301521</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2021-04-06</t>
+          <t>2021-04-07</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>21461794855</v>
+        <v>28017074765</v>
       </c>
       <c r="C9" t="n">
-        <v>54050852058</v>
+        <v>64809152710</v>
       </c>
       <c r="D9" t="n">
-        <v>0.3970667258301521</v>
+        <v>0.4323012042815518</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2021-04-07</t>
+          <t>2021-04-08</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>28017074765</v>
+        <v>31420565576</v>
       </c>
       <c r="C10" t="n">
-        <v>64809152710</v>
+        <v>70235765909</v>
       </c>
       <c r="D10" t="n">
-        <v>0.4323012042815518</v>
+        <v>0.4473584813855326</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2021-04-08</t>
+          <t>2021-04-09</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>31420565576</v>
+        <v>27209131167</v>
       </c>
       <c r="C11" t="n">
-        <v>70235765909</v>
+        <v>60941010440</v>
       </c>
       <c r="D11" t="n">
-        <v>0.4473584813855326</v>
+        <v>0.4464830985004586</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2021-04-09</t>
+          <t>2021-04-12</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>27209131167</v>
+        <v>29275293774</v>
       </c>
       <c r="C12" t="n">
-        <v>60941010440</v>
+        <v>66718307842</v>
       </c>
       <c r="D12" t="n">
-        <v>0.4464830985004586</v>
+        <v>0.4387895125177447</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2021-04-12</t>
+          <t>2021-04-13</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>29275293774</v>
+        <v>26344677943</v>
       </c>
       <c r="C13" t="n">
-        <v>66718307842</v>
+        <v>60133323390</v>
       </c>
       <c r="D13" t="n">
-        <v>0.4387895125177447</v>
+        <v>0.4381044728251465</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2021-04-13</t>
+          <t>2021-04-14</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>26344677943</v>
+        <v>24781421162</v>
       </c>
       <c r="C14" t="n">
-        <v>60133323390</v>
+        <v>56170980073</v>
       </c>
       <c r="D14" t="n">
-        <v>0.4381044728251465</v>
+        <v>0.4411783652304799</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2021-04-14</t>
+          <t>2021-04-15</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>24781421162</v>
+        <v>23433331402</v>
       </c>
       <c r="C15" t="n">
-        <v>56170980073</v>
+        <v>56751073003</v>
       </c>
       <c r="D15" t="n">
-        <v>0.4411783652304799</v>
+        <v>0.412914332047277</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2021-04-15</t>
+          <t>2021-04-16</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>23433331402</v>
+        <v>22954113918</v>
       </c>
       <c r="C16" t="n">
-        <v>56751073003</v>
+        <v>60774922264</v>
       </c>
       <c r="D16" t="n">
-        <v>0.412914332047277</v>
+        <v>0.3776905516767211</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2021-04-16</t>
+          <t>2021-04-19</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>22954113918</v>
+        <v>26230121790</v>
       </c>
       <c r="C17" t="n">
-        <v>60774922264</v>
+        <v>68737193244</v>
       </c>
       <c r="D17" t="n">
-        <v>0.3776905516767211</v>
+        <v>0.3816001287234637</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2021-04-19</t>
+          <t>2021-04-20</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>26230121790</v>
+        <v>26219403332</v>
       </c>
       <c r="C18" t="n">
-        <v>68737193244</v>
+        <v>66189842295</v>
       </c>
       <c r="D18" t="n">
-        <v>0.3816001287234637</v>
+        <v>0.3961242756123113</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2021-04-20</t>
+          <t>2021-04-21</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>26219403332</v>
+        <v>23695744997</v>
       </c>
       <c r="C19" t="n">
-        <v>66189842295</v>
+        <v>58680000024</v>
       </c>
       <c r="D19" t="n">
-        <v>0.3961242756123113</v>
+        <v>0.4038129684272067</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2021-04-21</t>
+          <t>2021-04-22</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>23695744997</v>
+        <v>23178816248</v>
       </c>
       <c r="C20" t="n">
-        <v>58680000024</v>
+        <v>57382777987</v>
       </c>
       <c r="D20" t="n">
-        <v>0.4038129684272067</v>
+        <v>0.4039333239190883</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2021-04-22</t>
+          <t>2021-04-23</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>23178816248</v>
+        <v>23008974358</v>
       </c>
       <c r="C21" t="n">
-        <v>57382777987</v>
+        <v>58814975695</v>
       </c>
       <c r="D21" t="n">
-        <v>0.4039333239190883</v>
+        <v>0.3912094510982863</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2021-04-23</t>
+          <t>2021-04-26</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>23008974358</v>
+        <v>25964986812</v>
       </c>
       <c r="C22" t="n">
-        <v>58814975695</v>
+        <v>65042511497</v>
       </c>
       <c r="D22" t="n">
-        <v>0.3912094510982863</v>
+        <v>0.3992002494122264</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2021-04-26</t>
+          <t>2021-04-27</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>25964986812</v>
+        <v>22708474693</v>
       </c>
       <c r="C23" t="n">
-        <v>65042511497</v>
+        <v>58483193042</v>
       </c>
       <c r="D23" t="n">
-        <v>0.3992002494122264</v>
+        <v>0.3882906098627651</v>
       </c>
     </row>
   </sheetData>

--- a/king_index/output/index.xlsx
+++ b/king_index/output/index.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:D24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -802,6 +802,22 @@
         <v>0.3882906098627651</v>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2021-04-28</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>21663821099</v>
+      </c>
+      <c r="C24" t="n">
+        <v>56230340487</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0.3852692498635767</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/king_index/output/index.xlsx
+++ b/king_index/output/index.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D24"/>
+  <dimension ref="A1:D25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -460,10 +460,10 @@
         <v>25622313889</v>
       </c>
       <c r="C2" t="n">
-        <v>61294951175</v>
+        <v>61294887575</v>
       </c>
       <c r="D2" t="n">
-        <v>0.4180167109660806</v>
+        <v>0.418017144703116</v>
       </c>
     </row>
     <row r="3">
@@ -476,10 +476,10 @@
         <v>25819724731</v>
       </c>
       <c r="C3" t="n">
-        <v>63039626762</v>
+        <v>63039562362</v>
       </c>
       <c r="D3" t="n">
-        <v>0.4095792766743348</v>
+        <v>0.4095796950926174</v>
       </c>
     </row>
     <row r="4">
@@ -492,10 +492,10 @@
         <v>25557342000</v>
       </c>
       <c r="C4" t="n">
-        <v>62900933835</v>
+        <v>62900547135</v>
       </c>
       <c r="D4" t="n">
-        <v>0.4063110106924854</v>
+        <v>0.4063135086114223</v>
       </c>
     </row>
     <row r="5">
@@ -508,10 +508,10 @@
         <v>25131445563</v>
       </c>
       <c r="C5" t="n">
-        <v>58986173387</v>
+        <v>58985778687</v>
       </c>
       <c r="D5" t="n">
-        <v>0.4260565505430589</v>
+        <v>0.4260594014763557</v>
       </c>
     </row>
     <row r="6">
@@ -524,10 +524,10 @@
         <v>24246862283</v>
       </c>
       <c r="C6" t="n">
-        <v>57781184827</v>
+        <v>57779218427</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4196324868656885</v>
+        <v>0.419646768217092</v>
       </c>
     </row>
     <row r="7">
@@ -537,13 +537,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>23614423639</v>
+        <v>23570642397</v>
       </c>
       <c r="C7" t="n">
-        <v>57759419275</v>
+        <v>57663434689</v>
       </c>
       <c r="D7" t="n">
-        <v>0.4088410848898723</v>
+        <v>0.4087623729686776</v>
       </c>
     </row>
     <row r="8">
@@ -556,10 +556,10 @@
         <v>21461794855</v>
       </c>
       <c r="C8" t="n">
-        <v>54050852058</v>
+        <v>54017511005</v>
       </c>
       <c r="D8" t="n">
-        <v>0.3970667258301521</v>
+        <v>0.3973118060366284</v>
       </c>
     </row>
     <row r="9">
@@ -572,10 +572,10 @@
         <v>28017074765</v>
       </c>
       <c r="C9" t="n">
-        <v>64809152710</v>
+        <v>64795802991</v>
       </c>
       <c r="D9" t="n">
-        <v>0.4323012042815518</v>
+        <v>0.4323902702292541</v>
       </c>
     </row>
     <row r="10">
@@ -588,10 +588,10 @@
         <v>31420565576</v>
       </c>
       <c r="C10" t="n">
-        <v>70235765909</v>
+        <v>70220876215</v>
       </c>
       <c r="D10" t="n">
-        <v>0.4473584813855326</v>
+        <v>0.4474533396563941</v>
       </c>
     </row>
     <row r="11">
@@ -604,10 +604,10 @@
         <v>27209131167</v>
       </c>
       <c r="C11" t="n">
-        <v>60941010440</v>
+        <v>60937819633</v>
       </c>
       <c r="D11" t="n">
-        <v>0.4464830985004586</v>
+        <v>0.4465064771084341</v>
       </c>
     </row>
     <row r="12">
@@ -620,10 +620,10 @@
         <v>29275293774</v>
       </c>
       <c r="C12" t="n">
-        <v>66718307842</v>
+        <v>66685356485</v>
       </c>
       <c r="D12" t="n">
-        <v>0.4387895125177447</v>
+        <v>0.4390063323810092</v>
       </c>
     </row>
     <row r="13">
@@ -636,10 +636,10 @@
         <v>26344677943</v>
       </c>
       <c r="C13" t="n">
-        <v>60133323390</v>
+        <v>60118484351</v>
       </c>
       <c r="D13" t="n">
-        <v>0.4381044728251465</v>
+        <v>0.4382126101048618</v>
       </c>
     </row>
     <row r="14">
@@ -649,13 +649,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>24781421162</v>
+        <v>24734018928</v>
       </c>
       <c r="C14" t="n">
-        <v>56170980073</v>
+        <v>56157225324</v>
       </c>
       <c r="D14" t="n">
-        <v>0.4411783652304799</v>
+        <v>0.4404423257256156</v>
       </c>
     </row>
     <row r="15">
@@ -668,10 +668,10 @@
         <v>23433331402</v>
       </c>
       <c r="C15" t="n">
-        <v>56751073003</v>
+        <v>56746035433</v>
       </c>
       <c r="D15" t="n">
-        <v>0.412914332047277</v>
+        <v>0.4129509880856385</v>
       </c>
     </row>
     <row r="16">
@@ -684,10 +684,10 @@
         <v>22954113918</v>
       </c>
       <c r="C16" t="n">
-        <v>60774922264</v>
+        <v>60763502531</v>
       </c>
       <c r="D16" t="n">
-        <v>0.3776905516767211</v>
+        <v>0.3777615338465618</v>
       </c>
     </row>
     <row r="17">
@@ -700,10 +700,10 @@
         <v>26230121790</v>
       </c>
       <c r="C17" t="n">
-        <v>68737193244</v>
+        <v>68724635317</v>
       </c>
       <c r="D17" t="n">
-        <v>0.3816001287234637</v>
+        <v>0.3816698578175156</v>
       </c>
     </row>
     <row r="18">
@@ -716,10 +716,10 @@
         <v>26219403332</v>
       </c>
       <c r="C18" t="n">
-        <v>66189842295</v>
+        <v>66180630909</v>
       </c>
       <c r="D18" t="n">
-        <v>0.3961242756123113</v>
+        <v>0.3961794103784282</v>
       </c>
     </row>
     <row r="19">
@@ -732,10 +732,10 @@
         <v>23695744997</v>
       </c>
       <c r="C19" t="n">
-        <v>58680000024</v>
+        <v>58664329618</v>
       </c>
       <c r="D19" t="n">
-        <v>0.4038129684272067</v>
+        <v>0.4039208348803738</v>
       </c>
     </row>
     <row r="20">
@@ -748,10 +748,10 @@
         <v>23178816248</v>
       </c>
       <c r="C20" t="n">
-        <v>57382777987</v>
+        <v>57369974923</v>
       </c>
       <c r="D20" t="n">
-        <v>0.4039333239190883</v>
+        <v>0.4040234683579661</v>
       </c>
     </row>
     <row r="21">
@@ -764,10 +764,10 @@
         <v>23008974358</v>
       </c>
       <c r="C21" t="n">
-        <v>58814975695</v>
+        <v>58786733784</v>
       </c>
       <c r="D21" t="n">
-        <v>0.3912094510982863</v>
+        <v>0.3913973932034026</v>
       </c>
     </row>
     <row r="22">
@@ -780,10 +780,10 @@
         <v>25964986812</v>
       </c>
       <c r="C22" t="n">
-        <v>65042511497</v>
+        <v>65016231391</v>
       </c>
       <c r="D22" t="n">
-        <v>0.3992002494122264</v>
+        <v>0.3993616095010123</v>
       </c>
     </row>
     <row r="23">
@@ -812,10 +812,26 @@
         <v>21663821099</v>
       </c>
       <c r="C24" t="n">
-        <v>56230340487</v>
+        <v>56280963455</v>
       </c>
       <c r="D24" t="n">
-        <v>0.3852692498635767</v>
+        <v>0.3849227122119457</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2020-12-29</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>28150174336</v>
+      </c>
+      <c r="C25" t="n">
+        <v>68090109927</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0.4134253031193524</v>
       </c>
     </row>
   </sheetData>

--- a/king_index/output/index.xlsx
+++ b/king_index/output/index.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D25"/>
+  <dimension ref="A1:D26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -821,17 +821,33 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2020-12-29</t>
+          <t>2021-04-29</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>28150174336</v>
+        <v>23761905634</v>
       </c>
       <c r="C25" t="n">
-        <v>68090109927</v>
+        <v>59697294098</v>
       </c>
       <c r="D25" t="n">
-        <v>0.4134253031193524</v>
+        <v>0.3980399110718836</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2021-04-30</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>26551609631</v>
+      </c>
+      <c r="C26" t="n">
+        <v>64642069838</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0.4107481350387016</v>
       </c>
     </row>
   </sheetData>

--- a/king_index/output/index.xlsx
+++ b/king_index/output/index.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D26"/>
+  <dimension ref="A1:D46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -453,401 +453,721 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2021-03-26</t>
+          <t>2021-03-01</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>25622313889</v>
+        <v>27680347479</v>
       </c>
       <c r="C2" t="n">
-        <v>61294887575</v>
+        <v>65847760652</v>
       </c>
       <c r="D2" t="n">
-        <v>0.418017144703116</v>
+        <v>0.4203688508905923</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2021-03-29</t>
+          <t>2021-03-02</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>25819724731</v>
+        <v>30189304329</v>
       </c>
       <c r="C3" t="n">
-        <v>63039562362</v>
+        <v>69441386639</v>
       </c>
       <c r="D3" t="n">
-        <v>0.4095796950926174</v>
+        <v>0.4347451252081556</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2021-03-30</t>
+          <t>2021-03-03</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>25557342000</v>
+        <v>31200723147</v>
       </c>
       <c r="C4" t="n">
-        <v>62900547135</v>
+        <v>69999474895</v>
       </c>
       <c r="D4" t="n">
-        <v>0.4063135086114223</v>
+        <v>0.4457279600140063</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2021-03-31</t>
+          <t>2021-03-04</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>25131445563</v>
+        <v>35686000296</v>
       </c>
       <c r="C5" t="n">
-        <v>58985778687</v>
+        <v>78562142790</v>
       </c>
       <c r="D5" t="n">
-        <v>0.4260594014763557</v>
+        <v>0.4542391415085281</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2021-04-01</t>
+          <t>2021-03-05</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>24246862283</v>
+        <v>31925237838</v>
       </c>
       <c r="C6" t="n">
-        <v>57779218427</v>
+        <v>73514786011</v>
       </c>
       <c r="D6" t="n">
-        <v>0.419646768217092</v>
+        <v>0.4342696152747154</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2021-04-02</t>
+          <t>2021-03-08</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>23570642397</v>
+        <v>33896120418</v>
       </c>
       <c r="C7" t="n">
-        <v>57663434689</v>
+        <v>78814375242</v>
       </c>
       <c r="D7" t="n">
-        <v>0.4087623729686776</v>
+        <v>0.4300753550849292</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2021-04-06</t>
+          <t>2021-03-09</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>21461794855</v>
+        <v>35480957371</v>
       </c>
       <c r="C8" t="n">
-        <v>54017511005</v>
+        <v>82850202998</v>
       </c>
       <c r="D8" t="n">
-        <v>0.3973118060366284</v>
+        <v>0.4282543202924501</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2021-04-07</t>
+          <t>2021-03-10</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>28017074765</v>
+        <v>26707850086</v>
       </c>
       <c r="C9" t="n">
-        <v>64795802991</v>
+        <v>62127335207</v>
       </c>
       <c r="D9" t="n">
-        <v>0.4323902702292541</v>
+        <v>0.429888872539165</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2021-04-08</t>
+          <t>2021-03-11</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>31420565576</v>
+        <v>30371987985</v>
       </c>
       <c r="C10" t="n">
-        <v>70220876215</v>
+        <v>66598157167</v>
       </c>
       <c r="D10" t="n">
-        <v>0.4474533396563941</v>
+        <v>0.4560484745672452</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2021-04-09</t>
+          <t>2021-03-12</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>27209131167</v>
+        <v>33515365360</v>
       </c>
       <c r="C11" t="n">
-        <v>60937819633</v>
+        <v>72238010975</v>
       </c>
       <c r="D11" t="n">
-        <v>0.4465064771084341</v>
+        <v>0.4639574776165825</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2021-04-12</t>
+          <t>2021-03-15</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>29275293774</v>
+        <v>34264676450</v>
       </c>
       <c r="C12" t="n">
-        <v>66685356485</v>
+        <v>71723136959</v>
       </c>
       <c r="D12" t="n">
-        <v>0.4390063323810092</v>
+        <v>0.4777353292506872</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2021-04-13</t>
+          <t>2021-03-16</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>26344677943</v>
+        <v>29674407853</v>
       </c>
       <c r="C13" t="n">
-        <v>60118484351</v>
+        <v>67049266583</v>
       </c>
       <c r="D13" t="n">
-        <v>0.4382126101048618</v>
+        <v>0.4425761736896283</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2021-04-14</t>
+          <t>2021-03-17</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>24734018928</v>
+        <v>27205109308</v>
       </c>
       <c r="C14" t="n">
-        <v>56157225324</v>
+        <v>62515062852</v>
       </c>
       <c r="D14" t="n">
-        <v>0.4404423257256156</v>
+        <v>0.4351768688516906</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2021-04-15</t>
+          <t>2021-03-18</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>23433331402</v>
+        <v>26446918115</v>
       </c>
       <c r="C15" t="n">
-        <v>56746035433</v>
+        <v>62832911819</v>
       </c>
       <c r="D15" t="n">
-        <v>0.4129509880856385</v>
+        <v>0.4209086822394046</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2021-04-16</t>
+          <t>2021-03-19</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>22954113918</v>
+        <v>28051529133</v>
       </c>
       <c r="C16" t="n">
-        <v>60763502531</v>
+        <v>65875538395</v>
       </c>
       <c r="D16" t="n">
-        <v>0.3777615338465618</v>
+        <v>0.425826183989551</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2021-04-19</t>
+          <t>2021-03-22</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>26230121790</v>
+        <v>28810574608</v>
       </c>
       <c r="C17" t="n">
-        <v>68724635317</v>
+        <v>67358290346</v>
       </c>
       <c r="D17" t="n">
-        <v>0.3816698578175156</v>
+        <v>0.4277212865707908</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2021-04-20</t>
+          <t>2021-03-23</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>26219403332</v>
+        <v>29061639858</v>
       </c>
       <c r="C18" t="n">
-        <v>66180630909</v>
+        <v>70323215899</v>
       </c>
       <c r="D18" t="n">
-        <v>0.3961794103784282</v>
+        <v>0.4132581180550541</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2021-04-21</t>
+          <t>2021-03-24</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>23695744997</v>
+        <v>28242888090</v>
       </c>
       <c r="C19" t="n">
-        <v>58664329618</v>
+        <v>67303672796</v>
       </c>
       <c r="D19" t="n">
-        <v>0.4039208348803738</v>
+        <v>0.4196336829284974</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2021-04-22</t>
+          <t>2021-03-25</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>23178816248</v>
+        <v>25646340206</v>
       </c>
       <c r="C20" t="n">
-        <v>57369974923</v>
+        <v>60650546817</v>
       </c>
       <c r="D20" t="n">
-        <v>0.4040234683579661</v>
+        <v>0.422854228889021</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2021-04-23</t>
+          <t>2021-03-26</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>23008974358</v>
+        <v>25622313889</v>
       </c>
       <c r="C21" t="n">
-        <v>58786733784</v>
+        <v>61294887575</v>
       </c>
       <c r="D21" t="n">
-        <v>0.3913973932034026</v>
+        <v>0.418017144703116</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2021-04-26</t>
+          <t>2021-03-29</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>25964986812</v>
+        <v>25819724731</v>
       </c>
       <c r="C22" t="n">
-        <v>65016231391</v>
+        <v>63039562362</v>
       </c>
       <c r="D22" t="n">
-        <v>0.3993616095010123</v>
+        <v>0.4095796950926174</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2021-04-27</t>
+          <t>2021-03-30</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>22708474693</v>
+        <v>25557342000</v>
       </c>
       <c r="C23" t="n">
-        <v>58483193042</v>
+        <v>62900547135</v>
       </c>
       <c r="D23" t="n">
-        <v>0.3882906098627651</v>
+        <v>0.4063135086114223</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2021-04-28</t>
+          <t>2021-03-31</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>21663821099</v>
+        <v>25131445563</v>
       </c>
       <c r="C24" t="n">
-        <v>56280963455</v>
+        <v>58985778687</v>
       </c>
       <c r="D24" t="n">
-        <v>0.3849227122119457</v>
+        <v>0.4260594014763557</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2021-04-29</t>
+          <t>2021-04-01</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>23761905634</v>
+        <v>24246862283</v>
       </c>
       <c r="C25" t="n">
-        <v>59697294098</v>
+        <v>57779218427</v>
       </c>
       <c r="D25" t="n">
-        <v>0.3980399110718836</v>
+        <v>0.419646768217092</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
+          <t>2021-04-02</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>23570642397</v>
+      </c>
+      <c r="C26" t="n">
+        <v>57663434689</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0.4087623729686776</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2021-04-06</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>21461794855</v>
+      </c>
+      <c r="C27" t="n">
+        <v>54017511005</v>
+      </c>
+      <c r="D27" t="n">
+        <v>0.3973118060366284</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2021-04-07</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>28017074765</v>
+      </c>
+      <c r="C28" t="n">
+        <v>64795802991</v>
+      </c>
+      <c r="D28" t="n">
+        <v>0.4323902702292541</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2021-04-08</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>31420565576</v>
+      </c>
+      <c r="C29" t="n">
+        <v>70220876215</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0.4474533396563941</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2021-04-09</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>27209131167</v>
+      </c>
+      <c r="C30" t="n">
+        <v>60937819633</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0.4465064771084341</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2021-04-12</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>29275293774</v>
+      </c>
+      <c r="C31" t="n">
+        <v>66685356485</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0.4390063323810092</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2021-04-13</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>26344677943</v>
+      </c>
+      <c r="C32" t="n">
+        <v>60118484351</v>
+      </c>
+      <c r="D32" t="n">
+        <v>0.4382126101048618</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2021-04-14</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>24734018928</v>
+      </c>
+      <c r="C33" t="n">
+        <v>56157225324</v>
+      </c>
+      <c r="D33" t="n">
+        <v>0.4404423257256156</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2021-04-15</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>23433331402</v>
+      </c>
+      <c r="C34" t="n">
+        <v>56746035433</v>
+      </c>
+      <c r="D34" t="n">
+        <v>0.4129509880856385</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2021-04-16</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>22954113918</v>
+      </c>
+      <c r="C35" t="n">
+        <v>60763502531</v>
+      </c>
+      <c r="D35" t="n">
+        <v>0.3777615338465618</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2021-04-19</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>26230121790</v>
+      </c>
+      <c r="C36" t="n">
+        <v>68724635317</v>
+      </c>
+      <c r="D36" t="n">
+        <v>0.3816698578175156</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2021-04-20</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>26219403332</v>
+      </c>
+      <c r="C37" t="n">
+        <v>66180630909</v>
+      </c>
+      <c r="D37" t="n">
+        <v>0.3961794103784282</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2021-04-21</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>23695744997</v>
+      </c>
+      <c r="C38" t="n">
+        <v>58664329618</v>
+      </c>
+      <c r="D38" t="n">
+        <v>0.4039208348803738</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2021-04-22</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>23178816248</v>
+      </c>
+      <c r="C39" t="n">
+        <v>57369974923</v>
+      </c>
+      <c r="D39" t="n">
+        <v>0.4040234683579661</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2021-04-23</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>23008974358</v>
+      </c>
+      <c r="C40" t="n">
+        <v>58786733784</v>
+      </c>
+      <c r="D40" t="n">
+        <v>0.3913973932034026</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2021-04-26</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>25964986812</v>
+      </c>
+      <c r="C41" t="n">
+        <v>65016231391</v>
+      </c>
+      <c r="D41" t="n">
+        <v>0.3993616095010123</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2021-04-27</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>22708474693</v>
+      </c>
+      <c r="C42" t="n">
+        <v>58483193042</v>
+      </c>
+      <c r="D42" t="n">
+        <v>0.3882906098627651</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2021-04-28</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>21663821099</v>
+      </c>
+      <c r="C43" t="n">
+        <v>56280963455</v>
+      </c>
+      <c r="D43" t="n">
+        <v>0.3849227122119457</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2021-04-29</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>23761905634</v>
+      </c>
+      <c r="C44" t="n">
+        <v>59697294098</v>
+      </c>
+      <c r="D44" t="n">
+        <v>0.3980399110718836</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
           <t>2021-04-30</t>
         </is>
       </c>
-      <c r="B26" t="n">
+      <c r="B45" t="n">
         <v>26551609631</v>
       </c>
-      <c r="C26" t="n">
+      <c r="C45" t="n">
         <v>64642069838</v>
       </c>
-      <c r="D26" t="n">
+      <c r="D45" t="n">
         <v>0.4107481350387016</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2021-05-06</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>28186220087</v>
+      </c>
+      <c r="C46" t="n">
+        <v>65018590611</v>
+      </c>
+      <c r="D46" t="n">
+        <v>0.4335101672018001</v>
       </c>
     </row>
   </sheetData>

--- a/king_index/output/index.xlsx
+++ b/king_index/output/index.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D46"/>
+  <dimension ref="A1:D47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -700,10 +700,10 @@
         <v>28810574608</v>
       </c>
       <c r="C17" t="n">
-        <v>67358290346</v>
+        <v>67358226346</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4277212865707908</v>
+        <v>0.4277216929675122</v>
       </c>
     </row>
     <row r="18">
@@ -713,13 +713,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>29061639858</v>
+        <v>28996759908</v>
       </c>
       <c r="C18" t="n">
-        <v>70323215899</v>
+        <v>70323191299</v>
       </c>
       <c r="D18" t="n">
-        <v>0.4132581180550541</v>
+        <v>0.4123356658362052</v>
       </c>
     </row>
     <row r="19">
@@ -732,10 +732,10 @@
         <v>28242888090</v>
       </c>
       <c r="C19" t="n">
-        <v>67303672796</v>
+        <v>67303523996</v>
       </c>
       <c r="D19" t="n">
-        <v>0.4196336829284974</v>
+        <v>0.41963461068812</v>
       </c>
     </row>
     <row r="20">
@@ -748,10 +748,10 @@
         <v>25646340206</v>
       </c>
       <c r="C20" t="n">
-        <v>60650546817</v>
+        <v>60650502617</v>
       </c>
       <c r="D20" t="n">
-        <v>0.422854228889021</v>
+        <v>0.4228545370506373</v>
       </c>
     </row>
     <row r="21">
@@ -764,10 +764,10 @@
         <v>25622313889</v>
       </c>
       <c r="C21" t="n">
-        <v>61294887575</v>
+        <v>61284664475</v>
       </c>
       <c r="D21" t="n">
-        <v>0.418017144703116</v>
+        <v>0.4180868755421215</v>
       </c>
     </row>
     <row r="22">
@@ -777,13 +777,13 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>25819724731</v>
+        <v>25803305477</v>
       </c>
       <c r="C22" t="n">
-        <v>63039562362</v>
+        <v>62965892538</v>
       </c>
       <c r="D22" t="n">
-        <v>0.4095796950926174</v>
+        <v>0.409798137323753</v>
       </c>
     </row>
     <row r="23">
@@ -796,10 +796,10 @@
         <v>25557342000</v>
       </c>
       <c r="C23" t="n">
-        <v>62900547135</v>
+        <v>62868502600</v>
       </c>
       <c r="D23" t="n">
-        <v>0.4063135086114223</v>
+        <v>0.4065206095746903</v>
       </c>
     </row>
     <row r="24">
@@ -812,10 +812,10 @@
         <v>25131445563</v>
       </c>
       <c r="C24" t="n">
-        <v>58985778687</v>
+        <v>58944651908</v>
       </c>
       <c r="D24" t="n">
-        <v>0.4260594014763557</v>
+        <v>0.4263566710381938</v>
       </c>
     </row>
     <row r="25">
@@ -828,10 +828,10 @@
         <v>24246862283</v>
       </c>
       <c r="C25" t="n">
-        <v>57779218427</v>
+        <v>57742915146</v>
       </c>
       <c r="D25" t="n">
-        <v>0.419646768217092</v>
+        <v>0.419910602394996</v>
       </c>
     </row>
     <row r="26">
@@ -844,10 +844,10 @@
         <v>23570642397</v>
       </c>
       <c r="C26" t="n">
-        <v>57663434689</v>
+        <v>57637646459</v>
       </c>
       <c r="D26" t="n">
-        <v>0.4087623729686776</v>
+        <v>0.4089452613886092</v>
       </c>
     </row>
     <row r="27">
@@ -860,10 +860,10 @@
         <v>21461794855</v>
       </c>
       <c r="C27" t="n">
-        <v>54017511005</v>
+        <v>54009467026</v>
       </c>
       <c r="D27" t="n">
-        <v>0.3973118060366284</v>
+        <v>0.3973709802518205</v>
       </c>
     </row>
     <row r="28">
@@ -876,10 +876,10 @@
         <v>28017074765</v>
       </c>
       <c r="C28" t="n">
-        <v>64795802991</v>
+        <v>64777711487</v>
       </c>
       <c r="D28" t="n">
-        <v>0.4323902702292541</v>
+        <v>0.4325110307520302</v>
       </c>
     </row>
     <row r="29">
@@ -892,10 +892,10 @@
         <v>31420565576</v>
       </c>
       <c r="C29" t="n">
-        <v>70220876215</v>
+        <v>70183037971</v>
       </c>
       <c r="D29" t="n">
-        <v>0.4474533396563941</v>
+        <v>0.4476945781256027</v>
       </c>
     </row>
     <row r="30">
@@ -908,10 +908,10 @@
         <v>27209131167</v>
       </c>
       <c r="C30" t="n">
-        <v>60937819633</v>
+        <v>60908586933</v>
       </c>
       <c r="D30" t="n">
-        <v>0.4465064771084341</v>
+        <v>0.4467207751335668</v>
       </c>
     </row>
     <row r="31">
@@ -924,10 +924,10 @@
         <v>29275293774</v>
       </c>
       <c r="C31" t="n">
-        <v>66685356485</v>
+        <v>66662877908</v>
       </c>
       <c r="D31" t="n">
-        <v>0.4390063323810092</v>
+        <v>0.4391543643585595</v>
       </c>
     </row>
     <row r="32">
@@ -940,10 +940,10 @@
         <v>26344677943</v>
       </c>
       <c r="C32" t="n">
-        <v>60118484351</v>
+        <v>60099497250</v>
       </c>
       <c r="D32" t="n">
-        <v>0.4382126101048618</v>
+        <v>0.4383510536437973</v>
       </c>
     </row>
     <row r="33">
@@ -956,10 +956,10 @@
         <v>24734018928</v>
       </c>
       <c r="C33" t="n">
-        <v>56157225324</v>
+        <v>56149660115</v>
       </c>
       <c r="D33" t="n">
-        <v>0.4404423257256156</v>
+        <v>0.4405016678167296</v>
       </c>
     </row>
     <row r="34">
@@ -972,10 +972,10 @@
         <v>23433331402</v>
       </c>
       <c r="C34" t="n">
-        <v>56746035433</v>
+        <v>56730832399</v>
       </c>
       <c r="D34" t="n">
-        <v>0.4129509880856385</v>
+        <v>0.4130616529154447</v>
       </c>
     </row>
     <row r="35">
@@ -988,10 +988,10 @@
         <v>22954113918</v>
       </c>
       <c r="C35" t="n">
-        <v>60763502531</v>
+        <v>60757105467</v>
       </c>
       <c r="D35" t="n">
-        <v>0.3777615338465618</v>
+        <v>0.3778013080374187</v>
       </c>
     </row>
     <row r="36">
@@ -1004,10 +1004,10 @@
         <v>26230121790</v>
       </c>
       <c r="C36" t="n">
-        <v>68724635317</v>
+        <v>68717257011</v>
       </c>
       <c r="D36" t="n">
-        <v>0.3816698578175156</v>
+        <v>0.3817108384550504</v>
       </c>
     </row>
     <row r="37">
@@ -1020,10 +1020,10 @@
         <v>26219403332</v>
       </c>
       <c r="C37" t="n">
-        <v>66180630909</v>
+        <v>66152179163</v>
       </c>
       <c r="D37" t="n">
-        <v>0.3961794103784282</v>
+        <v>0.3963498053086805</v>
       </c>
     </row>
     <row r="38">
@@ -1036,10 +1036,10 @@
         <v>23695744997</v>
       </c>
       <c r="C38" t="n">
-        <v>58664329618</v>
+        <v>58645267418</v>
       </c>
       <c r="D38" t="n">
-        <v>0.4039208348803738</v>
+        <v>0.4040521262884899</v>
       </c>
     </row>
     <row r="39">
@@ -1052,10 +1052,10 @@
         <v>23178816248</v>
       </c>
       <c r="C39" t="n">
-        <v>57369974923</v>
+        <v>57343158813</v>
       </c>
       <c r="D39" t="n">
-        <v>0.4040234683579661</v>
+        <v>0.4042124069862932</v>
       </c>
     </row>
     <row r="40">
@@ -1068,10 +1068,10 @@
         <v>23008974358</v>
       </c>
       <c r="C40" t="n">
-        <v>58786733784</v>
+        <v>58758936747</v>
       </c>
       <c r="D40" t="n">
-        <v>0.3913973932034026</v>
+        <v>0.3915825512137904</v>
       </c>
     </row>
     <row r="41">
@@ -1084,10 +1084,10 @@
         <v>25964986812</v>
       </c>
       <c r="C41" t="n">
-        <v>65016231391</v>
+        <v>64990659217</v>
       </c>
       <c r="D41" t="n">
-        <v>0.3993616095010123</v>
+        <v>0.3995187481527835</v>
       </c>
     </row>
     <row r="42">
@@ -1100,10 +1100,10 @@
         <v>22708474693</v>
       </c>
       <c r="C42" t="n">
-        <v>58483193042</v>
+        <v>58465572266</v>
       </c>
       <c r="D42" t="n">
-        <v>0.3882906098627651</v>
+        <v>0.3884076356882914</v>
       </c>
     </row>
     <row r="43">
@@ -1116,10 +1116,10 @@
         <v>21663821099</v>
       </c>
       <c r="C43" t="n">
-        <v>56280963455</v>
+        <v>56258757783</v>
       </c>
       <c r="D43" t="n">
-        <v>0.3849227122119457</v>
+        <v>0.385074643534811</v>
       </c>
     </row>
     <row r="44">
@@ -1132,10 +1132,10 @@
         <v>23761905634</v>
       </c>
       <c r="C44" t="n">
-        <v>59697294098</v>
+        <v>59672070298</v>
       </c>
       <c r="D44" t="n">
-        <v>0.3980399110718836</v>
+        <v>0.3982081653164364</v>
       </c>
     </row>
     <row r="45">
@@ -1148,10 +1148,10 @@
         <v>26551609631</v>
       </c>
       <c r="C45" t="n">
-        <v>64642069838</v>
+        <v>64623812735</v>
       </c>
       <c r="D45" t="n">
-        <v>0.4107481350387016</v>
+        <v>0.4108641769540743</v>
       </c>
     </row>
     <row r="46">
@@ -1164,10 +1164,26 @@
         <v>28186220087</v>
       </c>
       <c r="C46" t="n">
-        <v>65018590611</v>
+        <v>64995398044</v>
       </c>
       <c r="D46" t="n">
-        <v>0.4335101672018001</v>
+        <v>0.4336648583630298</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2021-05-07</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>33739236877</v>
+      </c>
+      <c r="C47" t="n">
+        <v>72689004129</v>
+      </c>
+      <c r="D47" t="n">
+        <v>0.4641587442458769</v>
       </c>
     </row>
   </sheetData>

--- a/king_index/output/index.xlsx
+++ b/king_index/output/index.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D47"/>
+  <dimension ref="A1:E47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -449,6 +449,11 @@
           <t>指标</t>
         </is>
       </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -465,6 +470,9 @@
       <c r="D2" t="n">
         <v>0.4203688508905923</v>
       </c>
+      <c r="E2" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -481,6 +489,9 @@
       <c r="D3" t="n">
         <v>0.4347451252081556</v>
       </c>
+      <c r="E3" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -497,6 +508,9 @@
       <c r="D4" t="n">
         <v>0.4457279600140063</v>
       </c>
+      <c r="E4" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -513,6 +527,9 @@
       <c r="D5" t="n">
         <v>0.4542391415085281</v>
       </c>
+      <c r="E5" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -529,6 +546,9 @@
       <c r="D6" t="n">
         <v>0.4342696152747154</v>
       </c>
+      <c r="E6" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -545,6 +565,9 @@
       <c r="D7" t="n">
         <v>0.4300753550849292</v>
       </c>
+      <c r="E7" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -561,6 +584,9 @@
       <c r="D8" t="n">
         <v>0.4282543202924501</v>
       </c>
+      <c r="E8" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -577,6 +603,9 @@
       <c r="D9" t="n">
         <v>0.429888872539165</v>
       </c>
+      <c r="E9" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -593,6 +622,9 @@
       <c r="D10" t="n">
         <v>0.4560484745672452</v>
       </c>
+      <c r="E10" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -609,6 +641,9 @@
       <c r="D11" t="n">
         <v>0.4639574776165825</v>
       </c>
+      <c r="E11" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -625,6 +660,9 @@
       <c r="D12" t="n">
         <v>0.4777353292506872</v>
       </c>
+      <c r="E12" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -641,6 +679,9 @@
       <c r="D13" t="n">
         <v>0.4425761736896283</v>
       </c>
+      <c r="E13" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -657,6 +698,9 @@
       <c r="D14" t="n">
         <v>0.4351768688516906</v>
       </c>
+      <c r="E14" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -673,6 +717,9 @@
       <c r="D15" t="n">
         <v>0.4209086822394046</v>
       </c>
+      <c r="E15" t="n">
+        <v>14</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -689,6 +736,9 @@
       <c r="D16" t="n">
         <v>0.425826183989551</v>
       </c>
+      <c r="E16" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -705,6 +755,9 @@
       <c r="D17" t="n">
         <v>0.4277216929675122</v>
       </c>
+      <c r="E17" t="n">
+        <v>16</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -721,6 +774,9 @@
       <c r="D18" t="n">
         <v>0.4123356658362052</v>
       </c>
+      <c r="E18" t="n">
+        <v>17</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -737,6 +793,9 @@
       <c r="D19" t="n">
         <v>0.41963461068812</v>
       </c>
+      <c r="E19" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -753,6 +812,9 @@
       <c r="D20" t="n">
         <v>0.4228545370506373</v>
       </c>
+      <c r="E20" t="n">
+        <v>19</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -769,6 +831,9 @@
       <c r="D21" t="n">
         <v>0.4180868755421215</v>
       </c>
+      <c r="E21" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -785,6 +850,9 @@
       <c r="D22" t="n">
         <v>0.409798137323753</v>
       </c>
+      <c r="E22" t="n">
+        <v>21</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -801,6 +869,9 @@
       <c r="D23" t="n">
         <v>0.4065206095746903</v>
       </c>
+      <c r="E23" t="n">
+        <v>22</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -817,6 +888,9 @@
       <c r="D24" t="n">
         <v>0.4263566710381938</v>
       </c>
+      <c r="E24" t="n">
+        <v>23</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -833,6 +907,9 @@
       <c r="D25" t="n">
         <v>0.419910602394996</v>
       </c>
+      <c r="E25" t="n">
+        <v>24</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -849,6 +926,9 @@
       <c r="D26" t="n">
         <v>0.4089452613886092</v>
       </c>
+      <c r="E26" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -865,6 +945,9 @@
       <c r="D27" t="n">
         <v>0.3973709802518205</v>
       </c>
+      <c r="E27" t="n">
+        <v>26</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -881,6 +964,9 @@
       <c r="D28" t="n">
         <v>0.4325110307520302</v>
       </c>
+      <c r="E28" t="n">
+        <v>27</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -897,6 +983,9 @@
       <c r="D29" t="n">
         <v>0.4476945781256027</v>
       </c>
+      <c r="E29" t="n">
+        <v>28</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -913,6 +1002,9 @@
       <c r="D30" t="n">
         <v>0.4467207751335668</v>
       </c>
+      <c r="E30" t="n">
+        <v>29</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -929,6 +1021,9 @@
       <c r="D31" t="n">
         <v>0.4391543643585595</v>
       </c>
+      <c r="E31" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -945,6 +1040,9 @@
       <c r="D32" t="n">
         <v>0.4383510536437973</v>
       </c>
+      <c r="E32" t="n">
+        <v>31</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -961,6 +1059,9 @@
       <c r="D33" t="n">
         <v>0.4405016678167296</v>
       </c>
+      <c r="E33" t="n">
+        <v>32</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -977,6 +1078,9 @@
       <c r="D34" t="n">
         <v>0.4130616529154447</v>
       </c>
+      <c r="E34" t="n">
+        <v>33</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -993,6 +1097,9 @@
       <c r="D35" t="n">
         <v>0.3778013080374187</v>
       </c>
+      <c r="E35" t="n">
+        <v>34</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1009,6 +1116,9 @@
       <c r="D36" t="n">
         <v>0.3817108384550504</v>
       </c>
+      <c r="E36" t="n">
+        <v>35</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1025,6 +1135,9 @@
       <c r="D37" t="n">
         <v>0.3963498053086805</v>
       </c>
+      <c r="E37" t="n">
+        <v>36</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1041,6 +1154,9 @@
       <c r="D38" t="n">
         <v>0.4040521262884899</v>
       </c>
+      <c r="E38" t="n">
+        <v>37</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1057,6 +1173,9 @@
       <c r="D39" t="n">
         <v>0.4042124069862932</v>
       </c>
+      <c r="E39" t="n">
+        <v>38</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1073,6 +1192,9 @@
       <c r="D40" t="n">
         <v>0.3915825512137904</v>
       </c>
+      <c r="E40" t="n">
+        <v>39</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1089,6 +1211,9 @@
       <c r="D41" t="n">
         <v>0.3995187481527835</v>
       </c>
+      <c r="E41" t="n">
+        <v>40</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1105,6 +1230,9 @@
       <c r="D42" t="n">
         <v>0.3884076356882914</v>
       </c>
+      <c r="E42" t="n">
+        <v>41</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1121,6 +1249,9 @@
       <c r="D43" t="n">
         <v>0.385074643534811</v>
       </c>
+      <c r="E43" t="n">
+        <v>42</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1137,6 +1268,9 @@
       <c r="D44" t="n">
         <v>0.3982081653164364</v>
       </c>
+      <c r="E44" t="n">
+        <v>43</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1153,6 +1287,9 @@
       <c r="D45" t="n">
         <v>0.4108641769540743</v>
       </c>
+      <c r="E45" t="n">
+        <v>44</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1169,6 +1306,9 @@
       <c r="D46" t="n">
         <v>0.4336648583630298</v>
       </c>
+      <c r="E46" t="n">
+        <v>45</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1184,6 +1324,9 @@
       </c>
       <c r="D47" t="n">
         <v>0.4641587442458769</v>
+      </c>
+      <c r="E47" t="n">
+        <v>46</v>
       </c>
     </row>
   </sheetData>

--- a/king_index/output/index.xlsx
+++ b/king_index/output/index.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E47"/>
+  <dimension ref="A1:E53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -458,17 +458,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2021-03-01</t>
+          <t>2021-02-22</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>27680347479</v>
+        <v>41263114607</v>
       </c>
       <c r="C2" t="n">
-        <v>65847760652</v>
+        <v>98345390597</v>
       </c>
       <c r="D2" t="n">
-        <v>0.4203688508905923</v>
+        <v>0.4195734477896183</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>
@@ -477,17 +477,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2021-03-02</t>
+          <t>2021-02-23</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>30189304329</v>
+        <v>36231161554</v>
       </c>
       <c r="C3" t="n">
-        <v>69441386639</v>
+        <v>79667225639</v>
       </c>
       <c r="D3" t="n">
-        <v>0.4347451252081556</v>
+        <v>0.4547812637304082</v>
       </c>
       <c r="E3" t="n">
         <v>2</v>
@@ -496,17 +496,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2021-03-03</t>
+          <t>2021-02-24</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>31200723147</v>
+        <v>32924792479</v>
       </c>
       <c r="C4" t="n">
-        <v>69999474895</v>
+        <v>74974298826</v>
       </c>
       <c r="D4" t="n">
-        <v>0.4457279600140063</v>
+        <v>0.4391477212132614</v>
       </c>
       <c r="E4" t="n">
         <v>3</v>
@@ -515,17 +515,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2021-03-04</t>
+          <t>2021-02-25</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>35686000296</v>
+        <v>32621098782</v>
       </c>
       <c r="C5" t="n">
-        <v>78562142790</v>
+        <v>72321851390</v>
       </c>
       <c r="D5" t="n">
-        <v>0.4542391415085281</v>
+        <v>0.4510545313074016</v>
       </c>
       <c r="E5" t="n">
         <v>4</v>
@@ -534,17 +534,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2021-03-05</t>
+          <t>2021-02-26</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>31925237838</v>
+        <v>29077783331</v>
       </c>
       <c r="C6" t="n">
-        <v>73514786011</v>
+        <v>67566280430</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4342696152747154</v>
+        <v>0.4303593914885571</v>
       </c>
       <c r="E6" t="n">
         <v>5</v>
@@ -553,17 +553,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2021-03-08</t>
+          <t>2021-03-01</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>33896120418</v>
+        <v>27680347479</v>
       </c>
       <c r="C7" t="n">
-        <v>78814375242</v>
+        <v>65847760652</v>
       </c>
       <c r="D7" t="n">
-        <v>0.4300753550849292</v>
+        <v>0.4203688508905923</v>
       </c>
       <c r="E7" t="n">
         <v>6</v>
@@ -572,17 +572,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2021-03-09</t>
+          <t>2021-03-02</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>35480957371</v>
+        <v>30189304329</v>
       </c>
       <c r="C8" t="n">
-        <v>82850202998</v>
+        <v>69441386639</v>
       </c>
       <c r="D8" t="n">
-        <v>0.4282543202924501</v>
+        <v>0.4347451252081556</v>
       </c>
       <c r="E8" t="n">
         <v>7</v>
@@ -591,17 +591,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2021-03-10</t>
+          <t>2021-03-03</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>26707850086</v>
+        <v>31200723147</v>
       </c>
       <c r="C9" t="n">
-        <v>62127335207</v>
+        <v>69999474895</v>
       </c>
       <c r="D9" t="n">
-        <v>0.429888872539165</v>
+        <v>0.4457279600140063</v>
       </c>
       <c r="E9" t="n">
         <v>8</v>
@@ -610,17 +610,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2021-03-11</t>
+          <t>2021-03-04</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>30371987985</v>
+        <v>35686000296</v>
       </c>
       <c r="C10" t="n">
-        <v>66598157167</v>
+        <v>78562142790</v>
       </c>
       <c r="D10" t="n">
-        <v>0.4560484745672452</v>
+        <v>0.4542391415085281</v>
       </c>
       <c r="E10" t="n">
         <v>9</v>
@@ -629,17 +629,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2021-03-12</t>
+          <t>2021-03-05</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>33515365360</v>
+        <v>31925237838</v>
       </c>
       <c r="C11" t="n">
-        <v>72238010975</v>
+        <v>73514786011</v>
       </c>
       <c r="D11" t="n">
-        <v>0.4639574776165825</v>
+        <v>0.4342696152747154</v>
       </c>
       <c r="E11" t="n">
         <v>10</v>
@@ -648,17 +648,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2021-03-15</t>
+          <t>2021-03-08</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>34264676450</v>
+        <v>33896120418</v>
       </c>
       <c r="C12" t="n">
-        <v>71723136959</v>
+        <v>78814375242</v>
       </c>
       <c r="D12" t="n">
-        <v>0.4777353292506872</v>
+        <v>0.4300753550849292</v>
       </c>
       <c r="E12" t="n">
         <v>11</v>
@@ -667,17 +667,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2021-03-16</t>
+          <t>2021-03-09</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>29674407853</v>
+        <v>35480957371</v>
       </c>
       <c r="C13" t="n">
-        <v>67049266583</v>
+        <v>82850202998</v>
       </c>
       <c r="D13" t="n">
-        <v>0.4425761736896283</v>
+        <v>0.4282543202924501</v>
       </c>
       <c r="E13" t="n">
         <v>12</v>
@@ -686,17 +686,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2021-03-17</t>
+          <t>2021-03-10</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>27205109308</v>
+        <v>26707850086</v>
       </c>
       <c r="C14" t="n">
-        <v>62515062852</v>
+        <v>62127335207</v>
       </c>
       <c r="D14" t="n">
-        <v>0.4351768688516906</v>
+        <v>0.429888872539165</v>
       </c>
       <c r="E14" t="n">
         <v>13</v>
@@ -705,17 +705,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2021-03-18</t>
+          <t>2021-03-11</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>26446918115</v>
+        <v>30371987985</v>
       </c>
       <c r="C15" t="n">
-        <v>62832911819</v>
+        <v>66598157167</v>
       </c>
       <c r="D15" t="n">
-        <v>0.4209086822394046</v>
+        <v>0.4560484745672452</v>
       </c>
       <c r="E15" t="n">
         <v>14</v>
@@ -724,17 +724,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2021-03-19</t>
+          <t>2021-03-12</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>28051529133</v>
+        <v>33515365360</v>
       </c>
       <c r="C16" t="n">
-        <v>65875538395</v>
+        <v>72238010975</v>
       </c>
       <c r="D16" t="n">
-        <v>0.425826183989551</v>
+        <v>0.4639574776165825</v>
       </c>
       <c r="E16" t="n">
         <v>15</v>
@@ -743,17 +743,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2021-03-22</t>
+          <t>2021-03-15</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>28810574608</v>
+        <v>34264676450</v>
       </c>
       <c r="C17" t="n">
-        <v>67358226346</v>
+        <v>71723136959</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4277216929675122</v>
+        <v>0.4777353292506872</v>
       </c>
       <c r="E17" t="n">
         <v>16</v>
@@ -762,17 +762,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2021-03-23</t>
+          <t>2021-03-16</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>28996759908</v>
+        <v>29674407853</v>
       </c>
       <c r="C18" t="n">
-        <v>70323191299</v>
+        <v>67049266583</v>
       </c>
       <c r="D18" t="n">
-        <v>0.4123356658362052</v>
+        <v>0.4425761736896283</v>
       </c>
       <c r="E18" t="n">
         <v>17</v>
@@ -781,17 +781,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2021-03-24</t>
+          <t>2021-03-17</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>28242888090</v>
+        <v>27205109308</v>
       </c>
       <c r="C19" t="n">
-        <v>67303523996</v>
+        <v>62515062852</v>
       </c>
       <c r="D19" t="n">
-        <v>0.41963461068812</v>
+        <v>0.4351768688516906</v>
       </c>
       <c r="E19" t="n">
         <v>18</v>
@@ -800,17 +800,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2021-03-25</t>
+          <t>2021-03-18</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>25646340206</v>
+        <v>26446918115</v>
       </c>
       <c r="C20" t="n">
-        <v>60650502617</v>
+        <v>62832911819</v>
       </c>
       <c r="D20" t="n">
-        <v>0.4228545370506373</v>
+        <v>0.4209086822394046</v>
       </c>
       <c r="E20" t="n">
         <v>19</v>
@@ -819,17 +819,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2021-03-26</t>
+          <t>2021-03-19</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>25622313889</v>
+        <v>28051529133</v>
       </c>
       <c r="C21" t="n">
-        <v>61284664475</v>
+        <v>65875538395</v>
       </c>
       <c r="D21" t="n">
-        <v>0.4180868755421215</v>
+        <v>0.425826183989551</v>
       </c>
       <c r="E21" t="n">
         <v>20</v>
@@ -838,17 +838,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2021-03-29</t>
+          <t>2021-03-22</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>25803305477</v>
+        <v>28810574608</v>
       </c>
       <c r="C22" t="n">
-        <v>62965892538</v>
+        <v>67358226346</v>
       </c>
       <c r="D22" t="n">
-        <v>0.409798137323753</v>
+        <v>0.4277216929675122</v>
       </c>
       <c r="E22" t="n">
         <v>21</v>
@@ -857,17 +857,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2021-03-30</t>
+          <t>2021-03-23</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>25557342000</v>
+        <v>28996759908</v>
       </c>
       <c r="C23" t="n">
-        <v>62868502600</v>
+        <v>70323191299</v>
       </c>
       <c r="D23" t="n">
-        <v>0.4065206095746903</v>
+        <v>0.4123356658362052</v>
       </c>
       <c r="E23" t="n">
         <v>22</v>
@@ -876,17 +876,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2021-03-31</t>
+          <t>2021-03-24</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>25131445563</v>
+        <v>28242888090</v>
       </c>
       <c r="C24" t="n">
-        <v>58944651908</v>
+        <v>67303523996</v>
       </c>
       <c r="D24" t="n">
-        <v>0.4263566710381938</v>
+        <v>0.41963461068812</v>
       </c>
       <c r="E24" t="n">
         <v>23</v>
@@ -895,17 +895,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2021-04-01</t>
+          <t>2021-03-25</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>24246862283</v>
+        <v>25646340206</v>
       </c>
       <c r="C25" t="n">
-        <v>57742915146</v>
+        <v>60650502617</v>
       </c>
       <c r="D25" t="n">
-        <v>0.419910602394996</v>
+        <v>0.4228545370506373</v>
       </c>
       <c r="E25" t="n">
         <v>24</v>
@@ -914,17 +914,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2021-04-02</t>
+          <t>2021-03-26</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>23570642397</v>
+        <v>25622313889</v>
       </c>
       <c r="C26" t="n">
-        <v>57637646459</v>
+        <v>61284664475</v>
       </c>
       <c r="D26" t="n">
-        <v>0.4089452613886092</v>
+        <v>0.4180868755421215</v>
       </c>
       <c r="E26" t="n">
         <v>25</v>
@@ -933,17 +933,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2021-04-06</t>
+          <t>2021-03-29</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>21461794855</v>
+        <v>25803305477</v>
       </c>
       <c r="C27" t="n">
-        <v>54009467026</v>
+        <v>62965892538</v>
       </c>
       <c r="D27" t="n">
-        <v>0.3973709802518205</v>
+        <v>0.409798137323753</v>
       </c>
       <c r="E27" t="n">
         <v>26</v>
@@ -952,17 +952,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2021-04-07</t>
+          <t>2021-03-30</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>28017074765</v>
+        <v>25557342000</v>
       </c>
       <c r="C28" t="n">
-        <v>64777711487</v>
+        <v>62868502600</v>
       </c>
       <c r="D28" t="n">
-        <v>0.4325110307520302</v>
+        <v>0.4065206095746903</v>
       </c>
       <c r="E28" t="n">
         <v>27</v>
@@ -971,17 +971,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2021-04-08</t>
+          <t>2021-03-31</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>31420565576</v>
+        <v>25131445563</v>
       </c>
       <c r="C29" t="n">
-        <v>70183037971</v>
+        <v>58944651908</v>
       </c>
       <c r="D29" t="n">
-        <v>0.4476945781256027</v>
+        <v>0.4263566710381938</v>
       </c>
       <c r="E29" t="n">
         <v>28</v>
@@ -990,17 +990,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2021-04-09</t>
+          <t>2021-04-01</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>27209131167</v>
+        <v>24246862283</v>
       </c>
       <c r="C30" t="n">
-        <v>60908586933</v>
+        <v>57742915146</v>
       </c>
       <c r="D30" t="n">
-        <v>0.4467207751335668</v>
+        <v>0.419910602394996</v>
       </c>
       <c r="E30" t="n">
         <v>29</v>
@@ -1009,17 +1009,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2021-04-12</t>
+          <t>2021-04-02</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>29275293774</v>
+        <v>23570642397</v>
       </c>
       <c r="C31" t="n">
-        <v>66662877908</v>
+        <v>57637646459</v>
       </c>
       <c r="D31" t="n">
-        <v>0.4391543643585595</v>
+        <v>0.4089452613886092</v>
       </c>
       <c r="E31" t="n">
         <v>30</v>
@@ -1028,17 +1028,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2021-04-13</t>
+          <t>2021-04-06</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>26344677943</v>
+        <v>21461794855</v>
       </c>
       <c r="C32" t="n">
-        <v>60099497250</v>
+        <v>54009467026</v>
       </c>
       <c r="D32" t="n">
-        <v>0.4383510536437973</v>
+        <v>0.3973709802518205</v>
       </c>
       <c r="E32" t="n">
         <v>31</v>
@@ -1047,17 +1047,17 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2021-04-14</t>
+          <t>2021-04-07</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>24734018928</v>
+        <v>28017074765</v>
       </c>
       <c r="C33" t="n">
-        <v>56149660115</v>
+        <v>64777711487</v>
       </c>
       <c r="D33" t="n">
-        <v>0.4405016678167296</v>
+        <v>0.4325110307520302</v>
       </c>
       <c r="E33" t="n">
         <v>32</v>
@@ -1066,17 +1066,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2021-04-15</t>
+          <t>2021-04-08</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>23433331402</v>
+        <v>31420565576</v>
       </c>
       <c r="C34" t="n">
-        <v>56730832399</v>
+        <v>70183037971</v>
       </c>
       <c r="D34" t="n">
-        <v>0.4130616529154447</v>
+        <v>0.4476945781256027</v>
       </c>
       <c r="E34" t="n">
         <v>33</v>
@@ -1085,17 +1085,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2021-04-16</t>
+          <t>2021-04-09</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>22954113918</v>
+        <v>27209131167</v>
       </c>
       <c r="C35" t="n">
-        <v>60757105467</v>
+        <v>60908586933</v>
       </c>
       <c r="D35" t="n">
-        <v>0.3778013080374187</v>
+        <v>0.4467207751335668</v>
       </c>
       <c r="E35" t="n">
         <v>34</v>
@@ -1104,17 +1104,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2021-04-19</t>
+          <t>2021-04-12</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>26230121790</v>
+        <v>29275293774</v>
       </c>
       <c r="C36" t="n">
-        <v>68717257011</v>
+        <v>66662877908</v>
       </c>
       <c r="D36" t="n">
-        <v>0.3817108384550504</v>
+        <v>0.4391543643585595</v>
       </c>
       <c r="E36" t="n">
         <v>35</v>
@@ -1123,17 +1123,17 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2021-04-20</t>
+          <t>2021-04-13</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>26219403332</v>
+        <v>26344677943</v>
       </c>
       <c r="C37" t="n">
-        <v>66152179163</v>
+        <v>60099497250</v>
       </c>
       <c r="D37" t="n">
-        <v>0.3963498053086805</v>
+        <v>0.4383510536437973</v>
       </c>
       <c r="E37" t="n">
         <v>36</v>
@@ -1142,17 +1142,17 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2021-04-21</t>
+          <t>2021-04-14</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>23695744997</v>
+        <v>24734018928</v>
       </c>
       <c r="C38" t="n">
-        <v>58645267418</v>
+        <v>56149660115</v>
       </c>
       <c r="D38" t="n">
-        <v>0.4040521262884899</v>
+        <v>0.4405016678167296</v>
       </c>
       <c r="E38" t="n">
         <v>37</v>
@@ -1161,17 +1161,17 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2021-04-22</t>
+          <t>2021-04-15</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>23178816248</v>
+        <v>23433331402</v>
       </c>
       <c r="C39" t="n">
-        <v>57343158813</v>
+        <v>56730832399</v>
       </c>
       <c r="D39" t="n">
-        <v>0.4042124069862932</v>
+        <v>0.4130616529154447</v>
       </c>
       <c r="E39" t="n">
         <v>38</v>
@@ -1180,17 +1180,17 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2021-04-23</t>
+          <t>2021-04-16</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>23008974358</v>
+        <v>22954113918</v>
       </c>
       <c r="C40" t="n">
-        <v>58758936747</v>
+        <v>60757105467</v>
       </c>
       <c r="D40" t="n">
-        <v>0.3915825512137904</v>
+        <v>0.3778013080374187</v>
       </c>
       <c r="E40" t="n">
         <v>39</v>
@@ -1199,17 +1199,17 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2021-04-26</t>
+          <t>2021-04-19</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>25964986812</v>
+        <v>26230121790</v>
       </c>
       <c r="C41" t="n">
-        <v>64990659217</v>
+        <v>68717257011</v>
       </c>
       <c r="D41" t="n">
-        <v>0.3995187481527835</v>
+        <v>0.3817108384550504</v>
       </c>
       <c r="E41" t="n">
         <v>40</v>
@@ -1218,17 +1218,17 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2021-04-27</t>
+          <t>2021-04-20</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>22708474693</v>
+        <v>26219403332</v>
       </c>
       <c r="C42" t="n">
-        <v>58465572266</v>
+        <v>66152179163</v>
       </c>
       <c r="D42" t="n">
-        <v>0.3884076356882914</v>
+        <v>0.3963498053086805</v>
       </c>
       <c r="E42" t="n">
         <v>41</v>
@@ -1237,17 +1237,17 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2021-04-28</t>
+          <t>2021-04-21</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>21663821099</v>
+        <v>23695744997</v>
       </c>
       <c r="C43" t="n">
-        <v>56258757783</v>
+        <v>58645267418</v>
       </c>
       <c r="D43" t="n">
-        <v>0.385074643534811</v>
+        <v>0.4040521262884899</v>
       </c>
       <c r="E43" t="n">
         <v>42</v>
@@ -1256,17 +1256,17 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2021-04-29</t>
+          <t>2021-04-22</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>23761905634</v>
+        <v>23178816248</v>
       </c>
       <c r="C44" t="n">
-        <v>59672070298</v>
+        <v>57343158813</v>
       </c>
       <c r="D44" t="n">
-        <v>0.3982081653164364</v>
+        <v>0.4042124069862932</v>
       </c>
       <c r="E44" t="n">
         <v>43</v>
@@ -1275,17 +1275,17 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2021-04-30</t>
+          <t>2021-04-23</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>26551609631</v>
+        <v>23008974358</v>
       </c>
       <c r="C45" t="n">
-        <v>64623812735</v>
+        <v>58758936747</v>
       </c>
       <c r="D45" t="n">
-        <v>0.4108641769540743</v>
+        <v>0.3915825512137904</v>
       </c>
       <c r="E45" t="n">
         <v>44</v>
@@ -1294,17 +1294,17 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2021-05-06</t>
+          <t>2021-04-26</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>28186220087</v>
+        <v>25964986812</v>
       </c>
       <c r="C46" t="n">
-        <v>64995398044</v>
+        <v>64990659217</v>
       </c>
       <c r="D46" t="n">
-        <v>0.4336648583630298</v>
+        <v>0.3995187481527835</v>
       </c>
       <c r="E46" t="n">
         <v>45</v>
@@ -1313,20 +1313,134 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2021-05-07</t>
+          <t>2021-04-27</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>33739236877</v>
+        <v>22708474693</v>
       </c>
       <c r="C47" t="n">
-        <v>72689004129</v>
+        <v>58465572266</v>
       </c>
       <c r="D47" t="n">
-        <v>0.4641587442458769</v>
+        <v>0.3884076356882914</v>
       </c>
       <c r="E47" t="n">
         <v>46</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2021-04-28</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>21663821099</v>
+      </c>
+      <c r="C48" t="n">
+        <v>56258757783</v>
+      </c>
+      <c r="D48" t="n">
+        <v>0.385074643534811</v>
+      </c>
+      <c r="E48" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2021-04-29</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>23761905634</v>
+      </c>
+      <c r="C49" t="n">
+        <v>59672070298</v>
+      </c>
+      <c r="D49" t="n">
+        <v>0.3982081653164364</v>
+      </c>
+      <c r="E49" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2021-04-30</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>26551609631</v>
+      </c>
+      <c r="C50" t="n">
+        <v>64623812735</v>
+      </c>
+      <c r="D50" t="n">
+        <v>0.4108641769540743</v>
+      </c>
+      <c r="E50" t="n">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2021-05-06</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>28186220087</v>
+      </c>
+      <c r="C51" t="n">
+        <v>64995398044</v>
+      </c>
+      <c r="D51" t="n">
+        <v>0.4336648583630298</v>
+      </c>
+      <c r="E51" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2021-05-07</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>33739236877</v>
+      </c>
+      <c r="C52" t="n">
+        <v>72689004129</v>
+      </c>
+      <c r="D52" t="n">
+        <v>0.4641587442458769</v>
+      </c>
+      <c r="E52" t="n">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2021-05-10</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>34911819241</v>
+      </c>
+      <c r="C53" t="n">
+        <v>74391256531</v>
+      </c>
+      <c r="D53" t="n">
+        <v>0.4693000342916872</v>
+      </c>
+      <c r="E53" t="n">
+        <v>52</v>
       </c>
     </row>
   </sheetData>

--- a/king_index/output/index.xlsx
+++ b/king_index/output/index.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E53"/>
+  <dimension ref="A1:E244"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -458,17 +458,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2021-02-22</t>
+          <t>2020-05-11</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>41263114607</v>
+        <v>21498726052</v>
       </c>
       <c r="C2" t="n">
-        <v>98345390597</v>
+        <v>57016622412</v>
       </c>
       <c r="D2" t="n">
-        <v>0.4195734477896183</v>
+        <v>0.3770606735813111</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>
@@ -477,17 +477,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2021-02-23</t>
+          <t>2020-05-12</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>36231161554</v>
+        <v>19188815582</v>
       </c>
       <c r="C3" t="n">
-        <v>79667225639</v>
+        <v>50239129593</v>
       </c>
       <c r="D3" t="n">
-        <v>0.4547812637304082</v>
+        <v>0.3819496025797717</v>
       </c>
       <c r="E3" t="n">
         <v>2</v>
@@ -496,17 +496,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2021-02-24</t>
+          <t>2020-05-13</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>32924792479</v>
+        <v>18559780599</v>
       </c>
       <c r="C4" t="n">
-        <v>74974298826</v>
+        <v>47805428174</v>
       </c>
       <c r="D4" t="n">
-        <v>0.4391477212132614</v>
+        <v>0.3882358407385656</v>
       </c>
       <c r="E4" t="n">
         <v>3</v>
@@ -515,17 +515,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2021-02-25</t>
+          <t>2020-05-14</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>32621098782</v>
+        <v>20187004918</v>
       </c>
       <c r="C5" t="n">
-        <v>72321851390</v>
+        <v>51752238810</v>
       </c>
       <c r="D5" t="n">
-        <v>0.4510545313074016</v>
+        <v>0.3900701763282808</v>
       </c>
       <c r="E5" t="n">
         <v>4</v>
@@ -534,17 +534,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2021-02-26</t>
+          <t>2020-05-15</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>29077783331</v>
+        <v>19718626995</v>
       </c>
       <c r="C6" t="n">
-        <v>67566280430</v>
+        <v>50182102488</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4303593914885571</v>
+        <v>0.3929414276676689</v>
       </c>
       <c r="E6" t="n">
         <v>5</v>
@@ -553,17 +553,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2021-03-01</t>
+          <t>2020-05-18</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>27680347479</v>
+        <v>22559505827</v>
       </c>
       <c r="C7" t="n">
-        <v>65847760652</v>
+        <v>58319431318</v>
       </c>
       <c r="D7" t="n">
-        <v>0.4203688508905923</v>
+        <v>0.3868265742165617</v>
       </c>
       <c r="E7" t="n">
         <v>6</v>
@@ -572,17 +572,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2021-03-02</t>
+          <t>2020-05-19</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>30189304329</v>
+        <v>18863773358</v>
       </c>
       <c r="C8" t="n">
-        <v>69441386639</v>
+        <v>50302048430</v>
       </c>
       <c r="D8" t="n">
-        <v>0.4347451252081556</v>
+        <v>0.3750100432639578</v>
       </c>
       <c r="E8" t="n">
         <v>7</v>
@@ -591,17 +591,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2021-03-03</t>
+          <t>2020-05-20</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>31200723147</v>
+        <v>21259230267</v>
       </c>
       <c r="C9" t="n">
-        <v>69999474895</v>
+        <v>55292303555</v>
       </c>
       <c r="D9" t="n">
-        <v>0.4457279600140063</v>
+        <v>0.3844880553014609</v>
       </c>
       <c r="E9" t="n">
         <v>8</v>
@@ -610,17 +610,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2021-03-04</t>
+          <t>2020-05-21</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>35686000296</v>
+        <v>19280128498</v>
       </c>
       <c r="C10" t="n">
-        <v>78562142790</v>
+        <v>52065201803</v>
       </c>
       <c r="D10" t="n">
-        <v>0.4542391415085281</v>
+        <v>0.370307380560063</v>
       </c>
       <c r="E10" t="n">
         <v>9</v>
@@ -629,17 +629,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2021-03-05</t>
+          <t>2020-05-22</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>31925237838</v>
+        <v>17897770797</v>
       </c>
       <c r="C11" t="n">
-        <v>73514786011</v>
+        <v>50417741953</v>
       </c>
       <c r="D11" t="n">
-        <v>0.4342696152747154</v>
+        <v>0.3549895355028892</v>
       </c>
       <c r="E11" t="n">
         <v>10</v>
@@ -648,17 +648,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2021-03-08</t>
+          <t>2020-05-25</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>33896120418</v>
+        <v>14723899014</v>
       </c>
       <c r="C12" t="n">
-        <v>78814375242</v>
+        <v>41053704521</v>
       </c>
       <c r="D12" t="n">
-        <v>0.4300753550849292</v>
+        <v>0.3586497049606901</v>
       </c>
       <c r="E12" t="n">
         <v>11</v>
@@ -667,17 +667,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2021-03-09</t>
+          <t>2020-05-26</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>35480957371</v>
+        <v>15738642741</v>
       </c>
       <c r="C13" t="n">
-        <v>82850202998</v>
+        <v>44120432080</v>
       </c>
       <c r="D13" t="n">
-        <v>0.4282543202924501</v>
+        <v>0.3567200500770799</v>
       </c>
       <c r="E13" t="n">
         <v>12</v>
@@ -686,17 +686,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2021-03-10</t>
+          <t>2020-05-27</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>26707850086</v>
+        <v>17872745345</v>
       </c>
       <c r="C14" t="n">
-        <v>62127335207</v>
+        <v>48783198139</v>
       </c>
       <c r="D14" t="n">
-        <v>0.429888872539165</v>
+        <v>0.366370923326397</v>
       </c>
       <c r="E14" t="n">
         <v>13</v>
@@ -705,17 +705,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2021-03-11</t>
+          <t>2020-05-28</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>30371987985</v>
+        <v>18416635989</v>
       </c>
       <c r="C15" t="n">
-        <v>66598157167</v>
+        <v>50047777669</v>
       </c>
       <c r="D15" t="n">
-        <v>0.4560484745672452</v>
+        <v>0.3679810942016595</v>
       </c>
       <c r="E15" t="n">
         <v>14</v>
@@ -724,17 +724,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2021-03-12</t>
+          <t>2020-05-29</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>33515365360</v>
+        <v>18782496399</v>
       </c>
       <c r="C16" t="n">
-        <v>72238010975</v>
+        <v>49396386216</v>
       </c>
       <c r="D16" t="n">
-        <v>0.4639574776165825</v>
+        <v>0.3802402936293375</v>
       </c>
       <c r="E16" t="n">
         <v>15</v>
@@ -743,17 +743,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2021-03-15</t>
+          <t>2020-06-01</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>34264676450</v>
+        <v>22806246928</v>
       </c>
       <c r="C17" t="n">
-        <v>71723136959</v>
+        <v>64259168243</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4777353292506872</v>
+        <v>0.3549103972487906</v>
       </c>
       <c r="E17" t="n">
         <v>16</v>
@@ -762,17 +762,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2021-03-16</t>
+          <t>2020-06-02</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>29674407853</v>
+        <v>26690797837</v>
       </c>
       <c r="C18" t="n">
-        <v>67049266583</v>
+        <v>67019269521</v>
       </c>
       <c r="D18" t="n">
-        <v>0.4425761736896283</v>
+        <v>0.3982555767582133</v>
       </c>
       <c r="E18" t="n">
         <v>17</v>
@@ -781,17 +781,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2021-03-17</t>
+          <t>2020-06-03</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>27205109308</v>
+        <v>25988325662</v>
       </c>
       <c r="C19" t="n">
-        <v>62515062852</v>
+        <v>66814592975</v>
       </c>
       <c r="D19" t="n">
-        <v>0.4351768688516906</v>
+        <v>0.3889618196390726</v>
       </c>
       <c r="E19" t="n">
         <v>18</v>
@@ -800,17 +800,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2021-03-18</t>
+          <t>2020-06-04</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>26446918115</v>
+        <v>22648232850</v>
       </c>
       <c r="C20" t="n">
-        <v>62832911819</v>
+        <v>57964700247</v>
       </c>
       <c r="D20" t="n">
-        <v>0.4209086822394046</v>
+        <v>0.3907245746720164</v>
       </c>
       <c r="E20" t="n">
         <v>19</v>
@@ -819,17 +819,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2021-03-19</t>
+          <t>2020-06-05</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>28051529133</v>
+        <v>21624249509</v>
       </c>
       <c r="C21" t="n">
-        <v>65875538395</v>
+        <v>55387084107</v>
       </c>
       <c r="D21" t="n">
-        <v>0.425826183989551</v>
+        <v>0.3904204356962539</v>
       </c>
       <c r="E21" t="n">
         <v>20</v>
@@ -838,17 +838,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2021-03-22</t>
+          <t>2020-06-08</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>28810574608</v>
+        <v>23546771032</v>
       </c>
       <c r="C22" t="n">
-        <v>67358226346</v>
+        <v>58352042780</v>
       </c>
       <c r="D22" t="n">
-        <v>0.4277216929675122</v>
+        <v>0.4035295065980208</v>
       </c>
       <c r="E22" t="n">
         <v>21</v>
@@ -857,17 +857,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2021-03-23</t>
+          <t>2020-06-09</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>28996759908</v>
+        <v>20955198305</v>
       </c>
       <c r="C23" t="n">
-        <v>70323191299</v>
+        <v>53192911283</v>
       </c>
       <c r="D23" t="n">
-        <v>0.4123356658362052</v>
+        <v>0.3939471970900961</v>
       </c>
       <c r="E23" t="n">
         <v>22</v>
@@ -876,17 +876,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2021-03-24</t>
+          <t>2020-06-10</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>28242888090</v>
+        <v>20190478240</v>
       </c>
       <c r="C24" t="n">
-        <v>67303523996</v>
+        <v>52136701032</v>
       </c>
       <c r="D24" t="n">
-        <v>0.41963461068812</v>
+        <v>0.3872603720670333</v>
       </c>
       <c r="E24" t="n">
         <v>23</v>
@@ -895,17 +895,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2021-03-25</t>
+          <t>2020-06-11</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>25646340206</v>
+        <v>21856153332</v>
       </c>
       <c r="C25" t="n">
-        <v>60650502617</v>
+        <v>58580995849</v>
       </c>
       <c r="D25" t="n">
-        <v>0.4228545370506373</v>
+        <v>0.3730928949780408</v>
       </c>
       <c r="E25" t="n">
         <v>24</v>
@@ -914,17 +914,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2021-03-26</t>
+          <t>2020-06-12</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>25622313889</v>
+        <v>22554032456</v>
       </c>
       <c r="C26" t="n">
-        <v>61284664475</v>
+        <v>58624630321</v>
       </c>
       <c r="D26" t="n">
-        <v>0.4180868755421215</v>
+        <v>0.3847193975041731</v>
       </c>
       <c r="E26" t="n">
         <v>25</v>
@@ -933,17 +933,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2021-03-29</t>
+          <t>2020-06-15</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>25803305477</v>
+        <v>24160399741</v>
       </c>
       <c r="C27" t="n">
-        <v>62965892538</v>
+        <v>62827231135</v>
       </c>
       <c r="D27" t="n">
-        <v>0.409798137323753</v>
+        <v>0.3845529924609497</v>
       </c>
       <c r="E27" t="n">
         <v>26</v>
@@ -952,17 +952,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2021-03-30</t>
+          <t>2020-06-16</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>25557342000</v>
+        <v>22302612612</v>
       </c>
       <c r="C28" t="n">
-        <v>62868502600</v>
+        <v>57871475779</v>
       </c>
       <c r="D28" t="n">
-        <v>0.4065206095746903</v>
+        <v>0.3853817845801855</v>
       </c>
       <c r="E28" t="n">
         <v>27</v>
@@ -971,17 +971,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2021-03-31</t>
+          <t>2020-06-17</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>25131445563</v>
+        <v>23156031895</v>
       </c>
       <c r="C29" t="n">
-        <v>58944651908</v>
+        <v>61386131654</v>
       </c>
       <c r="D29" t="n">
-        <v>0.4263566710381938</v>
+        <v>0.3772192720257707</v>
       </c>
       <c r="E29" t="n">
         <v>28</v>
@@ -990,17 +990,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2021-04-01</t>
+          <t>2020-06-18</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>24246862283</v>
+        <v>25733088111</v>
       </c>
       <c r="C30" t="n">
-        <v>57742915146</v>
+        <v>63354121102</v>
       </c>
       <c r="D30" t="n">
-        <v>0.419910602394996</v>
+        <v>0.4061785983830442</v>
       </c>
       <c r="E30" t="n">
         <v>29</v>
@@ -1009,17 +1009,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2021-04-02</t>
+          <t>2020-06-19</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>23570642397</v>
+        <v>24126480724</v>
       </c>
       <c r="C31" t="n">
-        <v>57637646459</v>
+        <v>61888832308</v>
       </c>
       <c r="D31" t="n">
-        <v>0.4089452613886092</v>
+        <v>0.3898357720489956</v>
       </c>
       <c r="E31" t="n">
         <v>30</v>
@@ -1028,17 +1028,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2021-04-06</t>
+          <t>2020-06-22</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>21461794855</v>
+        <v>25010112764</v>
       </c>
       <c r="C32" t="n">
-        <v>54009467026</v>
+        <v>63846785740</v>
       </c>
       <c r="D32" t="n">
-        <v>0.3973709802518205</v>
+        <v>0.3917207808369149</v>
       </c>
       <c r="E32" t="n">
         <v>31</v>
@@ -1047,17 +1047,17 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2021-04-07</t>
+          <t>2020-06-23</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>28017074765</v>
+        <v>21417149307</v>
       </c>
       <c r="C33" t="n">
-        <v>64777711487</v>
+        <v>56930673694</v>
       </c>
       <c r="D33" t="n">
-        <v>0.4325110307520302</v>
+        <v>0.3761970115111633</v>
       </c>
       <c r="E33" t="n">
         <v>32</v>
@@ -1066,17 +1066,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2021-04-08</t>
+          <t>2020-06-24</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>31420565576</v>
+        <v>19322024502</v>
       </c>
       <c r="C34" t="n">
-        <v>70183037971</v>
+        <v>52926747938</v>
       </c>
       <c r="D34" t="n">
-        <v>0.4476945781256027</v>
+        <v>0.3650710700123576</v>
       </c>
       <c r="E34" t="n">
         <v>33</v>
@@ -1085,17 +1085,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2021-04-09</t>
+          <t>2020-06-29</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>27209131167</v>
+        <v>20448932009</v>
       </c>
       <c r="C35" t="n">
-        <v>60908586933</v>
+        <v>54347085975</v>
       </c>
       <c r="D35" t="n">
-        <v>0.4467207751335668</v>
+        <v>0.3762654729713868</v>
       </c>
       <c r="E35" t="n">
         <v>34</v>
@@ -1104,17 +1104,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2021-04-12</t>
+          <t>2020-06-30</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>29275293774</v>
+        <v>20003048931</v>
       </c>
       <c r="C36" t="n">
-        <v>66662877908</v>
+        <v>53946886834</v>
       </c>
       <c r="D36" t="n">
-        <v>0.4391543643585595</v>
+        <v>0.3707915341352578</v>
       </c>
       <c r="E36" t="n">
         <v>35</v>
@@ -1123,17 +1123,17 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2021-04-13</t>
+          <t>2020-07-01</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>26344677943</v>
+        <v>25539868441</v>
       </c>
       <c r="C37" t="n">
-        <v>60099497250</v>
+        <v>66477208273</v>
       </c>
       <c r="D37" t="n">
-        <v>0.4383510536437973</v>
+        <v>0.3841898464826647</v>
       </c>
       <c r="E37" t="n">
         <v>36</v>
@@ -1142,17 +1142,17 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2021-04-14</t>
+          <t>2020-07-02</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>24734018928</v>
+        <v>35281401239</v>
       </c>
       <c r="C38" t="n">
-        <v>56149660115</v>
+        <v>86277275738</v>
       </c>
       <c r="D38" t="n">
-        <v>0.4405016678167296</v>
+        <v>0.4089304041789609</v>
       </c>
       <c r="E38" t="n">
         <v>37</v>
@@ -1161,17 +1161,17 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2021-04-15</t>
+          <t>2020-07-03</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>23433331402</v>
+        <v>39589081860</v>
       </c>
       <c r="C39" t="n">
-        <v>56730832399</v>
+        <v>96590527098</v>
       </c>
       <c r="D39" t="n">
-        <v>0.4130616529154447</v>
+        <v>0.4098650566409398</v>
       </c>
       <c r="E39" t="n">
         <v>38</v>
@@ -1180,17 +1180,17 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2021-04-16</t>
+          <t>2020-07-06</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>22954113918</v>
+        <v>51680326902</v>
       </c>
       <c r="C40" t="n">
-        <v>60757105467</v>
+        <v>132721246132</v>
       </c>
       <c r="D40" t="n">
-        <v>0.3778013080374187</v>
+        <v>0.3893900065600689</v>
       </c>
       <c r="E40" t="n">
         <v>39</v>
@@ -1199,17 +1199,17 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2021-04-19</t>
+          <t>2020-07-07</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>26230121790</v>
+        <v>54130474812</v>
       </c>
       <c r="C41" t="n">
-        <v>68717257011</v>
+        <v>140540263998</v>
       </c>
       <c r="D41" t="n">
-        <v>0.3817108384550504</v>
+        <v>0.3851599055824338</v>
       </c>
       <c r="E41" t="n">
         <v>40</v>
@@ -1218,17 +1218,17 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2021-04-20</t>
+          <t>2020-07-08</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>26219403332</v>
+        <v>48763694238</v>
       </c>
       <c r="C42" t="n">
-        <v>66152179163</v>
+        <v>124820435614</v>
       </c>
       <c r="D42" t="n">
-        <v>0.3963498053086805</v>
+        <v>0.3906707583427999</v>
       </c>
       <c r="E42" t="n">
         <v>41</v>
@@ -1237,17 +1237,17 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2021-04-21</t>
+          <t>2020-07-09</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>23695744997</v>
+        <v>50352644938</v>
       </c>
       <c r="C43" t="n">
-        <v>58645267418</v>
+        <v>137276438768</v>
       </c>
       <c r="D43" t="n">
-        <v>0.4040521262884899</v>
+        <v>0.3667974299879457</v>
       </c>
       <c r="E43" t="n">
         <v>42</v>
@@ -1256,17 +1256,17 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2021-04-22</t>
+          <t>2020-07-10</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>23178816248</v>
+        <v>45792064703</v>
       </c>
       <c r="C44" t="n">
-        <v>57343158813</v>
+        <v>124540979573</v>
       </c>
       <c r="D44" t="n">
-        <v>0.4042124069862932</v>
+        <v>0.3676867233580644</v>
       </c>
       <c r="E44" t="n">
         <v>43</v>
@@ -1275,17 +1275,17 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2021-04-23</t>
+          <t>2020-07-13</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>23008974358</v>
+        <v>45569190970</v>
       </c>
       <c r="C45" t="n">
-        <v>58758936747</v>
+        <v>125874117474</v>
       </c>
       <c r="D45" t="n">
-        <v>0.3915825512137904</v>
+        <v>0.3620219301987366</v>
       </c>
       <c r="E45" t="n">
         <v>44</v>
@@ -1294,17 +1294,17 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2021-04-26</t>
+          <t>2020-07-14</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>25964986812</v>
+        <v>44404671526</v>
       </c>
       <c r="C46" t="n">
-        <v>64990659217</v>
+        <v>127205292718</v>
       </c>
       <c r="D46" t="n">
-        <v>0.3995187481527835</v>
+        <v>0.3490788046409375</v>
       </c>
       <c r="E46" t="n">
         <v>45</v>
@@ -1313,17 +1313,17 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2021-04-27</t>
+          <t>2020-07-15</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>22708474693</v>
+        <v>40948010990</v>
       </c>
       <c r="C47" t="n">
-        <v>58465572266</v>
+        <v>115744357395</v>
       </c>
       <c r="D47" t="n">
-        <v>0.3884076356882914</v>
+        <v>0.3537797600815822</v>
       </c>
       <c r="E47" t="n">
         <v>46</v>
@@ -1332,17 +1332,17 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2021-04-28</t>
+          <t>2020-07-16</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>21663821099</v>
+        <v>41327517137</v>
       </c>
       <c r="C48" t="n">
-        <v>56258757783</v>
+        <v>110570972319</v>
       </c>
       <c r="D48" t="n">
-        <v>0.385074643534811</v>
+        <v>0.373764617152584</v>
       </c>
       <c r="E48" t="n">
         <v>47</v>
@@ -1351,17 +1351,17 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2021-04-29</t>
+          <t>2020-07-17</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>23761905634</v>
+        <v>30786629717</v>
       </c>
       <c r="C49" t="n">
-        <v>59672070298</v>
+        <v>83073812068</v>
       </c>
       <c r="D49" t="n">
-        <v>0.3982081653164364</v>
+        <v>0.3705936798927636</v>
       </c>
       <c r="E49" t="n">
         <v>48</v>
@@ -1370,17 +1370,17 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2021-04-30</t>
+          <t>2020-07-20</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>26551609631</v>
+        <v>33302406491</v>
       </c>
       <c r="C50" t="n">
-        <v>64623812735</v>
+        <v>90725025902</v>
       </c>
       <c r="D50" t="n">
-        <v>0.4108641769540743</v>
+        <v>0.3670696829226903</v>
       </c>
       <c r="E50" t="n">
         <v>49</v>
@@ -1389,17 +1389,17 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2021-05-06</t>
+          <t>2020-07-21</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>28186220087</v>
+        <v>29750727633</v>
       </c>
       <c r="C51" t="n">
-        <v>64995398044</v>
+        <v>82804408460</v>
       </c>
       <c r="D51" t="n">
-        <v>0.4336648583630298</v>
+        <v>0.3592891753749025</v>
       </c>
       <c r="E51" t="n">
         <v>50</v>
@@ -1408,17 +1408,17 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2021-05-07</t>
+          <t>2020-07-22</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>33739236877</v>
+        <v>32546369994</v>
       </c>
       <c r="C52" t="n">
-        <v>72689004129</v>
+        <v>88951002081</v>
       </c>
       <c r="D52" t="n">
-        <v>0.4641587442458769</v>
+        <v>0.3658909875389917</v>
       </c>
       <c r="E52" t="n">
         <v>51</v>
@@ -1427,20 +1427,3649 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2021-05-10</t>
+          <t>2020-07-23</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>34911819241</v>
+        <v>33380341470</v>
       </c>
       <c r="C53" t="n">
-        <v>74391256531</v>
+        <v>92918126099</v>
       </c>
       <c r="D53" t="n">
-        <v>0.4693000342916872</v>
+        <v>0.3592446691664313</v>
       </c>
       <c r="E53" t="n">
         <v>52</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2020-07-24</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>34826858650</v>
+      </c>
+      <c r="C54" t="n">
+        <v>98778010270</v>
+      </c>
+      <c r="D54" t="n">
+        <v>0.3525770417404056</v>
+      </c>
+      <c r="E54" t="n">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2020-07-27</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>25272101520</v>
+      </c>
+      <c r="C55" t="n">
+        <v>69273127708</v>
+      </c>
+      <c r="D55" t="n">
+        <v>0.3648182542951854</v>
+      </c>
+      <c r="E55" t="n">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2020-07-28</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>25533477451</v>
+      </c>
+      <c r="C56" t="n">
+        <v>67557159363</v>
+      </c>
+      <c r="D56" t="n">
+        <v>0.3779536868002814</v>
+      </c>
+      <c r="E56" t="n">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2020-07-29</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>27398207256</v>
+      </c>
+      <c r="C57" t="n">
+        <v>75808503607</v>
+      </c>
+      <c r="D57" t="n">
+        <v>0.3614133764997586</v>
+      </c>
+      <c r="E57" t="n">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2020-07-30</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>29316097538</v>
+      </c>
+      <c r="C58" t="n">
+        <v>80705680370</v>
+      </c>
+      <c r="D58" t="n">
+        <v>0.3632470156201968</v>
+      </c>
+      <c r="E58" t="n">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2020-07-31</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>30421341838</v>
+      </c>
+      <c r="C59" t="n">
+        <v>83388719271</v>
+      </c>
+      <c r="D59" t="n">
+        <v>0.3648136355126825</v>
+      </c>
+      <c r="E59" t="n">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2020-08-03</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>32534419194</v>
+      </c>
+      <c r="C60" t="n">
+        <v>97147468049</v>
+      </c>
+      <c r="D60" t="n">
+        <v>0.3348972427937086</v>
+      </c>
+      <c r="E60" t="n">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2020-08-04</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>35518548960</v>
+      </c>
+      <c r="C61" t="n">
+        <v>100401661483</v>
+      </c>
+      <c r="D61" t="n">
+        <v>0.3537645536474912</v>
+      </c>
+      <c r="E61" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2020-08-05</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>31118752071</v>
+      </c>
+      <c r="C62" t="n">
+        <v>88411991123</v>
+      </c>
+      <c r="D62" t="n">
+        <v>0.351974338273947</v>
+      </c>
+      <c r="E62" t="n">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2020-08-06</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>35289080996</v>
+      </c>
+      <c r="C63" t="n">
+        <v>94484631872</v>
+      </c>
+      <c r="D63" t="n">
+        <v>0.3734901676264849</v>
+      </c>
+      <c r="E63" t="n">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2020-08-07</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>33926327226</v>
+      </c>
+      <c r="C64" t="n">
+        <v>90977583613</v>
+      </c>
+      <c r="D64" t="n">
+        <v>0.3729086427522151</v>
+      </c>
+      <c r="E64" t="n">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2020-08-10</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>29708663069</v>
+      </c>
+      <c r="C65" t="n">
+        <v>82942928747</v>
+      </c>
+      <c r="D65" t="n">
+        <v>0.3581819875160189</v>
+      </c>
+      <c r="E65" t="n">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2020-08-11</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>30946369948</v>
+      </c>
+      <c r="C66" t="n">
+        <v>86295092754</v>
+      </c>
+      <c r="D66" t="n">
+        <v>0.3586110051033644</v>
+      </c>
+      <c r="E66" t="n">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2020-08-12</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>29856245191</v>
+      </c>
+      <c r="C67" t="n">
+        <v>82452473263</v>
+      </c>
+      <c r="D67" t="n">
+        <v>0.3621024817019988</v>
+      </c>
+      <c r="E67" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2020-08-13</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>27823565615</v>
+      </c>
+      <c r="C68" t="n">
+        <v>72532322436</v>
+      </c>
+      <c r="D68" t="n">
+        <v>0.3836022986793308</v>
+      </c>
+      <c r="E68" t="n">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2020-08-14</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>27261549866</v>
+      </c>
+      <c r="C69" t="n">
+        <v>69180221661</v>
+      </c>
+      <c r="D69" t="n">
+        <v>0.3940656622869504</v>
+      </c>
+      <c r="E69" t="n">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2020-08-17</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>37118467741</v>
+      </c>
+      <c r="C70" t="n">
+        <v>91788369903</v>
+      </c>
+      <c r="D70" t="n">
+        <v>0.4043918394043386</v>
+      </c>
+      <c r="E70" t="n">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2020-08-18</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>31325687773</v>
+      </c>
+      <c r="C71" t="n">
+        <v>85178317604</v>
+      </c>
+      <c r="D71" t="n">
+        <v>0.3677659838109897</v>
+      </c>
+      <c r="E71" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2020-08-19</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>33073383828</v>
+      </c>
+      <c r="C72" t="n">
+        <v>88140275731</v>
+      </c>
+      <c r="D72" t="n">
+        <v>0.375235765417145</v>
+      </c>
+      <c r="E72" t="n">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2020-08-20</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>27646953314</v>
+      </c>
+      <c r="C73" t="n">
+        <v>72119978332</v>
+      </c>
+      <c r="D73" t="n">
+        <v>0.3833466669489126</v>
+      </c>
+      <c r="E73" t="n">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2020-08-21</t>
+        </is>
+      </c>
+      <c r="B74" t="n">
+        <v>25486130617</v>
+      </c>
+      <c r="C74" t="n">
+        <v>66786682396</v>
+      </c>
+      <c r="D74" t="n">
+        <v>0.3816049802546626</v>
+      </c>
+      <c r="E74" t="n">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2020-08-24</t>
+        </is>
+      </c>
+      <c r="B75" t="n">
+        <v>25209284709</v>
+      </c>
+      <c r="C75" t="n">
+        <v>67412296336</v>
+      </c>
+      <c r="D75" t="n">
+        <v>0.3739567716748666</v>
+      </c>
+      <c r="E75" t="n">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2020-08-25</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>26619247474</v>
+      </c>
+      <c r="C76" t="n">
+        <v>73103731924</v>
+      </c>
+      <c r="D76" t="n">
+        <v>0.3641298025889275</v>
+      </c>
+      <c r="E76" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2020-08-26</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>26322908958</v>
+      </c>
+      <c r="C77" t="n">
+        <v>75716936591</v>
+      </c>
+      <c r="D77" t="n">
+        <v>0.3476488899727732</v>
+      </c>
+      <c r="E77" t="n">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2020-08-27</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>23276018839</v>
+      </c>
+      <c r="C78" t="n">
+        <v>65005692955</v>
+      </c>
+      <c r="D78" t="n">
+        <v>0.3580612371152286</v>
+      </c>
+      <c r="E78" t="n">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2020-08-28</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
+        <v>25701039669</v>
+      </c>
+      <c r="C79" t="n">
+        <v>70850828969</v>
+      </c>
+      <c r="D79" t="n">
+        <v>0.3627486091975749</v>
+      </c>
+      <c r="E79" t="n">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2020-08-31</t>
+        </is>
+      </c>
+      <c r="B80" t="n">
+        <v>28573296373</v>
+      </c>
+      <c r="C80" t="n">
+        <v>77184652221</v>
+      </c>
+      <c r="D80" t="n">
+        <v>0.3701940159189566</v>
+      </c>
+      <c r="E80" t="n">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2020-09-01</t>
+        </is>
+      </c>
+      <c r="B81" t="n">
+        <v>23964180511</v>
+      </c>
+      <c r="C81" t="n">
+        <v>64392996012</v>
+      </c>
+      <c r="D81" t="n">
+        <v>0.3721550788929613</v>
+      </c>
+      <c r="E81" t="n">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2020-09-02</t>
+        </is>
+      </c>
+      <c r="B82" t="n">
+        <v>30082062270</v>
+      </c>
+      <c r="C82" t="n">
+        <v>77531927895</v>
+      </c>
+      <c r="D82" t="n">
+        <v>0.3879957984630482</v>
+      </c>
+      <c r="E82" t="n">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2020-09-03</t>
+        </is>
+      </c>
+      <c r="B83" t="n">
+        <v>27715216294</v>
+      </c>
+      <c r="C83" t="n">
+        <v>73519808249</v>
+      </c>
+      <c r="D83" t="n">
+        <v>0.3769761776327399</v>
+      </c>
+      <c r="E83" t="n">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2020-09-04</t>
+        </is>
+      </c>
+      <c r="B84" t="n">
+        <v>24329945914</v>
+      </c>
+      <c r="C84" t="n">
+        <v>65573685675</v>
+      </c>
+      <c r="D84" t="n">
+        <v>0.37103215510236</v>
+      </c>
+      <c r="E84" t="n">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2020-09-07</t>
+        </is>
+      </c>
+      <c r="B85" t="n">
+        <v>29997390344</v>
+      </c>
+      <c r="C85" t="n">
+        <v>79881522723</v>
+      </c>
+      <c r="D85" t="n">
+        <v>0.375523516846568</v>
+      </c>
+      <c r="E85" t="n">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2020-09-08</t>
+        </is>
+      </c>
+      <c r="B86" t="n">
+        <v>32724062545</v>
+      </c>
+      <c r="C86" t="n">
+        <v>80161481426</v>
+      </c>
+      <c r="D86" t="n">
+        <v>0.4082267688030289</v>
+      </c>
+      <c r="E86" t="n">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2020-09-09</t>
+        </is>
+      </c>
+      <c r="B87" t="n">
+        <v>41720230941</v>
+      </c>
+      <c r="C87" t="n">
+        <v>98517765305</v>
+      </c>
+      <c r="D87" t="n">
+        <v>0.4234792660170358</v>
+      </c>
+      <c r="E87" t="n">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2020-09-10</t>
+        </is>
+      </c>
+      <c r="B88" t="n">
+        <v>32362586075</v>
+      </c>
+      <c r="C88" t="n">
+        <v>83938666669</v>
+      </c>
+      <c r="D88" t="n">
+        <v>0.3855503948212232</v>
+      </c>
+      <c r="E88" t="n">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>2020-09-11</t>
+        </is>
+      </c>
+      <c r="B89" t="n">
+        <v>23586290440</v>
+      </c>
+      <c r="C89" t="n">
+        <v>60330240577</v>
+      </c>
+      <c r="D89" t="n">
+        <v>0.3909530314220547</v>
+      </c>
+      <c r="E89" t="n">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>2020-09-14</t>
+        </is>
+      </c>
+      <c r="B90" t="n">
+        <v>24462170352</v>
+      </c>
+      <c r="C90" t="n">
+        <v>63101019998</v>
+      </c>
+      <c r="D90" t="n">
+        <v>0.3876667976646865</v>
+      </c>
+      <c r="E90" t="n">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2020-09-15</t>
+        </is>
+      </c>
+      <c r="B91" t="n">
+        <v>23106120892</v>
+      </c>
+      <c r="C91" t="n">
+        <v>58614407766</v>
+      </c>
+      <c r="D91" t="n">
+        <v>0.3942054824514151</v>
+      </c>
+      <c r="E91" t="n">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2020-09-16</t>
+        </is>
+      </c>
+      <c r="B92" t="n">
+        <v>21724638649</v>
+      </c>
+      <c r="C92" t="n">
+        <v>55182289033</v>
+      </c>
+      <c r="D92" t="n">
+        <v>0.3936886096915674</v>
+      </c>
+      <c r="E92" t="n">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2020-09-17</t>
+        </is>
+      </c>
+      <c r="B93" t="n">
+        <v>20554994106</v>
+      </c>
+      <c r="C93" t="n">
+        <v>55472969929</v>
+      </c>
+      <c r="D93" t="n">
+        <v>0.3705407179804577</v>
+      </c>
+      <c r="E93" t="n">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>2020-09-18</t>
+        </is>
+      </c>
+      <c r="B94" t="n">
+        <v>25018086444</v>
+      </c>
+      <c r="C94" t="n">
+        <v>64587549837</v>
+      </c>
+      <c r="D94" t="n">
+        <v>0.3873515330297914</v>
+      </c>
+      <c r="E94" t="n">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>2020-09-21</t>
+        </is>
+      </c>
+      <c r="B95" t="n">
+        <v>22182279260</v>
+      </c>
+      <c r="C95" t="n">
+        <v>58098440053</v>
+      </c>
+      <c r="D95" t="n">
+        <v>0.3818050749686968</v>
+      </c>
+      <c r="E95" t="n">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>2020-09-22</t>
+        </is>
+      </c>
+      <c r="B96" t="n">
+        <v>22099090990</v>
+      </c>
+      <c r="C96" t="n">
+        <v>56264182474</v>
+      </c>
+      <c r="D96" t="n">
+        <v>0.3927736975510506</v>
+      </c>
+      <c r="E96" t="n">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>2020-09-23</t>
+        </is>
+      </c>
+      <c r="B97" t="n">
+        <v>19077501915</v>
+      </c>
+      <c r="C97" t="n">
+        <v>48597940983</v>
+      </c>
+      <c r="D97" t="n">
+        <v>0.3925578230088695</v>
+      </c>
+      <c r="E97" t="n">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>2020-09-24</t>
+        </is>
+      </c>
+      <c r="B98" t="n">
+        <v>20859996043</v>
+      </c>
+      <c r="C98" t="n">
+        <v>54861814882</v>
+      </c>
+      <c r="D98" t="n">
+        <v>0.3802279616134993</v>
+      </c>
+      <c r="E98" t="n">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>2020-09-25</t>
+        </is>
+      </c>
+      <c r="B99" t="n">
+        <v>16281719043</v>
+      </c>
+      <c r="C99" t="n">
+        <v>43622575116</v>
+      </c>
+      <c r="D99" t="n">
+        <v>0.373240667239476</v>
+      </c>
+      <c r="E99" t="n">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>2020-09-28</t>
+        </is>
+      </c>
+      <c r="B100" t="n">
+        <v>14676583271</v>
+      </c>
+      <c r="C100" t="n">
+        <v>40556797589</v>
+      </c>
+      <c r="D100" t="n">
+        <v>0.3618772719614492</v>
+      </c>
+      <c r="E100" t="n">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>2020-09-29</t>
+        </is>
+      </c>
+      <c r="B101" t="n">
+        <v>14442107257</v>
+      </c>
+      <c r="C101" t="n">
+        <v>40163621965</v>
+      </c>
+      <c r="D101" t="n">
+        <v>0.3595817944304267</v>
+      </c>
+      <c r="E101" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>2020-09-30</t>
+        </is>
+      </c>
+      <c r="B102" t="n">
+        <v>15066784297</v>
+      </c>
+      <c r="C102" t="n">
+        <v>40300843448</v>
+      </c>
+      <c r="D102" t="n">
+        <v>0.3738577907541961</v>
+      </c>
+      <c r="E102" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>2020-10-09</t>
+        </is>
+      </c>
+      <c r="B103" t="n">
+        <v>18363804782</v>
+      </c>
+      <c r="C103" t="n">
+        <v>50410563994</v>
+      </c>
+      <c r="D103" t="n">
+        <v>0.3642848507742486</v>
+      </c>
+      <c r="E103" t="n">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>2020-10-12</t>
+        </is>
+      </c>
+      <c r="B104" t="n">
+        <v>24824121596</v>
+      </c>
+      <c r="C104" t="n">
+        <v>69075123930</v>
+      </c>
+      <c r="D104" t="n">
+        <v>0.3593786038104905</v>
+      </c>
+      <c r="E104" t="n">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>2020-10-13</t>
+        </is>
+      </c>
+      <c r="B105" t="n">
+        <v>21950874234</v>
+      </c>
+      <c r="C105" t="n">
+        <v>58435290007</v>
+      </c>
+      <c r="D105" t="n">
+        <v>0.3756441395494142</v>
+      </c>
+      <c r="E105" t="n">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>2020-10-14</t>
+        </is>
+      </c>
+      <c r="B106" t="n">
+        <v>21810988673</v>
+      </c>
+      <c r="C106" t="n">
+        <v>58022364557</v>
+      </c>
+      <c r="D106" t="n">
+        <v>0.3759065808421738</v>
+      </c>
+      <c r="E106" t="n">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>2020-10-15</t>
+        </is>
+      </c>
+      <c r="B107" t="n">
+        <v>20410751440</v>
+      </c>
+      <c r="C107" t="n">
+        <v>54415224691</v>
+      </c>
+      <c r="D107" t="n">
+        <v>0.3750926612157467</v>
+      </c>
+      <c r="E107" t="n">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>2020-10-16</t>
+        </is>
+      </c>
+      <c r="B108" t="n">
+        <v>19779199722</v>
+      </c>
+      <c r="C108" t="n">
+        <v>51552706029</v>
+      </c>
+      <c r="D108" t="n">
+        <v>0.3836694762613156</v>
+      </c>
+      <c r="E108" t="n">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>2020-10-19</t>
+        </is>
+      </c>
+      <c r="B109" t="n">
+        <v>20562725471</v>
+      </c>
+      <c r="C109" t="n">
+        <v>53895497648</v>
+      </c>
+      <c r="D109" t="n">
+        <v>0.3815295593947087</v>
+      </c>
+      <c r="E109" t="n">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>2020-10-20</t>
+        </is>
+      </c>
+      <c r="B110" t="n">
+        <v>18296672779</v>
+      </c>
+      <c r="C110" t="n">
+        <v>47922773316</v>
+      </c>
+      <c r="D110" t="n">
+        <v>0.3817949486844761</v>
+      </c>
+      <c r="E110" t="n">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>2020-10-21</t>
+        </is>
+      </c>
+      <c r="B111" t="n">
+        <v>18370049664</v>
+      </c>
+      <c r="C111" t="n">
+        <v>49307563396</v>
+      </c>
+      <c r="D111" t="n">
+        <v>0.3725604836009853</v>
+      </c>
+      <c r="E111" t="n">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>2020-10-22</t>
+        </is>
+      </c>
+      <c r="B112" t="n">
+        <v>17665602844</v>
+      </c>
+      <c r="C112" t="n">
+        <v>46460364776</v>
+      </c>
+      <c r="D112" t="n">
+        <v>0.3802295339085566</v>
+      </c>
+      <c r="E112" t="n">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>2020-10-23</t>
+        </is>
+      </c>
+      <c r="B113" t="n">
+        <v>17466910909</v>
+      </c>
+      <c r="C113" t="n">
+        <v>47398504650</v>
+      </c>
+      <c r="D113" t="n">
+        <v>0.3685118557637873</v>
+      </c>
+      <c r="E113" t="n">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>2020-10-26</t>
+        </is>
+      </c>
+      <c r="B114" t="n">
+        <v>16145407434</v>
+      </c>
+      <c r="C114" t="n">
+        <v>44150494774</v>
+      </c>
+      <c r="D114" t="n">
+        <v>0.3656902944496094</v>
+      </c>
+      <c r="E114" t="n">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>2020-10-27</t>
+        </is>
+      </c>
+      <c r="B115" t="n">
+        <v>15491813981</v>
+      </c>
+      <c r="C115" t="n">
+        <v>43505082864</v>
+      </c>
+      <c r="D115" t="n">
+        <v>0.356092046288672</v>
+      </c>
+      <c r="E115" t="n">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>2020-10-28</t>
+        </is>
+      </c>
+      <c r="B116" t="n">
+        <v>17543172634</v>
+      </c>
+      <c r="C116" t="n">
+        <v>49485508785</v>
+      </c>
+      <c r="D116" t="n">
+        <v>0.3545113117906887</v>
+      </c>
+      <c r="E116" t="n">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>2020-10-29</t>
+        </is>
+      </c>
+      <c r="B117" t="n">
+        <v>18553392322</v>
+      </c>
+      <c r="C117" t="n">
+        <v>51689467398</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.3589395142948963</v>
+      </c>
+      <c r="E117" t="n">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>2020-10-30</t>
+        </is>
+      </c>
+      <c r="B118" t="n">
+        <v>20650226596</v>
+      </c>
+      <c r="C118" t="n">
+        <v>60348197366</v>
+      </c>
+      <c r="D118" t="n">
+        <v>0.3421846467220954</v>
+      </c>
+      <c r="E118" t="n">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>2020-11-02</t>
+        </is>
+      </c>
+      <c r="B119" t="n">
+        <v>19992661394</v>
+      </c>
+      <c r="C119" t="n">
+        <v>56353918211</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.3547696775784711</v>
+      </c>
+      <c r="E119" t="n">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>2020-11-03</t>
+        </is>
+      </c>
+      <c r="B120" t="n">
+        <v>20249408150</v>
+      </c>
+      <c r="C120" t="n">
+        <v>55344378404</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.365880126111173</v>
+      </c>
+      <c r="E120" t="n">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>2020-11-04</t>
+        </is>
+      </c>
+      <c r="B121" t="n">
+        <v>18257580496</v>
+      </c>
+      <c r="C121" t="n">
+        <v>49909415865</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.3658143494483073</v>
+      </c>
+      <c r="E121" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>2020-11-05</t>
+        </is>
+      </c>
+      <c r="B122" t="n">
+        <v>21285267389</v>
+      </c>
+      <c r="C122" t="n">
+        <v>58980118835</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.3608888522002924</v>
+      </c>
+      <c r="E122" t="n">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>2020-11-06</t>
+        </is>
+      </c>
+      <c r="B123" t="n">
+        <v>23071856412</v>
+      </c>
+      <c r="C123" t="n">
+        <v>59902082650</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.3851595034984981</v>
+      </c>
+      <c r="E123" t="n">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>2020-11-09</t>
+        </is>
+      </c>
+      <c r="B124" t="n">
+        <v>27202863336</v>
+      </c>
+      <c r="C124" t="n">
+        <v>74478178320</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.3652460888492902</v>
+      </c>
+      <c r="E124" t="n">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>2020-11-10</t>
+        </is>
+      </c>
+      <c r="B125" t="n">
+        <v>25309810082</v>
+      </c>
+      <c r="C125" t="n">
+        <v>67090114044</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.3772509622714452</v>
+      </c>
+      <c r="E125" t="n">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>2020-11-11</t>
+        </is>
+      </c>
+      <c r="B126" t="n">
+        <v>23822441228</v>
+      </c>
+      <c r="C126" t="n">
+        <v>61988411650</v>
+      </c>
+      <c r="D126" t="n">
+        <v>0.3843047529997488</v>
+      </c>
+      <c r="E126" t="n">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>2020-11-12</t>
+        </is>
+      </c>
+      <c r="B127" t="n">
+        <v>19076439758</v>
+      </c>
+      <c r="C127" t="n">
+        <v>51703999860</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.3689548160616911</v>
+      </c>
+      <c r="E127" t="n">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>2020-11-13</t>
+        </is>
+      </c>
+      <c r="B128" t="n">
+        <v>20119982649</v>
+      </c>
+      <c r="C128" t="n">
+        <v>52210418675</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.3853633653896379</v>
+      </c>
+      <c r="E128" t="n">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>2020-11-16</t>
+        </is>
+      </c>
+      <c r="B129" t="n">
+        <v>23217241543</v>
+      </c>
+      <c r="C129" t="n">
+        <v>61350411349</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.3784366075546849</v>
+      </c>
+      <c r="E129" t="n">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>2020-11-17</t>
+        </is>
+      </c>
+      <c r="B130" t="n">
+        <v>24335506367</v>
+      </c>
+      <c r="C130" t="n">
+        <v>64241703103</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.3788116626980203</v>
+      </c>
+      <c r="E130" t="n">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>2020-11-18</t>
+        </is>
+      </c>
+      <c r="B131" t="n">
+        <v>25490702717</v>
+      </c>
+      <c r="C131" t="n">
+        <v>63205463709</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.4032990381078449</v>
+      </c>
+      <c r="E131" t="n">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>2020-11-19</t>
+        </is>
+      </c>
+      <c r="B132" t="n">
+        <v>23177522765</v>
+      </c>
+      <c r="C132" t="n">
+        <v>59756276020</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.3878675899623104</v>
+      </c>
+      <c r="E132" t="n">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>2020-11-20</t>
+        </is>
+      </c>
+      <c r="B133" t="n">
+        <v>22935620159</v>
+      </c>
+      <c r="C133" t="n">
+        <v>58875754449</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.3895596816320637</v>
+      </c>
+      <c r="E133" t="n">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>2020-11-23</t>
+        </is>
+      </c>
+      <c r="B134" t="n">
+        <v>32096579820</v>
+      </c>
+      <c r="C134" t="n">
+        <v>77198006469</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.4157695423506675</v>
+      </c>
+      <c r="E134" t="n">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>2020-11-24</t>
+        </is>
+      </c>
+      <c r="B135" t="n">
+        <v>26709718473</v>
+      </c>
+      <c r="C135" t="n">
+        <v>65410116144</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.408342318399171</v>
+      </c>
+      <c r="E135" t="n">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>2020-11-25</t>
+        </is>
+      </c>
+      <c r="B136" t="n">
+        <v>27089790866</v>
+      </c>
+      <c r="C136" t="n">
+        <v>68837443765</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.3935327836762824</v>
+      </c>
+      <c r="E136" t="n">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>2020-11-26</t>
+        </is>
+      </c>
+      <c r="B137" t="n">
+        <v>21689088930</v>
+      </c>
+      <c r="C137" t="n">
+        <v>57127013421</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0.3796643239540867</v>
+      </c>
+      <c r="E137" t="n">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>2020-11-27</t>
+        </is>
+      </c>
+      <c r="B138" t="n">
+        <v>23626364341</v>
+      </c>
+      <c r="C138" t="n">
+        <v>58765160877</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.4020471311301572</v>
+      </c>
+      <c r="E138" t="n">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>2020-11-30</t>
+        </is>
+      </c>
+      <c r="B139" t="n">
+        <v>33970232252</v>
+      </c>
+      <c r="C139" t="n">
+        <v>75092505579</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.4523784629381171</v>
+      </c>
+      <c r="E139" t="n">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>2020-12-01</t>
+        </is>
+      </c>
+      <c r="B140" t="n">
+        <v>28738868941</v>
+      </c>
+      <c r="C140" t="n">
+        <v>67936162045</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.4230275611089682</v>
+      </c>
+      <c r="E140" t="n">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>2020-12-02</t>
+        </is>
+      </c>
+      <c r="B141" t="n">
+        <v>28928357564</v>
+      </c>
+      <c r="C141" t="n">
+        <v>69689843826</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.4151014835996427</v>
+      </c>
+      <c r="E141" t="n">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>2020-12-03</t>
+        </is>
+      </c>
+      <c r="B142" t="n">
+        <v>28497726227</v>
+      </c>
+      <c r="C142" t="n">
+        <v>66950741850</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.4256521352795137</v>
+      </c>
+      <c r="E142" t="n">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>2020-12-04</t>
+        </is>
+      </c>
+      <c r="B143" t="n">
+        <v>23614518756</v>
+      </c>
+      <c r="C143" t="n">
+        <v>57124426015</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.4133874141649876</v>
+      </c>
+      <c r="E143" t="n">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>2020-12-07</t>
+        </is>
+      </c>
+      <c r="B144" t="n">
+        <v>22345056458</v>
+      </c>
+      <c r="C144" t="n">
+        <v>56856559648</v>
+      </c>
+      <c r="D144" t="n">
+        <v>0.3930075367967857</v>
+      </c>
+      <c r="E144" t="n">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>2020-12-08</t>
+        </is>
+      </c>
+      <c r="B145" t="n">
+        <v>20555717183</v>
+      </c>
+      <c r="C145" t="n">
+        <v>51665831943</v>
+      </c>
+      <c r="D145" t="n">
+        <v>0.3978590184259099</v>
+      </c>
+      <c r="E145" t="n">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>2020-12-09</t>
+        </is>
+      </c>
+      <c r="B146" t="n">
+        <v>22167887887</v>
+      </c>
+      <c r="C146" t="n">
+        <v>59426788696</v>
+      </c>
+      <c r="D146" t="n">
+        <v>0.3730285343265085</v>
+      </c>
+      <c r="E146" t="n">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>2020-12-10</t>
+        </is>
+      </c>
+      <c r="B147" t="n">
+        <v>21008686040</v>
+      </c>
+      <c r="C147" t="n">
+        <v>53530291688</v>
+      </c>
+      <c r="D147" t="n">
+        <v>0.3924635076238444</v>
+      </c>
+      <c r="E147" t="n">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>2020-12-11</t>
+        </is>
+      </c>
+      <c r="B148" t="n">
+        <v>24084146686</v>
+      </c>
+      <c r="C148" t="n">
+        <v>64194443337</v>
+      </c>
+      <c r="D148" t="n">
+        <v>0.3751749440300626</v>
+      </c>
+      <c r="E148" t="n">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>2020-12-14</t>
+        </is>
+      </c>
+      <c r="B149" t="n">
+        <v>20561369384</v>
+      </c>
+      <c r="C149" t="n">
+        <v>52737085483</v>
+      </c>
+      <c r="D149" t="n">
+        <v>0.3898844465082932</v>
+      </c>
+      <c r="E149" t="n">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>2020-12-15</t>
+        </is>
+      </c>
+      <c r="B150" t="n">
+        <v>20518702233</v>
+      </c>
+      <c r="C150" t="n">
+        <v>50712282528</v>
+      </c>
+      <c r="D150" t="n">
+        <v>0.4046101104139991</v>
+      </c>
+      <c r="E150" t="n">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>2020-12-16</t>
+        </is>
+      </c>
+      <c r="B151" t="n">
+        <v>20098821894</v>
+      </c>
+      <c r="C151" t="n">
+        <v>51594471274</v>
+      </c>
+      <c r="D151" t="n">
+        <v>0.3895537912824469</v>
+      </c>
+      <c r="E151" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>2020-12-17</t>
+        </is>
+      </c>
+      <c r="B152" t="n">
+        <v>23623180829</v>
+      </c>
+      <c r="C152" t="n">
+        <v>60346809075</v>
+      </c>
+      <c r="D152" t="n">
+        <v>0.3914569998165226</v>
+      </c>
+      <c r="E152" t="n">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>2020-12-18</t>
+        </is>
+      </c>
+      <c r="B153" t="n">
+        <v>24395319589</v>
+      </c>
+      <c r="C153" t="n">
+        <v>59011526731</v>
+      </c>
+      <c r="D153" t="n">
+        <v>0.4133992279204094</v>
+      </c>
+      <c r="E153" t="n">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>2020-12-21</t>
+        </is>
+      </c>
+      <c r="B154" t="n">
+        <v>25669905456</v>
+      </c>
+      <c r="C154" t="n">
+        <v>62473191028</v>
+      </c>
+      <c r="D154" t="n">
+        <v>0.410894737944392</v>
+      </c>
+      <c r="E154" t="n">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>2020-12-22</t>
+        </is>
+      </c>
+      <c r="B155" t="n">
+        <v>27752409533</v>
+      </c>
+      <c r="C155" t="n">
+        <v>70592976908</v>
+      </c>
+      <c r="D155" t="n">
+        <v>0.3931327271998773</v>
+      </c>
+      <c r="E155" t="n">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>2020-12-23</t>
+        </is>
+      </c>
+      <c r="B156" t="n">
+        <v>26781996550</v>
+      </c>
+      <c r="C156" t="n">
+        <v>66516491988</v>
+      </c>
+      <c r="D156" t="n">
+        <v>0.4026369363380084</v>
+      </c>
+      <c r="E156" t="n">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>2020-12-24</t>
+        </is>
+      </c>
+      <c r="B157" t="n">
+        <v>23869444669</v>
+      </c>
+      <c r="C157" t="n">
+        <v>63015856260</v>
+      </c>
+      <c r="D157" t="n">
+        <v>0.3787847390427572</v>
+      </c>
+      <c r="E157" t="n">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>2020-12-25</t>
+        </is>
+      </c>
+      <c r="B158" t="n">
+        <v>25870374333</v>
+      </c>
+      <c r="C158" t="n">
+        <v>63035613181</v>
+      </c>
+      <c r="D158" t="n">
+        <v>0.4104088629822002</v>
+      </c>
+      <c r="E158" t="n">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>2020-12-28</t>
+        </is>
+      </c>
+      <c r="B159" t="n">
+        <v>27591719605</v>
+      </c>
+      <c r="C159" t="n">
+        <v>68634054637</v>
+      </c>
+      <c r="D159" t="n">
+        <v>0.4020120878903394</v>
+      </c>
+      <c r="E159" t="n">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>2020-12-29</t>
+        </is>
+      </c>
+      <c r="B160" t="n">
+        <v>28714767727</v>
+      </c>
+      <c r="C160" t="n">
+        <v>68080937199</v>
+      </c>
+      <c r="D160" t="n">
+        <v>0.4217739782733451</v>
+      </c>
+      <c r="E160" t="n">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>2020-12-30</t>
+        </is>
+      </c>
+      <c r="B161" t="n">
+        <v>27431057672</v>
+      </c>
+      <c r="C161" t="n">
+        <v>63970764234</v>
+      </c>
+      <c r="D161" t="n">
+        <v>0.4288061585704895</v>
+      </c>
+      <c r="E161" t="n">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>2020-12-31</t>
+        </is>
+      </c>
+      <c r="B162" t="n">
+        <v>29516497306</v>
+      </c>
+      <c r="C162" t="n">
+        <v>70483427194</v>
+      </c>
+      <c r="D162" t="n">
+        <v>0.4187721636287379</v>
+      </c>
+      <c r="E162" t="n">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>2021-01-04</t>
+        </is>
+      </c>
+      <c r="B163" t="n">
+        <v>32842910849</v>
+      </c>
+      <c r="C163" t="n">
+        <v>81262611004</v>
+      </c>
+      <c r="D163" t="n">
+        <v>0.4041577109475767</v>
+      </c>
+      <c r="E163" t="n">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>2021-01-05</t>
+        </is>
+      </c>
+      <c r="B164" t="n">
+        <v>34955476638</v>
+      </c>
+      <c r="C164" t="n">
+        <v>86306603527</v>
+      </c>
+      <c r="D164" t="n">
+        <v>0.4050150881799513</v>
+      </c>
+      <c r="E164" t="n">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>2021-01-06</t>
+        </is>
+      </c>
+      <c r="B165" t="n">
+        <v>31318863380</v>
+      </c>
+      <c r="C165" t="n">
+        <v>79924024318</v>
+      </c>
+      <c r="D165" t="n">
+        <v>0.3918579381762507</v>
+      </c>
+      <c r="E165" t="n">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>2021-01-07</t>
+        </is>
+      </c>
+      <c r="B166" t="n">
+        <v>34820241307</v>
+      </c>
+      <c r="C166" t="n">
+        <v>87045282583</v>
+      </c>
+      <c r="D166" t="n">
+        <v>0.4000244501911746</v>
+      </c>
+      <c r="E166" t="n">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>2021-01-08</t>
+        </is>
+      </c>
+      <c r="B167" t="n">
+        <v>31741361539</v>
+      </c>
+      <c r="C167" t="n">
+        <v>76243328872</v>
+      </c>
+      <c r="D167" t="n">
+        <v>0.4163165749529185</v>
+      </c>
+      <c r="E167" t="n">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>2021-01-11</t>
+        </is>
+      </c>
+      <c r="B168" t="n">
+        <v>33861909952</v>
+      </c>
+      <c r="C168" t="n">
+        <v>79843929989</v>
+      </c>
+      <c r="D168" t="n">
+        <v>0.4241012429706943</v>
+      </c>
+      <c r="E168" t="n">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>2021-01-12</t>
+        </is>
+      </c>
+      <c r="B169" t="n">
+        <v>31336739617</v>
+      </c>
+      <c r="C169" t="n">
+        <v>70684174141</v>
+      </c>
+      <c r="D169" t="n">
+        <v>0.4433345936035105</v>
+      </c>
+      <c r="E169" t="n">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>2021-01-13</t>
+        </is>
+      </c>
+      <c r="B170" t="n">
+        <v>36176556832</v>
+      </c>
+      <c r="C170" t="n">
+        <v>81782457644</v>
+      </c>
+      <c r="D170" t="n">
+        <v>0.4423510600461162</v>
+      </c>
+      <c r="E170" t="n">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>2021-01-14</t>
+        </is>
+      </c>
+      <c r="B171" t="n">
+        <v>32971296424</v>
+      </c>
+      <c r="C171" t="n">
+        <v>74034016193</v>
+      </c>
+      <c r="D171" t="n">
+        <v>0.4453533405245341</v>
+      </c>
+      <c r="E171" t="n">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>2021-01-15</t>
+        </is>
+      </c>
+      <c r="B172" t="n">
+        <v>31268748151</v>
+      </c>
+      <c r="C172" t="n">
+        <v>68522530970</v>
+      </c>
+      <c r="D172" t="n">
+        <v>0.4563279801309417</v>
+      </c>
+      <c r="E172" t="n">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>2021-01-18</t>
+        </is>
+      </c>
+      <c r="B173" t="n">
+        <v>28025154838</v>
+      </c>
+      <c r="C173" t="n">
+        <v>66132336803</v>
+      </c>
+      <c r="D173" t="n">
+        <v>0.4237738479056539</v>
+      </c>
+      <c r="E173" t="n">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>2021-01-19</t>
+        </is>
+      </c>
+      <c r="B174" t="n">
+        <v>30160755219</v>
+      </c>
+      <c r="C174" t="n">
+        <v>71588657610</v>
+      </c>
+      <c r="D174" t="n">
+        <v>0.4213063385447102</v>
+      </c>
+      <c r="E174" t="n">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>2021-01-20</t>
+        </is>
+      </c>
+      <c r="B175" t="n">
+        <v>25498108632</v>
+      </c>
+      <c r="C175" t="n">
+        <v>61023142374</v>
+      </c>
+      <c r="D175" t="n">
+        <v>0.4178432581483041</v>
+      </c>
+      <c r="E175" t="n">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>2021-01-21</t>
+        </is>
+      </c>
+      <c r="B176" t="n">
+        <v>31550851527</v>
+      </c>
+      <c r="C176" t="n">
+        <v>73606094304</v>
+      </c>
+      <c r="D176" t="n">
+        <v>0.4286445548474839</v>
+      </c>
+      <c r="E176" t="n">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>2021-01-22</t>
+        </is>
+      </c>
+      <c r="B177" t="n">
+        <v>29587073243</v>
+      </c>
+      <c r="C177" t="n">
+        <v>71863919964</v>
+      </c>
+      <c r="D177" t="n">
+        <v>0.4117097043665521</v>
+      </c>
+      <c r="E177" t="n">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>2021-01-25</t>
+        </is>
+      </c>
+      <c r="B178" t="n">
+        <v>29768085597</v>
+      </c>
+      <c r="C178" t="n">
+        <v>72841620023</v>
+      </c>
+      <c r="D178" t="n">
+        <v>0.4086686373477226</v>
+      </c>
+      <c r="E178" t="n">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>2021-01-26</t>
+        </is>
+      </c>
+      <c r="B179" t="n">
+        <v>25588114580</v>
+      </c>
+      <c r="C179" t="n">
+        <v>62625061804</v>
+      </c>
+      <c r="D179" t="n">
+        <v>0.4085922447483418</v>
+      </c>
+      <c r="E179" t="n">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>2021-01-27</t>
+        </is>
+      </c>
+      <c r="B180" t="n">
+        <v>25604690493</v>
+      </c>
+      <c r="C180" t="n">
+        <v>60015878129</v>
+      </c>
+      <c r="D180" t="n">
+        <v>0.4266319396004584</v>
+      </c>
+      <c r="E180" t="n">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>2021-01-28</t>
+        </is>
+      </c>
+      <c r="B181" t="n">
+        <v>26286085867</v>
+      </c>
+      <c r="C181" t="n">
+        <v>62311898539</v>
+      </c>
+      <c r="D181" t="n">
+        <v>0.4218469743872106</v>
+      </c>
+      <c r="E181" t="n">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>2021-01-29</t>
+        </is>
+      </c>
+      <c r="B182" t="n">
+        <v>27002904913</v>
+      </c>
+      <c r="C182" t="n">
+        <v>66018503681</v>
+      </c>
+      <c r="D182" t="n">
+        <v>0.4090202504963981</v>
+      </c>
+      <c r="E182" t="n">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>2021-02-01</t>
+        </is>
+      </c>
+      <c r="B183" t="n">
+        <v>25457673045</v>
+      </c>
+      <c r="C183" t="n">
+        <v>61214730247</v>
+      </c>
+      <c r="D183" t="n">
+        <v>0.4158749526834291</v>
+      </c>
+      <c r="E183" t="n">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>2021-02-02</t>
+        </is>
+      </c>
+      <c r="B184" t="n">
+        <v>24585679056</v>
+      </c>
+      <c r="C184" t="n">
+        <v>59083806830</v>
+      </c>
+      <c r="D184" t="n">
+        <v>0.4161153516519274</v>
+      </c>
+      <c r="E184" t="n">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>2021-02-03</t>
+        </is>
+      </c>
+      <c r="B185" t="n">
+        <v>27946762653</v>
+      </c>
+      <c r="C185" t="n">
+        <v>64252239936</v>
+      </c>
+      <c r="D185" t="n">
+        <v>0.4349539048107436</v>
+      </c>
+      <c r="E185" t="n">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>2021-02-04</t>
+        </is>
+      </c>
+      <c r="B186" t="n">
+        <v>26745949814</v>
+      </c>
+      <c r="C186" t="n">
+        <v>65026335158</v>
+      </c>
+      <c r="D186" t="n">
+        <v>0.411309506356357</v>
+      </c>
+      <c r="E186" t="n">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>2021-02-05</t>
+        </is>
+      </c>
+      <c r="B187" t="n">
+        <v>27228530445</v>
+      </c>
+      <c r="C187" t="n">
+        <v>60817228192</v>
+      </c>
+      <c r="D187" t="n">
+        <v>0.44771080916479</v>
+      </c>
+      <c r="E187" t="n">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>2021-02-08</t>
+        </is>
+      </c>
+      <c r="B188" t="n">
+        <v>22845413099</v>
+      </c>
+      <c r="C188" t="n">
+        <v>53099229697</v>
+      </c>
+      <c r="D188" t="n">
+        <v>0.4302400096830542</v>
+      </c>
+      <c r="E188" t="n">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>2021-02-09</t>
+        </is>
+      </c>
+      <c r="B189" t="n">
+        <v>23052987297</v>
+      </c>
+      <c r="C189" t="n">
+        <v>54414450658</v>
+      </c>
+      <c r="D189" t="n">
+        <v>0.4236556101960896</v>
+      </c>
+      <c r="E189" t="n">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>2021-02-10</t>
+        </is>
+      </c>
+      <c r="B190" t="n">
+        <v>23672043794</v>
+      </c>
+      <c r="C190" t="n">
+        <v>53724833418</v>
+      </c>
+      <c r="D190" t="n">
+        <v>0.4406164205260971</v>
+      </c>
+      <c r="E190" t="n">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>2021-02-18</t>
+        </is>
+      </c>
+      <c r="B191" t="n">
+        <v>30305438799</v>
+      </c>
+      <c r="C191" t="n">
+        <v>70581483088</v>
+      </c>
+      <c r="D191" t="n">
+        <v>0.4293681213982937</v>
+      </c>
+      <c r="E191" t="n">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>2021-02-19</t>
+        </is>
+      </c>
+      <c r="B192" t="n">
+        <v>31871390359</v>
+      </c>
+      <c r="C192" t="n">
+        <v>74891926971</v>
+      </c>
+      <c r="D192" t="n">
+        <v>0.4255650995779744</v>
+      </c>
+      <c r="E192" t="n">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>2021-02-22</t>
+        </is>
+      </c>
+      <c r="B193" t="n">
+        <v>41800730539</v>
+      </c>
+      <c r="C193" t="n">
+        <v>98345390597</v>
+      </c>
+      <c r="D193" t="n">
+        <v>0.4250400581588124</v>
+      </c>
+      <c r="E193" t="n">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>2021-02-23</t>
+        </is>
+      </c>
+      <c r="B194" t="n">
+        <v>36659765914</v>
+      </c>
+      <c r="C194" t="n">
+        <v>79667225639</v>
+      </c>
+      <c r="D194" t="n">
+        <v>0.4601611970287279</v>
+      </c>
+      <c r="E194" t="n">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>2021-02-24</t>
+        </is>
+      </c>
+      <c r="B195" t="n">
+        <v>33328852498</v>
+      </c>
+      <c r="C195" t="n">
+        <v>74974298826</v>
+      </c>
+      <c r="D195" t="n">
+        <v>0.4445370349557979</v>
+      </c>
+      <c r="E195" t="n">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>2021-02-25</t>
+        </is>
+      </c>
+      <c r="B196" t="n">
+        <v>33009105938</v>
+      </c>
+      <c r="C196" t="n">
+        <v>72321851390</v>
+      </c>
+      <c r="D196" t="n">
+        <v>0.4564195371603028</v>
+      </c>
+      <c r="E196" t="n">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>2021-02-26</t>
+        </is>
+      </c>
+      <c r="B197" t="n">
+        <v>29437488128</v>
+      </c>
+      <c r="C197" t="n">
+        <v>67566280430</v>
+      </c>
+      <c r="D197" t="n">
+        <v>0.4356831238993216</v>
+      </c>
+      <c r="E197" t="n">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>2021-03-01</t>
+        </is>
+      </c>
+      <c r="B198" t="n">
+        <v>28022529242</v>
+      </c>
+      <c r="C198" t="n">
+        <v>65847760652</v>
+      </c>
+      <c r="D198" t="n">
+        <v>0.425565409734991</v>
+      </c>
+      <c r="E198" t="n">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>2021-03-02</t>
+        </is>
+      </c>
+      <c r="B199" t="n">
+        <v>30548474585</v>
+      </c>
+      <c r="C199" t="n">
+        <v>69441386639</v>
+      </c>
+      <c r="D199" t="n">
+        <v>0.4399174046424243</v>
+      </c>
+      <c r="E199" t="n">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>2021-03-03</t>
+        </is>
+      </c>
+      <c r="B200" t="n">
+        <v>31581683271</v>
+      </c>
+      <c r="C200" t="n">
+        <v>69999474895</v>
+      </c>
+      <c r="D200" t="n">
+        <v>0.4511702883253464</v>
+      </c>
+      <c r="E200" t="n">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>2021-03-04</t>
+        </is>
+      </c>
+      <c r="B201" t="n">
+        <v>36100282673</v>
+      </c>
+      <c r="C201" t="n">
+        <v>78562142790</v>
+      </c>
+      <c r="D201" t="n">
+        <v>0.4595124495203449</v>
+      </c>
+      <c r="E201" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>2021-03-05</t>
+        </is>
+      </c>
+      <c r="B202" t="n">
+        <v>32337135967</v>
+      </c>
+      <c r="C202" t="n">
+        <v>73514786011</v>
+      </c>
+      <c r="D202" t="n">
+        <v>0.4398725443091326</v>
+      </c>
+      <c r="E202" t="n">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>2021-03-08</t>
+        </is>
+      </c>
+      <c r="B203" t="n">
+        <v>34237890063</v>
+      </c>
+      <c r="C203" t="n">
+        <v>78814375242</v>
+      </c>
+      <c r="D203" t="n">
+        <v>0.4344117422471771</v>
+      </c>
+      <c r="E203" t="n">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>2021-03-09</t>
+        </is>
+      </c>
+      <c r="B204" t="n">
+        <v>35838361211</v>
+      </c>
+      <c r="C204" t="n">
+        <v>82850202998</v>
+      </c>
+      <c r="D204" t="n">
+        <v>0.4325681762284292</v>
+      </c>
+      <c r="E204" t="n">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>2021-03-10</t>
+        </is>
+      </c>
+      <c r="B205" t="n">
+        <v>26975456721</v>
+      </c>
+      <c r="C205" t="n">
+        <v>62127335207</v>
+      </c>
+      <c r="D205" t="n">
+        <v>0.4341962620981791</v>
+      </c>
+      <c r="E205" t="n">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>2021-03-11</t>
+        </is>
+      </c>
+      <c r="B206" t="n">
+        <v>30680047969</v>
+      </c>
+      <c r="C206" t="n">
+        <v>66598157167</v>
+      </c>
+      <c r="D206" t="n">
+        <v>0.4606741278451207</v>
+      </c>
+      <c r="E206" t="n">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>2021-03-12</t>
+        </is>
+      </c>
+      <c r="B207" t="n">
+        <v>33862968625</v>
+      </c>
+      <c r="C207" t="n">
+        <v>72238010975</v>
+      </c>
+      <c r="D207" t="n">
+        <v>0.4687693939513262</v>
+      </c>
+      <c r="E207" t="n">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>2021-03-15</t>
+        </is>
+      </c>
+      <c r="B208" t="n">
+        <v>34591765793</v>
+      </c>
+      <c r="C208" t="n">
+        <v>71723136959</v>
+      </c>
+      <c r="D208" t="n">
+        <v>0.4822957731585852</v>
+      </c>
+      <c r="E208" t="n">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>2021-03-16</t>
+        </is>
+      </c>
+      <c r="B209" t="n">
+        <v>29977825317</v>
+      </c>
+      <c r="C209" t="n">
+        <v>67049266583</v>
+      </c>
+      <c r="D209" t="n">
+        <v>0.447101465008429</v>
+      </c>
+      <c r="E209" t="n">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>2021-03-17</t>
+        </is>
+      </c>
+      <c r="B210" t="n">
+        <v>27491185060</v>
+      </c>
+      <c r="C210" t="n">
+        <v>62515062852</v>
+      </c>
+      <c r="D210" t="n">
+        <v>0.4397529780156095</v>
+      </c>
+      <c r="E210" t="n">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>2021-03-18</t>
+        </is>
+      </c>
+      <c r="B211" t="n">
+        <v>26739276351</v>
+      </c>
+      <c r="C211" t="n">
+        <v>62832911819</v>
+      </c>
+      <c r="D211" t="n">
+        <v>0.4255616296762858</v>
+      </c>
+      <c r="E211" t="n">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>2021-03-19</t>
+        </is>
+      </c>
+      <c r="B212" t="n">
+        <v>28358235249</v>
+      </c>
+      <c r="C212" t="n">
+        <v>65875538395</v>
+      </c>
+      <c r="D212" t="n">
+        <v>0.4304820262562349</v>
+      </c>
+      <c r="E212" t="n">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>2021-03-22</t>
+        </is>
+      </c>
+      <c r="B213" t="n">
+        <v>29121013208</v>
+      </c>
+      <c r="C213" t="n">
+        <v>67358226346</v>
+      </c>
+      <c r="D213" t="n">
+        <v>0.4323304633707791</v>
+      </c>
+      <c r="E213" t="n">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>2021-03-23</t>
+        </is>
+      </c>
+      <c r="B214" t="n">
+        <v>29320271653</v>
+      </c>
+      <c r="C214" t="n">
+        <v>70323191299</v>
+      </c>
+      <c r="D214" t="n">
+        <v>0.4169360222623591</v>
+      </c>
+      <c r="E214" t="n">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>2021-03-24</t>
+        </is>
+      </c>
+      <c r="B215" t="n">
+        <v>28494202046</v>
+      </c>
+      <c r="C215" t="n">
+        <v>67303523996</v>
+      </c>
+      <c r="D215" t="n">
+        <v>0.423368649280437</v>
+      </c>
+      <c r="E215" t="n">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>2021-03-25</t>
+        </is>
+      </c>
+      <c r="B216" t="n">
+        <v>25857769578</v>
+      </c>
+      <c r="C216" t="n">
+        <v>60650502617</v>
+      </c>
+      <c r="D216" t="n">
+        <v>0.426340565407816</v>
+      </c>
+      <c r="E216" t="n">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>2021-03-26</t>
+        </is>
+      </c>
+      <c r="B217" t="n">
+        <v>25857588064</v>
+      </c>
+      <c r="C217" t="n">
+        <v>61284664475</v>
+      </c>
+      <c r="D217" t="n">
+        <v>0.4219259138564452</v>
+      </c>
+      <c r="E217" t="n">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>2021-03-29</t>
+        </is>
+      </c>
+      <c r="B218" t="n">
+        <v>26030305012</v>
+      </c>
+      <c r="C218" t="n">
+        <v>62965892538</v>
+      </c>
+      <c r="D218" t="n">
+        <v>0.4134032563151658</v>
+      </c>
+      <c r="E218" t="n">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>2021-03-30</t>
+        </is>
+      </c>
+      <c r="B219" t="n">
+        <v>25780001010</v>
+      </c>
+      <c r="C219" t="n">
+        <v>62868502600</v>
+      </c>
+      <c r="D219" t="n">
+        <v>0.4100622719460158</v>
+      </c>
+      <c r="E219" t="n">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>2021-03-31</t>
+        </is>
+      </c>
+      <c r="B220" t="n">
+        <v>25340940136</v>
+      </c>
+      <c r="C220" t="n">
+        <v>58944651908</v>
+      </c>
+      <c r="D220" t="n">
+        <v>0.4299107606157687</v>
+      </c>
+      <c r="E220" t="n">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>2021-04-01</t>
+        </is>
+      </c>
+      <c r="B221" t="n">
+        <v>24459982838</v>
+      </c>
+      <c r="C221" t="n">
+        <v>57742915146</v>
+      </c>
+      <c r="D221" t="n">
+        <v>0.4236014544148696</v>
+      </c>
+      <c r="E221" t="n">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>2021-04-02</t>
+        </is>
+      </c>
+      <c r="B222" t="n">
+        <v>23776468616</v>
+      </c>
+      <c r="C222" t="n">
+        <v>57637646459</v>
+      </c>
+      <c r="D222" t="n">
+        <v>0.4125162992717471</v>
+      </c>
+      <c r="E222" t="n">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>2021-04-06</t>
+        </is>
+      </c>
+      <c r="B223" t="n">
+        <v>21609152872</v>
+      </c>
+      <c r="C223" t="n">
+        <v>54009467026</v>
+      </c>
+      <c r="D223" t="n">
+        <v>0.4000993540928189</v>
+      </c>
+      <c r="E223" t="n">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>2021-04-07</t>
+        </is>
+      </c>
+      <c r="B224" t="n">
+        <v>28192988226</v>
+      </c>
+      <c r="C224" t="n">
+        <v>64777711487</v>
+      </c>
+      <c r="D224" t="n">
+        <v>0.4352266787266473</v>
+      </c>
+      <c r="E224" t="n">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>2021-04-08</t>
+        </is>
+      </c>
+      <c r="B225" t="n">
+        <v>31610774016</v>
+      </c>
+      <c r="C225" t="n">
+        <v>70183037971</v>
+      </c>
+      <c r="D225" t="n">
+        <v>0.4504047549076137</v>
+      </c>
+      <c r="E225" t="n">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>2021-04-09</t>
+        </is>
+      </c>
+      <c r="B226" t="n">
+        <v>27363203695</v>
+      </c>
+      <c r="C226" t="n">
+        <v>60908586933</v>
+      </c>
+      <c r="D226" t="n">
+        <v>0.4492503450309851</v>
+      </c>
+      <c r="E226" t="n">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>2021-04-12</t>
+        </is>
+      </c>
+      <c r="B227" t="n">
+        <v>29441281600</v>
+      </c>
+      <c r="C227" t="n">
+        <v>66662877908</v>
+      </c>
+      <c r="D227" t="n">
+        <v>0.4416443232563598</v>
+      </c>
+      <c r="E227" t="n">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>2021-04-13</t>
+        </is>
+      </c>
+      <c r="B228" t="n">
+        <v>26500289609</v>
+      </c>
+      <c r="C228" t="n">
+        <v>60099497250</v>
+      </c>
+      <c r="D228" t="n">
+        <v>0.4409402877159675</v>
+      </c>
+      <c r="E228" t="n">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>2021-04-14</t>
+        </is>
+      </c>
+      <c r="B229" t="n">
+        <v>24875678254</v>
+      </c>
+      <c r="C229" t="n">
+        <v>56149660115</v>
+      </c>
+      <c r="D229" t="n">
+        <v>0.4430245562137362</v>
+      </c>
+      <c r="E229" t="n">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>2021-04-15</t>
+        </is>
+      </c>
+      <c r="B230" t="n">
+        <v>23587218127</v>
+      </c>
+      <c r="C230" t="n">
+        <v>56730832399</v>
+      </c>
+      <c r="D230" t="n">
+        <v>0.4157742294543835</v>
+      </c>
+      <c r="E230" t="n">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>2021-04-16</t>
+        </is>
+      </c>
+      <c r="B231" t="n">
+        <v>23064238930</v>
+      </c>
+      <c r="C231" t="n">
+        <v>60757105467</v>
+      </c>
+      <c r="D231" t="n">
+        <v>0.3796138534368998</v>
+      </c>
+      <c r="E231" t="n">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>2021-04-19</t>
+        </is>
+      </c>
+      <c r="B232" t="n">
+        <v>26349229565</v>
+      </c>
+      <c r="C232" t="n">
+        <v>68717257011</v>
+      </c>
+      <c r="D232" t="n">
+        <v>0.3834441406877186</v>
+      </c>
+      <c r="E232" t="n">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>2021-04-20</t>
+        </is>
+      </c>
+      <c r="B233" t="n">
+        <v>26332452757</v>
+      </c>
+      <c r="C233" t="n">
+        <v>66152179163</v>
+      </c>
+      <c r="D233" t="n">
+        <v>0.3980587350284626</v>
+      </c>
+      <c r="E233" t="n">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>2021-04-21</t>
+        </is>
+      </c>
+      <c r="B234" t="n">
+        <v>23796108657</v>
+      </c>
+      <c r="C234" t="n">
+        <v>58645267418</v>
+      </c>
+      <c r="D234" t="n">
+        <v>0.4057634947316526</v>
+      </c>
+      <c r="E234" t="n">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>2021-04-22</t>
+        </is>
+      </c>
+      <c r="B235" t="n">
+        <v>23283868400</v>
+      </c>
+      <c r="C235" t="n">
+        <v>57343158813</v>
+      </c>
+      <c r="D235" t="n">
+        <v>0.406044398006226</v>
+      </c>
+      <c r="E235" t="n">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>2021-04-23</t>
+        </is>
+      </c>
+      <c r="B236" t="n">
+        <v>23110619160</v>
+      </c>
+      <c r="C236" t="n">
+        <v>58758936747</v>
+      </c>
+      <c r="D236" t="n">
+        <v>0.3933124123655954</v>
+      </c>
+      <c r="E236" t="n">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>2021-04-26</t>
+        </is>
+      </c>
+      <c r="B237" t="n">
+        <v>26080656908</v>
+      </c>
+      <c r="C237" t="n">
+        <v>64990659217</v>
+      </c>
+      <c r="D237" t="n">
+        <v>0.4012985438556365</v>
+      </c>
+      <c r="E237" t="n">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>2021-04-27</t>
+        </is>
+      </c>
+      <c r="B238" t="n">
+        <v>22805398723</v>
+      </c>
+      <c r="C238" t="n">
+        <v>58465572266</v>
+      </c>
+      <c r="D238" t="n">
+        <v>0.3900654323409783</v>
+      </c>
+      <c r="E238" t="n">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>2021-04-28</t>
+        </is>
+      </c>
+      <c r="B239" t="n">
+        <v>21764975470</v>
+      </c>
+      <c r="C239" t="n">
+        <v>56258757783</v>
+      </c>
+      <c r="D239" t="n">
+        <v>0.3868726635229197</v>
+      </c>
+      <c r="E239" t="n">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>2021-04-29</t>
+        </is>
+      </c>
+      <c r="B240" t="n">
+        <v>23871290845</v>
+      </c>
+      <c r="C240" t="n">
+        <v>59672070298</v>
+      </c>
+      <c r="D240" t="n">
+        <v>0.400041270996426</v>
+      </c>
+      <c r="E240" t="n">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>2021-04-30</t>
+        </is>
+      </c>
+      <c r="B241" t="n">
+        <v>26727927563</v>
+      </c>
+      <c r="C241" t="n">
+        <v>64623812735</v>
+      </c>
+      <c r="D241" t="n">
+        <v>0.413592550978105</v>
+      </c>
+      <c r="E241" t="n">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>2021-05-06</t>
+        </is>
+      </c>
+      <c r="B242" t="n">
+        <v>28245158344</v>
+      </c>
+      <c r="C242" t="n">
+        <v>64995398044</v>
+      </c>
+      <c r="D242" t="n">
+        <v>0.4345716649797089</v>
+      </c>
+      <c r="E242" t="n">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>2021-05-07</t>
+        </is>
+      </c>
+      <c r="B243" t="n">
+        <v>33809492530</v>
+      </c>
+      <c r="C243" t="n">
+        <v>72689004129</v>
+      </c>
+      <c r="D243" t="n">
+        <v>0.4651252680529072</v>
+      </c>
+      <c r="E243" t="n">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>2021-05-10</t>
+        </is>
+      </c>
+      <c r="B244" t="n">
+        <v>34980447442</v>
+      </c>
+      <c r="C244" t="n">
+        <v>74391256531</v>
+      </c>
+      <c r="D244" t="n">
+        <v>0.4702225647636843</v>
+      </c>
+      <c r="E244" t="n">
+        <v>243</v>
       </c>
     </row>
   </sheetData>

--- a/king_index/output/index.xlsx
+++ b/king_index/output/index.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E244"/>
+  <dimension ref="A1:E245"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1054,10 +1054,10 @@
         <v>21417149307</v>
       </c>
       <c r="C33" t="n">
-        <v>56930673694</v>
+        <v>56906481203</v>
       </c>
       <c r="D33" t="n">
-        <v>0.3761970115111633</v>
+        <v>0.3763569430799901</v>
       </c>
       <c r="E33" t="n">
         <v>32</v>
@@ -5070,6 +5070,25 @@
       </c>
       <c r="E244" t="n">
         <v>243</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>2021-05-11</t>
+        </is>
+      </c>
+      <c r="B245" t="n">
+        <v>33682768573</v>
+      </c>
+      <c r="C245" t="n">
+        <v>73459473614</v>
+      </c>
+      <c r="D245" t="n">
+        <v>0.4585217796412401</v>
+      </c>
+      <c r="E245" t="n">
+        <v>244</v>
       </c>
     </row>
   </sheetData>

--- a/king_index/output/index.xlsx
+++ b/king_index/output/index.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E245"/>
+  <dimension ref="A1:E244"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -458,17 +458,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2020-05-11</t>
+          <t>2020-05-13</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>21498726052</v>
+        <v>18559780599</v>
       </c>
       <c r="C2" t="n">
-        <v>57016622412</v>
+        <v>47805428174</v>
       </c>
       <c r="D2" t="n">
-        <v>0.3770606735813111</v>
+        <v>0.3882358407385656</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>
@@ -477,17 +477,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2020-05-12</t>
+          <t>2020-05-14</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>19188815582</v>
+        <v>20187004918</v>
       </c>
       <c r="C3" t="n">
-        <v>50239129593</v>
+        <v>51752238810</v>
       </c>
       <c r="D3" t="n">
-        <v>0.3819496025797717</v>
+        <v>0.3900701763282808</v>
       </c>
       <c r="E3" t="n">
         <v>2</v>
@@ -496,17 +496,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2020-05-13</t>
+          <t>2020-05-15</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>18559780599</v>
+        <v>19718626995</v>
       </c>
       <c r="C4" t="n">
-        <v>47805428174</v>
+        <v>50182102488</v>
       </c>
       <c r="D4" t="n">
-        <v>0.3882358407385656</v>
+        <v>0.3929414276676689</v>
       </c>
       <c r="E4" t="n">
         <v>3</v>
@@ -515,17 +515,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2020-05-14</t>
+          <t>2020-05-18</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>20187004918</v>
+        <v>22559505827</v>
       </c>
       <c r="C5" t="n">
-        <v>51752238810</v>
+        <v>58319431318</v>
       </c>
       <c r="D5" t="n">
-        <v>0.3900701763282808</v>
+        <v>0.3868265742165617</v>
       </c>
       <c r="E5" t="n">
         <v>4</v>
@@ -534,17 +534,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2020-05-15</t>
+          <t>2020-05-19</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>19718626995</v>
+        <v>18863773358</v>
       </c>
       <c r="C6" t="n">
-        <v>50182102488</v>
+        <v>50302048430</v>
       </c>
       <c r="D6" t="n">
-        <v>0.3929414276676689</v>
+        <v>0.3750100432639578</v>
       </c>
       <c r="E6" t="n">
         <v>5</v>
@@ -553,17 +553,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2020-05-18</t>
+          <t>2020-05-20</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>22559505827</v>
+        <v>21259230267</v>
       </c>
       <c r="C7" t="n">
-        <v>58319431318</v>
+        <v>55292303555</v>
       </c>
       <c r="D7" t="n">
-        <v>0.3868265742165617</v>
+        <v>0.3844880553014609</v>
       </c>
       <c r="E7" t="n">
         <v>6</v>
@@ -572,17 +572,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2020-05-19</t>
+          <t>2020-05-21</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>18863773358</v>
+        <v>19280128498</v>
       </c>
       <c r="C8" t="n">
-        <v>50302048430</v>
+        <v>52065201803</v>
       </c>
       <c r="D8" t="n">
-        <v>0.3750100432639578</v>
+        <v>0.370307380560063</v>
       </c>
       <c r="E8" t="n">
         <v>7</v>
@@ -591,17 +591,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2020-05-20</t>
+          <t>2020-05-22</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>21259230267</v>
+        <v>17897770797</v>
       </c>
       <c r="C9" t="n">
-        <v>55292303555</v>
+        <v>50417741953</v>
       </c>
       <c r="D9" t="n">
-        <v>0.3844880553014609</v>
+        <v>0.3549895355028892</v>
       </c>
       <c r="E9" t="n">
         <v>8</v>
@@ -610,17 +610,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2020-05-21</t>
+          <t>2020-05-25</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>19280128498</v>
+        <v>14723899014</v>
       </c>
       <c r="C10" t="n">
-        <v>52065201803</v>
+        <v>41053704521</v>
       </c>
       <c r="D10" t="n">
-        <v>0.370307380560063</v>
+        <v>0.3586497049606901</v>
       </c>
       <c r="E10" t="n">
         <v>9</v>
@@ -629,17 +629,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2020-05-22</t>
+          <t>2020-05-26</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>17897770797</v>
+        <v>15738642741</v>
       </c>
       <c r="C11" t="n">
-        <v>50417741953</v>
+        <v>44120432080</v>
       </c>
       <c r="D11" t="n">
-        <v>0.3549895355028892</v>
+        <v>0.3567200500770799</v>
       </c>
       <c r="E11" t="n">
         <v>10</v>
@@ -648,17 +648,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2020-05-25</t>
+          <t>2020-05-27</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>14723899014</v>
+        <v>17872745345</v>
       </c>
       <c r="C12" t="n">
-        <v>41053704521</v>
+        <v>48783198139</v>
       </c>
       <c r="D12" t="n">
-        <v>0.3586497049606901</v>
+        <v>0.366370923326397</v>
       </c>
       <c r="E12" t="n">
         <v>11</v>
@@ -667,17 +667,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2020-05-26</t>
+          <t>2020-05-28</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>15738642741</v>
+        <v>18416635989</v>
       </c>
       <c r="C13" t="n">
-        <v>44120432080</v>
+        <v>50047777669</v>
       </c>
       <c r="D13" t="n">
-        <v>0.3567200500770799</v>
+        <v>0.3679810942016595</v>
       </c>
       <c r="E13" t="n">
         <v>12</v>
@@ -686,17 +686,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2020-05-27</t>
+          <t>2020-05-29</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>17872745345</v>
+        <v>18782496399</v>
       </c>
       <c r="C14" t="n">
-        <v>48783198139</v>
+        <v>49396386216</v>
       </c>
       <c r="D14" t="n">
-        <v>0.366370923326397</v>
+        <v>0.3802402936293375</v>
       </c>
       <c r="E14" t="n">
         <v>13</v>
@@ -705,17 +705,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2020-05-28</t>
+          <t>2020-06-01</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>18416635989</v>
+        <v>22806246928</v>
       </c>
       <c r="C15" t="n">
-        <v>50047777669</v>
+        <v>64259168243</v>
       </c>
       <c r="D15" t="n">
-        <v>0.3679810942016595</v>
+        <v>0.3549103972487906</v>
       </c>
       <c r="E15" t="n">
         <v>14</v>
@@ -724,17 +724,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2020-05-29</t>
+          <t>2020-06-02</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>18782496399</v>
+        <v>26690797837</v>
       </c>
       <c r="C16" t="n">
-        <v>49396386216</v>
+        <v>67019269521</v>
       </c>
       <c r="D16" t="n">
-        <v>0.3802402936293375</v>
+        <v>0.3982555767582133</v>
       </c>
       <c r="E16" t="n">
         <v>15</v>
@@ -743,17 +743,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2020-06-01</t>
+          <t>2020-06-03</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>22806246928</v>
+        <v>25988325662</v>
       </c>
       <c r="C17" t="n">
-        <v>64259168243</v>
+        <v>66814592975</v>
       </c>
       <c r="D17" t="n">
-        <v>0.3549103972487906</v>
+        <v>0.3889618196390726</v>
       </c>
       <c r="E17" t="n">
         <v>16</v>
@@ -762,17 +762,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2020-06-02</t>
+          <t>2020-06-04</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>26690797837</v>
+        <v>22648232850</v>
       </c>
       <c r="C18" t="n">
-        <v>67019269521</v>
+        <v>57964700247</v>
       </c>
       <c r="D18" t="n">
-        <v>0.3982555767582133</v>
+        <v>0.3907245746720164</v>
       </c>
       <c r="E18" t="n">
         <v>17</v>
@@ -781,17 +781,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2020-06-03</t>
+          <t>2020-06-05</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>25988325662</v>
+        <v>21624249509</v>
       </c>
       <c r="C19" t="n">
-        <v>66814592975</v>
+        <v>55387084107</v>
       </c>
       <c r="D19" t="n">
-        <v>0.3889618196390726</v>
+        <v>0.3904204356962539</v>
       </c>
       <c r="E19" t="n">
         <v>18</v>
@@ -800,17 +800,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2020-06-04</t>
+          <t>2020-06-08</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>22648232850</v>
+        <v>23546771032</v>
       </c>
       <c r="C20" t="n">
-        <v>57964700247</v>
+        <v>58352042780</v>
       </c>
       <c r="D20" t="n">
-        <v>0.3907245746720164</v>
+        <v>0.4035295065980208</v>
       </c>
       <c r="E20" t="n">
         <v>19</v>
@@ -819,17 +819,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2020-06-05</t>
+          <t>2020-06-09</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>21624249509</v>
+        <v>20955198305</v>
       </c>
       <c r="C21" t="n">
-        <v>55387084107</v>
+        <v>53192911283</v>
       </c>
       <c r="D21" t="n">
-        <v>0.3904204356962539</v>
+        <v>0.3939471970900961</v>
       </c>
       <c r="E21" t="n">
         <v>20</v>
@@ -838,17 +838,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2020-06-08</t>
+          <t>2020-06-10</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>23546771032</v>
+        <v>20190478240</v>
       </c>
       <c r="C22" t="n">
-        <v>58352042780</v>
+        <v>52136701032</v>
       </c>
       <c r="D22" t="n">
-        <v>0.4035295065980208</v>
+        <v>0.3872603720670333</v>
       </c>
       <c r="E22" t="n">
         <v>21</v>
@@ -857,17 +857,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2020-06-09</t>
+          <t>2020-06-11</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>20955198305</v>
+        <v>21856153332</v>
       </c>
       <c r="C23" t="n">
-        <v>53192911283</v>
+        <v>58580995849</v>
       </c>
       <c r="D23" t="n">
-        <v>0.3939471970900961</v>
+        <v>0.3730928949780408</v>
       </c>
       <c r="E23" t="n">
         <v>22</v>
@@ -876,17 +876,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2020-06-10</t>
+          <t>2020-06-12</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>20190478240</v>
+        <v>22554032456</v>
       </c>
       <c r="C24" t="n">
-        <v>52136701032</v>
+        <v>58624630321</v>
       </c>
       <c r="D24" t="n">
-        <v>0.3872603720670333</v>
+        <v>0.3847193975041731</v>
       </c>
       <c r="E24" t="n">
         <v>23</v>
@@ -895,17 +895,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2020-06-11</t>
+          <t>2020-06-15</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>21856153332</v>
+        <v>24160399741</v>
       </c>
       <c r="C25" t="n">
-        <v>58580995849</v>
+        <v>62827231135</v>
       </c>
       <c r="D25" t="n">
-        <v>0.3730928949780408</v>
+        <v>0.3845529924609497</v>
       </c>
       <c r="E25" t="n">
         <v>24</v>
@@ -914,17 +914,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2020-06-12</t>
+          <t>2020-06-16</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>22554032456</v>
+        <v>22302612612</v>
       </c>
       <c r="C26" t="n">
-        <v>58624630321</v>
+        <v>57871475779</v>
       </c>
       <c r="D26" t="n">
-        <v>0.3847193975041731</v>
+        <v>0.3853817845801855</v>
       </c>
       <c r="E26" t="n">
         <v>25</v>
@@ -933,17 +933,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2020-06-15</t>
+          <t>2020-06-17</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>24160399741</v>
+        <v>23156031895</v>
       </c>
       <c r="C27" t="n">
-        <v>62827231135</v>
+        <v>61386131654</v>
       </c>
       <c r="D27" t="n">
-        <v>0.3845529924609497</v>
+        <v>0.3772192720257707</v>
       </c>
       <c r="E27" t="n">
         <v>26</v>
@@ -952,17 +952,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2020-06-16</t>
+          <t>2020-06-18</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>22302612612</v>
+        <v>25733088111</v>
       </c>
       <c r="C28" t="n">
-        <v>57871475779</v>
+        <v>63354121102</v>
       </c>
       <c r="D28" t="n">
-        <v>0.3853817845801855</v>
+        <v>0.4061785983830442</v>
       </c>
       <c r="E28" t="n">
         <v>27</v>
@@ -971,17 +971,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2020-06-17</t>
+          <t>2020-06-19</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>23156031895</v>
+        <v>24126480724</v>
       </c>
       <c r="C29" t="n">
-        <v>61386131654</v>
+        <v>61888832308</v>
       </c>
       <c r="D29" t="n">
-        <v>0.3772192720257707</v>
+        <v>0.3898357720489956</v>
       </c>
       <c r="E29" t="n">
         <v>28</v>
@@ -990,17 +990,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2020-06-18</t>
+          <t>2020-06-22</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>25733088111</v>
+        <v>25010112764</v>
       </c>
       <c r="C30" t="n">
-        <v>63354121102</v>
+        <v>63846785740</v>
       </c>
       <c r="D30" t="n">
-        <v>0.4061785983830442</v>
+        <v>0.3917207808369149</v>
       </c>
       <c r="E30" t="n">
         <v>29</v>
@@ -1009,17 +1009,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2020-06-19</t>
+          <t>2020-06-23</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>24126480724</v>
+        <v>21417149307</v>
       </c>
       <c r="C31" t="n">
-        <v>61888832308</v>
+        <v>56906481203</v>
       </c>
       <c r="D31" t="n">
-        <v>0.3898357720489956</v>
+        <v>0.3763569430799901</v>
       </c>
       <c r="E31" t="n">
         <v>30</v>
@@ -1028,17 +1028,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2020-06-22</t>
+          <t>2020-06-24</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>25010112764</v>
+        <v>19322024502</v>
       </c>
       <c r="C32" t="n">
-        <v>63846785740</v>
+        <v>52926747938</v>
       </c>
       <c r="D32" t="n">
-        <v>0.3917207808369149</v>
+        <v>0.3650710700123576</v>
       </c>
       <c r="E32" t="n">
         <v>31</v>
@@ -1047,17 +1047,17 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2020-06-23</t>
+          <t>2020-06-29</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>21417149307</v>
+        <v>20448932009</v>
       </c>
       <c r="C33" t="n">
-        <v>56906481203</v>
+        <v>54347085975</v>
       </c>
       <c r="D33" t="n">
-        <v>0.3763569430799901</v>
+        <v>0.3762654729713868</v>
       </c>
       <c r="E33" t="n">
         <v>32</v>
@@ -1066,17 +1066,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2020-06-24</t>
+          <t>2020-06-30</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>19322024502</v>
+        <v>20003048931</v>
       </c>
       <c r="C34" t="n">
-        <v>52926747938</v>
+        <v>53946886834</v>
       </c>
       <c r="D34" t="n">
-        <v>0.3650710700123576</v>
+        <v>0.3707915341352578</v>
       </c>
       <c r="E34" t="n">
         <v>33</v>
@@ -1085,17 +1085,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2020-06-29</t>
+          <t>2020-07-01</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>20448932009</v>
+        <v>25539868441</v>
       </c>
       <c r="C35" t="n">
-        <v>54347085975</v>
+        <v>66477208273</v>
       </c>
       <c r="D35" t="n">
-        <v>0.3762654729713868</v>
+        <v>0.3841898464826647</v>
       </c>
       <c r="E35" t="n">
         <v>34</v>
@@ -1104,17 +1104,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2020-06-30</t>
+          <t>2020-07-02</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>20003048931</v>
+        <v>35281401239</v>
       </c>
       <c r="C36" t="n">
-        <v>53946886834</v>
+        <v>86277275738</v>
       </c>
       <c r="D36" t="n">
-        <v>0.3707915341352578</v>
+        <v>0.4089304041789609</v>
       </c>
       <c r="E36" t="n">
         <v>35</v>
@@ -1123,17 +1123,17 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2020-07-01</t>
+          <t>2020-07-03</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>25539868441</v>
+        <v>39589081860</v>
       </c>
       <c r="C37" t="n">
-        <v>66477208273</v>
+        <v>96590527098</v>
       </c>
       <c r="D37" t="n">
-        <v>0.3841898464826647</v>
+        <v>0.4098650566409398</v>
       </c>
       <c r="E37" t="n">
         <v>36</v>
@@ -1142,17 +1142,17 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2020-07-02</t>
+          <t>2020-07-06</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>35281401239</v>
+        <v>51680326902</v>
       </c>
       <c r="C38" t="n">
-        <v>86277275738</v>
+        <v>132721246132</v>
       </c>
       <c r="D38" t="n">
-        <v>0.4089304041789609</v>
+        <v>0.3893900065600689</v>
       </c>
       <c r="E38" t="n">
         <v>37</v>
@@ -1161,17 +1161,17 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2020-07-03</t>
+          <t>2020-07-07</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>39589081860</v>
+        <v>54130474812</v>
       </c>
       <c r="C39" t="n">
-        <v>96590527098</v>
+        <v>140540263998</v>
       </c>
       <c r="D39" t="n">
-        <v>0.4098650566409398</v>
+        <v>0.3851599055824338</v>
       </c>
       <c r="E39" t="n">
         <v>38</v>
@@ -1180,17 +1180,17 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2020-07-06</t>
+          <t>2020-07-08</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>51680326902</v>
+        <v>48763694238</v>
       </c>
       <c r="C40" t="n">
-        <v>132721246132</v>
+        <v>124820435614</v>
       </c>
       <c r="D40" t="n">
-        <v>0.3893900065600689</v>
+        <v>0.3906707583427999</v>
       </c>
       <c r="E40" t="n">
         <v>39</v>
@@ -1199,17 +1199,17 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2020-07-07</t>
+          <t>2020-07-09</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>54130474812</v>
+        <v>50352644938</v>
       </c>
       <c r="C41" t="n">
-        <v>140540263998</v>
+        <v>137276438768</v>
       </c>
       <c r="D41" t="n">
-        <v>0.3851599055824338</v>
+        <v>0.3667974299879457</v>
       </c>
       <c r="E41" t="n">
         <v>40</v>
@@ -1218,17 +1218,17 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2020-07-08</t>
+          <t>2020-07-10</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>48763694238</v>
+        <v>45792064703</v>
       </c>
       <c r="C42" t="n">
-        <v>124820435614</v>
+        <v>124540979573</v>
       </c>
       <c r="D42" t="n">
-        <v>0.3906707583427999</v>
+        <v>0.3676867233580644</v>
       </c>
       <c r="E42" t="n">
         <v>41</v>
@@ -1237,17 +1237,17 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2020-07-09</t>
+          <t>2020-07-13</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>50352644938</v>
+        <v>45569190970</v>
       </c>
       <c r="C43" t="n">
-        <v>137276438768</v>
+        <v>125874117474</v>
       </c>
       <c r="D43" t="n">
-        <v>0.3667974299879457</v>
+        <v>0.3620219301987366</v>
       </c>
       <c r="E43" t="n">
         <v>42</v>
@@ -1256,17 +1256,17 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2020-07-10</t>
+          <t>2020-07-14</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>45792064703</v>
+        <v>44404671526</v>
       </c>
       <c r="C44" t="n">
-        <v>124540979573</v>
+        <v>127205292718</v>
       </c>
       <c r="D44" t="n">
-        <v>0.3676867233580644</v>
+        <v>0.3490788046409375</v>
       </c>
       <c r="E44" t="n">
         <v>43</v>
@@ -1275,17 +1275,17 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2020-07-13</t>
+          <t>2020-07-15</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>45569190970</v>
+        <v>40948010990</v>
       </c>
       <c r="C45" t="n">
-        <v>125874117474</v>
+        <v>115744357395</v>
       </c>
       <c r="D45" t="n">
-        <v>0.3620219301987366</v>
+        <v>0.3537797600815822</v>
       </c>
       <c r="E45" t="n">
         <v>44</v>
@@ -1294,17 +1294,17 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2020-07-14</t>
+          <t>2020-07-16</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>44404671526</v>
+        <v>41327517137</v>
       </c>
       <c r="C46" t="n">
-        <v>127205292718</v>
+        <v>110570972319</v>
       </c>
       <c r="D46" t="n">
-        <v>0.3490788046409375</v>
+        <v>0.373764617152584</v>
       </c>
       <c r="E46" t="n">
         <v>45</v>
@@ -1313,17 +1313,17 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2020-07-15</t>
+          <t>2020-07-17</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>40948010990</v>
+        <v>30786629717</v>
       </c>
       <c r="C47" t="n">
-        <v>115744357395</v>
+        <v>83073812068</v>
       </c>
       <c r="D47" t="n">
-        <v>0.3537797600815822</v>
+        <v>0.3705936798927636</v>
       </c>
       <c r="E47" t="n">
         <v>46</v>
@@ -1332,17 +1332,17 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2020-07-16</t>
+          <t>2020-07-20</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>41327517137</v>
+        <v>33302406491</v>
       </c>
       <c r="C48" t="n">
-        <v>110570972319</v>
+        <v>90725025902</v>
       </c>
       <c r="D48" t="n">
-        <v>0.373764617152584</v>
+        <v>0.3670696829226903</v>
       </c>
       <c r="E48" t="n">
         <v>47</v>
@@ -1351,17 +1351,17 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2020-07-17</t>
+          <t>2020-07-21</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>30786629717</v>
+        <v>29750727633</v>
       </c>
       <c r="C49" t="n">
-        <v>83073812068</v>
+        <v>82804408460</v>
       </c>
       <c r="D49" t="n">
-        <v>0.3705936798927636</v>
+        <v>0.3592891753749025</v>
       </c>
       <c r="E49" t="n">
         <v>48</v>
@@ -1370,17 +1370,17 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2020-07-20</t>
+          <t>2020-07-22</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>33302406491</v>
+        <v>32546369994</v>
       </c>
       <c r="C50" t="n">
-        <v>90725025902</v>
+        <v>88951002081</v>
       </c>
       <c r="D50" t="n">
-        <v>0.3670696829226903</v>
+        <v>0.3658909875389917</v>
       </c>
       <c r="E50" t="n">
         <v>49</v>
@@ -1389,17 +1389,17 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2020-07-21</t>
+          <t>2020-07-23</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>29750727633</v>
+        <v>33380341470</v>
       </c>
       <c r="C51" t="n">
-        <v>82804408460</v>
+        <v>92918126099</v>
       </c>
       <c r="D51" t="n">
-        <v>0.3592891753749025</v>
+        <v>0.3592446691664313</v>
       </c>
       <c r="E51" t="n">
         <v>50</v>
@@ -1408,17 +1408,17 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2020-07-22</t>
+          <t>2020-07-24</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>32546369994</v>
+        <v>34826858650</v>
       </c>
       <c r="C52" t="n">
-        <v>88951002081</v>
+        <v>98778010270</v>
       </c>
       <c r="D52" t="n">
-        <v>0.3658909875389917</v>
+        <v>0.3525770417404056</v>
       </c>
       <c r="E52" t="n">
         <v>51</v>
@@ -1427,17 +1427,17 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2020-07-23</t>
+          <t>2020-07-27</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>33380341470</v>
+        <v>25272101520</v>
       </c>
       <c r="C53" t="n">
-        <v>92918126099</v>
+        <v>69273127708</v>
       </c>
       <c r="D53" t="n">
-        <v>0.3592446691664313</v>
+        <v>0.3648182542951854</v>
       </c>
       <c r="E53" t="n">
         <v>52</v>
@@ -1446,17 +1446,17 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2020-07-24</t>
+          <t>2020-07-28</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>34826858650</v>
+        <v>25533477451</v>
       </c>
       <c r="C54" t="n">
-        <v>98778010270</v>
+        <v>67557159363</v>
       </c>
       <c r="D54" t="n">
-        <v>0.3525770417404056</v>
+        <v>0.3779536868002814</v>
       </c>
       <c r="E54" t="n">
         <v>53</v>
@@ -1465,17 +1465,17 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2020-07-27</t>
+          <t>2020-07-29</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>25272101520</v>
+        <v>27398207256</v>
       </c>
       <c r="C55" t="n">
-        <v>69273127708</v>
+        <v>75808503607</v>
       </c>
       <c r="D55" t="n">
-        <v>0.3648182542951854</v>
+        <v>0.3614133764997586</v>
       </c>
       <c r="E55" t="n">
         <v>54</v>
@@ -1484,17 +1484,17 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2020-07-28</t>
+          <t>2020-07-30</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>25533477451</v>
+        <v>29316097538</v>
       </c>
       <c r="C56" t="n">
-        <v>67557159363</v>
+        <v>80705680370</v>
       </c>
       <c r="D56" t="n">
-        <v>0.3779536868002814</v>
+        <v>0.3632470156201968</v>
       </c>
       <c r="E56" t="n">
         <v>55</v>
@@ -1503,17 +1503,17 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2020-07-29</t>
+          <t>2020-07-31</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>27398207256</v>
+        <v>30421341838</v>
       </c>
       <c r="C57" t="n">
-        <v>75808503607</v>
+        <v>83388719271</v>
       </c>
       <c r="D57" t="n">
-        <v>0.3614133764997586</v>
+        <v>0.3648136355126825</v>
       </c>
       <c r="E57" t="n">
         <v>56</v>
@@ -1522,17 +1522,17 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2020-07-30</t>
+          <t>2020-08-03</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>29316097538</v>
+        <v>32534419194</v>
       </c>
       <c r="C58" t="n">
-        <v>80705680370</v>
+        <v>97147468049</v>
       </c>
       <c r="D58" t="n">
-        <v>0.3632470156201968</v>
+        <v>0.3348972427937086</v>
       </c>
       <c r="E58" t="n">
         <v>57</v>
@@ -1541,17 +1541,17 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2020-07-31</t>
+          <t>2020-08-04</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>30421341838</v>
+        <v>35518548960</v>
       </c>
       <c r="C59" t="n">
-        <v>83388719271</v>
+        <v>100401661483</v>
       </c>
       <c r="D59" t="n">
-        <v>0.3648136355126825</v>
+        <v>0.3537645536474912</v>
       </c>
       <c r="E59" t="n">
         <v>58</v>
@@ -1560,17 +1560,17 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2020-08-03</t>
+          <t>2020-08-05</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>32534419194</v>
+        <v>31118752071</v>
       </c>
       <c r="C60" t="n">
-        <v>97147468049</v>
+        <v>88411991123</v>
       </c>
       <c r="D60" t="n">
-        <v>0.3348972427937086</v>
+        <v>0.351974338273947</v>
       </c>
       <c r="E60" t="n">
         <v>59</v>
@@ -1579,17 +1579,17 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2020-08-04</t>
+          <t>2020-08-06</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>35518548960</v>
+        <v>35289080996</v>
       </c>
       <c r="C61" t="n">
-        <v>100401661483</v>
+        <v>94484631872</v>
       </c>
       <c r="D61" t="n">
-        <v>0.3537645536474912</v>
+        <v>0.3734901676264849</v>
       </c>
       <c r="E61" t="n">
         <v>60</v>
@@ -1598,17 +1598,17 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2020-08-05</t>
+          <t>2020-08-07</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>31118752071</v>
+        <v>33926327226</v>
       </c>
       <c r="C62" t="n">
-        <v>88411991123</v>
+        <v>90977583613</v>
       </c>
       <c r="D62" t="n">
-        <v>0.351974338273947</v>
+        <v>0.3729086427522151</v>
       </c>
       <c r="E62" t="n">
         <v>61</v>
@@ -1617,17 +1617,17 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2020-08-06</t>
+          <t>2020-08-10</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>35289080996</v>
+        <v>29708663069</v>
       </c>
       <c r="C63" t="n">
-        <v>94484631872</v>
+        <v>82942928747</v>
       </c>
       <c r="D63" t="n">
-        <v>0.3734901676264849</v>
+        <v>0.3581819875160189</v>
       </c>
       <c r="E63" t="n">
         <v>62</v>
@@ -1636,17 +1636,17 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2020-08-07</t>
+          <t>2020-08-11</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>33926327226</v>
+        <v>30946369948</v>
       </c>
       <c r="C64" t="n">
-        <v>90977583613</v>
+        <v>86295092754</v>
       </c>
       <c r="D64" t="n">
-        <v>0.3729086427522151</v>
+        <v>0.3586110051033644</v>
       </c>
       <c r="E64" t="n">
         <v>63</v>
@@ -1655,17 +1655,17 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2020-08-10</t>
+          <t>2020-08-12</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>29708663069</v>
+        <v>29856245191</v>
       </c>
       <c r="C65" t="n">
-        <v>82942928747</v>
+        <v>82452473263</v>
       </c>
       <c r="D65" t="n">
-        <v>0.3581819875160189</v>
+        <v>0.3621024817019988</v>
       </c>
       <c r="E65" t="n">
         <v>64</v>
@@ -1674,17 +1674,17 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2020-08-11</t>
+          <t>2020-08-13</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>30946369948</v>
+        <v>27823565615</v>
       </c>
       <c r="C66" t="n">
-        <v>86295092754</v>
+        <v>72532322436</v>
       </c>
       <c r="D66" t="n">
-        <v>0.3586110051033644</v>
+        <v>0.3836022986793308</v>
       </c>
       <c r="E66" t="n">
         <v>65</v>
@@ -1693,17 +1693,17 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2020-08-12</t>
+          <t>2020-08-14</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>29856245191</v>
+        <v>27261549866</v>
       </c>
       <c r="C67" t="n">
-        <v>82452473263</v>
+        <v>69180221661</v>
       </c>
       <c r="D67" t="n">
-        <v>0.3621024817019988</v>
+        <v>0.3940656622869504</v>
       </c>
       <c r="E67" t="n">
         <v>66</v>
@@ -1712,17 +1712,17 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2020-08-13</t>
+          <t>2020-08-17</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>27823565615</v>
+        <v>37118467741</v>
       </c>
       <c r="C68" t="n">
-        <v>72532322436</v>
+        <v>91788369903</v>
       </c>
       <c r="D68" t="n">
-        <v>0.3836022986793308</v>
+        <v>0.4043918394043386</v>
       </c>
       <c r="E68" t="n">
         <v>67</v>
@@ -1731,17 +1731,17 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2020-08-14</t>
+          <t>2020-08-18</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>27261549866</v>
+        <v>31325687773</v>
       </c>
       <c r="C69" t="n">
-        <v>69180221661</v>
+        <v>85178317604</v>
       </c>
       <c r="D69" t="n">
-        <v>0.3940656622869504</v>
+        <v>0.3677659838109897</v>
       </c>
       <c r="E69" t="n">
         <v>68</v>
@@ -1750,17 +1750,17 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2020-08-17</t>
+          <t>2020-08-19</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>37118467741</v>
+        <v>33073383828</v>
       </c>
       <c r="C70" t="n">
-        <v>91788369903</v>
+        <v>88140275731</v>
       </c>
       <c r="D70" t="n">
-        <v>0.4043918394043386</v>
+        <v>0.375235765417145</v>
       </c>
       <c r="E70" t="n">
         <v>69</v>
@@ -1769,17 +1769,17 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2020-08-18</t>
+          <t>2020-08-20</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>31325687773</v>
+        <v>27646953314</v>
       </c>
       <c r="C71" t="n">
-        <v>85178317604</v>
+        <v>72119978332</v>
       </c>
       <c r="D71" t="n">
-        <v>0.3677659838109897</v>
+        <v>0.3833466669489126</v>
       </c>
       <c r="E71" t="n">
         <v>70</v>
@@ -1788,17 +1788,17 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2020-08-19</t>
+          <t>2020-08-21</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>33073383828</v>
+        <v>25486130617</v>
       </c>
       <c r="C72" t="n">
-        <v>88140275731</v>
+        <v>66786682396</v>
       </c>
       <c r="D72" t="n">
-        <v>0.375235765417145</v>
+        <v>0.3816049802546626</v>
       </c>
       <c r="E72" t="n">
         <v>71</v>
@@ -1807,17 +1807,17 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2020-08-20</t>
+          <t>2020-08-24</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>27646953314</v>
+        <v>25209284709</v>
       </c>
       <c r="C73" t="n">
-        <v>72119978332</v>
+        <v>67412296336</v>
       </c>
       <c r="D73" t="n">
-        <v>0.3833466669489126</v>
+        <v>0.3739567716748666</v>
       </c>
       <c r="E73" t="n">
         <v>72</v>
@@ -1826,17 +1826,17 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2020-08-21</t>
+          <t>2020-08-25</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>25486130617</v>
+        <v>26619247474</v>
       </c>
       <c r="C74" t="n">
-        <v>66786682396</v>
+        <v>73103731924</v>
       </c>
       <c r="D74" t="n">
-        <v>0.3816049802546626</v>
+        <v>0.3641298025889275</v>
       </c>
       <c r="E74" t="n">
         <v>73</v>
@@ -1845,17 +1845,17 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2020-08-24</t>
+          <t>2020-08-26</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>25209284709</v>
+        <v>26322908958</v>
       </c>
       <c r="C75" t="n">
-        <v>67412296336</v>
+        <v>75716936591</v>
       </c>
       <c r="D75" t="n">
-        <v>0.3739567716748666</v>
+        <v>0.3476488899727732</v>
       </c>
       <c r="E75" t="n">
         <v>74</v>
@@ -1864,17 +1864,17 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2020-08-25</t>
+          <t>2020-08-27</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>26619247474</v>
+        <v>23276018839</v>
       </c>
       <c r="C76" t="n">
-        <v>73103731924</v>
+        <v>65005692955</v>
       </c>
       <c r="D76" t="n">
-        <v>0.3641298025889275</v>
+        <v>0.3580612371152286</v>
       </c>
       <c r="E76" t="n">
         <v>75</v>
@@ -1883,17 +1883,17 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2020-08-26</t>
+          <t>2020-08-28</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>26322908958</v>
+        <v>25701039669</v>
       </c>
       <c r="C77" t="n">
-        <v>75716936591</v>
+        <v>70850828969</v>
       </c>
       <c r="D77" t="n">
-        <v>0.3476488899727732</v>
+        <v>0.3627486091975749</v>
       </c>
       <c r="E77" t="n">
         <v>76</v>
@@ -1902,17 +1902,17 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2020-08-27</t>
+          <t>2020-08-31</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>23276018839</v>
+        <v>28573296373</v>
       </c>
       <c r="C78" t="n">
-        <v>65005692955</v>
+        <v>77184652221</v>
       </c>
       <c r="D78" t="n">
-        <v>0.3580612371152286</v>
+        <v>0.3701940159189566</v>
       </c>
       <c r="E78" t="n">
         <v>77</v>
@@ -1921,17 +1921,17 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2020-08-28</t>
+          <t>2020-09-01</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>25701039669</v>
+        <v>23964180511</v>
       </c>
       <c r="C79" t="n">
-        <v>70850828969</v>
+        <v>64392996012</v>
       </c>
       <c r="D79" t="n">
-        <v>0.3627486091975749</v>
+        <v>0.3721550788929613</v>
       </c>
       <c r="E79" t="n">
         <v>78</v>
@@ -1940,17 +1940,17 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2020-08-31</t>
+          <t>2020-09-02</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>28573296373</v>
+        <v>30082062270</v>
       </c>
       <c r="C80" t="n">
-        <v>77184652221</v>
+        <v>77531927895</v>
       </c>
       <c r="D80" t="n">
-        <v>0.3701940159189566</v>
+        <v>0.3879957984630482</v>
       </c>
       <c r="E80" t="n">
         <v>79</v>
@@ -1959,17 +1959,17 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2020-09-01</t>
+          <t>2020-09-03</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>23964180511</v>
+        <v>27715216294</v>
       </c>
       <c r="C81" t="n">
-        <v>64392996012</v>
+        <v>73519808249</v>
       </c>
       <c r="D81" t="n">
-        <v>0.3721550788929613</v>
+        <v>0.3769761776327399</v>
       </c>
       <c r="E81" t="n">
         <v>80</v>
@@ -1978,17 +1978,17 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2020-09-02</t>
+          <t>2020-09-04</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>30082062270</v>
+        <v>24329945914</v>
       </c>
       <c r="C82" t="n">
-        <v>77531927895</v>
+        <v>65573685675</v>
       </c>
       <c r="D82" t="n">
-        <v>0.3879957984630482</v>
+        <v>0.37103215510236</v>
       </c>
       <c r="E82" t="n">
         <v>81</v>
@@ -1997,17 +1997,17 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2020-09-03</t>
+          <t>2020-09-07</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>27715216294</v>
+        <v>29997390344</v>
       </c>
       <c r="C83" t="n">
-        <v>73519808249</v>
+        <v>79881522723</v>
       </c>
       <c r="D83" t="n">
-        <v>0.3769761776327399</v>
+        <v>0.375523516846568</v>
       </c>
       <c r="E83" t="n">
         <v>82</v>
@@ -2016,17 +2016,17 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2020-09-04</t>
+          <t>2020-09-08</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>24329945914</v>
+        <v>32724062545</v>
       </c>
       <c r="C84" t="n">
-        <v>65573685675</v>
+        <v>80161481426</v>
       </c>
       <c r="D84" t="n">
-        <v>0.37103215510236</v>
+        <v>0.4082267688030289</v>
       </c>
       <c r="E84" t="n">
         <v>83</v>
@@ -2035,17 +2035,17 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2020-09-07</t>
+          <t>2020-09-09</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>29997390344</v>
+        <v>41720230941</v>
       </c>
       <c r="C85" t="n">
-        <v>79881522723</v>
+        <v>98517765305</v>
       </c>
       <c r="D85" t="n">
-        <v>0.375523516846568</v>
+        <v>0.4234792660170358</v>
       </c>
       <c r="E85" t="n">
         <v>84</v>
@@ -2054,17 +2054,17 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2020-09-08</t>
+          <t>2020-09-10</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>32724062545</v>
+        <v>32362586075</v>
       </c>
       <c r="C86" t="n">
-        <v>80161481426</v>
+        <v>83938666669</v>
       </c>
       <c r="D86" t="n">
-        <v>0.4082267688030289</v>
+        <v>0.3855503948212232</v>
       </c>
       <c r="E86" t="n">
         <v>85</v>
@@ -2073,17 +2073,17 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2020-09-09</t>
+          <t>2020-09-11</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>41720230941</v>
+        <v>23586290440</v>
       </c>
       <c r="C87" t="n">
-        <v>98517765305</v>
+        <v>60330240577</v>
       </c>
       <c r="D87" t="n">
-        <v>0.4234792660170358</v>
+        <v>0.3909530314220547</v>
       </c>
       <c r="E87" t="n">
         <v>86</v>
@@ -2092,17 +2092,17 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2020-09-10</t>
+          <t>2020-09-14</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>32362586075</v>
+        <v>24462170352</v>
       </c>
       <c r="C88" t="n">
-        <v>83938666669</v>
+        <v>63101019998</v>
       </c>
       <c r="D88" t="n">
-        <v>0.3855503948212232</v>
+        <v>0.3876667976646865</v>
       </c>
       <c r="E88" t="n">
         <v>87</v>
@@ -2111,17 +2111,17 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2020-09-11</t>
+          <t>2020-09-15</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>23586290440</v>
+        <v>23106120892</v>
       </c>
       <c r="C89" t="n">
-        <v>60330240577</v>
+        <v>58614407766</v>
       </c>
       <c r="D89" t="n">
-        <v>0.3909530314220547</v>
+        <v>0.3942054824514151</v>
       </c>
       <c r="E89" t="n">
         <v>88</v>
@@ -2130,17 +2130,17 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2020-09-14</t>
+          <t>2020-09-16</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>24462170352</v>
+        <v>21724638649</v>
       </c>
       <c r="C90" t="n">
-        <v>63101019998</v>
+        <v>55182289033</v>
       </c>
       <c r="D90" t="n">
-        <v>0.3876667976646865</v>
+        <v>0.3936886096915674</v>
       </c>
       <c r="E90" t="n">
         <v>89</v>
@@ -2149,17 +2149,17 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2020-09-15</t>
+          <t>2020-09-17</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>23106120892</v>
+        <v>20554994106</v>
       </c>
       <c r="C91" t="n">
-        <v>58614407766</v>
+        <v>55472969929</v>
       </c>
       <c r="D91" t="n">
-        <v>0.3942054824514151</v>
+        <v>0.3705407179804577</v>
       </c>
       <c r="E91" t="n">
         <v>90</v>
@@ -2168,17 +2168,17 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2020-09-16</t>
+          <t>2020-09-18</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>21724638649</v>
+        <v>25018086444</v>
       </c>
       <c r="C92" t="n">
-        <v>55182289033</v>
+        <v>64587549837</v>
       </c>
       <c r="D92" t="n">
-        <v>0.3936886096915674</v>
+        <v>0.3873515330297914</v>
       </c>
       <c r="E92" t="n">
         <v>91</v>
@@ -2187,17 +2187,17 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2020-09-17</t>
+          <t>2020-09-21</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>20554994106</v>
+        <v>22182279260</v>
       </c>
       <c r="C93" t="n">
-        <v>55472969929</v>
+        <v>58098440053</v>
       </c>
       <c r="D93" t="n">
-        <v>0.3705407179804577</v>
+        <v>0.3818050749686968</v>
       </c>
       <c r="E93" t="n">
         <v>92</v>
@@ -2206,17 +2206,17 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2020-09-18</t>
+          <t>2020-09-22</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>25018086444</v>
+        <v>22099090990</v>
       </c>
       <c r="C94" t="n">
-        <v>64587549837</v>
+        <v>56264182474</v>
       </c>
       <c r="D94" t="n">
-        <v>0.3873515330297914</v>
+        <v>0.3927736975510506</v>
       </c>
       <c r="E94" t="n">
         <v>93</v>
@@ -2225,17 +2225,17 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2020-09-21</t>
+          <t>2020-09-23</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>22182279260</v>
+        <v>19077501915</v>
       </c>
       <c r="C95" t="n">
-        <v>58098440053</v>
+        <v>48597940983</v>
       </c>
       <c r="D95" t="n">
-        <v>0.3818050749686968</v>
+        <v>0.3925578230088695</v>
       </c>
       <c r="E95" t="n">
         <v>94</v>
@@ -2244,17 +2244,17 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2020-09-22</t>
+          <t>2020-09-24</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>22099090990</v>
+        <v>20859996043</v>
       </c>
       <c r="C96" t="n">
-        <v>56264182474</v>
+        <v>54861814882</v>
       </c>
       <c r="D96" t="n">
-        <v>0.3927736975510506</v>
+        <v>0.3802279616134993</v>
       </c>
       <c r="E96" t="n">
         <v>95</v>
@@ -2263,17 +2263,17 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2020-09-23</t>
+          <t>2020-09-25</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>19077501915</v>
+        <v>16281719043</v>
       </c>
       <c r="C97" t="n">
-        <v>48597940983</v>
+        <v>43622575116</v>
       </c>
       <c r="D97" t="n">
-        <v>0.3925578230088695</v>
+        <v>0.373240667239476</v>
       </c>
       <c r="E97" t="n">
         <v>96</v>
@@ -2282,17 +2282,17 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2020-09-24</t>
+          <t>2020-09-28</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>20859996043</v>
+        <v>14676583271</v>
       </c>
       <c r="C98" t="n">
-        <v>54861814882</v>
+        <v>40556797589</v>
       </c>
       <c r="D98" t="n">
-        <v>0.3802279616134993</v>
+        <v>0.3618772719614492</v>
       </c>
       <c r="E98" t="n">
         <v>97</v>
@@ -2301,17 +2301,17 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2020-09-25</t>
+          <t>2020-09-29</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>16281719043</v>
+        <v>14442107257</v>
       </c>
       <c r="C99" t="n">
-        <v>43622575116</v>
+        <v>40163621965</v>
       </c>
       <c r="D99" t="n">
-        <v>0.373240667239476</v>
+        <v>0.3595817944304267</v>
       </c>
       <c r="E99" t="n">
         <v>98</v>
@@ -2320,17 +2320,17 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2020-09-28</t>
+          <t>2020-09-30</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>14676583271</v>
+        <v>15066784297</v>
       </c>
       <c r="C100" t="n">
-        <v>40556797589</v>
+        <v>40300843448</v>
       </c>
       <c r="D100" t="n">
-        <v>0.3618772719614492</v>
+        <v>0.3738577907541961</v>
       </c>
       <c r="E100" t="n">
         <v>99</v>
@@ -2339,17 +2339,17 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2020-09-29</t>
+          <t>2020-10-09</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>14442107257</v>
+        <v>18363804782</v>
       </c>
       <c r="C101" t="n">
-        <v>40163621965</v>
+        <v>50410563994</v>
       </c>
       <c r="D101" t="n">
-        <v>0.3595817944304267</v>
+        <v>0.3642848507742486</v>
       </c>
       <c r="E101" t="n">
         <v>100</v>
@@ -2358,17 +2358,17 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2020-09-30</t>
+          <t>2020-10-12</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>15066784297</v>
+        <v>24824121596</v>
       </c>
       <c r="C102" t="n">
-        <v>40300843448</v>
+        <v>69075123930</v>
       </c>
       <c r="D102" t="n">
-        <v>0.3738577907541961</v>
+        <v>0.3593786038104905</v>
       </c>
       <c r="E102" t="n">
         <v>101</v>
@@ -2377,17 +2377,17 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2020-10-09</t>
+          <t>2020-10-13</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>18363804782</v>
+        <v>21950874234</v>
       </c>
       <c r="C103" t="n">
-        <v>50410563994</v>
+        <v>58435290007</v>
       </c>
       <c r="D103" t="n">
-        <v>0.3642848507742486</v>
+        <v>0.3756441395494142</v>
       </c>
       <c r="E103" t="n">
         <v>102</v>
@@ -2396,17 +2396,17 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2020-10-12</t>
+          <t>2020-10-14</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>24824121596</v>
+        <v>21810988673</v>
       </c>
       <c r="C104" t="n">
-        <v>69075123930</v>
+        <v>58022364557</v>
       </c>
       <c r="D104" t="n">
-        <v>0.3593786038104905</v>
+        <v>0.3759065808421738</v>
       </c>
       <c r="E104" t="n">
         <v>103</v>
@@ -2415,17 +2415,17 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2020-10-13</t>
+          <t>2020-10-15</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>21950874234</v>
+        <v>20410751440</v>
       </c>
       <c r="C105" t="n">
-        <v>58435290007</v>
+        <v>54415224691</v>
       </c>
       <c r="D105" t="n">
-        <v>0.3756441395494142</v>
+        <v>0.3750926612157467</v>
       </c>
       <c r="E105" t="n">
         <v>104</v>
@@ -2434,17 +2434,17 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2020-10-14</t>
+          <t>2020-10-16</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>21810988673</v>
+        <v>19779199722</v>
       </c>
       <c r="C106" t="n">
-        <v>58022364557</v>
+        <v>51552706029</v>
       </c>
       <c r="D106" t="n">
-        <v>0.3759065808421738</v>
+        <v>0.3836694762613156</v>
       </c>
       <c r="E106" t="n">
         <v>105</v>
@@ -2453,17 +2453,17 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2020-10-15</t>
+          <t>2020-10-19</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>20410751440</v>
+        <v>20562725471</v>
       </c>
       <c r="C107" t="n">
-        <v>54415224691</v>
+        <v>53895497648</v>
       </c>
       <c r="D107" t="n">
-        <v>0.3750926612157467</v>
+        <v>0.3815295593947087</v>
       </c>
       <c r="E107" t="n">
         <v>106</v>
@@ -2472,17 +2472,17 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2020-10-16</t>
+          <t>2020-10-20</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>19779199722</v>
+        <v>18296672779</v>
       </c>
       <c r="C108" t="n">
-        <v>51552706029</v>
+        <v>47922773316</v>
       </c>
       <c r="D108" t="n">
-        <v>0.3836694762613156</v>
+        <v>0.3817949486844761</v>
       </c>
       <c r="E108" t="n">
         <v>107</v>
@@ -2491,17 +2491,17 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2020-10-19</t>
+          <t>2020-10-21</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>20562725471</v>
+        <v>18370049664</v>
       </c>
       <c r="C109" t="n">
-        <v>53895497648</v>
+        <v>49307563396</v>
       </c>
       <c r="D109" t="n">
-        <v>0.3815295593947087</v>
+        <v>0.3725604836009853</v>
       </c>
       <c r="E109" t="n">
         <v>108</v>
@@ -2510,17 +2510,17 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2020-10-20</t>
+          <t>2020-10-22</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>18296672779</v>
+        <v>17665602844</v>
       </c>
       <c r="C110" t="n">
-        <v>47922773316</v>
+        <v>46460364776</v>
       </c>
       <c r="D110" t="n">
-        <v>0.3817949486844761</v>
+        <v>0.3802295339085566</v>
       </c>
       <c r="E110" t="n">
         <v>109</v>
@@ -2529,17 +2529,17 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2020-10-21</t>
+          <t>2020-10-23</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>18370049664</v>
+        <v>17466910909</v>
       </c>
       <c r="C111" t="n">
-        <v>49307563396</v>
+        <v>47398504650</v>
       </c>
       <c r="D111" t="n">
-        <v>0.3725604836009853</v>
+        <v>0.3685118557637873</v>
       </c>
       <c r="E111" t="n">
         <v>110</v>
@@ -2548,17 +2548,17 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2020-10-22</t>
+          <t>2020-10-26</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>17665602844</v>
+        <v>16145407434</v>
       </c>
       <c r="C112" t="n">
-        <v>46460364776</v>
+        <v>44150494774</v>
       </c>
       <c r="D112" t="n">
-        <v>0.3802295339085566</v>
+        <v>0.3656902944496094</v>
       </c>
       <c r="E112" t="n">
         <v>111</v>
@@ -2567,17 +2567,17 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2020-10-23</t>
+          <t>2020-10-27</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>17466910909</v>
+        <v>15491813981</v>
       </c>
       <c r="C113" t="n">
-        <v>47398504650</v>
+        <v>43505082864</v>
       </c>
       <c r="D113" t="n">
-        <v>0.3685118557637873</v>
+        <v>0.356092046288672</v>
       </c>
       <c r="E113" t="n">
         <v>112</v>
@@ -2586,17 +2586,17 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2020-10-26</t>
+          <t>2020-10-28</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>16145407434</v>
+        <v>17543172634</v>
       </c>
       <c r="C114" t="n">
-        <v>44150494774</v>
+        <v>49485508785</v>
       </c>
       <c r="D114" t="n">
-        <v>0.3656902944496094</v>
+        <v>0.3545113117906887</v>
       </c>
       <c r="E114" t="n">
         <v>113</v>
@@ -2605,17 +2605,17 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2020-10-27</t>
+          <t>2020-10-29</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>15491813981</v>
+        <v>18553392322</v>
       </c>
       <c r="C115" t="n">
-        <v>43505082864</v>
+        <v>51689467398</v>
       </c>
       <c r="D115" t="n">
-        <v>0.356092046288672</v>
+        <v>0.3589395142948963</v>
       </c>
       <c r="E115" t="n">
         <v>114</v>
@@ -2624,17 +2624,17 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2020-10-28</t>
+          <t>2020-10-30</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>17543172634</v>
+        <v>20650226596</v>
       </c>
       <c r="C116" t="n">
-        <v>49485508785</v>
+        <v>60348197366</v>
       </c>
       <c r="D116" t="n">
-        <v>0.3545113117906887</v>
+        <v>0.3421846467220954</v>
       </c>
       <c r="E116" t="n">
         <v>115</v>
@@ -2643,17 +2643,17 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2020-10-29</t>
+          <t>2020-11-02</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>18553392322</v>
+        <v>19992661394</v>
       </c>
       <c r="C117" t="n">
-        <v>51689467398</v>
+        <v>56353918211</v>
       </c>
       <c r="D117" t="n">
-        <v>0.3589395142948963</v>
+        <v>0.3547696775784711</v>
       </c>
       <c r="E117" t="n">
         <v>116</v>
@@ -2662,17 +2662,17 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2020-10-30</t>
+          <t>2020-11-03</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>20650226596</v>
+        <v>20249408150</v>
       </c>
       <c r="C118" t="n">
-        <v>60348197366</v>
+        <v>55344378404</v>
       </c>
       <c r="D118" t="n">
-        <v>0.3421846467220954</v>
+        <v>0.365880126111173</v>
       </c>
       <c r="E118" t="n">
         <v>117</v>
@@ -2681,17 +2681,17 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2020-11-02</t>
+          <t>2020-11-04</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>19992661394</v>
+        <v>18257580496</v>
       </c>
       <c r="C119" t="n">
-        <v>56353918211</v>
+        <v>49909415865</v>
       </c>
       <c r="D119" t="n">
-        <v>0.3547696775784711</v>
+        <v>0.3658143494483073</v>
       </c>
       <c r="E119" t="n">
         <v>118</v>
@@ -2700,17 +2700,17 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2020-11-03</t>
+          <t>2020-11-05</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>20249408150</v>
+        <v>21285267389</v>
       </c>
       <c r="C120" t="n">
-        <v>55344378404</v>
+        <v>58980118835</v>
       </c>
       <c r="D120" t="n">
-        <v>0.365880126111173</v>
+        <v>0.3608888522002924</v>
       </c>
       <c r="E120" t="n">
         <v>119</v>
@@ -2719,17 +2719,17 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2020-11-04</t>
+          <t>2020-11-06</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>18257580496</v>
+        <v>23071856412</v>
       </c>
       <c r="C121" t="n">
-        <v>49909415865</v>
+        <v>59902082650</v>
       </c>
       <c r="D121" t="n">
-        <v>0.3658143494483073</v>
+        <v>0.3851595034984981</v>
       </c>
       <c r="E121" t="n">
         <v>120</v>
@@ -2738,17 +2738,17 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2020-11-05</t>
+          <t>2020-11-09</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>21285267389</v>
+        <v>27202863336</v>
       </c>
       <c r="C122" t="n">
-        <v>58980118835</v>
+        <v>74478178320</v>
       </c>
       <c r="D122" t="n">
-        <v>0.3608888522002924</v>
+        <v>0.3652460888492902</v>
       </c>
       <c r="E122" t="n">
         <v>121</v>
@@ -2757,17 +2757,17 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2020-11-06</t>
+          <t>2020-11-10</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>23071856412</v>
+        <v>25309810082</v>
       </c>
       <c r="C123" t="n">
-        <v>59902082650</v>
+        <v>67090114044</v>
       </c>
       <c r="D123" t="n">
-        <v>0.3851595034984981</v>
+        <v>0.3772509622714452</v>
       </c>
       <c r="E123" t="n">
         <v>122</v>
@@ -2776,17 +2776,17 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2020-11-09</t>
+          <t>2020-11-11</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>27202863336</v>
+        <v>23822441228</v>
       </c>
       <c r="C124" t="n">
-        <v>74478178320</v>
+        <v>61988411650</v>
       </c>
       <c r="D124" t="n">
-        <v>0.3652460888492902</v>
+        <v>0.3843047529997488</v>
       </c>
       <c r="E124" t="n">
         <v>123</v>
@@ -2795,17 +2795,17 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2020-11-10</t>
+          <t>2020-11-12</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>25309810082</v>
+        <v>19076439758</v>
       </c>
       <c r="C125" t="n">
-        <v>67090114044</v>
+        <v>51703999860</v>
       </c>
       <c r="D125" t="n">
-        <v>0.3772509622714452</v>
+        <v>0.3689548160616911</v>
       </c>
       <c r="E125" t="n">
         <v>124</v>
@@ -2814,17 +2814,17 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2020-11-11</t>
+          <t>2020-11-13</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>23822441228</v>
+        <v>20119982649</v>
       </c>
       <c r="C126" t="n">
-        <v>61988411650</v>
+        <v>52210418675</v>
       </c>
       <c r="D126" t="n">
-        <v>0.3843047529997488</v>
+        <v>0.3853633653896379</v>
       </c>
       <c r="E126" t="n">
         <v>125</v>
@@ -2833,17 +2833,17 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2020-11-12</t>
+          <t>2020-11-16</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>19076439758</v>
+        <v>23217241543</v>
       </c>
       <c r="C127" t="n">
-        <v>51703999860</v>
+        <v>61350411349</v>
       </c>
       <c r="D127" t="n">
-        <v>0.3689548160616911</v>
+        <v>0.3784366075546849</v>
       </c>
       <c r="E127" t="n">
         <v>126</v>
@@ -2852,17 +2852,17 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2020-11-13</t>
+          <t>2020-11-17</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>20119982649</v>
+        <v>24335506367</v>
       </c>
       <c r="C128" t="n">
-        <v>52210418675</v>
+        <v>64241703103</v>
       </c>
       <c r="D128" t="n">
-        <v>0.3853633653896379</v>
+        <v>0.3788116626980203</v>
       </c>
       <c r="E128" t="n">
         <v>127</v>
@@ -2871,17 +2871,17 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2020-11-16</t>
+          <t>2020-11-18</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>23217241543</v>
+        <v>25490702717</v>
       </c>
       <c r="C129" t="n">
-        <v>61350411349</v>
+        <v>63205463709</v>
       </c>
       <c r="D129" t="n">
-        <v>0.3784366075546849</v>
+        <v>0.4032990381078449</v>
       </c>
       <c r="E129" t="n">
         <v>128</v>
@@ -2890,17 +2890,17 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2020-11-17</t>
+          <t>2020-11-19</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>24335506367</v>
+        <v>23177522765</v>
       </c>
       <c r="C130" t="n">
-        <v>64241703103</v>
+        <v>59756276020</v>
       </c>
       <c r="D130" t="n">
-        <v>0.3788116626980203</v>
+        <v>0.3878675899623104</v>
       </c>
       <c r="E130" t="n">
         <v>129</v>
@@ -2909,17 +2909,17 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2020-11-18</t>
+          <t>2020-11-20</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>25490702717</v>
+        <v>22935620159</v>
       </c>
       <c r="C131" t="n">
-        <v>63205463709</v>
+        <v>58875754449</v>
       </c>
       <c r="D131" t="n">
-        <v>0.4032990381078449</v>
+        <v>0.3895596816320637</v>
       </c>
       <c r="E131" t="n">
         <v>130</v>
@@ -2928,17 +2928,17 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>2020-11-19</t>
+          <t>2020-11-23</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>23177522765</v>
+        <v>32096579820</v>
       </c>
       <c r="C132" t="n">
-        <v>59756276020</v>
+        <v>77198006469</v>
       </c>
       <c r="D132" t="n">
-        <v>0.3878675899623104</v>
+        <v>0.4157695423506675</v>
       </c>
       <c r="E132" t="n">
         <v>131</v>
@@ -2947,17 +2947,17 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>2020-11-20</t>
+          <t>2020-11-24</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>22935620159</v>
+        <v>26709718473</v>
       </c>
       <c r="C133" t="n">
-        <v>58875754449</v>
+        <v>65410116144</v>
       </c>
       <c r="D133" t="n">
-        <v>0.3895596816320637</v>
+        <v>0.408342318399171</v>
       </c>
       <c r="E133" t="n">
         <v>132</v>
@@ -2966,17 +2966,17 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2020-11-23</t>
+          <t>2020-11-25</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>32096579820</v>
+        <v>27089790866</v>
       </c>
       <c r="C134" t="n">
-        <v>77198006469</v>
+        <v>68837443765</v>
       </c>
       <c r="D134" t="n">
-        <v>0.4157695423506675</v>
+        <v>0.3935327836762824</v>
       </c>
       <c r="E134" t="n">
         <v>133</v>
@@ -2985,17 +2985,17 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>2020-11-24</t>
+          <t>2020-11-26</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>26709718473</v>
+        <v>21689088930</v>
       </c>
       <c r="C135" t="n">
-        <v>65410116144</v>
+        <v>57127013421</v>
       </c>
       <c r="D135" t="n">
-        <v>0.408342318399171</v>
+        <v>0.3796643239540867</v>
       </c>
       <c r="E135" t="n">
         <v>134</v>
@@ -3004,17 +3004,17 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>2020-11-25</t>
+          <t>2020-11-27</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>27089790866</v>
+        <v>23626364341</v>
       </c>
       <c r="C136" t="n">
-        <v>68837443765</v>
+        <v>58765160877</v>
       </c>
       <c r="D136" t="n">
-        <v>0.3935327836762824</v>
+        <v>0.4020471311301572</v>
       </c>
       <c r="E136" t="n">
         <v>135</v>
@@ -3023,17 +3023,17 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>2020-11-26</t>
+          <t>2020-11-30</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>21689088930</v>
+        <v>33970232252</v>
       </c>
       <c r="C137" t="n">
-        <v>57127013421</v>
+        <v>75092505579</v>
       </c>
       <c r="D137" t="n">
-        <v>0.3796643239540867</v>
+        <v>0.4523784629381171</v>
       </c>
       <c r="E137" t="n">
         <v>136</v>
@@ -3042,17 +3042,17 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>2020-11-27</t>
+          <t>2020-12-01</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>23626364341</v>
+        <v>28738868941</v>
       </c>
       <c r="C138" t="n">
-        <v>58765160877</v>
+        <v>67936162045</v>
       </c>
       <c r="D138" t="n">
-        <v>0.4020471311301572</v>
+        <v>0.4230275611089682</v>
       </c>
       <c r="E138" t="n">
         <v>137</v>
@@ -3061,17 +3061,17 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>2020-11-30</t>
+          <t>2020-12-02</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>33970232252</v>
+        <v>28928357564</v>
       </c>
       <c r="C139" t="n">
-        <v>75092505579</v>
+        <v>69689843826</v>
       </c>
       <c r="D139" t="n">
-        <v>0.4523784629381171</v>
+        <v>0.4151014835996427</v>
       </c>
       <c r="E139" t="n">
         <v>138</v>
@@ -3080,17 +3080,17 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>2020-12-01</t>
+          <t>2020-12-03</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>28738868941</v>
+        <v>28497726227</v>
       </c>
       <c r="C140" t="n">
-        <v>67936162045</v>
+        <v>66950741850</v>
       </c>
       <c r="D140" t="n">
-        <v>0.4230275611089682</v>
+        <v>0.4256521352795137</v>
       </c>
       <c r="E140" t="n">
         <v>139</v>
@@ -3099,17 +3099,17 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>2020-12-02</t>
+          <t>2020-12-04</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>28928357564</v>
+        <v>23614518756</v>
       </c>
       <c r="C141" t="n">
-        <v>69689843826</v>
+        <v>57124426015</v>
       </c>
       <c r="D141" t="n">
-        <v>0.4151014835996427</v>
+        <v>0.4133874141649876</v>
       </c>
       <c r="E141" t="n">
         <v>140</v>
@@ -3118,17 +3118,17 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>2020-12-03</t>
+          <t>2020-12-07</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>28497726227</v>
+        <v>22345056458</v>
       </c>
       <c r="C142" t="n">
-        <v>66950741850</v>
+        <v>56856559648</v>
       </c>
       <c r="D142" t="n">
-        <v>0.4256521352795137</v>
+        <v>0.3930075367967857</v>
       </c>
       <c r="E142" t="n">
         <v>141</v>
@@ -3137,17 +3137,17 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>2020-12-04</t>
+          <t>2020-12-08</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>23614518756</v>
+        <v>20555717183</v>
       </c>
       <c r="C143" t="n">
-        <v>57124426015</v>
+        <v>51665831943</v>
       </c>
       <c r="D143" t="n">
-        <v>0.4133874141649876</v>
+        <v>0.3978590184259099</v>
       </c>
       <c r="E143" t="n">
         <v>142</v>
@@ -3156,17 +3156,17 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>2020-12-07</t>
+          <t>2020-12-09</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>22345056458</v>
+        <v>22167887887</v>
       </c>
       <c r="C144" t="n">
-        <v>56856559648</v>
+        <v>59426788696</v>
       </c>
       <c r="D144" t="n">
-        <v>0.3930075367967857</v>
+        <v>0.3730285343265085</v>
       </c>
       <c r="E144" t="n">
         <v>143</v>
@@ -3175,17 +3175,17 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>2020-12-08</t>
+          <t>2020-12-10</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>20555717183</v>
+        <v>21008686040</v>
       </c>
       <c r="C145" t="n">
-        <v>51665831943</v>
+        <v>53530291688</v>
       </c>
       <c r="D145" t="n">
-        <v>0.3978590184259099</v>
+        <v>0.3924635076238444</v>
       </c>
       <c r="E145" t="n">
         <v>144</v>
@@ -3194,17 +3194,17 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>2020-12-09</t>
+          <t>2020-12-11</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>22167887887</v>
+        <v>24084146686</v>
       </c>
       <c r="C146" t="n">
-        <v>59426788696</v>
+        <v>64194443337</v>
       </c>
       <c r="D146" t="n">
-        <v>0.3730285343265085</v>
+        <v>0.3751749440300626</v>
       </c>
       <c r="E146" t="n">
         <v>145</v>
@@ -3213,17 +3213,17 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>2020-12-10</t>
+          <t>2020-12-14</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>21008686040</v>
+        <v>20561369384</v>
       </c>
       <c r="C147" t="n">
-        <v>53530291688</v>
+        <v>52737085483</v>
       </c>
       <c r="D147" t="n">
-        <v>0.3924635076238444</v>
+        <v>0.3898844465082932</v>
       </c>
       <c r="E147" t="n">
         <v>146</v>
@@ -3232,17 +3232,17 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>2020-12-11</t>
+          <t>2020-12-15</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>24084146686</v>
+        <v>20518702233</v>
       </c>
       <c r="C148" t="n">
-        <v>64194443337</v>
+        <v>50712282528</v>
       </c>
       <c r="D148" t="n">
-        <v>0.3751749440300626</v>
+        <v>0.4046101104139991</v>
       </c>
       <c r="E148" t="n">
         <v>147</v>
@@ -3251,17 +3251,17 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>2020-12-14</t>
+          <t>2020-12-16</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>20561369384</v>
+        <v>20098821894</v>
       </c>
       <c r="C149" t="n">
-        <v>52737085483</v>
+        <v>51594471274</v>
       </c>
       <c r="D149" t="n">
-        <v>0.3898844465082932</v>
+        <v>0.3895537912824469</v>
       </c>
       <c r="E149" t="n">
         <v>148</v>
@@ -3270,17 +3270,17 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>2020-12-15</t>
+          <t>2020-12-17</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>20518702233</v>
+        <v>23623180829</v>
       </c>
       <c r="C150" t="n">
-        <v>50712282528</v>
+        <v>60346809075</v>
       </c>
       <c r="D150" t="n">
-        <v>0.4046101104139991</v>
+        <v>0.3914569998165226</v>
       </c>
       <c r="E150" t="n">
         <v>149</v>
@@ -3289,17 +3289,17 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>2020-12-16</t>
+          <t>2020-12-18</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>20098821894</v>
+        <v>24395319589</v>
       </c>
       <c r="C151" t="n">
-        <v>51594471274</v>
+        <v>59011526731</v>
       </c>
       <c r="D151" t="n">
-        <v>0.3895537912824469</v>
+        <v>0.4133992279204094</v>
       </c>
       <c r="E151" t="n">
         <v>150</v>
@@ -3308,17 +3308,17 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>2020-12-17</t>
+          <t>2020-12-21</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>23623180829</v>
+        <v>25669905456</v>
       </c>
       <c r="C152" t="n">
-        <v>60346809075</v>
+        <v>62473191028</v>
       </c>
       <c r="D152" t="n">
-        <v>0.3914569998165226</v>
+        <v>0.410894737944392</v>
       </c>
       <c r="E152" t="n">
         <v>151</v>
@@ -3327,17 +3327,17 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>2020-12-18</t>
+          <t>2020-12-22</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>24395319589</v>
+        <v>27752409533</v>
       </c>
       <c r="C153" t="n">
-        <v>59011526731</v>
+        <v>70592976908</v>
       </c>
       <c r="D153" t="n">
-        <v>0.4133992279204094</v>
+        <v>0.3931327271998773</v>
       </c>
       <c r="E153" t="n">
         <v>152</v>
@@ -3346,17 +3346,17 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>2020-12-21</t>
+          <t>2020-12-23</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>25669905456</v>
+        <v>26781996550</v>
       </c>
       <c r="C154" t="n">
-        <v>62473191028</v>
+        <v>66516491988</v>
       </c>
       <c r="D154" t="n">
-        <v>0.410894737944392</v>
+        <v>0.4026369363380084</v>
       </c>
       <c r="E154" t="n">
         <v>153</v>
@@ -3365,17 +3365,17 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>2020-12-22</t>
+          <t>2020-12-24</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>27752409533</v>
+        <v>23869444669</v>
       </c>
       <c r="C155" t="n">
-        <v>70592976908</v>
+        <v>63015856260</v>
       </c>
       <c r="D155" t="n">
-        <v>0.3931327271998773</v>
+        <v>0.3787847390427572</v>
       </c>
       <c r="E155" t="n">
         <v>154</v>
@@ -3384,17 +3384,17 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>2020-12-23</t>
+          <t>2020-12-25</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>26781996550</v>
+        <v>25870374333</v>
       </c>
       <c r="C156" t="n">
-        <v>66516491988</v>
+        <v>63035613181</v>
       </c>
       <c r="D156" t="n">
-        <v>0.4026369363380084</v>
+        <v>0.4104088629822002</v>
       </c>
       <c r="E156" t="n">
         <v>155</v>
@@ -3403,17 +3403,17 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>2020-12-24</t>
+          <t>2020-12-28</t>
         </is>
       </c>
       <c r="B157" t="n">
-        <v>23869444669</v>
+        <v>27591719605</v>
       </c>
       <c r="C157" t="n">
-        <v>63015856260</v>
+        <v>68634054637</v>
       </c>
       <c r="D157" t="n">
-        <v>0.3787847390427572</v>
+        <v>0.4020120878903394</v>
       </c>
       <c r="E157" t="n">
         <v>156</v>
@@ -3422,17 +3422,17 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>2020-12-25</t>
+          <t>2020-12-29</t>
         </is>
       </c>
       <c r="B158" t="n">
-        <v>25870374333</v>
+        <v>28714767727</v>
       </c>
       <c r="C158" t="n">
-        <v>63035613181</v>
+        <v>68080937199</v>
       </c>
       <c r="D158" t="n">
-        <v>0.4104088629822002</v>
+        <v>0.4217739782733451</v>
       </c>
       <c r="E158" t="n">
         <v>157</v>
@@ -3441,17 +3441,17 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>2020-12-28</t>
+          <t>2020-12-30</t>
         </is>
       </c>
       <c r="B159" t="n">
-        <v>27591719605</v>
+        <v>27431057672</v>
       </c>
       <c r="C159" t="n">
-        <v>68634054637</v>
+        <v>63970764234</v>
       </c>
       <c r="D159" t="n">
-        <v>0.4020120878903394</v>
+        <v>0.4288061585704895</v>
       </c>
       <c r="E159" t="n">
         <v>158</v>
@@ -3460,17 +3460,17 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>2020-12-29</t>
+          <t>2020-12-31</t>
         </is>
       </c>
       <c r="B160" t="n">
-        <v>28714767727</v>
+        <v>29516497306</v>
       </c>
       <c r="C160" t="n">
-        <v>68080937199</v>
+        <v>70483427194</v>
       </c>
       <c r="D160" t="n">
-        <v>0.4217739782733451</v>
+        <v>0.4187721636287379</v>
       </c>
       <c r="E160" t="n">
         <v>159</v>
@@ -3479,17 +3479,17 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>2020-12-30</t>
+          <t>2021-01-04</t>
         </is>
       </c>
       <c r="B161" t="n">
-        <v>27431057672</v>
+        <v>32842910849</v>
       </c>
       <c r="C161" t="n">
-        <v>63970764234</v>
+        <v>81262611004</v>
       </c>
       <c r="D161" t="n">
-        <v>0.4288061585704895</v>
+        <v>0.4041577109475767</v>
       </c>
       <c r="E161" t="n">
         <v>160</v>
@@ -3498,17 +3498,17 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>2020-12-31</t>
+          <t>2021-01-05</t>
         </is>
       </c>
       <c r="B162" t="n">
-        <v>29516497306</v>
+        <v>34955476638</v>
       </c>
       <c r="C162" t="n">
-        <v>70483427194</v>
+        <v>86306603527</v>
       </c>
       <c r="D162" t="n">
-        <v>0.4187721636287379</v>
+        <v>0.4050150881799513</v>
       </c>
       <c r="E162" t="n">
         <v>161</v>
@@ -3517,17 +3517,17 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>2021-01-04</t>
+          <t>2021-01-06</t>
         </is>
       </c>
       <c r="B163" t="n">
-        <v>32842910849</v>
+        <v>31318863380</v>
       </c>
       <c r="C163" t="n">
-        <v>81262611004</v>
+        <v>79924024318</v>
       </c>
       <c r="D163" t="n">
-        <v>0.4041577109475767</v>
+        <v>0.3918579381762507</v>
       </c>
       <c r="E163" t="n">
         <v>162</v>
@@ -3536,17 +3536,17 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>2021-01-05</t>
+          <t>2021-01-07</t>
         </is>
       </c>
       <c r="B164" t="n">
-        <v>34955476638</v>
+        <v>34820241307</v>
       </c>
       <c r="C164" t="n">
-        <v>86306603527</v>
+        <v>87045282583</v>
       </c>
       <c r="D164" t="n">
-        <v>0.4050150881799513</v>
+        <v>0.4000244501911746</v>
       </c>
       <c r="E164" t="n">
         <v>163</v>
@@ -3555,17 +3555,17 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>2021-01-06</t>
+          <t>2021-01-08</t>
         </is>
       </c>
       <c r="B165" t="n">
-        <v>31318863380</v>
+        <v>31741361539</v>
       </c>
       <c r="C165" t="n">
-        <v>79924024318</v>
+        <v>76243328872</v>
       </c>
       <c r="D165" t="n">
-        <v>0.3918579381762507</v>
+        <v>0.4163165749529185</v>
       </c>
       <c r="E165" t="n">
         <v>164</v>
@@ -3574,17 +3574,17 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>2021-01-07</t>
+          <t>2021-01-11</t>
         </is>
       </c>
       <c r="B166" t="n">
-        <v>34820241307</v>
+        <v>33861909952</v>
       </c>
       <c r="C166" t="n">
-        <v>87045282583</v>
+        <v>79843929989</v>
       </c>
       <c r="D166" t="n">
-        <v>0.4000244501911746</v>
+        <v>0.4241012429706943</v>
       </c>
       <c r="E166" t="n">
         <v>165</v>
@@ -3593,17 +3593,17 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>2021-01-08</t>
+          <t>2021-01-12</t>
         </is>
       </c>
       <c r="B167" t="n">
-        <v>31741361539</v>
+        <v>31336739617</v>
       </c>
       <c r="C167" t="n">
-        <v>76243328872</v>
+        <v>70684174141</v>
       </c>
       <c r="D167" t="n">
-        <v>0.4163165749529185</v>
+        <v>0.4433345936035105</v>
       </c>
       <c r="E167" t="n">
         <v>166</v>
@@ -3612,17 +3612,17 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>2021-01-11</t>
+          <t>2021-01-13</t>
         </is>
       </c>
       <c r="B168" t="n">
-        <v>33861909952</v>
+        <v>36176556832</v>
       </c>
       <c r="C168" t="n">
-        <v>79843929989</v>
+        <v>81782457644</v>
       </c>
       <c r="D168" t="n">
-        <v>0.4241012429706943</v>
+        <v>0.4423510600461162</v>
       </c>
       <c r="E168" t="n">
         <v>167</v>
@@ -3631,17 +3631,17 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>2021-01-12</t>
+          <t>2021-01-14</t>
         </is>
       </c>
       <c r="B169" t="n">
-        <v>31336739617</v>
+        <v>32971296424</v>
       </c>
       <c r="C169" t="n">
-        <v>70684174141</v>
+        <v>74034016193</v>
       </c>
       <c r="D169" t="n">
-        <v>0.4433345936035105</v>
+        <v>0.4453533405245341</v>
       </c>
       <c r="E169" t="n">
         <v>168</v>
@@ -3650,17 +3650,17 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>2021-01-13</t>
+          <t>2021-01-15</t>
         </is>
       </c>
       <c r="B170" t="n">
-        <v>36176556832</v>
+        <v>31268748151</v>
       </c>
       <c r="C170" t="n">
-        <v>81782457644</v>
+        <v>68522530970</v>
       </c>
       <c r="D170" t="n">
-        <v>0.4423510600461162</v>
+        <v>0.4563279801309417</v>
       </c>
       <c r="E170" t="n">
         <v>169</v>
@@ -3669,17 +3669,17 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>2021-01-14</t>
+          <t>2021-01-18</t>
         </is>
       </c>
       <c r="B171" t="n">
-        <v>32971296424</v>
+        <v>28025154838</v>
       </c>
       <c r="C171" t="n">
-        <v>74034016193</v>
+        <v>66132336803</v>
       </c>
       <c r="D171" t="n">
-        <v>0.4453533405245341</v>
+        <v>0.4237738479056539</v>
       </c>
       <c r="E171" t="n">
         <v>170</v>
@@ -3688,17 +3688,17 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>2021-01-15</t>
+          <t>2021-01-19</t>
         </is>
       </c>
       <c r="B172" t="n">
-        <v>31268748151</v>
+        <v>30160755219</v>
       </c>
       <c r="C172" t="n">
-        <v>68522530970</v>
+        <v>71588657610</v>
       </c>
       <c r="D172" t="n">
-        <v>0.4563279801309417</v>
+        <v>0.4213063385447102</v>
       </c>
       <c r="E172" t="n">
         <v>171</v>
@@ -3707,17 +3707,17 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>2021-01-18</t>
+          <t>2021-01-20</t>
         </is>
       </c>
       <c r="B173" t="n">
-        <v>28025154838</v>
+        <v>25498108632</v>
       </c>
       <c r="C173" t="n">
-        <v>66132336803</v>
+        <v>61023142374</v>
       </c>
       <c r="D173" t="n">
-        <v>0.4237738479056539</v>
+        <v>0.4178432581483041</v>
       </c>
       <c r="E173" t="n">
         <v>172</v>
@@ -3726,17 +3726,17 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>2021-01-19</t>
+          <t>2021-01-21</t>
         </is>
       </c>
       <c r="B174" t="n">
-        <v>30160755219</v>
+        <v>31550851527</v>
       </c>
       <c r="C174" t="n">
-        <v>71588657610</v>
+        <v>73606094304</v>
       </c>
       <c r="D174" t="n">
-        <v>0.4213063385447102</v>
+        <v>0.4286445548474839</v>
       </c>
       <c r="E174" t="n">
         <v>173</v>
@@ -3745,17 +3745,17 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>2021-01-20</t>
+          <t>2021-01-22</t>
         </is>
       </c>
       <c r="B175" t="n">
-        <v>25498108632</v>
+        <v>29587073243</v>
       </c>
       <c r="C175" t="n">
-        <v>61023142374</v>
+        <v>71863919964</v>
       </c>
       <c r="D175" t="n">
-        <v>0.4178432581483041</v>
+        <v>0.4117097043665521</v>
       </c>
       <c r="E175" t="n">
         <v>174</v>
@@ -3764,17 +3764,17 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>2021-01-21</t>
+          <t>2021-01-25</t>
         </is>
       </c>
       <c r="B176" t="n">
-        <v>31550851527</v>
+        <v>29768085597</v>
       </c>
       <c r="C176" t="n">
-        <v>73606094304</v>
+        <v>72841620023</v>
       </c>
       <c r="D176" t="n">
-        <v>0.4286445548474839</v>
+        <v>0.4086686373477226</v>
       </c>
       <c r="E176" t="n">
         <v>175</v>
@@ -3783,17 +3783,17 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>2021-01-22</t>
+          <t>2021-01-26</t>
         </is>
       </c>
       <c r="B177" t="n">
-        <v>29587073243</v>
+        <v>25588114580</v>
       </c>
       <c r="C177" t="n">
-        <v>71863919964</v>
+        <v>62625061804</v>
       </c>
       <c r="D177" t="n">
-        <v>0.4117097043665521</v>
+        <v>0.4085922447483418</v>
       </c>
       <c r="E177" t="n">
         <v>176</v>
@@ -3802,17 +3802,17 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>2021-01-25</t>
+          <t>2021-01-27</t>
         </is>
       </c>
       <c r="B178" t="n">
-        <v>29768085597</v>
+        <v>25604690493</v>
       </c>
       <c r="C178" t="n">
-        <v>72841620023</v>
+        <v>60015878129</v>
       </c>
       <c r="D178" t="n">
-        <v>0.4086686373477226</v>
+        <v>0.4266319396004584</v>
       </c>
       <c r="E178" t="n">
         <v>177</v>
@@ -3821,17 +3821,17 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>2021-01-26</t>
+          <t>2021-01-28</t>
         </is>
       </c>
       <c r="B179" t="n">
-        <v>25588114580</v>
+        <v>26286085867</v>
       </c>
       <c r="C179" t="n">
-        <v>62625061804</v>
+        <v>62311898539</v>
       </c>
       <c r="D179" t="n">
-        <v>0.4085922447483418</v>
+        <v>0.4218469743872106</v>
       </c>
       <c r="E179" t="n">
         <v>178</v>
@@ -3840,17 +3840,17 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>2021-01-27</t>
+          <t>2021-01-29</t>
         </is>
       </c>
       <c r="B180" t="n">
-        <v>25604690493</v>
+        <v>27002904913</v>
       </c>
       <c r="C180" t="n">
-        <v>60015878129</v>
+        <v>66018503681</v>
       </c>
       <c r="D180" t="n">
-        <v>0.4266319396004584</v>
+        <v>0.4090202504963981</v>
       </c>
       <c r="E180" t="n">
         <v>179</v>
@@ -3859,17 +3859,17 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>2021-01-28</t>
+          <t>2021-02-01</t>
         </is>
       </c>
       <c r="B181" t="n">
-        <v>26286085867</v>
+        <v>25457673045</v>
       </c>
       <c r="C181" t="n">
-        <v>62311898539</v>
+        <v>61214730247</v>
       </c>
       <c r="D181" t="n">
-        <v>0.4218469743872106</v>
+        <v>0.4158749526834291</v>
       </c>
       <c r="E181" t="n">
         <v>180</v>
@@ -3878,17 +3878,17 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>2021-01-29</t>
+          <t>2021-02-02</t>
         </is>
       </c>
       <c r="B182" t="n">
-        <v>27002904913</v>
+        <v>24585679056</v>
       </c>
       <c r="C182" t="n">
-        <v>66018503681</v>
+        <v>59083806830</v>
       </c>
       <c r="D182" t="n">
-        <v>0.4090202504963981</v>
+        <v>0.4161153516519274</v>
       </c>
       <c r="E182" t="n">
         <v>181</v>
@@ -3897,17 +3897,17 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>2021-02-01</t>
+          <t>2021-02-03</t>
         </is>
       </c>
       <c r="B183" t="n">
-        <v>25457673045</v>
+        <v>27946762653</v>
       </c>
       <c r="C183" t="n">
-        <v>61214730247</v>
+        <v>64252239936</v>
       </c>
       <c r="D183" t="n">
-        <v>0.4158749526834291</v>
+        <v>0.4349539048107436</v>
       </c>
       <c r="E183" t="n">
         <v>182</v>
@@ -3916,17 +3916,17 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>2021-02-02</t>
+          <t>2021-02-04</t>
         </is>
       </c>
       <c r="B184" t="n">
-        <v>24585679056</v>
+        <v>26745949814</v>
       </c>
       <c r="C184" t="n">
-        <v>59083806830</v>
+        <v>65026335158</v>
       </c>
       <c r="D184" t="n">
-        <v>0.4161153516519274</v>
+        <v>0.411309506356357</v>
       </c>
       <c r="E184" t="n">
         <v>183</v>
@@ -3935,17 +3935,17 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>2021-02-03</t>
+          <t>2021-02-05</t>
         </is>
       </c>
       <c r="B185" t="n">
-        <v>27946762653</v>
+        <v>27228530445</v>
       </c>
       <c r="C185" t="n">
-        <v>64252239936</v>
+        <v>60817228192</v>
       </c>
       <c r="D185" t="n">
-        <v>0.4349539048107436</v>
+        <v>0.44771080916479</v>
       </c>
       <c r="E185" t="n">
         <v>184</v>
@@ -3954,17 +3954,17 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>2021-02-04</t>
+          <t>2021-02-08</t>
         </is>
       </c>
       <c r="B186" t="n">
-        <v>26745949814</v>
+        <v>22845413099</v>
       </c>
       <c r="C186" t="n">
-        <v>65026335158</v>
+        <v>53099229697</v>
       </c>
       <c r="D186" t="n">
-        <v>0.411309506356357</v>
+        <v>0.4302400096830542</v>
       </c>
       <c r="E186" t="n">
         <v>185</v>
@@ -3973,17 +3973,17 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>2021-02-05</t>
+          <t>2021-02-09</t>
         </is>
       </c>
       <c r="B187" t="n">
-        <v>27228530445</v>
+        <v>23052987297</v>
       </c>
       <c r="C187" t="n">
-        <v>60817228192</v>
+        <v>54414450658</v>
       </c>
       <c r="D187" t="n">
-        <v>0.44771080916479</v>
+        <v>0.4236556101960896</v>
       </c>
       <c r="E187" t="n">
         <v>186</v>
@@ -3992,17 +3992,17 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>2021-02-08</t>
+          <t>2021-02-10</t>
         </is>
       </c>
       <c r="B188" t="n">
-        <v>22845413099</v>
+        <v>23672043794</v>
       </c>
       <c r="C188" t="n">
-        <v>53099229697</v>
+        <v>53724833418</v>
       </c>
       <c r="D188" t="n">
-        <v>0.4302400096830542</v>
+        <v>0.4406164205260971</v>
       </c>
       <c r="E188" t="n">
         <v>187</v>
@@ -4011,17 +4011,17 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>2021-02-09</t>
+          <t>2021-02-18</t>
         </is>
       </c>
       <c r="B189" t="n">
-        <v>23052987297</v>
+        <v>30305438799</v>
       </c>
       <c r="C189" t="n">
-        <v>54414450658</v>
+        <v>70581483088</v>
       </c>
       <c r="D189" t="n">
-        <v>0.4236556101960896</v>
+        <v>0.4293681213982937</v>
       </c>
       <c r="E189" t="n">
         <v>188</v>
@@ -4030,17 +4030,17 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>2021-02-10</t>
+          <t>2021-02-19</t>
         </is>
       </c>
       <c r="B190" t="n">
-        <v>23672043794</v>
+        <v>31871390359</v>
       </c>
       <c r="C190" t="n">
-        <v>53724833418</v>
+        <v>74891926971</v>
       </c>
       <c r="D190" t="n">
-        <v>0.4406164205260971</v>
+        <v>0.4255650995779744</v>
       </c>
       <c r="E190" t="n">
         <v>189</v>
@@ -4049,17 +4049,17 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>2021-02-18</t>
+          <t>2021-02-22</t>
         </is>
       </c>
       <c r="B191" t="n">
-        <v>30305438799</v>
+        <v>41800730539</v>
       </c>
       <c r="C191" t="n">
-        <v>70581483088</v>
+        <v>98345390597</v>
       </c>
       <c r="D191" t="n">
-        <v>0.4293681213982937</v>
+        <v>0.4250400581588124</v>
       </c>
       <c r="E191" t="n">
         <v>190</v>
@@ -4068,17 +4068,17 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>2021-02-19</t>
+          <t>2021-02-23</t>
         </is>
       </c>
       <c r="B192" t="n">
-        <v>31871390359</v>
+        <v>36659765914</v>
       </c>
       <c r="C192" t="n">
-        <v>74891926971</v>
+        <v>79667225639</v>
       </c>
       <c r="D192" t="n">
-        <v>0.4255650995779744</v>
+        <v>0.4601611970287279</v>
       </c>
       <c r="E192" t="n">
         <v>191</v>
@@ -4087,17 +4087,17 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>2021-02-22</t>
+          <t>2021-02-24</t>
         </is>
       </c>
       <c r="B193" t="n">
-        <v>41800730539</v>
+        <v>33328852498</v>
       </c>
       <c r="C193" t="n">
-        <v>98345390597</v>
+        <v>74974298826</v>
       </c>
       <c r="D193" t="n">
-        <v>0.4250400581588124</v>
+        <v>0.4445370349557979</v>
       </c>
       <c r="E193" t="n">
         <v>192</v>
@@ -4106,17 +4106,17 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>2021-02-23</t>
+          <t>2021-02-25</t>
         </is>
       </c>
       <c r="B194" t="n">
-        <v>36659765914</v>
+        <v>33009105938</v>
       </c>
       <c r="C194" t="n">
-        <v>79667225639</v>
+        <v>72321851390</v>
       </c>
       <c r="D194" t="n">
-        <v>0.4601611970287279</v>
+        <v>0.4564195371603028</v>
       </c>
       <c r="E194" t="n">
         <v>193</v>
@@ -4125,17 +4125,17 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>2021-02-24</t>
+          <t>2021-02-26</t>
         </is>
       </c>
       <c r="B195" t="n">
-        <v>33328852498</v>
+        <v>29437488128</v>
       </c>
       <c r="C195" t="n">
-        <v>74974298826</v>
+        <v>67566280430</v>
       </c>
       <c r="D195" t="n">
-        <v>0.4445370349557979</v>
+        <v>0.4356831238993216</v>
       </c>
       <c r="E195" t="n">
         <v>194</v>
@@ -4144,17 +4144,17 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>2021-02-25</t>
+          <t>2021-03-01</t>
         </is>
       </c>
       <c r="B196" t="n">
-        <v>33009105938</v>
+        <v>28022529242</v>
       </c>
       <c r="C196" t="n">
-        <v>72321851390</v>
+        <v>65847760652</v>
       </c>
       <c r="D196" t="n">
-        <v>0.4564195371603028</v>
+        <v>0.425565409734991</v>
       </c>
       <c r="E196" t="n">
         <v>195</v>
@@ -4163,17 +4163,17 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>2021-02-26</t>
+          <t>2021-03-02</t>
         </is>
       </c>
       <c r="B197" t="n">
-        <v>29437488128</v>
+        <v>30548474585</v>
       </c>
       <c r="C197" t="n">
-        <v>67566280430</v>
+        <v>69441386639</v>
       </c>
       <c r="D197" t="n">
-        <v>0.4356831238993216</v>
+        <v>0.4399174046424243</v>
       </c>
       <c r="E197" t="n">
         <v>196</v>
@@ -4182,17 +4182,17 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>2021-03-01</t>
+          <t>2021-03-03</t>
         </is>
       </c>
       <c r="B198" t="n">
-        <v>28022529242</v>
+        <v>31581683271</v>
       </c>
       <c r="C198" t="n">
-        <v>65847760652</v>
+        <v>69999474895</v>
       </c>
       <c r="D198" t="n">
-        <v>0.425565409734991</v>
+        <v>0.4511702883253464</v>
       </c>
       <c r="E198" t="n">
         <v>197</v>
@@ -4201,17 +4201,17 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>2021-03-02</t>
+          <t>2021-03-04</t>
         </is>
       </c>
       <c r="B199" t="n">
-        <v>30548474585</v>
+        <v>36100282673</v>
       </c>
       <c r="C199" t="n">
-        <v>69441386639</v>
+        <v>78562142790</v>
       </c>
       <c r="D199" t="n">
-        <v>0.4399174046424243</v>
+        <v>0.4595124495203449</v>
       </c>
       <c r="E199" t="n">
         <v>198</v>
@@ -4220,17 +4220,17 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>2021-03-03</t>
+          <t>2021-03-05</t>
         </is>
       </c>
       <c r="B200" t="n">
-        <v>31581683271</v>
+        <v>32337135967</v>
       </c>
       <c r="C200" t="n">
-        <v>69999474895</v>
+        <v>73514786011</v>
       </c>
       <c r="D200" t="n">
-        <v>0.4511702883253464</v>
+        <v>0.4398725443091326</v>
       </c>
       <c r="E200" t="n">
         <v>199</v>
@@ -4239,17 +4239,17 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>2021-03-04</t>
+          <t>2021-03-08</t>
         </is>
       </c>
       <c r="B201" t="n">
-        <v>36100282673</v>
+        <v>34237890063</v>
       </c>
       <c r="C201" t="n">
-        <v>78562142790</v>
+        <v>78814375242</v>
       </c>
       <c r="D201" t="n">
-        <v>0.4595124495203449</v>
+        <v>0.4344117422471771</v>
       </c>
       <c r="E201" t="n">
         <v>200</v>
@@ -4258,17 +4258,17 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>2021-03-05</t>
+          <t>2021-03-09</t>
         </is>
       </c>
       <c r="B202" t="n">
-        <v>32337135967</v>
+        <v>35838361211</v>
       </c>
       <c r="C202" t="n">
-        <v>73514786011</v>
+        <v>82850202998</v>
       </c>
       <c r="D202" t="n">
-        <v>0.4398725443091326</v>
+        <v>0.4325681762284292</v>
       </c>
       <c r="E202" t="n">
         <v>201</v>
@@ -4277,17 +4277,17 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>2021-03-08</t>
+          <t>2021-03-10</t>
         </is>
       </c>
       <c r="B203" t="n">
-        <v>34237890063</v>
+        <v>26975456721</v>
       </c>
       <c r="C203" t="n">
-        <v>78814375242</v>
+        <v>62127335207</v>
       </c>
       <c r="D203" t="n">
-        <v>0.4344117422471771</v>
+        <v>0.4341962620981791</v>
       </c>
       <c r="E203" t="n">
         <v>202</v>
@@ -4296,17 +4296,17 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>2021-03-09</t>
+          <t>2021-03-11</t>
         </is>
       </c>
       <c r="B204" t="n">
-        <v>35838361211</v>
+        <v>30680047969</v>
       </c>
       <c r="C204" t="n">
-        <v>82850202998</v>
+        <v>66598157167</v>
       </c>
       <c r="D204" t="n">
-        <v>0.4325681762284292</v>
+        <v>0.4606741278451207</v>
       </c>
       <c r="E204" t="n">
         <v>203</v>
@@ -4315,17 +4315,17 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>2021-03-10</t>
+          <t>2021-03-12</t>
         </is>
       </c>
       <c r="B205" t="n">
-        <v>26975456721</v>
+        <v>33862968625</v>
       </c>
       <c r="C205" t="n">
-        <v>62127335207</v>
+        <v>72238010975</v>
       </c>
       <c r="D205" t="n">
-        <v>0.4341962620981791</v>
+        <v>0.4687693939513262</v>
       </c>
       <c r="E205" t="n">
         <v>204</v>
@@ -4334,17 +4334,17 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>2021-03-11</t>
+          <t>2021-03-15</t>
         </is>
       </c>
       <c r="B206" t="n">
-        <v>30680047969</v>
+        <v>34591765793</v>
       </c>
       <c r="C206" t="n">
-        <v>66598157167</v>
+        <v>71723136959</v>
       </c>
       <c r="D206" t="n">
-        <v>0.4606741278451207</v>
+        <v>0.4822957731585852</v>
       </c>
       <c r="E206" t="n">
         <v>205</v>
@@ -4353,17 +4353,17 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>2021-03-12</t>
+          <t>2021-03-16</t>
         </is>
       </c>
       <c r="B207" t="n">
-        <v>33862968625</v>
+        <v>29977825317</v>
       </c>
       <c r="C207" t="n">
-        <v>72238010975</v>
+        <v>67049266583</v>
       </c>
       <c r="D207" t="n">
-        <v>0.4687693939513262</v>
+        <v>0.447101465008429</v>
       </c>
       <c r="E207" t="n">
         <v>206</v>
@@ -4372,17 +4372,17 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>2021-03-15</t>
+          <t>2021-03-17</t>
         </is>
       </c>
       <c r="B208" t="n">
-        <v>34591765793</v>
+        <v>27491185060</v>
       </c>
       <c r="C208" t="n">
-        <v>71723136959</v>
+        <v>62515062852</v>
       </c>
       <c r="D208" t="n">
-        <v>0.4822957731585852</v>
+        <v>0.4397529780156095</v>
       </c>
       <c r="E208" t="n">
         <v>207</v>
@@ -4391,17 +4391,17 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>2021-03-16</t>
+          <t>2021-03-18</t>
         </is>
       </c>
       <c r="B209" t="n">
-        <v>29977825317</v>
+        <v>26739276351</v>
       </c>
       <c r="C209" t="n">
-        <v>67049266583</v>
+        <v>62832911819</v>
       </c>
       <c r="D209" t="n">
-        <v>0.447101465008429</v>
+        <v>0.4255616296762858</v>
       </c>
       <c r="E209" t="n">
         <v>208</v>
@@ -4410,17 +4410,17 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>2021-03-17</t>
+          <t>2021-03-19</t>
         </is>
       </c>
       <c r="B210" t="n">
-        <v>27491185060</v>
+        <v>28358235249</v>
       </c>
       <c r="C210" t="n">
-        <v>62515062852</v>
+        <v>65875538395</v>
       </c>
       <c r="D210" t="n">
-        <v>0.4397529780156095</v>
+        <v>0.4304820262562349</v>
       </c>
       <c r="E210" t="n">
         <v>209</v>
@@ -4429,17 +4429,17 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>2021-03-18</t>
+          <t>2021-03-22</t>
         </is>
       </c>
       <c r="B211" t="n">
-        <v>26739276351</v>
+        <v>29121013208</v>
       </c>
       <c r="C211" t="n">
-        <v>62832911819</v>
+        <v>67358226346</v>
       </c>
       <c r="D211" t="n">
-        <v>0.4255616296762858</v>
+        <v>0.4323304633707791</v>
       </c>
       <c r="E211" t="n">
         <v>210</v>
@@ -4448,17 +4448,17 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>2021-03-19</t>
+          <t>2021-03-23</t>
         </is>
       </c>
       <c r="B212" t="n">
-        <v>28358235249</v>
+        <v>29320271653</v>
       </c>
       <c r="C212" t="n">
-        <v>65875538395</v>
+        <v>70323191299</v>
       </c>
       <c r="D212" t="n">
-        <v>0.4304820262562349</v>
+        <v>0.4169360222623591</v>
       </c>
       <c r="E212" t="n">
         <v>211</v>
@@ -4467,17 +4467,17 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>2021-03-22</t>
+          <t>2021-03-24</t>
         </is>
       </c>
       <c r="B213" t="n">
-        <v>29121013208</v>
+        <v>28494202046</v>
       </c>
       <c r="C213" t="n">
-        <v>67358226346</v>
+        <v>67303523996</v>
       </c>
       <c r="D213" t="n">
-        <v>0.4323304633707791</v>
+        <v>0.423368649280437</v>
       </c>
       <c r="E213" t="n">
         <v>212</v>
@@ -4486,17 +4486,17 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>2021-03-23</t>
+          <t>2021-03-25</t>
         </is>
       </c>
       <c r="B214" t="n">
-        <v>29320271653</v>
+        <v>25857769578</v>
       </c>
       <c r="C214" t="n">
-        <v>70323191299</v>
+        <v>60650502617</v>
       </c>
       <c r="D214" t="n">
-        <v>0.4169360222623591</v>
+        <v>0.426340565407816</v>
       </c>
       <c r="E214" t="n">
         <v>213</v>
@@ -4505,17 +4505,17 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>2021-03-24</t>
+          <t>2021-03-26</t>
         </is>
       </c>
       <c r="B215" t="n">
-        <v>28494202046</v>
+        <v>25857588064</v>
       </c>
       <c r="C215" t="n">
-        <v>67303523996</v>
+        <v>61284664475</v>
       </c>
       <c r="D215" t="n">
-        <v>0.423368649280437</v>
+        <v>0.4219259138564452</v>
       </c>
       <c r="E215" t="n">
         <v>214</v>
@@ -4524,17 +4524,17 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>2021-03-25</t>
+          <t>2021-03-29</t>
         </is>
       </c>
       <c r="B216" t="n">
-        <v>25857769578</v>
+        <v>26030305012</v>
       </c>
       <c r="C216" t="n">
-        <v>60650502617</v>
+        <v>62965892538</v>
       </c>
       <c r="D216" t="n">
-        <v>0.426340565407816</v>
+        <v>0.4134032563151658</v>
       </c>
       <c r="E216" t="n">
         <v>215</v>
@@ -4543,17 +4543,17 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>2021-03-26</t>
+          <t>2021-03-30</t>
         </is>
       </c>
       <c r="B217" t="n">
-        <v>25857588064</v>
+        <v>25780001010</v>
       </c>
       <c r="C217" t="n">
-        <v>61284664475</v>
+        <v>62868502600</v>
       </c>
       <c r="D217" t="n">
-        <v>0.4219259138564452</v>
+        <v>0.4100622719460158</v>
       </c>
       <c r="E217" t="n">
         <v>216</v>
@@ -4562,17 +4562,17 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>2021-03-29</t>
+          <t>2021-03-31</t>
         </is>
       </c>
       <c r="B218" t="n">
-        <v>26030305012</v>
+        <v>25340940136</v>
       </c>
       <c r="C218" t="n">
-        <v>62965892538</v>
+        <v>58944651908</v>
       </c>
       <c r="D218" t="n">
-        <v>0.4134032563151658</v>
+        <v>0.4299107606157687</v>
       </c>
       <c r="E218" t="n">
         <v>217</v>
@@ -4581,17 +4581,17 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>2021-03-30</t>
+          <t>2021-04-01</t>
         </is>
       </c>
       <c r="B219" t="n">
-        <v>25780001010</v>
+        <v>24459982838</v>
       </c>
       <c r="C219" t="n">
-        <v>62868502600</v>
+        <v>57742915146</v>
       </c>
       <c r="D219" t="n">
-        <v>0.4100622719460158</v>
+        <v>0.4236014544148696</v>
       </c>
       <c r="E219" t="n">
         <v>218</v>
@@ -4600,17 +4600,17 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>2021-03-31</t>
+          <t>2021-04-02</t>
         </is>
       </c>
       <c r="B220" t="n">
-        <v>25340940136</v>
+        <v>23776468616</v>
       </c>
       <c r="C220" t="n">
-        <v>58944651908</v>
+        <v>57637646459</v>
       </c>
       <c r="D220" t="n">
-        <v>0.4299107606157687</v>
+        <v>0.4125162992717471</v>
       </c>
       <c r="E220" t="n">
         <v>219</v>
@@ -4619,17 +4619,17 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>2021-04-01</t>
+          <t>2021-04-06</t>
         </is>
       </c>
       <c r="B221" t="n">
-        <v>24459982838</v>
+        <v>21609152872</v>
       </c>
       <c r="C221" t="n">
-        <v>57742915146</v>
+        <v>54009467026</v>
       </c>
       <c r="D221" t="n">
-        <v>0.4236014544148696</v>
+        <v>0.4000993540928189</v>
       </c>
       <c r="E221" t="n">
         <v>220</v>
@@ -4638,17 +4638,17 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>2021-04-02</t>
+          <t>2021-04-07</t>
         </is>
       </c>
       <c r="B222" t="n">
-        <v>23776468616</v>
+        <v>28192988226</v>
       </c>
       <c r="C222" t="n">
-        <v>57637646459</v>
+        <v>64777711487</v>
       </c>
       <c r="D222" t="n">
-        <v>0.4125162992717471</v>
+        <v>0.4352266787266473</v>
       </c>
       <c r="E222" t="n">
         <v>221</v>
@@ -4657,17 +4657,17 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>2021-04-06</t>
+          <t>2021-04-08</t>
         </is>
       </c>
       <c r="B223" t="n">
-        <v>21609152872</v>
+        <v>31610774016</v>
       </c>
       <c r="C223" t="n">
-        <v>54009467026</v>
+        <v>70183037971</v>
       </c>
       <c r="D223" t="n">
-        <v>0.4000993540928189</v>
+        <v>0.4504047549076137</v>
       </c>
       <c r="E223" t="n">
         <v>222</v>
@@ -4676,17 +4676,17 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>2021-04-07</t>
+          <t>2021-04-09</t>
         </is>
       </c>
       <c r="B224" t="n">
-        <v>28192988226</v>
+        <v>27363203695</v>
       </c>
       <c r="C224" t="n">
-        <v>64777711487</v>
+        <v>60908586933</v>
       </c>
       <c r="D224" t="n">
-        <v>0.4352266787266473</v>
+        <v>0.4492503450309851</v>
       </c>
       <c r="E224" t="n">
         <v>223</v>
@@ -4695,17 +4695,17 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>2021-04-08</t>
+          <t>2021-04-12</t>
         </is>
       </c>
       <c r="B225" t="n">
-        <v>31610774016</v>
+        <v>29441281600</v>
       </c>
       <c r="C225" t="n">
-        <v>70183037971</v>
+        <v>66662877908</v>
       </c>
       <c r="D225" t="n">
-        <v>0.4504047549076137</v>
+        <v>0.4416443232563598</v>
       </c>
       <c r="E225" t="n">
         <v>224</v>
@@ -4714,17 +4714,17 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>2021-04-09</t>
+          <t>2021-04-13</t>
         </is>
       </c>
       <c r="B226" t="n">
-        <v>27363203695</v>
+        <v>26500289609</v>
       </c>
       <c r="C226" t="n">
-        <v>60908586933</v>
+        <v>60099497250</v>
       </c>
       <c r="D226" t="n">
-        <v>0.4492503450309851</v>
+        <v>0.4409402877159675</v>
       </c>
       <c r="E226" t="n">
         <v>225</v>
@@ -4733,17 +4733,17 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>2021-04-12</t>
+          <t>2021-04-14</t>
         </is>
       </c>
       <c r="B227" t="n">
-        <v>29441281600</v>
+        <v>24875678254</v>
       </c>
       <c r="C227" t="n">
-        <v>66662877908</v>
+        <v>56149660115</v>
       </c>
       <c r="D227" t="n">
-        <v>0.4416443232563598</v>
+        <v>0.4430245562137362</v>
       </c>
       <c r="E227" t="n">
         <v>226</v>
@@ -4752,17 +4752,17 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>2021-04-13</t>
+          <t>2021-04-15</t>
         </is>
       </c>
       <c r="B228" t="n">
-        <v>26500289609</v>
+        <v>23587218127</v>
       </c>
       <c r="C228" t="n">
-        <v>60099497250</v>
+        <v>56730832399</v>
       </c>
       <c r="D228" t="n">
-        <v>0.4409402877159675</v>
+        <v>0.4157742294543835</v>
       </c>
       <c r="E228" t="n">
         <v>227</v>
@@ -4771,17 +4771,17 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>2021-04-14</t>
+          <t>2021-04-16</t>
         </is>
       </c>
       <c r="B229" t="n">
-        <v>24875678254</v>
+        <v>23064238930</v>
       </c>
       <c r="C229" t="n">
-        <v>56149660115</v>
+        <v>60757105467</v>
       </c>
       <c r="D229" t="n">
-        <v>0.4430245562137362</v>
+        <v>0.3796138534368998</v>
       </c>
       <c r="E229" t="n">
         <v>228</v>
@@ -4790,17 +4790,17 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>2021-04-15</t>
+          <t>2021-04-19</t>
         </is>
       </c>
       <c r="B230" t="n">
-        <v>23587218127</v>
+        <v>26349229565</v>
       </c>
       <c r="C230" t="n">
-        <v>56730832399</v>
+        <v>68717257011</v>
       </c>
       <c r="D230" t="n">
-        <v>0.4157742294543835</v>
+        <v>0.3834441406877186</v>
       </c>
       <c r="E230" t="n">
         <v>229</v>
@@ -4809,17 +4809,17 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>2021-04-16</t>
+          <t>2021-04-20</t>
         </is>
       </c>
       <c r="B231" t="n">
-        <v>23064238930</v>
+        <v>26332452757</v>
       </c>
       <c r="C231" t="n">
-        <v>60757105467</v>
+        <v>66152179163</v>
       </c>
       <c r="D231" t="n">
-        <v>0.3796138534368998</v>
+        <v>0.3980587350284626</v>
       </c>
       <c r="E231" t="n">
         <v>230</v>
@@ -4828,17 +4828,17 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>2021-04-19</t>
+          <t>2021-04-21</t>
         </is>
       </c>
       <c r="B232" t="n">
-        <v>26349229565</v>
+        <v>23796108657</v>
       </c>
       <c r="C232" t="n">
-        <v>68717257011</v>
+        <v>58645267418</v>
       </c>
       <c r="D232" t="n">
-        <v>0.3834441406877186</v>
+        <v>0.4057634947316526</v>
       </c>
       <c r="E232" t="n">
         <v>231</v>
@@ -4847,17 +4847,17 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>2021-04-20</t>
+          <t>2021-04-22</t>
         </is>
       </c>
       <c r="B233" t="n">
-        <v>26332452757</v>
+        <v>23283868400</v>
       </c>
       <c r="C233" t="n">
-        <v>66152179163</v>
+        <v>57343158813</v>
       </c>
       <c r="D233" t="n">
-        <v>0.3980587350284626</v>
+        <v>0.406044398006226</v>
       </c>
       <c r="E233" t="n">
         <v>232</v>
@@ -4866,17 +4866,17 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>2021-04-21</t>
+          <t>2021-04-23</t>
         </is>
       </c>
       <c r="B234" t="n">
-        <v>23796108657</v>
+        <v>23110619160</v>
       </c>
       <c r="C234" t="n">
-        <v>58645267418</v>
+        <v>58758936747</v>
       </c>
       <c r="D234" t="n">
-        <v>0.4057634947316526</v>
+        <v>0.3933124123655954</v>
       </c>
       <c r="E234" t="n">
         <v>233</v>
@@ -4885,17 +4885,17 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>2021-04-22</t>
+          <t>2021-04-26</t>
         </is>
       </c>
       <c r="B235" t="n">
-        <v>23283868400</v>
+        <v>26080656908</v>
       </c>
       <c r="C235" t="n">
-        <v>57343158813</v>
+        <v>64990659217</v>
       </c>
       <c r="D235" t="n">
-        <v>0.406044398006226</v>
+        <v>0.4012985438556365</v>
       </c>
       <c r="E235" t="n">
         <v>234</v>
@@ -4904,17 +4904,17 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>2021-04-23</t>
+          <t>2021-04-27</t>
         </is>
       </c>
       <c r="B236" t="n">
-        <v>23110619160</v>
+        <v>22805398723</v>
       </c>
       <c r="C236" t="n">
-        <v>58758936747</v>
+        <v>58465572266</v>
       </c>
       <c r="D236" t="n">
-        <v>0.3933124123655954</v>
+        <v>0.3900654323409783</v>
       </c>
       <c r="E236" t="n">
         <v>235</v>
@@ -4923,17 +4923,17 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>2021-04-26</t>
+          <t>2021-04-28</t>
         </is>
       </c>
       <c r="B237" t="n">
-        <v>26080656908</v>
+        <v>21764975470</v>
       </c>
       <c r="C237" t="n">
-        <v>64990659217</v>
+        <v>56258757783</v>
       </c>
       <c r="D237" t="n">
-        <v>0.4012985438556365</v>
+        <v>0.3868726635229197</v>
       </c>
       <c r="E237" t="n">
         <v>236</v>
@@ -4942,17 +4942,17 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>2021-04-27</t>
+          <t>2021-04-29</t>
         </is>
       </c>
       <c r="B238" t="n">
-        <v>22805398723</v>
+        <v>23871290845</v>
       </c>
       <c r="C238" t="n">
-        <v>58465572266</v>
+        <v>59672070298</v>
       </c>
       <c r="D238" t="n">
-        <v>0.3900654323409783</v>
+        <v>0.400041270996426</v>
       </c>
       <c r="E238" t="n">
         <v>237</v>
@@ -4961,17 +4961,17 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>2021-04-28</t>
+          <t>2021-04-30</t>
         </is>
       </c>
       <c r="B239" t="n">
-        <v>21764975470</v>
+        <v>26727927563</v>
       </c>
       <c r="C239" t="n">
-        <v>56258757783</v>
+        <v>64623812735</v>
       </c>
       <c r="D239" t="n">
-        <v>0.3868726635229197</v>
+        <v>0.413592550978105</v>
       </c>
       <c r="E239" t="n">
         <v>238</v>
@@ -4980,17 +4980,17 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>2021-04-29</t>
+          <t>2021-05-06</t>
         </is>
       </c>
       <c r="B240" t="n">
-        <v>23871290845</v>
+        <v>28245158344</v>
       </c>
       <c r="C240" t="n">
-        <v>59672070298</v>
+        <v>64995398044</v>
       </c>
       <c r="D240" t="n">
-        <v>0.400041270996426</v>
+        <v>0.4345716649797089</v>
       </c>
       <c r="E240" t="n">
         <v>239</v>
@@ -4999,17 +4999,17 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>2021-04-30</t>
+          <t>2021-05-07</t>
         </is>
       </c>
       <c r="B241" t="n">
-        <v>26727927563</v>
+        <v>33809492530</v>
       </c>
       <c r="C241" t="n">
-        <v>64623812735</v>
+        <v>72689004129</v>
       </c>
       <c r="D241" t="n">
-        <v>0.413592550978105</v>
+        <v>0.4651252680529072</v>
       </c>
       <c r="E241" t="n">
         <v>240</v>
@@ -5018,17 +5018,17 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>2021-05-06</t>
+          <t>2021-05-10</t>
         </is>
       </c>
       <c r="B242" t="n">
-        <v>28245158344</v>
+        <v>34980447442</v>
       </c>
       <c r="C242" t="n">
-        <v>64995398044</v>
+        <v>74391256531</v>
       </c>
       <c r="D242" t="n">
-        <v>0.4345716649797089</v>
+        <v>0.4702225647636843</v>
       </c>
       <c r="E242" t="n">
         <v>241</v>
@@ -5037,17 +5037,17 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>2021-05-07</t>
+          <t>2021-05-11</t>
         </is>
       </c>
       <c r="B243" t="n">
-        <v>33809492530</v>
+        <v>33682768573</v>
       </c>
       <c r="C243" t="n">
-        <v>72689004129</v>
+        <v>73459473614</v>
       </c>
       <c r="D243" t="n">
-        <v>0.4651252680529072</v>
+        <v>0.4585217796412401</v>
       </c>
       <c r="E243" t="n">
         <v>242</v>
@@ -5056,39 +5056,20 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>2021-05-10</t>
+          <t>2021-05-12</t>
         </is>
       </c>
       <c r="B244" t="n">
-        <v>34980447442</v>
+        <v>28011409229</v>
       </c>
       <c r="C244" t="n">
-        <v>74391256531</v>
+        <v>66061705250</v>
       </c>
       <c r="D244" t="n">
-        <v>0.4702225647636843</v>
+        <v>0.4240188642269418</v>
       </c>
       <c r="E244" t="n">
         <v>243</v>
-      </c>
-    </row>
-    <row r="245">
-      <c r="A245" t="inlineStr">
-        <is>
-          <t>2021-05-11</t>
-        </is>
-      </c>
-      <c r="B245" t="n">
-        <v>33682768573</v>
-      </c>
-      <c r="C245" t="n">
-        <v>73459473614</v>
-      </c>
-      <c r="D245" t="n">
-        <v>0.4585217796412401</v>
-      </c>
-      <c r="E245" t="n">
-        <v>244</v>
       </c>
     </row>
   </sheetData>

--- a/king_index/output/index.xlsx
+++ b/king_index/output/index.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E244"/>
+  <dimension ref="A1:E245"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5072,6 +5072,25 @@
         <v>243</v>
       </c>
     </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>2021-05-13</t>
+        </is>
+      </c>
+      <c r="B245" t="n">
+        <v>29021959092</v>
+      </c>
+      <c r="C245" t="n">
+        <v>69247970457</v>
+      </c>
+      <c r="D245" t="n">
+        <v>0.4191019448002651</v>
+      </c>
+      <c r="E245" t="n">
+        <v>244</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/king_index/output/index.xlsx
+++ b/king_index/output/index.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E245"/>
+  <dimension ref="A1:E246"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5091,6 +5091,25 @@
         <v>244</v>
       </c>
     </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>2021-05-14</t>
+        </is>
+      </c>
+      <c r="B246" t="n">
+        <v>29087549466</v>
+      </c>
+      <c r="C246" t="n">
+        <v>72865719627</v>
+      </c>
+      <c r="D246" t="n">
+        <v>0.3991938817718307</v>
+      </c>
+      <c r="E246" t="n">
+        <v>245</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/king_index/output/index.xlsx
+++ b/king_index/output/index.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E246"/>
+  <dimension ref="A1:E247"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5110,6 +5110,25 @@
         <v>245</v>
       </c>
     </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>2021-05-17</t>
+        </is>
+      </c>
+      <c r="B247" t="n">
+        <v>26738086558</v>
+      </c>
+      <c r="C247" t="n">
+        <v>68865623007</v>
+      </c>
+      <c r="D247" t="n">
+        <v>0.3882646433806625</v>
+      </c>
+      <c r="E247" t="n">
+        <v>246</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/king_index/output/index.xlsx
+++ b/king_index/output/index.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E247"/>
+  <dimension ref="A1:E248"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5129,6 +5129,25 @@
         <v>246</v>
       </c>
     </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>2021-05-18</t>
+        </is>
+      </c>
+      <c r="B248" t="n">
+        <v>23944078372</v>
+      </c>
+      <c r="C248" t="n">
+        <v>58781317109</v>
+      </c>
+      <c r="D248" t="n">
+        <v>0.4073416444139855</v>
+      </c>
+      <c r="E248" t="n">
+        <v>247</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/king_index/output/index.xlsx
+++ b/king_index/output/index.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E248"/>
+  <dimension ref="A1:E245"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -458,17 +458,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2020-05-13</t>
+          <t>2020-05-19</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>18559780599</v>
+        <v>18863773358</v>
       </c>
       <c r="C2" t="n">
-        <v>47805428174</v>
+        <v>50302048430</v>
       </c>
       <c r="D2" t="n">
-        <v>0.3882358407385656</v>
+        <v>0.3750100432639578</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>
@@ -477,17 +477,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2020-05-14</t>
+          <t>2020-05-20</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>20187004918</v>
+        <v>21259230267</v>
       </c>
       <c r="C3" t="n">
-        <v>51752238810</v>
+        <v>55292303555</v>
       </c>
       <c r="D3" t="n">
-        <v>0.3900701763282808</v>
+        <v>0.3844880553014609</v>
       </c>
       <c r="E3" t="n">
         <v>2</v>
@@ -496,17 +496,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2020-05-15</t>
+          <t>2020-05-21</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>19718626995</v>
+        <v>19280128498</v>
       </c>
       <c r="C4" t="n">
-        <v>50182102488</v>
+        <v>52065201803</v>
       </c>
       <c r="D4" t="n">
-        <v>0.3929414276676689</v>
+        <v>0.370307380560063</v>
       </c>
       <c r="E4" t="n">
         <v>3</v>
@@ -515,17 +515,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2020-05-18</t>
+          <t>2020-05-22</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>22559505827</v>
+        <v>17897770797</v>
       </c>
       <c r="C5" t="n">
-        <v>58319431318</v>
+        <v>50417741953</v>
       </c>
       <c r="D5" t="n">
-        <v>0.3868265742165617</v>
+        <v>0.3549895355028892</v>
       </c>
       <c r="E5" t="n">
         <v>4</v>
@@ -534,17 +534,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2020-05-19</t>
+          <t>2020-05-25</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>18863773358</v>
+        <v>14723899014</v>
       </c>
       <c r="C6" t="n">
-        <v>50302048430</v>
+        <v>41053704521</v>
       </c>
       <c r="D6" t="n">
-        <v>0.3750100432639578</v>
+        <v>0.3586497049606901</v>
       </c>
       <c r="E6" t="n">
         <v>5</v>
@@ -553,17 +553,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2020-05-20</t>
+          <t>2020-05-26</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>21259230267</v>
+        <v>15738642741</v>
       </c>
       <c r="C7" t="n">
-        <v>55292303555</v>
+        <v>44120432080</v>
       </c>
       <c r="D7" t="n">
-        <v>0.3844880553014609</v>
+        <v>0.3567200500770799</v>
       </c>
       <c r="E7" t="n">
         <v>6</v>
@@ -572,17 +572,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2020-05-21</t>
+          <t>2020-05-27</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>19280128498</v>
+        <v>17872745345</v>
       </c>
       <c r="C8" t="n">
-        <v>52065201803</v>
+        <v>48783198139</v>
       </c>
       <c r="D8" t="n">
-        <v>0.370307380560063</v>
+        <v>0.366370923326397</v>
       </c>
       <c r="E8" t="n">
         <v>7</v>
@@ -591,17 +591,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2020-05-22</t>
+          <t>2020-05-28</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>17897770797</v>
+        <v>18416635989</v>
       </c>
       <c r="C9" t="n">
-        <v>50417741953</v>
+        <v>50047777669</v>
       </c>
       <c r="D9" t="n">
-        <v>0.3549895355028892</v>
+        <v>0.3679810942016595</v>
       </c>
       <c r="E9" t="n">
         <v>8</v>
@@ -610,17 +610,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2020-05-25</t>
+          <t>2020-05-29</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>14723899014</v>
+        <v>18782496399</v>
       </c>
       <c r="C10" t="n">
-        <v>41053704521</v>
+        <v>49396386216</v>
       </c>
       <c r="D10" t="n">
-        <v>0.3586497049606901</v>
+        <v>0.3802402936293375</v>
       </c>
       <c r="E10" t="n">
         <v>9</v>
@@ -629,17 +629,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2020-05-26</t>
+          <t>2020-06-01</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>15738642741</v>
+        <v>22806246928</v>
       </c>
       <c r="C11" t="n">
-        <v>44120432080</v>
+        <v>64259168243</v>
       </c>
       <c r="D11" t="n">
-        <v>0.3567200500770799</v>
+        <v>0.3549103972487906</v>
       </c>
       <c r="E11" t="n">
         <v>10</v>
@@ -648,17 +648,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2020-05-27</t>
+          <t>2020-06-02</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>17872745345</v>
+        <v>26690797837</v>
       </c>
       <c r="C12" t="n">
-        <v>48783198139</v>
+        <v>67019269521</v>
       </c>
       <c r="D12" t="n">
-        <v>0.366370923326397</v>
+        <v>0.3982555767582133</v>
       </c>
       <c r="E12" t="n">
         <v>11</v>
@@ -667,17 +667,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2020-05-28</t>
+          <t>2020-06-03</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>18416635989</v>
+        <v>25988325662</v>
       </c>
       <c r="C13" t="n">
-        <v>50047777669</v>
+        <v>66814592975</v>
       </c>
       <c r="D13" t="n">
-        <v>0.3679810942016595</v>
+        <v>0.3889618196390726</v>
       </c>
       <c r="E13" t="n">
         <v>12</v>
@@ -686,17 +686,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2020-05-29</t>
+          <t>2020-06-04</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>18782496399</v>
+        <v>22648232850</v>
       </c>
       <c r="C14" t="n">
-        <v>49396386216</v>
+        <v>57964700247</v>
       </c>
       <c r="D14" t="n">
-        <v>0.3802402936293375</v>
+        <v>0.3907245746720164</v>
       </c>
       <c r="E14" t="n">
         <v>13</v>
@@ -705,17 +705,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2020-06-01</t>
+          <t>2020-06-05</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>22806246928</v>
+        <v>21624249509</v>
       </c>
       <c r="C15" t="n">
-        <v>64259168243</v>
+        <v>55387084107</v>
       </c>
       <c r="D15" t="n">
-        <v>0.3549103972487906</v>
+        <v>0.3904204356962539</v>
       </c>
       <c r="E15" t="n">
         <v>14</v>
@@ -724,17 +724,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2020-06-02</t>
+          <t>2020-06-08</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>26690797837</v>
+        <v>23546771032</v>
       </c>
       <c r="C16" t="n">
-        <v>67019269521</v>
+        <v>58352042780</v>
       </c>
       <c r="D16" t="n">
-        <v>0.3982555767582133</v>
+        <v>0.4035295065980208</v>
       </c>
       <c r="E16" t="n">
         <v>15</v>
@@ -743,17 +743,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2020-06-03</t>
+          <t>2020-06-09</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>25988325662</v>
+        <v>20955198305</v>
       </c>
       <c r="C17" t="n">
-        <v>66814592975</v>
+        <v>53192911283</v>
       </c>
       <c r="D17" t="n">
-        <v>0.3889618196390726</v>
+        <v>0.3939471970900961</v>
       </c>
       <c r="E17" t="n">
         <v>16</v>
@@ -762,17 +762,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2020-06-04</t>
+          <t>2020-06-10</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>22648232850</v>
+        <v>20190478240</v>
       </c>
       <c r="C18" t="n">
-        <v>57964700247</v>
+        <v>52136701032</v>
       </c>
       <c r="D18" t="n">
-        <v>0.3907245746720164</v>
+        <v>0.3872603720670333</v>
       </c>
       <c r="E18" t="n">
         <v>17</v>
@@ -781,17 +781,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2020-06-05</t>
+          <t>2020-06-11</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>21624249509</v>
+        <v>21856153332</v>
       </c>
       <c r="C19" t="n">
-        <v>55387084107</v>
+        <v>58580995849</v>
       </c>
       <c r="D19" t="n">
-        <v>0.3904204356962539</v>
+        <v>0.3730928949780408</v>
       </c>
       <c r="E19" t="n">
         <v>18</v>
@@ -800,17 +800,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2020-06-08</t>
+          <t>2020-06-12</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>23546771032</v>
+        <v>22554032456</v>
       </c>
       <c r="C20" t="n">
-        <v>58352042780</v>
+        <v>58624630321</v>
       </c>
       <c r="D20" t="n">
-        <v>0.4035295065980208</v>
+        <v>0.3847193975041731</v>
       </c>
       <c r="E20" t="n">
         <v>19</v>
@@ -819,17 +819,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2020-06-09</t>
+          <t>2020-06-15</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>20955198305</v>
+        <v>24160399741</v>
       </c>
       <c r="C21" t="n">
-        <v>53192911283</v>
+        <v>62827231135</v>
       </c>
       <c r="D21" t="n">
-        <v>0.3939471970900961</v>
+        <v>0.3845529924609497</v>
       </c>
       <c r="E21" t="n">
         <v>20</v>
@@ -838,17 +838,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2020-06-10</t>
+          <t>2020-06-16</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>20190478240</v>
+        <v>22302612612</v>
       </c>
       <c r="C22" t="n">
-        <v>52136701032</v>
+        <v>57871475779</v>
       </c>
       <c r="D22" t="n">
-        <v>0.3872603720670333</v>
+        <v>0.3853817845801855</v>
       </c>
       <c r="E22" t="n">
         <v>21</v>
@@ -857,17 +857,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2020-06-11</t>
+          <t>2020-06-17</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>21856153332</v>
+        <v>23156031895</v>
       </c>
       <c r="C23" t="n">
-        <v>58580995849</v>
+        <v>61386131654</v>
       </c>
       <c r="D23" t="n">
-        <v>0.3730928949780408</v>
+        <v>0.3772192720257707</v>
       </c>
       <c r="E23" t="n">
         <v>22</v>
@@ -876,17 +876,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2020-06-12</t>
+          <t>2020-06-18</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>22554032456</v>
+        <v>25733088111</v>
       </c>
       <c r="C24" t="n">
-        <v>58624630321</v>
+        <v>63354121102</v>
       </c>
       <c r="D24" t="n">
-        <v>0.3847193975041731</v>
+        <v>0.4061785983830442</v>
       </c>
       <c r="E24" t="n">
         <v>23</v>
@@ -895,17 +895,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2020-06-15</t>
+          <t>2020-06-19</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>24160399741</v>
+        <v>24126480724</v>
       </c>
       <c r="C25" t="n">
-        <v>62827231135</v>
+        <v>61888832308</v>
       </c>
       <c r="D25" t="n">
-        <v>0.3845529924609497</v>
+        <v>0.3898357720489956</v>
       </c>
       <c r="E25" t="n">
         <v>24</v>
@@ -914,17 +914,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2020-06-16</t>
+          <t>2020-06-22</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>22302612612</v>
+        <v>25010112764</v>
       </c>
       <c r="C26" t="n">
-        <v>57871475779</v>
+        <v>63846785740</v>
       </c>
       <c r="D26" t="n">
-        <v>0.3853817845801855</v>
+        <v>0.3917207808369149</v>
       </c>
       <c r="E26" t="n">
         <v>25</v>
@@ -933,17 +933,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2020-06-17</t>
+          <t>2020-06-23</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>23156031895</v>
+        <v>21417149307</v>
       </c>
       <c r="C27" t="n">
-        <v>61386131654</v>
+        <v>56906481203</v>
       </c>
       <c r="D27" t="n">
-        <v>0.3772192720257707</v>
+        <v>0.3763569430799901</v>
       </c>
       <c r="E27" t="n">
         <v>26</v>
@@ -952,17 +952,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2020-06-18</t>
+          <t>2020-06-24</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>25733088111</v>
+        <v>19322024502</v>
       </c>
       <c r="C28" t="n">
-        <v>63354121102</v>
+        <v>52926747938</v>
       </c>
       <c r="D28" t="n">
-        <v>0.4061785983830442</v>
+        <v>0.3650710700123576</v>
       </c>
       <c r="E28" t="n">
         <v>27</v>
@@ -971,17 +971,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2020-06-19</t>
+          <t>2020-06-29</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>24126480724</v>
+        <v>20448932009</v>
       </c>
       <c r="C29" t="n">
-        <v>61888832308</v>
+        <v>54347085975</v>
       </c>
       <c r="D29" t="n">
-        <v>0.3898357720489956</v>
+        <v>0.3762654729713868</v>
       </c>
       <c r="E29" t="n">
         <v>28</v>
@@ -990,17 +990,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2020-06-22</t>
+          <t>2020-06-30</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>25010112764</v>
+        <v>20003048931</v>
       </c>
       <c r="C30" t="n">
-        <v>63846785740</v>
+        <v>53946886834</v>
       </c>
       <c r="D30" t="n">
-        <v>0.3917207808369149</v>
+        <v>0.3707915341352578</v>
       </c>
       <c r="E30" t="n">
         <v>29</v>
@@ -1009,17 +1009,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2020-06-23</t>
+          <t>2020-07-01</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>21417149307</v>
+        <v>25539868441</v>
       </c>
       <c r="C31" t="n">
-        <v>56906481203</v>
+        <v>66477208273</v>
       </c>
       <c r="D31" t="n">
-        <v>0.3763569430799901</v>
+        <v>0.3841898464826647</v>
       </c>
       <c r="E31" t="n">
         <v>30</v>
@@ -1028,17 +1028,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2020-06-24</t>
+          <t>2020-07-02</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>19322024502</v>
+        <v>35281401239</v>
       </c>
       <c r="C32" t="n">
-        <v>52926747938</v>
+        <v>86277275738</v>
       </c>
       <c r="D32" t="n">
-        <v>0.3650710700123576</v>
+        <v>0.4089304041789609</v>
       </c>
       <c r="E32" t="n">
         <v>31</v>
@@ -1047,17 +1047,17 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2020-06-29</t>
+          <t>2020-07-03</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>20448932009</v>
+        <v>39589081860</v>
       </c>
       <c r="C33" t="n">
-        <v>54347085975</v>
+        <v>96590527098</v>
       </c>
       <c r="D33" t="n">
-        <v>0.3762654729713868</v>
+        <v>0.4098650566409398</v>
       </c>
       <c r="E33" t="n">
         <v>32</v>
@@ -1066,17 +1066,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2020-06-30</t>
+          <t>2020-07-06</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>20003048931</v>
+        <v>51680326902</v>
       </c>
       <c r="C34" t="n">
-        <v>53946886834</v>
+        <v>132721246132</v>
       </c>
       <c r="D34" t="n">
-        <v>0.3707915341352578</v>
+        <v>0.3893900065600689</v>
       </c>
       <c r="E34" t="n">
         <v>33</v>
@@ -1085,17 +1085,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2020-07-01</t>
+          <t>2020-07-07</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>25539868441</v>
+        <v>54130474812</v>
       </c>
       <c r="C35" t="n">
-        <v>66477208273</v>
+        <v>140540263998</v>
       </c>
       <c r="D35" t="n">
-        <v>0.3841898464826647</v>
+        <v>0.3851599055824338</v>
       </c>
       <c r="E35" t="n">
         <v>34</v>
@@ -1104,17 +1104,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2020-07-02</t>
+          <t>2020-07-08</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>35281401239</v>
+        <v>48763694238</v>
       </c>
       <c r="C36" t="n">
-        <v>86277275738</v>
+        <v>124820435614</v>
       </c>
       <c r="D36" t="n">
-        <v>0.4089304041789609</v>
+        <v>0.3906707583427999</v>
       </c>
       <c r="E36" t="n">
         <v>35</v>
@@ -1123,17 +1123,17 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2020-07-03</t>
+          <t>2020-07-09</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>39589081860</v>
+        <v>50352644938</v>
       </c>
       <c r="C37" t="n">
-        <v>96590527098</v>
+        <v>137276438768</v>
       </c>
       <c r="D37" t="n">
-        <v>0.4098650566409398</v>
+        <v>0.3667974299879457</v>
       </c>
       <c r="E37" t="n">
         <v>36</v>
@@ -1142,17 +1142,17 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2020-07-06</t>
+          <t>2020-07-10</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>51680326902</v>
+        <v>45792064703</v>
       </c>
       <c r="C38" t="n">
-        <v>132721246132</v>
+        <v>124540979573</v>
       </c>
       <c r="D38" t="n">
-        <v>0.3893900065600689</v>
+        <v>0.3676867233580644</v>
       </c>
       <c r="E38" t="n">
         <v>37</v>
@@ -1161,17 +1161,17 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2020-07-07</t>
+          <t>2020-07-13</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>54130474812</v>
+        <v>45569190970</v>
       </c>
       <c r="C39" t="n">
-        <v>140540263998</v>
+        <v>125874117474</v>
       </c>
       <c r="D39" t="n">
-        <v>0.3851599055824338</v>
+        <v>0.3620219301987366</v>
       </c>
       <c r="E39" t="n">
         <v>38</v>
@@ -1180,17 +1180,17 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2020-07-08</t>
+          <t>2020-07-14</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>48763694238</v>
+        <v>44404671526</v>
       </c>
       <c r="C40" t="n">
-        <v>124820435614</v>
+        <v>127205292718</v>
       </c>
       <c r="D40" t="n">
-        <v>0.3906707583427999</v>
+        <v>0.3490788046409375</v>
       </c>
       <c r="E40" t="n">
         <v>39</v>
@@ -1199,17 +1199,17 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2020-07-09</t>
+          <t>2020-07-15</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>50352644938</v>
+        <v>40948010990</v>
       </c>
       <c r="C41" t="n">
-        <v>137276438768</v>
+        <v>115744357395</v>
       </c>
       <c r="D41" t="n">
-        <v>0.3667974299879457</v>
+        <v>0.3537797600815822</v>
       </c>
       <c r="E41" t="n">
         <v>40</v>
@@ -1218,17 +1218,17 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2020-07-10</t>
+          <t>2020-07-16</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>45792064703</v>
+        <v>41327517137</v>
       </c>
       <c r="C42" t="n">
-        <v>124540979573</v>
+        <v>110570972319</v>
       </c>
       <c r="D42" t="n">
-        <v>0.3676867233580644</v>
+        <v>0.373764617152584</v>
       </c>
       <c r="E42" t="n">
         <v>41</v>
@@ -1237,17 +1237,17 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2020-07-13</t>
+          <t>2020-07-17</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>45569190970</v>
+        <v>30786629717</v>
       </c>
       <c r="C43" t="n">
-        <v>125874117474</v>
+        <v>83073812068</v>
       </c>
       <c r="D43" t="n">
-        <v>0.3620219301987366</v>
+        <v>0.3705936798927636</v>
       </c>
       <c r="E43" t="n">
         <v>42</v>
@@ -1256,17 +1256,17 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2020-07-14</t>
+          <t>2020-07-20</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>44404671526</v>
+        <v>33302406491</v>
       </c>
       <c r="C44" t="n">
-        <v>127205292718</v>
+        <v>90725025902</v>
       </c>
       <c r="D44" t="n">
-        <v>0.3490788046409375</v>
+        <v>0.3670696829226903</v>
       </c>
       <c r="E44" t="n">
         <v>43</v>
@@ -1275,17 +1275,17 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2020-07-15</t>
+          <t>2020-07-21</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>40948010990</v>
+        <v>29750727633</v>
       </c>
       <c r="C45" t="n">
-        <v>115744357395</v>
+        <v>82804408460</v>
       </c>
       <c r="D45" t="n">
-        <v>0.3537797600815822</v>
+        <v>0.3592891753749025</v>
       </c>
       <c r="E45" t="n">
         <v>44</v>
@@ -1294,17 +1294,17 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2020-07-16</t>
+          <t>2020-07-22</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>41327517137</v>
+        <v>32546369994</v>
       </c>
       <c r="C46" t="n">
-        <v>110570972319</v>
+        <v>88951002081</v>
       </c>
       <c r="D46" t="n">
-        <v>0.373764617152584</v>
+        <v>0.3658909875389917</v>
       </c>
       <c r="E46" t="n">
         <v>45</v>
@@ -1313,17 +1313,17 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2020-07-17</t>
+          <t>2020-07-23</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>30786629717</v>
+        <v>33380341470</v>
       </c>
       <c r="C47" t="n">
-        <v>83073812068</v>
+        <v>92918126099</v>
       </c>
       <c r="D47" t="n">
-        <v>0.3705936798927636</v>
+        <v>0.3592446691664313</v>
       </c>
       <c r="E47" t="n">
         <v>46</v>
@@ -1332,17 +1332,17 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2020-07-20</t>
+          <t>2020-07-24</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>33302406491</v>
+        <v>34826858650</v>
       </c>
       <c r="C48" t="n">
-        <v>90725025902</v>
+        <v>98778010270</v>
       </c>
       <c r="D48" t="n">
-        <v>0.3670696829226903</v>
+        <v>0.3525770417404056</v>
       </c>
       <c r="E48" t="n">
         <v>47</v>
@@ -1351,17 +1351,17 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2020-07-21</t>
+          <t>2020-07-27</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>29750727633</v>
+        <v>25272101520</v>
       </c>
       <c r="C49" t="n">
-        <v>82804408460</v>
+        <v>69273127708</v>
       </c>
       <c r="D49" t="n">
-        <v>0.3592891753749025</v>
+        <v>0.3648182542951854</v>
       </c>
       <c r="E49" t="n">
         <v>48</v>
@@ -1370,17 +1370,17 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2020-07-22</t>
+          <t>2020-07-28</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>32546369994</v>
+        <v>25533477451</v>
       </c>
       <c r="C50" t="n">
-        <v>88951002081</v>
+        <v>67557159363</v>
       </c>
       <c r="D50" t="n">
-        <v>0.3658909875389917</v>
+        <v>0.3779536868002814</v>
       </c>
       <c r="E50" t="n">
         <v>49</v>
@@ -1389,17 +1389,17 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2020-07-23</t>
+          <t>2020-07-29</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>33380341470</v>
+        <v>27398207256</v>
       </c>
       <c r="C51" t="n">
-        <v>92918126099</v>
+        <v>75808503607</v>
       </c>
       <c r="D51" t="n">
-        <v>0.3592446691664313</v>
+        <v>0.3614133764997586</v>
       </c>
       <c r="E51" t="n">
         <v>50</v>
@@ -1408,17 +1408,17 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2020-07-24</t>
+          <t>2020-07-30</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>34826858650</v>
+        <v>29316097538</v>
       </c>
       <c r="C52" t="n">
-        <v>98778010270</v>
+        <v>80705680370</v>
       </c>
       <c r="D52" t="n">
-        <v>0.3525770417404056</v>
+        <v>0.3632470156201968</v>
       </c>
       <c r="E52" t="n">
         <v>51</v>
@@ -1427,17 +1427,17 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2020-07-27</t>
+          <t>2020-07-31</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>25272101520</v>
+        <v>30421341838</v>
       </c>
       <c r="C53" t="n">
-        <v>69273127708</v>
+        <v>83388719271</v>
       </c>
       <c r="D53" t="n">
-        <v>0.3648182542951854</v>
+        <v>0.3648136355126825</v>
       </c>
       <c r="E53" t="n">
         <v>52</v>
@@ -1446,17 +1446,17 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2020-07-28</t>
+          <t>2020-08-03</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>25533477451</v>
+        <v>32534419194</v>
       </c>
       <c r="C54" t="n">
-        <v>67557159363</v>
+        <v>97147468049</v>
       </c>
       <c r="D54" t="n">
-        <v>0.3779536868002814</v>
+        <v>0.3348972427937086</v>
       </c>
       <c r="E54" t="n">
         <v>53</v>
@@ -1465,17 +1465,17 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2020-07-29</t>
+          <t>2020-08-04</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>27398207256</v>
+        <v>35518548960</v>
       </c>
       <c r="C55" t="n">
-        <v>75808503607</v>
+        <v>100401661483</v>
       </c>
       <c r="D55" t="n">
-        <v>0.3614133764997586</v>
+        <v>0.3537645536474912</v>
       </c>
       <c r="E55" t="n">
         <v>54</v>
@@ -1484,17 +1484,17 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2020-07-30</t>
+          <t>2020-08-05</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>29316097538</v>
+        <v>31118752071</v>
       </c>
       <c r="C56" t="n">
-        <v>80705680370</v>
+        <v>88411991123</v>
       </c>
       <c r="D56" t="n">
-        <v>0.3632470156201968</v>
+        <v>0.351974338273947</v>
       </c>
       <c r="E56" t="n">
         <v>55</v>
@@ -1503,17 +1503,17 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2020-07-31</t>
+          <t>2020-08-06</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>30421341838</v>
+        <v>35289080996</v>
       </c>
       <c r="C57" t="n">
-        <v>83388719271</v>
+        <v>94484631872</v>
       </c>
       <c r="D57" t="n">
-        <v>0.3648136355126825</v>
+        <v>0.3734901676264849</v>
       </c>
       <c r="E57" t="n">
         <v>56</v>
@@ -1522,17 +1522,17 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2020-08-03</t>
+          <t>2020-08-07</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>32534419194</v>
+        <v>33926327226</v>
       </c>
       <c r="C58" t="n">
-        <v>97147468049</v>
+        <v>90977583613</v>
       </c>
       <c r="D58" t="n">
-        <v>0.3348972427937086</v>
+        <v>0.3729086427522151</v>
       </c>
       <c r="E58" t="n">
         <v>57</v>
@@ -1541,17 +1541,17 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2020-08-04</t>
+          <t>2020-08-10</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>35518548960</v>
+        <v>29708663069</v>
       </c>
       <c r="C59" t="n">
-        <v>100401661483</v>
+        <v>82942928747</v>
       </c>
       <c r="D59" t="n">
-        <v>0.3537645536474912</v>
+        <v>0.3581819875160189</v>
       </c>
       <c r="E59" t="n">
         <v>58</v>
@@ -1560,17 +1560,17 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2020-08-05</t>
+          <t>2020-08-11</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>31118752071</v>
+        <v>30946369948</v>
       </c>
       <c r="C60" t="n">
-        <v>88411991123</v>
+        <v>86295092754</v>
       </c>
       <c r="D60" t="n">
-        <v>0.351974338273947</v>
+        <v>0.3586110051033644</v>
       </c>
       <c r="E60" t="n">
         <v>59</v>
@@ -1579,17 +1579,17 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2020-08-06</t>
+          <t>2020-08-12</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>35289080996</v>
+        <v>29856245191</v>
       </c>
       <c r="C61" t="n">
-        <v>94484631872</v>
+        <v>82452473263</v>
       </c>
       <c r="D61" t="n">
-        <v>0.3734901676264849</v>
+        <v>0.3621024817019988</v>
       </c>
       <c r="E61" t="n">
         <v>60</v>
@@ -1598,17 +1598,17 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2020-08-07</t>
+          <t>2020-08-13</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>33926327226</v>
+        <v>27823565615</v>
       </c>
       <c r="C62" t="n">
-        <v>90977583613</v>
+        <v>72532322436</v>
       </c>
       <c r="D62" t="n">
-        <v>0.3729086427522151</v>
+        <v>0.3836022986793308</v>
       </c>
       <c r="E62" t="n">
         <v>61</v>
@@ -1617,17 +1617,17 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2020-08-10</t>
+          <t>2020-08-14</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>29708663069</v>
+        <v>27261549866</v>
       </c>
       <c r="C63" t="n">
-        <v>82942928747</v>
+        <v>69180221661</v>
       </c>
       <c r="D63" t="n">
-        <v>0.3581819875160189</v>
+        <v>0.3940656622869504</v>
       </c>
       <c r="E63" t="n">
         <v>62</v>
@@ -1636,17 +1636,17 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2020-08-11</t>
+          <t>2020-08-17</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>30946369948</v>
+        <v>37118467741</v>
       </c>
       <c r="C64" t="n">
-        <v>86295092754</v>
+        <v>91788369903</v>
       </c>
       <c r="D64" t="n">
-        <v>0.3586110051033644</v>
+        <v>0.4043918394043386</v>
       </c>
       <c r="E64" t="n">
         <v>63</v>
@@ -1655,17 +1655,17 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2020-08-12</t>
+          <t>2020-08-18</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>29856245191</v>
+        <v>31325687773</v>
       </c>
       <c r="C65" t="n">
-        <v>82452473263</v>
+        <v>85178317604</v>
       </c>
       <c r="D65" t="n">
-        <v>0.3621024817019988</v>
+        <v>0.3677659838109897</v>
       </c>
       <c r="E65" t="n">
         <v>64</v>
@@ -1674,17 +1674,17 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2020-08-13</t>
+          <t>2020-08-19</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>27823565615</v>
+        <v>33073383828</v>
       </c>
       <c r="C66" t="n">
-        <v>72532322436</v>
+        <v>88140275731</v>
       </c>
       <c r="D66" t="n">
-        <v>0.3836022986793308</v>
+        <v>0.375235765417145</v>
       </c>
       <c r="E66" t="n">
         <v>65</v>
@@ -1693,17 +1693,17 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2020-08-14</t>
+          <t>2020-08-20</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>27261549866</v>
+        <v>27646953314</v>
       </c>
       <c r="C67" t="n">
-        <v>69180221661</v>
+        <v>72119978332</v>
       </c>
       <c r="D67" t="n">
-        <v>0.3940656622869504</v>
+        <v>0.3833466669489126</v>
       </c>
       <c r="E67" t="n">
         <v>66</v>
@@ -1712,17 +1712,17 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2020-08-17</t>
+          <t>2020-08-21</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>37118467741</v>
+        <v>25486130617</v>
       </c>
       <c r="C68" t="n">
-        <v>91788369903</v>
+        <v>66786682396</v>
       </c>
       <c r="D68" t="n">
-        <v>0.4043918394043386</v>
+        <v>0.3816049802546626</v>
       </c>
       <c r="E68" t="n">
         <v>67</v>
@@ -1731,17 +1731,17 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2020-08-18</t>
+          <t>2020-08-24</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>31325687773</v>
+        <v>25209284709</v>
       </c>
       <c r="C69" t="n">
-        <v>85178317604</v>
+        <v>67412296336</v>
       </c>
       <c r="D69" t="n">
-        <v>0.3677659838109897</v>
+        <v>0.3739567716748666</v>
       </c>
       <c r="E69" t="n">
         <v>68</v>
@@ -1750,17 +1750,17 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2020-08-19</t>
+          <t>2020-08-25</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>33073383828</v>
+        <v>26619247474</v>
       </c>
       <c r="C70" t="n">
-        <v>88140275731</v>
+        <v>73103731924</v>
       </c>
       <c r="D70" t="n">
-        <v>0.375235765417145</v>
+        <v>0.3641298025889275</v>
       </c>
       <c r="E70" t="n">
         <v>69</v>
@@ -1769,17 +1769,17 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2020-08-20</t>
+          <t>2020-08-26</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>27646953314</v>
+        <v>26322908958</v>
       </c>
       <c r="C71" t="n">
-        <v>72119978332</v>
+        <v>75716936591</v>
       </c>
       <c r="D71" t="n">
-        <v>0.3833466669489126</v>
+        <v>0.3476488899727732</v>
       </c>
       <c r="E71" t="n">
         <v>70</v>
@@ -1788,17 +1788,17 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2020-08-21</t>
+          <t>2020-08-27</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>25486130617</v>
+        <v>23276018839</v>
       </c>
       <c r="C72" t="n">
-        <v>66786682396</v>
+        <v>65005692955</v>
       </c>
       <c r="D72" t="n">
-        <v>0.3816049802546626</v>
+        <v>0.3580612371152286</v>
       </c>
       <c r="E72" t="n">
         <v>71</v>
@@ -1807,17 +1807,17 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2020-08-24</t>
+          <t>2020-08-28</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>25209284709</v>
+        <v>25701039669</v>
       </c>
       <c r="C73" t="n">
-        <v>67412296336</v>
+        <v>70850828969</v>
       </c>
       <c r="D73" t="n">
-        <v>0.3739567716748666</v>
+        <v>0.3627486091975749</v>
       </c>
       <c r="E73" t="n">
         <v>72</v>
@@ -1826,17 +1826,17 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2020-08-25</t>
+          <t>2020-08-31</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>26619247474</v>
+        <v>28573296373</v>
       </c>
       <c r="C74" t="n">
-        <v>73103731924</v>
+        <v>77184652221</v>
       </c>
       <c r="D74" t="n">
-        <v>0.3641298025889275</v>
+        <v>0.3701940159189566</v>
       </c>
       <c r="E74" t="n">
         <v>73</v>
@@ -1845,17 +1845,17 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2020-08-26</t>
+          <t>2020-09-01</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>26322908958</v>
+        <v>23964180511</v>
       </c>
       <c r="C75" t="n">
-        <v>75716936591</v>
+        <v>64392996012</v>
       </c>
       <c r="D75" t="n">
-        <v>0.3476488899727732</v>
+        <v>0.3721550788929613</v>
       </c>
       <c r="E75" t="n">
         <v>74</v>
@@ -1864,17 +1864,17 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2020-08-27</t>
+          <t>2020-09-02</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>23276018839</v>
+        <v>30082062270</v>
       </c>
       <c r="C76" t="n">
-        <v>65005692955</v>
+        <v>77531927895</v>
       </c>
       <c r="D76" t="n">
-        <v>0.3580612371152286</v>
+        <v>0.3879957984630482</v>
       </c>
       <c r="E76" t="n">
         <v>75</v>
@@ -1883,17 +1883,17 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2020-08-28</t>
+          <t>2020-09-03</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>25701039669</v>
+        <v>27715216294</v>
       </c>
       <c r="C77" t="n">
-        <v>70850828969</v>
+        <v>73519808249</v>
       </c>
       <c r="D77" t="n">
-        <v>0.3627486091975749</v>
+        <v>0.3769761776327399</v>
       </c>
       <c r="E77" t="n">
         <v>76</v>
@@ -1902,17 +1902,17 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2020-08-31</t>
+          <t>2020-09-04</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>28573296373</v>
+        <v>24329945914</v>
       </c>
       <c r="C78" t="n">
-        <v>77184652221</v>
+        <v>65573685675</v>
       </c>
       <c r="D78" t="n">
-        <v>0.3701940159189566</v>
+        <v>0.37103215510236</v>
       </c>
       <c r="E78" t="n">
         <v>77</v>
@@ -1921,17 +1921,17 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2020-09-01</t>
+          <t>2020-09-07</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>23964180511</v>
+        <v>29997390344</v>
       </c>
       <c r="C79" t="n">
-        <v>64392996012</v>
+        <v>79881522723</v>
       </c>
       <c r="D79" t="n">
-        <v>0.3721550788929613</v>
+        <v>0.375523516846568</v>
       </c>
       <c r="E79" t="n">
         <v>78</v>
@@ -1940,17 +1940,17 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2020-09-02</t>
+          <t>2020-09-08</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>30082062270</v>
+        <v>32724062545</v>
       </c>
       <c r="C80" t="n">
-        <v>77531927895</v>
+        <v>80161481426</v>
       </c>
       <c r="D80" t="n">
-        <v>0.3879957984630482</v>
+        <v>0.4082267688030289</v>
       </c>
       <c r="E80" t="n">
         <v>79</v>
@@ -1959,17 +1959,17 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2020-09-03</t>
+          <t>2020-09-09</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>27715216294</v>
+        <v>41720230941</v>
       </c>
       <c r="C81" t="n">
-        <v>73519808249</v>
+        <v>98517765305</v>
       </c>
       <c r="D81" t="n">
-        <v>0.3769761776327399</v>
+        <v>0.4234792660170358</v>
       </c>
       <c r="E81" t="n">
         <v>80</v>
@@ -1978,17 +1978,17 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2020-09-04</t>
+          <t>2020-09-10</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>24329945914</v>
+        <v>32362586075</v>
       </c>
       <c r="C82" t="n">
-        <v>65573685675</v>
+        <v>83938666669</v>
       </c>
       <c r="D82" t="n">
-        <v>0.37103215510236</v>
+        <v>0.3855503948212232</v>
       </c>
       <c r="E82" t="n">
         <v>81</v>
@@ -1997,17 +1997,17 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2020-09-07</t>
+          <t>2020-09-11</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>29997390344</v>
+        <v>23586290440</v>
       </c>
       <c r="C83" t="n">
-        <v>79881522723</v>
+        <v>60330240577</v>
       </c>
       <c r="D83" t="n">
-        <v>0.375523516846568</v>
+        <v>0.3909530314220547</v>
       </c>
       <c r="E83" t="n">
         <v>82</v>
@@ -2016,17 +2016,17 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2020-09-08</t>
+          <t>2020-09-14</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>32724062545</v>
+        <v>24462170352</v>
       </c>
       <c r="C84" t="n">
-        <v>80161481426</v>
+        <v>63101019998</v>
       </c>
       <c r="D84" t="n">
-        <v>0.4082267688030289</v>
+        <v>0.3876667976646865</v>
       </c>
       <c r="E84" t="n">
         <v>83</v>
@@ -2035,17 +2035,17 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2020-09-09</t>
+          <t>2020-09-15</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>41720230941</v>
+        <v>23106120892</v>
       </c>
       <c r="C85" t="n">
-        <v>98517765305</v>
+        <v>58614407766</v>
       </c>
       <c r="D85" t="n">
-        <v>0.4234792660170358</v>
+        <v>0.3942054824514151</v>
       </c>
       <c r="E85" t="n">
         <v>84</v>
@@ -2054,17 +2054,17 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2020-09-10</t>
+          <t>2020-09-16</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>32362586075</v>
+        <v>21724638649</v>
       </c>
       <c r="C86" t="n">
-        <v>83938666669</v>
+        <v>55182289033</v>
       </c>
       <c r="D86" t="n">
-        <v>0.3855503948212232</v>
+        <v>0.3936886096915674</v>
       </c>
       <c r="E86" t="n">
         <v>85</v>
@@ -2073,17 +2073,17 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2020-09-11</t>
+          <t>2020-09-17</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>23586290440</v>
+        <v>20554994106</v>
       </c>
       <c r="C87" t="n">
-        <v>60330240577</v>
+        <v>55472969929</v>
       </c>
       <c r="D87" t="n">
-        <v>0.3909530314220547</v>
+        <v>0.3705407179804577</v>
       </c>
       <c r="E87" t="n">
         <v>86</v>
@@ -2092,17 +2092,17 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2020-09-14</t>
+          <t>2020-09-18</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>24462170352</v>
+        <v>25018086444</v>
       </c>
       <c r="C88" t="n">
-        <v>63101019998</v>
+        <v>64587549837</v>
       </c>
       <c r="D88" t="n">
-        <v>0.3876667976646865</v>
+        <v>0.3873515330297914</v>
       </c>
       <c r="E88" t="n">
         <v>87</v>
@@ -2111,17 +2111,17 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2020-09-15</t>
+          <t>2020-09-21</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>23106120892</v>
+        <v>22182279260</v>
       </c>
       <c r="C89" t="n">
-        <v>58614407766</v>
+        <v>58098440053</v>
       </c>
       <c r="D89" t="n">
-        <v>0.3942054824514151</v>
+        <v>0.3818050749686968</v>
       </c>
       <c r="E89" t="n">
         <v>88</v>
@@ -2130,17 +2130,17 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2020-09-16</t>
+          <t>2020-09-22</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>21724638649</v>
+        <v>22099090990</v>
       </c>
       <c r="C90" t="n">
-        <v>55182289033</v>
+        <v>56264182474</v>
       </c>
       <c r="D90" t="n">
-        <v>0.3936886096915674</v>
+        <v>0.3927736975510506</v>
       </c>
       <c r="E90" t="n">
         <v>89</v>
@@ -2149,17 +2149,17 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2020-09-17</t>
+          <t>2020-09-23</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>20554994106</v>
+        <v>19077501915</v>
       </c>
       <c r="C91" t="n">
-        <v>55472969929</v>
+        <v>48597940983</v>
       </c>
       <c r="D91" t="n">
-        <v>0.3705407179804577</v>
+        <v>0.3925578230088695</v>
       </c>
       <c r="E91" t="n">
         <v>90</v>
@@ -2168,17 +2168,17 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2020-09-18</t>
+          <t>2020-09-24</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>25018086444</v>
+        <v>20859996043</v>
       </c>
       <c r="C92" t="n">
-        <v>64587549837</v>
+        <v>54861814882</v>
       </c>
       <c r="D92" t="n">
-        <v>0.3873515330297914</v>
+        <v>0.3802279616134993</v>
       </c>
       <c r="E92" t="n">
         <v>91</v>
@@ -2187,17 +2187,17 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2020-09-21</t>
+          <t>2020-09-25</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>22182279260</v>
+        <v>16281719043</v>
       </c>
       <c r="C93" t="n">
-        <v>58098440053</v>
+        <v>43622575116</v>
       </c>
       <c r="D93" t="n">
-        <v>0.3818050749686968</v>
+        <v>0.373240667239476</v>
       </c>
       <c r="E93" t="n">
         <v>92</v>
@@ -2206,17 +2206,17 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2020-09-22</t>
+          <t>2020-09-28</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>22099090990</v>
+        <v>14676583271</v>
       </c>
       <c r="C94" t="n">
-        <v>56264182474</v>
+        <v>40556797589</v>
       </c>
       <c r="D94" t="n">
-        <v>0.3927736975510506</v>
+        <v>0.3618772719614492</v>
       </c>
       <c r="E94" t="n">
         <v>93</v>
@@ -2225,17 +2225,17 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2020-09-23</t>
+          <t>2020-09-29</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>19077501915</v>
+        <v>14442107257</v>
       </c>
       <c r="C95" t="n">
-        <v>48597940983</v>
+        <v>40163621965</v>
       </c>
       <c r="D95" t="n">
-        <v>0.3925578230088695</v>
+        <v>0.3595817944304267</v>
       </c>
       <c r="E95" t="n">
         <v>94</v>
@@ -2244,17 +2244,17 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2020-09-24</t>
+          <t>2020-09-30</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>20859996043</v>
+        <v>15066784297</v>
       </c>
       <c r="C96" t="n">
-        <v>54861814882</v>
+        <v>40300843448</v>
       </c>
       <c r="D96" t="n">
-        <v>0.3802279616134993</v>
+        <v>0.3738577907541961</v>
       </c>
       <c r="E96" t="n">
         <v>95</v>
@@ -2263,17 +2263,17 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2020-09-25</t>
+          <t>2020-10-09</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>16281719043</v>
+        <v>18363804782</v>
       </c>
       <c r="C97" t="n">
-        <v>43622575116</v>
+        <v>50410563994</v>
       </c>
       <c r="D97" t="n">
-        <v>0.373240667239476</v>
+        <v>0.3642848507742486</v>
       </c>
       <c r="E97" t="n">
         <v>96</v>
@@ -2282,17 +2282,17 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2020-09-28</t>
+          <t>2020-10-12</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>14676583271</v>
+        <v>24824121596</v>
       </c>
       <c r="C98" t="n">
-        <v>40556797589</v>
+        <v>69075123930</v>
       </c>
       <c r="D98" t="n">
-        <v>0.3618772719614492</v>
+        <v>0.3593786038104905</v>
       </c>
       <c r="E98" t="n">
         <v>97</v>
@@ -2301,17 +2301,17 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2020-09-29</t>
+          <t>2020-10-13</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>14442107257</v>
+        <v>21950874234</v>
       </c>
       <c r="C99" t="n">
-        <v>40163621965</v>
+        <v>58435290007</v>
       </c>
       <c r="D99" t="n">
-        <v>0.3595817944304267</v>
+        <v>0.3756441395494142</v>
       </c>
       <c r="E99" t="n">
         <v>98</v>
@@ -2320,17 +2320,17 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2020-09-30</t>
+          <t>2020-10-14</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>15066784297</v>
+        <v>21810988673</v>
       </c>
       <c r="C100" t="n">
-        <v>40300843448</v>
+        <v>58022364557</v>
       </c>
       <c r="D100" t="n">
-        <v>0.3738577907541961</v>
+        <v>0.3759065808421738</v>
       </c>
       <c r="E100" t="n">
         <v>99</v>
@@ -2339,17 +2339,17 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2020-10-09</t>
+          <t>2020-10-15</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>18363804782</v>
+        <v>20410751440</v>
       </c>
       <c r="C101" t="n">
-        <v>50410563994</v>
+        <v>54415224691</v>
       </c>
       <c r="D101" t="n">
-        <v>0.3642848507742486</v>
+        <v>0.3750926612157467</v>
       </c>
       <c r="E101" t="n">
         <v>100</v>
@@ -2358,17 +2358,17 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2020-10-12</t>
+          <t>2020-10-16</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>24824121596</v>
+        <v>19779199722</v>
       </c>
       <c r="C102" t="n">
-        <v>69075123930</v>
+        <v>51552706029</v>
       </c>
       <c r="D102" t="n">
-        <v>0.3593786038104905</v>
+        <v>0.3836694762613156</v>
       </c>
       <c r="E102" t="n">
         <v>101</v>
@@ -2377,17 +2377,17 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2020-10-13</t>
+          <t>2020-10-19</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>21950874234</v>
+        <v>20562725471</v>
       </c>
       <c r="C103" t="n">
-        <v>58435290007</v>
+        <v>53895497648</v>
       </c>
       <c r="D103" t="n">
-        <v>0.3756441395494142</v>
+        <v>0.3815295593947087</v>
       </c>
       <c r="E103" t="n">
         <v>102</v>
@@ -2396,17 +2396,17 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2020-10-14</t>
+          <t>2020-10-20</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>21810988673</v>
+        <v>18296672779</v>
       </c>
       <c r="C104" t="n">
-        <v>58022364557</v>
+        <v>47922773316</v>
       </c>
       <c r="D104" t="n">
-        <v>0.3759065808421738</v>
+        <v>0.3817949486844761</v>
       </c>
       <c r="E104" t="n">
         <v>103</v>
@@ -2415,17 +2415,17 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2020-10-15</t>
+          <t>2020-10-21</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>20410751440</v>
+        <v>18370049664</v>
       </c>
       <c r="C105" t="n">
-        <v>54415224691</v>
+        <v>49307563396</v>
       </c>
       <c r="D105" t="n">
-        <v>0.3750926612157467</v>
+        <v>0.3725604836009853</v>
       </c>
       <c r="E105" t="n">
         <v>104</v>
@@ -2434,17 +2434,17 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2020-10-16</t>
+          <t>2020-10-22</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>19779199722</v>
+        <v>17665602844</v>
       </c>
       <c r="C106" t="n">
-        <v>51552706029</v>
+        <v>46460364776</v>
       </c>
       <c r="D106" t="n">
-        <v>0.3836694762613156</v>
+        <v>0.3802295339085566</v>
       </c>
       <c r="E106" t="n">
         <v>105</v>
@@ -2453,17 +2453,17 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2020-10-19</t>
+          <t>2020-10-23</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>20562725471</v>
+        <v>17466910909</v>
       </c>
       <c r="C107" t="n">
-        <v>53895497648</v>
+        <v>47398504650</v>
       </c>
       <c r="D107" t="n">
-        <v>0.3815295593947087</v>
+        <v>0.3685118557637873</v>
       </c>
       <c r="E107" t="n">
         <v>106</v>
@@ -2472,17 +2472,17 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2020-10-20</t>
+          <t>2020-10-26</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>18296672779</v>
+        <v>16145407434</v>
       </c>
       <c r="C108" t="n">
-        <v>47922773316</v>
+        <v>44150494774</v>
       </c>
       <c r="D108" t="n">
-        <v>0.3817949486844761</v>
+        <v>0.3656902944496094</v>
       </c>
       <c r="E108" t="n">
         <v>107</v>
@@ -2491,17 +2491,17 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2020-10-21</t>
+          <t>2020-10-27</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>18370049664</v>
+        <v>15491813981</v>
       </c>
       <c r="C109" t="n">
-        <v>49307563396</v>
+        <v>43505082864</v>
       </c>
       <c r="D109" t="n">
-        <v>0.3725604836009853</v>
+        <v>0.356092046288672</v>
       </c>
       <c r="E109" t="n">
         <v>108</v>
@@ -2510,17 +2510,17 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2020-10-22</t>
+          <t>2020-10-28</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>17665602844</v>
+        <v>17543172634</v>
       </c>
       <c r="C110" t="n">
-        <v>46460364776</v>
+        <v>49485508785</v>
       </c>
       <c r="D110" t="n">
-        <v>0.3802295339085566</v>
+        <v>0.3545113117906887</v>
       </c>
       <c r="E110" t="n">
         <v>109</v>
@@ -2529,17 +2529,17 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2020-10-23</t>
+          <t>2020-10-29</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>17466910909</v>
+        <v>18553392322</v>
       </c>
       <c r="C111" t="n">
-        <v>47398504650</v>
+        <v>51689467398</v>
       </c>
       <c r="D111" t="n">
-        <v>0.3685118557637873</v>
+        <v>0.3589395142948963</v>
       </c>
       <c r="E111" t="n">
         <v>110</v>
@@ -2548,17 +2548,17 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2020-10-26</t>
+          <t>2020-10-30</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>16145407434</v>
+        <v>20650226596</v>
       </c>
       <c r="C112" t="n">
-        <v>44150494774</v>
+        <v>60348197366</v>
       </c>
       <c r="D112" t="n">
-        <v>0.3656902944496094</v>
+        <v>0.3421846467220954</v>
       </c>
       <c r="E112" t="n">
         <v>111</v>
@@ -2567,17 +2567,17 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2020-10-27</t>
+          <t>2020-11-02</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>15491813981</v>
+        <v>19992661394</v>
       </c>
       <c r="C113" t="n">
-        <v>43505082864</v>
+        <v>56353918211</v>
       </c>
       <c r="D113" t="n">
-        <v>0.356092046288672</v>
+        <v>0.3547696775784711</v>
       </c>
       <c r="E113" t="n">
         <v>112</v>
@@ -2586,17 +2586,17 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2020-10-28</t>
+          <t>2020-11-03</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>17543172634</v>
+        <v>20249408150</v>
       </c>
       <c r="C114" t="n">
-        <v>49485508785</v>
+        <v>55344378404</v>
       </c>
       <c r="D114" t="n">
-        <v>0.3545113117906887</v>
+        <v>0.365880126111173</v>
       </c>
       <c r="E114" t="n">
         <v>113</v>
@@ -2605,17 +2605,17 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2020-10-29</t>
+          <t>2020-11-04</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>18553392322</v>
+        <v>18257580496</v>
       </c>
       <c r="C115" t="n">
-        <v>51689467398</v>
+        <v>49909415865</v>
       </c>
       <c r="D115" t="n">
-        <v>0.3589395142948963</v>
+        <v>0.3658143494483073</v>
       </c>
       <c r="E115" t="n">
         <v>114</v>
@@ -2624,17 +2624,17 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2020-10-30</t>
+          <t>2020-11-05</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>20650226596</v>
+        <v>21285267389</v>
       </c>
       <c r="C116" t="n">
-        <v>60348197366</v>
+        <v>58980118835</v>
       </c>
       <c r="D116" t="n">
-        <v>0.3421846467220954</v>
+        <v>0.3608888522002924</v>
       </c>
       <c r="E116" t="n">
         <v>115</v>
@@ -2643,17 +2643,17 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2020-11-02</t>
+          <t>2020-11-06</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>19992661394</v>
+        <v>23071856412</v>
       </c>
       <c r="C117" t="n">
-        <v>56353918211</v>
+        <v>59902082650</v>
       </c>
       <c r="D117" t="n">
-        <v>0.3547696775784711</v>
+        <v>0.3851595034984981</v>
       </c>
       <c r="E117" t="n">
         <v>116</v>
@@ -2662,17 +2662,17 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2020-11-03</t>
+          <t>2020-11-09</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>20249408150</v>
+        <v>27202863336</v>
       </c>
       <c r="C118" t="n">
-        <v>55344378404</v>
+        <v>74478178320</v>
       </c>
       <c r="D118" t="n">
-        <v>0.365880126111173</v>
+        <v>0.3652460888492902</v>
       </c>
       <c r="E118" t="n">
         <v>117</v>
@@ -2681,17 +2681,17 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2020-11-04</t>
+          <t>2020-11-10</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>18257580496</v>
+        <v>25309810082</v>
       </c>
       <c r="C119" t="n">
-        <v>49909415865</v>
+        <v>67090114044</v>
       </c>
       <c r="D119" t="n">
-        <v>0.3658143494483073</v>
+        <v>0.3772509622714452</v>
       </c>
       <c r="E119" t="n">
         <v>118</v>
@@ -2700,17 +2700,17 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2020-11-05</t>
+          <t>2020-11-11</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>21285267389</v>
+        <v>23822441228</v>
       </c>
       <c r="C120" t="n">
-        <v>58980118835</v>
+        <v>61988411650</v>
       </c>
       <c r="D120" t="n">
-        <v>0.3608888522002924</v>
+        <v>0.3843047529997488</v>
       </c>
       <c r="E120" t="n">
         <v>119</v>
@@ -2719,17 +2719,17 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2020-11-06</t>
+          <t>2020-11-12</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>23071856412</v>
+        <v>19076439758</v>
       </c>
       <c r="C121" t="n">
-        <v>59902082650</v>
+        <v>51703999860</v>
       </c>
       <c r="D121" t="n">
-        <v>0.3851595034984981</v>
+        <v>0.3689548160616911</v>
       </c>
       <c r="E121" t="n">
         <v>120</v>
@@ -2738,17 +2738,17 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2020-11-09</t>
+          <t>2020-11-13</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>27202863336</v>
+        <v>20119982649</v>
       </c>
       <c r="C122" t="n">
-        <v>74478178320</v>
+        <v>52210418675</v>
       </c>
       <c r="D122" t="n">
-        <v>0.3652460888492902</v>
+        <v>0.3853633653896379</v>
       </c>
       <c r="E122" t="n">
         <v>121</v>
@@ -2757,17 +2757,17 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2020-11-10</t>
+          <t>2020-11-16</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>25309810082</v>
+        <v>23217241543</v>
       </c>
       <c r="C123" t="n">
-        <v>67090114044</v>
+        <v>61350411349</v>
       </c>
       <c r="D123" t="n">
-        <v>0.3772509622714452</v>
+        <v>0.3784366075546849</v>
       </c>
       <c r="E123" t="n">
         <v>122</v>
@@ -2776,17 +2776,17 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2020-11-11</t>
+          <t>2020-11-17</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>23822441228</v>
+        <v>24335506367</v>
       </c>
       <c r="C124" t="n">
-        <v>61988411650</v>
+        <v>64241703103</v>
       </c>
       <c r="D124" t="n">
-        <v>0.3843047529997488</v>
+        <v>0.3788116626980203</v>
       </c>
       <c r="E124" t="n">
         <v>123</v>
@@ -2795,17 +2795,17 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2020-11-12</t>
+          <t>2020-11-18</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>19076439758</v>
+        <v>25490702717</v>
       </c>
       <c r="C125" t="n">
-        <v>51703999860</v>
+        <v>63205463709</v>
       </c>
       <c r="D125" t="n">
-        <v>0.3689548160616911</v>
+        <v>0.4032990381078449</v>
       </c>
       <c r="E125" t="n">
         <v>124</v>
@@ -2814,17 +2814,17 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2020-11-13</t>
+          <t>2020-11-19</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>20119982649</v>
+        <v>23177522765</v>
       </c>
       <c r="C126" t="n">
-        <v>52210418675</v>
+        <v>59756276020</v>
       </c>
       <c r="D126" t="n">
-        <v>0.3853633653896379</v>
+        <v>0.3878675899623104</v>
       </c>
       <c r="E126" t="n">
         <v>125</v>
@@ -2833,17 +2833,17 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2020-11-16</t>
+          <t>2020-11-20</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>23217241543</v>
+        <v>22935620159</v>
       </c>
       <c r="C127" t="n">
-        <v>61350411349</v>
+        <v>58875754449</v>
       </c>
       <c r="D127" t="n">
-        <v>0.3784366075546849</v>
+        <v>0.3895596816320637</v>
       </c>
       <c r="E127" t="n">
         <v>126</v>
@@ -2852,17 +2852,17 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2020-11-17</t>
+          <t>2020-11-23</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>24335506367</v>
+        <v>32096579820</v>
       </c>
       <c r="C128" t="n">
-        <v>64241703103</v>
+        <v>77198006469</v>
       </c>
       <c r="D128" t="n">
-        <v>0.3788116626980203</v>
+        <v>0.4157695423506675</v>
       </c>
       <c r="E128" t="n">
         <v>127</v>
@@ -2871,17 +2871,17 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2020-11-18</t>
+          <t>2020-11-24</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>25490702717</v>
+        <v>26709718473</v>
       </c>
       <c r="C129" t="n">
-        <v>63205463709</v>
+        <v>65410116144</v>
       </c>
       <c r="D129" t="n">
-        <v>0.4032990381078449</v>
+        <v>0.408342318399171</v>
       </c>
       <c r="E129" t="n">
         <v>128</v>
@@ -2890,17 +2890,17 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2020-11-19</t>
+          <t>2020-11-25</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>23177522765</v>
+        <v>27089790866</v>
       </c>
       <c r="C130" t="n">
-        <v>59756276020</v>
+        <v>68837443765</v>
       </c>
       <c r="D130" t="n">
-        <v>0.3878675899623104</v>
+        <v>0.3935327836762824</v>
       </c>
       <c r="E130" t="n">
         <v>129</v>
@@ -2909,17 +2909,17 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2020-11-20</t>
+          <t>2020-11-26</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>22935620159</v>
+        <v>21689088930</v>
       </c>
       <c r="C131" t="n">
-        <v>58875754449</v>
+        <v>57127013421</v>
       </c>
       <c r="D131" t="n">
-        <v>0.3895596816320637</v>
+        <v>0.3796643239540867</v>
       </c>
       <c r="E131" t="n">
         <v>130</v>
@@ -2928,17 +2928,17 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>2020-11-23</t>
+          <t>2020-11-27</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>32096579820</v>
+        <v>23626364341</v>
       </c>
       <c r="C132" t="n">
-        <v>77198006469</v>
+        <v>58765160877</v>
       </c>
       <c r="D132" t="n">
-        <v>0.4157695423506675</v>
+        <v>0.4020471311301572</v>
       </c>
       <c r="E132" t="n">
         <v>131</v>
@@ -2947,17 +2947,17 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>2020-11-24</t>
+          <t>2020-11-30</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>26709718473</v>
+        <v>33970232252</v>
       </c>
       <c r="C133" t="n">
-        <v>65410116144</v>
+        <v>75092505579</v>
       </c>
       <c r="D133" t="n">
-        <v>0.408342318399171</v>
+        <v>0.4523784629381171</v>
       </c>
       <c r="E133" t="n">
         <v>132</v>
@@ -2966,17 +2966,17 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2020-11-25</t>
+          <t>2020-12-01</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>27089790866</v>
+        <v>28738868941</v>
       </c>
       <c r="C134" t="n">
-        <v>68837443765</v>
+        <v>67936162045</v>
       </c>
       <c r="D134" t="n">
-        <v>0.3935327836762824</v>
+        <v>0.4230275611089682</v>
       </c>
       <c r="E134" t="n">
         <v>133</v>
@@ -2985,17 +2985,17 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>2020-11-26</t>
+          <t>2020-12-02</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>21689088930</v>
+        <v>28928357564</v>
       </c>
       <c r="C135" t="n">
-        <v>57127013421</v>
+        <v>69689843826</v>
       </c>
       <c r="D135" t="n">
-        <v>0.3796643239540867</v>
+        <v>0.4151014835996427</v>
       </c>
       <c r="E135" t="n">
         <v>134</v>
@@ -3004,17 +3004,17 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>2020-11-27</t>
+          <t>2020-12-03</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>23626364341</v>
+        <v>28497726227</v>
       </c>
       <c r="C136" t="n">
-        <v>58765160877</v>
+        <v>66950741850</v>
       </c>
       <c r="D136" t="n">
-        <v>0.4020471311301572</v>
+        <v>0.4256521352795137</v>
       </c>
       <c r="E136" t="n">
         <v>135</v>
@@ -3023,17 +3023,17 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>2020-11-30</t>
+          <t>2020-12-04</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>33970232252</v>
+        <v>23614518756</v>
       </c>
       <c r="C137" t="n">
-        <v>75092505579</v>
+        <v>57124426015</v>
       </c>
       <c r="D137" t="n">
-        <v>0.4523784629381171</v>
+        <v>0.4133874141649876</v>
       </c>
       <c r="E137" t="n">
         <v>136</v>
@@ -3042,17 +3042,17 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>2020-12-01</t>
+          <t>2020-12-07</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>28738868941</v>
+        <v>22345056458</v>
       </c>
       <c r="C138" t="n">
-        <v>67936162045</v>
+        <v>56856559648</v>
       </c>
       <c r="D138" t="n">
-        <v>0.4230275611089682</v>
+        <v>0.3930075367967857</v>
       </c>
       <c r="E138" t="n">
         <v>137</v>
@@ -3061,17 +3061,17 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>2020-12-02</t>
+          <t>2020-12-08</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>28928357564</v>
+        <v>20555717183</v>
       </c>
       <c r="C139" t="n">
-        <v>69689843826</v>
+        <v>51665831943</v>
       </c>
       <c r="D139" t="n">
-        <v>0.4151014835996427</v>
+        <v>0.3978590184259099</v>
       </c>
       <c r="E139" t="n">
         <v>138</v>
@@ -3080,17 +3080,17 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>2020-12-03</t>
+          <t>2020-12-09</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>28497726227</v>
+        <v>22167887887</v>
       </c>
       <c r="C140" t="n">
-        <v>66950741850</v>
+        <v>59426788696</v>
       </c>
       <c r="D140" t="n">
-        <v>0.4256521352795137</v>
+        <v>0.3730285343265085</v>
       </c>
       <c r="E140" t="n">
         <v>139</v>
@@ -3099,17 +3099,17 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>2020-12-04</t>
+          <t>2020-12-10</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>23614518756</v>
+        <v>21008686040</v>
       </c>
       <c r="C141" t="n">
-        <v>57124426015</v>
+        <v>53530291688</v>
       </c>
       <c r="D141" t="n">
-        <v>0.4133874141649876</v>
+        <v>0.3924635076238444</v>
       </c>
       <c r="E141" t="n">
         <v>140</v>
@@ -3118,17 +3118,17 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>2020-12-07</t>
+          <t>2020-12-11</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>22345056458</v>
+        <v>24084146686</v>
       </c>
       <c r="C142" t="n">
-        <v>56856559648</v>
+        <v>64194443337</v>
       </c>
       <c r="D142" t="n">
-        <v>0.3930075367967857</v>
+        <v>0.3751749440300626</v>
       </c>
       <c r="E142" t="n">
         <v>141</v>
@@ -3137,17 +3137,17 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>2020-12-08</t>
+          <t>2020-12-14</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>20555717183</v>
+        <v>20561369384</v>
       </c>
       <c r="C143" t="n">
-        <v>51665831943</v>
+        <v>52737085483</v>
       </c>
       <c r="D143" t="n">
-        <v>0.3978590184259099</v>
+        <v>0.3898844465082932</v>
       </c>
       <c r="E143" t="n">
         <v>142</v>
@@ -3156,17 +3156,17 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>2020-12-09</t>
+          <t>2020-12-15</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>22167887887</v>
+        <v>20518702233</v>
       </c>
       <c r="C144" t="n">
-        <v>59426788696</v>
+        <v>50712282528</v>
       </c>
       <c r="D144" t="n">
-        <v>0.3730285343265085</v>
+        <v>0.4046101104139991</v>
       </c>
       <c r="E144" t="n">
         <v>143</v>
@@ -3175,17 +3175,17 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>2020-12-10</t>
+          <t>2020-12-16</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>21008686040</v>
+        <v>20098821894</v>
       </c>
       <c r="C145" t="n">
-        <v>53530291688</v>
+        <v>51594471274</v>
       </c>
       <c r="D145" t="n">
-        <v>0.3924635076238444</v>
+        <v>0.3895537912824469</v>
       </c>
       <c r="E145" t="n">
         <v>144</v>
@@ -3194,17 +3194,17 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>2020-12-11</t>
+          <t>2020-12-17</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>24084146686</v>
+        <v>23623180829</v>
       </c>
       <c r="C146" t="n">
-        <v>64194443337</v>
+        <v>60346809075</v>
       </c>
       <c r="D146" t="n">
-        <v>0.3751749440300626</v>
+        <v>0.3914569998165226</v>
       </c>
       <c r="E146" t="n">
         <v>145</v>
@@ -3213,17 +3213,17 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>2020-12-14</t>
+          <t>2020-12-18</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>20561369384</v>
+        <v>24395319589</v>
       </c>
       <c r="C147" t="n">
-        <v>52737085483</v>
+        <v>59011526731</v>
       </c>
       <c r="D147" t="n">
-        <v>0.3898844465082932</v>
+        <v>0.4133992279204094</v>
       </c>
       <c r="E147" t="n">
         <v>146</v>
@@ -3232,17 +3232,17 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>2020-12-15</t>
+          <t>2020-12-21</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>20518702233</v>
+        <v>25669905456</v>
       </c>
       <c r="C148" t="n">
-        <v>50712282528</v>
+        <v>62473191028</v>
       </c>
       <c r="D148" t="n">
-        <v>0.4046101104139991</v>
+        <v>0.410894737944392</v>
       </c>
       <c r="E148" t="n">
         <v>147</v>
@@ -3251,17 +3251,17 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>2020-12-16</t>
+          <t>2020-12-22</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>20098821894</v>
+        <v>27752409533</v>
       </c>
       <c r="C149" t="n">
-        <v>51594471274</v>
+        <v>70592976908</v>
       </c>
       <c r="D149" t="n">
-        <v>0.3895537912824469</v>
+        <v>0.3931327271998773</v>
       </c>
       <c r="E149" t="n">
         <v>148</v>
@@ -3270,17 +3270,17 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>2020-12-17</t>
+          <t>2020-12-23</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>23623180829</v>
+        <v>26781996550</v>
       </c>
       <c r="C150" t="n">
-        <v>60346809075</v>
+        <v>66516491988</v>
       </c>
       <c r="D150" t="n">
-        <v>0.3914569998165226</v>
+        <v>0.4026369363380084</v>
       </c>
       <c r="E150" t="n">
         <v>149</v>
@@ -3289,17 +3289,17 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>2020-12-18</t>
+          <t>2020-12-24</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>24395319589</v>
+        <v>23869444669</v>
       </c>
       <c r="C151" t="n">
-        <v>59011526731</v>
+        <v>63015856260</v>
       </c>
       <c r="D151" t="n">
-        <v>0.4133992279204094</v>
+        <v>0.3787847390427572</v>
       </c>
       <c r="E151" t="n">
         <v>150</v>
@@ -3308,17 +3308,17 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>2020-12-21</t>
+          <t>2020-12-25</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>25669905456</v>
+        <v>25870374333</v>
       </c>
       <c r="C152" t="n">
-        <v>62473191028</v>
+        <v>63035613181</v>
       </c>
       <c r="D152" t="n">
-        <v>0.410894737944392</v>
+        <v>0.4104088629822002</v>
       </c>
       <c r="E152" t="n">
         <v>151</v>
@@ -3327,17 +3327,17 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>2020-12-22</t>
+          <t>2020-12-28</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>27752409533</v>
+        <v>27591719605</v>
       </c>
       <c r="C153" t="n">
-        <v>70592976908</v>
+        <v>68634054637</v>
       </c>
       <c r="D153" t="n">
-        <v>0.3931327271998773</v>
+        <v>0.4020120878903394</v>
       </c>
       <c r="E153" t="n">
         <v>152</v>
@@ -3346,17 +3346,17 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>2020-12-23</t>
+          <t>2020-12-29</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>26781996550</v>
+        <v>28714767727</v>
       </c>
       <c r="C154" t="n">
-        <v>66516491988</v>
+        <v>68080937199</v>
       </c>
       <c r="D154" t="n">
-        <v>0.4026369363380084</v>
+        <v>0.4217739782733451</v>
       </c>
       <c r="E154" t="n">
         <v>153</v>
@@ -3365,17 +3365,17 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>2020-12-24</t>
+          <t>2020-12-30</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>23869444669</v>
+        <v>27431057672</v>
       </c>
       <c r="C155" t="n">
-        <v>63015856260</v>
+        <v>63970764234</v>
       </c>
       <c r="D155" t="n">
-        <v>0.3787847390427572</v>
+        <v>0.4288061585704895</v>
       </c>
       <c r="E155" t="n">
         <v>154</v>
@@ -3384,17 +3384,17 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>2020-12-25</t>
+          <t>2020-12-31</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>25870374333</v>
+        <v>29516497306</v>
       </c>
       <c r="C156" t="n">
-        <v>63035613181</v>
+        <v>70483427194</v>
       </c>
       <c r="D156" t="n">
-        <v>0.4104088629822002</v>
+        <v>0.4187721636287379</v>
       </c>
       <c r="E156" t="n">
         <v>155</v>
@@ -3403,17 +3403,17 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>2020-12-28</t>
+          <t>2021-01-04</t>
         </is>
       </c>
       <c r="B157" t="n">
-        <v>27591719605</v>
+        <v>32842910849</v>
       </c>
       <c r="C157" t="n">
-        <v>68634054637</v>
+        <v>81262611004</v>
       </c>
       <c r="D157" t="n">
-        <v>0.4020120878903394</v>
+        <v>0.4041577109475767</v>
       </c>
       <c r="E157" t="n">
         <v>156</v>
@@ -3422,17 +3422,17 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>2020-12-29</t>
+          <t>2021-01-05</t>
         </is>
       </c>
       <c r="B158" t="n">
-        <v>28714767727</v>
+        <v>34955476638</v>
       </c>
       <c r="C158" t="n">
-        <v>68080937199</v>
+        <v>86306603527</v>
       </c>
       <c r="D158" t="n">
-        <v>0.4217739782733451</v>
+        <v>0.4050150881799513</v>
       </c>
       <c r="E158" t="n">
         <v>157</v>
@@ -3441,17 +3441,17 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>2020-12-30</t>
+          <t>2021-01-06</t>
         </is>
       </c>
       <c r="B159" t="n">
-        <v>27431057672</v>
+        <v>31318863380</v>
       </c>
       <c r="C159" t="n">
-        <v>63970764234</v>
+        <v>79924024318</v>
       </c>
       <c r="D159" t="n">
-        <v>0.4288061585704895</v>
+        <v>0.3918579381762507</v>
       </c>
       <c r="E159" t="n">
         <v>158</v>
@@ -3460,17 +3460,17 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>2020-12-31</t>
+          <t>2021-01-07</t>
         </is>
       </c>
       <c r="B160" t="n">
-        <v>29516497306</v>
+        <v>34820241307</v>
       </c>
       <c r="C160" t="n">
-        <v>70483427194</v>
+        <v>87045282583</v>
       </c>
       <c r="D160" t="n">
-        <v>0.4187721636287379</v>
+        <v>0.4000244501911746</v>
       </c>
       <c r="E160" t="n">
         <v>159</v>
@@ -3479,17 +3479,17 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>2021-01-04</t>
+          <t>2021-01-08</t>
         </is>
       </c>
       <c r="B161" t="n">
-        <v>32842910849</v>
+        <v>31741361539</v>
       </c>
       <c r="C161" t="n">
-        <v>81262611004</v>
+        <v>76243328872</v>
       </c>
       <c r="D161" t="n">
-        <v>0.4041577109475767</v>
+        <v>0.4163165749529185</v>
       </c>
       <c r="E161" t="n">
         <v>160</v>
@@ -3498,17 +3498,17 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>2021-01-05</t>
+          <t>2021-01-11</t>
         </is>
       </c>
       <c r="B162" t="n">
-        <v>34955476638</v>
+        <v>33861909952</v>
       </c>
       <c r="C162" t="n">
-        <v>86306603527</v>
+        <v>79843929989</v>
       </c>
       <c r="D162" t="n">
-        <v>0.4050150881799513</v>
+        <v>0.4241012429706943</v>
       </c>
       <c r="E162" t="n">
         <v>161</v>
@@ -3517,17 +3517,17 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>2021-01-06</t>
+          <t>2021-01-12</t>
         </is>
       </c>
       <c r="B163" t="n">
-        <v>31318863380</v>
+        <v>31336739617</v>
       </c>
       <c r="C163" t="n">
-        <v>79924024318</v>
+        <v>70684174141</v>
       </c>
       <c r="D163" t="n">
-        <v>0.3918579381762507</v>
+        <v>0.4433345936035105</v>
       </c>
       <c r="E163" t="n">
         <v>162</v>
@@ -3536,17 +3536,17 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>2021-01-07</t>
+          <t>2021-01-13</t>
         </is>
       </c>
       <c r="B164" t="n">
-        <v>34820241307</v>
+        <v>36176556832</v>
       </c>
       <c r="C164" t="n">
-        <v>87045282583</v>
+        <v>81782457644</v>
       </c>
       <c r="D164" t="n">
-        <v>0.4000244501911746</v>
+        <v>0.4423510600461162</v>
       </c>
       <c r="E164" t="n">
         <v>163</v>
@@ -3555,17 +3555,17 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>2021-01-08</t>
+          <t>2021-01-14</t>
         </is>
       </c>
       <c r="B165" t="n">
-        <v>31741361539</v>
+        <v>32971296424</v>
       </c>
       <c r="C165" t="n">
-        <v>76243328872</v>
+        <v>74034016193</v>
       </c>
       <c r="D165" t="n">
-        <v>0.4163165749529185</v>
+        <v>0.4453533405245341</v>
       </c>
       <c r="E165" t="n">
         <v>164</v>
@@ -3574,17 +3574,17 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>2021-01-11</t>
+          <t>2021-01-15</t>
         </is>
       </c>
       <c r="B166" t="n">
-        <v>33861909952</v>
+        <v>31268748151</v>
       </c>
       <c r="C166" t="n">
-        <v>79843929989</v>
+        <v>68522530970</v>
       </c>
       <c r="D166" t="n">
-        <v>0.4241012429706943</v>
+        <v>0.4563279801309417</v>
       </c>
       <c r="E166" t="n">
         <v>165</v>
@@ -3593,17 +3593,17 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>2021-01-12</t>
+          <t>2021-01-18</t>
         </is>
       </c>
       <c r="B167" t="n">
-        <v>31336739617</v>
+        <v>28025154838</v>
       </c>
       <c r="C167" t="n">
-        <v>70684174141</v>
+        <v>66132336803</v>
       </c>
       <c r="D167" t="n">
-        <v>0.4433345936035105</v>
+        <v>0.4237738479056539</v>
       </c>
       <c r="E167" t="n">
         <v>166</v>
@@ -3612,17 +3612,17 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>2021-01-13</t>
+          <t>2021-01-19</t>
         </is>
       </c>
       <c r="B168" t="n">
-        <v>36176556832</v>
+        <v>30160755219</v>
       </c>
       <c r="C168" t="n">
-        <v>81782457644</v>
+        <v>71588657610</v>
       </c>
       <c r="D168" t="n">
-        <v>0.4423510600461162</v>
+        <v>0.4213063385447102</v>
       </c>
       <c r="E168" t="n">
         <v>167</v>
@@ -3631,17 +3631,17 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>2021-01-14</t>
+          <t>2021-01-20</t>
         </is>
       </c>
       <c r="B169" t="n">
-        <v>32971296424</v>
+        <v>25498108632</v>
       </c>
       <c r="C169" t="n">
-        <v>74034016193</v>
+        <v>61023142374</v>
       </c>
       <c r="D169" t="n">
-        <v>0.4453533405245341</v>
+        <v>0.4178432581483041</v>
       </c>
       <c r="E169" t="n">
         <v>168</v>
@@ -3650,17 +3650,17 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>2021-01-15</t>
+          <t>2021-01-21</t>
         </is>
       </c>
       <c r="B170" t="n">
-        <v>31268748151</v>
+        <v>31550851527</v>
       </c>
       <c r="C170" t="n">
-        <v>68522530970</v>
+        <v>73606094304</v>
       </c>
       <c r="D170" t="n">
-        <v>0.4563279801309417</v>
+        <v>0.4286445548474839</v>
       </c>
       <c r="E170" t="n">
         <v>169</v>
@@ -3669,17 +3669,17 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>2021-01-18</t>
+          <t>2021-01-22</t>
         </is>
       </c>
       <c r="B171" t="n">
-        <v>28025154838</v>
+        <v>29587073243</v>
       </c>
       <c r="C171" t="n">
-        <v>66132336803</v>
+        <v>71863919964</v>
       </c>
       <c r="D171" t="n">
-        <v>0.4237738479056539</v>
+        <v>0.4117097043665521</v>
       </c>
       <c r="E171" t="n">
         <v>170</v>
@@ -3688,17 +3688,17 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>2021-01-19</t>
+          <t>2021-01-25</t>
         </is>
       </c>
       <c r="B172" t="n">
-        <v>30160755219</v>
+        <v>29768085597</v>
       </c>
       <c r="C172" t="n">
-        <v>71588657610</v>
+        <v>72841620023</v>
       </c>
       <c r="D172" t="n">
-        <v>0.4213063385447102</v>
+        <v>0.4086686373477226</v>
       </c>
       <c r="E172" t="n">
         <v>171</v>
@@ -3707,17 +3707,17 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>2021-01-20</t>
+          <t>2021-01-26</t>
         </is>
       </c>
       <c r="B173" t="n">
-        <v>25498108632</v>
+        <v>25588114580</v>
       </c>
       <c r="C173" t="n">
-        <v>61023142374</v>
+        <v>62625061804</v>
       </c>
       <c r="D173" t="n">
-        <v>0.4178432581483041</v>
+        <v>0.4085922447483418</v>
       </c>
       <c r="E173" t="n">
         <v>172</v>
@@ -3726,17 +3726,17 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>2021-01-21</t>
+          <t>2021-01-27</t>
         </is>
       </c>
       <c r="B174" t="n">
-        <v>31550851527</v>
+        <v>25604690493</v>
       </c>
       <c r="C174" t="n">
-        <v>73606094304</v>
+        <v>60015878129</v>
       </c>
       <c r="D174" t="n">
-        <v>0.4286445548474839</v>
+        <v>0.4266319396004584</v>
       </c>
       <c r="E174" t="n">
         <v>173</v>
@@ -3745,17 +3745,17 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>2021-01-22</t>
+          <t>2021-01-28</t>
         </is>
       </c>
       <c r="B175" t="n">
-        <v>29587073243</v>
+        <v>26286085867</v>
       </c>
       <c r="C175" t="n">
-        <v>71863919964</v>
+        <v>62311898539</v>
       </c>
       <c r="D175" t="n">
-        <v>0.4117097043665521</v>
+        <v>0.4218469743872106</v>
       </c>
       <c r="E175" t="n">
         <v>174</v>
@@ -3764,17 +3764,17 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>2021-01-25</t>
+          <t>2021-01-29</t>
         </is>
       </c>
       <c r="B176" t="n">
-        <v>29768085597</v>
+        <v>27002904913</v>
       </c>
       <c r="C176" t="n">
-        <v>72841620023</v>
+        <v>66018503681</v>
       </c>
       <c r="D176" t="n">
-        <v>0.4086686373477226</v>
+        <v>0.4090202504963981</v>
       </c>
       <c r="E176" t="n">
         <v>175</v>
@@ -3783,17 +3783,17 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>2021-01-26</t>
+          <t>2021-02-01</t>
         </is>
       </c>
       <c r="B177" t="n">
-        <v>25588114580</v>
+        <v>25457673045</v>
       </c>
       <c r="C177" t="n">
-        <v>62625061804</v>
+        <v>61214730247</v>
       </c>
       <c r="D177" t="n">
-        <v>0.4085922447483418</v>
+        <v>0.4158749526834291</v>
       </c>
       <c r="E177" t="n">
         <v>176</v>
@@ -3802,17 +3802,17 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>2021-01-27</t>
+          <t>2021-02-02</t>
         </is>
       </c>
       <c r="B178" t="n">
-        <v>25604690493</v>
+        <v>24585679056</v>
       </c>
       <c r="C178" t="n">
-        <v>60015878129</v>
+        <v>59083806830</v>
       </c>
       <c r="D178" t="n">
-        <v>0.4266319396004584</v>
+        <v>0.4161153516519274</v>
       </c>
       <c r="E178" t="n">
         <v>177</v>
@@ -3821,17 +3821,17 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>2021-01-28</t>
+          <t>2021-02-03</t>
         </is>
       </c>
       <c r="B179" t="n">
-        <v>26286085867</v>
+        <v>27946762653</v>
       </c>
       <c r="C179" t="n">
-        <v>62311898539</v>
+        <v>64252239936</v>
       </c>
       <c r="D179" t="n">
-        <v>0.4218469743872106</v>
+        <v>0.4349539048107436</v>
       </c>
       <c r="E179" t="n">
         <v>178</v>
@@ -3840,17 +3840,17 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>2021-01-29</t>
+          <t>2021-02-04</t>
         </is>
       </c>
       <c r="B180" t="n">
-        <v>27002904913</v>
+        <v>26745949814</v>
       </c>
       <c r="C180" t="n">
-        <v>66018503681</v>
+        <v>65026335158</v>
       </c>
       <c r="D180" t="n">
-        <v>0.4090202504963981</v>
+        <v>0.411309506356357</v>
       </c>
       <c r="E180" t="n">
         <v>179</v>
@@ -3859,17 +3859,17 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>2021-02-01</t>
+          <t>2021-02-05</t>
         </is>
       </c>
       <c r="B181" t="n">
-        <v>25457673045</v>
+        <v>27228530445</v>
       </c>
       <c r="C181" t="n">
-        <v>61214730247</v>
+        <v>60817228192</v>
       </c>
       <c r="D181" t="n">
-        <v>0.4158749526834291</v>
+        <v>0.44771080916479</v>
       </c>
       <c r="E181" t="n">
         <v>180</v>
@@ -3878,17 +3878,17 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>2021-02-02</t>
+          <t>2021-02-08</t>
         </is>
       </c>
       <c r="B182" t="n">
-        <v>24585679056</v>
+        <v>22845413099</v>
       </c>
       <c r="C182" t="n">
-        <v>59083806830</v>
+        <v>53099229697</v>
       </c>
       <c r="D182" t="n">
-        <v>0.4161153516519274</v>
+        <v>0.4302400096830542</v>
       </c>
       <c r="E182" t="n">
         <v>181</v>
@@ -3897,17 +3897,17 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>2021-02-03</t>
+          <t>2021-02-09</t>
         </is>
       </c>
       <c r="B183" t="n">
-        <v>27946762653</v>
+        <v>23052987297</v>
       </c>
       <c r="C183" t="n">
-        <v>64252239936</v>
+        <v>54414450658</v>
       </c>
       <c r="D183" t="n">
-        <v>0.4349539048107436</v>
+        <v>0.4236556101960896</v>
       </c>
       <c r="E183" t="n">
         <v>182</v>
@@ -3916,17 +3916,17 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>2021-02-04</t>
+          <t>2021-02-10</t>
         </is>
       </c>
       <c r="B184" t="n">
-        <v>26745949814</v>
+        <v>23672043794</v>
       </c>
       <c r="C184" t="n">
-        <v>65026335158</v>
+        <v>53724833418</v>
       </c>
       <c r="D184" t="n">
-        <v>0.411309506356357</v>
+        <v>0.4406164205260971</v>
       </c>
       <c r="E184" t="n">
         <v>183</v>
@@ -3935,17 +3935,17 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>2021-02-05</t>
+          <t>2021-02-18</t>
         </is>
       </c>
       <c r="B185" t="n">
-        <v>27228530445</v>
+        <v>30305438799</v>
       </c>
       <c r="C185" t="n">
-        <v>60817228192</v>
+        <v>70581483088</v>
       </c>
       <c r="D185" t="n">
-        <v>0.44771080916479</v>
+        <v>0.4293681213982937</v>
       </c>
       <c r="E185" t="n">
         <v>184</v>
@@ -3954,17 +3954,17 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>2021-02-08</t>
+          <t>2021-02-19</t>
         </is>
       </c>
       <c r="B186" t="n">
-        <v>22845413099</v>
+        <v>31871390359</v>
       </c>
       <c r="C186" t="n">
-        <v>53099229697</v>
+        <v>74891926971</v>
       </c>
       <c r="D186" t="n">
-        <v>0.4302400096830542</v>
+        <v>0.4255650995779744</v>
       </c>
       <c r="E186" t="n">
         <v>185</v>
@@ -3973,17 +3973,17 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>2021-02-09</t>
+          <t>2021-02-22</t>
         </is>
       </c>
       <c r="B187" t="n">
-        <v>23052987297</v>
+        <v>41800730539</v>
       </c>
       <c r="C187" t="n">
-        <v>54414450658</v>
+        <v>98345390597</v>
       </c>
       <c r="D187" t="n">
-        <v>0.4236556101960896</v>
+        <v>0.4250400581588124</v>
       </c>
       <c r="E187" t="n">
         <v>186</v>
@@ -3992,17 +3992,17 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>2021-02-10</t>
+          <t>2021-02-23</t>
         </is>
       </c>
       <c r="B188" t="n">
-        <v>23672043794</v>
+        <v>36659765914</v>
       </c>
       <c r="C188" t="n">
-        <v>53724833418</v>
+        <v>79667225639</v>
       </c>
       <c r="D188" t="n">
-        <v>0.4406164205260971</v>
+        <v>0.4601611970287279</v>
       </c>
       <c r="E188" t="n">
         <v>187</v>
@@ -4011,17 +4011,17 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>2021-02-18</t>
+          <t>2021-02-24</t>
         </is>
       </c>
       <c r="B189" t="n">
-        <v>30305438799</v>
+        <v>33328852498</v>
       </c>
       <c r="C189" t="n">
-        <v>70581483088</v>
+        <v>74974298826</v>
       </c>
       <c r="D189" t="n">
-        <v>0.4293681213982937</v>
+        <v>0.4445370349557979</v>
       </c>
       <c r="E189" t="n">
         <v>188</v>
@@ -4030,17 +4030,17 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>2021-02-19</t>
+          <t>2021-02-25</t>
         </is>
       </c>
       <c r="B190" t="n">
-        <v>31871390359</v>
+        <v>33009105938</v>
       </c>
       <c r="C190" t="n">
-        <v>74891926971</v>
+        <v>72321851390</v>
       </c>
       <c r="D190" t="n">
-        <v>0.4255650995779744</v>
+        <v>0.4564195371603028</v>
       </c>
       <c r="E190" t="n">
         <v>189</v>
@@ -4049,17 +4049,17 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>2021-02-22</t>
+          <t>2021-02-26</t>
         </is>
       </c>
       <c r="B191" t="n">
-        <v>41800730539</v>
+        <v>29437488128</v>
       </c>
       <c r="C191" t="n">
-        <v>98345390597</v>
+        <v>67566280430</v>
       </c>
       <c r="D191" t="n">
-        <v>0.4250400581588124</v>
+        <v>0.4356831238993216</v>
       </c>
       <c r="E191" t="n">
         <v>190</v>
@@ -4068,17 +4068,17 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>2021-02-23</t>
+          <t>2021-03-01</t>
         </is>
       </c>
       <c r="B192" t="n">
-        <v>36659765914</v>
+        <v>28022529242</v>
       </c>
       <c r="C192" t="n">
-        <v>79667225639</v>
+        <v>65847760652</v>
       </c>
       <c r="D192" t="n">
-        <v>0.4601611970287279</v>
+        <v>0.425565409734991</v>
       </c>
       <c r="E192" t="n">
         <v>191</v>
@@ -4087,17 +4087,17 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>2021-02-24</t>
+          <t>2021-03-02</t>
         </is>
       </c>
       <c r="B193" t="n">
-        <v>33328852498</v>
+        <v>30548474585</v>
       </c>
       <c r="C193" t="n">
-        <v>74974298826</v>
+        <v>69441386639</v>
       </c>
       <c r="D193" t="n">
-        <v>0.4445370349557979</v>
+        <v>0.4399174046424243</v>
       </c>
       <c r="E193" t="n">
         <v>192</v>
@@ -4106,17 +4106,17 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>2021-02-25</t>
+          <t>2021-03-03</t>
         </is>
       </c>
       <c r="B194" t="n">
-        <v>33009105938</v>
+        <v>31581683271</v>
       </c>
       <c r="C194" t="n">
-        <v>72321851390</v>
+        <v>69999474895</v>
       </c>
       <c r="D194" t="n">
-        <v>0.4564195371603028</v>
+        <v>0.4511702883253464</v>
       </c>
       <c r="E194" t="n">
         <v>193</v>
@@ -4125,17 +4125,17 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>2021-02-26</t>
+          <t>2021-03-04</t>
         </is>
       </c>
       <c r="B195" t="n">
-        <v>29437488128</v>
+        <v>36100282673</v>
       </c>
       <c r="C195" t="n">
-        <v>67566280430</v>
+        <v>78562142790</v>
       </c>
       <c r="D195" t="n">
-        <v>0.4356831238993216</v>
+        <v>0.4595124495203449</v>
       </c>
       <c r="E195" t="n">
         <v>194</v>
@@ -4144,17 +4144,17 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>2021-03-01</t>
+          <t>2021-03-05</t>
         </is>
       </c>
       <c r="B196" t="n">
-        <v>28022529242</v>
+        <v>32337135967</v>
       </c>
       <c r="C196" t="n">
-        <v>65847760652</v>
+        <v>73514786011</v>
       </c>
       <c r="D196" t="n">
-        <v>0.425565409734991</v>
+        <v>0.4398725443091326</v>
       </c>
       <c r="E196" t="n">
         <v>195</v>
@@ -4163,17 +4163,17 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>2021-03-02</t>
+          <t>2021-03-08</t>
         </is>
       </c>
       <c r="B197" t="n">
-        <v>30548474585</v>
+        <v>34237890063</v>
       </c>
       <c r="C197" t="n">
-        <v>69441386639</v>
+        <v>78814375242</v>
       </c>
       <c r="D197" t="n">
-        <v>0.4399174046424243</v>
+        <v>0.4344117422471771</v>
       </c>
       <c r="E197" t="n">
         <v>196</v>
@@ -4182,17 +4182,17 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>2021-03-03</t>
+          <t>2021-03-09</t>
         </is>
       </c>
       <c r="B198" t="n">
-        <v>31581683271</v>
+        <v>35838361211</v>
       </c>
       <c r="C198" t="n">
-        <v>69999474895</v>
+        <v>82850202998</v>
       </c>
       <c r="D198" t="n">
-        <v>0.4511702883253464</v>
+        <v>0.4325681762284292</v>
       </c>
       <c r="E198" t="n">
         <v>197</v>
@@ -4201,17 +4201,17 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>2021-03-04</t>
+          <t>2021-03-10</t>
         </is>
       </c>
       <c r="B199" t="n">
-        <v>36100282673</v>
+        <v>26975456721</v>
       </c>
       <c r="C199" t="n">
-        <v>78562142790</v>
+        <v>62127335207</v>
       </c>
       <c r="D199" t="n">
-        <v>0.4595124495203449</v>
+        <v>0.4341962620981791</v>
       </c>
       <c r="E199" t="n">
         <v>198</v>
@@ -4220,17 +4220,17 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>2021-03-05</t>
+          <t>2021-03-11</t>
         </is>
       </c>
       <c r="B200" t="n">
-        <v>32337135967</v>
+        <v>30680047969</v>
       </c>
       <c r="C200" t="n">
-        <v>73514786011</v>
+        <v>66598157167</v>
       </c>
       <c r="D200" t="n">
-        <v>0.4398725443091326</v>
+        <v>0.4606741278451207</v>
       </c>
       <c r="E200" t="n">
         <v>199</v>
@@ -4239,17 +4239,17 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>2021-03-08</t>
+          <t>2021-03-12</t>
         </is>
       </c>
       <c r="B201" t="n">
-        <v>34237890063</v>
+        <v>33862968625</v>
       </c>
       <c r="C201" t="n">
-        <v>78814375242</v>
+        <v>72238010975</v>
       </c>
       <c r="D201" t="n">
-        <v>0.4344117422471771</v>
+        <v>0.4687693939513262</v>
       </c>
       <c r="E201" t="n">
         <v>200</v>
@@ -4258,17 +4258,17 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>2021-03-09</t>
+          <t>2021-03-15</t>
         </is>
       </c>
       <c r="B202" t="n">
-        <v>35838361211</v>
+        <v>34591765793</v>
       </c>
       <c r="C202" t="n">
-        <v>82850202998</v>
+        <v>71723136959</v>
       </c>
       <c r="D202" t="n">
-        <v>0.4325681762284292</v>
+        <v>0.4822957731585852</v>
       </c>
       <c r="E202" t="n">
         <v>201</v>
@@ -4277,17 +4277,17 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>2021-03-10</t>
+          <t>2021-03-16</t>
         </is>
       </c>
       <c r="B203" t="n">
-        <v>26975456721</v>
+        <v>29977825317</v>
       </c>
       <c r="C203" t="n">
-        <v>62127335207</v>
+        <v>67049266583</v>
       </c>
       <c r="D203" t="n">
-        <v>0.4341962620981791</v>
+        <v>0.447101465008429</v>
       </c>
       <c r="E203" t="n">
         <v>202</v>
@@ -4296,17 +4296,17 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>2021-03-11</t>
+          <t>2021-03-17</t>
         </is>
       </c>
       <c r="B204" t="n">
-        <v>30680047969</v>
+        <v>27491185060</v>
       </c>
       <c r="C204" t="n">
-        <v>66598157167</v>
+        <v>62515062852</v>
       </c>
       <c r="D204" t="n">
-        <v>0.4606741278451207</v>
+        <v>0.4397529780156095</v>
       </c>
       <c r="E204" t="n">
         <v>203</v>
@@ -4315,17 +4315,17 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>2021-03-12</t>
+          <t>2021-03-18</t>
         </is>
       </c>
       <c r="B205" t="n">
-        <v>33862968625</v>
+        <v>26739276351</v>
       </c>
       <c r="C205" t="n">
-        <v>72238010975</v>
+        <v>62832911819</v>
       </c>
       <c r="D205" t="n">
-        <v>0.4687693939513262</v>
+        <v>0.4255616296762858</v>
       </c>
       <c r="E205" t="n">
         <v>204</v>
@@ -4334,17 +4334,17 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>2021-03-15</t>
+          <t>2021-03-19</t>
         </is>
       </c>
       <c r="B206" t="n">
-        <v>34591765793</v>
+        <v>28358235249</v>
       </c>
       <c r="C206" t="n">
-        <v>71723136959</v>
+        <v>65875538395</v>
       </c>
       <c r="D206" t="n">
-        <v>0.4822957731585852</v>
+        <v>0.4304820262562349</v>
       </c>
       <c r="E206" t="n">
         <v>205</v>
@@ -4353,17 +4353,17 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>2021-03-16</t>
+          <t>2021-03-22</t>
         </is>
       </c>
       <c r="B207" t="n">
-        <v>29977825317</v>
+        <v>29121013208</v>
       </c>
       <c r="C207" t="n">
-        <v>67049266583</v>
+        <v>67358226346</v>
       </c>
       <c r="D207" t="n">
-        <v>0.447101465008429</v>
+        <v>0.4323304633707791</v>
       </c>
       <c r="E207" t="n">
         <v>206</v>
@@ -4372,17 +4372,17 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>2021-03-17</t>
+          <t>2021-03-23</t>
         </is>
       </c>
       <c r="B208" t="n">
-        <v>27491185060</v>
+        <v>29320271653</v>
       </c>
       <c r="C208" t="n">
-        <v>62515062852</v>
+        <v>70323191299</v>
       </c>
       <c r="D208" t="n">
-        <v>0.4397529780156095</v>
+        <v>0.4169360222623591</v>
       </c>
       <c r="E208" t="n">
         <v>207</v>
@@ -4391,17 +4391,17 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>2021-03-18</t>
+          <t>2021-03-24</t>
         </is>
       </c>
       <c r="B209" t="n">
-        <v>26739276351</v>
+        <v>28494202046</v>
       </c>
       <c r="C209" t="n">
-        <v>62832911819</v>
+        <v>67303523996</v>
       </c>
       <c r="D209" t="n">
-        <v>0.4255616296762858</v>
+        <v>0.423368649280437</v>
       </c>
       <c r="E209" t="n">
         <v>208</v>
@@ -4410,17 +4410,17 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>2021-03-19</t>
+          <t>2021-03-25</t>
         </is>
       </c>
       <c r="B210" t="n">
-        <v>28358235249</v>
+        <v>25857769578</v>
       </c>
       <c r="C210" t="n">
-        <v>65875538395</v>
+        <v>60650502617</v>
       </c>
       <c r="D210" t="n">
-        <v>0.4304820262562349</v>
+        <v>0.426340565407816</v>
       </c>
       <c r="E210" t="n">
         <v>209</v>
@@ -4429,17 +4429,17 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>2021-03-22</t>
+          <t>2021-03-26</t>
         </is>
       </c>
       <c r="B211" t="n">
-        <v>29121013208</v>
+        <v>25857588064</v>
       </c>
       <c r="C211" t="n">
-        <v>67358226346</v>
+        <v>61284664475</v>
       </c>
       <c r="D211" t="n">
-        <v>0.4323304633707791</v>
+        <v>0.4219259138564452</v>
       </c>
       <c r="E211" t="n">
         <v>210</v>
@@ -4448,17 +4448,17 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>2021-03-23</t>
+          <t>2021-03-29</t>
         </is>
       </c>
       <c r="B212" t="n">
-        <v>29320271653</v>
+        <v>26030305012</v>
       </c>
       <c r="C212" t="n">
-        <v>70323191299</v>
+        <v>62965892538</v>
       </c>
       <c r="D212" t="n">
-        <v>0.4169360222623591</v>
+        <v>0.4134032563151658</v>
       </c>
       <c r="E212" t="n">
         <v>211</v>
@@ -4467,17 +4467,17 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>2021-03-24</t>
+          <t>2021-03-30</t>
         </is>
       </c>
       <c r="B213" t="n">
-        <v>28494202046</v>
+        <v>25780001010</v>
       </c>
       <c r="C213" t="n">
-        <v>67303523996</v>
+        <v>62868502600</v>
       </c>
       <c r="D213" t="n">
-        <v>0.423368649280437</v>
+        <v>0.4100622719460158</v>
       </c>
       <c r="E213" t="n">
         <v>212</v>
@@ -4486,17 +4486,17 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>2021-03-25</t>
+          <t>2021-03-31</t>
         </is>
       </c>
       <c r="B214" t="n">
-        <v>25857769578</v>
+        <v>25340940136</v>
       </c>
       <c r="C214" t="n">
-        <v>60650502617</v>
+        <v>58944651908</v>
       </c>
       <c r="D214" t="n">
-        <v>0.426340565407816</v>
+        <v>0.4299107606157687</v>
       </c>
       <c r="E214" t="n">
         <v>213</v>
@@ -4505,17 +4505,17 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>2021-03-26</t>
+          <t>2021-04-01</t>
         </is>
       </c>
       <c r="B215" t="n">
-        <v>25857588064</v>
+        <v>24459982838</v>
       </c>
       <c r="C215" t="n">
-        <v>61284664475</v>
+        <v>57742915146</v>
       </c>
       <c r="D215" t="n">
-        <v>0.4219259138564452</v>
+        <v>0.4236014544148696</v>
       </c>
       <c r="E215" t="n">
         <v>214</v>
@@ -4524,17 +4524,17 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>2021-03-29</t>
+          <t>2021-04-02</t>
         </is>
       </c>
       <c r="B216" t="n">
-        <v>26030305012</v>
+        <v>23776468616</v>
       </c>
       <c r="C216" t="n">
-        <v>62965892538</v>
+        <v>57637646459</v>
       </c>
       <c r="D216" t="n">
-        <v>0.4134032563151658</v>
+        <v>0.4125162992717471</v>
       </c>
       <c r="E216" t="n">
         <v>215</v>
@@ -4543,17 +4543,17 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>2021-03-30</t>
+          <t>2021-04-06</t>
         </is>
       </c>
       <c r="B217" t="n">
-        <v>25780001010</v>
+        <v>21609152872</v>
       </c>
       <c r="C217" t="n">
-        <v>62868502600</v>
+        <v>54009467026</v>
       </c>
       <c r="D217" t="n">
-        <v>0.4100622719460158</v>
+        <v>0.4000993540928189</v>
       </c>
       <c r="E217" t="n">
         <v>216</v>
@@ -4562,17 +4562,17 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>2021-03-31</t>
+          <t>2021-04-07</t>
         </is>
       </c>
       <c r="B218" t="n">
-        <v>25340940136</v>
+        <v>28192988226</v>
       </c>
       <c r="C218" t="n">
-        <v>58944651908</v>
+        <v>64777711487</v>
       </c>
       <c r="D218" t="n">
-        <v>0.4299107606157687</v>
+        <v>0.4352266787266473</v>
       </c>
       <c r="E218" t="n">
         <v>217</v>
@@ -4581,17 +4581,17 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>2021-04-01</t>
+          <t>2021-04-08</t>
         </is>
       </c>
       <c r="B219" t="n">
-        <v>24459982838</v>
+        <v>31610774016</v>
       </c>
       <c r="C219" t="n">
-        <v>57742915146</v>
+        <v>70183037971</v>
       </c>
       <c r="D219" t="n">
-        <v>0.4236014544148696</v>
+        <v>0.4504047549076137</v>
       </c>
       <c r="E219" t="n">
         <v>218</v>
@@ -4600,17 +4600,17 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>2021-04-02</t>
+          <t>2021-04-09</t>
         </is>
       </c>
       <c r="B220" t="n">
-        <v>23776468616</v>
+        <v>27363203695</v>
       </c>
       <c r="C220" t="n">
-        <v>57637646459</v>
+        <v>60908586933</v>
       </c>
       <c r="D220" t="n">
-        <v>0.4125162992717471</v>
+        <v>0.4492503450309851</v>
       </c>
       <c r="E220" t="n">
         <v>219</v>
@@ -4619,17 +4619,17 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>2021-04-06</t>
+          <t>2021-04-12</t>
         </is>
       </c>
       <c r="B221" t="n">
-        <v>21609152872</v>
+        <v>29441281600</v>
       </c>
       <c r="C221" t="n">
-        <v>54009467026</v>
+        <v>66662877908</v>
       </c>
       <c r="D221" t="n">
-        <v>0.4000993540928189</v>
+        <v>0.4416443232563598</v>
       </c>
       <c r="E221" t="n">
         <v>220</v>
@@ -4638,17 +4638,17 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>2021-04-07</t>
+          <t>2021-04-13</t>
         </is>
       </c>
       <c r="B222" t="n">
-        <v>28192988226</v>
+        <v>26500289609</v>
       </c>
       <c r="C222" t="n">
-        <v>64777711487</v>
+        <v>60099497250</v>
       </c>
       <c r="D222" t="n">
-        <v>0.4352266787266473</v>
+        <v>0.4409402877159675</v>
       </c>
       <c r="E222" t="n">
         <v>221</v>
@@ -4657,17 +4657,17 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>2021-04-08</t>
+          <t>2021-04-14</t>
         </is>
       </c>
       <c r="B223" t="n">
-        <v>31610774016</v>
+        <v>24875678254</v>
       </c>
       <c r="C223" t="n">
-        <v>70183037971</v>
+        <v>56149660115</v>
       </c>
       <c r="D223" t="n">
-        <v>0.4504047549076137</v>
+        <v>0.4430245562137362</v>
       </c>
       <c r="E223" t="n">
         <v>222</v>
@@ -4676,17 +4676,17 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>2021-04-09</t>
+          <t>2021-04-15</t>
         </is>
       </c>
       <c r="B224" t="n">
-        <v>27363203695</v>
+        <v>23587218127</v>
       </c>
       <c r="C224" t="n">
-        <v>60908586933</v>
+        <v>56730832399</v>
       </c>
       <c r="D224" t="n">
-        <v>0.4492503450309851</v>
+        <v>0.4157742294543835</v>
       </c>
       <c r="E224" t="n">
         <v>223</v>
@@ -4695,17 +4695,17 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>2021-04-12</t>
+          <t>2021-04-16</t>
         </is>
       </c>
       <c r="B225" t="n">
-        <v>29441281600</v>
+        <v>23064238930</v>
       </c>
       <c r="C225" t="n">
-        <v>66662877908</v>
+        <v>60757105467</v>
       </c>
       <c r="D225" t="n">
-        <v>0.4416443232563598</v>
+        <v>0.3796138534368998</v>
       </c>
       <c r="E225" t="n">
         <v>224</v>
@@ -4714,17 +4714,17 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>2021-04-13</t>
+          <t>2021-04-19</t>
         </is>
       </c>
       <c r="B226" t="n">
-        <v>26500289609</v>
+        <v>26349229565</v>
       </c>
       <c r="C226" t="n">
-        <v>60099497250</v>
+        <v>68717257011</v>
       </c>
       <c r="D226" t="n">
-        <v>0.4409402877159675</v>
+        <v>0.3834441406877186</v>
       </c>
       <c r="E226" t="n">
         <v>225</v>
@@ -4733,17 +4733,17 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>2021-04-14</t>
+          <t>2021-04-20</t>
         </is>
       </c>
       <c r="B227" t="n">
-        <v>24875678254</v>
+        <v>26332452757</v>
       </c>
       <c r="C227" t="n">
-        <v>56149660115</v>
+        <v>66152179163</v>
       </c>
       <c r="D227" t="n">
-        <v>0.4430245562137362</v>
+        <v>0.3980587350284626</v>
       </c>
       <c r="E227" t="n">
         <v>226</v>
@@ -4752,17 +4752,17 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>2021-04-15</t>
+          <t>2021-04-21</t>
         </is>
       </c>
       <c r="B228" t="n">
-        <v>23587218127</v>
+        <v>23796108657</v>
       </c>
       <c r="C228" t="n">
-        <v>56730832399</v>
+        <v>58645267418</v>
       </c>
       <c r="D228" t="n">
-        <v>0.4157742294543835</v>
+        <v>0.4057634947316526</v>
       </c>
       <c r="E228" t="n">
         <v>227</v>
@@ -4771,17 +4771,17 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>2021-04-16</t>
+          <t>2021-04-22</t>
         </is>
       </c>
       <c r="B229" t="n">
-        <v>23064238930</v>
+        <v>23283868400</v>
       </c>
       <c r="C229" t="n">
-        <v>60757105467</v>
+        <v>57343158813</v>
       </c>
       <c r="D229" t="n">
-        <v>0.3796138534368998</v>
+        <v>0.406044398006226</v>
       </c>
       <c r="E229" t="n">
         <v>228</v>
@@ -4790,17 +4790,17 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>2021-04-19</t>
+          <t>2021-04-23</t>
         </is>
       </c>
       <c r="B230" t="n">
-        <v>26349229565</v>
+        <v>23110619160</v>
       </c>
       <c r="C230" t="n">
-        <v>68717257011</v>
+        <v>58758936747</v>
       </c>
       <c r="D230" t="n">
-        <v>0.3834441406877186</v>
+        <v>0.3933124123655954</v>
       </c>
       <c r="E230" t="n">
         <v>229</v>
@@ -4809,17 +4809,17 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>2021-04-20</t>
+          <t>2021-04-26</t>
         </is>
       </c>
       <c r="B231" t="n">
-        <v>26332452757</v>
+        <v>26080656908</v>
       </c>
       <c r="C231" t="n">
-        <v>66152179163</v>
+        <v>64990659217</v>
       </c>
       <c r="D231" t="n">
-        <v>0.3980587350284626</v>
+        <v>0.4012985438556365</v>
       </c>
       <c r="E231" t="n">
         <v>230</v>
@@ -4828,17 +4828,17 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>2021-04-21</t>
+          <t>2021-04-27</t>
         </is>
       </c>
       <c r="B232" t="n">
-        <v>23796108657</v>
+        <v>22805398723</v>
       </c>
       <c r="C232" t="n">
-        <v>58645267418</v>
+        <v>58465572266</v>
       </c>
       <c r="D232" t="n">
-        <v>0.4057634947316526</v>
+        <v>0.3900654323409783</v>
       </c>
       <c r="E232" t="n">
         <v>231</v>
@@ -4847,17 +4847,17 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>2021-04-22</t>
+          <t>2021-04-28</t>
         </is>
       </c>
       <c r="B233" t="n">
-        <v>23283868400</v>
+        <v>21764975470</v>
       </c>
       <c r="C233" t="n">
-        <v>57343158813</v>
+        <v>56258757783</v>
       </c>
       <c r="D233" t="n">
-        <v>0.406044398006226</v>
+        <v>0.3868726635229197</v>
       </c>
       <c r="E233" t="n">
         <v>232</v>
@@ -4866,17 +4866,17 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>2021-04-23</t>
+          <t>2021-04-29</t>
         </is>
       </c>
       <c r="B234" t="n">
-        <v>23110619160</v>
+        <v>23871290845</v>
       </c>
       <c r="C234" t="n">
-        <v>58758936747</v>
+        <v>59672070298</v>
       </c>
       <c r="D234" t="n">
-        <v>0.3933124123655954</v>
+        <v>0.400041270996426</v>
       </c>
       <c r="E234" t="n">
         <v>233</v>
@@ -4885,17 +4885,17 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>2021-04-26</t>
+          <t>2021-04-30</t>
         </is>
       </c>
       <c r="B235" t="n">
-        <v>26080656908</v>
+        <v>26727927563</v>
       </c>
       <c r="C235" t="n">
-        <v>64990659217</v>
+        <v>64623812735</v>
       </c>
       <c r="D235" t="n">
-        <v>0.4012985438556365</v>
+        <v>0.413592550978105</v>
       </c>
       <c r="E235" t="n">
         <v>234</v>
@@ -4904,17 +4904,17 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>2021-04-27</t>
+          <t>2021-05-06</t>
         </is>
       </c>
       <c r="B236" t="n">
-        <v>22805398723</v>
+        <v>28245158344</v>
       </c>
       <c r="C236" t="n">
-        <v>58465572266</v>
+        <v>64995398044</v>
       </c>
       <c r="D236" t="n">
-        <v>0.3900654323409783</v>
+        <v>0.4345716649797089</v>
       </c>
       <c r="E236" t="n">
         <v>235</v>
@@ -4923,17 +4923,17 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>2021-04-28</t>
+          <t>2021-05-07</t>
         </is>
       </c>
       <c r="B237" t="n">
-        <v>21764975470</v>
+        <v>33809492530</v>
       </c>
       <c r="C237" t="n">
-        <v>56258757783</v>
+        <v>72689004129</v>
       </c>
       <c r="D237" t="n">
-        <v>0.3868726635229197</v>
+        <v>0.4651252680529072</v>
       </c>
       <c r="E237" t="n">
         <v>236</v>
@@ -4942,17 +4942,17 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>2021-04-29</t>
+          <t>2021-05-10</t>
         </is>
       </c>
       <c r="B238" t="n">
-        <v>23871290845</v>
+        <v>34980447442</v>
       </c>
       <c r="C238" t="n">
-        <v>59672070298</v>
+        <v>74391256531</v>
       </c>
       <c r="D238" t="n">
-        <v>0.400041270996426</v>
+        <v>0.4702225647636843</v>
       </c>
       <c r="E238" t="n">
         <v>237</v>
@@ -4961,17 +4961,17 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>2021-04-30</t>
+          <t>2021-05-11</t>
         </is>
       </c>
       <c r="B239" t="n">
-        <v>26727927563</v>
+        <v>33682768573</v>
       </c>
       <c r="C239" t="n">
-        <v>64623812735</v>
+        <v>73459473614</v>
       </c>
       <c r="D239" t="n">
-        <v>0.413592550978105</v>
+        <v>0.4585217796412401</v>
       </c>
       <c r="E239" t="n">
         <v>238</v>
@@ -4980,17 +4980,17 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>2021-05-06</t>
+          <t>2021-05-12</t>
         </is>
       </c>
       <c r="B240" t="n">
-        <v>28245158344</v>
+        <v>28011409229</v>
       </c>
       <c r="C240" t="n">
-        <v>64995398044</v>
+        <v>66061705250</v>
       </c>
       <c r="D240" t="n">
-        <v>0.4345716649797089</v>
+        <v>0.4240188642269418</v>
       </c>
       <c r="E240" t="n">
         <v>239</v>
@@ -4999,17 +4999,17 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>2021-05-07</t>
+          <t>2021-05-13</t>
         </is>
       </c>
       <c r="B241" t="n">
-        <v>33809492530</v>
+        <v>29021959092</v>
       </c>
       <c r="C241" t="n">
-        <v>72689004129</v>
+        <v>69247970457</v>
       </c>
       <c r="D241" t="n">
-        <v>0.4651252680529072</v>
+        <v>0.4191019448002651</v>
       </c>
       <c r="E241" t="n">
         <v>240</v>
@@ -5018,17 +5018,17 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>2021-05-10</t>
+          <t>2021-05-14</t>
         </is>
       </c>
       <c r="B242" t="n">
-        <v>34980447442</v>
+        <v>29087549466</v>
       </c>
       <c r="C242" t="n">
-        <v>74391256531</v>
+        <v>72865719627</v>
       </c>
       <c r="D242" t="n">
-        <v>0.4702225647636843</v>
+        <v>0.3991938817718307</v>
       </c>
       <c r="E242" t="n">
         <v>241</v>
@@ -5037,17 +5037,17 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>2021-05-11</t>
+          <t>2021-05-17</t>
         </is>
       </c>
       <c r="B243" t="n">
-        <v>33682768573</v>
+        <v>26738086558</v>
       </c>
       <c r="C243" t="n">
-        <v>73459473614</v>
+        <v>68865623007</v>
       </c>
       <c r="D243" t="n">
-        <v>0.4585217796412401</v>
+        <v>0.3882646433806625</v>
       </c>
       <c r="E243" t="n">
         <v>242</v>
@@ -5056,17 +5056,17 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>2021-05-12</t>
+          <t>2021-05-18</t>
         </is>
       </c>
       <c r="B244" t="n">
-        <v>28011409229</v>
+        <v>23944078372</v>
       </c>
       <c r="C244" t="n">
-        <v>66061705250</v>
+        <v>58781317109</v>
       </c>
       <c r="D244" t="n">
-        <v>0.4240188642269418</v>
+        <v>0.4073416444139855</v>
       </c>
       <c r="E244" t="n">
         <v>243</v>
@@ -5075,77 +5075,20 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>2021-05-13</t>
+          <t>2021-05-19</t>
         </is>
       </c>
       <c r="B245" t="n">
-        <v>29021959092</v>
+        <v>25053218592</v>
       </c>
       <c r="C245" t="n">
-        <v>69247970457</v>
+        <v>60763325645</v>
       </c>
       <c r="D245" t="n">
-        <v>0.4191019448002651</v>
+        <v>0.4123082192434532</v>
       </c>
       <c r="E245" t="n">
         <v>244</v>
-      </c>
-    </row>
-    <row r="246">
-      <c r="A246" t="inlineStr">
-        <is>
-          <t>2021-05-14</t>
-        </is>
-      </c>
-      <c r="B246" t="n">
-        <v>29087549466</v>
-      </c>
-      <c r="C246" t="n">
-        <v>72865719627</v>
-      </c>
-      <c r="D246" t="n">
-        <v>0.3991938817718307</v>
-      </c>
-      <c r="E246" t="n">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="247">
-      <c r="A247" t="inlineStr">
-        <is>
-          <t>2021-05-17</t>
-        </is>
-      </c>
-      <c r="B247" t="n">
-        <v>26738086558</v>
-      </c>
-      <c r="C247" t="n">
-        <v>68865623007</v>
-      </c>
-      <c r="D247" t="n">
-        <v>0.3882646433806625</v>
-      </c>
-      <c r="E247" t="n">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="248">
-      <c r="A248" t="inlineStr">
-        <is>
-          <t>2021-05-18</t>
-        </is>
-      </c>
-      <c r="B248" t="n">
-        <v>23944078372</v>
-      </c>
-      <c r="C248" t="n">
-        <v>58781317109</v>
-      </c>
-      <c r="D248" t="n">
-        <v>0.4073416444139855</v>
-      </c>
-      <c r="E248" t="n">
-        <v>247</v>
       </c>
     </row>
   </sheetData>

--- a/king_index/output/index.xlsx
+++ b/king_index/output/index.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E245"/>
+  <dimension ref="A1:E246"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5091,6 +5091,25 @@
         <v>244</v>
       </c>
     </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>2021-05-20</t>
+        </is>
+      </c>
+      <c r="B246" t="n">
+        <v>28722723747</v>
+      </c>
+      <c r="C246" t="n">
+        <v>68566840023</v>
+      </c>
+      <c r="D246" t="n">
+        <v>0.4189010859675796</v>
+      </c>
+      <c r="E246" t="n">
+        <v>245</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/king_index/output/index.xlsx
+++ b/king_index/output/index.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E246"/>
+  <dimension ref="A1:E247"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5110,6 +5110,25 @@
         <v>245</v>
       </c>
     </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>2021-05-21</t>
+        </is>
+      </c>
+      <c r="B247" t="n">
+        <v>25545536529</v>
+      </c>
+      <c r="C247" t="n">
+        <v>61418379955</v>
+      </c>
+      <c r="D247" t="n">
+        <v>0.4159265768279251</v>
+      </c>
+      <c r="E247" t="n">
+        <v>246</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/king_index/output/index.xlsx
+++ b/king_index/output/index.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E247"/>
+  <dimension ref="A1:E248"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5129,6 +5129,25 @@
         <v>246</v>
       </c>
     </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>2021-05-24</t>
+        </is>
+      </c>
+      <c r="B248" t="n">
+        <v>25923087661</v>
+      </c>
+      <c r="C248" t="n">
+        <v>63386616118</v>
+      </c>
+      <c r="D248" t="n">
+        <v>0.4089678428761964</v>
+      </c>
+      <c r="E248" t="n">
+        <v>247</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/king_index/output/index.xlsx
+++ b/king_index/output/index.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E248"/>
+  <dimension ref="A1:E249"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5148,6 +5148,25 @@
         <v>247</v>
       </c>
     </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>2021-05-25</t>
+        </is>
+      </c>
+      <c r="B249" t="n">
+        <v>29902389375</v>
+      </c>
+      <c r="C249" t="n">
+        <v>71817033145</v>
+      </c>
+      <c r="D249" t="n">
+        <v>0.4163690431854305</v>
+      </c>
+      <c r="E249" t="n">
+        <v>248</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/king_index/output/index.xlsx
+++ b/king_index/output/index.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E249"/>
+  <dimension ref="A1:E250"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5167,6 +5167,25 @@
         <v>248</v>
       </c>
     </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>2021-05-26</t>
+        </is>
+      </c>
+      <c r="B250" t="n">
+        <v>29496722494</v>
+      </c>
+      <c r="C250" t="n">
+        <v>72933630614</v>
+      </c>
+      <c r="D250" t="n">
+        <v>0.4044323893611015</v>
+      </c>
+      <c r="E250" t="n">
+        <v>249</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/king_index/output/index.xlsx
+++ b/king_index/output/index.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E250"/>
+  <dimension ref="A1:E251"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5186,6 +5186,25 @@
         <v>249</v>
       </c>
     </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>2021-05-27</t>
+        </is>
+      </c>
+      <c r="B251" t="n">
+        <v>26896810605</v>
+      </c>
+      <c r="C251" t="n">
+        <v>68968444971</v>
+      </c>
+      <c r="D251" t="n">
+        <v>0.3899871980049663</v>
+      </c>
+      <c r="E251" t="n">
+        <v>250</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/king_index/output/index.xlsx
+++ b/king_index/output/index.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E251"/>
+  <dimension ref="A1:E253"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5205,6 +5205,44 @@
         <v>250</v>
       </c>
     </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>2021-05-27</t>
+        </is>
+      </c>
+      <c r="B252" t="n">
+        <v>26896810605</v>
+      </c>
+      <c r="C252" t="n">
+        <v>68968444971</v>
+      </c>
+      <c r="D252" t="n">
+        <v>0.3899871980049663</v>
+      </c>
+      <c r="E252" t="n">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>2021-05-28</t>
+        </is>
+      </c>
+      <c r="B253" t="n">
+        <v>29791926043</v>
+      </c>
+      <c r="C253" t="n">
+        <v>73972884560</v>
+      </c>
+      <c r="D253" t="n">
+        <v>0.4027411695543051</v>
+      </c>
+      <c r="E253" t="n">
+        <v>252</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/king_index/output/index.xlsx
+++ b/king_index/output/index.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E253"/>
+  <dimension ref="A1:E254"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5243,6 +5243,25 @@
         <v>252</v>
       </c>
     </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>2021-05-31</t>
+        </is>
+      </c>
+      <c r="B254" t="n">
+        <v>27775314244</v>
+      </c>
+      <c r="C254" t="n">
+        <v>70615016083</v>
+      </c>
+      <c r="D254" t="n">
+        <v>0.3933343895490053</v>
+      </c>
+      <c r="E254" t="n">
+        <v>253</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/king_index/output/index.xlsx
+++ b/king_index/output/index.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E254"/>
+  <dimension ref="A1:E255"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5262,6 +5262,25 @@
         <v>253</v>
       </c>
     </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>2021-06-01</t>
+        </is>
+      </c>
+      <c r="B255" t="n">
+        <v>28722955321</v>
+      </c>
+      <c r="C255" t="n">
+        <v>75176823860</v>
+      </c>
+      <c r="D255" t="n">
+        <v>0.3820719451315218</v>
+      </c>
+      <c r="E255" t="n">
+        <v>254</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/king_index/output/index.xlsx
+++ b/king_index/output/index.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E255"/>
+  <dimension ref="A1:E249"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -458,17 +458,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2020-05-19</t>
+          <t>2020-05-28</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>18863773358</v>
+        <v>18416635989</v>
       </c>
       <c r="C2" t="n">
-        <v>50302048430</v>
+        <v>50047777669</v>
       </c>
       <c r="D2" t="n">
-        <v>0.3750100432639578</v>
+        <v>0.3679810942016595</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>
@@ -477,17 +477,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2020-05-20</t>
+          <t>2020-05-29</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>21259230267</v>
+        <v>18782496399</v>
       </c>
       <c r="C3" t="n">
-        <v>55292303555</v>
+        <v>49396386216</v>
       </c>
       <c r="D3" t="n">
-        <v>0.3844880553014609</v>
+        <v>0.3802402936293375</v>
       </c>
       <c r="E3" t="n">
         <v>2</v>
@@ -496,17 +496,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2020-05-21</t>
+          <t>2020-06-01</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>19280128498</v>
+        <v>22806246928</v>
       </c>
       <c r="C4" t="n">
-        <v>52065201803</v>
+        <v>64259168243</v>
       </c>
       <c r="D4" t="n">
-        <v>0.370307380560063</v>
+        <v>0.3549103972487906</v>
       </c>
       <c r="E4" t="n">
         <v>3</v>
@@ -515,17 +515,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2020-05-22</t>
+          <t>2020-06-02</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>17897770797</v>
+        <v>26690797837</v>
       </c>
       <c r="C5" t="n">
-        <v>50417741953</v>
+        <v>67019269521</v>
       </c>
       <c r="D5" t="n">
-        <v>0.3549895355028892</v>
+        <v>0.3982555767582133</v>
       </c>
       <c r="E5" t="n">
         <v>4</v>
@@ -534,17 +534,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2020-05-25</t>
+          <t>2020-06-03</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>14723899014</v>
+        <v>25988325662</v>
       </c>
       <c r="C6" t="n">
-        <v>41053704521</v>
+        <v>66814592975</v>
       </c>
       <c r="D6" t="n">
-        <v>0.3586497049606901</v>
+        <v>0.3889618196390726</v>
       </c>
       <c r="E6" t="n">
         <v>5</v>
@@ -553,17 +553,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2020-05-26</t>
+          <t>2020-06-04</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>15738642741</v>
+        <v>22648232850</v>
       </c>
       <c r="C7" t="n">
-        <v>44120432080</v>
+        <v>57964700247</v>
       </c>
       <c r="D7" t="n">
-        <v>0.3567200500770799</v>
+        <v>0.3907245746720164</v>
       </c>
       <c r="E7" t="n">
         <v>6</v>
@@ -572,17 +572,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2020-05-27</t>
+          <t>2020-06-05</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>17872745345</v>
+        <v>21624249509</v>
       </c>
       <c r="C8" t="n">
-        <v>48783198139</v>
+        <v>55387084107</v>
       </c>
       <c r="D8" t="n">
-        <v>0.366370923326397</v>
+        <v>0.3904204356962539</v>
       </c>
       <c r="E8" t="n">
         <v>7</v>
@@ -591,17 +591,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2020-05-28</t>
+          <t>2020-06-08</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>18416635989</v>
+        <v>23546771032</v>
       </c>
       <c r="C9" t="n">
-        <v>50047777669</v>
+        <v>58352042780</v>
       </c>
       <c r="D9" t="n">
-        <v>0.3679810942016595</v>
+        <v>0.4035295065980208</v>
       </c>
       <c r="E9" t="n">
         <v>8</v>
@@ -610,17 +610,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2020-05-29</t>
+          <t>2020-06-09</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>18782496399</v>
+        <v>20955198305</v>
       </c>
       <c r="C10" t="n">
-        <v>49396386216</v>
+        <v>53192911283</v>
       </c>
       <c r="D10" t="n">
-        <v>0.3802402936293375</v>
+        <v>0.3939471970900961</v>
       </c>
       <c r="E10" t="n">
         <v>9</v>
@@ -629,17 +629,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2020-06-01</t>
+          <t>2020-06-10</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>22806246928</v>
+        <v>20190478240</v>
       </c>
       <c r="C11" t="n">
-        <v>64259168243</v>
+        <v>52136701032</v>
       </c>
       <c r="D11" t="n">
-        <v>0.3549103972487906</v>
+        <v>0.3872603720670333</v>
       </c>
       <c r="E11" t="n">
         <v>10</v>
@@ -648,17 +648,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2020-06-02</t>
+          <t>2020-06-11</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>26690797837</v>
+        <v>21856153332</v>
       </c>
       <c r="C12" t="n">
-        <v>67019269521</v>
+        <v>58580995849</v>
       </c>
       <c r="D12" t="n">
-        <v>0.3982555767582133</v>
+        <v>0.3730928949780408</v>
       </c>
       <c r="E12" t="n">
         <v>11</v>
@@ -667,17 +667,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2020-06-03</t>
+          <t>2020-06-12</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>25988325662</v>
+        <v>22554032456</v>
       </c>
       <c r="C13" t="n">
-        <v>66814592975</v>
+        <v>58624630321</v>
       </c>
       <c r="D13" t="n">
-        <v>0.3889618196390726</v>
+        <v>0.3847193975041731</v>
       </c>
       <c r="E13" t="n">
         <v>12</v>
@@ -686,17 +686,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2020-06-04</t>
+          <t>2020-06-15</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>22648232850</v>
+        <v>24160399741</v>
       </c>
       <c r="C14" t="n">
-        <v>57964700247</v>
+        <v>62827231135</v>
       </c>
       <c r="D14" t="n">
-        <v>0.3907245746720164</v>
+        <v>0.3845529924609497</v>
       </c>
       <c r="E14" t="n">
         <v>13</v>
@@ -705,17 +705,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2020-06-05</t>
+          <t>2020-06-16</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>21624249509</v>
+        <v>22302612612</v>
       </c>
       <c r="C15" t="n">
-        <v>55387084107</v>
+        <v>57871475779</v>
       </c>
       <c r="D15" t="n">
-        <v>0.3904204356962539</v>
+        <v>0.3853817845801855</v>
       </c>
       <c r="E15" t="n">
         <v>14</v>
@@ -724,17 +724,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2020-06-08</t>
+          <t>2020-06-17</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>23546771032</v>
+        <v>23156031895</v>
       </c>
       <c r="C16" t="n">
-        <v>58352042780</v>
+        <v>61386131654</v>
       </c>
       <c r="D16" t="n">
-        <v>0.4035295065980208</v>
+        <v>0.3772192720257707</v>
       </c>
       <c r="E16" t="n">
         <v>15</v>
@@ -743,17 +743,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2020-06-09</t>
+          <t>2020-06-18</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>20955198305</v>
+        <v>25733088111</v>
       </c>
       <c r="C17" t="n">
-        <v>53192911283</v>
+        <v>63354121102</v>
       </c>
       <c r="D17" t="n">
-        <v>0.3939471970900961</v>
+        <v>0.4061785983830442</v>
       </c>
       <c r="E17" t="n">
         <v>16</v>
@@ -762,17 +762,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2020-06-10</t>
+          <t>2020-06-19</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>20190478240</v>
+        <v>24126480724</v>
       </c>
       <c r="C18" t="n">
-        <v>52136701032</v>
+        <v>61888832308</v>
       </c>
       <c r="D18" t="n">
-        <v>0.3872603720670333</v>
+        <v>0.3898357720489956</v>
       </c>
       <c r="E18" t="n">
         <v>17</v>
@@ -781,17 +781,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2020-06-11</t>
+          <t>2020-06-22</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>21856153332</v>
+        <v>25010112764</v>
       </c>
       <c r="C19" t="n">
-        <v>58580995849</v>
+        <v>63846785740</v>
       </c>
       <c r="D19" t="n">
-        <v>0.3730928949780408</v>
+        <v>0.3917207808369149</v>
       </c>
       <c r="E19" t="n">
         <v>18</v>
@@ -800,17 +800,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2020-06-12</t>
+          <t>2020-06-23</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>22554032456</v>
+        <v>21417149307</v>
       </c>
       <c r="C20" t="n">
-        <v>58624630321</v>
+        <v>56906481203</v>
       </c>
       <c r="D20" t="n">
-        <v>0.3847193975041731</v>
+        <v>0.3763569430799901</v>
       </c>
       <c r="E20" t="n">
         <v>19</v>
@@ -819,17 +819,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2020-06-15</t>
+          <t>2020-06-24</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>24160399741</v>
+        <v>19322024502</v>
       </c>
       <c r="C21" t="n">
-        <v>62827231135</v>
+        <v>52926747938</v>
       </c>
       <c r="D21" t="n">
-        <v>0.3845529924609497</v>
+        <v>0.3650710700123576</v>
       </c>
       <c r="E21" t="n">
         <v>20</v>
@@ -838,17 +838,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2020-06-16</t>
+          <t>2020-06-29</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>22302612612</v>
+        <v>20448932009</v>
       </c>
       <c r="C22" t="n">
-        <v>57871475779</v>
+        <v>54347085975</v>
       </c>
       <c r="D22" t="n">
-        <v>0.3853817845801855</v>
+        <v>0.3762654729713868</v>
       </c>
       <c r="E22" t="n">
         <v>21</v>
@@ -857,17 +857,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2020-06-17</t>
+          <t>2020-06-30</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>23156031895</v>
+        <v>20003048931</v>
       </c>
       <c r="C23" t="n">
-        <v>61386131654</v>
+        <v>53946886834</v>
       </c>
       <c r="D23" t="n">
-        <v>0.3772192720257707</v>
+        <v>0.3707915341352578</v>
       </c>
       <c r="E23" t="n">
         <v>22</v>
@@ -876,17 +876,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2020-06-18</t>
+          <t>2020-07-01</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>25733088111</v>
+        <v>25539868441</v>
       </c>
       <c r="C24" t="n">
-        <v>63354121102</v>
+        <v>66477208273</v>
       </c>
       <c r="D24" t="n">
-        <v>0.4061785983830442</v>
+        <v>0.3841898464826647</v>
       </c>
       <c r="E24" t="n">
         <v>23</v>
@@ -895,17 +895,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2020-06-19</t>
+          <t>2020-07-02</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>24126480724</v>
+        <v>35281401239</v>
       </c>
       <c r="C25" t="n">
-        <v>61888832308</v>
+        <v>86277275738</v>
       </c>
       <c r="D25" t="n">
-        <v>0.3898357720489956</v>
+        <v>0.4089304041789609</v>
       </c>
       <c r="E25" t="n">
         <v>24</v>
@@ -914,17 +914,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2020-06-22</t>
+          <t>2020-07-03</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>25010112764</v>
+        <v>39589081860</v>
       </c>
       <c r="C26" t="n">
-        <v>63846785740</v>
+        <v>96590527098</v>
       </c>
       <c r="D26" t="n">
-        <v>0.3917207808369149</v>
+        <v>0.4098650566409398</v>
       </c>
       <c r="E26" t="n">
         <v>25</v>
@@ -933,17 +933,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2020-06-23</t>
+          <t>2020-07-06</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>21417149307</v>
+        <v>51680326902</v>
       </c>
       <c r="C27" t="n">
-        <v>56906481203</v>
+        <v>132721246132</v>
       </c>
       <c r="D27" t="n">
-        <v>0.3763569430799901</v>
+        <v>0.3893900065600689</v>
       </c>
       <c r="E27" t="n">
         <v>26</v>
@@ -952,17 +952,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2020-06-24</t>
+          <t>2020-07-07</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>19322024502</v>
+        <v>54130474812</v>
       </c>
       <c r="C28" t="n">
-        <v>52926747938</v>
+        <v>140540263998</v>
       </c>
       <c r="D28" t="n">
-        <v>0.3650710700123576</v>
+        <v>0.3851599055824338</v>
       </c>
       <c r="E28" t="n">
         <v>27</v>
@@ -971,17 +971,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2020-06-29</t>
+          <t>2020-07-08</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>20448932009</v>
+        <v>48763694238</v>
       </c>
       <c r="C29" t="n">
-        <v>54347085975</v>
+        <v>124820435614</v>
       </c>
       <c r="D29" t="n">
-        <v>0.3762654729713868</v>
+        <v>0.3906707583427999</v>
       </c>
       <c r="E29" t="n">
         <v>28</v>
@@ -990,17 +990,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2020-06-30</t>
+          <t>2020-07-09</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>20003048931</v>
+        <v>50352644938</v>
       </c>
       <c r="C30" t="n">
-        <v>53946886834</v>
+        <v>137276438768</v>
       </c>
       <c r="D30" t="n">
-        <v>0.3707915341352578</v>
+        <v>0.3667974299879457</v>
       </c>
       <c r="E30" t="n">
         <v>29</v>
@@ -1009,17 +1009,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2020-07-01</t>
+          <t>2020-07-10</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>25539868441</v>
+        <v>45792064703</v>
       </c>
       <c r="C31" t="n">
-        <v>66477208273</v>
+        <v>124540979573</v>
       </c>
       <c r="D31" t="n">
-        <v>0.3841898464826647</v>
+        <v>0.3676867233580644</v>
       </c>
       <c r="E31" t="n">
         <v>30</v>
@@ -1028,17 +1028,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2020-07-02</t>
+          <t>2020-07-13</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>35281401239</v>
+        <v>45569190970</v>
       </c>
       <c r="C32" t="n">
-        <v>86277275738</v>
+        <v>125874117474</v>
       </c>
       <c r="D32" t="n">
-        <v>0.4089304041789609</v>
+        <v>0.3620219301987366</v>
       </c>
       <c r="E32" t="n">
         <v>31</v>
@@ -1047,17 +1047,17 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2020-07-03</t>
+          <t>2020-07-14</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>39589081860</v>
+        <v>44404671526</v>
       </c>
       <c r="C33" t="n">
-        <v>96590527098</v>
+        <v>127205292718</v>
       </c>
       <c r="D33" t="n">
-        <v>0.4098650566409398</v>
+        <v>0.3490788046409375</v>
       </c>
       <c r="E33" t="n">
         <v>32</v>
@@ -1066,17 +1066,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2020-07-06</t>
+          <t>2020-07-15</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>51680326902</v>
+        <v>40948010990</v>
       </c>
       <c r="C34" t="n">
-        <v>132721246132</v>
+        <v>115744357395</v>
       </c>
       <c r="D34" t="n">
-        <v>0.3893900065600689</v>
+        <v>0.3537797600815822</v>
       </c>
       <c r="E34" t="n">
         <v>33</v>
@@ -1085,17 +1085,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2020-07-07</t>
+          <t>2020-07-16</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>54130474812</v>
+        <v>41327517137</v>
       </c>
       <c r="C35" t="n">
-        <v>140540263998</v>
+        <v>110570972319</v>
       </c>
       <c r="D35" t="n">
-        <v>0.3851599055824338</v>
+        <v>0.373764617152584</v>
       </c>
       <c r="E35" t="n">
         <v>34</v>
@@ -1104,17 +1104,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2020-07-08</t>
+          <t>2020-07-17</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>48763694238</v>
+        <v>30786629717</v>
       </c>
       <c r="C36" t="n">
-        <v>124820435614</v>
+        <v>83073812068</v>
       </c>
       <c r="D36" t="n">
-        <v>0.3906707583427999</v>
+        <v>0.3705936798927636</v>
       </c>
       <c r="E36" t="n">
         <v>35</v>
@@ -1123,17 +1123,17 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2020-07-09</t>
+          <t>2020-07-20</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>50352644938</v>
+        <v>33302406491</v>
       </c>
       <c r="C37" t="n">
-        <v>137276438768</v>
+        <v>90725025902</v>
       </c>
       <c r="D37" t="n">
-        <v>0.3667974299879457</v>
+        <v>0.3670696829226903</v>
       </c>
       <c r="E37" t="n">
         <v>36</v>
@@ -1142,17 +1142,17 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2020-07-10</t>
+          <t>2020-07-21</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>45792064703</v>
+        <v>29750727633</v>
       </c>
       <c r="C38" t="n">
-        <v>124540979573</v>
+        <v>82804408460</v>
       </c>
       <c r="D38" t="n">
-        <v>0.3676867233580644</v>
+        <v>0.3592891753749025</v>
       </c>
       <c r="E38" t="n">
         <v>37</v>
@@ -1161,17 +1161,17 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2020-07-13</t>
+          <t>2020-07-22</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>45569190970</v>
+        <v>32546369994</v>
       </c>
       <c r="C39" t="n">
-        <v>125874117474</v>
+        <v>88951002081</v>
       </c>
       <c r="D39" t="n">
-        <v>0.3620219301987366</v>
+        <v>0.3658909875389917</v>
       </c>
       <c r="E39" t="n">
         <v>38</v>
@@ -1180,17 +1180,17 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2020-07-14</t>
+          <t>2020-07-23</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>44404671526</v>
+        <v>33380341470</v>
       </c>
       <c r="C40" t="n">
-        <v>127205292718</v>
+        <v>92918126099</v>
       </c>
       <c r="D40" t="n">
-        <v>0.3490788046409375</v>
+        <v>0.3592446691664313</v>
       </c>
       <c r="E40" t="n">
         <v>39</v>
@@ -1199,17 +1199,17 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2020-07-15</t>
+          <t>2020-07-24</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>40948010990</v>
+        <v>34826858650</v>
       </c>
       <c r="C41" t="n">
-        <v>115744357395</v>
+        <v>98778010270</v>
       </c>
       <c r="D41" t="n">
-        <v>0.3537797600815822</v>
+        <v>0.3525770417404056</v>
       </c>
       <c r="E41" t="n">
         <v>40</v>
@@ -1218,17 +1218,17 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2020-07-16</t>
+          <t>2020-07-27</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>41327517137</v>
+        <v>25272101520</v>
       </c>
       <c r="C42" t="n">
-        <v>110570972319</v>
+        <v>69273127708</v>
       </c>
       <c r="D42" t="n">
-        <v>0.373764617152584</v>
+        <v>0.3648182542951854</v>
       </c>
       <c r="E42" t="n">
         <v>41</v>
@@ -1237,17 +1237,17 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2020-07-17</t>
+          <t>2020-07-28</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>30786629717</v>
+        <v>25533477451</v>
       </c>
       <c r="C43" t="n">
-        <v>83073812068</v>
+        <v>67557159363</v>
       </c>
       <c r="D43" t="n">
-        <v>0.3705936798927636</v>
+        <v>0.3779536868002814</v>
       </c>
       <c r="E43" t="n">
         <v>42</v>
@@ -1256,17 +1256,17 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2020-07-20</t>
+          <t>2020-07-29</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>33302406491</v>
+        <v>27398207256</v>
       </c>
       <c r="C44" t="n">
-        <v>90725025902</v>
+        <v>75808503607</v>
       </c>
       <c r="D44" t="n">
-        <v>0.3670696829226903</v>
+        <v>0.3614133764997586</v>
       </c>
       <c r="E44" t="n">
         <v>43</v>
@@ -1275,17 +1275,17 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2020-07-21</t>
+          <t>2020-07-30</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>29750727633</v>
+        <v>29316097538</v>
       </c>
       <c r="C45" t="n">
-        <v>82804408460</v>
+        <v>80705680370</v>
       </c>
       <c r="D45" t="n">
-        <v>0.3592891753749025</v>
+        <v>0.3632470156201968</v>
       </c>
       <c r="E45" t="n">
         <v>44</v>
@@ -1294,17 +1294,17 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2020-07-22</t>
+          <t>2020-07-31</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>32546369994</v>
+        <v>30421341838</v>
       </c>
       <c r="C46" t="n">
-        <v>88951002081</v>
+        <v>83388719271</v>
       </c>
       <c r="D46" t="n">
-        <v>0.3658909875389917</v>
+        <v>0.3648136355126825</v>
       </c>
       <c r="E46" t="n">
         <v>45</v>
@@ -1313,17 +1313,17 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2020-07-23</t>
+          <t>2020-08-03</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>33380341470</v>
+        <v>32534419194</v>
       </c>
       <c r="C47" t="n">
-        <v>92918126099</v>
+        <v>97147468049</v>
       </c>
       <c r="D47" t="n">
-        <v>0.3592446691664313</v>
+        <v>0.3348972427937086</v>
       </c>
       <c r="E47" t="n">
         <v>46</v>
@@ -1332,17 +1332,17 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2020-07-24</t>
+          <t>2020-08-04</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>34826858650</v>
+        <v>35518548960</v>
       </c>
       <c r="C48" t="n">
-        <v>98778010270</v>
+        <v>100401661483</v>
       </c>
       <c r="D48" t="n">
-        <v>0.3525770417404056</v>
+        <v>0.3537645536474912</v>
       </c>
       <c r="E48" t="n">
         <v>47</v>
@@ -1351,17 +1351,17 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2020-07-27</t>
+          <t>2020-08-05</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>25272101520</v>
+        <v>31118752071</v>
       </c>
       <c r="C49" t="n">
-        <v>69273127708</v>
+        <v>88411991123</v>
       </c>
       <c r="D49" t="n">
-        <v>0.3648182542951854</v>
+        <v>0.351974338273947</v>
       </c>
       <c r="E49" t="n">
         <v>48</v>
@@ -1370,17 +1370,17 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2020-07-28</t>
+          <t>2020-08-06</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>25533477451</v>
+        <v>35289080996</v>
       </c>
       <c r="C50" t="n">
-        <v>67557159363</v>
+        <v>94484631872</v>
       </c>
       <c r="D50" t="n">
-        <v>0.3779536868002814</v>
+        <v>0.3734901676264849</v>
       </c>
       <c r="E50" t="n">
         <v>49</v>
@@ -1389,17 +1389,17 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2020-07-29</t>
+          <t>2020-08-07</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>27398207256</v>
+        <v>33926327226</v>
       </c>
       <c r="C51" t="n">
-        <v>75808503607</v>
+        <v>90977583613</v>
       </c>
       <c r="D51" t="n">
-        <v>0.3614133764997586</v>
+        <v>0.3729086427522151</v>
       </c>
       <c r="E51" t="n">
         <v>50</v>
@@ -1408,17 +1408,17 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2020-07-30</t>
+          <t>2020-08-10</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>29316097538</v>
+        <v>29708663069</v>
       </c>
       <c r="C52" t="n">
-        <v>80705680370</v>
+        <v>82942928747</v>
       </c>
       <c r="D52" t="n">
-        <v>0.3632470156201968</v>
+        <v>0.3581819875160189</v>
       </c>
       <c r="E52" t="n">
         <v>51</v>
@@ -1427,17 +1427,17 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2020-07-31</t>
+          <t>2020-08-11</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>30421341838</v>
+        <v>30946369948</v>
       </c>
       <c r="C53" t="n">
-        <v>83388719271</v>
+        <v>86295092754</v>
       </c>
       <c r="D53" t="n">
-        <v>0.3648136355126825</v>
+        <v>0.3586110051033644</v>
       </c>
       <c r="E53" t="n">
         <v>52</v>
@@ -1446,17 +1446,17 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2020-08-03</t>
+          <t>2020-08-12</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>32534419194</v>
+        <v>29856245191</v>
       </c>
       <c r="C54" t="n">
-        <v>97147468049</v>
+        <v>82452473263</v>
       </c>
       <c r="D54" t="n">
-        <v>0.3348972427937086</v>
+        <v>0.3621024817019988</v>
       </c>
       <c r="E54" t="n">
         <v>53</v>
@@ -1465,17 +1465,17 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2020-08-04</t>
+          <t>2020-08-13</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>35518548960</v>
+        <v>27823565615</v>
       </c>
       <c r="C55" t="n">
-        <v>100401661483</v>
+        <v>72532322436</v>
       </c>
       <c r="D55" t="n">
-        <v>0.3537645536474912</v>
+        <v>0.3836022986793308</v>
       </c>
       <c r="E55" t="n">
         <v>54</v>
@@ -1484,17 +1484,17 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2020-08-05</t>
+          <t>2020-08-14</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>31118752071</v>
+        <v>27261549866</v>
       </c>
       <c r="C56" t="n">
-        <v>88411991123</v>
+        <v>69180221661</v>
       </c>
       <c r="D56" t="n">
-        <v>0.351974338273947</v>
+        <v>0.3940656622869504</v>
       </c>
       <c r="E56" t="n">
         <v>55</v>
@@ -1503,17 +1503,17 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2020-08-06</t>
+          <t>2020-08-17</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>35289080996</v>
+        <v>37118467741</v>
       </c>
       <c r="C57" t="n">
-        <v>94484631872</v>
+        <v>91788369903</v>
       </c>
       <c r="D57" t="n">
-        <v>0.3734901676264849</v>
+        <v>0.4043918394043386</v>
       </c>
       <c r="E57" t="n">
         <v>56</v>
@@ -1522,17 +1522,17 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2020-08-07</t>
+          <t>2020-08-18</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>33926327226</v>
+        <v>31325687773</v>
       </c>
       <c r="C58" t="n">
-        <v>90977583613</v>
+        <v>85178317604</v>
       </c>
       <c r="D58" t="n">
-        <v>0.3729086427522151</v>
+        <v>0.3677659838109897</v>
       </c>
       <c r="E58" t="n">
         <v>57</v>
@@ -1541,17 +1541,17 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2020-08-10</t>
+          <t>2020-08-19</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>29708663069</v>
+        <v>33073383828</v>
       </c>
       <c r="C59" t="n">
-        <v>82942928747</v>
+        <v>88140275731</v>
       </c>
       <c r="D59" t="n">
-        <v>0.3581819875160189</v>
+        <v>0.375235765417145</v>
       </c>
       <c r="E59" t="n">
         <v>58</v>
@@ -1560,17 +1560,17 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2020-08-11</t>
+          <t>2020-08-20</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>30946369948</v>
+        <v>27646953314</v>
       </c>
       <c r="C60" t="n">
-        <v>86295092754</v>
+        <v>72119978332</v>
       </c>
       <c r="D60" t="n">
-        <v>0.3586110051033644</v>
+        <v>0.3833466669489126</v>
       </c>
       <c r="E60" t="n">
         <v>59</v>
@@ -1579,17 +1579,17 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2020-08-12</t>
+          <t>2020-08-21</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>29856245191</v>
+        <v>25486130617</v>
       </c>
       <c r="C61" t="n">
-        <v>82452473263</v>
+        <v>66786682396</v>
       </c>
       <c r="D61" t="n">
-        <v>0.3621024817019988</v>
+        <v>0.3816049802546626</v>
       </c>
       <c r="E61" t="n">
         <v>60</v>
@@ -1598,17 +1598,17 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2020-08-13</t>
+          <t>2020-08-24</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>27823565615</v>
+        <v>25209284709</v>
       </c>
       <c r="C62" t="n">
-        <v>72532322436</v>
+        <v>67412296336</v>
       </c>
       <c r="D62" t="n">
-        <v>0.3836022986793308</v>
+        <v>0.3739567716748666</v>
       </c>
       <c r="E62" t="n">
         <v>61</v>
@@ -1617,17 +1617,17 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2020-08-14</t>
+          <t>2020-08-25</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>27261549866</v>
+        <v>26619247474</v>
       </c>
       <c r="C63" t="n">
-        <v>69180221661</v>
+        <v>73103731924</v>
       </c>
       <c r="D63" t="n">
-        <v>0.3940656622869504</v>
+        <v>0.3641298025889275</v>
       </c>
       <c r="E63" t="n">
         <v>62</v>
@@ -1636,17 +1636,17 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2020-08-17</t>
+          <t>2020-08-26</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>37118467741</v>
+        <v>26322908958</v>
       </c>
       <c r="C64" t="n">
-        <v>91788369903</v>
+        <v>75716936591</v>
       </c>
       <c r="D64" t="n">
-        <v>0.4043918394043386</v>
+        <v>0.3476488899727732</v>
       </c>
       <c r="E64" t="n">
         <v>63</v>
@@ -1655,17 +1655,17 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2020-08-18</t>
+          <t>2020-08-27</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>31325687773</v>
+        <v>23276018839</v>
       </c>
       <c r="C65" t="n">
-        <v>85178317604</v>
+        <v>65005692955</v>
       </c>
       <c r="D65" t="n">
-        <v>0.3677659838109897</v>
+        <v>0.3580612371152286</v>
       </c>
       <c r="E65" t="n">
         <v>64</v>
@@ -1674,17 +1674,17 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2020-08-19</t>
+          <t>2020-08-28</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>33073383828</v>
+        <v>25701039669</v>
       </c>
       <c r="C66" t="n">
-        <v>88140275731</v>
+        <v>70850828969</v>
       </c>
       <c r="D66" t="n">
-        <v>0.375235765417145</v>
+        <v>0.3627486091975749</v>
       </c>
       <c r="E66" t="n">
         <v>65</v>
@@ -1693,17 +1693,17 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2020-08-20</t>
+          <t>2020-08-31</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>27646953314</v>
+        <v>28573296373</v>
       </c>
       <c r="C67" t="n">
-        <v>72119978332</v>
+        <v>77184652221</v>
       </c>
       <c r="D67" t="n">
-        <v>0.3833466669489126</v>
+        <v>0.3701940159189566</v>
       </c>
       <c r="E67" t="n">
         <v>66</v>
@@ -1712,17 +1712,17 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2020-08-21</t>
+          <t>2020-09-01</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>25486130617</v>
+        <v>23964180511</v>
       </c>
       <c r="C68" t="n">
-        <v>66786682396</v>
+        <v>64392996012</v>
       </c>
       <c r="D68" t="n">
-        <v>0.3816049802546626</v>
+        <v>0.3721550788929613</v>
       </c>
       <c r="E68" t="n">
         <v>67</v>
@@ -1731,17 +1731,17 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2020-08-24</t>
+          <t>2020-09-02</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>25209284709</v>
+        <v>30082062270</v>
       </c>
       <c r="C69" t="n">
-        <v>67412296336</v>
+        <v>77531927895</v>
       </c>
       <c r="D69" t="n">
-        <v>0.3739567716748666</v>
+        <v>0.3879957984630482</v>
       </c>
       <c r="E69" t="n">
         <v>68</v>
@@ -1750,17 +1750,17 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2020-08-25</t>
+          <t>2020-09-03</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>26619247474</v>
+        <v>27715216294</v>
       </c>
       <c r="C70" t="n">
-        <v>73103731924</v>
+        <v>73519808249</v>
       </c>
       <c r="D70" t="n">
-        <v>0.3641298025889275</v>
+        <v>0.3769761776327399</v>
       </c>
       <c r="E70" t="n">
         <v>69</v>
@@ -1769,17 +1769,17 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2020-08-26</t>
+          <t>2020-09-04</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>26322908958</v>
+        <v>24329945914</v>
       </c>
       <c r="C71" t="n">
-        <v>75716936591</v>
+        <v>65573685675</v>
       </c>
       <c r="D71" t="n">
-        <v>0.3476488899727732</v>
+        <v>0.37103215510236</v>
       </c>
       <c r="E71" t="n">
         <v>70</v>
@@ -1788,17 +1788,17 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2020-08-27</t>
+          <t>2020-09-07</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>23276018839</v>
+        <v>29997390344</v>
       </c>
       <c r="C72" t="n">
-        <v>65005692955</v>
+        <v>79881522723</v>
       </c>
       <c r="D72" t="n">
-        <v>0.3580612371152286</v>
+        <v>0.375523516846568</v>
       </c>
       <c r="E72" t="n">
         <v>71</v>
@@ -1807,17 +1807,17 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2020-08-28</t>
+          <t>2020-09-08</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>25701039669</v>
+        <v>32724062545</v>
       </c>
       <c r="C73" t="n">
-        <v>70850828969</v>
+        <v>80161481426</v>
       </c>
       <c r="D73" t="n">
-        <v>0.3627486091975749</v>
+        <v>0.4082267688030289</v>
       </c>
       <c r="E73" t="n">
         <v>72</v>
@@ -1826,17 +1826,17 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2020-08-31</t>
+          <t>2020-09-09</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>28573296373</v>
+        <v>41720230941</v>
       </c>
       <c r="C74" t="n">
-        <v>77184652221</v>
+        <v>98517765305</v>
       </c>
       <c r="D74" t="n">
-        <v>0.3701940159189566</v>
+        <v>0.4234792660170358</v>
       </c>
       <c r="E74" t="n">
         <v>73</v>
@@ -1845,17 +1845,17 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2020-09-01</t>
+          <t>2020-09-10</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>23964180511</v>
+        <v>32362586075</v>
       </c>
       <c r="C75" t="n">
-        <v>64392996012</v>
+        <v>83938666669</v>
       </c>
       <c r="D75" t="n">
-        <v>0.3721550788929613</v>
+        <v>0.3855503948212232</v>
       </c>
       <c r="E75" t="n">
         <v>74</v>
@@ -1864,17 +1864,17 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2020-09-02</t>
+          <t>2020-09-11</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>30082062270</v>
+        <v>23586290440</v>
       </c>
       <c r="C76" t="n">
-        <v>77531927895</v>
+        <v>60330240577</v>
       </c>
       <c r="D76" t="n">
-        <v>0.3879957984630482</v>
+        <v>0.3909530314220547</v>
       </c>
       <c r="E76" t="n">
         <v>75</v>
@@ -1883,17 +1883,17 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2020-09-03</t>
+          <t>2020-09-14</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>27715216294</v>
+        <v>24462170352</v>
       </c>
       <c r="C77" t="n">
-        <v>73519808249</v>
+        <v>63101019998</v>
       </c>
       <c r="D77" t="n">
-        <v>0.3769761776327399</v>
+        <v>0.3876667976646865</v>
       </c>
       <c r="E77" t="n">
         <v>76</v>
@@ -1902,17 +1902,17 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2020-09-04</t>
+          <t>2020-09-15</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>24329945914</v>
+        <v>23106120892</v>
       </c>
       <c r="C78" t="n">
-        <v>65573685675</v>
+        <v>58614407766</v>
       </c>
       <c r="D78" t="n">
-        <v>0.37103215510236</v>
+        <v>0.3942054824514151</v>
       </c>
       <c r="E78" t="n">
         <v>77</v>
@@ -1921,17 +1921,17 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2020-09-07</t>
+          <t>2020-09-16</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>29997390344</v>
+        <v>21724638649</v>
       </c>
       <c r="C79" t="n">
-        <v>79881522723</v>
+        <v>55182289033</v>
       </c>
       <c r="D79" t="n">
-        <v>0.375523516846568</v>
+        <v>0.3936886096915674</v>
       </c>
       <c r="E79" t="n">
         <v>78</v>
@@ -1940,17 +1940,17 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2020-09-08</t>
+          <t>2020-09-17</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>32724062545</v>
+        <v>20554994106</v>
       </c>
       <c r="C80" t="n">
-        <v>80161481426</v>
+        <v>55472969929</v>
       </c>
       <c r="D80" t="n">
-        <v>0.4082267688030289</v>
+        <v>0.3705407179804577</v>
       </c>
       <c r="E80" t="n">
         <v>79</v>
@@ -1959,17 +1959,17 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2020-09-09</t>
+          <t>2020-09-18</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>41720230941</v>
+        <v>25018086444</v>
       </c>
       <c r="C81" t="n">
-        <v>98517765305</v>
+        <v>64587549837</v>
       </c>
       <c r="D81" t="n">
-        <v>0.4234792660170358</v>
+        <v>0.3873515330297914</v>
       </c>
       <c r="E81" t="n">
         <v>80</v>
@@ -1978,17 +1978,17 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2020-09-10</t>
+          <t>2020-09-21</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>32362586075</v>
+        <v>22182279260</v>
       </c>
       <c r="C82" t="n">
-        <v>83938666669</v>
+        <v>58098440053</v>
       </c>
       <c r="D82" t="n">
-        <v>0.3855503948212232</v>
+        <v>0.3818050749686968</v>
       </c>
       <c r="E82" t="n">
         <v>81</v>
@@ -1997,17 +1997,17 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2020-09-11</t>
+          <t>2020-09-22</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>23586290440</v>
+        <v>22099090990</v>
       </c>
       <c r="C83" t="n">
-        <v>60330240577</v>
+        <v>56264182474</v>
       </c>
       <c r="D83" t="n">
-        <v>0.3909530314220547</v>
+        <v>0.3927736975510506</v>
       </c>
       <c r="E83" t="n">
         <v>82</v>
@@ -2016,17 +2016,17 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2020-09-14</t>
+          <t>2020-09-23</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>24462170352</v>
+        <v>19077501915</v>
       </c>
       <c r="C84" t="n">
-        <v>63101019998</v>
+        <v>48597940983</v>
       </c>
       <c r="D84" t="n">
-        <v>0.3876667976646865</v>
+        <v>0.3925578230088695</v>
       </c>
       <c r="E84" t="n">
         <v>83</v>
@@ -2035,17 +2035,17 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2020-09-15</t>
+          <t>2020-09-24</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>23106120892</v>
+        <v>20859996043</v>
       </c>
       <c r="C85" t="n">
-        <v>58614407766</v>
+        <v>54861814882</v>
       </c>
       <c r="D85" t="n">
-        <v>0.3942054824514151</v>
+        <v>0.3802279616134993</v>
       </c>
       <c r="E85" t="n">
         <v>84</v>
@@ -2054,17 +2054,17 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2020-09-16</t>
+          <t>2020-09-25</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>21724638649</v>
+        <v>16281719043</v>
       </c>
       <c r="C86" t="n">
-        <v>55182289033</v>
+        <v>43622575116</v>
       </c>
       <c r="D86" t="n">
-        <v>0.3936886096915674</v>
+        <v>0.373240667239476</v>
       </c>
       <c r="E86" t="n">
         <v>85</v>
@@ -2073,17 +2073,17 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2020-09-17</t>
+          <t>2020-09-28</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>20554994106</v>
+        <v>14676583271</v>
       </c>
       <c r="C87" t="n">
-        <v>55472969929</v>
+        <v>40556797589</v>
       </c>
       <c r="D87" t="n">
-        <v>0.3705407179804577</v>
+        <v>0.3618772719614492</v>
       </c>
       <c r="E87" t="n">
         <v>86</v>
@@ -2092,17 +2092,17 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2020-09-18</t>
+          <t>2020-09-29</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>25018086444</v>
+        <v>14442107257</v>
       </c>
       <c r="C88" t="n">
-        <v>64587549837</v>
+        <v>40163621965</v>
       </c>
       <c r="D88" t="n">
-        <v>0.3873515330297914</v>
+        <v>0.3595817944304267</v>
       </c>
       <c r="E88" t="n">
         <v>87</v>
@@ -2111,17 +2111,17 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2020-09-21</t>
+          <t>2020-09-30</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>22182279260</v>
+        <v>15066784297</v>
       </c>
       <c r="C89" t="n">
-        <v>58098440053</v>
+        <v>40300843448</v>
       </c>
       <c r="D89" t="n">
-        <v>0.3818050749686968</v>
+        <v>0.3738577907541961</v>
       </c>
       <c r="E89" t="n">
         <v>88</v>
@@ -2130,17 +2130,17 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2020-09-22</t>
+          <t>2020-10-09</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>22099090990</v>
+        <v>18363804782</v>
       </c>
       <c r="C90" t="n">
-        <v>56264182474</v>
+        <v>50410563994</v>
       </c>
       <c r="D90" t="n">
-        <v>0.3927736975510506</v>
+        <v>0.3642848507742486</v>
       </c>
       <c r="E90" t="n">
         <v>89</v>
@@ -2149,17 +2149,17 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2020-09-23</t>
+          <t>2020-10-12</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>19077501915</v>
+        <v>24824121596</v>
       </c>
       <c r="C91" t="n">
-        <v>48597940983</v>
+        <v>69075123930</v>
       </c>
       <c r="D91" t="n">
-        <v>0.3925578230088695</v>
+        <v>0.3593786038104905</v>
       </c>
       <c r="E91" t="n">
         <v>90</v>
@@ -2168,17 +2168,17 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2020-09-24</t>
+          <t>2020-10-13</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>20859996043</v>
+        <v>21950874234</v>
       </c>
       <c r="C92" t="n">
-        <v>54861814882</v>
+        <v>58435290007</v>
       </c>
       <c r="D92" t="n">
-        <v>0.3802279616134993</v>
+        <v>0.3756441395494142</v>
       </c>
       <c r="E92" t="n">
         <v>91</v>
@@ -2187,17 +2187,17 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2020-09-25</t>
+          <t>2020-10-14</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>16281719043</v>
+        <v>21810988673</v>
       </c>
       <c r="C93" t="n">
-        <v>43622575116</v>
+        <v>58022364557</v>
       </c>
       <c r="D93" t="n">
-        <v>0.373240667239476</v>
+        <v>0.3759065808421738</v>
       </c>
       <c r="E93" t="n">
         <v>92</v>
@@ -2206,17 +2206,17 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2020-09-28</t>
+          <t>2020-10-15</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>14676583271</v>
+        <v>20410751440</v>
       </c>
       <c r="C94" t="n">
-        <v>40556797589</v>
+        <v>54415224691</v>
       </c>
       <c r="D94" t="n">
-        <v>0.3618772719614492</v>
+        <v>0.3750926612157467</v>
       </c>
       <c r="E94" t="n">
         <v>93</v>
@@ -2225,17 +2225,17 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2020-09-29</t>
+          <t>2020-10-16</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>14442107257</v>
+        <v>19779199722</v>
       </c>
       <c r="C95" t="n">
-        <v>40163621965</v>
+        <v>51552706029</v>
       </c>
       <c r="D95" t="n">
-        <v>0.3595817944304267</v>
+        <v>0.3836694762613156</v>
       </c>
       <c r="E95" t="n">
         <v>94</v>
@@ -2244,17 +2244,17 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2020-09-30</t>
+          <t>2020-10-19</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>15066784297</v>
+        <v>20562725471</v>
       </c>
       <c r="C96" t="n">
-        <v>40300843448</v>
+        <v>53895497648</v>
       </c>
       <c r="D96" t="n">
-        <v>0.3738577907541961</v>
+        <v>0.3815295593947087</v>
       </c>
       <c r="E96" t="n">
         <v>95</v>
@@ -2263,17 +2263,17 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2020-10-09</t>
+          <t>2020-10-20</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>18363804782</v>
+        <v>18296672779</v>
       </c>
       <c r="C97" t="n">
-        <v>50410563994</v>
+        <v>47922773316</v>
       </c>
       <c r="D97" t="n">
-        <v>0.3642848507742486</v>
+        <v>0.3817949486844761</v>
       </c>
       <c r="E97" t="n">
         <v>96</v>
@@ -2282,17 +2282,17 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2020-10-12</t>
+          <t>2020-10-21</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>24824121596</v>
+        <v>18370049664</v>
       </c>
       <c r="C98" t="n">
-        <v>69075123930</v>
+        <v>49307563396</v>
       </c>
       <c r="D98" t="n">
-        <v>0.3593786038104905</v>
+        <v>0.3725604836009853</v>
       </c>
       <c r="E98" t="n">
         <v>97</v>
@@ -2301,17 +2301,17 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2020-10-13</t>
+          <t>2020-10-22</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>21950874234</v>
+        <v>17665602844</v>
       </c>
       <c r="C99" t="n">
-        <v>58435290007</v>
+        <v>46460364776</v>
       </c>
       <c r="D99" t="n">
-        <v>0.3756441395494142</v>
+        <v>0.3802295339085566</v>
       </c>
       <c r="E99" t="n">
         <v>98</v>
@@ -2320,17 +2320,17 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2020-10-14</t>
+          <t>2020-10-23</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>21810988673</v>
+        <v>17466910909</v>
       </c>
       <c r="C100" t="n">
-        <v>58022364557</v>
+        <v>47398504650</v>
       </c>
       <c r="D100" t="n">
-        <v>0.3759065808421738</v>
+        <v>0.3685118557637873</v>
       </c>
       <c r="E100" t="n">
         <v>99</v>
@@ -2339,17 +2339,17 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2020-10-15</t>
+          <t>2020-10-26</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>20410751440</v>
+        <v>16145407434</v>
       </c>
       <c r="C101" t="n">
-        <v>54415224691</v>
+        <v>44150494774</v>
       </c>
       <c r="D101" t="n">
-        <v>0.3750926612157467</v>
+        <v>0.3656902944496094</v>
       </c>
       <c r="E101" t="n">
         <v>100</v>
@@ -2358,17 +2358,17 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2020-10-16</t>
+          <t>2020-10-27</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>19779199722</v>
+        <v>15491813981</v>
       </c>
       <c r="C102" t="n">
-        <v>51552706029</v>
+        <v>43505082864</v>
       </c>
       <c r="D102" t="n">
-        <v>0.3836694762613156</v>
+        <v>0.356092046288672</v>
       </c>
       <c r="E102" t="n">
         <v>101</v>
@@ -2377,17 +2377,17 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2020-10-19</t>
+          <t>2020-10-28</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>20562725471</v>
+        <v>17543172634</v>
       </c>
       <c r="C103" t="n">
-        <v>53895497648</v>
+        <v>49485508785</v>
       </c>
       <c r="D103" t="n">
-        <v>0.3815295593947087</v>
+        <v>0.3545113117906887</v>
       </c>
       <c r="E103" t="n">
         <v>102</v>
@@ -2396,17 +2396,17 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2020-10-20</t>
+          <t>2020-10-29</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>18296672779</v>
+        <v>18553392322</v>
       </c>
       <c r="C104" t="n">
-        <v>47922773316</v>
+        <v>51689467398</v>
       </c>
       <c r="D104" t="n">
-        <v>0.3817949486844761</v>
+        <v>0.3589395142948963</v>
       </c>
       <c r="E104" t="n">
         <v>103</v>
@@ -2415,17 +2415,17 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2020-10-21</t>
+          <t>2020-10-30</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>18370049664</v>
+        <v>20650226596</v>
       </c>
       <c r="C105" t="n">
-        <v>49307563396</v>
+        <v>60348197366</v>
       </c>
       <c r="D105" t="n">
-        <v>0.3725604836009853</v>
+        <v>0.3421846467220954</v>
       </c>
       <c r="E105" t="n">
         <v>104</v>
@@ -2434,17 +2434,17 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2020-10-22</t>
+          <t>2020-11-02</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>17665602844</v>
+        <v>19992661394</v>
       </c>
       <c r="C106" t="n">
-        <v>46460364776</v>
+        <v>56353918211</v>
       </c>
       <c r="D106" t="n">
-        <v>0.3802295339085566</v>
+        <v>0.3547696775784711</v>
       </c>
       <c r="E106" t="n">
         <v>105</v>
@@ -2453,17 +2453,17 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2020-10-23</t>
+          <t>2020-11-03</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>17466910909</v>
+        <v>20249408150</v>
       </c>
       <c r="C107" t="n">
-        <v>47398504650</v>
+        <v>55344378404</v>
       </c>
       <c r="D107" t="n">
-        <v>0.3685118557637873</v>
+        <v>0.365880126111173</v>
       </c>
       <c r="E107" t="n">
         <v>106</v>
@@ -2472,17 +2472,17 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2020-10-26</t>
+          <t>2020-11-04</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>16145407434</v>
+        <v>18257580496</v>
       </c>
       <c r="C108" t="n">
-        <v>44150494774</v>
+        <v>49909415865</v>
       </c>
       <c r="D108" t="n">
-        <v>0.3656902944496094</v>
+        <v>0.3658143494483073</v>
       </c>
       <c r="E108" t="n">
         <v>107</v>
@@ -2491,17 +2491,17 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2020-10-27</t>
+          <t>2020-11-05</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>15491813981</v>
+        <v>21285267389</v>
       </c>
       <c r="C109" t="n">
-        <v>43505082864</v>
+        <v>58980118835</v>
       </c>
       <c r="D109" t="n">
-        <v>0.356092046288672</v>
+        <v>0.3608888522002924</v>
       </c>
       <c r="E109" t="n">
         <v>108</v>
@@ -2510,17 +2510,17 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2020-10-28</t>
+          <t>2020-11-06</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>17543172634</v>
+        <v>23071856412</v>
       </c>
       <c r="C110" t="n">
-        <v>49485508785</v>
+        <v>59902082650</v>
       </c>
       <c r="D110" t="n">
-        <v>0.3545113117906887</v>
+        <v>0.3851595034984981</v>
       </c>
       <c r="E110" t="n">
         <v>109</v>
@@ -2529,17 +2529,17 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2020-10-29</t>
+          <t>2020-11-09</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>18553392322</v>
+        <v>27202863336</v>
       </c>
       <c r="C111" t="n">
-        <v>51689467398</v>
+        <v>74478178320</v>
       </c>
       <c r="D111" t="n">
-        <v>0.3589395142948963</v>
+        <v>0.3652460888492902</v>
       </c>
       <c r="E111" t="n">
         <v>110</v>
@@ -2548,17 +2548,17 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2020-10-30</t>
+          <t>2020-11-10</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>20650226596</v>
+        <v>25309810082</v>
       </c>
       <c r="C112" t="n">
-        <v>60348197366</v>
+        <v>67090114044</v>
       </c>
       <c r="D112" t="n">
-        <v>0.3421846467220954</v>
+        <v>0.3772509622714452</v>
       </c>
       <c r="E112" t="n">
         <v>111</v>
@@ -2567,17 +2567,17 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2020-11-02</t>
+          <t>2020-11-11</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>19992661394</v>
+        <v>23822441228</v>
       </c>
       <c r="C113" t="n">
-        <v>56353918211</v>
+        <v>61988411650</v>
       </c>
       <c r="D113" t="n">
-        <v>0.3547696775784711</v>
+        <v>0.3843047529997488</v>
       </c>
       <c r="E113" t="n">
         <v>112</v>
@@ -2586,17 +2586,17 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2020-11-03</t>
+          <t>2020-11-12</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>20249408150</v>
+        <v>19076439758</v>
       </c>
       <c r="C114" t="n">
-        <v>55344378404</v>
+        <v>51703999860</v>
       </c>
       <c r="D114" t="n">
-        <v>0.365880126111173</v>
+        <v>0.3689548160616911</v>
       </c>
       <c r="E114" t="n">
         <v>113</v>
@@ -2605,17 +2605,17 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2020-11-04</t>
+          <t>2020-11-13</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>18257580496</v>
+        <v>20119982649</v>
       </c>
       <c r="C115" t="n">
-        <v>49909415865</v>
+        <v>52210418675</v>
       </c>
       <c r="D115" t="n">
-        <v>0.3658143494483073</v>
+        <v>0.3853633653896379</v>
       </c>
       <c r="E115" t="n">
         <v>114</v>
@@ -2624,17 +2624,17 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2020-11-05</t>
+          <t>2020-11-16</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>21285267389</v>
+        <v>23217241543</v>
       </c>
       <c r="C116" t="n">
-        <v>58980118835</v>
+        <v>61350411349</v>
       </c>
       <c r="D116" t="n">
-        <v>0.3608888522002924</v>
+        <v>0.3784366075546849</v>
       </c>
       <c r="E116" t="n">
         <v>115</v>
@@ -2643,17 +2643,17 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2020-11-06</t>
+          <t>2020-11-17</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>23071856412</v>
+        <v>24335506367</v>
       </c>
       <c r="C117" t="n">
-        <v>59902082650</v>
+        <v>64241703103</v>
       </c>
       <c r="D117" t="n">
-        <v>0.3851595034984981</v>
+        <v>0.3788116626980203</v>
       </c>
       <c r="E117" t="n">
         <v>116</v>
@@ -2662,17 +2662,17 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2020-11-09</t>
+          <t>2020-11-18</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>27202863336</v>
+        <v>25490702717</v>
       </c>
       <c r="C118" t="n">
-        <v>74478178320</v>
+        <v>63205463709</v>
       </c>
       <c r="D118" t="n">
-        <v>0.3652460888492902</v>
+        <v>0.4032990381078449</v>
       </c>
       <c r="E118" t="n">
         <v>117</v>
@@ -2681,17 +2681,17 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2020-11-10</t>
+          <t>2020-11-19</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>25309810082</v>
+        <v>23177522765</v>
       </c>
       <c r="C119" t="n">
-        <v>67090114044</v>
+        <v>59756276020</v>
       </c>
       <c r="D119" t="n">
-        <v>0.3772509622714452</v>
+        <v>0.3878675899623104</v>
       </c>
       <c r="E119" t="n">
         <v>118</v>
@@ -2700,17 +2700,17 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2020-11-11</t>
+          <t>2020-11-20</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>23822441228</v>
+        <v>22935620159</v>
       </c>
       <c r="C120" t="n">
-        <v>61988411650</v>
+        <v>58875754449</v>
       </c>
       <c r="D120" t="n">
-        <v>0.3843047529997488</v>
+        <v>0.3895596816320637</v>
       </c>
       <c r="E120" t="n">
         <v>119</v>
@@ -2719,17 +2719,17 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2020-11-12</t>
+          <t>2020-11-23</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>19076439758</v>
+        <v>32096579820</v>
       </c>
       <c r="C121" t="n">
-        <v>51703999860</v>
+        <v>77198006469</v>
       </c>
       <c r="D121" t="n">
-        <v>0.3689548160616911</v>
+        <v>0.4157695423506675</v>
       </c>
       <c r="E121" t="n">
         <v>120</v>
@@ -2738,17 +2738,17 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2020-11-13</t>
+          <t>2020-11-24</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>20119982649</v>
+        <v>26709718473</v>
       </c>
       <c r="C122" t="n">
-        <v>52210418675</v>
+        <v>65410116144</v>
       </c>
       <c r="D122" t="n">
-        <v>0.3853633653896379</v>
+        <v>0.408342318399171</v>
       </c>
       <c r="E122" t="n">
         <v>121</v>
@@ -2757,17 +2757,17 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2020-11-16</t>
+          <t>2020-11-25</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>23217241543</v>
+        <v>27089790866</v>
       </c>
       <c r="C123" t="n">
-        <v>61350411349</v>
+        <v>68837443765</v>
       </c>
       <c r="D123" t="n">
-        <v>0.3784366075546849</v>
+        <v>0.3935327836762824</v>
       </c>
       <c r="E123" t="n">
         <v>122</v>
@@ -2776,17 +2776,17 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2020-11-17</t>
+          <t>2020-11-26</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>24335506367</v>
+        <v>21689088930</v>
       </c>
       <c r="C124" t="n">
-        <v>64241703103</v>
+        <v>57127013421</v>
       </c>
       <c r="D124" t="n">
-        <v>0.3788116626980203</v>
+        <v>0.3796643239540867</v>
       </c>
       <c r="E124" t="n">
         <v>123</v>
@@ -2795,17 +2795,17 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2020-11-18</t>
+          <t>2020-11-27</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>25490702717</v>
+        <v>23626364341</v>
       </c>
       <c r="C125" t="n">
-        <v>63205463709</v>
+        <v>58765160877</v>
       </c>
       <c r="D125" t="n">
-        <v>0.4032990381078449</v>
+        <v>0.4020471311301572</v>
       </c>
       <c r="E125" t="n">
         <v>124</v>
@@ -2814,17 +2814,17 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2020-11-19</t>
+          <t>2020-11-30</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>23177522765</v>
+        <v>33970232252</v>
       </c>
       <c r="C126" t="n">
-        <v>59756276020</v>
+        <v>75092505579</v>
       </c>
       <c r="D126" t="n">
-        <v>0.3878675899623104</v>
+        <v>0.4523784629381171</v>
       </c>
       <c r="E126" t="n">
         <v>125</v>
@@ -2833,17 +2833,17 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2020-11-20</t>
+          <t>2020-12-01</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>22935620159</v>
+        <v>28738868941</v>
       </c>
       <c r="C127" t="n">
-        <v>58875754449</v>
+        <v>67936162045</v>
       </c>
       <c r="D127" t="n">
-        <v>0.3895596816320637</v>
+        <v>0.4230275611089682</v>
       </c>
       <c r="E127" t="n">
         <v>126</v>
@@ -2852,17 +2852,17 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2020-11-23</t>
+          <t>2020-12-02</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>32096579820</v>
+        <v>28928357564</v>
       </c>
       <c r="C128" t="n">
-        <v>77198006469</v>
+        <v>69689843826</v>
       </c>
       <c r="D128" t="n">
-        <v>0.4157695423506675</v>
+        <v>0.4151014835996427</v>
       </c>
       <c r="E128" t="n">
         <v>127</v>
@@ -2871,17 +2871,17 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2020-11-24</t>
+          <t>2020-12-03</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>26709718473</v>
+        <v>28497726227</v>
       </c>
       <c r="C129" t="n">
-        <v>65410116144</v>
+        <v>66950741850</v>
       </c>
       <c r="D129" t="n">
-        <v>0.408342318399171</v>
+        <v>0.4256521352795137</v>
       </c>
       <c r="E129" t="n">
         <v>128</v>
@@ -2890,17 +2890,17 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2020-11-25</t>
+          <t>2020-12-04</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>27089790866</v>
+        <v>23614518756</v>
       </c>
       <c r="C130" t="n">
-        <v>68837443765</v>
+        <v>57124426015</v>
       </c>
       <c r="D130" t="n">
-        <v>0.3935327836762824</v>
+        <v>0.4133874141649876</v>
       </c>
       <c r="E130" t="n">
         <v>129</v>
@@ -2909,17 +2909,17 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2020-11-26</t>
+          <t>2020-12-07</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>21689088930</v>
+        <v>22345056458</v>
       </c>
       <c r="C131" t="n">
-        <v>57127013421</v>
+        <v>56856559648</v>
       </c>
       <c r="D131" t="n">
-        <v>0.3796643239540867</v>
+        <v>0.3930075367967857</v>
       </c>
       <c r="E131" t="n">
         <v>130</v>
@@ -2928,17 +2928,17 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>2020-11-27</t>
+          <t>2020-12-08</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>23626364341</v>
+        <v>20555717183</v>
       </c>
       <c r="C132" t="n">
-        <v>58765160877</v>
+        <v>51665831943</v>
       </c>
       <c r="D132" t="n">
-        <v>0.4020471311301572</v>
+        <v>0.3978590184259099</v>
       </c>
       <c r="E132" t="n">
         <v>131</v>
@@ -2947,17 +2947,17 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>2020-11-30</t>
+          <t>2020-12-09</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>33970232252</v>
+        <v>22167887887</v>
       </c>
       <c r="C133" t="n">
-        <v>75092505579</v>
+        <v>59426788696</v>
       </c>
       <c r="D133" t="n">
-        <v>0.4523784629381171</v>
+        <v>0.3730285343265085</v>
       </c>
       <c r="E133" t="n">
         <v>132</v>
@@ -2966,17 +2966,17 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2020-12-01</t>
+          <t>2020-12-10</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>28738868941</v>
+        <v>21008686040</v>
       </c>
       <c r="C134" t="n">
-        <v>67936162045</v>
+        <v>53530291688</v>
       </c>
       <c r="D134" t="n">
-        <v>0.4230275611089682</v>
+        <v>0.3924635076238444</v>
       </c>
       <c r="E134" t="n">
         <v>133</v>
@@ -2985,17 +2985,17 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>2020-12-02</t>
+          <t>2020-12-11</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>28928357564</v>
+        <v>24084146686</v>
       </c>
       <c r="C135" t="n">
-        <v>69689843826</v>
+        <v>64194443337</v>
       </c>
       <c r="D135" t="n">
-        <v>0.4151014835996427</v>
+        <v>0.3751749440300626</v>
       </c>
       <c r="E135" t="n">
         <v>134</v>
@@ -3004,17 +3004,17 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>2020-12-03</t>
+          <t>2020-12-14</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>28497726227</v>
+        <v>20561369384</v>
       </c>
       <c r="C136" t="n">
-        <v>66950741850</v>
+        <v>52737085483</v>
       </c>
       <c r="D136" t="n">
-        <v>0.4256521352795137</v>
+        <v>0.3898844465082932</v>
       </c>
       <c r="E136" t="n">
         <v>135</v>
@@ -3023,17 +3023,17 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>2020-12-04</t>
+          <t>2020-12-15</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>23614518756</v>
+        <v>20518702233</v>
       </c>
       <c r="C137" t="n">
-        <v>57124426015</v>
+        <v>50712282528</v>
       </c>
       <c r="D137" t="n">
-        <v>0.4133874141649876</v>
+        <v>0.4046101104139991</v>
       </c>
       <c r="E137" t="n">
         <v>136</v>
@@ -3042,17 +3042,17 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>2020-12-07</t>
+          <t>2020-12-16</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>22345056458</v>
+        <v>20098821894</v>
       </c>
       <c r="C138" t="n">
-        <v>56856559648</v>
+        <v>51594471274</v>
       </c>
       <c r="D138" t="n">
-        <v>0.3930075367967857</v>
+        <v>0.3895537912824469</v>
       </c>
       <c r="E138" t="n">
         <v>137</v>
@@ -3061,17 +3061,17 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>2020-12-08</t>
+          <t>2020-12-17</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>20555717183</v>
+        <v>23623180829</v>
       </c>
       <c r="C139" t="n">
-        <v>51665831943</v>
+        <v>60346809075</v>
       </c>
       <c r="D139" t="n">
-        <v>0.3978590184259099</v>
+        <v>0.3914569998165226</v>
       </c>
       <c r="E139" t="n">
         <v>138</v>
@@ -3080,17 +3080,17 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>2020-12-09</t>
+          <t>2020-12-18</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>22167887887</v>
+        <v>24395319589</v>
       </c>
       <c r="C140" t="n">
-        <v>59426788696</v>
+        <v>59011526731</v>
       </c>
       <c r="D140" t="n">
-        <v>0.3730285343265085</v>
+        <v>0.4133992279204094</v>
       </c>
       <c r="E140" t="n">
         <v>139</v>
@@ -3099,17 +3099,17 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>2020-12-10</t>
+          <t>2020-12-21</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>21008686040</v>
+        <v>25669905456</v>
       </c>
       <c r="C141" t="n">
-        <v>53530291688</v>
+        <v>62473191028</v>
       </c>
       <c r="D141" t="n">
-        <v>0.3924635076238444</v>
+        <v>0.410894737944392</v>
       </c>
       <c r="E141" t="n">
         <v>140</v>
@@ -3118,17 +3118,17 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>2020-12-11</t>
+          <t>2020-12-22</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>24084146686</v>
+        <v>27752409533</v>
       </c>
       <c r="C142" t="n">
-        <v>64194443337</v>
+        <v>70592976908</v>
       </c>
       <c r="D142" t="n">
-        <v>0.3751749440300626</v>
+        <v>0.3931327271998773</v>
       </c>
       <c r="E142" t="n">
         <v>141</v>
@@ -3137,17 +3137,17 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>2020-12-14</t>
+          <t>2020-12-23</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>20561369384</v>
+        <v>26781996550</v>
       </c>
       <c r="C143" t="n">
-        <v>52737085483</v>
+        <v>66516491988</v>
       </c>
       <c r="D143" t="n">
-        <v>0.3898844465082932</v>
+        <v>0.4026369363380084</v>
       </c>
       <c r="E143" t="n">
         <v>142</v>
@@ -3156,17 +3156,17 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>2020-12-15</t>
+          <t>2020-12-24</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>20518702233</v>
+        <v>23869444669</v>
       </c>
       <c r="C144" t="n">
-        <v>50712282528</v>
+        <v>63015856260</v>
       </c>
       <c r="D144" t="n">
-        <v>0.4046101104139991</v>
+        <v>0.3787847390427572</v>
       </c>
       <c r="E144" t="n">
         <v>143</v>
@@ -3175,17 +3175,17 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>2020-12-16</t>
+          <t>2020-12-25</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>20098821894</v>
+        <v>25870374333</v>
       </c>
       <c r="C145" t="n">
-        <v>51594471274</v>
+        <v>63035613181</v>
       </c>
       <c r="D145" t="n">
-        <v>0.3895537912824469</v>
+        <v>0.4104088629822002</v>
       </c>
       <c r="E145" t="n">
         <v>144</v>
@@ -3194,17 +3194,17 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>2020-12-17</t>
+          <t>2020-12-28</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>23623180829</v>
+        <v>27591719605</v>
       </c>
       <c r="C146" t="n">
-        <v>60346809075</v>
+        <v>68634054637</v>
       </c>
       <c r="D146" t="n">
-        <v>0.3914569998165226</v>
+        <v>0.4020120878903394</v>
       </c>
       <c r="E146" t="n">
         <v>145</v>
@@ -3213,17 +3213,17 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>2020-12-18</t>
+          <t>2020-12-29</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>24395319589</v>
+        <v>28714767727</v>
       </c>
       <c r="C147" t="n">
-        <v>59011526731</v>
+        <v>68080937199</v>
       </c>
       <c r="D147" t="n">
-        <v>0.4133992279204094</v>
+        <v>0.4217739782733451</v>
       </c>
       <c r="E147" t="n">
         <v>146</v>
@@ -3232,17 +3232,17 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>2020-12-21</t>
+          <t>2020-12-30</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>25669905456</v>
+        <v>27431057672</v>
       </c>
       <c r="C148" t="n">
-        <v>62473191028</v>
+        <v>63970764234</v>
       </c>
       <c r="D148" t="n">
-        <v>0.410894737944392</v>
+        <v>0.4288061585704895</v>
       </c>
       <c r="E148" t="n">
         <v>147</v>
@@ -3251,17 +3251,17 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>2020-12-22</t>
+          <t>2020-12-31</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>27752409533</v>
+        <v>29516497306</v>
       </c>
       <c r="C149" t="n">
-        <v>70592976908</v>
+        <v>70483427194</v>
       </c>
       <c r="D149" t="n">
-        <v>0.3931327271998773</v>
+        <v>0.4187721636287379</v>
       </c>
       <c r="E149" t="n">
         <v>148</v>
@@ -3270,17 +3270,17 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>2020-12-23</t>
+          <t>2021-01-04</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>26781996550</v>
+        <v>32842910849</v>
       </c>
       <c r="C150" t="n">
-        <v>66516491988</v>
+        <v>81262611004</v>
       </c>
       <c r="D150" t="n">
-        <v>0.4026369363380084</v>
+        <v>0.4041577109475767</v>
       </c>
       <c r="E150" t="n">
         <v>149</v>
@@ -3289,17 +3289,17 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>2020-12-24</t>
+          <t>2021-01-05</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>23869444669</v>
+        <v>34955476638</v>
       </c>
       <c r="C151" t="n">
-        <v>63015856260</v>
+        <v>86306603527</v>
       </c>
       <c r="D151" t="n">
-        <v>0.3787847390427572</v>
+        <v>0.4050150881799513</v>
       </c>
       <c r="E151" t="n">
         <v>150</v>
@@ -3308,17 +3308,17 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>2020-12-25</t>
+          <t>2021-01-06</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>25870374333</v>
+        <v>31318863380</v>
       </c>
       <c r="C152" t="n">
-        <v>63035613181</v>
+        <v>79924024318</v>
       </c>
       <c r="D152" t="n">
-        <v>0.4104088629822002</v>
+        <v>0.3918579381762507</v>
       </c>
       <c r="E152" t="n">
         <v>151</v>
@@ -3327,17 +3327,17 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>2020-12-28</t>
+          <t>2021-01-07</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>27591719605</v>
+        <v>34820241307</v>
       </c>
       <c r="C153" t="n">
-        <v>68634054637</v>
+        <v>87045282583</v>
       </c>
       <c r="D153" t="n">
-        <v>0.4020120878903394</v>
+        <v>0.4000244501911746</v>
       </c>
       <c r="E153" t="n">
         <v>152</v>
@@ -3346,17 +3346,17 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>2020-12-29</t>
+          <t>2021-01-08</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>28714767727</v>
+        <v>31741361539</v>
       </c>
       <c r="C154" t="n">
-        <v>68080937199</v>
+        <v>76243328872</v>
       </c>
       <c r="D154" t="n">
-        <v>0.4217739782733451</v>
+        <v>0.4163165749529185</v>
       </c>
       <c r="E154" t="n">
         <v>153</v>
@@ -3365,17 +3365,17 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>2020-12-30</t>
+          <t>2021-01-11</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>27431057672</v>
+        <v>33861909952</v>
       </c>
       <c r="C155" t="n">
-        <v>63970764234</v>
+        <v>79843929989</v>
       </c>
       <c r="D155" t="n">
-        <v>0.4288061585704895</v>
+        <v>0.4241012429706943</v>
       </c>
       <c r="E155" t="n">
         <v>154</v>
@@ -3384,17 +3384,17 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>2020-12-31</t>
+          <t>2021-01-12</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>29516497306</v>
+        <v>31336739617</v>
       </c>
       <c r="C156" t="n">
-        <v>70483427194</v>
+        <v>70684174141</v>
       </c>
       <c r="D156" t="n">
-        <v>0.4187721636287379</v>
+        <v>0.4433345936035105</v>
       </c>
       <c r="E156" t="n">
         <v>155</v>
@@ -3403,17 +3403,17 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>2021-01-04</t>
+          <t>2021-01-13</t>
         </is>
       </c>
       <c r="B157" t="n">
-        <v>32842910849</v>
+        <v>36176556832</v>
       </c>
       <c r="C157" t="n">
-        <v>81262611004</v>
+        <v>81782457644</v>
       </c>
       <c r="D157" t="n">
-        <v>0.4041577109475767</v>
+        <v>0.4423510600461162</v>
       </c>
       <c r="E157" t="n">
         <v>156</v>
@@ -3422,17 +3422,17 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>2021-01-05</t>
+          <t>2021-01-14</t>
         </is>
       </c>
       <c r="B158" t="n">
-        <v>34955476638</v>
+        <v>32971296424</v>
       </c>
       <c r="C158" t="n">
-        <v>86306603527</v>
+        <v>74034016193</v>
       </c>
       <c r="D158" t="n">
-        <v>0.4050150881799513</v>
+        <v>0.4453533405245341</v>
       </c>
       <c r="E158" t="n">
         <v>157</v>
@@ -3441,17 +3441,17 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>2021-01-06</t>
+          <t>2021-01-15</t>
         </is>
       </c>
       <c r="B159" t="n">
-        <v>31318863380</v>
+        <v>31268748151</v>
       </c>
       <c r="C159" t="n">
-        <v>79924024318</v>
+        <v>68522530970</v>
       </c>
       <c r="D159" t="n">
-        <v>0.3918579381762507</v>
+        <v>0.4563279801309417</v>
       </c>
       <c r="E159" t="n">
         <v>158</v>
@@ -3460,17 +3460,17 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>2021-01-07</t>
+          <t>2021-01-18</t>
         </is>
       </c>
       <c r="B160" t="n">
-        <v>34820241307</v>
+        <v>28025154838</v>
       </c>
       <c r="C160" t="n">
-        <v>87045282583</v>
+        <v>66132336803</v>
       </c>
       <c r="D160" t="n">
-        <v>0.4000244501911746</v>
+        <v>0.4237738479056539</v>
       </c>
       <c r="E160" t="n">
         <v>159</v>
@@ -3479,17 +3479,17 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>2021-01-08</t>
+          <t>2021-01-19</t>
         </is>
       </c>
       <c r="B161" t="n">
-        <v>31741361539</v>
+        <v>30160755219</v>
       </c>
       <c r="C161" t="n">
-        <v>76243328872</v>
+        <v>71588657610</v>
       </c>
       <c r="D161" t="n">
-        <v>0.4163165749529185</v>
+        <v>0.4213063385447102</v>
       </c>
       <c r="E161" t="n">
         <v>160</v>
@@ -3498,17 +3498,17 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>2021-01-11</t>
+          <t>2021-01-20</t>
         </is>
       </c>
       <c r="B162" t="n">
-        <v>33861909952</v>
+        <v>25498108632</v>
       </c>
       <c r="C162" t="n">
-        <v>79843929989</v>
+        <v>61023142374</v>
       </c>
       <c r="D162" t="n">
-        <v>0.4241012429706943</v>
+        <v>0.4178432581483041</v>
       </c>
       <c r="E162" t="n">
         <v>161</v>
@@ -3517,17 +3517,17 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>2021-01-12</t>
+          <t>2021-01-21</t>
         </is>
       </c>
       <c r="B163" t="n">
-        <v>31336739617</v>
+        <v>31550851527</v>
       </c>
       <c r="C163" t="n">
-        <v>70684174141</v>
+        <v>73606094304</v>
       </c>
       <c r="D163" t="n">
-        <v>0.4433345936035105</v>
+        <v>0.4286445548474839</v>
       </c>
       <c r="E163" t="n">
         <v>162</v>
@@ -3536,17 +3536,17 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>2021-01-13</t>
+          <t>2021-01-22</t>
         </is>
       </c>
       <c r="B164" t="n">
-        <v>36176556832</v>
+        <v>29587073243</v>
       </c>
       <c r="C164" t="n">
-        <v>81782457644</v>
+        <v>71863919964</v>
       </c>
       <c r="D164" t="n">
-        <v>0.4423510600461162</v>
+        <v>0.4117097043665521</v>
       </c>
       <c r="E164" t="n">
         <v>163</v>
@@ -3555,17 +3555,17 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>2021-01-14</t>
+          <t>2021-01-25</t>
         </is>
       </c>
       <c r="B165" t="n">
-        <v>32971296424</v>
+        <v>29768085597</v>
       </c>
       <c r="C165" t="n">
-        <v>74034016193</v>
+        <v>72841620023</v>
       </c>
       <c r="D165" t="n">
-        <v>0.4453533405245341</v>
+        <v>0.4086686373477226</v>
       </c>
       <c r="E165" t="n">
         <v>164</v>
@@ -3574,17 +3574,17 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>2021-01-15</t>
+          <t>2021-01-26</t>
         </is>
       </c>
       <c r="B166" t="n">
-        <v>31268748151</v>
+        <v>25588114580</v>
       </c>
       <c r="C166" t="n">
-        <v>68522530970</v>
+        <v>62625061804</v>
       </c>
       <c r="D166" t="n">
-        <v>0.4563279801309417</v>
+        <v>0.4085922447483418</v>
       </c>
       <c r="E166" t="n">
         <v>165</v>
@@ -3593,17 +3593,17 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>2021-01-18</t>
+          <t>2021-01-27</t>
         </is>
       </c>
       <c r="B167" t="n">
-        <v>28025154838</v>
+        <v>25604690493</v>
       </c>
       <c r="C167" t="n">
-        <v>66132336803</v>
+        <v>60015878129</v>
       </c>
       <c r="D167" t="n">
-        <v>0.4237738479056539</v>
+        <v>0.4266319396004584</v>
       </c>
       <c r="E167" t="n">
         <v>166</v>
@@ -3612,17 +3612,17 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>2021-01-19</t>
+          <t>2021-01-28</t>
         </is>
       </c>
       <c r="B168" t="n">
-        <v>30160755219</v>
+        <v>26286085867</v>
       </c>
       <c r="C168" t="n">
-        <v>71588657610</v>
+        <v>62311898539</v>
       </c>
       <c r="D168" t="n">
-        <v>0.4213063385447102</v>
+        <v>0.4218469743872106</v>
       </c>
       <c r="E168" t="n">
         <v>167</v>
@@ -3631,17 +3631,17 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>2021-01-20</t>
+          <t>2021-01-29</t>
         </is>
       </c>
       <c r="B169" t="n">
-        <v>25498108632</v>
+        <v>27002904913</v>
       </c>
       <c r="C169" t="n">
-        <v>61023142374</v>
+        <v>66018503681</v>
       </c>
       <c r="D169" t="n">
-        <v>0.4178432581483041</v>
+        <v>0.4090202504963981</v>
       </c>
       <c r="E169" t="n">
         <v>168</v>
@@ -3650,17 +3650,17 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>2021-01-21</t>
+          <t>2021-02-01</t>
         </is>
       </c>
       <c r="B170" t="n">
-        <v>31550851527</v>
+        <v>25457673045</v>
       </c>
       <c r="C170" t="n">
-        <v>73606094304</v>
+        <v>61214730247</v>
       </c>
       <c r="D170" t="n">
-        <v>0.4286445548474839</v>
+        <v>0.4158749526834291</v>
       </c>
       <c r="E170" t="n">
         <v>169</v>
@@ -3669,17 +3669,17 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>2021-01-22</t>
+          <t>2021-02-02</t>
         </is>
       </c>
       <c r="B171" t="n">
-        <v>29587073243</v>
+        <v>24585679056</v>
       </c>
       <c r="C171" t="n">
-        <v>71863919964</v>
+        <v>59083806830</v>
       </c>
       <c r="D171" t="n">
-        <v>0.4117097043665521</v>
+        <v>0.4161153516519274</v>
       </c>
       <c r="E171" t="n">
         <v>170</v>
@@ -3688,17 +3688,17 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>2021-01-25</t>
+          <t>2021-02-03</t>
         </is>
       </c>
       <c r="B172" t="n">
-        <v>29768085597</v>
+        <v>27946762653</v>
       </c>
       <c r="C172" t="n">
-        <v>72841620023</v>
+        <v>64252239936</v>
       </c>
       <c r="D172" t="n">
-        <v>0.4086686373477226</v>
+        <v>0.4349539048107436</v>
       </c>
       <c r="E172" t="n">
         <v>171</v>
@@ -3707,17 +3707,17 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>2021-01-26</t>
+          <t>2021-02-04</t>
         </is>
       </c>
       <c r="B173" t="n">
-        <v>25588114580</v>
+        <v>26745949814</v>
       </c>
       <c r="C173" t="n">
-        <v>62625061804</v>
+        <v>65026335158</v>
       </c>
       <c r="D173" t="n">
-        <v>0.4085922447483418</v>
+        <v>0.411309506356357</v>
       </c>
       <c r="E173" t="n">
         <v>172</v>
@@ -3726,17 +3726,17 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>2021-01-27</t>
+          <t>2021-02-05</t>
         </is>
       </c>
       <c r="B174" t="n">
-        <v>25604690493</v>
+        <v>27228530445</v>
       </c>
       <c r="C174" t="n">
-        <v>60015878129</v>
+        <v>60817228192</v>
       </c>
       <c r="D174" t="n">
-        <v>0.4266319396004584</v>
+        <v>0.44771080916479</v>
       </c>
       <c r="E174" t="n">
         <v>173</v>
@@ -3745,17 +3745,17 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>2021-01-28</t>
+          <t>2021-02-08</t>
         </is>
       </c>
       <c r="B175" t="n">
-        <v>26286085867</v>
+        <v>22845413099</v>
       </c>
       <c r="C175" t="n">
-        <v>62311898539</v>
+        <v>53099229697</v>
       </c>
       <c r="D175" t="n">
-        <v>0.4218469743872106</v>
+        <v>0.4302400096830542</v>
       </c>
       <c r="E175" t="n">
         <v>174</v>
@@ -3764,17 +3764,17 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>2021-01-29</t>
+          <t>2021-02-09</t>
         </is>
       </c>
       <c r="B176" t="n">
-        <v>27002904913</v>
+        <v>23052987297</v>
       </c>
       <c r="C176" t="n">
-        <v>66018503681</v>
+        <v>54414450658</v>
       </c>
       <c r="D176" t="n">
-        <v>0.4090202504963981</v>
+        <v>0.4236556101960896</v>
       </c>
       <c r="E176" t="n">
         <v>175</v>
@@ -3783,17 +3783,17 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>2021-02-01</t>
+          <t>2021-02-10</t>
         </is>
       </c>
       <c r="B177" t="n">
-        <v>25457673045</v>
+        <v>23672043794</v>
       </c>
       <c r="C177" t="n">
-        <v>61214730247</v>
+        <v>53724833418</v>
       </c>
       <c r="D177" t="n">
-        <v>0.4158749526834291</v>
+        <v>0.4406164205260971</v>
       </c>
       <c r="E177" t="n">
         <v>176</v>
@@ -3802,17 +3802,17 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>2021-02-02</t>
+          <t>2021-02-18</t>
         </is>
       </c>
       <c r="B178" t="n">
-        <v>24585679056</v>
+        <v>30305438799</v>
       </c>
       <c r="C178" t="n">
-        <v>59083806830</v>
+        <v>70581483088</v>
       </c>
       <c r="D178" t="n">
-        <v>0.4161153516519274</v>
+        <v>0.4293681213982937</v>
       </c>
       <c r="E178" t="n">
         <v>177</v>
@@ -3821,17 +3821,17 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>2021-02-03</t>
+          <t>2021-02-19</t>
         </is>
       </c>
       <c r="B179" t="n">
-        <v>27946762653</v>
+        <v>31871390359</v>
       </c>
       <c r="C179" t="n">
-        <v>64252239936</v>
+        <v>74891926971</v>
       </c>
       <c r="D179" t="n">
-        <v>0.4349539048107436</v>
+        <v>0.4255650995779744</v>
       </c>
       <c r="E179" t="n">
         <v>178</v>
@@ -3840,17 +3840,17 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>2021-02-04</t>
+          <t>2021-02-22</t>
         </is>
       </c>
       <c r="B180" t="n">
-        <v>26745949814</v>
+        <v>41800730539</v>
       </c>
       <c r="C180" t="n">
-        <v>65026335158</v>
+        <v>98345390597</v>
       </c>
       <c r="D180" t="n">
-        <v>0.411309506356357</v>
+        <v>0.4250400581588124</v>
       </c>
       <c r="E180" t="n">
         <v>179</v>
@@ -3859,17 +3859,17 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>2021-02-05</t>
+          <t>2021-02-23</t>
         </is>
       </c>
       <c r="B181" t="n">
-        <v>27228530445</v>
+        <v>36659765914</v>
       </c>
       <c r="C181" t="n">
-        <v>60817228192</v>
+        <v>79667225639</v>
       </c>
       <c r="D181" t="n">
-        <v>0.44771080916479</v>
+        <v>0.4601611970287279</v>
       </c>
       <c r="E181" t="n">
         <v>180</v>
@@ -3878,17 +3878,17 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>2021-02-08</t>
+          <t>2021-02-24</t>
         </is>
       </c>
       <c r="B182" t="n">
-        <v>22845413099</v>
+        <v>33328852498</v>
       </c>
       <c r="C182" t="n">
-        <v>53099229697</v>
+        <v>74974298826</v>
       </c>
       <c r="D182" t="n">
-        <v>0.4302400096830542</v>
+        <v>0.4445370349557979</v>
       </c>
       <c r="E182" t="n">
         <v>181</v>
@@ -3897,17 +3897,17 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>2021-02-09</t>
+          <t>2021-02-25</t>
         </is>
       </c>
       <c r="B183" t="n">
-        <v>23052987297</v>
+        <v>33009105938</v>
       </c>
       <c r="C183" t="n">
-        <v>54414450658</v>
+        <v>72321851390</v>
       </c>
       <c r="D183" t="n">
-        <v>0.4236556101960896</v>
+        <v>0.4564195371603028</v>
       </c>
       <c r="E183" t="n">
         <v>182</v>
@@ -3916,17 +3916,17 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>2021-02-10</t>
+          <t>2021-02-26</t>
         </is>
       </c>
       <c r="B184" t="n">
-        <v>23672043794</v>
+        <v>29437488128</v>
       </c>
       <c r="C184" t="n">
-        <v>53724833418</v>
+        <v>67566280430</v>
       </c>
       <c r="D184" t="n">
-        <v>0.4406164205260971</v>
+        <v>0.4356831238993216</v>
       </c>
       <c r="E184" t="n">
         <v>183</v>
@@ -3935,17 +3935,17 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>2021-02-18</t>
+          <t>2021-03-01</t>
         </is>
       </c>
       <c r="B185" t="n">
-        <v>30305438799</v>
+        <v>28022529242</v>
       </c>
       <c r="C185" t="n">
-        <v>70581483088</v>
+        <v>65847760652</v>
       </c>
       <c r="D185" t="n">
-        <v>0.4293681213982937</v>
+        <v>0.425565409734991</v>
       </c>
       <c r="E185" t="n">
         <v>184</v>
@@ -3954,17 +3954,17 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>2021-02-19</t>
+          <t>2021-03-02</t>
         </is>
       </c>
       <c r="B186" t="n">
-        <v>31871390359</v>
+        <v>30548474585</v>
       </c>
       <c r="C186" t="n">
-        <v>74891926971</v>
+        <v>69441386639</v>
       </c>
       <c r="D186" t="n">
-        <v>0.4255650995779744</v>
+        <v>0.4399174046424243</v>
       </c>
       <c r="E186" t="n">
         <v>185</v>
@@ -3973,17 +3973,17 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>2021-02-22</t>
+          <t>2021-03-03</t>
         </is>
       </c>
       <c r="B187" t="n">
-        <v>41800730539</v>
+        <v>31581683271</v>
       </c>
       <c r="C187" t="n">
-        <v>98345390597</v>
+        <v>69999474895</v>
       </c>
       <c r="D187" t="n">
-        <v>0.4250400581588124</v>
+        <v>0.4511702883253464</v>
       </c>
       <c r="E187" t="n">
         <v>186</v>
@@ -3992,17 +3992,17 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>2021-02-23</t>
+          <t>2021-03-04</t>
         </is>
       </c>
       <c r="B188" t="n">
-        <v>36659765914</v>
+        <v>36100282673</v>
       </c>
       <c r="C188" t="n">
-        <v>79667225639</v>
+        <v>78562142790</v>
       </c>
       <c r="D188" t="n">
-        <v>0.4601611970287279</v>
+        <v>0.4595124495203449</v>
       </c>
       <c r="E188" t="n">
         <v>187</v>
@@ -4011,17 +4011,17 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>2021-02-24</t>
+          <t>2021-03-05</t>
         </is>
       </c>
       <c r="B189" t="n">
-        <v>33328852498</v>
+        <v>32337135967</v>
       </c>
       <c r="C189" t="n">
-        <v>74974298826</v>
+        <v>73514786011</v>
       </c>
       <c r="D189" t="n">
-        <v>0.4445370349557979</v>
+        <v>0.4398725443091326</v>
       </c>
       <c r="E189" t="n">
         <v>188</v>
@@ -4030,17 +4030,17 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>2021-02-25</t>
+          <t>2021-03-08</t>
         </is>
       </c>
       <c r="B190" t="n">
-        <v>33009105938</v>
+        <v>34237890063</v>
       </c>
       <c r="C190" t="n">
-        <v>72321851390</v>
+        <v>78814375242</v>
       </c>
       <c r="D190" t="n">
-        <v>0.4564195371603028</v>
+        <v>0.4344117422471771</v>
       </c>
       <c r="E190" t="n">
         <v>189</v>
@@ -4049,17 +4049,17 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>2021-02-26</t>
+          <t>2021-03-09</t>
         </is>
       </c>
       <c r="B191" t="n">
-        <v>29437488128</v>
+        <v>35838361211</v>
       </c>
       <c r="C191" t="n">
-        <v>67566280430</v>
+        <v>82850202998</v>
       </c>
       <c r="D191" t="n">
-        <v>0.4356831238993216</v>
+        <v>0.4325681762284292</v>
       </c>
       <c r="E191" t="n">
         <v>190</v>
@@ -4068,17 +4068,17 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>2021-03-01</t>
+          <t>2021-03-10</t>
         </is>
       </c>
       <c r="B192" t="n">
-        <v>28022529242</v>
+        <v>26975456721</v>
       </c>
       <c r="C192" t="n">
-        <v>65847760652</v>
+        <v>62127335207</v>
       </c>
       <c r="D192" t="n">
-        <v>0.425565409734991</v>
+        <v>0.4341962620981791</v>
       </c>
       <c r="E192" t="n">
         <v>191</v>
@@ -4087,17 +4087,17 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>2021-03-02</t>
+          <t>2021-03-11</t>
         </is>
       </c>
       <c r="B193" t="n">
-        <v>30548474585</v>
+        <v>30680047969</v>
       </c>
       <c r="C193" t="n">
-        <v>69441386639</v>
+        <v>66598157167</v>
       </c>
       <c r="D193" t="n">
-        <v>0.4399174046424243</v>
+        <v>0.4606741278451207</v>
       </c>
       <c r="E193" t="n">
         <v>192</v>
@@ -4106,17 +4106,17 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>2021-03-03</t>
+          <t>2021-03-12</t>
         </is>
       </c>
       <c r="B194" t="n">
-        <v>31581683271</v>
+        <v>33862968625</v>
       </c>
       <c r="C194" t="n">
-        <v>69999474895</v>
+        <v>72238010975</v>
       </c>
       <c r="D194" t="n">
-        <v>0.4511702883253464</v>
+        <v>0.4687693939513262</v>
       </c>
       <c r="E194" t="n">
         <v>193</v>
@@ -4125,17 +4125,17 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>2021-03-04</t>
+          <t>2021-03-15</t>
         </is>
       </c>
       <c r="B195" t="n">
-        <v>36100282673</v>
+        <v>34591765793</v>
       </c>
       <c r="C195" t="n">
-        <v>78562142790</v>
+        <v>71723136959</v>
       </c>
       <c r="D195" t="n">
-        <v>0.4595124495203449</v>
+        <v>0.4822957731585852</v>
       </c>
       <c r="E195" t="n">
         <v>194</v>
@@ -4144,17 +4144,17 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>2021-03-05</t>
+          <t>2021-03-16</t>
         </is>
       </c>
       <c r="B196" t="n">
-        <v>32337135967</v>
+        <v>29977825317</v>
       </c>
       <c r="C196" t="n">
-        <v>73514786011</v>
+        <v>67049266583</v>
       </c>
       <c r="D196" t="n">
-        <v>0.4398725443091326</v>
+        <v>0.447101465008429</v>
       </c>
       <c r="E196" t="n">
         <v>195</v>
@@ -4163,17 +4163,17 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>2021-03-08</t>
+          <t>2021-03-17</t>
         </is>
       </c>
       <c r="B197" t="n">
-        <v>34237890063</v>
+        <v>27491185060</v>
       </c>
       <c r="C197" t="n">
-        <v>78814375242</v>
+        <v>62515062852</v>
       </c>
       <c r="D197" t="n">
-        <v>0.4344117422471771</v>
+        <v>0.4397529780156095</v>
       </c>
       <c r="E197" t="n">
         <v>196</v>
@@ -4182,17 +4182,17 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>2021-03-09</t>
+          <t>2021-03-18</t>
         </is>
       </c>
       <c r="B198" t="n">
-        <v>35838361211</v>
+        <v>26739276351</v>
       </c>
       <c r="C198" t="n">
-        <v>82850202998</v>
+        <v>62832911819</v>
       </c>
       <c r="D198" t="n">
-        <v>0.4325681762284292</v>
+        <v>0.4255616296762858</v>
       </c>
       <c r="E198" t="n">
         <v>197</v>
@@ -4201,17 +4201,17 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>2021-03-10</t>
+          <t>2021-03-19</t>
         </is>
       </c>
       <c r="B199" t="n">
-        <v>26975456721</v>
+        <v>28358235249</v>
       </c>
       <c r="C199" t="n">
-        <v>62127335207</v>
+        <v>65875538395</v>
       </c>
       <c r="D199" t="n">
-        <v>0.4341962620981791</v>
+        <v>0.4304820262562349</v>
       </c>
       <c r="E199" t="n">
         <v>198</v>
@@ -4220,17 +4220,17 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>2021-03-11</t>
+          <t>2021-03-22</t>
         </is>
       </c>
       <c r="B200" t="n">
-        <v>30680047969</v>
+        <v>29121013208</v>
       </c>
       <c r="C200" t="n">
-        <v>66598157167</v>
+        <v>67358226346</v>
       </c>
       <c r="D200" t="n">
-        <v>0.4606741278451207</v>
+        <v>0.4323304633707791</v>
       </c>
       <c r="E200" t="n">
         <v>199</v>
@@ -4239,17 +4239,17 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>2021-03-12</t>
+          <t>2021-03-23</t>
         </is>
       </c>
       <c r="B201" t="n">
-        <v>33862968625</v>
+        <v>29320271653</v>
       </c>
       <c r="C201" t="n">
-        <v>72238010975</v>
+        <v>70323191299</v>
       </c>
       <c r="D201" t="n">
-        <v>0.4687693939513262</v>
+        <v>0.4169360222623591</v>
       </c>
       <c r="E201" t="n">
         <v>200</v>
@@ -4258,17 +4258,17 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>2021-03-15</t>
+          <t>2021-03-24</t>
         </is>
       </c>
       <c r="B202" t="n">
-        <v>34591765793</v>
+        <v>28494202046</v>
       </c>
       <c r="C202" t="n">
-        <v>71723136959</v>
+        <v>67303523996</v>
       </c>
       <c r="D202" t="n">
-        <v>0.4822957731585852</v>
+        <v>0.423368649280437</v>
       </c>
       <c r="E202" t="n">
         <v>201</v>
@@ -4277,17 +4277,17 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>2021-03-16</t>
+          <t>2021-03-25</t>
         </is>
       </c>
       <c r="B203" t="n">
-        <v>29977825317</v>
+        <v>25857769578</v>
       </c>
       <c r="C203" t="n">
-        <v>67049266583</v>
+        <v>60650502617</v>
       </c>
       <c r="D203" t="n">
-        <v>0.447101465008429</v>
+        <v>0.426340565407816</v>
       </c>
       <c r="E203" t="n">
         <v>202</v>
@@ -4296,17 +4296,17 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>2021-03-17</t>
+          <t>2021-03-26</t>
         </is>
       </c>
       <c r="B204" t="n">
-        <v>27491185060</v>
+        <v>25857588064</v>
       </c>
       <c r="C204" t="n">
-        <v>62515062852</v>
+        <v>61284664475</v>
       </c>
       <c r="D204" t="n">
-        <v>0.4397529780156095</v>
+        <v>0.4219259138564452</v>
       </c>
       <c r="E204" t="n">
         <v>203</v>
@@ -4315,17 +4315,17 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>2021-03-18</t>
+          <t>2021-03-29</t>
         </is>
       </c>
       <c r="B205" t="n">
-        <v>26739276351</v>
+        <v>26030305012</v>
       </c>
       <c r="C205" t="n">
-        <v>62832911819</v>
+        <v>62965892538</v>
       </c>
       <c r="D205" t="n">
-        <v>0.4255616296762858</v>
+        <v>0.4134032563151658</v>
       </c>
       <c r="E205" t="n">
         <v>204</v>
@@ -4334,17 +4334,17 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>2021-03-19</t>
+          <t>2021-03-30</t>
         </is>
       </c>
       <c r="B206" t="n">
-        <v>28358235249</v>
+        <v>25780001010</v>
       </c>
       <c r="C206" t="n">
-        <v>65875538395</v>
+        <v>62868502600</v>
       </c>
       <c r="D206" t="n">
-        <v>0.4304820262562349</v>
+        <v>0.4100622719460158</v>
       </c>
       <c r="E206" t="n">
         <v>205</v>
@@ -4353,17 +4353,17 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>2021-03-22</t>
+          <t>2021-03-31</t>
         </is>
       </c>
       <c r="B207" t="n">
-        <v>29121013208</v>
+        <v>25340940136</v>
       </c>
       <c r="C207" t="n">
-        <v>67358226346</v>
+        <v>58944651908</v>
       </c>
       <c r="D207" t="n">
-        <v>0.4323304633707791</v>
+        <v>0.4299107606157687</v>
       </c>
       <c r="E207" t="n">
         <v>206</v>
@@ -4372,17 +4372,17 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>2021-03-23</t>
+          <t>2021-04-01</t>
         </is>
       </c>
       <c r="B208" t="n">
-        <v>29320271653</v>
+        <v>24459982838</v>
       </c>
       <c r="C208" t="n">
-        <v>70323191299</v>
+        <v>57742915146</v>
       </c>
       <c r="D208" t="n">
-        <v>0.4169360222623591</v>
+        <v>0.4236014544148696</v>
       </c>
       <c r="E208" t="n">
         <v>207</v>
@@ -4391,17 +4391,17 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>2021-03-24</t>
+          <t>2021-04-02</t>
         </is>
       </c>
       <c r="B209" t="n">
-        <v>28494202046</v>
+        <v>23776468616</v>
       </c>
       <c r="C209" t="n">
-        <v>67303523996</v>
+        <v>57637646459</v>
       </c>
       <c r="D209" t="n">
-        <v>0.423368649280437</v>
+        <v>0.4125162992717471</v>
       </c>
       <c r="E209" t="n">
         <v>208</v>
@@ -4410,17 +4410,17 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>2021-03-25</t>
+          <t>2021-04-06</t>
         </is>
       </c>
       <c r="B210" t="n">
-        <v>25857769578</v>
+        <v>21609152872</v>
       </c>
       <c r="C210" t="n">
-        <v>60650502617</v>
+        <v>54009467026</v>
       </c>
       <c r="D210" t="n">
-        <v>0.426340565407816</v>
+        <v>0.4000993540928189</v>
       </c>
       <c r="E210" t="n">
         <v>209</v>
@@ -4429,17 +4429,17 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>2021-03-26</t>
+          <t>2021-04-07</t>
         </is>
       </c>
       <c r="B211" t="n">
-        <v>25857588064</v>
+        <v>28192988226</v>
       </c>
       <c r="C211" t="n">
-        <v>61284664475</v>
+        <v>64777711487</v>
       </c>
       <c r="D211" t="n">
-        <v>0.4219259138564452</v>
+        <v>0.4352266787266473</v>
       </c>
       <c r="E211" t="n">
         <v>210</v>
@@ -4448,17 +4448,17 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>2021-03-29</t>
+          <t>2021-04-08</t>
         </is>
       </c>
       <c r="B212" t="n">
-        <v>26030305012</v>
+        <v>31610774016</v>
       </c>
       <c r="C212" t="n">
-        <v>62965892538</v>
+        <v>70183037971</v>
       </c>
       <c r="D212" t="n">
-        <v>0.4134032563151658</v>
+        <v>0.4504047549076137</v>
       </c>
       <c r="E212" t="n">
         <v>211</v>
@@ -4467,17 +4467,17 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>2021-03-30</t>
+          <t>2021-04-09</t>
         </is>
       </c>
       <c r="B213" t="n">
-        <v>25780001010</v>
+        <v>27363203695</v>
       </c>
       <c r="C213" t="n">
-        <v>62868502600</v>
+        <v>60908586933</v>
       </c>
       <c r="D213" t="n">
-        <v>0.4100622719460158</v>
+        <v>0.4492503450309851</v>
       </c>
       <c r="E213" t="n">
         <v>212</v>
@@ -4486,17 +4486,17 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>2021-03-31</t>
+          <t>2021-04-12</t>
         </is>
       </c>
       <c r="B214" t="n">
-        <v>25340940136</v>
+        <v>29441281600</v>
       </c>
       <c r="C214" t="n">
-        <v>58944651908</v>
+        <v>66662877908</v>
       </c>
       <c r="D214" t="n">
-        <v>0.4299107606157687</v>
+        <v>0.4416443232563598</v>
       </c>
       <c r="E214" t="n">
         <v>213</v>
@@ -4505,17 +4505,17 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>2021-04-01</t>
+          <t>2021-04-13</t>
         </is>
       </c>
       <c r="B215" t="n">
-        <v>24459982838</v>
+        <v>26500289609</v>
       </c>
       <c r="C215" t="n">
-        <v>57742915146</v>
+        <v>60099497250</v>
       </c>
       <c r="D215" t="n">
-        <v>0.4236014544148696</v>
+        <v>0.4409402877159675</v>
       </c>
       <c r="E215" t="n">
         <v>214</v>
@@ -4524,17 +4524,17 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>2021-04-02</t>
+          <t>2021-04-14</t>
         </is>
       </c>
       <c r="B216" t="n">
-        <v>23776468616</v>
+        <v>24875678254</v>
       </c>
       <c r="C216" t="n">
-        <v>57637646459</v>
+        <v>56149660115</v>
       </c>
       <c r="D216" t="n">
-        <v>0.4125162992717471</v>
+        <v>0.4430245562137362</v>
       </c>
       <c r="E216" t="n">
         <v>215</v>
@@ -4543,17 +4543,17 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>2021-04-06</t>
+          <t>2021-04-15</t>
         </is>
       </c>
       <c r="B217" t="n">
-        <v>21609152872</v>
+        <v>23587218127</v>
       </c>
       <c r="C217" t="n">
-        <v>54009467026</v>
+        <v>56730832399</v>
       </c>
       <c r="D217" t="n">
-        <v>0.4000993540928189</v>
+        <v>0.4157742294543835</v>
       </c>
       <c r="E217" t="n">
         <v>216</v>
@@ -4562,17 +4562,17 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>2021-04-07</t>
+          <t>2021-04-16</t>
         </is>
       </c>
       <c r="B218" t="n">
-        <v>28192988226</v>
+        <v>23064238930</v>
       </c>
       <c r="C218" t="n">
-        <v>64777711487</v>
+        <v>60757105467</v>
       </c>
       <c r="D218" t="n">
-        <v>0.4352266787266473</v>
+        <v>0.3796138534368998</v>
       </c>
       <c r="E218" t="n">
         <v>217</v>
@@ -4581,17 +4581,17 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>2021-04-08</t>
+          <t>2021-04-19</t>
         </is>
       </c>
       <c r="B219" t="n">
-        <v>31610774016</v>
+        <v>26349229565</v>
       </c>
       <c r="C219" t="n">
-        <v>70183037971</v>
+        <v>68717257011</v>
       </c>
       <c r="D219" t="n">
-        <v>0.4504047549076137</v>
+        <v>0.3834441406877186</v>
       </c>
       <c r="E219" t="n">
         <v>218</v>
@@ -4600,17 +4600,17 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>2021-04-09</t>
+          <t>2021-04-20</t>
         </is>
       </c>
       <c r="B220" t="n">
-        <v>27363203695</v>
+        <v>26332452757</v>
       </c>
       <c r="C220" t="n">
-        <v>60908586933</v>
+        <v>66152179163</v>
       </c>
       <c r="D220" t="n">
-        <v>0.4492503450309851</v>
+        <v>0.3980587350284626</v>
       </c>
       <c r="E220" t="n">
         <v>219</v>
@@ -4619,17 +4619,17 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>2021-04-12</t>
+          <t>2021-04-21</t>
         </is>
       </c>
       <c r="B221" t="n">
-        <v>29441281600</v>
+        <v>23796108657</v>
       </c>
       <c r="C221" t="n">
-        <v>66662877908</v>
+        <v>58645267418</v>
       </c>
       <c r="D221" t="n">
-        <v>0.4416443232563598</v>
+        <v>0.4057634947316526</v>
       </c>
       <c r="E221" t="n">
         <v>220</v>
@@ -4638,17 +4638,17 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>2021-04-13</t>
+          <t>2021-04-22</t>
         </is>
       </c>
       <c r="B222" t="n">
-        <v>26500289609</v>
+        <v>23283868400</v>
       </c>
       <c r="C222" t="n">
-        <v>60099497250</v>
+        <v>57343158813</v>
       </c>
       <c r="D222" t="n">
-        <v>0.4409402877159675</v>
+        <v>0.406044398006226</v>
       </c>
       <c r="E222" t="n">
         <v>221</v>
@@ -4657,17 +4657,17 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>2021-04-14</t>
+          <t>2021-04-23</t>
         </is>
       </c>
       <c r="B223" t="n">
-        <v>24875678254</v>
+        <v>23110619160</v>
       </c>
       <c r="C223" t="n">
-        <v>56149660115</v>
+        <v>58758936747</v>
       </c>
       <c r="D223" t="n">
-        <v>0.4430245562137362</v>
+        <v>0.3933124123655954</v>
       </c>
       <c r="E223" t="n">
         <v>222</v>
@@ -4676,17 +4676,17 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>2021-04-15</t>
+          <t>2021-04-26</t>
         </is>
       </c>
       <c r="B224" t="n">
-        <v>23587218127</v>
+        <v>26080656908</v>
       </c>
       <c r="C224" t="n">
-        <v>56730832399</v>
+        <v>64990659217</v>
       </c>
       <c r="D224" t="n">
-        <v>0.4157742294543835</v>
+        <v>0.4012985438556365</v>
       </c>
       <c r="E224" t="n">
         <v>223</v>
@@ -4695,17 +4695,17 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>2021-04-16</t>
+          <t>2021-04-27</t>
         </is>
       </c>
       <c r="B225" t="n">
-        <v>23064238930</v>
+        <v>22805398723</v>
       </c>
       <c r="C225" t="n">
-        <v>60757105467</v>
+        <v>58465572266</v>
       </c>
       <c r="D225" t="n">
-        <v>0.3796138534368998</v>
+        <v>0.3900654323409783</v>
       </c>
       <c r="E225" t="n">
         <v>224</v>
@@ -4714,17 +4714,17 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>2021-04-19</t>
+          <t>2021-04-28</t>
         </is>
       </c>
       <c r="B226" t="n">
-        <v>26349229565</v>
+        <v>21764975470</v>
       </c>
       <c r="C226" t="n">
-        <v>68717257011</v>
+        <v>56258757783</v>
       </c>
       <c r="D226" t="n">
-        <v>0.3834441406877186</v>
+        <v>0.3868726635229197</v>
       </c>
       <c r="E226" t="n">
         <v>225</v>
@@ -4733,17 +4733,17 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>2021-04-20</t>
+          <t>2021-04-29</t>
         </is>
       </c>
       <c r="B227" t="n">
-        <v>26332452757</v>
+        <v>23871290845</v>
       </c>
       <c r="C227" t="n">
-        <v>66152179163</v>
+        <v>59672070298</v>
       </c>
       <c r="D227" t="n">
-        <v>0.3980587350284626</v>
+        <v>0.400041270996426</v>
       </c>
       <c r="E227" t="n">
         <v>226</v>
@@ -4752,17 +4752,17 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>2021-04-21</t>
+          <t>2021-04-30</t>
         </is>
       </c>
       <c r="B228" t="n">
-        <v>23796108657</v>
+        <v>26727927563</v>
       </c>
       <c r="C228" t="n">
-        <v>58645267418</v>
+        <v>64623812735</v>
       </c>
       <c r="D228" t="n">
-        <v>0.4057634947316526</v>
+        <v>0.413592550978105</v>
       </c>
       <c r="E228" t="n">
         <v>227</v>
@@ -4771,17 +4771,17 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>2021-04-22</t>
+          <t>2021-05-06</t>
         </is>
       </c>
       <c r="B229" t="n">
-        <v>23283868400</v>
+        <v>28245158344</v>
       </c>
       <c r="C229" t="n">
-        <v>57343158813</v>
+        <v>64995398044</v>
       </c>
       <c r="D229" t="n">
-        <v>0.406044398006226</v>
+        <v>0.4345716649797089</v>
       </c>
       <c r="E229" t="n">
         <v>228</v>
@@ -4790,17 +4790,17 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>2021-04-23</t>
+          <t>2021-05-07</t>
         </is>
       </c>
       <c r="B230" t="n">
-        <v>23110619160</v>
+        <v>33809492530</v>
       </c>
       <c r="C230" t="n">
-        <v>58758936747</v>
+        <v>72689004129</v>
       </c>
       <c r="D230" t="n">
-        <v>0.3933124123655954</v>
+        <v>0.4651252680529072</v>
       </c>
       <c r="E230" t="n">
         <v>229</v>
@@ -4809,17 +4809,17 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>2021-04-26</t>
+          <t>2021-05-10</t>
         </is>
       </c>
       <c r="B231" t="n">
-        <v>26080656908</v>
+        <v>34980447442</v>
       </c>
       <c r="C231" t="n">
-        <v>64990659217</v>
+        <v>74391256531</v>
       </c>
       <c r="D231" t="n">
-        <v>0.4012985438556365</v>
+        <v>0.4702225647636843</v>
       </c>
       <c r="E231" t="n">
         <v>230</v>
@@ -4828,17 +4828,17 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>2021-04-27</t>
+          <t>2021-05-11</t>
         </is>
       </c>
       <c r="B232" t="n">
-        <v>22805398723</v>
+        <v>33682768573</v>
       </c>
       <c r="C232" t="n">
-        <v>58465572266</v>
+        <v>73459473614</v>
       </c>
       <c r="D232" t="n">
-        <v>0.3900654323409783</v>
+        <v>0.4585217796412401</v>
       </c>
       <c r="E232" t="n">
         <v>231</v>
@@ -4847,17 +4847,17 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>2021-04-28</t>
+          <t>2021-05-12</t>
         </is>
       </c>
       <c r="B233" t="n">
-        <v>21764975470</v>
+        <v>28011409229</v>
       </c>
       <c r="C233" t="n">
-        <v>56258757783</v>
+        <v>66061705250</v>
       </c>
       <c r="D233" t="n">
-        <v>0.3868726635229197</v>
+        <v>0.4240188642269418</v>
       </c>
       <c r="E233" t="n">
         <v>232</v>
@@ -4866,17 +4866,17 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>2021-04-29</t>
+          <t>2021-05-13</t>
         </is>
       </c>
       <c r="B234" t="n">
-        <v>23871290845</v>
+        <v>29021959092</v>
       </c>
       <c r="C234" t="n">
-        <v>59672070298</v>
+        <v>69247970457</v>
       </c>
       <c r="D234" t="n">
-        <v>0.400041270996426</v>
+        <v>0.4191019448002651</v>
       </c>
       <c r="E234" t="n">
         <v>233</v>
@@ -4885,17 +4885,17 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>2021-04-30</t>
+          <t>2021-05-14</t>
         </is>
       </c>
       <c r="B235" t="n">
-        <v>26727927563</v>
+        <v>29087549466</v>
       </c>
       <c r="C235" t="n">
-        <v>64623812735</v>
+        <v>72865719627</v>
       </c>
       <c r="D235" t="n">
-        <v>0.413592550978105</v>
+        <v>0.3991938817718307</v>
       </c>
       <c r="E235" t="n">
         <v>234</v>
@@ -4904,17 +4904,17 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>2021-05-06</t>
+          <t>2021-05-17</t>
         </is>
       </c>
       <c r="B236" t="n">
-        <v>28245158344</v>
+        <v>26738086558</v>
       </c>
       <c r="C236" t="n">
-        <v>64995398044</v>
+        <v>68865623007</v>
       </c>
       <c r="D236" t="n">
-        <v>0.4345716649797089</v>
+        <v>0.3882646433806625</v>
       </c>
       <c r="E236" t="n">
         <v>235</v>
@@ -4923,17 +4923,17 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>2021-05-07</t>
+          <t>2021-05-18</t>
         </is>
       </c>
       <c r="B237" t="n">
-        <v>33809492530</v>
+        <v>23944078372</v>
       </c>
       <c r="C237" t="n">
-        <v>72689004129</v>
+        <v>58781317109</v>
       </c>
       <c r="D237" t="n">
-        <v>0.4651252680529072</v>
+        <v>0.4073416444139855</v>
       </c>
       <c r="E237" t="n">
         <v>236</v>
@@ -4942,17 +4942,17 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>2021-05-10</t>
+          <t>2021-05-19</t>
         </is>
       </c>
       <c r="B238" t="n">
-        <v>34980447442</v>
+        <v>25053218592</v>
       </c>
       <c r="C238" t="n">
-        <v>74391256531</v>
+        <v>60763325645</v>
       </c>
       <c r="D238" t="n">
-        <v>0.4702225647636843</v>
+        <v>0.4123082192434532</v>
       </c>
       <c r="E238" t="n">
         <v>237</v>
@@ -4961,17 +4961,17 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>2021-05-11</t>
+          <t>2021-05-20</t>
         </is>
       </c>
       <c r="B239" t="n">
-        <v>33682768573</v>
+        <v>28722723747</v>
       </c>
       <c r="C239" t="n">
-        <v>73459473614</v>
+        <v>68566840023</v>
       </c>
       <c r="D239" t="n">
-        <v>0.4585217796412401</v>
+        <v>0.4189010859675796</v>
       </c>
       <c r="E239" t="n">
         <v>238</v>
@@ -4980,17 +4980,17 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>2021-05-12</t>
+          <t>2021-05-21</t>
         </is>
       </c>
       <c r="B240" t="n">
-        <v>28011409229</v>
+        <v>25545536529</v>
       </c>
       <c r="C240" t="n">
-        <v>66061705250</v>
+        <v>61418379955</v>
       </c>
       <c r="D240" t="n">
-        <v>0.4240188642269418</v>
+        <v>0.4159265768279251</v>
       </c>
       <c r="E240" t="n">
         <v>239</v>
@@ -4999,17 +4999,17 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>2021-05-13</t>
+          <t>2021-05-24</t>
         </is>
       </c>
       <c r="B241" t="n">
-        <v>29021959092</v>
+        <v>25923087661</v>
       </c>
       <c r="C241" t="n">
-        <v>69247970457</v>
+        <v>63386616118</v>
       </c>
       <c r="D241" t="n">
-        <v>0.4191019448002651</v>
+        <v>0.4089678428761964</v>
       </c>
       <c r="E241" t="n">
         <v>240</v>
@@ -5018,17 +5018,17 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>2021-05-14</t>
+          <t>2021-05-25</t>
         </is>
       </c>
       <c r="B242" t="n">
-        <v>29087549466</v>
+        <v>29902389375</v>
       </c>
       <c r="C242" t="n">
-        <v>72865719627</v>
+        <v>71817033145</v>
       </c>
       <c r="D242" t="n">
-        <v>0.3991938817718307</v>
+        <v>0.4163690431854305</v>
       </c>
       <c r="E242" t="n">
         <v>241</v>
@@ -5037,17 +5037,17 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>2021-05-17</t>
+          <t>2021-05-26</t>
         </is>
       </c>
       <c r="B243" t="n">
-        <v>26738086558</v>
+        <v>29496722494</v>
       </c>
       <c r="C243" t="n">
-        <v>68865623007</v>
+        <v>72933630614</v>
       </c>
       <c r="D243" t="n">
-        <v>0.3882646433806625</v>
+        <v>0.4044323893611015</v>
       </c>
       <c r="E243" t="n">
         <v>242</v>
@@ -5056,17 +5056,17 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>2021-05-18</t>
+          <t>2021-05-27</t>
         </is>
       </c>
       <c r="B244" t="n">
-        <v>23944078372</v>
+        <v>26896810605</v>
       </c>
       <c r="C244" t="n">
-        <v>58781317109</v>
+        <v>68968444971</v>
       </c>
       <c r="D244" t="n">
-        <v>0.4073416444139855</v>
+        <v>0.3899871980049663</v>
       </c>
       <c r="E244" t="n">
         <v>243</v>
@@ -5075,17 +5075,17 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>2021-05-19</t>
+          <t>2021-05-27</t>
         </is>
       </c>
       <c r="B245" t="n">
-        <v>25053218592</v>
+        <v>26896810605</v>
       </c>
       <c r="C245" t="n">
-        <v>60763325645</v>
+        <v>68968444971</v>
       </c>
       <c r="D245" t="n">
-        <v>0.4123082192434532</v>
+        <v>0.3899871980049663</v>
       </c>
       <c r="E245" t="n">
         <v>244</v>
@@ -5094,17 +5094,17 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>2021-05-20</t>
+          <t>2021-05-28</t>
         </is>
       </c>
       <c r="B246" t="n">
-        <v>28722723747</v>
+        <v>29791926043</v>
       </c>
       <c r="C246" t="n">
-        <v>68566840023</v>
+        <v>73972884560</v>
       </c>
       <c r="D246" t="n">
-        <v>0.4189010859675796</v>
+        <v>0.4027411695543051</v>
       </c>
       <c r="E246" t="n">
         <v>245</v>
@@ -5113,17 +5113,17 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>2021-05-21</t>
+          <t>2021-05-31</t>
         </is>
       </c>
       <c r="B247" t="n">
-        <v>25545536529</v>
+        <v>27775314244</v>
       </c>
       <c r="C247" t="n">
-        <v>61418379955</v>
+        <v>70615016083</v>
       </c>
       <c r="D247" t="n">
-        <v>0.4159265768279251</v>
+        <v>0.3933343895490053</v>
       </c>
       <c r="E247" t="n">
         <v>246</v>
@@ -5132,17 +5132,17 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>2021-05-24</t>
+          <t>2021-06-01</t>
         </is>
       </c>
       <c r="B248" t="n">
-        <v>25923087661</v>
+        <v>28722955321</v>
       </c>
       <c r="C248" t="n">
-        <v>63386616118</v>
+        <v>75176823860</v>
       </c>
       <c r="D248" t="n">
-        <v>0.4089678428761964</v>
+        <v>0.3820719451315218</v>
       </c>
       <c r="E248" t="n">
         <v>247</v>
@@ -5151,134 +5151,20 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>2021-05-25</t>
+          <t>2021-06-02</t>
         </is>
       </c>
       <c r="B249" t="n">
-        <v>29902389375</v>
+        <v>29120888356</v>
       </c>
       <c r="C249" t="n">
-        <v>71817033145</v>
+        <v>75272955834</v>
       </c>
       <c r="D249" t="n">
-        <v>0.4163690431854305</v>
+        <v>0.3868705305026218</v>
       </c>
       <c r="E249" t="n">
         <v>248</v>
-      </c>
-    </row>
-    <row r="250">
-      <c r="A250" t="inlineStr">
-        <is>
-          <t>2021-05-26</t>
-        </is>
-      </c>
-      <c r="B250" t="n">
-        <v>29496722494</v>
-      </c>
-      <c r="C250" t="n">
-        <v>72933630614</v>
-      </c>
-      <c r="D250" t="n">
-        <v>0.4044323893611015</v>
-      </c>
-      <c r="E250" t="n">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="251">
-      <c r="A251" t="inlineStr">
-        <is>
-          <t>2021-05-27</t>
-        </is>
-      </c>
-      <c r="B251" t="n">
-        <v>26896810605</v>
-      </c>
-      <c r="C251" t="n">
-        <v>68968444971</v>
-      </c>
-      <c r="D251" t="n">
-        <v>0.3899871980049663</v>
-      </c>
-      <c r="E251" t="n">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="252">
-      <c r="A252" t="inlineStr">
-        <is>
-          <t>2021-05-27</t>
-        </is>
-      </c>
-      <c r="B252" t="n">
-        <v>26896810605</v>
-      </c>
-      <c r="C252" t="n">
-        <v>68968444971</v>
-      </c>
-      <c r="D252" t="n">
-        <v>0.3899871980049663</v>
-      </c>
-      <c r="E252" t="n">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="253">
-      <c r="A253" t="inlineStr">
-        <is>
-          <t>2021-05-28</t>
-        </is>
-      </c>
-      <c r="B253" t="n">
-        <v>29791926043</v>
-      </c>
-      <c r="C253" t="n">
-        <v>73972884560</v>
-      </c>
-      <c r="D253" t="n">
-        <v>0.4027411695543051</v>
-      </c>
-      <c r="E253" t="n">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="254">
-      <c r="A254" t="inlineStr">
-        <is>
-          <t>2021-05-31</t>
-        </is>
-      </c>
-      <c r="B254" t="n">
-        <v>27775314244</v>
-      </c>
-      <c r="C254" t="n">
-        <v>70615016083</v>
-      </c>
-      <c r="D254" t="n">
-        <v>0.3933343895490053</v>
-      </c>
-      <c r="E254" t="n">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="255">
-      <c r="A255" t="inlineStr">
-        <is>
-          <t>2021-06-01</t>
-        </is>
-      </c>
-      <c r="B255" t="n">
-        <v>28722955321</v>
-      </c>
-      <c r="C255" t="n">
-        <v>75176823860</v>
-      </c>
-      <c r="D255" t="n">
-        <v>0.3820719451315218</v>
-      </c>
-      <c r="E255" t="n">
-        <v>254</v>
       </c>
     </row>
   </sheetData>

--- a/king_index/output/index.xlsx
+++ b/king_index/output/index.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E249"/>
+  <dimension ref="A1:E250"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5167,6 +5167,25 @@
         <v>248</v>
       </c>
     </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>2021-06-03</t>
+        </is>
+      </c>
+      <c r="B250" t="n">
+        <v>29199450254</v>
+      </c>
+      <c r="C250" t="n">
+        <v>72798616374</v>
+      </c>
+      <c r="D250" t="n">
+        <v>0.4010989728704318</v>
+      </c>
+      <c r="E250" t="n">
+        <v>249</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/king_index/output/index.xlsx
+++ b/king_index/output/index.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E250"/>
+  <dimension ref="A1:E251"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5186,6 +5186,25 @@
         <v>249</v>
       </c>
     </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>2021-06-04</t>
+        </is>
+      </c>
+      <c r="B251" t="n">
+        <v>27330244158</v>
+      </c>
+      <c r="C251" t="n">
+        <v>68930352581</v>
+      </c>
+      <c r="D251" t="n">
+        <v>0.3964907059757783</v>
+      </c>
+      <c r="E251" t="n">
+        <v>250</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/king_index/output/index.xlsx
+++ b/king_index/output/index.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E251"/>
+  <dimension ref="A1:E252"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5205,6 +5205,25 @@
         <v>250</v>
       </c>
     </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>2021-06-07</t>
+        </is>
+      </c>
+      <c r="B252" t="n">
+        <v>25294989410</v>
+      </c>
+      <c r="C252" t="n">
+        <v>66558910303</v>
+      </c>
+      <c r="D252" t="n">
+        <v>0.3800391156472988</v>
+      </c>
+      <c r="E252" t="n">
+        <v>251</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/king_index/output/index.xlsx
+++ b/king_index/output/index.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E252"/>
+  <dimension ref="A1:E253"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5224,6 +5224,25 @@
         <v>251</v>
       </c>
     </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>2021-06-08</t>
+        </is>
+      </c>
+      <c r="B253" t="n">
+        <v>25589368881</v>
+      </c>
+      <c r="C253" t="n">
+        <v>68255065080</v>
+      </c>
+      <c r="D253" t="n">
+        <v>0.3749079844991337</v>
+      </c>
+      <c r="E253" t="n">
+        <v>252</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/king_index/output/index.xlsx
+++ b/king_index/output/index.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E253"/>
+  <dimension ref="A1:E254"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5243,6 +5243,25 @@
         <v>252</v>
       </c>
     </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>2021-06-09</t>
+        </is>
+      </c>
+      <c r="B254" t="n">
+        <v>25270907666</v>
+      </c>
+      <c r="C254" t="n">
+        <v>66612688195</v>
+      </c>
+      <c r="D254" t="n">
+        <v>0.3793707828157707</v>
+      </c>
+      <c r="E254" t="n">
+        <v>253</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/king_index/output/index.xlsx
+++ b/king_index/output/index.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E254"/>
+  <dimension ref="A1:E246"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -458,17 +458,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2020-05-28</t>
+          <t>2020-06-10</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>18416635989</v>
+        <v>20190478240</v>
       </c>
       <c r="C2" t="n">
-        <v>50047777669</v>
+        <v>52136701032</v>
       </c>
       <c r="D2" t="n">
-        <v>0.3679810942016595</v>
+        <v>0.3872603720670333</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>
@@ -477,17 +477,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2020-05-29</t>
+          <t>2020-06-11</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>18782496399</v>
+        <v>21856153332</v>
       </c>
       <c r="C3" t="n">
-        <v>49396386216</v>
+        <v>58580995849</v>
       </c>
       <c r="D3" t="n">
-        <v>0.3802402936293375</v>
+        <v>0.3730928949780408</v>
       </c>
       <c r="E3" t="n">
         <v>2</v>
@@ -496,17 +496,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2020-06-01</t>
+          <t>2020-06-12</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>22806246928</v>
+        <v>22554032456</v>
       </c>
       <c r="C4" t="n">
-        <v>64259168243</v>
+        <v>58624630321</v>
       </c>
       <c r="D4" t="n">
-        <v>0.3549103972487906</v>
+        <v>0.3847193975041731</v>
       </c>
       <c r="E4" t="n">
         <v>3</v>
@@ -515,17 +515,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2020-06-02</t>
+          <t>2020-06-15</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>26690797837</v>
+        <v>24160399741</v>
       </c>
       <c r="C5" t="n">
-        <v>67019269521</v>
+        <v>62827231135</v>
       </c>
       <c r="D5" t="n">
-        <v>0.3982555767582133</v>
+        <v>0.3845529924609497</v>
       </c>
       <c r="E5" t="n">
         <v>4</v>
@@ -534,17 +534,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2020-06-03</t>
+          <t>2020-06-16</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>25988325662</v>
+        <v>22302612612</v>
       </c>
       <c r="C6" t="n">
-        <v>66814592975</v>
+        <v>57871475779</v>
       </c>
       <c r="D6" t="n">
-        <v>0.3889618196390726</v>
+        <v>0.3853817845801855</v>
       </c>
       <c r="E6" t="n">
         <v>5</v>
@@ -553,17 +553,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2020-06-04</t>
+          <t>2020-06-17</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>22648232850</v>
+        <v>23156031895</v>
       </c>
       <c r="C7" t="n">
-        <v>57964700247</v>
+        <v>61386131654</v>
       </c>
       <c r="D7" t="n">
-        <v>0.3907245746720164</v>
+        <v>0.3772192720257707</v>
       </c>
       <c r="E7" t="n">
         <v>6</v>
@@ -572,17 +572,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2020-06-05</t>
+          <t>2020-06-18</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>21624249509</v>
+        <v>25733088111</v>
       </c>
       <c r="C8" t="n">
-        <v>55387084107</v>
+        <v>63354121102</v>
       </c>
       <c r="D8" t="n">
-        <v>0.3904204356962539</v>
+        <v>0.4061785983830442</v>
       </c>
       <c r="E8" t="n">
         <v>7</v>
@@ -591,17 +591,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2020-06-08</t>
+          <t>2020-06-19</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>23546771032</v>
+        <v>24126480724</v>
       </c>
       <c r="C9" t="n">
-        <v>58352042780</v>
+        <v>61888832308</v>
       </c>
       <c r="D9" t="n">
-        <v>0.4035295065980208</v>
+        <v>0.3898357720489956</v>
       </c>
       <c r="E9" t="n">
         <v>8</v>
@@ -610,17 +610,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2020-06-09</t>
+          <t>2020-06-22</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>20955198305</v>
+        <v>25010112764</v>
       </c>
       <c r="C10" t="n">
-        <v>53192911283</v>
+        <v>63846785740</v>
       </c>
       <c r="D10" t="n">
-        <v>0.3939471970900961</v>
+        <v>0.3917207808369149</v>
       </c>
       <c r="E10" t="n">
         <v>9</v>
@@ -629,17 +629,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2020-06-10</t>
+          <t>2020-06-23</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>20190478240</v>
+        <v>21417149307</v>
       </c>
       <c r="C11" t="n">
-        <v>52136701032</v>
+        <v>56906481203</v>
       </c>
       <c r="D11" t="n">
-        <v>0.3872603720670333</v>
+        <v>0.3763569430799901</v>
       </c>
       <c r="E11" t="n">
         <v>10</v>
@@ -648,17 +648,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2020-06-11</t>
+          <t>2020-06-24</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>21856153332</v>
+        <v>19322024502</v>
       </c>
       <c r="C12" t="n">
-        <v>58580995849</v>
+        <v>52926747938</v>
       </c>
       <c r="D12" t="n">
-        <v>0.3730928949780408</v>
+        <v>0.3650710700123576</v>
       </c>
       <c r="E12" t="n">
         <v>11</v>
@@ -667,17 +667,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2020-06-12</t>
+          <t>2020-06-29</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>22554032456</v>
+        <v>20448932009</v>
       </c>
       <c r="C13" t="n">
-        <v>58624630321</v>
+        <v>54347085975</v>
       </c>
       <c r="D13" t="n">
-        <v>0.3847193975041731</v>
+        <v>0.3762654729713868</v>
       </c>
       <c r="E13" t="n">
         <v>12</v>
@@ -686,17 +686,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2020-06-15</t>
+          <t>2020-06-30</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>24160399741</v>
+        <v>20003048931</v>
       </c>
       <c r="C14" t="n">
-        <v>62827231135</v>
+        <v>53946886834</v>
       </c>
       <c r="D14" t="n">
-        <v>0.3845529924609497</v>
+        <v>0.3707915341352578</v>
       </c>
       <c r="E14" t="n">
         <v>13</v>
@@ -705,17 +705,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2020-06-16</t>
+          <t>2020-07-01</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>22302612612</v>
+        <v>25539868441</v>
       </c>
       <c r="C15" t="n">
-        <v>57871475779</v>
+        <v>66477208273</v>
       </c>
       <c r="D15" t="n">
-        <v>0.3853817845801855</v>
+        <v>0.3841898464826647</v>
       </c>
       <c r="E15" t="n">
         <v>14</v>
@@ -724,17 +724,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2020-06-17</t>
+          <t>2020-07-02</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>23156031895</v>
+        <v>35281401239</v>
       </c>
       <c r="C16" t="n">
-        <v>61386131654</v>
+        <v>86277275738</v>
       </c>
       <c r="D16" t="n">
-        <v>0.3772192720257707</v>
+        <v>0.4089304041789609</v>
       </c>
       <c r="E16" t="n">
         <v>15</v>
@@ -743,17 +743,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2020-06-18</t>
+          <t>2020-07-03</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>25733088111</v>
+        <v>39589081860</v>
       </c>
       <c r="C17" t="n">
-        <v>63354121102</v>
+        <v>96590527098</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4061785983830442</v>
+        <v>0.4098650566409398</v>
       </c>
       <c r="E17" t="n">
         <v>16</v>
@@ -762,17 +762,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2020-06-19</t>
+          <t>2020-07-06</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>24126480724</v>
+        <v>51680326902</v>
       </c>
       <c r="C18" t="n">
-        <v>61888832308</v>
+        <v>132721246132</v>
       </c>
       <c r="D18" t="n">
-        <v>0.3898357720489956</v>
+        <v>0.3893900065600689</v>
       </c>
       <c r="E18" t="n">
         <v>17</v>
@@ -781,17 +781,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2020-06-22</t>
+          <t>2020-07-07</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>25010112764</v>
+        <v>54130474812</v>
       </c>
       <c r="C19" t="n">
-        <v>63846785740</v>
+        <v>140540263998</v>
       </c>
       <c r="D19" t="n">
-        <v>0.3917207808369149</v>
+        <v>0.3851599055824338</v>
       </c>
       <c r="E19" t="n">
         <v>18</v>
@@ -800,17 +800,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2020-06-23</t>
+          <t>2020-07-08</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>21417149307</v>
+        <v>48763694238</v>
       </c>
       <c r="C20" t="n">
-        <v>56906481203</v>
+        <v>124820435614</v>
       </c>
       <c r="D20" t="n">
-        <v>0.3763569430799901</v>
+        <v>0.3906707583427999</v>
       </c>
       <c r="E20" t="n">
         <v>19</v>
@@ -819,17 +819,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2020-06-24</t>
+          <t>2020-07-09</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>19322024502</v>
+        <v>50352644938</v>
       </c>
       <c r="C21" t="n">
-        <v>52926747938</v>
+        <v>137276438768</v>
       </c>
       <c r="D21" t="n">
-        <v>0.3650710700123576</v>
+        <v>0.3667974299879457</v>
       </c>
       <c r="E21" t="n">
         <v>20</v>
@@ -838,17 +838,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2020-06-29</t>
+          <t>2020-07-10</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>20448932009</v>
+        <v>45792064703</v>
       </c>
       <c r="C22" t="n">
-        <v>54347085975</v>
+        <v>124540979573</v>
       </c>
       <c r="D22" t="n">
-        <v>0.3762654729713868</v>
+        <v>0.3676867233580644</v>
       </c>
       <c r="E22" t="n">
         <v>21</v>
@@ -857,17 +857,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2020-06-30</t>
+          <t>2020-07-13</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>20003048931</v>
+        <v>45569190970</v>
       </c>
       <c r="C23" t="n">
-        <v>53946886834</v>
+        <v>125874117474</v>
       </c>
       <c r="D23" t="n">
-        <v>0.3707915341352578</v>
+        <v>0.3620219301987366</v>
       </c>
       <c r="E23" t="n">
         <v>22</v>
@@ -876,17 +876,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2020-07-01</t>
+          <t>2020-07-14</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>25539868441</v>
+        <v>44404671526</v>
       </c>
       <c r="C24" t="n">
-        <v>66477208273</v>
+        <v>127205292718</v>
       </c>
       <c r="D24" t="n">
-        <v>0.3841898464826647</v>
+        <v>0.3490788046409375</v>
       </c>
       <c r="E24" t="n">
         <v>23</v>
@@ -895,17 +895,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2020-07-02</t>
+          <t>2020-07-15</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>35281401239</v>
+        <v>40948010990</v>
       </c>
       <c r="C25" t="n">
-        <v>86277275738</v>
+        <v>115744357395</v>
       </c>
       <c r="D25" t="n">
-        <v>0.4089304041789609</v>
+        <v>0.3537797600815822</v>
       </c>
       <c r="E25" t="n">
         <v>24</v>
@@ -914,17 +914,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2020-07-03</t>
+          <t>2020-07-16</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>39589081860</v>
+        <v>41327517137</v>
       </c>
       <c r="C26" t="n">
-        <v>96590527098</v>
+        <v>110570972319</v>
       </c>
       <c r="D26" t="n">
-        <v>0.4098650566409398</v>
+        <v>0.373764617152584</v>
       </c>
       <c r="E26" t="n">
         <v>25</v>
@@ -933,17 +933,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2020-07-06</t>
+          <t>2020-07-17</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>51680326902</v>
+        <v>30786629717</v>
       </c>
       <c r="C27" t="n">
-        <v>132721246132</v>
+        <v>83073812068</v>
       </c>
       <c r="D27" t="n">
-        <v>0.3893900065600689</v>
+        <v>0.3705936798927636</v>
       </c>
       <c r="E27" t="n">
         <v>26</v>
@@ -952,17 +952,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2020-07-07</t>
+          <t>2020-07-20</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>54130474812</v>
+        <v>33302406491</v>
       </c>
       <c r="C28" t="n">
-        <v>140540263998</v>
+        <v>90725025902</v>
       </c>
       <c r="D28" t="n">
-        <v>0.3851599055824338</v>
+        <v>0.3670696829226903</v>
       </c>
       <c r="E28" t="n">
         <v>27</v>
@@ -971,17 +971,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2020-07-08</t>
+          <t>2020-07-21</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>48763694238</v>
+        <v>29750727633</v>
       </c>
       <c r="C29" t="n">
-        <v>124820435614</v>
+        <v>82804408460</v>
       </c>
       <c r="D29" t="n">
-        <v>0.3906707583427999</v>
+        <v>0.3592891753749025</v>
       </c>
       <c r="E29" t="n">
         <v>28</v>
@@ -990,17 +990,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2020-07-09</t>
+          <t>2020-07-22</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>50352644938</v>
+        <v>32546369994</v>
       </c>
       <c r="C30" t="n">
-        <v>137276438768</v>
+        <v>88951002081</v>
       </c>
       <c r="D30" t="n">
-        <v>0.3667974299879457</v>
+        <v>0.3658909875389917</v>
       </c>
       <c r="E30" t="n">
         <v>29</v>
@@ -1009,17 +1009,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2020-07-10</t>
+          <t>2020-07-23</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>45792064703</v>
+        <v>33380341470</v>
       </c>
       <c r="C31" t="n">
-        <v>124540979573</v>
+        <v>92918126099</v>
       </c>
       <c r="D31" t="n">
-        <v>0.3676867233580644</v>
+        <v>0.3592446691664313</v>
       </c>
       <c r="E31" t="n">
         <v>30</v>
@@ -1028,17 +1028,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2020-07-13</t>
+          <t>2020-07-24</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>45569190970</v>
+        <v>34826858650</v>
       </c>
       <c r="C32" t="n">
-        <v>125874117474</v>
+        <v>98778010270</v>
       </c>
       <c r="D32" t="n">
-        <v>0.3620219301987366</v>
+        <v>0.3525770417404056</v>
       </c>
       <c r="E32" t="n">
         <v>31</v>
@@ -1047,17 +1047,17 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2020-07-14</t>
+          <t>2020-07-27</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>44404671526</v>
+        <v>25272101520</v>
       </c>
       <c r="C33" t="n">
-        <v>127205292718</v>
+        <v>69273127708</v>
       </c>
       <c r="D33" t="n">
-        <v>0.3490788046409375</v>
+        <v>0.3648182542951854</v>
       </c>
       <c r="E33" t="n">
         <v>32</v>
@@ -1066,17 +1066,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2020-07-15</t>
+          <t>2020-07-28</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>40948010990</v>
+        <v>25533477451</v>
       </c>
       <c r="C34" t="n">
-        <v>115744357395</v>
+        <v>67557159363</v>
       </c>
       <c r="D34" t="n">
-        <v>0.3537797600815822</v>
+        <v>0.3779536868002814</v>
       </c>
       <c r="E34" t="n">
         <v>33</v>
@@ -1085,17 +1085,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2020-07-16</t>
+          <t>2020-07-29</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>41327517137</v>
+        <v>27398207256</v>
       </c>
       <c r="C35" t="n">
-        <v>110570972319</v>
+        <v>75808503607</v>
       </c>
       <c r="D35" t="n">
-        <v>0.373764617152584</v>
+        <v>0.3614133764997586</v>
       </c>
       <c r="E35" t="n">
         <v>34</v>
@@ -1104,17 +1104,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2020-07-17</t>
+          <t>2020-07-30</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>30786629717</v>
+        <v>29316097538</v>
       </c>
       <c r="C36" t="n">
-        <v>83073812068</v>
+        <v>80705680370</v>
       </c>
       <c r="D36" t="n">
-        <v>0.3705936798927636</v>
+        <v>0.3632470156201968</v>
       </c>
       <c r="E36" t="n">
         <v>35</v>
@@ -1123,17 +1123,17 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2020-07-20</t>
+          <t>2020-07-31</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>33302406491</v>
+        <v>30421341838</v>
       </c>
       <c r="C37" t="n">
-        <v>90725025902</v>
+        <v>83388719271</v>
       </c>
       <c r="D37" t="n">
-        <v>0.3670696829226903</v>
+        <v>0.3648136355126825</v>
       </c>
       <c r="E37" t="n">
         <v>36</v>
@@ -1142,17 +1142,17 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2020-07-21</t>
+          <t>2020-08-03</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>29750727633</v>
+        <v>32534419194</v>
       </c>
       <c r="C38" t="n">
-        <v>82804408460</v>
+        <v>97147468049</v>
       </c>
       <c r="D38" t="n">
-        <v>0.3592891753749025</v>
+        <v>0.3348972427937086</v>
       </c>
       <c r="E38" t="n">
         <v>37</v>
@@ -1161,17 +1161,17 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2020-07-22</t>
+          <t>2020-08-04</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>32546369994</v>
+        <v>35518548960</v>
       </c>
       <c r="C39" t="n">
-        <v>88951002081</v>
+        <v>100401661483</v>
       </c>
       <c r="D39" t="n">
-        <v>0.3658909875389917</v>
+        <v>0.3537645536474912</v>
       </c>
       <c r="E39" t="n">
         <v>38</v>
@@ -1180,17 +1180,17 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2020-07-23</t>
+          <t>2020-08-05</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>33380341470</v>
+        <v>31118752071</v>
       </c>
       <c r="C40" t="n">
-        <v>92918126099</v>
+        <v>88411991123</v>
       </c>
       <c r="D40" t="n">
-        <v>0.3592446691664313</v>
+        <v>0.351974338273947</v>
       </c>
       <c r="E40" t="n">
         <v>39</v>
@@ -1199,17 +1199,17 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2020-07-24</t>
+          <t>2020-08-06</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>34826858650</v>
+        <v>35289080996</v>
       </c>
       <c r="C41" t="n">
-        <v>98778010270</v>
+        <v>94484631872</v>
       </c>
       <c r="D41" t="n">
-        <v>0.3525770417404056</v>
+        <v>0.3734901676264849</v>
       </c>
       <c r="E41" t="n">
         <v>40</v>
@@ -1218,17 +1218,17 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2020-07-27</t>
+          <t>2020-08-07</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>25272101520</v>
+        <v>33926327226</v>
       </c>
       <c r="C42" t="n">
-        <v>69273127708</v>
+        <v>90977583613</v>
       </c>
       <c r="D42" t="n">
-        <v>0.3648182542951854</v>
+        <v>0.3729086427522151</v>
       </c>
       <c r="E42" t="n">
         <v>41</v>
@@ -1237,17 +1237,17 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2020-07-28</t>
+          <t>2020-08-10</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>25533477451</v>
+        <v>29708663069</v>
       </c>
       <c r="C43" t="n">
-        <v>67557159363</v>
+        <v>82942928747</v>
       </c>
       <c r="D43" t="n">
-        <v>0.3779536868002814</v>
+        <v>0.3581819875160189</v>
       </c>
       <c r="E43" t="n">
         <v>42</v>
@@ -1256,17 +1256,17 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2020-07-29</t>
+          <t>2020-08-11</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>27398207256</v>
+        <v>30946369948</v>
       </c>
       <c r="C44" t="n">
-        <v>75808503607</v>
+        <v>86295092754</v>
       </c>
       <c r="D44" t="n">
-        <v>0.3614133764997586</v>
+        <v>0.3586110051033644</v>
       </c>
       <c r="E44" t="n">
         <v>43</v>
@@ -1275,17 +1275,17 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2020-07-30</t>
+          <t>2020-08-12</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>29316097538</v>
+        <v>29856245191</v>
       </c>
       <c r="C45" t="n">
-        <v>80705680370</v>
+        <v>82452473263</v>
       </c>
       <c r="D45" t="n">
-        <v>0.3632470156201968</v>
+        <v>0.3621024817019988</v>
       </c>
       <c r="E45" t="n">
         <v>44</v>
@@ -1294,17 +1294,17 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2020-07-31</t>
+          <t>2020-08-13</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>30421341838</v>
+        <v>27823565615</v>
       </c>
       <c r="C46" t="n">
-        <v>83388719271</v>
+        <v>72532322436</v>
       </c>
       <c r="D46" t="n">
-        <v>0.3648136355126825</v>
+        <v>0.3836022986793308</v>
       </c>
       <c r="E46" t="n">
         <v>45</v>
@@ -1313,17 +1313,17 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2020-08-03</t>
+          <t>2020-08-14</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>32534419194</v>
+        <v>27261549866</v>
       </c>
       <c r="C47" t="n">
-        <v>97147468049</v>
+        <v>69180221661</v>
       </c>
       <c r="D47" t="n">
-        <v>0.3348972427937086</v>
+        <v>0.3940656622869504</v>
       </c>
       <c r="E47" t="n">
         <v>46</v>
@@ -1332,17 +1332,17 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2020-08-04</t>
+          <t>2020-08-17</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>35518548960</v>
+        <v>37118467741</v>
       </c>
       <c r="C48" t="n">
-        <v>100401661483</v>
+        <v>91788369903</v>
       </c>
       <c r="D48" t="n">
-        <v>0.3537645536474912</v>
+        <v>0.4043918394043386</v>
       </c>
       <c r="E48" t="n">
         <v>47</v>
@@ -1351,17 +1351,17 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2020-08-05</t>
+          <t>2020-08-18</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>31118752071</v>
+        <v>31325687773</v>
       </c>
       <c r="C49" t="n">
-        <v>88411991123</v>
+        <v>85178317604</v>
       </c>
       <c r="D49" t="n">
-        <v>0.351974338273947</v>
+        <v>0.3677659838109897</v>
       </c>
       <c r="E49" t="n">
         <v>48</v>
@@ -1370,17 +1370,17 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2020-08-06</t>
+          <t>2020-08-19</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>35289080996</v>
+        <v>33073383828</v>
       </c>
       <c r="C50" t="n">
-        <v>94484631872</v>
+        <v>88140275731</v>
       </c>
       <c r="D50" t="n">
-        <v>0.3734901676264849</v>
+        <v>0.375235765417145</v>
       </c>
       <c r="E50" t="n">
         <v>49</v>
@@ -1389,17 +1389,17 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2020-08-07</t>
+          <t>2020-08-20</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>33926327226</v>
+        <v>27646953314</v>
       </c>
       <c r="C51" t="n">
-        <v>90977583613</v>
+        <v>72119978332</v>
       </c>
       <c r="D51" t="n">
-        <v>0.3729086427522151</v>
+        <v>0.3833466669489126</v>
       </c>
       <c r="E51" t="n">
         <v>50</v>
@@ -1408,17 +1408,17 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2020-08-10</t>
+          <t>2020-08-21</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>29708663069</v>
+        <v>25486130617</v>
       </c>
       <c r="C52" t="n">
-        <v>82942928747</v>
+        <v>66786682396</v>
       </c>
       <c r="D52" t="n">
-        <v>0.3581819875160189</v>
+        <v>0.3816049802546626</v>
       </c>
       <c r="E52" t="n">
         <v>51</v>
@@ -1427,17 +1427,17 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2020-08-11</t>
+          <t>2020-08-24</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>30946369948</v>
+        <v>25209284709</v>
       </c>
       <c r="C53" t="n">
-        <v>86295092754</v>
+        <v>67412296336</v>
       </c>
       <c r="D53" t="n">
-        <v>0.3586110051033644</v>
+        <v>0.3739567716748666</v>
       </c>
       <c r="E53" t="n">
         <v>52</v>
@@ -1446,17 +1446,17 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2020-08-12</t>
+          <t>2020-08-25</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>29856245191</v>
+        <v>26619247474</v>
       </c>
       <c r="C54" t="n">
-        <v>82452473263</v>
+        <v>73103731924</v>
       </c>
       <c r="D54" t="n">
-        <v>0.3621024817019988</v>
+        <v>0.3641298025889275</v>
       </c>
       <c r="E54" t="n">
         <v>53</v>
@@ -1465,17 +1465,17 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2020-08-13</t>
+          <t>2020-08-26</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>27823565615</v>
+        <v>26322908958</v>
       </c>
       <c r="C55" t="n">
-        <v>72532322436</v>
+        <v>75716936591</v>
       </c>
       <c r="D55" t="n">
-        <v>0.3836022986793308</v>
+        <v>0.3476488899727732</v>
       </c>
       <c r="E55" t="n">
         <v>54</v>
@@ -1484,17 +1484,17 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2020-08-14</t>
+          <t>2020-08-27</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>27261549866</v>
+        <v>23276018839</v>
       </c>
       <c r="C56" t="n">
-        <v>69180221661</v>
+        <v>65005692955</v>
       </c>
       <c r="D56" t="n">
-        <v>0.3940656622869504</v>
+        <v>0.3580612371152286</v>
       </c>
       <c r="E56" t="n">
         <v>55</v>
@@ -1503,17 +1503,17 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2020-08-17</t>
+          <t>2020-08-28</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>37118467741</v>
+        <v>25701039669</v>
       </c>
       <c r="C57" t="n">
-        <v>91788369903</v>
+        <v>70850828969</v>
       </c>
       <c r="D57" t="n">
-        <v>0.4043918394043386</v>
+        <v>0.3627486091975749</v>
       </c>
       <c r="E57" t="n">
         <v>56</v>
@@ -1522,17 +1522,17 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2020-08-18</t>
+          <t>2020-08-31</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>31325687773</v>
+        <v>28573296373</v>
       </c>
       <c r="C58" t="n">
-        <v>85178317604</v>
+        <v>77184652221</v>
       </c>
       <c r="D58" t="n">
-        <v>0.3677659838109897</v>
+        <v>0.3701940159189566</v>
       </c>
       <c r="E58" t="n">
         <v>57</v>
@@ -1541,17 +1541,17 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2020-08-19</t>
+          <t>2020-09-01</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>33073383828</v>
+        <v>23964180511</v>
       </c>
       <c r="C59" t="n">
-        <v>88140275731</v>
+        <v>64392996012</v>
       </c>
       <c r="D59" t="n">
-        <v>0.375235765417145</v>
+        <v>0.3721550788929613</v>
       </c>
       <c r="E59" t="n">
         <v>58</v>
@@ -1560,17 +1560,17 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2020-08-20</t>
+          <t>2020-09-02</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>27646953314</v>
+        <v>30082062270</v>
       </c>
       <c r="C60" t="n">
-        <v>72119978332</v>
+        <v>77531927895</v>
       </c>
       <c r="D60" t="n">
-        <v>0.3833466669489126</v>
+        <v>0.3879957984630482</v>
       </c>
       <c r="E60" t="n">
         <v>59</v>
@@ -1579,17 +1579,17 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2020-08-21</t>
+          <t>2020-09-03</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>25486130617</v>
+        <v>27715216294</v>
       </c>
       <c r="C61" t="n">
-        <v>66786682396</v>
+        <v>73519808249</v>
       </c>
       <c r="D61" t="n">
-        <v>0.3816049802546626</v>
+        <v>0.3769761776327399</v>
       </c>
       <c r="E61" t="n">
         <v>60</v>
@@ -1598,17 +1598,17 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2020-08-24</t>
+          <t>2020-09-04</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>25209284709</v>
+        <v>24329945914</v>
       </c>
       <c r="C62" t="n">
-        <v>67412296336</v>
+        <v>65573685675</v>
       </c>
       <c r="D62" t="n">
-        <v>0.3739567716748666</v>
+        <v>0.37103215510236</v>
       </c>
       <c r="E62" t="n">
         <v>61</v>
@@ -1617,17 +1617,17 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2020-08-25</t>
+          <t>2020-09-07</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>26619247474</v>
+        <v>29997390344</v>
       </c>
       <c r="C63" t="n">
-        <v>73103731924</v>
+        <v>79881522723</v>
       </c>
       <c r="D63" t="n">
-        <v>0.3641298025889275</v>
+        <v>0.375523516846568</v>
       </c>
       <c r="E63" t="n">
         <v>62</v>
@@ -1636,17 +1636,17 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2020-08-26</t>
+          <t>2020-09-08</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>26322908958</v>
+        <v>32724062545</v>
       </c>
       <c r="C64" t="n">
-        <v>75716936591</v>
+        <v>80161481426</v>
       </c>
       <c r="D64" t="n">
-        <v>0.3476488899727732</v>
+        <v>0.4082267688030289</v>
       </c>
       <c r="E64" t="n">
         <v>63</v>
@@ -1655,17 +1655,17 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2020-08-27</t>
+          <t>2020-09-09</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>23276018839</v>
+        <v>41720230941</v>
       </c>
       <c r="C65" t="n">
-        <v>65005692955</v>
+        <v>98517765305</v>
       </c>
       <c r="D65" t="n">
-        <v>0.3580612371152286</v>
+        <v>0.4234792660170358</v>
       </c>
       <c r="E65" t="n">
         <v>64</v>
@@ -1674,17 +1674,17 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2020-08-28</t>
+          <t>2020-09-10</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>25701039669</v>
+        <v>32362586075</v>
       </c>
       <c r="C66" t="n">
-        <v>70850828969</v>
+        <v>83938666669</v>
       </c>
       <c r="D66" t="n">
-        <v>0.3627486091975749</v>
+        <v>0.3855503948212232</v>
       </c>
       <c r="E66" t="n">
         <v>65</v>
@@ -1693,17 +1693,17 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2020-08-31</t>
+          <t>2020-09-11</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>28573296373</v>
+        <v>23586290440</v>
       </c>
       <c r="C67" t="n">
-        <v>77184652221</v>
+        <v>60330240577</v>
       </c>
       <c r="D67" t="n">
-        <v>0.3701940159189566</v>
+        <v>0.3909530314220547</v>
       </c>
       <c r="E67" t="n">
         <v>66</v>
@@ -1712,17 +1712,17 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2020-09-01</t>
+          <t>2020-09-14</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>23964180511</v>
+        <v>24462170352</v>
       </c>
       <c r="C68" t="n">
-        <v>64392996012</v>
+        <v>63101019998</v>
       </c>
       <c r="D68" t="n">
-        <v>0.3721550788929613</v>
+        <v>0.3876667976646865</v>
       </c>
       <c r="E68" t="n">
         <v>67</v>
@@ -1731,17 +1731,17 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2020-09-02</t>
+          <t>2020-09-15</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>30082062270</v>
+        <v>23106120892</v>
       </c>
       <c r="C69" t="n">
-        <v>77531927895</v>
+        <v>58614407766</v>
       </c>
       <c r="D69" t="n">
-        <v>0.3879957984630482</v>
+        <v>0.3942054824514151</v>
       </c>
       <c r="E69" t="n">
         <v>68</v>
@@ -1750,17 +1750,17 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2020-09-03</t>
+          <t>2020-09-16</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>27715216294</v>
+        <v>21724638649</v>
       </c>
       <c r="C70" t="n">
-        <v>73519808249</v>
+        <v>55182289033</v>
       </c>
       <c r="D70" t="n">
-        <v>0.3769761776327399</v>
+        <v>0.3936886096915674</v>
       </c>
       <c r="E70" t="n">
         <v>69</v>
@@ -1769,17 +1769,17 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2020-09-04</t>
+          <t>2020-09-17</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>24329945914</v>
+        <v>20554994106</v>
       </c>
       <c r="C71" t="n">
-        <v>65573685675</v>
+        <v>55472969929</v>
       </c>
       <c r="D71" t="n">
-        <v>0.37103215510236</v>
+        <v>0.3705407179804577</v>
       </c>
       <c r="E71" t="n">
         <v>70</v>
@@ -1788,17 +1788,17 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2020-09-07</t>
+          <t>2020-09-18</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>29997390344</v>
+        <v>25018086444</v>
       </c>
       <c r="C72" t="n">
-        <v>79881522723</v>
+        <v>64587549837</v>
       </c>
       <c r="D72" t="n">
-        <v>0.375523516846568</v>
+        <v>0.3873515330297914</v>
       </c>
       <c r="E72" t="n">
         <v>71</v>
@@ -1807,17 +1807,17 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2020-09-08</t>
+          <t>2020-09-21</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>32724062545</v>
+        <v>22182279260</v>
       </c>
       <c r="C73" t="n">
-        <v>80161481426</v>
+        <v>58098440053</v>
       </c>
       <c r="D73" t="n">
-        <v>0.4082267688030289</v>
+        <v>0.3818050749686968</v>
       </c>
       <c r="E73" t="n">
         <v>72</v>
@@ -1826,17 +1826,17 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2020-09-09</t>
+          <t>2020-09-22</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>41720230941</v>
+        <v>22099090990</v>
       </c>
       <c r="C74" t="n">
-        <v>98517765305</v>
+        <v>56264182474</v>
       </c>
       <c r="D74" t="n">
-        <v>0.4234792660170358</v>
+        <v>0.3927736975510506</v>
       </c>
       <c r="E74" t="n">
         <v>73</v>
@@ -1845,17 +1845,17 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2020-09-10</t>
+          <t>2020-09-23</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>32362586075</v>
+        <v>19077501915</v>
       </c>
       <c r="C75" t="n">
-        <v>83938666669</v>
+        <v>48597940983</v>
       </c>
       <c r="D75" t="n">
-        <v>0.3855503948212232</v>
+        <v>0.3925578230088695</v>
       </c>
       <c r="E75" t="n">
         <v>74</v>
@@ -1864,17 +1864,17 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2020-09-11</t>
+          <t>2020-09-24</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>23586290440</v>
+        <v>20859996043</v>
       </c>
       <c r="C76" t="n">
-        <v>60330240577</v>
+        <v>54861814882</v>
       </c>
       <c r="D76" t="n">
-        <v>0.3909530314220547</v>
+        <v>0.3802279616134993</v>
       </c>
       <c r="E76" t="n">
         <v>75</v>
@@ -1883,17 +1883,17 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2020-09-14</t>
+          <t>2020-09-25</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>24462170352</v>
+        <v>16281719043</v>
       </c>
       <c r="C77" t="n">
-        <v>63101019998</v>
+        <v>43622575116</v>
       </c>
       <c r="D77" t="n">
-        <v>0.3876667976646865</v>
+        <v>0.373240667239476</v>
       </c>
       <c r="E77" t="n">
         <v>76</v>
@@ -1902,17 +1902,17 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2020-09-15</t>
+          <t>2020-09-28</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>23106120892</v>
+        <v>14676583271</v>
       </c>
       <c r="C78" t="n">
-        <v>58614407766</v>
+        <v>40556797589</v>
       </c>
       <c r="D78" t="n">
-        <v>0.3942054824514151</v>
+        <v>0.3618772719614492</v>
       </c>
       <c r="E78" t="n">
         <v>77</v>
@@ -1921,17 +1921,17 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2020-09-16</t>
+          <t>2020-09-29</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>21724638649</v>
+        <v>14442107257</v>
       </c>
       <c r="C79" t="n">
-        <v>55182289033</v>
+        <v>40163621965</v>
       </c>
       <c r="D79" t="n">
-        <v>0.3936886096915674</v>
+        <v>0.3595817944304267</v>
       </c>
       <c r="E79" t="n">
         <v>78</v>
@@ -1940,17 +1940,17 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2020-09-17</t>
+          <t>2020-09-30</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>20554994106</v>
+        <v>15066784297</v>
       </c>
       <c r="C80" t="n">
-        <v>55472969929</v>
+        <v>40300843448</v>
       </c>
       <c r="D80" t="n">
-        <v>0.3705407179804577</v>
+        <v>0.3738577907541961</v>
       </c>
       <c r="E80" t="n">
         <v>79</v>
@@ -1959,17 +1959,17 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2020-09-18</t>
+          <t>2020-10-09</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>25018086444</v>
+        <v>18363804782</v>
       </c>
       <c r="C81" t="n">
-        <v>64587549837</v>
+        <v>50410563994</v>
       </c>
       <c r="D81" t="n">
-        <v>0.3873515330297914</v>
+        <v>0.3642848507742486</v>
       </c>
       <c r="E81" t="n">
         <v>80</v>
@@ -1978,17 +1978,17 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2020-09-21</t>
+          <t>2020-10-12</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>22182279260</v>
+        <v>24824121596</v>
       </c>
       <c r="C82" t="n">
-        <v>58098440053</v>
+        <v>69075123930</v>
       </c>
       <c r="D82" t="n">
-        <v>0.3818050749686968</v>
+        <v>0.3593786038104905</v>
       </c>
       <c r="E82" t="n">
         <v>81</v>
@@ -1997,17 +1997,17 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2020-09-22</t>
+          <t>2020-10-13</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>22099090990</v>
+        <v>21950874234</v>
       </c>
       <c r="C83" t="n">
-        <v>56264182474</v>
+        <v>58435290007</v>
       </c>
       <c r="D83" t="n">
-        <v>0.3927736975510506</v>
+        <v>0.3756441395494142</v>
       </c>
       <c r="E83" t="n">
         <v>82</v>
@@ -2016,17 +2016,17 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2020-09-23</t>
+          <t>2020-10-14</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>19077501915</v>
+        <v>21810988673</v>
       </c>
       <c r="C84" t="n">
-        <v>48597940983</v>
+        <v>58022364557</v>
       </c>
       <c r="D84" t="n">
-        <v>0.3925578230088695</v>
+        <v>0.3759065808421738</v>
       </c>
       <c r="E84" t="n">
         <v>83</v>
@@ -2035,17 +2035,17 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2020-09-24</t>
+          <t>2020-10-15</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>20859996043</v>
+        <v>20410751440</v>
       </c>
       <c r="C85" t="n">
-        <v>54861814882</v>
+        <v>54415224691</v>
       </c>
       <c r="D85" t="n">
-        <v>0.3802279616134993</v>
+        <v>0.3750926612157467</v>
       </c>
       <c r="E85" t="n">
         <v>84</v>
@@ -2054,17 +2054,17 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2020-09-25</t>
+          <t>2020-10-16</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>16281719043</v>
+        <v>19779199722</v>
       </c>
       <c r="C86" t="n">
-        <v>43622575116</v>
+        <v>51552706029</v>
       </c>
       <c r="D86" t="n">
-        <v>0.373240667239476</v>
+        <v>0.3836694762613156</v>
       </c>
       <c r="E86" t="n">
         <v>85</v>
@@ -2073,17 +2073,17 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2020-09-28</t>
+          <t>2020-10-19</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>14676583271</v>
+        <v>20562725471</v>
       </c>
       <c r="C87" t="n">
-        <v>40556797589</v>
+        <v>53895497648</v>
       </c>
       <c r="D87" t="n">
-        <v>0.3618772719614492</v>
+        <v>0.3815295593947087</v>
       </c>
       <c r="E87" t="n">
         <v>86</v>
@@ -2092,17 +2092,17 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2020-09-29</t>
+          <t>2020-10-20</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>14442107257</v>
+        <v>18296672779</v>
       </c>
       <c r="C88" t="n">
-        <v>40163621965</v>
+        <v>47922773316</v>
       </c>
       <c r="D88" t="n">
-        <v>0.3595817944304267</v>
+        <v>0.3817949486844761</v>
       </c>
       <c r="E88" t="n">
         <v>87</v>
@@ -2111,17 +2111,17 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2020-09-30</t>
+          <t>2020-10-21</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>15066784297</v>
+        <v>18370049664</v>
       </c>
       <c r="C89" t="n">
-        <v>40300843448</v>
+        <v>49307563396</v>
       </c>
       <c r="D89" t="n">
-        <v>0.3738577907541961</v>
+        <v>0.3725604836009853</v>
       </c>
       <c r="E89" t="n">
         <v>88</v>
@@ -2130,17 +2130,17 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2020-10-09</t>
+          <t>2020-10-22</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>18363804782</v>
+        <v>17665602844</v>
       </c>
       <c r="C90" t="n">
-        <v>50410563994</v>
+        <v>46460364776</v>
       </c>
       <c r="D90" t="n">
-        <v>0.3642848507742486</v>
+        <v>0.3802295339085566</v>
       </c>
       <c r="E90" t="n">
         <v>89</v>
@@ -2149,17 +2149,17 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2020-10-12</t>
+          <t>2020-10-23</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>24824121596</v>
+        <v>17466910909</v>
       </c>
       <c r="C91" t="n">
-        <v>69075123930</v>
+        <v>47398504650</v>
       </c>
       <c r="D91" t="n">
-        <v>0.3593786038104905</v>
+        <v>0.3685118557637873</v>
       </c>
       <c r="E91" t="n">
         <v>90</v>
@@ -2168,17 +2168,17 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2020-10-13</t>
+          <t>2020-10-26</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>21950874234</v>
+        <v>16145407434</v>
       </c>
       <c r="C92" t="n">
-        <v>58435290007</v>
+        <v>44150494774</v>
       </c>
       <c r="D92" t="n">
-        <v>0.3756441395494142</v>
+        <v>0.3656902944496094</v>
       </c>
       <c r="E92" t="n">
         <v>91</v>
@@ -2187,17 +2187,17 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2020-10-14</t>
+          <t>2020-10-27</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>21810988673</v>
+        <v>15491813981</v>
       </c>
       <c r="C93" t="n">
-        <v>58022364557</v>
+        <v>43505082864</v>
       </c>
       <c r="D93" t="n">
-        <v>0.3759065808421738</v>
+        <v>0.356092046288672</v>
       </c>
       <c r="E93" t="n">
         <v>92</v>
@@ -2206,17 +2206,17 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2020-10-15</t>
+          <t>2020-10-28</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>20410751440</v>
+        <v>17543172634</v>
       </c>
       <c r="C94" t="n">
-        <v>54415224691</v>
+        <v>49485508785</v>
       </c>
       <c r="D94" t="n">
-        <v>0.3750926612157467</v>
+        <v>0.3545113117906887</v>
       </c>
       <c r="E94" t="n">
         <v>93</v>
@@ -2225,17 +2225,17 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2020-10-16</t>
+          <t>2020-10-29</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>19779199722</v>
+        <v>18553392322</v>
       </c>
       <c r="C95" t="n">
-        <v>51552706029</v>
+        <v>51689467398</v>
       </c>
       <c r="D95" t="n">
-        <v>0.3836694762613156</v>
+        <v>0.3589395142948963</v>
       </c>
       <c r="E95" t="n">
         <v>94</v>
@@ -2244,17 +2244,17 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2020-10-19</t>
+          <t>2020-10-30</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>20562725471</v>
+        <v>20650226596</v>
       </c>
       <c r="C96" t="n">
-        <v>53895497648</v>
+        <v>60348197366</v>
       </c>
       <c r="D96" t="n">
-        <v>0.3815295593947087</v>
+        <v>0.3421846467220954</v>
       </c>
       <c r="E96" t="n">
         <v>95</v>
@@ -2263,17 +2263,17 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2020-10-20</t>
+          <t>2020-11-02</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>18296672779</v>
+        <v>19992661394</v>
       </c>
       <c r="C97" t="n">
-        <v>47922773316</v>
+        <v>56353918211</v>
       </c>
       <c r="D97" t="n">
-        <v>0.3817949486844761</v>
+        <v>0.3547696775784711</v>
       </c>
       <c r="E97" t="n">
         <v>96</v>
@@ -2282,17 +2282,17 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2020-10-21</t>
+          <t>2020-11-03</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>18370049664</v>
+        <v>20249408150</v>
       </c>
       <c r="C98" t="n">
-        <v>49307563396</v>
+        <v>55344378404</v>
       </c>
       <c r="D98" t="n">
-        <v>0.3725604836009853</v>
+        <v>0.365880126111173</v>
       </c>
       <c r="E98" t="n">
         <v>97</v>
@@ -2301,17 +2301,17 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2020-10-22</t>
+          <t>2020-11-04</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>17665602844</v>
+        <v>18257580496</v>
       </c>
       <c r="C99" t="n">
-        <v>46460364776</v>
+        <v>49909415865</v>
       </c>
       <c r="D99" t="n">
-        <v>0.3802295339085566</v>
+        <v>0.3658143494483073</v>
       </c>
       <c r="E99" t="n">
         <v>98</v>
@@ -2320,17 +2320,17 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2020-10-23</t>
+          <t>2020-11-05</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>17466910909</v>
+        <v>21285267389</v>
       </c>
       <c r="C100" t="n">
-        <v>47398504650</v>
+        <v>58980118835</v>
       </c>
       <c r="D100" t="n">
-        <v>0.3685118557637873</v>
+        <v>0.3608888522002924</v>
       </c>
       <c r="E100" t="n">
         <v>99</v>
@@ -2339,17 +2339,17 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2020-10-26</t>
+          <t>2020-11-06</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>16145407434</v>
+        <v>23071856412</v>
       </c>
       <c r="C101" t="n">
-        <v>44150494774</v>
+        <v>59902082650</v>
       </c>
       <c r="D101" t="n">
-        <v>0.3656902944496094</v>
+        <v>0.3851595034984981</v>
       </c>
       <c r="E101" t="n">
         <v>100</v>
@@ -2358,17 +2358,17 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2020-10-27</t>
+          <t>2020-11-09</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>15491813981</v>
+        <v>27202863336</v>
       </c>
       <c r="C102" t="n">
-        <v>43505082864</v>
+        <v>74478178320</v>
       </c>
       <c r="D102" t="n">
-        <v>0.356092046288672</v>
+        <v>0.3652460888492902</v>
       </c>
       <c r="E102" t="n">
         <v>101</v>
@@ -2377,17 +2377,17 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2020-10-28</t>
+          <t>2020-11-10</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>17543172634</v>
+        <v>25309810082</v>
       </c>
       <c r="C103" t="n">
-        <v>49485508785</v>
+        <v>67090114044</v>
       </c>
       <c r="D103" t="n">
-        <v>0.3545113117906887</v>
+        <v>0.3772509622714452</v>
       </c>
       <c r="E103" t="n">
         <v>102</v>
@@ -2396,17 +2396,17 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2020-10-29</t>
+          <t>2020-11-11</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>18553392322</v>
+        <v>23822441228</v>
       </c>
       <c r="C104" t="n">
-        <v>51689467398</v>
+        <v>61988411650</v>
       </c>
       <c r="D104" t="n">
-        <v>0.3589395142948963</v>
+        <v>0.3843047529997488</v>
       </c>
       <c r="E104" t="n">
         <v>103</v>
@@ -2415,17 +2415,17 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2020-10-30</t>
+          <t>2020-11-12</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>20650226596</v>
+        <v>19076439758</v>
       </c>
       <c r="C105" t="n">
-        <v>60348197366</v>
+        <v>51703999860</v>
       </c>
       <c r="D105" t="n">
-        <v>0.3421846467220954</v>
+        <v>0.3689548160616911</v>
       </c>
       <c r="E105" t="n">
         <v>104</v>
@@ -2434,17 +2434,17 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2020-11-02</t>
+          <t>2020-11-13</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>19992661394</v>
+        <v>20119982649</v>
       </c>
       <c r="C106" t="n">
-        <v>56353918211</v>
+        <v>52210418675</v>
       </c>
       <c r="D106" t="n">
-        <v>0.3547696775784711</v>
+        <v>0.3853633653896379</v>
       </c>
       <c r="E106" t="n">
         <v>105</v>
@@ -2453,17 +2453,17 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2020-11-03</t>
+          <t>2020-11-16</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>20249408150</v>
+        <v>23217241543</v>
       </c>
       <c r="C107" t="n">
-        <v>55344378404</v>
+        <v>61350411349</v>
       </c>
       <c r="D107" t="n">
-        <v>0.365880126111173</v>
+        <v>0.3784366075546849</v>
       </c>
       <c r="E107" t="n">
         <v>106</v>
@@ -2472,17 +2472,17 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2020-11-04</t>
+          <t>2020-11-17</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>18257580496</v>
+        <v>24335506367</v>
       </c>
       <c r="C108" t="n">
-        <v>49909415865</v>
+        <v>64241703103</v>
       </c>
       <c r="D108" t="n">
-        <v>0.3658143494483073</v>
+        <v>0.3788116626980203</v>
       </c>
       <c r="E108" t="n">
         <v>107</v>
@@ -2491,17 +2491,17 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2020-11-05</t>
+          <t>2020-11-18</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>21285267389</v>
+        <v>25490702717</v>
       </c>
       <c r="C109" t="n">
-        <v>58980118835</v>
+        <v>63205463709</v>
       </c>
       <c r="D109" t="n">
-        <v>0.3608888522002924</v>
+        <v>0.4032990381078449</v>
       </c>
       <c r="E109" t="n">
         <v>108</v>
@@ -2510,17 +2510,17 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2020-11-06</t>
+          <t>2020-11-19</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>23071856412</v>
+        <v>23177522765</v>
       </c>
       <c r="C110" t="n">
-        <v>59902082650</v>
+        <v>59756276020</v>
       </c>
       <c r="D110" t="n">
-        <v>0.3851595034984981</v>
+        <v>0.3878675899623104</v>
       </c>
       <c r="E110" t="n">
         <v>109</v>
@@ -2529,17 +2529,17 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2020-11-09</t>
+          <t>2020-11-20</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>27202863336</v>
+        <v>22935620159</v>
       </c>
       <c r="C111" t="n">
-        <v>74478178320</v>
+        <v>58875754449</v>
       </c>
       <c r="D111" t="n">
-        <v>0.3652460888492902</v>
+        <v>0.3895596816320637</v>
       </c>
       <c r="E111" t="n">
         <v>110</v>
@@ -2548,17 +2548,17 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2020-11-10</t>
+          <t>2020-11-23</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>25309810082</v>
+        <v>32096579820</v>
       </c>
       <c r="C112" t="n">
-        <v>67090114044</v>
+        <v>77198006469</v>
       </c>
       <c r="D112" t="n">
-        <v>0.3772509622714452</v>
+        <v>0.4157695423506675</v>
       </c>
       <c r="E112" t="n">
         <v>111</v>
@@ -2567,17 +2567,17 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2020-11-11</t>
+          <t>2020-11-24</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>23822441228</v>
+        <v>26709718473</v>
       </c>
       <c r="C113" t="n">
-        <v>61988411650</v>
+        <v>65410116144</v>
       </c>
       <c r="D113" t="n">
-        <v>0.3843047529997488</v>
+        <v>0.408342318399171</v>
       </c>
       <c r="E113" t="n">
         <v>112</v>
@@ -2586,17 +2586,17 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2020-11-12</t>
+          <t>2020-11-25</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>19076439758</v>
+        <v>27089790866</v>
       </c>
       <c r="C114" t="n">
-        <v>51703999860</v>
+        <v>68837443765</v>
       </c>
       <c r="D114" t="n">
-        <v>0.3689548160616911</v>
+        <v>0.3935327836762824</v>
       </c>
       <c r="E114" t="n">
         <v>113</v>
@@ -2605,17 +2605,17 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2020-11-13</t>
+          <t>2020-11-26</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>20119982649</v>
+        <v>21689088930</v>
       </c>
       <c r="C115" t="n">
-        <v>52210418675</v>
+        <v>57127013421</v>
       </c>
       <c r="D115" t="n">
-        <v>0.3853633653896379</v>
+        <v>0.3796643239540867</v>
       </c>
       <c r="E115" t="n">
         <v>114</v>
@@ -2624,17 +2624,17 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2020-11-16</t>
+          <t>2020-11-27</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>23217241543</v>
+        <v>23626364341</v>
       </c>
       <c r="C116" t="n">
-        <v>61350411349</v>
+        <v>58765160877</v>
       </c>
       <c r="D116" t="n">
-        <v>0.3784366075546849</v>
+        <v>0.4020471311301572</v>
       </c>
       <c r="E116" t="n">
         <v>115</v>
@@ -2643,17 +2643,17 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2020-11-17</t>
+          <t>2020-11-30</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>24335506367</v>
+        <v>33970232252</v>
       </c>
       <c r="C117" t="n">
-        <v>64241703103</v>
+        <v>75092505579</v>
       </c>
       <c r="D117" t="n">
-        <v>0.3788116626980203</v>
+        <v>0.4523784629381171</v>
       </c>
       <c r="E117" t="n">
         <v>116</v>
@@ -2662,17 +2662,17 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2020-11-18</t>
+          <t>2020-12-01</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>25490702717</v>
+        <v>28738868941</v>
       </c>
       <c r="C118" t="n">
-        <v>63205463709</v>
+        <v>67936162045</v>
       </c>
       <c r="D118" t="n">
-        <v>0.4032990381078449</v>
+        <v>0.4230275611089682</v>
       </c>
       <c r="E118" t="n">
         <v>117</v>
@@ -2681,17 +2681,17 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2020-11-19</t>
+          <t>2020-12-02</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>23177522765</v>
+        <v>28928357564</v>
       </c>
       <c r="C119" t="n">
-        <v>59756276020</v>
+        <v>69689843826</v>
       </c>
       <c r="D119" t="n">
-        <v>0.3878675899623104</v>
+        <v>0.4151014835996427</v>
       </c>
       <c r="E119" t="n">
         <v>118</v>
@@ -2700,17 +2700,17 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2020-11-20</t>
+          <t>2020-12-03</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>22935620159</v>
+        <v>28497726227</v>
       </c>
       <c r="C120" t="n">
-        <v>58875754449</v>
+        <v>66950741850</v>
       </c>
       <c r="D120" t="n">
-        <v>0.3895596816320637</v>
+        <v>0.4256521352795137</v>
       </c>
       <c r="E120" t="n">
         <v>119</v>
@@ -2719,17 +2719,17 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2020-11-23</t>
+          <t>2020-12-04</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>32096579820</v>
+        <v>23614518756</v>
       </c>
       <c r="C121" t="n">
-        <v>77198006469</v>
+        <v>57124426015</v>
       </c>
       <c r="D121" t="n">
-        <v>0.4157695423506675</v>
+        <v>0.4133874141649876</v>
       </c>
       <c r="E121" t="n">
         <v>120</v>
@@ -2738,17 +2738,17 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2020-11-24</t>
+          <t>2020-12-07</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>26709718473</v>
+        <v>22345056458</v>
       </c>
       <c r="C122" t="n">
-        <v>65410116144</v>
+        <v>56856559648</v>
       </c>
       <c r="D122" t="n">
-        <v>0.408342318399171</v>
+        <v>0.3930075367967857</v>
       </c>
       <c r="E122" t="n">
         <v>121</v>
@@ -2757,17 +2757,17 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2020-11-25</t>
+          <t>2020-12-08</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>27089790866</v>
+        <v>20555717183</v>
       </c>
       <c r="C123" t="n">
-        <v>68837443765</v>
+        <v>51665831943</v>
       </c>
       <c r="D123" t="n">
-        <v>0.3935327836762824</v>
+        <v>0.3978590184259099</v>
       </c>
       <c r="E123" t="n">
         <v>122</v>
@@ -2776,17 +2776,17 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2020-11-26</t>
+          <t>2020-12-09</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>21689088930</v>
+        <v>22167887887</v>
       </c>
       <c r="C124" t="n">
-        <v>57127013421</v>
+        <v>59426788696</v>
       </c>
       <c r="D124" t="n">
-        <v>0.3796643239540867</v>
+        <v>0.3730285343265085</v>
       </c>
       <c r="E124" t="n">
         <v>123</v>
@@ -2795,17 +2795,17 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2020-11-27</t>
+          <t>2020-12-10</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>23626364341</v>
+        <v>21008686040</v>
       </c>
       <c r="C125" t="n">
-        <v>58765160877</v>
+        <v>53530291688</v>
       </c>
       <c r="D125" t="n">
-        <v>0.4020471311301572</v>
+        <v>0.3924635076238444</v>
       </c>
       <c r="E125" t="n">
         <v>124</v>
@@ -2814,17 +2814,17 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2020-11-30</t>
+          <t>2020-12-11</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>33970232252</v>
+        <v>24084146686</v>
       </c>
       <c r="C126" t="n">
-        <v>75092505579</v>
+        <v>64194443337</v>
       </c>
       <c r="D126" t="n">
-        <v>0.4523784629381171</v>
+        <v>0.3751749440300626</v>
       </c>
       <c r="E126" t="n">
         <v>125</v>
@@ -2833,17 +2833,17 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2020-12-01</t>
+          <t>2020-12-14</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>28738868941</v>
+        <v>20561369384</v>
       </c>
       <c r="C127" t="n">
-        <v>67936162045</v>
+        <v>52737085483</v>
       </c>
       <c r="D127" t="n">
-        <v>0.4230275611089682</v>
+        <v>0.3898844465082932</v>
       </c>
       <c r="E127" t="n">
         <v>126</v>
@@ -2852,17 +2852,17 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2020-12-02</t>
+          <t>2020-12-15</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>28928357564</v>
+        <v>20518702233</v>
       </c>
       <c r="C128" t="n">
-        <v>69689843826</v>
+        <v>50712282528</v>
       </c>
       <c r="D128" t="n">
-        <v>0.4151014835996427</v>
+        <v>0.4046101104139991</v>
       </c>
       <c r="E128" t="n">
         <v>127</v>
@@ -2871,17 +2871,17 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2020-12-03</t>
+          <t>2020-12-16</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>28497726227</v>
+        <v>20098821894</v>
       </c>
       <c r="C129" t="n">
-        <v>66950741850</v>
+        <v>51594471274</v>
       </c>
       <c r="D129" t="n">
-        <v>0.4256521352795137</v>
+        <v>0.3895537912824469</v>
       </c>
       <c r="E129" t="n">
         <v>128</v>
@@ -2890,17 +2890,17 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2020-12-04</t>
+          <t>2020-12-17</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>23614518756</v>
+        <v>23623180829</v>
       </c>
       <c r="C130" t="n">
-        <v>57124426015</v>
+        <v>60346809075</v>
       </c>
       <c r="D130" t="n">
-        <v>0.4133874141649876</v>
+        <v>0.3914569998165226</v>
       </c>
       <c r="E130" t="n">
         <v>129</v>
@@ -2909,17 +2909,17 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2020-12-07</t>
+          <t>2020-12-18</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>22345056458</v>
+        <v>24395319589</v>
       </c>
       <c r="C131" t="n">
-        <v>56856559648</v>
+        <v>59011526731</v>
       </c>
       <c r="D131" t="n">
-        <v>0.3930075367967857</v>
+        <v>0.4133992279204094</v>
       </c>
       <c r="E131" t="n">
         <v>130</v>
@@ -2928,17 +2928,17 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>2020-12-08</t>
+          <t>2020-12-21</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>20555717183</v>
+        <v>25669905456</v>
       </c>
       <c r="C132" t="n">
-        <v>51665831943</v>
+        <v>62473191028</v>
       </c>
       <c r="D132" t="n">
-        <v>0.3978590184259099</v>
+        <v>0.410894737944392</v>
       </c>
       <c r="E132" t="n">
         <v>131</v>
@@ -2947,17 +2947,17 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>2020-12-09</t>
+          <t>2020-12-22</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>22167887887</v>
+        <v>27752409533</v>
       </c>
       <c r="C133" t="n">
-        <v>59426788696</v>
+        <v>70592976908</v>
       </c>
       <c r="D133" t="n">
-        <v>0.3730285343265085</v>
+        <v>0.3931327271998773</v>
       </c>
       <c r="E133" t="n">
         <v>132</v>
@@ -2966,17 +2966,17 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2020-12-10</t>
+          <t>2020-12-23</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>21008686040</v>
+        <v>26781996550</v>
       </c>
       <c r="C134" t="n">
-        <v>53530291688</v>
+        <v>66516491988</v>
       </c>
       <c r="D134" t="n">
-        <v>0.3924635076238444</v>
+        <v>0.4026369363380084</v>
       </c>
       <c r="E134" t="n">
         <v>133</v>
@@ -2985,17 +2985,17 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>2020-12-11</t>
+          <t>2020-12-24</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>24084146686</v>
+        <v>23869444669</v>
       </c>
       <c r="C135" t="n">
-        <v>64194443337</v>
+        <v>63015856260</v>
       </c>
       <c r="D135" t="n">
-        <v>0.3751749440300626</v>
+        <v>0.3787847390427572</v>
       </c>
       <c r="E135" t="n">
         <v>134</v>
@@ -3004,17 +3004,17 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>2020-12-14</t>
+          <t>2020-12-25</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>20561369384</v>
+        <v>25870374333</v>
       </c>
       <c r="C136" t="n">
-        <v>52737085483</v>
+        <v>63035613181</v>
       </c>
       <c r="D136" t="n">
-        <v>0.3898844465082932</v>
+        <v>0.4104088629822002</v>
       </c>
       <c r="E136" t="n">
         <v>135</v>
@@ -3023,17 +3023,17 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>2020-12-15</t>
+          <t>2020-12-28</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>20518702233</v>
+        <v>27591719605</v>
       </c>
       <c r="C137" t="n">
-        <v>50712282528</v>
+        <v>68634054637</v>
       </c>
       <c r="D137" t="n">
-        <v>0.4046101104139991</v>
+        <v>0.4020120878903394</v>
       </c>
       <c r="E137" t="n">
         <v>136</v>
@@ -3042,17 +3042,17 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>2020-12-16</t>
+          <t>2020-12-29</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>20098821894</v>
+        <v>28714767727</v>
       </c>
       <c r="C138" t="n">
-        <v>51594471274</v>
+        <v>68080937199</v>
       </c>
       <c r="D138" t="n">
-        <v>0.3895537912824469</v>
+        <v>0.4217739782733451</v>
       </c>
       <c r="E138" t="n">
         <v>137</v>
@@ -3061,17 +3061,17 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>2020-12-17</t>
+          <t>2020-12-30</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>23623180829</v>
+        <v>27431057672</v>
       </c>
       <c r="C139" t="n">
-        <v>60346809075</v>
+        <v>63970764234</v>
       </c>
       <c r="D139" t="n">
-        <v>0.3914569998165226</v>
+        <v>0.4288061585704895</v>
       </c>
       <c r="E139" t="n">
         <v>138</v>
@@ -3080,17 +3080,17 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>2020-12-18</t>
+          <t>2020-12-31</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>24395319589</v>
+        <v>29516497306</v>
       </c>
       <c r="C140" t="n">
-        <v>59011526731</v>
+        <v>70483427194</v>
       </c>
       <c r="D140" t="n">
-        <v>0.4133992279204094</v>
+        <v>0.4187721636287379</v>
       </c>
       <c r="E140" t="n">
         <v>139</v>
@@ -3099,17 +3099,17 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>2020-12-21</t>
+          <t>2021-01-04</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>25669905456</v>
+        <v>32842910849</v>
       </c>
       <c r="C141" t="n">
-        <v>62473191028</v>
+        <v>81262611004</v>
       </c>
       <c r="D141" t="n">
-        <v>0.410894737944392</v>
+        <v>0.4041577109475767</v>
       </c>
       <c r="E141" t="n">
         <v>140</v>
@@ -3118,17 +3118,17 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>2020-12-22</t>
+          <t>2021-01-05</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>27752409533</v>
+        <v>34955476638</v>
       </c>
       <c r="C142" t="n">
-        <v>70592976908</v>
+        <v>86306603527</v>
       </c>
       <c r="D142" t="n">
-        <v>0.3931327271998773</v>
+        <v>0.4050150881799513</v>
       </c>
       <c r="E142" t="n">
         <v>141</v>
@@ -3137,17 +3137,17 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>2020-12-23</t>
+          <t>2021-01-06</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>26781996550</v>
+        <v>31318863380</v>
       </c>
       <c r="C143" t="n">
-        <v>66516491988</v>
+        <v>79924024318</v>
       </c>
       <c r="D143" t="n">
-        <v>0.4026369363380084</v>
+        <v>0.3918579381762507</v>
       </c>
       <c r="E143" t="n">
         <v>142</v>
@@ -3156,17 +3156,17 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>2020-12-24</t>
+          <t>2021-01-07</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>23869444669</v>
+        <v>34820241307</v>
       </c>
       <c r="C144" t="n">
-        <v>63015856260</v>
+        <v>87045282583</v>
       </c>
       <c r="D144" t="n">
-        <v>0.3787847390427572</v>
+        <v>0.4000244501911746</v>
       </c>
       <c r="E144" t="n">
         <v>143</v>
@@ -3175,17 +3175,17 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>2020-12-25</t>
+          <t>2021-01-08</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>25870374333</v>
+        <v>31741361539</v>
       </c>
       <c r="C145" t="n">
-        <v>63035613181</v>
+        <v>76243328872</v>
       </c>
       <c r="D145" t="n">
-        <v>0.4104088629822002</v>
+        <v>0.4163165749529185</v>
       </c>
       <c r="E145" t="n">
         <v>144</v>
@@ -3194,17 +3194,17 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>2020-12-28</t>
+          <t>2021-01-11</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>27591719605</v>
+        <v>33861909952</v>
       </c>
       <c r="C146" t="n">
-        <v>68634054637</v>
+        <v>79843929989</v>
       </c>
       <c r="D146" t="n">
-        <v>0.4020120878903394</v>
+        <v>0.4241012429706943</v>
       </c>
       <c r="E146" t="n">
         <v>145</v>
@@ -3213,17 +3213,17 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>2020-12-29</t>
+          <t>2021-01-12</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>28714767727</v>
+        <v>31336739617</v>
       </c>
       <c r="C147" t="n">
-        <v>68080937199</v>
+        <v>70684174141</v>
       </c>
       <c r="D147" t="n">
-        <v>0.4217739782733451</v>
+        <v>0.4433345936035105</v>
       </c>
       <c r="E147" t="n">
         <v>146</v>
@@ -3232,17 +3232,17 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>2020-12-30</t>
+          <t>2021-01-13</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>27431057672</v>
+        <v>36176556832</v>
       </c>
       <c r="C148" t="n">
-        <v>63970764234</v>
+        <v>81782457644</v>
       </c>
       <c r="D148" t="n">
-        <v>0.4288061585704895</v>
+        <v>0.4423510600461162</v>
       </c>
       <c r="E148" t="n">
         <v>147</v>
@@ -3251,17 +3251,17 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>2020-12-31</t>
+          <t>2021-01-14</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>29516497306</v>
+        <v>32971296424</v>
       </c>
       <c r="C149" t="n">
-        <v>70483427194</v>
+        <v>74034016193</v>
       </c>
       <c r="D149" t="n">
-        <v>0.4187721636287379</v>
+        <v>0.4453533405245341</v>
       </c>
       <c r="E149" t="n">
         <v>148</v>
@@ -3270,17 +3270,17 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>2021-01-04</t>
+          <t>2021-01-15</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>32842910849</v>
+        <v>31268748151</v>
       </c>
       <c r="C150" t="n">
-        <v>81262611004</v>
+        <v>68522530970</v>
       </c>
       <c r="D150" t="n">
-        <v>0.4041577109475767</v>
+        <v>0.4563279801309417</v>
       </c>
       <c r="E150" t="n">
         <v>149</v>
@@ -3289,17 +3289,17 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>2021-01-05</t>
+          <t>2021-01-18</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>34955476638</v>
+        <v>28025154838</v>
       </c>
       <c r="C151" t="n">
-        <v>86306603527</v>
+        <v>66132336803</v>
       </c>
       <c r="D151" t="n">
-        <v>0.4050150881799513</v>
+        <v>0.4237738479056539</v>
       </c>
       <c r="E151" t="n">
         <v>150</v>
@@ -3308,17 +3308,17 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>2021-01-06</t>
+          <t>2021-01-19</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>31318863380</v>
+        <v>30160755219</v>
       </c>
       <c r="C152" t="n">
-        <v>79924024318</v>
+        <v>71588657610</v>
       </c>
       <c r="D152" t="n">
-        <v>0.3918579381762507</v>
+        <v>0.4213063385447102</v>
       </c>
       <c r="E152" t="n">
         <v>151</v>
@@ -3327,17 +3327,17 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>2021-01-07</t>
+          <t>2021-01-20</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>34820241307</v>
+        <v>25498108632</v>
       </c>
       <c r="C153" t="n">
-        <v>87045282583</v>
+        <v>61023142374</v>
       </c>
       <c r="D153" t="n">
-        <v>0.4000244501911746</v>
+        <v>0.4178432581483041</v>
       </c>
       <c r="E153" t="n">
         <v>152</v>
@@ -3346,17 +3346,17 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>2021-01-08</t>
+          <t>2021-01-21</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>31741361539</v>
+        <v>31550851527</v>
       </c>
       <c r="C154" t="n">
-        <v>76243328872</v>
+        <v>73606094304</v>
       </c>
       <c r="D154" t="n">
-        <v>0.4163165749529185</v>
+        <v>0.4286445548474839</v>
       </c>
       <c r="E154" t="n">
         <v>153</v>
@@ -3365,17 +3365,17 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>2021-01-11</t>
+          <t>2021-01-22</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>33861909952</v>
+        <v>29587073243</v>
       </c>
       <c r="C155" t="n">
-        <v>79843929989</v>
+        <v>71863919964</v>
       </c>
       <c r="D155" t="n">
-        <v>0.4241012429706943</v>
+        <v>0.4117097043665521</v>
       </c>
       <c r="E155" t="n">
         <v>154</v>
@@ -3384,17 +3384,17 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>2021-01-12</t>
+          <t>2021-01-25</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>31336739617</v>
+        <v>29768085597</v>
       </c>
       <c r="C156" t="n">
-        <v>70684174141</v>
+        <v>72841620023</v>
       </c>
       <c r="D156" t="n">
-        <v>0.4433345936035105</v>
+        <v>0.4086686373477226</v>
       </c>
       <c r="E156" t="n">
         <v>155</v>
@@ -3403,17 +3403,17 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>2021-01-13</t>
+          <t>2021-01-26</t>
         </is>
       </c>
       <c r="B157" t="n">
-        <v>36176556832</v>
+        <v>25588114580</v>
       </c>
       <c r="C157" t="n">
-        <v>81782457644</v>
+        <v>62625061804</v>
       </c>
       <c r="D157" t="n">
-        <v>0.4423510600461162</v>
+        <v>0.4085922447483418</v>
       </c>
       <c r="E157" t="n">
         <v>156</v>
@@ -3422,17 +3422,17 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>2021-01-14</t>
+          <t>2021-01-27</t>
         </is>
       </c>
       <c r="B158" t="n">
-        <v>32971296424</v>
+        <v>25604690493</v>
       </c>
       <c r="C158" t="n">
-        <v>74034016193</v>
+        <v>60015878129</v>
       </c>
       <c r="D158" t="n">
-        <v>0.4453533405245341</v>
+        <v>0.4266319396004584</v>
       </c>
       <c r="E158" t="n">
         <v>157</v>
@@ -3441,17 +3441,17 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>2021-01-15</t>
+          <t>2021-01-28</t>
         </is>
       </c>
       <c r="B159" t="n">
-        <v>31268748151</v>
+        <v>26286085867</v>
       </c>
       <c r="C159" t="n">
-        <v>68522530970</v>
+        <v>62311898539</v>
       </c>
       <c r="D159" t="n">
-        <v>0.4563279801309417</v>
+        <v>0.4218469743872106</v>
       </c>
       <c r="E159" t="n">
         <v>158</v>
@@ -3460,17 +3460,17 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>2021-01-18</t>
+          <t>2021-01-29</t>
         </is>
       </c>
       <c r="B160" t="n">
-        <v>28025154838</v>
+        <v>27002904913</v>
       </c>
       <c r="C160" t="n">
-        <v>66132336803</v>
+        <v>66018503681</v>
       </c>
       <c r="D160" t="n">
-        <v>0.4237738479056539</v>
+        <v>0.4090202504963981</v>
       </c>
       <c r="E160" t="n">
         <v>159</v>
@@ -3479,17 +3479,17 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>2021-01-19</t>
+          <t>2021-02-01</t>
         </is>
       </c>
       <c r="B161" t="n">
-        <v>30160755219</v>
+        <v>25457673045</v>
       </c>
       <c r="C161" t="n">
-        <v>71588657610</v>
+        <v>61214730247</v>
       </c>
       <c r="D161" t="n">
-        <v>0.4213063385447102</v>
+        <v>0.4158749526834291</v>
       </c>
       <c r="E161" t="n">
         <v>160</v>
@@ -3498,17 +3498,17 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>2021-01-20</t>
+          <t>2021-02-02</t>
         </is>
       </c>
       <c r="B162" t="n">
-        <v>25498108632</v>
+        <v>24585679056</v>
       </c>
       <c r="C162" t="n">
-        <v>61023142374</v>
+        <v>59083806830</v>
       </c>
       <c r="D162" t="n">
-        <v>0.4178432581483041</v>
+        <v>0.4161153516519274</v>
       </c>
       <c r="E162" t="n">
         <v>161</v>
@@ -3517,17 +3517,17 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>2021-01-21</t>
+          <t>2021-02-03</t>
         </is>
       </c>
       <c r="B163" t="n">
-        <v>31550851527</v>
+        <v>27946762653</v>
       </c>
       <c r="C163" t="n">
-        <v>73606094304</v>
+        <v>64252239936</v>
       </c>
       <c r="D163" t="n">
-        <v>0.4286445548474839</v>
+        <v>0.4349539048107436</v>
       </c>
       <c r="E163" t="n">
         <v>162</v>
@@ -3536,17 +3536,17 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>2021-01-22</t>
+          <t>2021-02-04</t>
         </is>
       </c>
       <c r="B164" t="n">
-        <v>29587073243</v>
+        <v>26745949814</v>
       </c>
       <c r="C164" t="n">
-        <v>71863919964</v>
+        <v>65026335158</v>
       </c>
       <c r="D164" t="n">
-        <v>0.4117097043665521</v>
+        <v>0.411309506356357</v>
       </c>
       <c r="E164" t="n">
         <v>163</v>
@@ -3555,17 +3555,17 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>2021-01-25</t>
+          <t>2021-02-05</t>
         </is>
       </c>
       <c r="B165" t="n">
-        <v>29768085597</v>
+        <v>27228530445</v>
       </c>
       <c r="C165" t="n">
-        <v>72841620023</v>
+        <v>60817228192</v>
       </c>
       <c r="D165" t="n">
-        <v>0.4086686373477226</v>
+        <v>0.44771080916479</v>
       </c>
       <c r="E165" t="n">
         <v>164</v>
@@ -3574,17 +3574,17 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>2021-01-26</t>
+          <t>2021-02-08</t>
         </is>
       </c>
       <c r="B166" t="n">
-        <v>25588114580</v>
+        <v>22845413099</v>
       </c>
       <c r="C166" t="n">
-        <v>62625061804</v>
+        <v>53099229697</v>
       </c>
       <c r="D166" t="n">
-        <v>0.4085922447483418</v>
+        <v>0.4302400096830542</v>
       </c>
       <c r="E166" t="n">
         <v>165</v>
@@ -3593,17 +3593,17 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>2021-01-27</t>
+          <t>2021-02-09</t>
         </is>
       </c>
       <c r="B167" t="n">
-        <v>25604690493</v>
+        <v>23052987297</v>
       </c>
       <c r="C167" t="n">
-        <v>60015878129</v>
+        <v>54414450658</v>
       </c>
       <c r="D167" t="n">
-        <v>0.4266319396004584</v>
+        <v>0.4236556101960896</v>
       </c>
       <c r="E167" t="n">
         <v>166</v>
@@ -3612,17 +3612,17 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>2021-01-28</t>
+          <t>2021-02-10</t>
         </is>
       </c>
       <c r="B168" t="n">
-        <v>26286085867</v>
+        <v>23672043794</v>
       </c>
       <c r="C168" t="n">
-        <v>62311898539</v>
+        <v>53724833418</v>
       </c>
       <c r="D168" t="n">
-        <v>0.4218469743872106</v>
+        <v>0.4406164205260971</v>
       </c>
       <c r="E168" t="n">
         <v>167</v>
@@ -3631,17 +3631,17 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>2021-01-29</t>
+          <t>2021-02-18</t>
         </is>
       </c>
       <c r="B169" t="n">
-        <v>27002904913</v>
+        <v>30305438799</v>
       </c>
       <c r="C169" t="n">
-        <v>66018503681</v>
+        <v>70581483088</v>
       </c>
       <c r="D169" t="n">
-        <v>0.4090202504963981</v>
+        <v>0.4293681213982937</v>
       </c>
       <c r="E169" t="n">
         <v>168</v>
@@ -3650,17 +3650,17 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>2021-02-01</t>
+          <t>2021-02-19</t>
         </is>
       </c>
       <c r="B170" t="n">
-        <v>25457673045</v>
+        <v>31871390359</v>
       </c>
       <c r="C170" t="n">
-        <v>61214730247</v>
+        <v>74891926971</v>
       </c>
       <c r="D170" t="n">
-        <v>0.4158749526834291</v>
+        <v>0.4255650995779744</v>
       </c>
       <c r="E170" t="n">
         <v>169</v>
@@ -3669,17 +3669,17 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>2021-02-02</t>
+          <t>2021-02-22</t>
         </is>
       </c>
       <c r="B171" t="n">
-        <v>24585679056</v>
+        <v>41800730539</v>
       </c>
       <c r="C171" t="n">
-        <v>59083806830</v>
+        <v>98345390597</v>
       </c>
       <c r="D171" t="n">
-        <v>0.4161153516519274</v>
+        <v>0.4250400581588124</v>
       </c>
       <c r="E171" t="n">
         <v>170</v>
@@ -3688,17 +3688,17 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>2021-02-03</t>
+          <t>2021-02-23</t>
         </is>
       </c>
       <c r="B172" t="n">
-        <v>27946762653</v>
+        <v>36659765914</v>
       </c>
       <c r="C172" t="n">
-        <v>64252239936</v>
+        <v>79667225639</v>
       </c>
       <c r="D172" t="n">
-        <v>0.4349539048107436</v>
+        <v>0.4601611970287279</v>
       </c>
       <c r="E172" t="n">
         <v>171</v>
@@ -3707,17 +3707,17 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>2021-02-04</t>
+          <t>2021-02-24</t>
         </is>
       </c>
       <c r="B173" t="n">
-        <v>26745949814</v>
+        <v>33328852498</v>
       </c>
       <c r="C173" t="n">
-        <v>65026335158</v>
+        <v>74974298826</v>
       </c>
       <c r="D173" t="n">
-        <v>0.411309506356357</v>
+        <v>0.4445370349557979</v>
       </c>
       <c r="E173" t="n">
         <v>172</v>
@@ -3726,17 +3726,17 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>2021-02-05</t>
+          <t>2021-02-25</t>
         </is>
       </c>
       <c r="B174" t="n">
-        <v>27228530445</v>
+        <v>33009105938</v>
       </c>
       <c r="C174" t="n">
-        <v>60817228192</v>
+        <v>72321851390</v>
       </c>
       <c r="D174" t="n">
-        <v>0.44771080916479</v>
+        <v>0.4564195371603028</v>
       </c>
       <c r="E174" t="n">
         <v>173</v>
@@ -3745,17 +3745,17 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>2021-02-08</t>
+          <t>2021-02-26</t>
         </is>
       </c>
       <c r="B175" t="n">
-        <v>22845413099</v>
+        <v>29437488128</v>
       </c>
       <c r="C175" t="n">
-        <v>53099229697</v>
+        <v>67566280430</v>
       </c>
       <c r="D175" t="n">
-        <v>0.4302400096830542</v>
+        <v>0.4356831238993216</v>
       </c>
       <c r="E175" t="n">
         <v>174</v>
@@ -3764,17 +3764,17 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>2021-02-09</t>
+          <t>2021-03-01</t>
         </is>
       </c>
       <c r="B176" t="n">
-        <v>23052987297</v>
+        <v>28022529242</v>
       </c>
       <c r="C176" t="n">
-        <v>54414450658</v>
+        <v>65847760652</v>
       </c>
       <c r="D176" t="n">
-        <v>0.4236556101960896</v>
+        <v>0.425565409734991</v>
       </c>
       <c r="E176" t="n">
         <v>175</v>
@@ -3783,17 +3783,17 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>2021-02-10</t>
+          <t>2021-03-02</t>
         </is>
       </c>
       <c r="B177" t="n">
-        <v>23672043794</v>
+        <v>30548474585</v>
       </c>
       <c r="C177" t="n">
-        <v>53724833418</v>
+        <v>69441386639</v>
       </c>
       <c r="D177" t="n">
-        <v>0.4406164205260971</v>
+        <v>0.4399174046424243</v>
       </c>
       <c r="E177" t="n">
         <v>176</v>
@@ -3802,17 +3802,17 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>2021-02-18</t>
+          <t>2021-03-03</t>
         </is>
       </c>
       <c r="B178" t="n">
-        <v>30305438799</v>
+        <v>31581683271</v>
       </c>
       <c r="C178" t="n">
-        <v>70581483088</v>
+        <v>69999474895</v>
       </c>
       <c r="D178" t="n">
-        <v>0.4293681213982937</v>
+        <v>0.4511702883253464</v>
       </c>
       <c r="E178" t="n">
         <v>177</v>
@@ -3821,17 +3821,17 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>2021-02-19</t>
+          <t>2021-03-04</t>
         </is>
       </c>
       <c r="B179" t="n">
-        <v>31871390359</v>
+        <v>36100282673</v>
       </c>
       <c r="C179" t="n">
-        <v>74891926971</v>
+        <v>78562142790</v>
       </c>
       <c r="D179" t="n">
-        <v>0.4255650995779744</v>
+        <v>0.4595124495203449</v>
       </c>
       <c r="E179" t="n">
         <v>178</v>
@@ -3840,17 +3840,17 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>2021-02-22</t>
+          <t>2021-03-05</t>
         </is>
       </c>
       <c r="B180" t="n">
-        <v>41800730539</v>
+        <v>32337135967</v>
       </c>
       <c r="C180" t="n">
-        <v>98345390597</v>
+        <v>73514786011</v>
       </c>
       <c r="D180" t="n">
-        <v>0.4250400581588124</v>
+        <v>0.4398725443091326</v>
       </c>
       <c r="E180" t="n">
         <v>179</v>
@@ -3859,17 +3859,17 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>2021-02-23</t>
+          <t>2021-03-08</t>
         </is>
       </c>
       <c r="B181" t="n">
-        <v>36659765914</v>
+        <v>34237890063</v>
       </c>
       <c r="C181" t="n">
-        <v>79667225639</v>
+        <v>78814375242</v>
       </c>
       <c r="D181" t="n">
-        <v>0.4601611970287279</v>
+        <v>0.4344117422471771</v>
       </c>
       <c r="E181" t="n">
         <v>180</v>
@@ -3878,17 +3878,17 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>2021-02-24</t>
+          <t>2021-03-09</t>
         </is>
       </c>
       <c r="B182" t="n">
-        <v>33328852498</v>
+        <v>35838361211</v>
       </c>
       <c r="C182" t="n">
-        <v>74974298826</v>
+        <v>82850202998</v>
       </c>
       <c r="D182" t="n">
-        <v>0.4445370349557979</v>
+        <v>0.4325681762284292</v>
       </c>
       <c r="E182" t="n">
         <v>181</v>
@@ -3897,17 +3897,17 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>2021-02-25</t>
+          <t>2021-03-10</t>
         </is>
       </c>
       <c r="B183" t="n">
-        <v>33009105938</v>
+        <v>26975456721</v>
       </c>
       <c r="C183" t="n">
-        <v>72321851390</v>
+        <v>62127335207</v>
       </c>
       <c r="D183" t="n">
-        <v>0.4564195371603028</v>
+        <v>0.4341962620981791</v>
       </c>
       <c r="E183" t="n">
         <v>182</v>
@@ -3916,17 +3916,17 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>2021-02-26</t>
+          <t>2021-03-11</t>
         </is>
       </c>
       <c r="B184" t="n">
-        <v>29437488128</v>
+        <v>30680047969</v>
       </c>
       <c r="C184" t="n">
-        <v>67566280430</v>
+        <v>66598157167</v>
       </c>
       <c r="D184" t="n">
-        <v>0.4356831238993216</v>
+        <v>0.4606741278451207</v>
       </c>
       <c r="E184" t="n">
         <v>183</v>
@@ -3935,17 +3935,17 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>2021-03-01</t>
+          <t>2021-03-12</t>
         </is>
       </c>
       <c r="B185" t="n">
-        <v>28022529242</v>
+        <v>33862968625</v>
       </c>
       <c r="C185" t="n">
-        <v>65847760652</v>
+        <v>72238010975</v>
       </c>
       <c r="D185" t="n">
-        <v>0.425565409734991</v>
+        <v>0.4687693939513262</v>
       </c>
       <c r="E185" t="n">
         <v>184</v>
@@ -3954,17 +3954,17 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>2021-03-02</t>
+          <t>2021-03-15</t>
         </is>
       </c>
       <c r="B186" t="n">
-        <v>30548474585</v>
+        <v>34591765793</v>
       </c>
       <c r="C186" t="n">
-        <v>69441386639</v>
+        <v>71723136959</v>
       </c>
       <c r="D186" t="n">
-        <v>0.4399174046424243</v>
+        <v>0.4822957731585852</v>
       </c>
       <c r="E186" t="n">
         <v>185</v>
@@ -3973,17 +3973,17 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>2021-03-03</t>
+          <t>2021-03-16</t>
         </is>
       </c>
       <c r="B187" t="n">
-        <v>31581683271</v>
+        <v>29977825317</v>
       </c>
       <c r="C187" t="n">
-        <v>69999474895</v>
+        <v>67049266583</v>
       </c>
       <c r="D187" t="n">
-        <v>0.4511702883253464</v>
+        <v>0.447101465008429</v>
       </c>
       <c r="E187" t="n">
         <v>186</v>
@@ -3992,17 +3992,17 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>2021-03-04</t>
+          <t>2021-03-17</t>
         </is>
       </c>
       <c r="B188" t="n">
-        <v>36100282673</v>
+        <v>27491185060</v>
       </c>
       <c r="C188" t="n">
-        <v>78562142790</v>
+        <v>62515062852</v>
       </c>
       <c r="D188" t="n">
-        <v>0.4595124495203449</v>
+        <v>0.4397529780156095</v>
       </c>
       <c r="E188" t="n">
         <v>187</v>
@@ -4011,17 +4011,17 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>2021-03-05</t>
+          <t>2021-03-18</t>
         </is>
       </c>
       <c r="B189" t="n">
-        <v>32337135967</v>
+        <v>26739276351</v>
       </c>
       <c r="C189" t="n">
-        <v>73514786011</v>
+        <v>62832911819</v>
       </c>
       <c r="D189" t="n">
-        <v>0.4398725443091326</v>
+        <v>0.4255616296762858</v>
       </c>
       <c r="E189" t="n">
         <v>188</v>
@@ -4030,17 +4030,17 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>2021-03-08</t>
+          <t>2021-03-19</t>
         </is>
       </c>
       <c r="B190" t="n">
-        <v>34237890063</v>
+        <v>28358235249</v>
       </c>
       <c r="C190" t="n">
-        <v>78814375242</v>
+        <v>65875538395</v>
       </c>
       <c r="D190" t="n">
-        <v>0.4344117422471771</v>
+        <v>0.4304820262562349</v>
       </c>
       <c r="E190" t="n">
         <v>189</v>
@@ -4049,17 +4049,17 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>2021-03-09</t>
+          <t>2021-03-22</t>
         </is>
       </c>
       <c r="B191" t="n">
-        <v>35838361211</v>
+        <v>29121013208</v>
       </c>
       <c r="C191" t="n">
-        <v>82850202998</v>
+        <v>67358226346</v>
       </c>
       <c r="D191" t="n">
-        <v>0.4325681762284292</v>
+        <v>0.4323304633707791</v>
       </c>
       <c r="E191" t="n">
         <v>190</v>
@@ -4068,17 +4068,17 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>2021-03-10</t>
+          <t>2021-03-23</t>
         </is>
       </c>
       <c r="B192" t="n">
-        <v>26975456721</v>
+        <v>29320271653</v>
       </c>
       <c r="C192" t="n">
-        <v>62127335207</v>
+        <v>70323191299</v>
       </c>
       <c r="D192" t="n">
-        <v>0.4341962620981791</v>
+        <v>0.4169360222623591</v>
       </c>
       <c r="E192" t="n">
         <v>191</v>
@@ -4087,17 +4087,17 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>2021-03-11</t>
+          <t>2021-03-24</t>
         </is>
       </c>
       <c r="B193" t="n">
-        <v>30680047969</v>
+        <v>28494202046</v>
       </c>
       <c r="C193" t="n">
-        <v>66598157167</v>
+        <v>67303523996</v>
       </c>
       <c r="D193" t="n">
-        <v>0.4606741278451207</v>
+        <v>0.423368649280437</v>
       </c>
       <c r="E193" t="n">
         <v>192</v>
@@ -4106,17 +4106,17 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>2021-03-12</t>
+          <t>2021-03-25</t>
         </is>
       </c>
       <c r="B194" t="n">
-        <v>33862968625</v>
+        <v>25857769578</v>
       </c>
       <c r="C194" t="n">
-        <v>72238010975</v>
+        <v>60650502617</v>
       </c>
       <c r="D194" t="n">
-        <v>0.4687693939513262</v>
+        <v>0.426340565407816</v>
       </c>
       <c r="E194" t="n">
         <v>193</v>
@@ -4125,17 +4125,17 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>2021-03-15</t>
+          <t>2021-03-26</t>
         </is>
       </c>
       <c r="B195" t="n">
-        <v>34591765793</v>
+        <v>25857588064</v>
       </c>
       <c r="C195" t="n">
-        <v>71723136959</v>
+        <v>61284664475</v>
       </c>
       <c r="D195" t="n">
-        <v>0.4822957731585852</v>
+        <v>0.4219259138564452</v>
       </c>
       <c r="E195" t="n">
         <v>194</v>
@@ -4144,17 +4144,17 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>2021-03-16</t>
+          <t>2021-03-29</t>
         </is>
       </c>
       <c r="B196" t="n">
-        <v>29977825317</v>
+        <v>26030305012</v>
       </c>
       <c r="C196" t="n">
-        <v>67049266583</v>
+        <v>62965892538</v>
       </c>
       <c r="D196" t="n">
-        <v>0.447101465008429</v>
+        <v>0.4134032563151658</v>
       </c>
       <c r="E196" t="n">
         <v>195</v>
@@ -4163,17 +4163,17 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>2021-03-17</t>
+          <t>2021-03-30</t>
         </is>
       </c>
       <c r="B197" t="n">
-        <v>27491185060</v>
+        <v>25780001010</v>
       </c>
       <c r="C197" t="n">
-        <v>62515062852</v>
+        <v>62868502600</v>
       </c>
       <c r="D197" t="n">
-        <v>0.4397529780156095</v>
+        <v>0.4100622719460158</v>
       </c>
       <c r="E197" t="n">
         <v>196</v>
@@ -4182,17 +4182,17 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>2021-03-18</t>
+          <t>2021-03-31</t>
         </is>
       </c>
       <c r="B198" t="n">
-        <v>26739276351</v>
+        <v>25340940136</v>
       </c>
       <c r="C198" t="n">
-        <v>62832911819</v>
+        <v>58944651908</v>
       </c>
       <c r="D198" t="n">
-        <v>0.4255616296762858</v>
+        <v>0.4299107606157687</v>
       </c>
       <c r="E198" t="n">
         <v>197</v>
@@ -4201,17 +4201,17 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>2021-03-19</t>
+          <t>2021-04-01</t>
         </is>
       </c>
       <c r="B199" t="n">
-        <v>28358235249</v>
+        <v>24459982838</v>
       </c>
       <c r="C199" t="n">
-        <v>65875538395</v>
+        <v>57742915146</v>
       </c>
       <c r="D199" t="n">
-        <v>0.4304820262562349</v>
+        <v>0.4236014544148696</v>
       </c>
       <c r="E199" t="n">
         <v>198</v>
@@ -4220,17 +4220,17 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>2021-03-22</t>
+          <t>2021-04-02</t>
         </is>
       </c>
       <c r="B200" t="n">
-        <v>29121013208</v>
+        <v>23776468616</v>
       </c>
       <c r="C200" t="n">
-        <v>67358226346</v>
+        <v>57637646459</v>
       </c>
       <c r="D200" t="n">
-        <v>0.4323304633707791</v>
+        <v>0.4125162992717471</v>
       </c>
       <c r="E200" t="n">
         <v>199</v>
@@ -4239,17 +4239,17 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>2021-03-23</t>
+          <t>2021-04-06</t>
         </is>
       </c>
       <c r="B201" t="n">
-        <v>29320271653</v>
+        <v>21609152872</v>
       </c>
       <c r="C201" t="n">
-        <v>70323191299</v>
+        <v>54009467026</v>
       </c>
       <c r="D201" t="n">
-        <v>0.4169360222623591</v>
+        <v>0.4000993540928189</v>
       </c>
       <c r="E201" t="n">
         <v>200</v>
@@ -4258,17 +4258,17 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>2021-03-24</t>
+          <t>2021-04-07</t>
         </is>
       </c>
       <c r="B202" t="n">
-        <v>28494202046</v>
+        <v>28192988226</v>
       </c>
       <c r="C202" t="n">
-        <v>67303523996</v>
+        <v>64777711487</v>
       </c>
       <c r="D202" t="n">
-        <v>0.423368649280437</v>
+        <v>0.4352266787266473</v>
       </c>
       <c r="E202" t="n">
         <v>201</v>
@@ -4277,17 +4277,17 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>2021-03-25</t>
+          <t>2021-04-08</t>
         </is>
       </c>
       <c r="B203" t="n">
-        <v>25857769578</v>
+        <v>31610774016</v>
       </c>
       <c r="C203" t="n">
-        <v>60650502617</v>
+        <v>70183037971</v>
       </c>
       <c r="D203" t="n">
-        <v>0.426340565407816</v>
+        <v>0.4504047549076137</v>
       </c>
       <c r="E203" t="n">
         <v>202</v>
@@ -4296,17 +4296,17 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>2021-03-26</t>
+          <t>2021-04-09</t>
         </is>
       </c>
       <c r="B204" t="n">
-        <v>25857588064</v>
+        <v>27363203695</v>
       </c>
       <c r="C204" t="n">
-        <v>61284664475</v>
+        <v>60908586933</v>
       </c>
       <c r="D204" t="n">
-        <v>0.4219259138564452</v>
+        <v>0.4492503450309851</v>
       </c>
       <c r="E204" t="n">
         <v>203</v>
@@ -4315,17 +4315,17 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>2021-03-29</t>
+          <t>2021-04-12</t>
         </is>
       </c>
       <c r="B205" t="n">
-        <v>26030305012</v>
+        <v>29441281600</v>
       </c>
       <c r="C205" t="n">
-        <v>62965892538</v>
+        <v>66662877908</v>
       </c>
       <c r="D205" t="n">
-        <v>0.4134032563151658</v>
+        <v>0.4416443232563598</v>
       </c>
       <c r="E205" t="n">
         <v>204</v>
@@ -4334,17 +4334,17 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>2021-03-30</t>
+          <t>2021-04-13</t>
         </is>
       </c>
       <c r="B206" t="n">
-        <v>25780001010</v>
+        <v>26500289609</v>
       </c>
       <c r="C206" t="n">
-        <v>62868502600</v>
+        <v>60099497250</v>
       </c>
       <c r="D206" t="n">
-        <v>0.4100622719460158</v>
+        <v>0.4409402877159675</v>
       </c>
       <c r="E206" t="n">
         <v>205</v>
@@ -4353,17 +4353,17 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>2021-03-31</t>
+          <t>2021-04-14</t>
         </is>
       </c>
       <c r="B207" t="n">
-        <v>25340940136</v>
+        <v>24875678254</v>
       </c>
       <c r="C207" t="n">
-        <v>58944651908</v>
+        <v>56149660115</v>
       </c>
       <c r="D207" t="n">
-        <v>0.4299107606157687</v>
+        <v>0.4430245562137362</v>
       </c>
       <c r="E207" t="n">
         <v>206</v>
@@ -4372,17 +4372,17 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>2021-04-01</t>
+          <t>2021-04-15</t>
         </is>
       </c>
       <c r="B208" t="n">
-        <v>24459982838</v>
+        <v>23587218127</v>
       </c>
       <c r="C208" t="n">
-        <v>57742915146</v>
+        <v>56730832399</v>
       </c>
       <c r="D208" t="n">
-        <v>0.4236014544148696</v>
+        <v>0.4157742294543835</v>
       </c>
       <c r="E208" t="n">
         <v>207</v>
@@ -4391,17 +4391,17 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>2021-04-02</t>
+          <t>2021-04-16</t>
         </is>
       </c>
       <c r="B209" t="n">
-        <v>23776468616</v>
+        <v>23064238930</v>
       </c>
       <c r="C209" t="n">
-        <v>57637646459</v>
+        <v>60757105467</v>
       </c>
       <c r="D209" t="n">
-        <v>0.4125162992717471</v>
+        <v>0.3796138534368998</v>
       </c>
       <c r="E209" t="n">
         <v>208</v>
@@ -4410,17 +4410,17 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>2021-04-06</t>
+          <t>2021-04-19</t>
         </is>
       </c>
       <c r="B210" t="n">
-        <v>21609152872</v>
+        <v>26349229565</v>
       </c>
       <c r="C210" t="n">
-        <v>54009467026</v>
+        <v>68717257011</v>
       </c>
       <c r="D210" t="n">
-        <v>0.4000993540928189</v>
+        <v>0.3834441406877186</v>
       </c>
       <c r="E210" t="n">
         <v>209</v>
@@ -4429,17 +4429,17 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>2021-04-07</t>
+          <t>2021-04-20</t>
         </is>
       </c>
       <c r="B211" t="n">
-        <v>28192988226</v>
+        <v>26332452757</v>
       </c>
       <c r="C211" t="n">
-        <v>64777711487</v>
+        <v>66152179163</v>
       </c>
       <c r="D211" t="n">
-        <v>0.4352266787266473</v>
+        <v>0.3980587350284626</v>
       </c>
       <c r="E211" t="n">
         <v>210</v>
@@ -4448,17 +4448,17 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>2021-04-08</t>
+          <t>2021-04-21</t>
         </is>
       </c>
       <c r="B212" t="n">
-        <v>31610774016</v>
+        <v>23796108657</v>
       </c>
       <c r="C212" t="n">
-        <v>70183037971</v>
+        <v>58645267418</v>
       </c>
       <c r="D212" t="n">
-        <v>0.4504047549076137</v>
+        <v>0.4057634947316526</v>
       </c>
       <c r="E212" t="n">
         <v>211</v>
@@ -4467,17 +4467,17 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>2021-04-09</t>
+          <t>2021-04-22</t>
         </is>
       </c>
       <c r="B213" t="n">
-        <v>27363203695</v>
+        <v>23283868400</v>
       </c>
       <c r="C213" t="n">
-        <v>60908586933</v>
+        <v>57343158813</v>
       </c>
       <c r="D213" t="n">
-        <v>0.4492503450309851</v>
+        <v>0.406044398006226</v>
       </c>
       <c r="E213" t="n">
         <v>212</v>
@@ -4486,17 +4486,17 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>2021-04-12</t>
+          <t>2021-04-23</t>
         </is>
       </c>
       <c r="B214" t="n">
-        <v>29441281600</v>
+        <v>23110619160</v>
       </c>
       <c r="C214" t="n">
-        <v>66662877908</v>
+        <v>58758936747</v>
       </c>
       <c r="D214" t="n">
-        <v>0.4416443232563598</v>
+        <v>0.3933124123655954</v>
       </c>
       <c r="E214" t="n">
         <v>213</v>
@@ -4505,17 +4505,17 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>2021-04-13</t>
+          <t>2021-04-26</t>
         </is>
       </c>
       <c r="B215" t="n">
-        <v>26500289609</v>
+        <v>26080656908</v>
       </c>
       <c r="C215" t="n">
-        <v>60099497250</v>
+        <v>64990659217</v>
       </c>
       <c r="D215" t="n">
-        <v>0.4409402877159675</v>
+        <v>0.4012985438556365</v>
       </c>
       <c r="E215" t="n">
         <v>214</v>
@@ -4524,17 +4524,17 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>2021-04-14</t>
+          <t>2021-04-27</t>
         </is>
       </c>
       <c r="B216" t="n">
-        <v>24875678254</v>
+        <v>22805398723</v>
       </c>
       <c r="C216" t="n">
-        <v>56149660115</v>
+        <v>58465572266</v>
       </c>
       <c r="D216" t="n">
-        <v>0.4430245562137362</v>
+        <v>0.3900654323409783</v>
       </c>
       <c r="E216" t="n">
         <v>215</v>
@@ -4543,17 +4543,17 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>2021-04-15</t>
+          <t>2021-04-28</t>
         </is>
       </c>
       <c r="B217" t="n">
-        <v>23587218127</v>
+        <v>21764975470</v>
       </c>
       <c r="C217" t="n">
-        <v>56730832399</v>
+        <v>56258757783</v>
       </c>
       <c r="D217" t="n">
-        <v>0.4157742294543835</v>
+        <v>0.3868726635229197</v>
       </c>
       <c r="E217" t="n">
         <v>216</v>
@@ -4562,17 +4562,17 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>2021-04-16</t>
+          <t>2021-04-29</t>
         </is>
       </c>
       <c r="B218" t="n">
-        <v>23064238930</v>
+        <v>23871290845</v>
       </c>
       <c r="C218" t="n">
-        <v>60757105467</v>
+        <v>59672070298</v>
       </c>
       <c r="D218" t="n">
-        <v>0.3796138534368998</v>
+        <v>0.400041270996426</v>
       </c>
       <c r="E218" t="n">
         <v>217</v>
@@ -4581,17 +4581,17 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>2021-04-19</t>
+          <t>2021-04-30</t>
         </is>
       </c>
       <c r="B219" t="n">
-        <v>26349229565</v>
+        <v>26727927563</v>
       </c>
       <c r="C219" t="n">
-        <v>68717257011</v>
+        <v>64623812735</v>
       </c>
       <c r="D219" t="n">
-        <v>0.3834441406877186</v>
+        <v>0.413592550978105</v>
       </c>
       <c r="E219" t="n">
         <v>218</v>
@@ -4600,17 +4600,17 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>2021-04-20</t>
+          <t>2021-05-06</t>
         </is>
       </c>
       <c r="B220" t="n">
-        <v>26332452757</v>
+        <v>28245158344</v>
       </c>
       <c r="C220" t="n">
-        <v>66152179163</v>
+        <v>64995398044</v>
       </c>
       <c r="D220" t="n">
-        <v>0.3980587350284626</v>
+        <v>0.4345716649797089</v>
       </c>
       <c r="E220" t="n">
         <v>219</v>
@@ -4619,17 +4619,17 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>2021-04-21</t>
+          <t>2021-05-07</t>
         </is>
       </c>
       <c r="B221" t="n">
-        <v>23796108657</v>
+        <v>33809492530</v>
       </c>
       <c r="C221" t="n">
-        <v>58645267418</v>
+        <v>72689004129</v>
       </c>
       <c r="D221" t="n">
-        <v>0.4057634947316526</v>
+        <v>0.4651252680529072</v>
       </c>
       <c r="E221" t="n">
         <v>220</v>
@@ -4638,17 +4638,17 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>2021-04-22</t>
+          <t>2021-05-10</t>
         </is>
       </c>
       <c r="B222" t="n">
-        <v>23283868400</v>
+        <v>34980447442</v>
       </c>
       <c r="C222" t="n">
-        <v>57343158813</v>
+        <v>74391256531</v>
       </c>
       <c r="D222" t="n">
-        <v>0.406044398006226</v>
+        <v>0.4702225647636843</v>
       </c>
       <c r="E222" t="n">
         <v>221</v>
@@ -4657,17 +4657,17 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>2021-04-23</t>
+          <t>2021-05-11</t>
         </is>
       </c>
       <c r="B223" t="n">
-        <v>23110619160</v>
+        <v>33682768573</v>
       </c>
       <c r="C223" t="n">
-        <v>58758936747</v>
+        <v>73459473614</v>
       </c>
       <c r="D223" t="n">
-        <v>0.3933124123655954</v>
+        <v>0.4585217796412401</v>
       </c>
       <c r="E223" t="n">
         <v>222</v>
@@ -4676,17 +4676,17 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>2021-04-26</t>
+          <t>2021-05-12</t>
         </is>
       </c>
       <c r="B224" t="n">
-        <v>26080656908</v>
+        <v>28011409229</v>
       </c>
       <c r="C224" t="n">
-        <v>64990659217</v>
+        <v>66061705250</v>
       </c>
       <c r="D224" t="n">
-        <v>0.4012985438556365</v>
+        <v>0.4240188642269418</v>
       </c>
       <c r="E224" t="n">
         <v>223</v>
@@ -4695,17 +4695,17 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>2021-04-27</t>
+          <t>2021-05-13</t>
         </is>
       </c>
       <c r="B225" t="n">
-        <v>22805398723</v>
+        <v>29021959092</v>
       </c>
       <c r="C225" t="n">
-        <v>58465572266</v>
+        <v>69247970457</v>
       </c>
       <c r="D225" t="n">
-        <v>0.3900654323409783</v>
+        <v>0.4191019448002651</v>
       </c>
       <c r="E225" t="n">
         <v>224</v>
@@ -4714,17 +4714,17 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>2021-04-28</t>
+          <t>2021-05-14</t>
         </is>
       </c>
       <c r="B226" t="n">
-        <v>21764975470</v>
+        <v>29087549466</v>
       </c>
       <c r="C226" t="n">
-        <v>56258757783</v>
+        <v>72865719627</v>
       </c>
       <c r="D226" t="n">
-        <v>0.3868726635229197</v>
+        <v>0.3991938817718307</v>
       </c>
       <c r="E226" t="n">
         <v>225</v>
@@ -4733,17 +4733,17 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>2021-04-29</t>
+          <t>2021-05-17</t>
         </is>
       </c>
       <c r="B227" t="n">
-        <v>23871290845</v>
+        <v>26738086558</v>
       </c>
       <c r="C227" t="n">
-        <v>59672070298</v>
+        <v>68865623007</v>
       </c>
       <c r="D227" t="n">
-        <v>0.400041270996426</v>
+        <v>0.3882646433806625</v>
       </c>
       <c r="E227" t="n">
         <v>226</v>
@@ -4752,17 +4752,17 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>2021-04-30</t>
+          <t>2021-05-18</t>
         </is>
       </c>
       <c r="B228" t="n">
-        <v>26727927563</v>
+        <v>23944078372</v>
       </c>
       <c r="C228" t="n">
-        <v>64623812735</v>
+        <v>58781317109</v>
       </c>
       <c r="D228" t="n">
-        <v>0.413592550978105</v>
+        <v>0.4073416444139855</v>
       </c>
       <c r="E228" t="n">
         <v>227</v>
@@ -4771,17 +4771,17 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>2021-05-06</t>
+          <t>2021-05-19</t>
         </is>
       </c>
       <c r="B229" t="n">
-        <v>28245158344</v>
+        <v>25053218592</v>
       </c>
       <c r="C229" t="n">
-        <v>64995398044</v>
+        <v>60763325645</v>
       </c>
       <c r="D229" t="n">
-        <v>0.4345716649797089</v>
+        <v>0.4123082192434532</v>
       </c>
       <c r="E229" t="n">
         <v>228</v>
@@ -4790,17 +4790,17 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>2021-05-07</t>
+          <t>2021-05-20</t>
         </is>
       </c>
       <c r="B230" t="n">
-        <v>33809492530</v>
+        <v>28722723747</v>
       </c>
       <c r="C230" t="n">
-        <v>72689004129</v>
+        <v>68566840023</v>
       </c>
       <c r="D230" t="n">
-        <v>0.4651252680529072</v>
+        <v>0.4189010859675796</v>
       </c>
       <c r="E230" t="n">
         <v>229</v>
@@ -4809,17 +4809,17 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>2021-05-10</t>
+          <t>2021-05-21</t>
         </is>
       </c>
       <c r="B231" t="n">
-        <v>34980447442</v>
+        <v>25545536529</v>
       </c>
       <c r="C231" t="n">
-        <v>74391256531</v>
+        <v>61418379955</v>
       </c>
       <c r="D231" t="n">
-        <v>0.4702225647636843</v>
+        <v>0.4159265768279251</v>
       </c>
       <c r="E231" t="n">
         <v>230</v>
@@ -4828,17 +4828,17 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>2021-05-11</t>
+          <t>2021-05-24</t>
         </is>
       </c>
       <c r="B232" t="n">
-        <v>33682768573</v>
+        <v>25923087661</v>
       </c>
       <c r="C232" t="n">
-        <v>73459473614</v>
+        <v>63386616118</v>
       </c>
       <c r="D232" t="n">
-        <v>0.4585217796412401</v>
+        <v>0.4089678428761964</v>
       </c>
       <c r="E232" t="n">
         <v>231</v>
@@ -4847,17 +4847,17 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>2021-05-12</t>
+          <t>2021-05-25</t>
         </is>
       </c>
       <c r="B233" t="n">
-        <v>28011409229</v>
+        <v>29902389375</v>
       </c>
       <c r="C233" t="n">
-        <v>66061705250</v>
+        <v>71817033145</v>
       </c>
       <c r="D233" t="n">
-        <v>0.4240188642269418</v>
+        <v>0.4163690431854305</v>
       </c>
       <c r="E233" t="n">
         <v>232</v>
@@ -4866,17 +4866,17 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>2021-05-13</t>
+          <t>2021-05-26</t>
         </is>
       </c>
       <c r="B234" t="n">
-        <v>29021959092</v>
+        <v>29496722494</v>
       </c>
       <c r="C234" t="n">
-        <v>69247970457</v>
+        <v>72933630614</v>
       </c>
       <c r="D234" t="n">
-        <v>0.4191019448002651</v>
+        <v>0.4044323893611015</v>
       </c>
       <c r="E234" t="n">
         <v>233</v>
@@ -4885,17 +4885,17 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>2021-05-14</t>
+          <t>2021-05-27</t>
         </is>
       </c>
       <c r="B235" t="n">
-        <v>29087549466</v>
+        <v>26896810605</v>
       </c>
       <c r="C235" t="n">
-        <v>72865719627</v>
+        <v>68968444971</v>
       </c>
       <c r="D235" t="n">
-        <v>0.3991938817718307</v>
+        <v>0.3899871980049663</v>
       </c>
       <c r="E235" t="n">
         <v>234</v>
@@ -4904,17 +4904,17 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>2021-05-17</t>
+          <t>2021-05-27</t>
         </is>
       </c>
       <c r="B236" t="n">
-        <v>26738086558</v>
+        <v>26896810605</v>
       </c>
       <c r="C236" t="n">
-        <v>68865623007</v>
+        <v>68968444971</v>
       </c>
       <c r="D236" t="n">
-        <v>0.3882646433806625</v>
+        <v>0.3899871980049663</v>
       </c>
       <c r="E236" t="n">
         <v>235</v>
@@ -4923,17 +4923,17 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>2021-05-18</t>
+          <t>2021-05-28</t>
         </is>
       </c>
       <c r="B237" t="n">
-        <v>23944078372</v>
+        <v>29791926043</v>
       </c>
       <c r="C237" t="n">
-        <v>58781317109</v>
+        <v>73972884560</v>
       </c>
       <c r="D237" t="n">
-        <v>0.4073416444139855</v>
+        <v>0.4027411695543051</v>
       </c>
       <c r="E237" t="n">
         <v>236</v>
@@ -4942,17 +4942,17 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>2021-05-19</t>
+          <t>2021-05-31</t>
         </is>
       </c>
       <c r="B238" t="n">
-        <v>25053218592</v>
+        <v>27775314244</v>
       </c>
       <c r="C238" t="n">
-        <v>60763325645</v>
+        <v>70615016083</v>
       </c>
       <c r="D238" t="n">
-        <v>0.4123082192434532</v>
+        <v>0.3933343895490053</v>
       </c>
       <c r="E238" t="n">
         <v>237</v>
@@ -4961,17 +4961,17 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>2021-05-20</t>
+          <t>2021-06-01</t>
         </is>
       </c>
       <c r="B239" t="n">
-        <v>28722723747</v>
+        <v>28722955321</v>
       </c>
       <c r="C239" t="n">
-        <v>68566840023</v>
+        <v>75176823860</v>
       </c>
       <c r="D239" t="n">
-        <v>0.4189010859675796</v>
+        <v>0.3820719451315218</v>
       </c>
       <c r="E239" t="n">
         <v>238</v>
@@ -4980,17 +4980,17 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>2021-05-21</t>
+          <t>2021-06-02</t>
         </is>
       </c>
       <c r="B240" t="n">
-        <v>25545536529</v>
+        <v>29120888356</v>
       </c>
       <c r="C240" t="n">
-        <v>61418379955</v>
+        <v>75272955834</v>
       </c>
       <c r="D240" t="n">
-        <v>0.4159265768279251</v>
+        <v>0.3868705305026218</v>
       </c>
       <c r="E240" t="n">
         <v>239</v>
@@ -4999,17 +4999,17 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>2021-05-24</t>
+          <t>2021-06-03</t>
         </is>
       </c>
       <c r="B241" t="n">
-        <v>25923087661</v>
+        <v>29199450254</v>
       </c>
       <c r="C241" t="n">
-        <v>63386616118</v>
+        <v>72798616374</v>
       </c>
       <c r="D241" t="n">
-        <v>0.4089678428761964</v>
+        <v>0.4010989728704318</v>
       </c>
       <c r="E241" t="n">
         <v>240</v>
@@ -5018,17 +5018,17 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>2021-05-25</t>
+          <t>2021-06-04</t>
         </is>
       </c>
       <c r="B242" t="n">
-        <v>29902389375</v>
+        <v>27330244158</v>
       </c>
       <c r="C242" t="n">
-        <v>71817033145</v>
+        <v>68930352581</v>
       </c>
       <c r="D242" t="n">
-        <v>0.4163690431854305</v>
+        <v>0.3964907059757783</v>
       </c>
       <c r="E242" t="n">
         <v>241</v>
@@ -5037,17 +5037,17 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>2021-05-26</t>
+          <t>2021-06-07</t>
         </is>
       </c>
       <c r="B243" t="n">
-        <v>29496722494</v>
+        <v>25294989410</v>
       </c>
       <c r="C243" t="n">
-        <v>72933630614</v>
+        <v>66558910303</v>
       </c>
       <c r="D243" t="n">
-        <v>0.4044323893611015</v>
+        <v>0.3800391156472988</v>
       </c>
       <c r="E243" t="n">
         <v>242</v>
@@ -5056,17 +5056,17 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>2021-05-27</t>
+          <t>2021-06-08</t>
         </is>
       </c>
       <c r="B244" t="n">
-        <v>26896810605</v>
+        <v>25589368881</v>
       </c>
       <c r="C244" t="n">
-        <v>68968444971</v>
+        <v>68255065080</v>
       </c>
       <c r="D244" t="n">
-        <v>0.3899871980049663</v>
+        <v>0.3749079844991337</v>
       </c>
       <c r="E244" t="n">
         <v>243</v>
@@ -5075,17 +5075,17 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>2021-05-27</t>
+          <t>2021-06-09</t>
         </is>
       </c>
       <c r="B245" t="n">
-        <v>26896810605</v>
+        <v>25270907666</v>
       </c>
       <c r="C245" t="n">
-        <v>68968444971</v>
+        <v>66612688195</v>
       </c>
       <c r="D245" t="n">
-        <v>0.3899871980049663</v>
+        <v>0.3793707828157707</v>
       </c>
       <c r="E245" t="n">
         <v>244</v>
@@ -5094,172 +5094,20 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>2021-05-28</t>
+          <t>2021-06-10</t>
         </is>
       </c>
       <c r="B246" t="n">
-        <v>29791926043</v>
+        <v>27144684274</v>
       </c>
       <c r="C246" t="n">
-        <v>73972884560</v>
+        <v>72726642476</v>
       </c>
       <c r="D246" t="n">
-        <v>0.4027411695543051</v>
+        <v>0.3732426432714507</v>
       </c>
       <c r="E246" t="n">
         <v>245</v>
-      </c>
-    </row>
-    <row r="247">
-      <c r="A247" t="inlineStr">
-        <is>
-          <t>2021-05-31</t>
-        </is>
-      </c>
-      <c r="B247" t="n">
-        <v>27775314244</v>
-      </c>
-      <c r="C247" t="n">
-        <v>70615016083</v>
-      </c>
-      <c r="D247" t="n">
-        <v>0.3933343895490053</v>
-      </c>
-      <c r="E247" t="n">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="248">
-      <c r="A248" t="inlineStr">
-        <is>
-          <t>2021-06-01</t>
-        </is>
-      </c>
-      <c r="B248" t="n">
-        <v>28722955321</v>
-      </c>
-      <c r="C248" t="n">
-        <v>75176823860</v>
-      </c>
-      <c r="D248" t="n">
-        <v>0.3820719451315218</v>
-      </c>
-      <c r="E248" t="n">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="249">
-      <c r="A249" t="inlineStr">
-        <is>
-          <t>2021-06-02</t>
-        </is>
-      </c>
-      <c r="B249" t="n">
-        <v>29120888356</v>
-      </c>
-      <c r="C249" t="n">
-        <v>75272955834</v>
-      </c>
-      <c r="D249" t="n">
-        <v>0.3868705305026218</v>
-      </c>
-      <c r="E249" t="n">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="250">
-      <c r="A250" t="inlineStr">
-        <is>
-          <t>2021-06-03</t>
-        </is>
-      </c>
-      <c r="B250" t="n">
-        <v>29199450254</v>
-      </c>
-      <c r="C250" t="n">
-        <v>72798616374</v>
-      </c>
-      <c r="D250" t="n">
-        <v>0.4010989728704318</v>
-      </c>
-      <c r="E250" t="n">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="251">
-      <c r="A251" t="inlineStr">
-        <is>
-          <t>2021-06-04</t>
-        </is>
-      </c>
-      <c r="B251" t="n">
-        <v>27330244158</v>
-      </c>
-      <c r="C251" t="n">
-        <v>68930352581</v>
-      </c>
-      <c r="D251" t="n">
-        <v>0.3964907059757783</v>
-      </c>
-      <c r="E251" t="n">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="252">
-      <c r="A252" t="inlineStr">
-        <is>
-          <t>2021-06-07</t>
-        </is>
-      </c>
-      <c r="B252" t="n">
-        <v>25294989410</v>
-      </c>
-      <c r="C252" t="n">
-        <v>66558910303</v>
-      </c>
-      <c r="D252" t="n">
-        <v>0.3800391156472988</v>
-      </c>
-      <c r="E252" t="n">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="253">
-      <c r="A253" t="inlineStr">
-        <is>
-          <t>2021-06-08</t>
-        </is>
-      </c>
-      <c r="B253" t="n">
-        <v>25589368881</v>
-      </c>
-      <c r="C253" t="n">
-        <v>68255065080</v>
-      </c>
-      <c r="D253" t="n">
-        <v>0.3749079844991337</v>
-      </c>
-      <c r="E253" t="n">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="254">
-      <c r="A254" t="inlineStr">
-        <is>
-          <t>2021-06-09</t>
-        </is>
-      </c>
-      <c r="B254" t="n">
-        <v>25270907666</v>
-      </c>
-      <c r="C254" t="n">
-        <v>66612688195</v>
-      </c>
-      <c r="D254" t="n">
-        <v>0.3793707828157707</v>
-      </c>
-      <c r="E254" t="n">
-        <v>253</v>
       </c>
     </row>
   </sheetData>

--- a/king_index/output/index.xlsx
+++ b/king_index/output/index.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E246"/>
+  <dimension ref="A1:E247"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5110,6 +5110,25 @@
         <v>245</v>
       </c>
     </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>2021-06-11</t>
+        </is>
+      </c>
+      <c r="B247" t="n">
+        <v>31253551848</v>
+      </c>
+      <c r="C247" t="n">
+        <v>80603106508</v>
+      </c>
+      <c r="D247" t="n">
+        <v>0.3877462445556987</v>
+      </c>
+      <c r="E247" t="n">
+        <v>246</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/king_index/output/index.xlsx
+++ b/king_index/output/index.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E247"/>
+  <dimension ref="A1:E248"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5129,6 +5129,25 @@
         <v>246</v>
       </c>
     </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>2021-06-15</t>
+        </is>
+      </c>
+      <c r="B248" t="n">
+        <v>26600340763</v>
+      </c>
+      <c r="C248" t="n">
+        <v>71269245087</v>
+      </c>
+      <c r="D248" t="n">
+        <v>0.3732373021564681</v>
+      </c>
+      <c r="E248" t="n">
+        <v>247</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/king_index/output/index.xlsx
+++ b/king_index/output/index.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E248"/>
+  <dimension ref="A1:E249"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5148,6 +5148,25 @@
         <v>247</v>
       </c>
     </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>2021-06-16</t>
+        </is>
+      </c>
+      <c r="B249" t="n">
+        <v>25225237352</v>
+      </c>
+      <c r="C249" t="n">
+        <v>65304111913</v>
+      </c>
+      <c r="D249" t="n">
+        <v>0.3862733388918263</v>
+      </c>
+      <c r="E249" t="n">
+        <v>248</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/king_index/output/index.xlsx
+++ b/king_index/output/index.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E249"/>
+  <dimension ref="A1:E250"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5167,6 +5167,25 @@
         <v>248</v>
       </c>
     </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>2021-06-17</t>
+        </is>
+      </c>
+      <c r="B250" t="n">
+        <v>23865594042</v>
+      </c>
+      <c r="C250" t="n">
+        <v>62073104309</v>
+      </c>
+      <c r="D250" t="n">
+        <v>0.3844756003050377</v>
+      </c>
+      <c r="E250" t="n">
+        <v>249</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/king_index/output/index.xlsx
+++ b/king_index/output/index.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E250"/>
+  <dimension ref="A1:E251"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5186,6 +5186,25 @@
         <v>249</v>
       </c>
     </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>2021-06-18</t>
+        </is>
+      </c>
+      <c r="B251" t="n">
+        <v>26773348572</v>
+      </c>
+      <c r="C251" t="n">
+        <v>68507417006</v>
+      </c>
+      <c r="D251" t="n">
+        <v>0.3908094881121433</v>
+      </c>
+      <c r="E251" t="n">
+        <v>250</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/king_index/output/index.xlsx
+++ b/king_index/output/index.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E251"/>
+  <dimension ref="A1:E252"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5205,6 +5205,25 @@
         <v>250</v>
       </c>
     </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>2021-06-21</t>
+        </is>
+      </c>
+      <c r="B252" t="n">
+        <v>25810884254</v>
+      </c>
+      <c r="C252" t="n">
+        <v>68094480065</v>
+      </c>
+      <c r="D252" t="n">
+        <v>0.3790451770740016</v>
+      </c>
+      <c r="E252" t="n">
+        <v>251</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/king_index/output/index.xlsx
+++ b/king_index/output/index.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E252"/>
+  <dimension ref="A1:E253"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5224,6 +5224,25 @@
         <v>251</v>
       </c>
     </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>2021-06-22</t>
+        </is>
+      </c>
+      <c r="B253" t="n">
+        <v>27325435943</v>
+      </c>
+      <c r="C253" t="n">
+        <v>71331165214</v>
+      </c>
+      <c r="D253" t="n">
+        <v>0.3830785023772036</v>
+      </c>
+      <c r="E253" t="n">
+        <v>252</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/king_index/output/index.xlsx
+++ b/king_index/output/index.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E253"/>
+  <dimension ref="A1:E254"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5243,6 +5243,25 @@
         <v>252</v>
       </c>
     </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>2021-06-23</t>
+        </is>
+      </c>
+      <c r="B254" t="n">
+        <v>26948115800</v>
+      </c>
+      <c r="C254" t="n">
+        <v>71129212592</v>
+      </c>
+      <c r="D254" t="n">
+        <v>0.3788614384721994</v>
+      </c>
+      <c r="E254" t="n">
+        <v>253</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/king_index/output/index.xlsx
+++ b/king_index/output/index.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E254"/>
+  <dimension ref="A1:E255"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5262,6 +5262,25 @@
         <v>253</v>
       </c>
     </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>2021-06-24</t>
+        </is>
+      </c>
+      <c r="B255" t="n">
+        <v>25431794302</v>
+      </c>
+      <c r="C255" t="n">
+        <v>68625630748</v>
+      </c>
+      <c r="D255" t="n">
+        <v>0.3705874033477087</v>
+      </c>
+      <c r="E255" t="n">
+        <v>254</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/king_index/output/index.xlsx
+++ b/king_index/output/index.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E255"/>
+  <dimension ref="A1:E251"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -458,17 +458,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2020-06-10</t>
+          <t>2020-06-17</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>20190478240</v>
+        <v>23156031895</v>
       </c>
       <c r="C2" t="n">
-        <v>52136701032</v>
+        <v>61386131654</v>
       </c>
       <c r="D2" t="n">
-        <v>0.3872603720670333</v>
+        <v>0.3772192720257707</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>
@@ -477,17 +477,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2020-06-11</t>
+          <t>2020-06-18</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>21856153332</v>
+        <v>25733088111</v>
       </c>
       <c r="C3" t="n">
-        <v>58580995849</v>
+        <v>63354121102</v>
       </c>
       <c r="D3" t="n">
-        <v>0.3730928949780408</v>
+        <v>0.4061785983830442</v>
       </c>
       <c r="E3" t="n">
         <v>2</v>
@@ -496,17 +496,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2020-06-12</t>
+          <t>2020-06-19</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>22554032456</v>
+        <v>24126480724</v>
       </c>
       <c r="C4" t="n">
-        <v>58624630321</v>
+        <v>61888832308</v>
       </c>
       <c r="D4" t="n">
-        <v>0.3847193975041731</v>
+        <v>0.3898357720489956</v>
       </c>
       <c r="E4" t="n">
         <v>3</v>
@@ -515,17 +515,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2020-06-15</t>
+          <t>2020-06-22</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>24160399741</v>
+        <v>25010112764</v>
       </c>
       <c r="C5" t="n">
-        <v>62827231135</v>
+        <v>63846785740</v>
       </c>
       <c r="D5" t="n">
-        <v>0.3845529924609497</v>
+        <v>0.3917207808369149</v>
       </c>
       <c r="E5" t="n">
         <v>4</v>
@@ -534,17 +534,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2020-06-16</t>
+          <t>2020-06-23</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>22302612612</v>
+        <v>21417149307</v>
       </c>
       <c r="C6" t="n">
-        <v>57871475779</v>
+        <v>56906481203</v>
       </c>
       <c r="D6" t="n">
-        <v>0.3853817845801855</v>
+        <v>0.3763569430799901</v>
       </c>
       <c r="E6" t="n">
         <v>5</v>
@@ -553,17 +553,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2020-06-17</t>
+          <t>2020-06-24</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>23156031895</v>
+        <v>19322024502</v>
       </c>
       <c r="C7" t="n">
-        <v>61386131654</v>
+        <v>52926747938</v>
       </c>
       <c r="D7" t="n">
-        <v>0.3772192720257707</v>
+        <v>0.3650710700123576</v>
       </c>
       <c r="E7" t="n">
         <v>6</v>
@@ -572,17 +572,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2020-06-18</t>
+          <t>2020-06-29</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>25733088111</v>
+        <v>20448932009</v>
       </c>
       <c r="C8" t="n">
-        <v>63354121102</v>
+        <v>54347085975</v>
       </c>
       <c r="D8" t="n">
-        <v>0.4061785983830442</v>
+        <v>0.3762654729713868</v>
       </c>
       <c r="E8" t="n">
         <v>7</v>
@@ -591,17 +591,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2020-06-19</t>
+          <t>2020-06-30</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>24126480724</v>
+        <v>20003048931</v>
       </c>
       <c r="C9" t="n">
-        <v>61888832308</v>
+        <v>53946886834</v>
       </c>
       <c r="D9" t="n">
-        <v>0.3898357720489956</v>
+        <v>0.3707915341352578</v>
       </c>
       <c r="E9" t="n">
         <v>8</v>
@@ -610,17 +610,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2020-06-22</t>
+          <t>2020-07-01</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>25010112764</v>
+        <v>25539868441</v>
       </c>
       <c r="C10" t="n">
-        <v>63846785740</v>
+        <v>66477208273</v>
       </c>
       <c r="D10" t="n">
-        <v>0.3917207808369149</v>
+        <v>0.3841898464826647</v>
       </c>
       <c r="E10" t="n">
         <v>9</v>
@@ -629,17 +629,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2020-06-23</t>
+          <t>2020-07-02</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>21417149307</v>
+        <v>35281401239</v>
       </c>
       <c r="C11" t="n">
-        <v>56906481203</v>
+        <v>86277275738</v>
       </c>
       <c r="D11" t="n">
-        <v>0.3763569430799901</v>
+        <v>0.4089304041789609</v>
       </c>
       <c r="E11" t="n">
         <v>10</v>
@@ -648,17 +648,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2020-06-24</t>
+          <t>2020-07-03</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>19322024502</v>
+        <v>39589081860</v>
       </c>
       <c r="C12" t="n">
-        <v>52926747938</v>
+        <v>96590527098</v>
       </c>
       <c r="D12" t="n">
-        <v>0.3650710700123576</v>
+        <v>0.4098650566409398</v>
       </c>
       <c r="E12" t="n">
         <v>11</v>
@@ -667,17 +667,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2020-06-29</t>
+          <t>2020-07-06</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>20448932009</v>
+        <v>51680326902</v>
       </c>
       <c r="C13" t="n">
-        <v>54347085975</v>
+        <v>132721246132</v>
       </c>
       <c r="D13" t="n">
-        <v>0.3762654729713868</v>
+        <v>0.3893900065600689</v>
       </c>
       <c r="E13" t="n">
         <v>12</v>
@@ -686,17 +686,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2020-06-30</t>
+          <t>2020-07-07</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>20003048931</v>
+        <v>54130474812</v>
       </c>
       <c r="C14" t="n">
-        <v>53946886834</v>
+        <v>140540263998</v>
       </c>
       <c r="D14" t="n">
-        <v>0.3707915341352578</v>
+        <v>0.3851599055824338</v>
       </c>
       <c r="E14" t="n">
         <v>13</v>
@@ -705,17 +705,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2020-07-01</t>
+          <t>2020-07-08</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>25539868441</v>
+        <v>48763694238</v>
       </c>
       <c r="C15" t="n">
-        <v>66477208273</v>
+        <v>124820435614</v>
       </c>
       <c r="D15" t="n">
-        <v>0.3841898464826647</v>
+        <v>0.3906707583427999</v>
       </c>
       <c r="E15" t="n">
         <v>14</v>
@@ -724,17 +724,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2020-07-02</t>
+          <t>2020-07-09</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>35281401239</v>
+        <v>50352644938</v>
       </c>
       <c r="C16" t="n">
-        <v>86277275738</v>
+        <v>137276438768</v>
       </c>
       <c r="D16" t="n">
-        <v>0.4089304041789609</v>
+        <v>0.3667974299879457</v>
       </c>
       <c r="E16" t="n">
         <v>15</v>
@@ -743,17 +743,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2020-07-03</t>
+          <t>2020-07-10</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>39589081860</v>
+        <v>45792064703</v>
       </c>
       <c r="C17" t="n">
-        <v>96590527098</v>
+        <v>124540979573</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4098650566409398</v>
+        <v>0.3676867233580644</v>
       </c>
       <c r="E17" t="n">
         <v>16</v>
@@ -762,17 +762,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2020-07-06</t>
+          <t>2020-07-13</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>51680326902</v>
+        <v>45569190970</v>
       </c>
       <c r="C18" t="n">
-        <v>132721246132</v>
+        <v>125874117474</v>
       </c>
       <c r="D18" t="n">
-        <v>0.3893900065600689</v>
+        <v>0.3620219301987366</v>
       </c>
       <c r="E18" t="n">
         <v>17</v>
@@ -781,17 +781,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2020-07-07</t>
+          <t>2020-07-14</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>54130474812</v>
+        <v>44404671526</v>
       </c>
       <c r="C19" t="n">
-        <v>140540263998</v>
+        <v>127205292718</v>
       </c>
       <c r="D19" t="n">
-        <v>0.3851599055824338</v>
+        <v>0.3490788046409375</v>
       </c>
       <c r="E19" t="n">
         <v>18</v>
@@ -800,17 +800,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2020-07-08</t>
+          <t>2020-07-15</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>48763694238</v>
+        <v>40948010990</v>
       </c>
       <c r="C20" t="n">
-        <v>124820435614</v>
+        <v>115744357395</v>
       </c>
       <c r="D20" t="n">
-        <v>0.3906707583427999</v>
+        <v>0.3537797600815822</v>
       </c>
       <c r="E20" t="n">
         <v>19</v>
@@ -819,17 +819,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2020-07-09</t>
+          <t>2020-07-16</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>50352644938</v>
+        <v>41327517137</v>
       </c>
       <c r="C21" t="n">
-        <v>137276438768</v>
+        <v>110570972319</v>
       </c>
       <c r="D21" t="n">
-        <v>0.3667974299879457</v>
+        <v>0.373764617152584</v>
       </c>
       <c r="E21" t="n">
         <v>20</v>
@@ -838,17 +838,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2020-07-10</t>
+          <t>2020-07-17</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>45792064703</v>
+        <v>30786629717</v>
       </c>
       <c r="C22" t="n">
-        <v>124540979573</v>
+        <v>83073812068</v>
       </c>
       <c r="D22" t="n">
-        <v>0.3676867233580644</v>
+        <v>0.3705936798927636</v>
       </c>
       <c r="E22" t="n">
         <v>21</v>
@@ -857,17 +857,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2020-07-13</t>
+          <t>2020-07-20</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>45569190970</v>
+        <v>33302406491</v>
       </c>
       <c r="C23" t="n">
-        <v>125874117474</v>
+        <v>90725025902</v>
       </c>
       <c r="D23" t="n">
-        <v>0.3620219301987366</v>
+        <v>0.3670696829226903</v>
       </c>
       <c r="E23" t="n">
         <v>22</v>
@@ -876,17 +876,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2020-07-14</t>
+          <t>2020-07-21</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>44404671526</v>
+        <v>29750727633</v>
       </c>
       <c r="C24" t="n">
-        <v>127205292718</v>
+        <v>82804408460</v>
       </c>
       <c r="D24" t="n">
-        <v>0.3490788046409375</v>
+        <v>0.3592891753749025</v>
       </c>
       <c r="E24" t="n">
         <v>23</v>
@@ -895,17 +895,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2020-07-15</t>
+          <t>2020-07-22</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>40948010990</v>
+        <v>32546369994</v>
       </c>
       <c r="C25" t="n">
-        <v>115744357395</v>
+        <v>88951002081</v>
       </c>
       <c r="D25" t="n">
-        <v>0.3537797600815822</v>
+        <v>0.3658909875389917</v>
       </c>
       <c r="E25" t="n">
         <v>24</v>
@@ -914,17 +914,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2020-07-16</t>
+          <t>2020-07-23</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>41327517137</v>
+        <v>33380341470</v>
       </c>
       <c r="C26" t="n">
-        <v>110570972319</v>
+        <v>92918126099</v>
       </c>
       <c r="D26" t="n">
-        <v>0.373764617152584</v>
+        <v>0.3592446691664313</v>
       </c>
       <c r="E26" t="n">
         <v>25</v>
@@ -933,17 +933,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2020-07-17</t>
+          <t>2020-07-24</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>30786629717</v>
+        <v>34826858650</v>
       </c>
       <c r="C27" t="n">
-        <v>83073812068</v>
+        <v>98778010270</v>
       </c>
       <c r="D27" t="n">
-        <v>0.3705936798927636</v>
+        <v>0.3525770417404056</v>
       </c>
       <c r="E27" t="n">
         <v>26</v>
@@ -952,17 +952,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2020-07-20</t>
+          <t>2020-07-27</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>33302406491</v>
+        <v>25272101520</v>
       </c>
       <c r="C28" t="n">
-        <v>90725025902</v>
+        <v>69273127708</v>
       </c>
       <c r="D28" t="n">
-        <v>0.3670696829226903</v>
+        <v>0.3648182542951854</v>
       </c>
       <c r="E28" t="n">
         <v>27</v>
@@ -971,17 +971,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2020-07-21</t>
+          <t>2020-07-28</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>29750727633</v>
+        <v>25533477451</v>
       </c>
       <c r="C29" t="n">
-        <v>82804408460</v>
+        <v>67557159363</v>
       </c>
       <c r="D29" t="n">
-        <v>0.3592891753749025</v>
+        <v>0.3779536868002814</v>
       </c>
       <c r="E29" t="n">
         <v>28</v>
@@ -990,17 +990,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2020-07-22</t>
+          <t>2020-07-29</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>32546369994</v>
+        <v>27398207256</v>
       </c>
       <c r="C30" t="n">
-        <v>88951002081</v>
+        <v>75808503607</v>
       </c>
       <c r="D30" t="n">
-        <v>0.3658909875389917</v>
+        <v>0.3614133764997586</v>
       </c>
       <c r="E30" t="n">
         <v>29</v>
@@ -1009,17 +1009,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2020-07-23</t>
+          <t>2020-07-30</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>33380341470</v>
+        <v>29316097538</v>
       </c>
       <c r="C31" t="n">
-        <v>92918126099</v>
+        <v>80705680370</v>
       </c>
       <c r="D31" t="n">
-        <v>0.3592446691664313</v>
+        <v>0.3632470156201968</v>
       </c>
       <c r="E31" t="n">
         <v>30</v>
@@ -1028,17 +1028,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2020-07-24</t>
+          <t>2020-07-31</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>34826858650</v>
+        <v>30421341838</v>
       </c>
       <c r="C32" t="n">
-        <v>98778010270</v>
+        <v>83388719271</v>
       </c>
       <c r="D32" t="n">
-        <v>0.3525770417404056</v>
+        <v>0.3648136355126825</v>
       </c>
       <c r="E32" t="n">
         <v>31</v>
@@ -1047,17 +1047,17 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2020-07-27</t>
+          <t>2020-08-03</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>25272101520</v>
+        <v>32534419194</v>
       </c>
       <c r="C33" t="n">
-        <v>69273127708</v>
+        <v>97147468049</v>
       </c>
       <c r="D33" t="n">
-        <v>0.3648182542951854</v>
+        <v>0.3348972427937086</v>
       </c>
       <c r="E33" t="n">
         <v>32</v>
@@ -1066,17 +1066,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2020-07-28</t>
+          <t>2020-08-04</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>25533477451</v>
+        <v>35518548960</v>
       </c>
       <c r="C34" t="n">
-        <v>67557159363</v>
+        <v>100401661483</v>
       </c>
       <c r="D34" t="n">
-        <v>0.3779536868002814</v>
+        <v>0.3537645536474912</v>
       </c>
       <c r="E34" t="n">
         <v>33</v>
@@ -1085,17 +1085,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2020-07-29</t>
+          <t>2020-08-05</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>27398207256</v>
+        <v>31118752071</v>
       </c>
       <c r="C35" t="n">
-        <v>75808503607</v>
+        <v>88411991123</v>
       </c>
       <c r="D35" t="n">
-        <v>0.3614133764997586</v>
+        <v>0.351974338273947</v>
       </c>
       <c r="E35" t="n">
         <v>34</v>
@@ -1104,17 +1104,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2020-07-30</t>
+          <t>2020-08-06</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>29316097538</v>
+        <v>35289080996</v>
       </c>
       <c r="C36" t="n">
-        <v>80705680370</v>
+        <v>94484631872</v>
       </c>
       <c r="D36" t="n">
-        <v>0.3632470156201968</v>
+        <v>0.3734901676264849</v>
       </c>
       <c r="E36" t="n">
         <v>35</v>
@@ -1123,17 +1123,17 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2020-07-31</t>
+          <t>2020-08-07</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>30421341838</v>
+        <v>33926327226</v>
       </c>
       <c r="C37" t="n">
-        <v>83388719271</v>
+        <v>90977583613</v>
       </c>
       <c r="D37" t="n">
-        <v>0.3648136355126825</v>
+        <v>0.3729086427522151</v>
       </c>
       <c r="E37" t="n">
         <v>36</v>
@@ -1142,17 +1142,17 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2020-08-03</t>
+          <t>2020-08-10</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>32534419194</v>
+        <v>29708663069</v>
       </c>
       <c r="C38" t="n">
-        <v>97147468049</v>
+        <v>82942928747</v>
       </c>
       <c r="D38" t="n">
-        <v>0.3348972427937086</v>
+        <v>0.3581819875160189</v>
       </c>
       <c r="E38" t="n">
         <v>37</v>
@@ -1161,17 +1161,17 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2020-08-04</t>
+          <t>2020-08-11</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>35518548960</v>
+        <v>30946369948</v>
       </c>
       <c r="C39" t="n">
-        <v>100401661483</v>
+        <v>86295092754</v>
       </c>
       <c r="D39" t="n">
-        <v>0.3537645536474912</v>
+        <v>0.3586110051033644</v>
       </c>
       <c r="E39" t="n">
         <v>38</v>
@@ -1180,17 +1180,17 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2020-08-05</t>
+          <t>2020-08-12</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>31118752071</v>
+        <v>29856245191</v>
       </c>
       <c r="C40" t="n">
-        <v>88411991123</v>
+        <v>82452473263</v>
       </c>
       <c r="D40" t="n">
-        <v>0.351974338273947</v>
+        <v>0.3621024817019988</v>
       </c>
       <c r="E40" t="n">
         <v>39</v>
@@ -1199,17 +1199,17 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2020-08-06</t>
+          <t>2020-08-13</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>35289080996</v>
+        <v>27823565615</v>
       </c>
       <c r="C41" t="n">
-        <v>94484631872</v>
+        <v>72532322436</v>
       </c>
       <c r="D41" t="n">
-        <v>0.3734901676264849</v>
+        <v>0.3836022986793308</v>
       </c>
       <c r="E41" t="n">
         <v>40</v>
@@ -1218,17 +1218,17 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2020-08-07</t>
+          <t>2020-08-14</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>33926327226</v>
+        <v>27261549866</v>
       </c>
       <c r="C42" t="n">
-        <v>90977583613</v>
+        <v>69180221661</v>
       </c>
       <c r="D42" t="n">
-        <v>0.3729086427522151</v>
+        <v>0.3940656622869504</v>
       </c>
       <c r="E42" t="n">
         <v>41</v>
@@ -1237,17 +1237,17 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2020-08-10</t>
+          <t>2020-08-17</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>29708663069</v>
+        <v>37118467741</v>
       </c>
       <c r="C43" t="n">
-        <v>82942928747</v>
+        <v>91788369903</v>
       </c>
       <c r="D43" t="n">
-        <v>0.3581819875160189</v>
+        <v>0.4043918394043386</v>
       </c>
       <c r="E43" t="n">
         <v>42</v>
@@ -1256,17 +1256,17 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2020-08-11</t>
+          <t>2020-08-18</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>30946369948</v>
+        <v>31325687773</v>
       </c>
       <c r="C44" t="n">
-        <v>86295092754</v>
+        <v>85178317604</v>
       </c>
       <c r="D44" t="n">
-        <v>0.3586110051033644</v>
+        <v>0.3677659838109897</v>
       </c>
       <c r="E44" t="n">
         <v>43</v>
@@ -1275,17 +1275,17 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2020-08-12</t>
+          <t>2020-08-19</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>29856245191</v>
+        <v>33073383828</v>
       </c>
       <c r="C45" t="n">
-        <v>82452473263</v>
+        <v>88140275731</v>
       </c>
       <c r="D45" t="n">
-        <v>0.3621024817019988</v>
+        <v>0.375235765417145</v>
       </c>
       <c r="E45" t="n">
         <v>44</v>
@@ -1294,17 +1294,17 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2020-08-13</t>
+          <t>2020-08-20</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>27823565615</v>
+        <v>27646953314</v>
       </c>
       <c r="C46" t="n">
-        <v>72532322436</v>
+        <v>72119978332</v>
       </c>
       <c r="D46" t="n">
-        <v>0.3836022986793308</v>
+        <v>0.3833466669489126</v>
       </c>
       <c r="E46" t="n">
         <v>45</v>
@@ -1313,17 +1313,17 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2020-08-14</t>
+          <t>2020-08-21</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>27261549866</v>
+        <v>25486130617</v>
       </c>
       <c r="C47" t="n">
-        <v>69180221661</v>
+        <v>66786682396</v>
       </c>
       <c r="D47" t="n">
-        <v>0.3940656622869504</v>
+        <v>0.3816049802546626</v>
       </c>
       <c r="E47" t="n">
         <v>46</v>
@@ -1332,17 +1332,17 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2020-08-17</t>
+          <t>2020-08-24</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>37118467741</v>
+        <v>25209284709</v>
       </c>
       <c r="C48" t="n">
-        <v>91788369903</v>
+        <v>67412296336</v>
       </c>
       <c r="D48" t="n">
-        <v>0.4043918394043386</v>
+        <v>0.3739567716748666</v>
       </c>
       <c r="E48" t="n">
         <v>47</v>
@@ -1351,17 +1351,17 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2020-08-18</t>
+          <t>2020-08-25</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>31325687773</v>
+        <v>26619247474</v>
       </c>
       <c r="C49" t="n">
-        <v>85178317604</v>
+        <v>73103731924</v>
       </c>
       <c r="D49" t="n">
-        <v>0.3677659838109897</v>
+        <v>0.3641298025889275</v>
       </c>
       <c r="E49" t="n">
         <v>48</v>
@@ -1370,17 +1370,17 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2020-08-19</t>
+          <t>2020-08-26</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>33073383828</v>
+        <v>26322908958</v>
       </c>
       <c r="C50" t="n">
-        <v>88140275731</v>
+        <v>75716936591</v>
       </c>
       <c r="D50" t="n">
-        <v>0.375235765417145</v>
+        <v>0.3476488899727732</v>
       </c>
       <c r="E50" t="n">
         <v>49</v>
@@ -1389,17 +1389,17 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2020-08-20</t>
+          <t>2020-08-27</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>27646953314</v>
+        <v>23276018839</v>
       </c>
       <c r="C51" t="n">
-        <v>72119978332</v>
+        <v>65005692955</v>
       </c>
       <c r="D51" t="n">
-        <v>0.3833466669489126</v>
+        <v>0.3580612371152286</v>
       </c>
       <c r="E51" t="n">
         <v>50</v>
@@ -1408,17 +1408,17 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2020-08-21</t>
+          <t>2020-08-28</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>25486130617</v>
+        <v>25701039669</v>
       </c>
       <c r="C52" t="n">
-        <v>66786682396</v>
+        <v>70850828969</v>
       </c>
       <c r="D52" t="n">
-        <v>0.3816049802546626</v>
+        <v>0.3627486091975749</v>
       </c>
       <c r="E52" t="n">
         <v>51</v>
@@ -1427,17 +1427,17 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2020-08-24</t>
+          <t>2020-08-31</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>25209284709</v>
+        <v>28573296373</v>
       </c>
       <c r="C53" t="n">
-        <v>67412296336</v>
+        <v>77184652221</v>
       </c>
       <c r="D53" t="n">
-        <v>0.3739567716748666</v>
+        <v>0.3701940159189566</v>
       </c>
       <c r="E53" t="n">
         <v>52</v>
@@ -1446,17 +1446,17 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2020-08-25</t>
+          <t>2020-09-01</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>26619247474</v>
+        <v>23964180511</v>
       </c>
       <c r="C54" t="n">
-        <v>73103731924</v>
+        <v>64392996012</v>
       </c>
       <c r="D54" t="n">
-        <v>0.3641298025889275</v>
+        <v>0.3721550788929613</v>
       </c>
       <c r="E54" t="n">
         <v>53</v>
@@ -1465,17 +1465,17 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2020-08-26</t>
+          <t>2020-09-02</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>26322908958</v>
+        <v>30082062270</v>
       </c>
       <c r="C55" t="n">
-        <v>75716936591</v>
+        <v>77531927895</v>
       </c>
       <c r="D55" t="n">
-        <v>0.3476488899727732</v>
+        <v>0.3879957984630482</v>
       </c>
       <c r="E55" t="n">
         <v>54</v>
@@ -1484,17 +1484,17 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2020-08-27</t>
+          <t>2020-09-03</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>23276018839</v>
+        <v>27715216294</v>
       </c>
       <c r="C56" t="n">
-        <v>65005692955</v>
+        <v>73519808249</v>
       </c>
       <c r="D56" t="n">
-        <v>0.3580612371152286</v>
+        <v>0.3769761776327399</v>
       </c>
       <c r="E56" t="n">
         <v>55</v>
@@ -1503,17 +1503,17 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2020-08-28</t>
+          <t>2020-09-04</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>25701039669</v>
+        <v>24329945914</v>
       </c>
       <c r="C57" t="n">
-        <v>70850828969</v>
+        <v>65573685675</v>
       </c>
       <c r="D57" t="n">
-        <v>0.3627486091975749</v>
+        <v>0.37103215510236</v>
       </c>
       <c r="E57" t="n">
         <v>56</v>
@@ -1522,17 +1522,17 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2020-08-31</t>
+          <t>2020-09-07</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>28573296373</v>
+        <v>29997390344</v>
       </c>
       <c r="C58" t="n">
-        <v>77184652221</v>
+        <v>79881522723</v>
       </c>
       <c r="D58" t="n">
-        <v>0.3701940159189566</v>
+        <v>0.375523516846568</v>
       </c>
       <c r="E58" t="n">
         <v>57</v>
@@ -1541,17 +1541,17 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2020-09-01</t>
+          <t>2020-09-08</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>23964180511</v>
+        <v>32724062545</v>
       </c>
       <c r="C59" t="n">
-        <v>64392996012</v>
+        <v>80161481426</v>
       </c>
       <c r="D59" t="n">
-        <v>0.3721550788929613</v>
+        <v>0.4082267688030289</v>
       </c>
       <c r="E59" t="n">
         <v>58</v>
@@ -1560,17 +1560,17 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2020-09-02</t>
+          <t>2020-09-09</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>30082062270</v>
+        <v>41720230941</v>
       </c>
       <c r="C60" t="n">
-        <v>77531927895</v>
+        <v>98517765305</v>
       </c>
       <c r="D60" t="n">
-        <v>0.3879957984630482</v>
+        <v>0.4234792660170358</v>
       </c>
       <c r="E60" t="n">
         <v>59</v>
@@ -1579,17 +1579,17 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2020-09-03</t>
+          <t>2020-09-10</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>27715216294</v>
+        <v>32362586075</v>
       </c>
       <c r="C61" t="n">
-        <v>73519808249</v>
+        <v>83938666669</v>
       </c>
       <c r="D61" t="n">
-        <v>0.3769761776327399</v>
+        <v>0.3855503948212232</v>
       </c>
       <c r="E61" t="n">
         <v>60</v>
@@ -1598,17 +1598,17 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2020-09-04</t>
+          <t>2020-09-11</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>24329945914</v>
+        <v>23586290440</v>
       </c>
       <c r="C62" t="n">
-        <v>65573685675</v>
+        <v>60330240577</v>
       </c>
       <c r="D62" t="n">
-        <v>0.37103215510236</v>
+        <v>0.3909530314220547</v>
       </c>
       <c r="E62" t="n">
         <v>61</v>
@@ -1617,17 +1617,17 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2020-09-07</t>
+          <t>2020-09-14</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>29997390344</v>
+        <v>24462170352</v>
       </c>
       <c r="C63" t="n">
-        <v>79881522723</v>
+        <v>63101019998</v>
       </c>
       <c r="D63" t="n">
-        <v>0.375523516846568</v>
+        <v>0.3876667976646865</v>
       </c>
       <c r="E63" t="n">
         <v>62</v>
@@ -1636,17 +1636,17 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2020-09-08</t>
+          <t>2020-09-15</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>32724062545</v>
+        <v>23106120892</v>
       </c>
       <c r="C64" t="n">
-        <v>80161481426</v>
+        <v>58614407766</v>
       </c>
       <c r="D64" t="n">
-        <v>0.4082267688030289</v>
+        <v>0.3942054824514151</v>
       </c>
       <c r="E64" t="n">
         <v>63</v>
@@ -1655,17 +1655,17 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2020-09-09</t>
+          <t>2020-09-16</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>41720230941</v>
+        <v>21724638649</v>
       </c>
       <c r="C65" t="n">
-        <v>98517765305</v>
+        <v>55182289033</v>
       </c>
       <c r="D65" t="n">
-        <v>0.4234792660170358</v>
+        <v>0.3936886096915674</v>
       </c>
       <c r="E65" t="n">
         <v>64</v>
@@ -1674,17 +1674,17 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2020-09-10</t>
+          <t>2020-09-17</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>32362586075</v>
+        <v>20554994106</v>
       </c>
       <c r="C66" t="n">
-        <v>83938666669</v>
+        <v>55472969929</v>
       </c>
       <c r="D66" t="n">
-        <v>0.3855503948212232</v>
+        <v>0.3705407179804577</v>
       </c>
       <c r="E66" t="n">
         <v>65</v>
@@ -1693,17 +1693,17 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2020-09-11</t>
+          <t>2020-09-18</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>23586290440</v>
+        <v>25018086444</v>
       </c>
       <c r="C67" t="n">
-        <v>60330240577</v>
+        <v>64587549837</v>
       </c>
       <c r="D67" t="n">
-        <v>0.3909530314220547</v>
+        <v>0.3873515330297914</v>
       </c>
       <c r="E67" t="n">
         <v>66</v>
@@ -1712,17 +1712,17 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2020-09-14</t>
+          <t>2020-09-21</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>24462170352</v>
+        <v>22182279260</v>
       </c>
       <c r="C68" t="n">
-        <v>63101019998</v>
+        <v>58098440053</v>
       </c>
       <c r="D68" t="n">
-        <v>0.3876667976646865</v>
+        <v>0.3818050749686968</v>
       </c>
       <c r="E68" t="n">
         <v>67</v>
@@ -1731,17 +1731,17 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2020-09-15</t>
+          <t>2020-09-22</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>23106120892</v>
+        <v>22099090990</v>
       </c>
       <c r="C69" t="n">
-        <v>58614407766</v>
+        <v>56264182474</v>
       </c>
       <c r="D69" t="n">
-        <v>0.3942054824514151</v>
+        <v>0.3927736975510506</v>
       </c>
       <c r="E69" t="n">
         <v>68</v>
@@ -1750,17 +1750,17 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2020-09-16</t>
+          <t>2020-09-23</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>21724638649</v>
+        <v>19077501915</v>
       </c>
       <c r="C70" t="n">
-        <v>55182289033</v>
+        <v>48597940983</v>
       </c>
       <c r="D70" t="n">
-        <v>0.3936886096915674</v>
+        <v>0.3925578230088695</v>
       </c>
       <c r="E70" t="n">
         <v>69</v>
@@ -1769,17 +1769,17 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2020-09-17</t>
+          <t>2020-09-24</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>20554994106</v>
+        <v>20859996043</v>
       </c>
       <c r="C71" t="n">
-        <v>55472969929</v>
+        <v>54861814882</v>
       </c>
       <c r="D71" t="n">
-        <v>0.3705407179804577</v>
+        <v>0.3802279616134993</v>
       </c>
       <c r="E71" t="n">
         <v>70</v>
@@ -1788,17 +1788,17 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2020-09-18</t>
+          <t>2020-09-25</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>25018086444</v>
+        <v>16281719043</v>
       </c>
       <c r="C72" t="n">
-        <v>64587549837</v>
+        <v>43622575116</v>
       </c>
       <c r="D72" t="n">
-        <v>0.3873515330297914</v>
+        <v>0.373240667239476</v>
       </c>
       <c r="E72" t="n">
         <v>71</v>
@@ -1807,17 +1807,17 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2020-09-21</t>
+          <t>2020-09-28</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>22182279260</v>
+        <v>14676583271</v>
       </c>
       <c r="C73" t="n">
-        <v>58098440053</v>
+        <v>40556797589</v>
       </c>
       <c r="D73" t="n">
-        <v>0.3818050749686968</v>
+        <v>0.3618772719614492</v>
       </c>
       <c r="E73" t="n">
         <v>72</v>
@@ -1826,17 +1826,17 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2020-09-22</t>
+          <t>2020-09-29</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>22099090990</v>
+        <v>14442107257</v>
       </c>
       <c r="C74" t="n">
-        <v>56264182474</v>
+        <v>40163621965</v>
       </c>
       <c r="D74" t="n">
-        <v>0.3927736975510506</v>
+        <v>0.3595817944304267</v>
       </c>
       <c r="E74" t="n">
         <v>73</v>
@@ -1845,17 +1845,17 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2020-09-23</t>
+          <t>2020-09-30</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>19077501915</v>
+        <v>15066784297</v>
       </c>
       <c r="C75" t="n">
-        <v>48597940983</v>
+        <v>40300843448</v>
       </c>
       <c r="D75" t="n">
-        <v>0.3925578230088695</v>
+        <v>0.3738577907541961</v>
       </c>
       <c r="E75" t="n">
         <v>74</v>
@@ -1864,17 +1864,17 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2020-09-24</t>
+          <t>2020-10-09</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>20859996043</v>
+        <v>18363804782</v>
       </c>
       <c r="C76" t="n">
-        <v>54861814882</v>
+        <v>50410563994</v>
       </c>
       <c r="D76" t="n">
-        <v>0.3802279616134993</v>
+        <v>0.3642848507742486</v>
       </c>
       <c r="E76" t="n">
         <v>75</v>
@@ -1883,17 +1883,17 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2020-09-25</t>
+          <t>2020-10-12</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>16281719043</v>
+        <v>24824121596</v>
       </c>
       <c r="C77" t="n">
-        <v>43622575116</v>
+        <v>69075123930</v>
       </c>
       <c r="D77" t="n">
-        <v>0.373240667239476</v>
+        <v>0.3593786038104905</v>
       </c>
       <c r="E77" t="n">
         <v>76</v>
@@ -1902,17 +1902,17 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2020-09-28</t>
+          <t>2020-10-13</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>14676583271</v>
+        <v>21950874234</v>
       </c>
       <c r="C78" t="n">
-        <v>40556797589</v>
+        <v>58435290007</v>
       </c>
       <c r="D78" t="n">
-        <v>0.3618772719614492</v>
+        <v>0.3756441395494142</v>
       </c>
       <c r="E78" t="n">
         <v>77</v>
@@ -1921,17 +1921,17 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2020-09-29</t>
+          <t>2020-10-14</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>14442107257</v>
+        <v>21810988673</v>
       </c>
       <c r="C79" t="n">
-        <v>40163621965</v>
+        <v>58022364557</v>
       </c>
       <c r="D79" t="n">
-        <v>0.3595817944304267</v>
+        <v>0.3759065808421738</v>
       </c>
       <c r="E79" t="n">
         <v>78</v>
@@ -1940,17 +1940,17 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2020-09-30</t>
+          <t>2020-10-15</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>15066784297</v>
+        <v>20410751440</v>
       </c>
       <c r="C80" t="n">
-        <v>40300843448</v>
+        <v>54415224691</v>
       </c>
       <c r="D80" t="n">
-        <v>0.3738577907541961</v>
+        <v>0.3750926612157467</v>
       </c>
       <c r="E80" t="n">
         <v>79</v>
@@ -1959,17 +1959,17 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2020-10-09</t>
+          <t>2020-10-16</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>18363804782</v>
+        <v>19779199722</v>
       </c>
       <c r="C81" t="n">
-        <v>50410563994</v>
+        <v>51552706029</v>
       </c>
       <c r="D81" t="n">
-        <v>0.3642848507742486</v>
+        <v>0.3836694762613156</v>
       </c>
       <c r="E81" t="n">
         <v>80</v>
@@ -1978,17 +1978,17 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2020-10-12</t>
+          <t>2020-10-19</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>24824121596</v>
+        <v>20562725471</v>
       </c>
       <c r="C82" t="n">
-        <v>69075123930</v>
+        <v>53895497648</v>
       </c>
       <c r="D82" t="n">
-        <v>0.3593786038104905</v>
+        <v>0.3815295593947087</v>
       </c>
       <c r="E82" t="n">
         <v>81</v>
@@ -1997,17 +1997,17 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2020-10-13</t>
+          <t>2020-10-20</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>21950874234</v>
+        <v>18296672779</v>
       </c>
       <c r="C83" t="n">
-        <v>58435290007</v>
+        <v>47922773316</v>
       </c>
       <c r="D83" t="n">
-        <v>0.3756441395494142</v>
+        <v>0.3817949486844761</v>
       </c>
       <c r="E83" t="n">
         <v>82</v>
@@ -2016,17 +2016,17 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2020-10-14</t>
+          <t>2020-10-21</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>21810988673</v>
+        <v>18370049664</v>
       </c>
       <c r="C84" t="n">
-        <v>58022364557</v>
+        <v>49307563396</v>
       </c>
       <c r="D84" t="n">
-        <v>0.3759065808421738</v>
+        <v>0.3725604836009853</v>
       </c>
       <c r="E84" t="n">
         <v>83</v>
@@ -2035,17 +2035,17 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2020-10-15</t>
+          <t>2020-10-22</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>20410751440</v>
+        <v>17665602844</v>
       </c>
       <c r="C85" t="n">
-        <v>54415224691</v>
+        <v>46460364776</v>
       </c>
       <c r="D85" t="n">
-        <v>0.3750926612157467</v>
+        <v>0.3802295339085566</v>
       </c>
       <c r="E85" t="n">
         <v>84</v>
@@ -2054,17 +2054,17 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2020-10-16</t>
+          <t>2020-10-23</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>19779199722</v>
+        <v>17466910909</v>
       </c>
       <c r="C86" t="n">
-        <v>51552706029</v>
+        <v>47398504650</v>
       </c>
       <c r="D86" t="n">
-        <v>0.3836694762613156</v>
+        <v>0.3685118557637873</v>
       </c>
       <c r="E86" t="n">
         <v>85</v>
@@ -2073,17 +2073,17 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2020-10-19</t>
+          <t>2020-10-26</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>20562725471</v>
+        <v>16145407434</v>
       </c>
       <c r="C87" t="n">
-        <v>53895497648</v>
+        <v>44150494774</v>
       </c>
       <c r="D87" t="n">
-        <v>0.3815295593947087</v>
+        <v>0.3656902944496094</v>
       </c>
       <c r="E87" t="n">
         <v>86</v>
@@ -2092,17 +2092,17 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2020-10-20</t>
+          <t>2020-10-27</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>18296672779</v>
+        <v>15491813981</v>
       </c>
       <c r="C88" t="n">
-        <v>47922773316</v>
+        <v>43505082864</v>
       </c>
       <c r="D88" t="n">
-        <v>0.3817949486844761</v>
+        <v>0.356092046288672</v>
       </c>
       <c r="E88" t="n">
         <v>87</v>
@@ -2111,17 +2111,17 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2020-10-21</t>
+          <t>2020-10-28</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>18370049664</v>
+        <v>17543172634</v>
       </c>
       <c r="C89" t="n">
-        <v>49307563396</v>
+        <v>49485508785</v>
       </c>
       <c r="D89" t="n">
-        <v>0.3725604836009853</v>
+        <v>0.3545113117906887</v>
       </c>
       <c r="E89" t="n">
         <v>88</v>
@@ -2130,17 +2130,17 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2020-10-22</t>
+          <t>2020-10-29</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>17665602844</v>
+        <v>18553392322</v>
       </c>
       <c r="C90" t="n">
-        <v>46460364776</v>
+        <v>51689467398</v>
       </c>
       <c r="D90" t="n">
-        <v>0.3802295339085566</v>
+        <v>0.3589395142948963</v>
       </c>
       <c r="E90" t="n">
         <v>89</v>
@@ -2149,17 +2149,17 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2020-10-23</t>
+          <t>2020-10-30</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>17466910909</v>
+        <v>20650226596</v>
       </c>
       <c r="C91" t="n">
-        <v>47398504650</v>
+        <v>60348197366</v>
       </c>
       <c r="D91" t="n">
-        <v>0.3685118557637873</v>
+        <v>0.3421846467220954</v>
       </c>
       <c r="E91" t="n">
         <v>90</v>
@@ -2168,17 +2168,17 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2020-10-26</t>
+          <t>2020-11-02</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>16145407434</v>
+        <v>19992661394</v>
       </c>
       <c r="C92" t="n">
-        <v>44150494774</v>
+        <v>56353918211</v>
       </c>
       <c r="D92" t="n">
-        <v>0.3656902944496094</v>
+        <v>0.3547696775784711</v>
       </c>
       <c r="E92" t="n">
         <v>91</v>
@@ -2187,17 +2187,17 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2020-10-27</t>
+          <t>2020-11-03</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>15491813981</v>
+        <v>20249408150</v>
       </c>
       <c r="C93" t="n">
-        <v>43505082864</v>
+        <v>55344378404</v>
       </c>
       <c r="D93" t="n">
-        <v>0.356092046288672</v>
+        <v>0.365880126111173</v>
       </c>
       <c r="E93" t="n">
         <v>92</v>
@@ -2206,17 +2206,17 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2020-10-28</t>
+          <t>2020-11-04</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>17543172634</v>
+        <v>18257580496</v>
       </c>
       <c r="C94" t="n">
-        <v>49485508785</v>
+        <v>49909415865</v>
       </c>
       <c r="D94" t="n">
-        <v>0.3545113117906887</v>
+        <v>0.3658143494483073</v>
       </c>
       <c r="E94" t="n">
         <v>93</v>
@@ -2225,17 +2225,17 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2020-10-29</t>
+          <t>2020-11-05</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>18553392322</v>
+        <v>21285267389</v>
       </c>
       <c r="C95" t="n">
-        <v>51689467398</v>
+        <v>58980118835</v>
       </c>
       <c r="D95" t="n">
-        <v>0.3589395142948963</v>
+        <v>0.3608888522002924</v>
       </c>
       <c r="E95" t="n">
         <v>94</v>
@@ -2244,17 +2244,17 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2020-10-30</t>
+          <t>2020-11-06</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>20650226596</v>
+        <v>23071856412</v>
       </c>
       <c r="C96" t="n">
-        <v>60348197366</v>
+        <v>59902082650</v>
       </c>
       <c r="D96" t="n">
-        <v>0.3421846467220954</v>
+        <v>0.3851595034984981</v>
       </c>
       <c r="E96" t="n">
         <v>95</v>
@@ -2263,17 +2263,17 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2020-11-02</t>
+          <t>2020-11-09</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>19992661394</v>
+        <v>27202863336</v>
       </c>
       <c r="C97" t="n">
-        <v>56353918211</v>
+        <v>74478178320</v>
       </c>
       <c r="D97" t="n">
-        <v>0.3547696775784711</v>
+        <v>0.3652460888492902</v>
       </c>
       <c r="E97" t="n">
         <v>96</v>
@@ -2282,17 +2282,17 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2020-11-03</t>
+          <t>2020-11-10</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>20249408150</v>
+        <v>25309810082</v>
       </c>
       <c r="C98" t="n">
-        <v>55344378404</v>
+        <v>67090114044</v>
       </c>
       <c r="D98" t="n">
-        <v>0.365880126111173</v>
+        <v>0.3772509622714452</v>
       </c>
       <c r="E98" t="n">
         <v>97</v>
@@ -2301,17 +2301,17 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2020-11-04</t>
+          <t>2020-11-11</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>18257580496</v>
+        <v>23822441228</v>
       </c>
       <c r="C99" t="n">
-        <v>49909415865</v>
+        <v>61988411650</v>
       </c>
       <c r="D99" t="n">
-        <v>0.3658143494483073</v>
+        <v>0.3843047529997488</v>
       </c>
       <c r="E99" t="n">
         <v>98</v>
@@ -2320,17 +2320,17 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2020-11-05</t>
+          <t>2020-11-12</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>21285267389</v>
+        <v>19076439758</v>
       </c>
       <c r="C100" t="n">
-        <v>58980118835</v>
+        <v>51703999860</v>
       </c>
       <c r="D100" t="n">
-        <v>0.3608888522002924</v>
+        <v>0.3689548160616911</v>
       </c>
       <c r="E100" t="n">
         <v>99</v>
@@ -2339,17 +2339,17 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2020-11-06</t>
+          <t>2020-11-13</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>23071856412</v>
+        <v>20119982649</v>
       </c>
       <c r="C101" t="n">
-        <v>59902082650</v>
+        <v>52210418675</v>
       </c>
       <c r="D101" t="n">
-        <v>0.3851595034984981</v>
+        <v>0.3853633653896379</v>
       </c>
       <c r="E101" t="n">
         <v>100</v>
@@ -2358,17 +2358,17 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2020-11-09</t>
+          <t>2020-11-16</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>27202863336</v>
+        <v>23217241543</v>
       </c>
       <c r="C102" t="n">
-        <v>74478178320</v>
+        <v>61350411349</v>
       </c>
       <c r="D102" t="n">
-        <v>0.3652460888492902</v>
+        <v>0.3784366075546849</v>
       </c>
       <c r="E102" t="n">
         <v>101</v>
@@ -2377,17 +2377,17 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2020-11-10</t>
+          <t>2020-11-17</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>25309810082</v>
+        <v>24335506367</v>
       </c>
       <c r="C103" t="n">
-        <v>67090114044</v>
+        <v>64241703103</v>
       </c>
       <c r="D103" t="n">
-        <v>0.3772509622714452</v>
+        <v>0.3788116626980203</v>
       </c>
       <c r="E103" t="n">
         <v>102</v>
@@ -2396,17 +2396,17 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2020-11-11</t>
+          <t>2020-11-18</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>23822441228</v>
+        <v>25490702717</v>
       </c>
       <c r="C104" t="n">
-        <v>61988411650</v>
+        <v>63205463709</v>
       </c>
       <c r="D104" t="n">
-        <v>0.3843047529997488</v>
+        <v>0.4032990381078449</v>
       </c>
       <c r="E104" t="n">
         <v>103</v>
@@ -2415,17 +2415,17 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2020-11-12</t>
+          <t>2020-11-19</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>19076439758</v>
+        <v>23177522765</v>
       </c>
       <c r="C105" t="n">
-        <v>51703999860</v>
+        <v>59756276020</v>
       </c>
       <c r="D105" t="n">
-        <v>0.3689548160616911</v>
+        <v>0.3878675899623104</v>
       </c>
       <c r="E105" t="n">
         <v>104</v>
@@ -2434,17 +2434,17 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2020-11-13</t>
+          <t>2020-11-20</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>20119982649</v>
+        <v>22935620159</v>
       </c>
       <c r="C106" t="n">
-        <v>52210418675</v>
+        <v>58875754449</v>
       </c>
       <c r="D106" t="n">
-        <v>0.3853633653896379</v>
+        <v>0.3895596816320637</v>
       </c>
       <c r="E106" t="n">
         <v>105</v>
@@ -2453,17 +2453,17 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2020-11-16</t>
+          <t>2020-11-23</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>23217241543</v>
+        <v>32096579820</v>
       </c>
       <c r="C107" t="n">
-        <v>61350411349</v>
+        <v>77198006469</v>
       </c>
       <c r="D107" t="n">
-        <v>0.3784366075546849</v>
+        <v>0.4157695423506675</v>
       </c>
       <c r="E107" t="n">
         <v>106</v>
@@ -2472,17 +2472,17 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2020-11-17</t>
+          <t>2020-11-24</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>24335506367</v>
+        <v>26709718473</v>
       </c>
       <c r="C108" t="n">
-        <v>64241703103</v>
+        <v>65410116144</v>
       </c>
       <c r="D108" t="n">
-        <v>0.3788116626980203</v>
+        <v>0.408342318399171</v>
       </c>
       <c r="E108" t="n">
         <v>107</v>
@@ -2491,17 +2491,17 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2020-11-18</t>
+          <t>2020-11-25</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>25490702717</v>
+        <v>27089790866</v>
       </c>
       <c r="C109" t="n">
-        <v>63205463709</v>
+        <v>68837443765</v>
       </c>
       <c r="D109" t="n">
-        <v>0.4032990381078449</v>
+        <v>0.3935327836762824</v>
       </c>
       <c r="E109" t="n">
         <v>108</v>
@@ -2510,17 +2510,17 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2020-11-19</t>
+          <t>2020-11-26</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>23177522765</v>
+        <v>21689088930</v>
       </c>
       <c r="C110" t="n">
-        <v>59756276020</v>
+        <v>57127013421</v>
       </c>
       <c r="D110" t="n">
-        <v>0.3878675899623104</v>
+        <v>0.3796643239540867</v>
       </c>
       <c r="E110" t="n">
         <v>109</v>
@@ -2529,17 +2529,17 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2020-11-20</t>
+          <t>2020-11-27</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>22935620159</v>
+        <v>23626364341</v>
       </c>
       <c r="C111" t="n">
-        <v>58875754449</v>
+        <v>58765160877</v>
       </c>
       <c r="D111" t="n">
-        <v>0.3895596816320637</v>
+        <v>0.4020471311301572</v>
       </c>
       <c r="E111" t="n">
         <v>110</v>
@@ -2548,17 +2548,17 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2020-11-23</t>
+          <t>2020-11-30</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>32096579820</v>
+        <v>33970232252</v>
       </c>
       <c r="C112" t="n">
-        <v>77198006469</v>
+        <v>75092505579</v>
       </c>
       <c r="D112" t="n">
-        <v>0.4157695423506675</v>
+        <v>0.4523784629381171</v>
       </c>
       <c r="E112" t="n">
         <v>111</v>
@@ -2567,17 +2567,17 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2020-11-24</t>
+          <t>2020-12-01</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>26709718473</v>
+        <v>28738868941</v>
       </c>
       <c r="C113" t="n">
-        <v>65410116144</v>
+        <v>67936162045</v>
       </c>
       <c r="D113" t="n">
-        <v>0.408342318399171</v>
+        <v>0.4230275611089682</v>
       </c>
       <c r="E113" t="n">
         <v>112</v>
@@ -2586,17 +2586,17 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2020-11-25</t>
+          <t>2020-12-02</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>27089790866</v>
+        <v>28928357564</v>
       </c>
       <c r="C114" t="n">
-        <v>68837443765</v>
+        <v>69689843826</v>
       </c>
       <c r="D114" t="n">
-        <v>0.3935327836762824</v>
+        <v>0.4151014835996427</v>
       </c>
       <c r="E114" t="n">
         <v>113</v>
@@ -2605,17 +2605,17 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2020-11-26</t>
+          <t>2020-12-03</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>21689088930</v>
+        <v>28497726227</v>
       </c>
       <c r="C115" t="n">
-        <v>57127013421</v>
+        <v>66950741850</v>
       </c>
       <c r="D115" t="n">
-        <v>0.3796643239540867</v>
+        <v>0.4256521352795137</v>
       </c>
       <c r="E115" t="n">
         <v>114</v>
@@ -2624,17 +2624,17 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2020-11-27</t>
+          <t>2020-12-04</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>23626364341</v>
+        <v>23614518756</v>
       </c>
       <c r="C116" t="n">
-        <v>58765160877</v>
+        <v>57124426015</v>
       </c>
       <c r="D116" t="n">
-        <v>0.4020471311301572</v>
+        <v>0.4133874141649876</v>
       </c>
       <c r="E116" t="n">
         <v>115</v>
@@ -2643,17 +2643,17 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2020-11-30</t>
+          <t>2020-12-07</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>33970232252</v>
+        <v>22345056458</v>
       </c>
       <c r="C117" t="n">
-        <v>75092505579</v>
+        <v>56856559648</v>
       </c>
       <c r="D117" t="n">
-        <v>0.4523784629381171</v>
+        <v>0.3930075367967857</v>
       </c>
       <c r="E117" t="n">
         <v>116</v>
@@ -2662,17 +2662,17 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2020-12-01</t>
+          <t>2020-12-08</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>28738868941</v>
+        <v>20555717183</v>
       </c>
       <c r="C118" t="n">
-        <v>67936162045</v>
+        <v>51665831943</v>
       </c>
       <c r="D118" t="n">
-        <v>0.4230275611089682</v>
+        <v>0.3978590184259099</v>
       </c>
       <c r="E118" t="n">
         <v>117</v>
@@ -2681,17 +2681,17 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2020-12-02</t>
+          <t>2020-12-09</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>28928357564</v>
+        <v>22167887887</v>
       </c>
       <c r="C119" t="n">
-        <v>69689843826</v>
+        <v>59426788696</v>
       </c>
       <c r="D119" t="n">
-        <v>0.4151014835996427</v>
+        <v>0.3730285343265085</v>
       </c>
       <c r="E119" t="n">
         <v>118</v>
@@ -2700,17 +2700,17 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2020-12-03</t>
+          <t>2020-12-10</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>28497726227</v>
+        <v>21008686040</v>
       </c>
       <c r="C120" t="n">
-        <v>66950741850</v>
+        <v>53530291688</v>
       </c>
       <c r="D120" t="n">
-        <v>0.4256521352795137</v>
+        <v>0.3924635076238444</v>
       </c>
       <c r="E120" t="n">
         <v>119</v>
@@ -2719,17 +2719,17 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2020-12-04</t>
+          <t>2020-12-11</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>23614518756</v>
+        <v>24084146686</v>
       </c>
       <c r="C121" t="n">
-        <v>57124426015</v>
+        <v>64194443337</v>
       </c>
       <c r="D121" t="n">
-        <v>0.4133874141649876</v>
+        <v>0.3751749440300626</v>
       </c>
       <c r="E121" t="n">
         <v>120</v>
@@ -2738,17 +2738,17 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2020-12-07</t>
+          <t>2020-12-14</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>22345056458</v>
+        <v>20561369384</v>
       </c>
       <c r="C122" t="n">
-        <v>56856559648</v>
+        <v>52737085483</v>
       </c>
       <c r="D122" t="n">
-        <v>0.3930075367967857</v>
+        <v>0.3898844465082932</v>
       </c>
       <c r="E122" t="n">
         <v>121</v>
@@ -2757,17 +2757,17 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2020-12-08</t>
+          <t>2020-12-15</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>20555717183</v>
+        <v>20518702233</v>
       </c>
       <c r="C123" t="n">
-        <v>51665831943</v>
+        <v>50712282528</v>
       </c>
       <c r="D123" t="n">
-        <v>0.3978590184259099</v>
+        <v>0.4046101104139991</v>
       </c>
       <c r="E123" t="n">
         <v>122</v>
@@ -2776,17 +2776,17 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2020-12-09</t>
+          <t>2020-12-16</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>22167887887</v>
+        <v>20098821894</v>
       </c>
       <c r="C124" t="n">
-        <v>59426788696</v>
+        <v>51594471274</v>
       </c>
       <c r="D124" t="n">
-        <v>0.3730285343265085</v>
+        <v>0.3895537912824469</v>
       </c>
       <c r="E124" t="n">
         <v>123</v>
@@ -2795,17 +2795,17 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2020-12-10</t>
+          <t>2020-12-17</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>21008686040</v>
+        <v>23623180829</v>
       </c>
       <c r="C125" t="n">
-        <v>53530291688</v>
+        <v>60346809075</v>
       </c>
       <c r="D125" t="n">
-        <v>0.3924635076238444</v>
+        <v>0.3914569998165226</v>
       </c>
       <c r="E125" t="n">
         <v>124</v>
@@ -2814,17 +2814,17 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2020-12-11</t>
+          <t>2020-12-18</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>24084146686</v>
+        <v>24395319589</v>
       </c>
       <c r="C126" t="n">
-        <v>64194443337</v>
+        <v>59011526731</v>
       </c>
       <c r="D126" t="n">
-        <v>0.3751749440300626</v>
+        <v>0.4133992279204094</v>
       </c>
       <c r="E126" t="n">
         <v>125</v>
@@ -2833,17 +2833,17 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2020-12-14</t>
+          <t>2020-12-21</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>20561369384</v>
+        <v>25669905456</v>
       </c>
       <c r="C127" t="n">
-        <v>52737085483</v>
+        <v>62473191028</v>
       </c>
       <c r="D127" t="n">
-        <v>0.3898844465082932</v>
+        <v>0.410894737944392</v>
       </c>
       <c r="E127" t="n">
         <v>126</v>
@@ -2852,17 +2852,17 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2020-12-15</t>
+          <t>2020-12-22</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>20518702233</v>
+        <v>27752409533</v>
       </c>
       <c r="C128" t="n">
-        <v>50712282528</v>
+        <v>70592976908</v>
       </c>
       <c r="D128" t="n">
-        <v>0.4046101104139991</v>
+        <v>0.3931327271998773</v>
       </c>
       <c r="E128" t="n">
         <v>127</v>
@@ -2871,17 +2871,17 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2020-12-16</t>
+          <t>2020-12-23</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>20098821894</v>
+        <v>26781996550</v>
       </c>
       <c r="C129" t="n">
-        <v>51594471274</v>
+        <v>66516491988</v>
       </c>
       <c r="D129" t="n">
-        <v>0.3895537912824469</v>
+        <v>0.4026369363380084</v>
       </c>
       <c r="E129" t="n">
         <v>128</v>
@@ -2890,17 +2890,17 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2020-12-17</t>
+          <t>2020-12-24</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>23623180829</v>
+        <v>23869444669</v>
       </c>
       <c r="C130" t="n">
-        <v>60346809075</v>
+        <v>63015856260</v>
       </c>
       <c r="D130" t="n">
-        <v>0.3914569998165226</v>
+        <v>0.3787847390427572</v>
       </c>
       <c r="E130" t="n">
         <v>129</v>
@@ -2909,17 +2909,17 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2020-12-18</t>
+          <t>2020-12-25</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>24395319589</v>
+        <v>25870374333</v>
       </c>
       <c r="C131" t="n">
-        <v>59011526731</v>
+        <v>63035613181</v>
       </c>
       <c r="D131" t="n">
-        <v>0.4133992279204094</v>
+        <v>0.4104088629822002</v>
       </c>
       <c r="E131" t="n">
         <v>130</v>
@@ -2928,17 +2928,17 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>2020-12-21</t>
+          <t>2020-12-28</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>25669905456</v>
+        <v>27591719605</v>
       </c>
       <c r="C132" t="n">
-        <v>62473191028</v>
+        <v>68634054637</v>
       </c>
       <c r="D132" t="n">
-        <v>0.410894737944392</v>
+        <v>0.4020120878903394</v>
       </c>
       <c r="E132" t="n">
         <v>131</v>
@@ -2947,17 +2947,17 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>2020-12-22</t>
+          <t>2020-12-29</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>27752409533</v>
+        <v>28714767727</v>
       </c>
       <c r="C133" t="n">
-        <v>70592976908</v>
+        <v>68080937199</v>
       </c>
       <c r="D133" t="n">
-        <v>0.3931327271998773</v>
+        <v>0.4217739782733451</v>
       </c>
       <c r="E133" t="n">
         <v>132</v>
@@ -2966,17 +2966,17 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2020-12-23</t>
+          <t>2020-12-30</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>26781996550</v>
+        <v>27431057672</v>
       </c>
       <c r="C134" t="n">
-        <v>66516491988</v>
+        <v>63970764234</v>
       </c>
       <c r="D134" t="n">
-        <v>0.4026369363380084</v>
+        <v>0.4288061585704895</v>
       </c>
       <c r="E134" t="n">
         <v>133</v>
@@ -2985,17 +2985,17 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>2020-12-24</t>
+          <t>2020-12-31</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>23869444669</v>
+        <v>29516497306</v>
       </c>
       <c r="C135" t="n">
-        <v>63015856260</v>
+        <v>70483427194</v>
       </c>
       <c r="D135" t="n">
-        <v>0.3787847390427572</v>
+        <v>0.4187721636287379</v>
       </c>
       <c r="E135" t="n">
         <v>134</v>
@@ -3004,17 +3004,17 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>2020-12-25</t>
+          <t>2021-01-04</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>25870374333</v>
+        <v>32842910849</v>
       </c>
       <c r="C136" t="n">
-        <v>63035613181</v>
+        <v>81262611004</v>
       </c>
       <c r="D136" t="n">
-        <v>0.4104088629822002</v>
+        <v>0.4041577109475767</v>
       </c>
       <c r="E136" t="n">
         <v>135</v>
@@ -3023,17 +3023,17 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>2020-12-28</t>
+          <t>2021-01-05</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>27591719605</v>
+        <v>34955476638</v>
       </c>
       <c r="C137" t="n">
-        <v>68634054637</v>
+        <v>86306603527</v>
       </c>
       <c r="D137" t="n">
-        <v>0.4020120878903394</v>
+        <v>0.4050150881799513</v>
       </c>
       <c r="E137" t="n">
         <v>136</v>
@@ -3042,17 +3042,17 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>2020-12-29</t>
+          <t>2021-01-06</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>28714767727</v>
+        <v>31318863380</v>
       </c>
       <c r="C138" t="n">
-        <v>68080937199</v>
+        <v>79924024318</v>
       </c>
       <c r="D138" t="n">
-        <v>0.4217739782733451</v>
+        <v>0.3918579381762507</v>
       </c>
       <c r="E138" t="n">
         <v>137</v>
@@ -3061,17 +3061,17 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>2020-12-30</t>
+          <t>2021-01-07</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>27431057672</v>
+        <v>34820241307</v>
       </c>
       <c r="C139" t="n">
-        <v>63970764234</v>
+        <v>87045282583</v>
       </c>
       <c r="D139" t="n">
-        <v>0.4288061585704895</v>
+        <v>0.4000244501911746</v>
       </c>
       <c r="E139" t="n">
         <v>138</v>
@@ -3080,17 +3080,17 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>2020-12-31</t>
+          <t>2021-01-08</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>29516497306</v>
+        <v>31741361539</v>
       </c>
       <c r="C140" t="n">
-        <v>70483427194</v>
+        <v>76243328872</v>
       </c>
       <c r="D140" t="n">
-        <v>0.4187721636287379</v>
+        <v>0.4163165749529185</v>
       </c>
       <c r="E140" t="n">
         <v>139</v>
@@ -3099,17 +3099,17 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>2021-01-04</t>
+          <t>2021-01-11</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>32842910849</v>
+        <v>33861909952</v>
       </c>
       <c r="C141" t="n">
-        <v>81262611004</v>
+        <v>79843929989</v>
       </c>
       <c r="D141" t="n">
-        <v>0.4041577109475767</v>
+        <v>0.4241012429706943</v>
       </c>
       <c r="E141" t="n">
         <v>140</v>
@@ -3118,17 +3118,17 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>2021-01-05</t>
+          <t>2021-01-12</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>34955476638</v>
+        <v>31336739617</v>
       </c>
       <c r="C142" t="n">
-        <v>86306603527</v>
+        <v>70684174141</v>
       </c>
       <c r="D142" t="n">
-        <v>0.4050150881799513</v>
+        <v>0.4433345936035105</v>
       </c>
       <c r="E142" t="n">
         <v>141</v>
@@ -3137,17 +3137,17 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>2021-01-06</t>
+          <t>2021-01-13</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>31318863380</v>
+        <v>36176556832</v>
       </c>
       <c r="C143" t="n">
-        <v>79924024318</v>
+        <v>81782457644</v>
       </c>
       <c r="D143" t="n">
-        <v>0.3918579381762507</v>
+        <v>0.4423510600461162</v>
       </c>
       <c r="E143" t="n">
         <v>142</v>
@@ -3156,17 +3156,17 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>2021-01-07</t>
+          <t>2021-01-14</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>34820241307</v>
+        <v>32971296424</v>
       </c>
       <c r="C144" t="n">
-        <v>87045282583</v>
+        <v>74034016193</v>
       </c>
       <c r="D144" t="n">
-        <v>0.4000244501911746</v>
+        <v>0.4453533405245341</v>
       </c>
       <c r="E144" t="n">
         <v>143</v>
@@ -3175,17 +3175,17 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>2021-01-08</t>
+          <t>2021-01-15</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>31741361539</v>
+        <v>31268748151</v>
       </c>
       <c r="C145" t="n">
-        <v>76243328872</v>
+        <v>68522530970</v>
       </c>
       <c r="D145" t="n">
-        <v>0.4163165749529185</v>
+        <v>0.4563279801309417</v>
       </c>
       <c r="E145" t="n">
         <v>144</v>
@@ -3194,17 +3194,17 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>2021-01-11</t>
+          <t>2021-01-18</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>33861909952</v>
+        <v>28025154838</v>
       </c>
       <c r="C146" t="n">
-        <v>79843929989</v>
+        <v>66132336803</v>
       </c>
       <c r="D146" t="n">
-        <v>0.4241012429706943</v>
+        <v>0.4237738479056539</v>
       </c>
       <c r="E146" t="n">
         <v>145</v>
@@ -3213,17 +3213,17 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>2021-01-12</t>
+          <t>2021-01-19</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>31336739617</v>
+        <v>30160755219</v>
       </c>
       <c r="C147" t="n">
-        <v>70684174141</v>
+        <v>71588657610</v>
       </c>
       <c r="D147" t="n">
-        <v>0.4433345936035105</v>
+        <v>0.4213063385447102</v>
       </c>
       <c r="E147" t="n">
         <v>146</v>
@@ -3232,17 +3232,17 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>2021-01-13</t>
+          <t>2021-01-20</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>36176556832</v>
+        <v>25498108632</v>
       </c>
       <c r="C148" t="n">
-        <v>81782457644</v>
+        <v>61023142374</v>
       </c>
       <c r="D148" t="n">
-        <v>0.4423510600461162</v>
+        <v>0.4178432581483041</v>
       </c>
       <c r="E148" t="n">
         <v>147</v>
@@ -3251,17 +3251,17 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>2021-01-14</t>
+          <t>2021-01-21</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>32971296424</v>
+        <v>31550851527</v>
       </c>
       <c r="C149" t="n">
-        <v>74034016193</v>
+        <v>73606094304</v>
       </c>
       <c r="D149" t="n">
-        <v>0.4453533405245341</v>
+        <v>0.4286445548474839</v>
       </c>
       <c r="E149" t="n">
         <v>148</v>
@@ -3270,17 +3270,17 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>2021-01-15</t>
+          <t>2021-01-22</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>31268748151</v>
+        <v>29587073243</v>
       </c>
       <c r="C150" t="n">
-        <v>68522530970</v>
+        <v>71863919964</v>
       </c>
       <c r="D150" t="n">
-        <v>0.4563279801309417</v>
+        <v>0.4117097043665521</v>
       </c>
       <c r="E150" t="n">
         <v>149</v>
@@ -3289,17 +3289,17 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>2021-01-18</t>
+          <t>2021-01-25</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>28025154838</v>
+        <v>29768085597</v>
       </c>
       <c r="C151" t="n">
-        <v>66132336803</v>
+        <v>72841620023</v>
       </c>
       <c r="D151" t="n">
-        <v>0.4237738479056539</v>
+        <v>0.4086686373477226</v>
       </c>
       <c r="E151" t="n">
         <v>150</v>
@@ -3308,17 +3308,17 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>2021-01-19</t>
+          <t>2021-01-26</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>30160755219</v>
+        <v>25588114580</v>
       </c>
       <c r="C152" t="n">
-        <v>71588657610</v>
+        <v>62625061804</v>
       </c>
       <c r="D152" t="n">
-        <v>0.4213063385447102</v>
+        <v>0.4085922447483418</v>
       </c>
       <c r="E152" t="n">
         <v>151</v>
@@ -3327,17 +3327,17 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>2021-01-20</t>
+          <t>2021-01-27</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>25498108632</v>
+        <v>25604690493</v>
       </c>
       <c r="C153" t="n">
-        <v>61023142374</v>
+        <v>60015878129</v>
       </c>
       <c r="D153" t="n">
-        <v>0.4178432581483041</v>
+        <v>0.4266319396004584</v>
       </c>
       <c r="E153" t="n">
         <v>152</v>
@@ -3346,17 +3346,17 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>2021-01-21</t>
+          <t>2021-01-28</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>31550851527</v>
+        <v>26286085867</v>
       </c>
       <c r="C154" t="n">
-        <v>73606094304</v>
+        <v>62311898539</v>
       </c>
       <c r="D154" t="n">
-        <v>0.4286445548474839</v>
+        <v>0.4218469743872106</v>
       </c>
       <c r="E154" t="n">
         <v>153</v>
@@ -3365,17 +3365,17 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>2021-01-22</t>
+          <t>2021-01-29</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>29587073243</v>
+        <v>27002904913</v>
       </c>
       <c r="C155" t="n">
-        <v>71863919964</v>
+        <v>66018503681</v>
       </c>
       <c r="D155" t="n">
-        <v>0.4117097043665521</v>
+        <v>0.4090202504963981</v>
       </c>
       <c r="E155" t="n">
         <v>154</v>
@@ -3384,17 +3384,17 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>2021-01-25</t>
+          <t>2021-02-01</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>29768085597</v>
+        <v>25457673045</v>
       </c>
       <c r="C156" t="n">
-        <v>72841620023</v>
+        <v>61214730247</v>
       </c>
       <c r="D156" t="n">
-        <v>0.4086686373477226</v>
+        <v>0.4158749526834291</v>
       </c>
       <c r="E156" t="n">
         <v>155</v>
@@ -3403,17 +3403,17 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>2021-01-26</t>
+          <t>2021-02-02</t>
         </is>
       </c>
       <c r="B157" t="n">
-        <v>25588114580</v>
+        <v>24585679056</v>
       </c>
       <c r="C157" t="n">
-        <v>62625061804</v>
+        <v>59083806830</v>
       </c>
       <c r="D157" t="n">
-        <v>0.4085922447483418</v>
+        <v>0.4161153516519274</v>
       </c>
       <c r="E157" t="n">
         <v>156</v>
@@ -3422,17 +3422,17 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>2021-01-27</t>
+          <t>2021-02-03</t>
         </is>
       </c>
       <c r="B158" t="n">
-        <v>25604690493</v>
+        <v>27946762653</v>
       </c>
       <c r="C158" t="n">
-        <v>60015878129</v>
+        <v>64252239936</v>
       </c>
       <c r="D158" t="n">
-        <v>0.4266319396004584</v>
+        <v>0.4349539048107436</v>
       </c>
       <c r="E158" t="n">
         <v>157</v>
@@ -3441,17 +3441,17 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>2021-01-28</t>
+          <t>2021-02-04</t>
         </is>
       </c>
       <c r="B159" t="n">
-        <v>26286085867</v>
+        <v>26745949814</v>
       </c>
       <c r="C159" t="n">
-        <v>62311898539</v>
+        <v>65026335158</v>
       </c>
       <c r="D159" t="n">
-        <v>0.4218469743872106</v>
+        <v>0.411309506356357</v>
       </c>
       <c r="E159" t="n">
         <v>158</v>
@@ -3460,17 +3460,17 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>2021-01-29</t>
+          <t>2021-02-05</t>
         </is>
       </c>
       <c r="B160" t="n">
-        <v>27002904913</v>
+        <v>27228530445</v>
       </c>
       <c r="C160" t="n">
-        <v>66018503681</v>
+        <v>60817228192</v>
       </c>
       <c r="D160" t="n">
-        <v>0.4090202504963981</v>
+        <v>0.44771080916479</v>
       </c>
       <c r="E160" t="n">
         <v>159</v>
@@ -3479,17 +3479,17 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>2021-02-01</t>
+          <t>2021-02-08</t>
         </is>
       </c>
       <c r="B161" t="n">
-        <v>25457673045</v>
+        <v>22845413099</v>
       </c>
       <c r="C161" t="n">
-        <v>61214730247</v>
+        <v>53099229697</v>
       </c>
       <c r="D161" t="n">
-        <v>0.4158749526834291</v>
+        <v>0.4302400096830542</v>
       </c>
       <c r="E161" t="n">
         <v>160</v>
@@ -3498,17 +3498,17 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>2021-02-02</t>
+          <t>2021-02-09</t>
         </is>
       </c>
       <c r="B162" t="n">
-        <v>24585679056</v>
+        <v>23052987297</v>
       </c>
       <c r="C162" t="n">
-        <v>59083806830</v>
+        <v>54414450658</v>
       </c>
       <c r="D162" t="n">
-        <v>0.4161153516519274</v>
+        <v>0.4236556101960896</v>
       </c>
       <c r="E162" t="n">
         <v>161</v>
@@ -3517,17 +3517,17 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>2021-02-03</t>
+          <t>2021-02-10</t>
         </is>
       </c>
       <c r="B163" t="n">
-        <v>27946762653</v>
+        <v>23672043794</v>
       </c>
       <c r="C163" t="n">
-        <v>64252239936</v>
+        <v>53724833418</v>
       </c>
       <c r="D163" t="n">
-        <v>0.4349539048107436</v>
+        <v>0.4406164205260971</v>
       </c>
       <c r="E163" t="n">
         <v>162</v>
@@ -3536,17 +3536,17 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>2021-02-04</t>
+          <t>2021-02-18</t>
         </is>
       </c>
       <c r="B164" t="n">
-        <v>26745949814</v>
+        <v>30305438799</v>
       </c>
       <c r="C164" t="n">
-        <v>65026335158</v>
+        <v>70581483088</v>
       </c>
       <c r="D164" t="n">
-        <v>0.411309506356357</v>
+        <v>0.4293681213982937</v>
       </c>
       <c r="E164" t="n">
         <v>163</v>
@@ -3555,17 +3555,17 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>2021-02-05</t>
+          <t>2021-02-19</t>
         </is>
       </c>
       <c r="B165" t="n">
-        <v>27228530445</v>
+        <v>31871390359</v>
       </c>
       <c r="C165" t="n">
-        <v>60817228192</v>
+        <v>74891926971</v>
       </c>
       <c r="D165" t="n">
-        <v>0.44771080916479</v>
+        <v>0.4255650995779744</v>
       </c>
       <c r="E165" t="n">
         <v>164</v>
@@ -3574,17 +3574,17 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>2021-02-08</t>
+          <t>2021-02-22</t>
         </is>
       </c>
       <c r="B166" t="n">
-        <v>22845413099</v>
+        <v>41800730539</v>
       </c>
       <c r="C166" t="n">
-        <v>53099229697</v>
+        <v>98345390597</v>
       </c>
       <c r="D166" t="n">
-        <v>0.4302400096830542</v>
+        <v>0.4250400581588124</v>
       </c>
       <c r="E166" t="n">
         <v>165</v>
@@ -3593,17 +3593,17 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>2021-02-09</t>
+          <t>2021-02-23</t>
         </is>
       </c>
       <c r="B167" t="n">
-        <v>23052987297</v>
+        <v>36659765914</v>
       </c>
       <c r="C167" t="n">
-        <v>54414450658</v>
+        <v>79667225639</v>
       </c>
       <c r="D167" t="n">
-        <v>0.4236556101960896</v>
+        <v>0.4601611970287279</v>
       </c>
       <c r="E167" t="n">
         <v>166</v>
@@ -3612,17 +3612,17 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>2021-02-10</t>
+          <t>2021-02-24</t>
         </is>
       </c>
       <c r="B168" t="n">
-        <v>23672043794</v>
+        <v>33328852498</v>
       </c>
       <c r="C168" t="n">
-        <v>53724833418</v>
+        <v>74974298826</v>
       </c>
       <c r="D168" t="n">
-        <v>0.4406164205260971</v>
+        <v>0.4445370349557979</v>
       </c>
       <c r="E168" t="n">
         <v>167</v>
@@ -3631,17 +3631,17 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>2021-02-18</t>
+          <t>2021-02-25</t>
         </is>
       </c>
       <c r="B169" t="n">
-        <v>30305438799</v>
+        <v>33009105938</v>
       </c>
       <c r="C169" t="n">
-        <v>70581483088</v>
+        <v>72321851390</v>
       </c>
       <c r="D169" t="n">
-        <v>0.4293681213982937</v>
+        <v>0.4564195371603028</v>
       </c>
       <c r="E169" t="n">
         <v>168</v>
@@ -3650,17 +3650,17 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>2021-02-19</t>
+          <t>2021-02-26</t>
         </is>
       </c>
       <c r="B170" t="n">
-        <v>31871390359</v>
+        <v>29437488128</v>
       </c>
       <c r="C170" t="n">
-        <v>74891926971</v>
+        <v>67566280430</v>
       </c>
       <c r="D170" t="n">
-        <v>0.4255650995779744</v>
+        <v>0.4356831238993216</v>
       </c>
       <c r="E170" t="n">
         <v>169</v>
@@ -3669,17 +3669,17 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>2021-02-22</t>
+          <t>2021-03-01</t>
         </is>
       </c>
       <c r="B171" t="n">
-        <v>41800730539</v>
+        <v>28022529242</v>
       </c>
       <c r="C171" t="n">
-        <v>98345390597</v>
+        <v>65847760652</v>
       </c>
       <c r="D171" t="n">
-        <v>0.4250400581588124</v>
+        <v>0.425565409734991</v>
       </c>
       <c r="E171" t="n">
         <v>170</v>
@@ -3688,17 +3688,17 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>2021-02-23</t>
+          <t>2021-03-02</t>
         </is>
       </c>
       <c r="B172" t="n">
-        <v>36659765914</v>
+        <v>30548474585</v>
       </c>
       <c r="C172" t="n">
-        <v>79667225639</v>
+        <v>69441386639</v>
       </c>
       <c r="D172" t="n">
-        <v>0.4601611970287279</v>
+        <v>0.4399174046424243</v>
       </c>
       <c r="E172" t="n">
         <v>171</v>
@@ -3707,17 +3707,17 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>2021-02-24</t>
+          <t>2021-03-03</t>
         </is>
       </c>
       <c r="B173" t="n">
-        <v>33328852498</v>
+        <v>31581683271</v>
       </c>
       <c r="C173" t="n">
-        <v>74974298826</v>
+        <v>69999474895</v>
       </c>
       <c r="D173" t="n">
-        <v>0.4445370349557979</v>
+        <v>0.4511702883253464</v>
       </c>
       <c r="E173" t="n">
         <v>172</v>
@@ -3726,17 +3726,17 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>2021-02-25</t>
+          <t>2021-03-04</t>
         </is>
       </c>
       <c r="B174" t="n">
-        <v>33009105938</v>
+        <v>36100282673</v>
       </c>
       <c r="C174" t="n">
-        <v>72321851390</v>
+        <v>78562142790</v>
       </c>
       <c r="D174" t="n">
-        <v>0.4564195371603028</v>
+        <v>0.4595124495203449</v>
       </c>
       <c r="E174" t="n">
         <v>173</v>
@@ -3745,17 +3745,17 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>2021-02-26</t>
+          <t>2021-03-05</t>
         </is>
       </c>
       <c r="B175" t="n">
-        <v>29437488128</v>
+        <v>32337135967</v>
       </c>
       <c r="C175" t="n">
-        <v>67566280430</v>
+        <v>73514786011</v>
       </c>
       <c r="D175" t="n">
-        <v>0.4356831238993216</v>
+        <v>0.4398725443091326</v>
       </c>
       <c r="E175" t="n">
         <v>174</v>
@@ -3764,17 +3764,17 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>2021-03-01</t>
+          <t>2021-03-08</t>
         </is>
       </c>
       <c r="B176" t="n">
-        <v>28022529242</v>
+        <v>34237890063</v>
       </c>
       <c r="C176" t="n">
-        <v>65847760652</v>
+        <v>78814375242</v>
       </c>
       <c r="D176" t="n">
-        <v>0.425565409734991</v>
+        <v>0.4344117422471771</v>
       </c>
       <c r="E176" t="n">
         <v>175</v>
@@ -3783,17 +3783,17 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>2021-03-02</t>
+          <t>2021-03-09</t>
         </is>
       </c>
       <c r="B177" t="n">
-        <v>30548474585</v>
+        <v>35838361211</v>
       </c>
       <c r="C177" t="n">
-        <v>69441386639</v>
+        <v>82850202998</v>
       </c>
       <c r="D177" t="n">
-        <v>0.4399174046424243</v>
+        <v>0.4325681762284292</v>
       </c>
       <c r="E177" t="n">
         <v>176</v>
@@ -3802,17 +3802,17 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>2021-03-03</t>
+          <t>2021-03-10</t>
         </is>
       </c>
       <c r="B178" t="n">
-        <v>31581683271</v>
+        <v>26975456721</v>
       </c>
       <c r="C178" t="n">
-        <v>69999474895</v>
+        <v>62127335207</v>
       </c>
       <c r="D178" t="n">
-        <v>0.4511702883253464</v>
+        <v>0.4341962620981791</v>
       </c>
       <c r="E178" t="n">
         <v>177</v>
@@ -3821,17 +3821,17 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>2021-03-04</t>
+          <t>2021-03-11</t>
         </is>
       </c>
       <c r="B179" t="n">
-        <v>36100282673</v>
+        <v>30680047969</v>
       </c>
       <c r="C179" t="n">
-        <v>78562142790</v>
+        <v>66598157167</v>
       </c>
       <c r="D179" t="n">
-        <v>0.4595124495203449</v>
+        <v>0.4606741278451207</v>
       </c>
       <c r="E179" t="n">
         <v>178</v>
@@ -3840,17 +3840,17 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>2021-03-05</t>
+          <t>2021-03-12</t>
         </is>
       </c>
       <c r="B180" t="n">
-        <v>32337135967</v>
+        <v>33862968625</v>
       </c>
       <c r="C180" t="n">
-        <v>73514786011</v>
+        <v>72238010975</v>
       </c>
       <c r="D180" t="n">
-        <v>0.4398725443091326</v>
+        <v>0.4687693939513262</v>
       </c>
       <c r="E180" t="n">
         <v>179</v>
@@ -3859,17 +3859,17 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>2021-03-08</t>
+          <t>2021-03-15</t>
         </is>
       </c>
       <c r="B181" t="n">
-        <v>34237890063</v>
+        <v>34591765793</v>
       </c>
       <c r="C181" t="n">
-        <v>78814375242</v>
+        <v>71723136959</v>
       </c>
       <c r="D181" t="n">
-        <v>0.4344117422471771</v>
+        <v>0.4822957731585852</v>
       </c>
       <c r="E181" t="n">
         <v>180</v>
@@ -3878,17 +3878,17 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>2021-03-09</t>
+          <t>2021-03-16</t>
         </is>
       </c>
       <c r="B182" t="n">
-        <v>35838361211</v>
+        <v>29977825317</v>
       </c>
       <c r="C182" t="n">
-        <v>82850202998</v>
+        <v>67049266583</v>
       </c>
       <c r="D182" t="n">
-        <v>0.4325681762284292</v>
+        <v>0.447101465008429</v>
       </c>
       <c r="E182" t="n">
         <v>181</v>
@@ -3897,17 +3897,17 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>2021-03-10</t>
+          <t>2021-03-17</t>
         </is>
       </c>
       <c r="B183" t="n">
-        <v>26975456721</v>
+        <v>27491185060</v>
       </c>
       <c r="C183" t="n">
-        <v>62127335207</v>
+        <v>62515062852</v>
       </c>
       <c r="D183" t="n">
-        <v>0.4341962620981791</v>
+        <v>0.4397529780156095</v>
       </c>
       <c r="E183" t="n">
         <v>182</v>
@@ -3916,17 +3916,17 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>2021-03-11</t>
+          <t>2021-03-18</t>
         </is>
       </c>
       <c r="B184" t="n">
-        <v>30680047969</v>
+        <v>26739276351</v>
       </c>
       <c r="C184" t="n">
-        <v>66598157167</v>
+        <v>62832911819</v>
       </c>
       <c r="D184" t="n">
-        <v>0.4606741278451207</v>
+        <v>0.4255616296762858</v>
       </c>
       <c r="E184" t="n">
         <v>183</v>
@@ -3935,17 +3935,17 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>2021-03-12</t>
+          <t>2021-03-19</t>
         </is>
       </c>
       <c r="B185" t="n">
-        <v>33862968625</v>
+        <v>28358235249</v>
       </c>
       <c r="C185" t="n">
-        <v>72238010975</v>
+        <v>65875538395</v>
       </c>
       <c r="D185" t="n">
-        <v>0.4687693939513262</v>
+        <v>0.4304820262562349</v>
       </c>
       <c r="E185" t="n">
         <v>184</v>
@@ -3954,17 +3954,17 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>2021-03-15</t>
+          <t>2021-03-22</t>
         </is>
       </c>
       <c r="B186" t="n">
-        <v>34591765793</v>
+        <v>29121013208</v>
       </c>
       <c r="C186" t="n">
-        <v>71723136959</v>
+        <v>67358226346</v>
       </c>
       <c r="D186" t="n">
-        <v>0.4822957731585852</v>
+        <v>0.4323304633707791</v>
       </c>
       <c r="E186" t="n">
         <v>185</v>
@@ -3973,17 +3973,17 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>2021-03-16</t>
+          <t>2021-03-23</t>
         </is>
       </c>
       <c r="B187" t="n">
-        <v>29977825317</v>
+        <v>29320271653</v>
       </c>
       <c r="C187" t="n">
-        <v>67049266583</v>
+        <v>70323191299</v>
       </c>
       <c r="D187" t="n">
-        <v>0.447101465008429</v>
+        <v>0.4169360222623591</v>
       </c>
       <c r="E187" t="n">
         <v>186</v>
@@ -3992,17 +3992,17 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>2021-03-17</t>
+          <t>2021-03-24</t>
         </is>
       </c>
       <c r="B188" t="n">
-        <v>27491185060</v>
+        <v>28494202046</v>
       </c>
       <c r="C188" t="n">
-        <v>62515062852</v>
+        <v>67303523996</v>
       </c>
       <c r="D188" t="n">
-        <v>0.4397529780156095</v>
+        <v>0.423368649280437</v>
       </c>
       <c r="E188" t="n">
         <v>187</v>
@@ -4011,17 +4011,17 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>2021-03-18</t>
+          <t>2021-03-25</t>
         </is>
       </c>
       <c r="B189" t="n">
-        <v>26739276351</v>
+        <v>25857769578</v>
       </c>
       <c r="C189" t="n">
-        <v>62832911819</v>
+        <v>60650502617</v>
       </c>
       <c r="D189" t="n">
-        <v>0.4255616296762858</v>
+        <v>0.426340565407816</v>
       </c>
       <c r="E189" t="n">
         <v>188</v>
@@ -4030,17 +4030,17 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>2021-03-19</t>
+          <t>2021-03-26</t>
         </is>
       </c>
       <c r="B190" t="n">
-        <v>28358235249</v>
+        <v>25857588064</v>
       </c>
       <c r="C190" t="n">
-        <v>65875538395</v>
+        <v>61284664475</v>
       </c>
       <c r="D190" t="n">
-        <v>0.4304820262562349</v>
+        <v>0.4219259138564452</v>
       </c>
       <c r="E190" t="n">
         <v>189</v>
@@ -4049,17 +4049,17 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>2021-03-22</t>
+          <t>2021-03-29</t>
         </is>
       </c>
       <c r="B191" t="n">
-        <v>29121013208</v>
+        <v>26030305012</v>
       </c>
       <c r="C191" t="n">
-        <v>67358226346</v>
+        <v>62965892538</v>
       </c>
       <c r="D191" t="n">
-        <v>0.4323304633707791</v>
+        <v>0.4134032563151658</v>
       </c>
       <c r="E191" t="n">
         <v>190</v>
@@ -4068,17 +4068,17 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>2021-03-23</t>
+          <t>2021-03-30</t>
         </is>
       </c>
       <c r="B192" t="n">
-        <v>29320271653</v>
+        <v>25780001010</v>
       </c>
       <c r="C192" t="n">
-        <v>70323191299</v>
+        <v>62868502600</v>
       </c>
       <c r="D192" t="n">
-        <v>0.4169360222623591</v>
+        <v>0.4100622719460158</v>
       </c>
       <c r="E192" t="n">
         <v>191</v>
@@ -4087,17 +4087,17 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>2021-03-24</t>
+          <t>2021-03-31</t>
         </is>
       </c>
       <c r="B193" t="n">
-        <v>28494202046</v>
+        <v>25340940136</v>
       </c>
       <c r="C193" t="n">
-        <v>67303523996</v>
+        <v>58944651908</v>
       </c>
       <c r="D193" t="n">
-        <v>0.423368649280437</v>
+        <v>0.4299107606157687</v>
       </c>
       <c r="E193" t="n">
         <v>192</v>
@@ -4106,17 +4106,17 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>2021-03-25</t>
+          <t>2021-04-01</t>
         </is>
       </c>
       <c r="B194" t="n">
-        <v>25857769578</v>
+        <v>24459982838</v>
       </c>
       <c r="C194" t="n">
-        <v>60650502617</v>
+        <v>57742915146</v>
       </c>
       <c r="D194" t="n">
-        <v>0.426340565407816</v>
+        <v>0.4236014544148696</v>
       </c>
       <c r="E194" t="n">
         <v>193</v>
@@ -4125,17 +4125,17 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>2021-03-26</t>
+          <t>2021-04-02</t>
         </is>
       </c>
       <c r="B195" t="n">
-        <v>25857588064</v>
+        <v>23776468616</v>
       </c>
       <c r="C195" t="n">
-        <v>61284664475</v>
+        <v>57637646459</v>
       </c>
       <c r="D195" t="n">
-        <v>0.4219259138564452</v>
+        <v>0.4125162992717471</v>
       </c>
       <c r="E195" t="n">
         <v>194</v>
@@ -4144,17 +4144,17 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>2021-03-29</t>
+          <t>2021-04-06</t>
         </is>
       </c>
       <c r="B196" t="n">
-        <v>26030305012</v>
+        <v>21609152872</v>
       </c>
       <c r="C196" t="n">
-        <v>62965892538</v>
+        <v>54009467026</v>
       </c>
       <c r="D196" t="n">
-        <v>0.4134032563151658</v>
+        <v>0.4000993540928189</v>
       </c>
       <c r="E196" t="n">
         <v>195</v>
@@ -4163,17 +4163,17 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>2021-03-30</t>
+          <t>2021-04-07</t>
         </is>
       </c>
       <c r="B197" t="n">
-        <v>25780001010</v>
+        <v>28192988226</v>
       </c>
       <c r="C197" t="n">
-        <v>62868502600</v>
+        <v>64777711487</v>
       </c>
       <c r="D197" t="n">
-        <v>0.4100622719460158</v>
+        <v>0.4352266787266473</v>
       </c>
       <c r="E197" t="n">
         <v>196</v>
@@ -4182,17 +4182,17 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>2021-03-31</t>
+          <t>2021-04-08</t>
         </is>
       </c>
       <c r="B198" t="n">
-        <v>25340940136</v>
+        <v>31610774016</v>
       </c>
       <c r="C198" t="n">
-        <v>58944651908</v>
+        <v>70183037971</v>
       </c>
       <c r="D198" t="n">
-        <v>0.4299107606157687</v>
+        <v>0.4504047549076137</v>
       </c>
       <c r="E198" t="n">
         <v>197</v>
@@ -4201,17 +4201,17 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>2021-04-01</t>
+          <t>2021-04-09</t>
         </is>
       </c>
       <c r="B199" t="n">
-        <v>24459982838</v>
+        <v>27363203695</v>
       </c>
       <c r="C199" t="n">
-        <v>57742915146</v>
+        <v>60908586933</v>
       </c>
       <c r="D199" t="n">
-        <v>0.4236014544148696</v>
+        <v>0.4492503450309851</v>
       </c>
       <c r="E199" t="n">
         <v>198</v>
@@ -4220,17 +4220,17 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>2021-04-02</t>
+          <t>2021-04-12</t>
         </is>
       </c>
       <c r="B200" t="n">
-        <v>23776468616</v>
+        <v>29441281600</v>
       </c>
       <c r="C200" t="n">
-        <v>57637646459</v>
+        <v>66662877908</v>
       </c>
       <c r="D200" t="n">
-        <v>0.4125162992717471</v>
+        <v>0.4416443232563598</v>
       </c>
       <c r="E200" t="n">
         <v>199</v>
@@ -4239,17 +4239,17 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>2021-04-06</t>
+          <t>2021-04-13</t>
         </is>
       </c>
       <c r="B201" t="n">
-        <v>21609152872</v>
+        <v>26500289609</v>
       </c>
       <c r="C201" t="n">
-        <v>54009467026</v>
+        <v>60099497250</v>
       </c>
       <c r="D201" t="n">
-        <v>0.4000993540928189</v>
+        <v>0.4409402877159675</v>
       </c>
       <c r="E201" t="n">
         <v>200</v>
@@ -4258,17 +4258,17 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>2021-04-07</t>
+          <t>2021-04-14</t>
         </is>
       </c>
       <c r="B202" t="n">
-        <v>28192988226</v>
+        <v>24875678254</v>
       </c>
       <c r="C202" t="n">
-        <v>64777711487</v>
+        <v>56149660115</v>
       </c>
       <c r="D202" t="n">
-        <v>0.4352266787266473</v>
+        <v>0.4430245562137362</v>
       </c>
       <c r="E202" t="n">
         <v>201</v>
@@ -4277,17 +4277,17 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>2021-04-08</t>
+          <t>2021-04-15</t>
         </is>
       </c>
       <c r="B203" t="n">
-        <v>31610774016</v>
+        <v>23587218127</v>
       </c>
       <c r="C203" t="n">
-        <v>70183037971</v>
+        <v>56730832399</v>
       </c>
       <c r="D203" t="n">
-        <v>0.4504047549076137</v>
+        <v>0.4157742294543835</v>
       </c>
       <c r="E203" t="n">
         <v>202</v>
@@ -4296,17 +4296,17 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>2021-04-09</t>
+          <t>2021-04-16</t>
         </is>
       </c>
       <c r="B204" t="n">
-        <v>27363203695</v>
+        <v>23064238930</v>
       </c>
       <c r="C204" t="n">
-        <v>60908586933</v>
+        <v>60757105467</v>
       </c>
       <c r="D204" t="n">
-        <v>0.4492503450309851</v>
+        <v>0.3796138534368998</v>
       </c>
       <c r="E204" t="n">
         <v>203</v>
@@ -4315,17 +4315,17 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>2021-04-12</t>
+          <t>2021-04-19</t>
         </is>
       </c>
       <c r="B205" t="n">
-        <v>29441281600</v>
+        <v>26349229565</v>
       </c>
       <c r="C205" t="n">
-        <v>66662877908</v>
+        <v>68717257011</v>
       </c>
       <c r="D205" t="n">
-        <v>0.4416443232563598</v>
+        <v>0.3834441406877186</v>
       </c>
       <c r="E205" t="n">
         <v>204</v>
@@ -4334,17 +4334,17 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>2021-04-13</t>
+          <t>2021-04-20</t>
         </is>
       </c>
       <c r="B206" t="n">
-        <v>26500289609</v>
+        <v>26332452757</v>
       </c>
       <c r="C206" t="n">
-        <v>60099497250</v>
+        <v>66152179163</v>
       </c>
       <c r="D206" t="n">
-        <v>0.4409402877159675</v>
+        <v>0.3980587350284626</v>
       </c>
       <c r="E206" t="n">
         <v>205</v>
@@ -4353,17 +4353,17 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>2021-04-14</t>
+          <t>2021-04-21</t>
         </is>
       </c>
       <c r="B207" t="n">
-        <v>24875678254</v>
+        <v>23796108657</v>
       </c>
       <c r="C207" t="n">
-        <v>56149660115</v>
+        <v>58645267418</v>
       </c>
       <c r="D207" t="n">
-        <v>0.4430245562137362</v>
+        <v>0.4057634947316526</v>
       </c>
       <c r="E207" t="n">
         <v>206</v>
@@ -4372,17 +4372,17 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>2021-04-15</t>
+          <t>2021-04-22</t>
         </is>
       </c>
       <c r="B208" t="n">
-        <v>23587218127</v>
+        <v>23283868400</v>
       </c>
       <c r="C208" t="n">
-        <v>56730832399</v>
+        <v>57343158813</v>
       </c>
       <c r="D208" t="n">
-        <v>0.4157742294543835</v>
+        <v>0.406044398006226</v>
       </c>
       <c r="E208" t="n">
         <v>207</v>
@@ -4391,17 +4391,17 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>2021-04-16</t>
+          <t>2021-04-23</t>
         </is>
       </c>
       <c r="B209" t="n">
-        <v>23064238930</v>
+        <v>23110619160</v>
       </c>
       <c r="C209" t="n">
-        <v>60757105467</v>
+        <v>58758936747</v>
       </c>
       <c r="D209" t="n">
-        <v>0.3796138534368998</v>
+        <v>0.3933124123655954</v>
       </c>
       <c r="E209" t="n">
         <v>208</v>
@@ -4410,17 +4410,17 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>2021-04-19</t>
+          <t>2021-04-26</t>
         </is>
       </c>
       <c r="B210" t="n">
-        <v>26349229565</v>
+        <v>26080656908</v>
       </c>
       <c r="C210" t="n">
-        <v>68717257011</v>
+        <v>64990659217</v>
       </c>
       <c r="D210" t="n">
-        <v>0.3834441406877186</v>
+        <v>0.4012985438556365</v>
       </c>
       <c r="E210" t="n">
         <v>209</v>
@@ -4429,17 +4429,17 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>2021-04-20</t>
+          <t>2021-04-27</t>
         </is>
       </c>
       <c r="B211" t="n">
-        <v>26332452757</v>
+        <v>22805398723</v>
       </c>
       <c r="C211" t="n">
-        <v>66152179163</v>
+        <v>58465572266</v>
       </c>
       <c r="D211" t="n">
-        <v>0.3980587350284626</v>
+        <v>0.3900654323409783</v>
       </c>
       <c r="E211" t="n">
         <v>210</v>
@@ -4448,17 +4448,17 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>2021-04-21</t>
+          <t>2021-04-28</t>
         </is>
       </c>
       <c r="B212" t="n">
-        <v>23796108657</v>
+        <v>21764975470</v>
       </c>
       <c r="C212" t="n">
-        <v>58645267418</v>
+        <v>56258757783</v>
       </c>
       <c r="D212" t="n">
-        <v>0.4057634947316526</v>
+        <v>0.3868726635229197</v>
       </c>
       <c r="E212" t="n">
         <v>211</v>
@@ -4467,17 +4467,17 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>2021-04-22</t>
+          <t>2021-04-29</t>
         </is>
       </c>
       <c r="B213" t="n">
-        <v>23283868400</v>
+        <v>23871290845</v>
       </c>
       <c r="C213" t="n">
-        <v>57343158813</v>
+        <v>59672070298</v>
       </c>
       <c r="D213" t="n">
-        <v>0.406044398006226</v>
+        <v>0.400041270996426</v>
       </c>
       <c r="E213" t="n">
         <v>212</v>
@@ -4486,17 +4486,17 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>2021-04-23</t>
+          <t>2021-04-30</t>
         </is>
       </c>
       <c r="B214" t="n">
-        <v>23110619160</v>
+        <v>26727927563</v>
       </c>
       <c r="C214" t="n">
-        <v>58758936747</v>
+        <v>64623812735</v>
       </c>
       <c r="D214" t="n">
-        <v>0.3933124123655954</v>
+        <v>0.413592550978105</v>
       </c>
       <c r="E214" t="n">
         <v>213</v>
@@ -4505,17 +4505,17 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>2021-04-26</t>
+          <t>2021-05-06</t>
         </is>
       </c>
       <c r="B215" t="n">
-        <v>26080656908</v>
+        <v>28245158344</v>
       </c>
       <c r="C215" t="n">
-        <v>64990659217</v>
+        <v>64995398044</v>
       </c>
       <c r="D215" t="n">
-        <v>0.4012985438556365</v>
+        <v>0.4345716649797089</v>
       </c>
       <c r="E215" t="n">
         <v>214</v>
@@ -4524,17 +4524,17 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>2021-04-27</t>
+          <t>2021-05-07</t>
         </is>
       </c>
       <c r="B216" t="n">
-        <v>22805398723</v>
+        <v>33809492530</v>
       </c>
       <c r="C216" t="n">
-        <v>58465572266</v>
+        <v>72689004129</v>
       </c>
       <c r="D216" t="n">
-        <v>0.3900654323409783</v>
+        <v>0.4651252680529072</v>
       </c>
       <c r="E216" t="n">
         <v>215</v>
@@ -4543,17 +4543,17 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>2021-04-28</t>
+          <t>2021-05-10</t>
         </is>
       </c>
       <c r="B217" t="n">
-        <v>21764975470</v>
+        <v>34980447442</v>
       </c>
       <c r="C217" t="n">
-        <v>56258757783</v>
+        <v>74391256531</v>
       </c>
       <c r="D217" t="n">
-        <v>0.3868726635229197</v>
+        <v>0.4702225647636843</v>
       </c>
       <c r="E217" t="n">
         <v>216</v>
@@ -4562,17 +4562,17 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>2021-04-29</t>
+          <t>2021-05-11</t>
         </is>
       </c>
       <c r="B218" t="n">
-        <v>23871290845</v>
+        <v>33682768573</v>
       </c>
       <c r="C218" t="n">
-        <v>59672070298</v>
+        <v>73459473614</v>
       </c>
       <c r="D218" t="n">
-        <v>0.400041270996426</v>
+        <v>0.4585217796412401</v>
       </c>
       <c r="E218" t="n">
         <v>217</v>
@@ -4581,17 +4581,17 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>2021-04-30</t>
+          <t>2021-05-12</t>
         </is>
       </c>
       <c r="B219" t="n">
-        <v>26727927563</v>
+        <v>28011409229</v>
       </c>
       <c r="C219" t="n">
-        <v>64623812735</v>
+        <v>66061705250</v>
       </c>
       <c r="D219" t="n">
-        <v>0.413592550978105</v>
+        <v>0.4240188642269418</v>
       </c>
       <c r="E219" t="n">
         <v>218</v>
@@ -4600,17 +4600,17 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>2021-05-06</t>
+          <t>2021-05-13</t>
         </is>
       </c>
       <c r="B220" t="n">
-        <v>28245158344</v>
+        <v>29021959092</v>
       </c>
       <c r="C220" t="n">
-        <v>64995398044</v>
+        <v>69247970457</v>
       </c>
       <c r="D220" t="n">
-        <v>0.4345716649797089</v>
+        <v>0.4191019448002651</v>
       </c>
       <c r="E220" t="n">
         <v>219</v>
@@ -4619,17 +4619,17 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>2021-05-07</t>
+          <t>2021-05-14</t>
         </is>
       </c>
       <c r="B221" t="n">
-        <v>33809492530</v>
+        <v>29087549466</v>
       </c>
       <c r="C221" t="n">
-        <v>72689004129</v>
+        <v>72865719627</v>
       </c>
       <c r="D221" t="n">
-        <v>0.4651252680529072</v>
+        <v>0.3991938817718307</v>
       </c>
       <c r="E221" t="n">
         <v>220</v>
@@ -4638,17 +4638,17 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>2021-05-10</t>
+          <t>2021-05-17</t>
         </is>
       </c>
       <c r="B222" t="n">
-        <v>34980447442</v>
+        <v>26738086558</v>
       </c>
       <c r="C222" t="n">
-        <v>74391256531</v>
+        <v>68865623007</v>
       </c>
       <c r="D222" t="n">
-        <v>0.4702225647636843</v>
+        <v>0.3882646433806625</v>
       </c>
       <c r="E222" t="n">
         <v>221</v>
@@ -4657,17 +4657,17 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>2021-05-11</t>
+          <t>2021-05-18</t>
         </is>
       </c>
       <c r="B223" t="n">
-        <v>33682768573</v>
+        <v>23944078372</v>
       </c>
       <c r="C223" t="n">
-        <v>73459473614</v>
+        <v>58781317109</v>
       </c>
       <c r="D223" t="n">
-        <v>0.4585217796412401</v>
+        <v>0.4073416444139855</v>
       </c>
       <c r="E223" t="n">
         <v>222</v>
@@ -4676,17 +4676,17 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>2021-05-12</t>
+          <t>2021-05-19</t>
         </is>
       </c>
       <c r="B224" t="n">
-        <v>28011409229</v>
+        <v>25053218592</v>
       </c>
       <c r="C224" t="n">
-        <v>66061705250</v>
+        <v>60763325645</v>
       </c>
       <c r="D224" t="n">
-        <v>0.4240188642269418</v>
+        <v>0.4123082192434532</v>
       </c>
       <c r="E224" t="n">
         <v>223</v>
@@ -4695,17 +4695,17 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>2021-05-13</t>
+          <t>2021-05-20</t>
         </is>
       </c>
       <c r="B225" t="n">
-        <v>29021959092</v>
+        <v>28722723747</v>
       </c>
       <c r="C225" t="n">
-        <v>69247970457</v>
+        <v>68566840023</v>
       </c>
       <c r="D225" t="n">
-        <v>0.4191019448002651</v>
+        <v>0.4189010859675796</v>
       </c>
       <c r="E225" t="n">
         <v>224</v>
@@ -4714,17 +4714,17 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>2021-05-14</t>
+          <t>2021-05-21</t>
         </is>
       </c>
       <c r="B226" t="n">
-        <v>29087549466</v>
+        <v>25545536529</v>
       </c>
       <c r="C226" t="n">
-        <v>72865719627</v>
+        <v>61418379955</v>
       </c>
       <c r="D226" t="n">
-        <v>0.3991938817718307</v>
+        <v>0.4159265768279251</v>
       </c>
       <c r="E226" t="n">
         <v>225</v>
@@ -4733,17 +4733,17 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>2021-05-17</t>
+          <t>2021-05-24</t>
         </is>
       </c>
       <c r="B227" t="n">
-        <v>26738086558</v>
+        <v>25923087661</v>
       </c>
       <c r="C227" t="n">
-        <v>68865623007</v>
+        <v>63386616118</v>
       </c>
       <c r="D227" t="n">
-        <v>0.3882646433806625</v>
+        <v>0.4089678428761964</v>
       </c>
       <c r="E227" t="n">
         <v>226</v>
@@ -4752,17 +4752,17 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>2021-05-18</t>
+          <t>2021-05-25</t>
         </is>
       </c>
       <c r="B228" t="n">
-        <v>23944078372</v>
+        <v>29902389375</v>
       </c>
       <c r="C228" t="n">
-        <v>58781317109</v>
+        <v>71817033145</v>
       </c>
       <c r="D228" t="n">
-        <v>0.4073416444139855</v>
+        <v>0.4163690431854305</v>
       </c>
       <c r="E228" t="n">
         <v>227</v>
@@ -4771,17 +4771,17 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>2021-05-19</t>
+          <t>2021-05-26</t>
         </is>
       </c>
       <c r="B229" t="n">
-        <v>25053218592</v>
+        <v>29496722494</v>
       </c>
       <c r="C229" t="n">
-        <v>60763325645</v>
+        <v>72933630614</v>
       </c>
       <c r="D229" t="n">
-        <v>0.4123082192434532</v>
+        <v>0.4044323893611015</v>
       </c>
       <c r="E229" t="n">
         <v>228</v>
@@ -4790,17 +4790,17 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>2021-05-20</t>
+          <t>2021-05-27</t>
         </is>
       </c>
       <c r="B230" t="n">
-        <v>28722723747</v>
+        <v>26896810605</v>
       </c>
       <c r="C230" t="n">
-        <v>68566840023</v>
+        <v>68968444971</v>
       </c>
       <c r="D230" t="n">
-        <v>0.4189010859675796</v>
+        <v>0.3899871980049663</v>
       </c>
       <c r="E230" t="n">
         <v>229</v>
@@ -4809,17 +4809,17 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>2021-05-21</t>
+          <t>2021-05-27</t>
         </is>
       </c>
       <c r="B231" t="n">
-        <v>25545536529</v>
+        <v>26896810605</v>
       </c>
       <c r="C231" t="n">
-        <v>61418379955</v>
+        <v>68968444971</v>
       </c>
       <c r="D231" t="n">
-        <v>0.4159265768279251</v>
+        <v>0.3899871980049663</v>
       </c>
       <c r="E231" t="n">
         <v>230</v>
@@ -4828,17 +4828,17 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>2021-05-24</t>
+          <t>2021-05-28</t>
         </is>
       </c>
       <c r="B232" t="n">
-        <v>25923087661</v>
+        <v>29791926043</v>
       </c>
       <c r="C232" t="n">
-        <v>63386616118</v>
+        <v>73972884560</v>
       </c>
       <c r="D232" t="n">
-        <v>0.4089678428761964</v>
+        <v>0.4027411695543051</v>
       </c>
       <c r="E232" t="n">
         <v>231</v>
@@ -4847,17 +4847,17 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>2021-05-25</t>
+          <t>2021-05-31</t>
         </is>
       </c>
       <c r="B233" t="n">
-        <v>29902389375</v>
+        <v>27775314244</v>
       </c>
       <c r="C233" t="n">
-        <v>71817033145</v>
+        <v>70615016083</v>
       </c>
       <c r="D233" t="n">
-        <v>0.4163690431854305</v>
+        <v>0.3933343895490053</v>
       </c>
       <c r="E233" t="n">
         <v>232</v>
@@ -4866,17 +4866,17 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>2021-05-26</t>
+          <t>2021-06-01</t>
         </is>
       </c>
       <c r="B234" t="n">
-        <v>29496722494</v>
+        <v>28722955321</v>
       </c>
       <c r="C234" t="n">
-        <v>72933630614</v>
+        <v>75176823860</v>
       </c>
       <c r="D234" t="n">
-        <v>0.4044323893611015</v>
+        <v>0.3820719451315218</v>
       </c>
       <c r="E234" t="n">
         <v>233</v>
@@ -4885,17 +4885,17 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>2021-05-27</t>
+          <t>2021-06-02</t>
         </is>
       </c>
       <c r="B235" t="n">
-        <v>26896810605</v>
+        <v>29120888356</v>
       </c>
       <c r="C235" t="n">
-        <v>68968444971</v>
+        <v>75272955834</v>
       </c>
       <c r="D235" t="n">
-        <v>0.3899871980049663</v>
+        <v>0.3868705305026218</v>
       </c>
       <c r="E235" t="n">
         <v>234</v>
@@ -4904,17 +4904,17 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>2021-05-27</t>
+          <t>2021-06-03</t>
         </is>
       </c>
       <c r="B236" t="n">
-        <v>26896810605</v>
+        <v>29199450254</v>
       </c>
       <c r="C236" t="n">
-        <v>68968444971</v>
+        <v>72798616374</v>
       </c>
       <c r="D236" t="n">
-        <v>0.3899871980049663</v>
+        <v>0.4010989728704318</v>
       </c>
       <c r="E236" t="n">
         <v>235</v>
@@ -4923,17 +4923,17 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>2021-05-28</t>
+          <t>2021-06-04</t>
         </is>
       </c>
       <c r="B237" t="n">
-        <v>29791926043</v>
+        <v>27330244158</v>
       </c>
       <c r="C237" t="n">
-        <v>73972884560</v>
+        <v>68930352581</v>
       </c>
       <c r="D237" t="n">
-        <v>0.4027411695543051</v>
+        <v>0.3964907059757783</v>
       </c>
       <c r="E237" t="n">
         <v>236</v>
@@ -4942,17 +4942,17 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>2021-05-31</t>
+          <t>2021-06-07</t>
         </is>
       </c>
       <c r="B238" t="n">
-        <v>27775314244</v>
+        <v>25294989410</v>
       </c>
       <c r="C238" t="n">
-        <v>70615016083</v>
+        <v>66558910303</v>
       </c>
       <c r="D238" t="n">
-        <v>0.3933343895490053</v>
+        <v>0.3800391156472988</v>
       </c>
       <c r="E238" t="n">
         <v>237</v>
@@ -4961,17 +4961,17 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>2021-06-01</t>
+          <t>2021-06-08</t>
         </is>
       </c>
       <c r="B239" t="n">
-        <v>28722955321</v>
+        <v>25589368881</v>
       </c>
       <c r="C239" t="n">
-        <v>75176823860</v>
+        <v>68255065080</v>
       </c>
       <c r="D239" t="n">
-        <v>0.3820719451315218</v>
+        <v>0.3749079844991337</v>
       </c>
       <c r="E239" t="n">
         <v>238</v>
@@ -4980,17 +4980,17 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>2021-06-02</t>
+          <t>2021-06-09</t>
         </is>
       </c>
       <c r="B240" t="n">
-        <v>29120888356</v>
+        <v>25270907666</v>
       </c>
       <c r="C240" t="n">
-        <v>75272955834</v>
+        <v>66612688195</v>
       </c>
       <c r="D240" t="n">
-        <v>0.3868705305026218</v>
+        <v>0.3793707828157707</v>
       </c>
       <c r="E240" t="n">
         <v>239</v>
@@ -4999,17 +4999,17 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>2021-06-03</t>
+          <t>2021-06-10</t>
         </is>
       </c>
       <c r="B241" t="n">
-        <v>29199450254</v>
+        <v>27144684274</v>
       </c>
       <c r="C241" t="n">
-        <v>72798616374</v>
+        <v>72726642476</v>
       </c>
       <c r="D241" t="n">
-        <v>0.4010989728704318</v>
+        <v>0.3732426432714507</v>
       </c>
       <c r="E241" t="n">
         <v>240</v>
@@ -5018,17 +5018,17 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>2021-06-04</t>
+          <t>2021-06-11</t>
         </is>
       </c>
       <c r="B242" t="n">
-        <v>27330244158</v>
+        <v>31253551848</v>
       </c>
       <c r="C242" t="n">
-        <v>68930352581</v>
+        <v>80603106508</v>
       </c>
       <c r="D242" t="n">
-        <v>0.3964907059757783</v>
+        <v>0.3877462445556987</v>
       </c>
       <c r="E242" t="n">
         <v>241</v>
@@ -5037,17 +5037,17 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>2021-06-07</t>
+          <t>2021-06-15</t>
         </is>
       </c>
       <c r="B243" t="n">
-        <v>25294989410</v>
+        <v>26600340763</v>
       </c>
       <c r="C243" t="n">
-        <v>66558910303</v>
+        <v>71269245087</v>
       </c>
       <c r="D243" t="n">
-        <v>0.3800391156472988</v>
+        <v>0.3732373021564681</v>
       </c>
       <c r="E243" t="n">
         <v>242</v>
@@ -5056,17 +5056,17 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>2021-06-08</t>
+          <t>2021-06-16</t>
         </is>
       </c>
       <c r="B244" t="n">
-        <v>25589368881</v>
+        <v>25225237352</v>
       </c>
       <c r="C244" t="n">
-        <v>68255065080</v>
+        <v>65304111913</v>
       </c>
       <c r="D244" t="n">
-        <v>0.3749079844991337</v>
+        <v>0.3862733388918263</v>
       </c>
       <c r="E244" t="n">
         <v>243</v>
@@ -5075,17 +5075,17 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>2021-06-09</t>
+          <t>2021-06-17</t>
         </is>
       </c>
       <c r="B245" t="n">
-        <v>25270907666</v>
+        <v>23865594042</v>
       </c>
       <c r="C245" t="n">
-        <v>66612688195</v>
+        <v>62073104309</v>
       </c>
       <c r="D245" t="n">
-        <v>0.3793707828157707</v>
+        <v>0.3844756003050377</v>
       </c>
       <c r="E245" t="n">
         <v>244</v>
@@ -5094,17 +5094,17 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>2021-06-10</t>
+          <t>2021-06-18</t>
         </is>
       </c>
       <c r="B246" t="n">
-        <v>27144684274</v>
+        <v>26773348572</v>
       </c>
       <c r="C246" t="n">
-        <v>72726642476</v>
+        <v>68507417006</v>
       </c>
       <c r="D246" t="n">
-        <v>0.3732426432714507</v>
+        <v>0.3908094881121433</v>
       </c>
       <c r="E246" t="n">
         <v>245</v>
@@ -5113,17 +5113,17 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>2021-06-11</t>
+          <t>2021-06-21</t>
         </is>
       </c>
       <c r="B247" t="n">
-        <v>31253551848</v>
+        <v>25810884254</v>
       </c>
       <c r="C247" t="n">
-        <v>80603106508</v>
+        <v>68094480065</v>
       </c>
       <c r="D247" t="n">
-        <v>0.3877462445556987</v>
+        <v>0.3790451770740016</v>
       </c>
       <c r="E247" t="n">
         <v>246</v>
@@ -5132,17 +5132,17 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>2021-06-15</t>
+          <t>2021-06-22</t>
         </is>
       </c>
       <c r="B248" t="n">
-        <v>26600340763</v>
+        <v>27325435943</v>
       </c>
       <c r="C248" t="n">
-        <v>71269245087</v>
+        <v>71331165214</v>
       </c>
       <c r="D248" t="n">
-        <v>0.3732373021564681</v>
+        <v>0.3830785023772036</v>
       </c>
       <c r="E248" t="n">
         <v>247</v>
@@ -5151,17 +5151,17 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>2021-06-16</t>
+          <t>2021-06-23</t>
         </is>
       </c>
       <c r="B249" t="n">
-        <v>25225237352</v>
+        <v>26948115800</v>
       </c>
       <c r="C249" t="n">
-        <v>65304111913</v>
+        <v>71129212592</v>
       </c>
       <c r="D249" t="n">
-        <v>0.3862733388918263</v>
+        <v>0.3788614384721994</v>
       </c>
       <c r="E249" t="n">
         <v>248</v>
@@ -5170,17 +5170,17 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>2021-06-17</t>
+          <t>2021-06-24</t>
         </is>
       </c>
       <c r="B250" t="n">
-        <v>23865594042</v>
+        <v>25431794302</v>
       </c>
       <c r="C250" t="n">
-        <v>62073104309</v>
+        <v>68625630748</v>
       </c>
       <c r="D250" t="n">
-        <v>0.3844756003050377</v>
+        <v>0.3705874033477087</v>
       </c>
       <c r="E250" t="n">
         <v>249</v>
@@ -5189,96 +5189,20 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>2021-06-18</t>
+          <t>2021-06-25</t>
         </is>
       </c>
       <c r="B251" t="n">
-        <v>26773348572</v>
+        <v>27857858703</v>
       </c>
       <c r="C251" t="n">
-        <v>68507417006</v>
+        <v>71470857871</v>
       </c>
       <c r="D251" t="n">
-        <v>0.3908094881121433</v>
+        <v>0.3897792685416135</v>
       </c>
       <c r="E251" t="n">
         <v>250</v>
-      </c>
-    </row>
-    <row r="252">
-      <c r="A252" t="inlineStr">
-        <is>
-          <t>2021-06-21</t>
-        </is>
-      </c>
-      <c r="B252" t="n">
-        <v>25810884254</v>
-      </c>
-      <c r="C252" t="n">
-        <v>68094480065</v>
-      </c>
-      <c r="D252" t="n">
-        <v>0.3790451770740016</v>
-      </c>
-      <c r="E252" t="n">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="253">
-      <c r="A253" t="inlineStr">
-        <is>
-          <t>2021-06-22</t>
-        </is>
-      </c>
-      <c r="B253" t="n">
-        <v>27325435943</v>
-      </c>
-      <c r="C253" t="n">
-        <v>71331165214</v>
-      </c>
-      <c r="D253" t="n">
-        <v>0.3830785023772036</v>
-      </c>
-      <c r="E253" t="n">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="254">
-      <c r="A254" t="inlineStr">
-        <is>
-          <t>2021-06-23</t>
-        </is>
-      </c>
-      <c r="B254" t="n">
-        <v>26948115800</v>
-      </c>
-      <c r="C254" t="n">
-        <v>71129212592</v>
-      </c>
-      <c r="D254" t="n">
-        <v>0.3788614384721994</v>
-      </c>
-      <c r="E254" t="n">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="255">
-      <c r="A255" t="inlineStr">
-        <is>
-          <t>2021-06-24</t>
-        </is>
-      </c>
-      <c r="B255" t="n">
-        <v>25431794302</v>
-      </c>
-      <c r="C255" t="n">
-        <v>68625630748</v>
-      </c>
-      <c r="D255" t="n">
-        <v>0.3705874033477087</v>
-      </c>
-      <c r="E255" t="n">
-        <v>254</v>
       </c>
     </row>
   </sheetData>

--- a/king_index/output/index.xlsx
+++ b/king_index/output/index.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E251"/>
+  <dimension ref="A1:E252"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5205,6 +5205,25 @@
         <v>250</v>
       </c>
     </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>2021-06-28</t>
+        </is>
+      </c>
+      <c r="B252" t="n">
+        <v>25041439447</v>
+      </c>
+      <c r="C252" t="n">
+        <v>67772533030</v>
+      </c>
+      <c r="D252" t="n">
+        <v>0.369492452582748</v>
+      </c>
+      <c r="E252" t="n">
+        <v>251</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/king_index/output/index.xlsx
+++ b/king_index/output/index.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E252"/>
+  <dimension ref="A1:E253"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5224,6 +5224,25 @@
         <v>251</v>
       </c>
     </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>2021-06-29</t>
+        </is>
+      </c>
+      <c r="B253" t="n">
+        <v>23759674387</v>
+      </c>
+      <c r="C253" t="n">
+        <v>65504552666</v>
+      </c>
+      <c r="D253" t="n">
+        <v>0.3627179092138493</v>
+      </c>
+      <c r="E253" t="n">
+        <v>252</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/king_index/output/index.xlsx
+++ b/king_index/output/index.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E253"/>
+  <dimension ref="A1:E254"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5243,6 +5243,25 @@
         <v>252</v>
       </c>
     </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>2021-06-30</t>
+        </is>
+      </c>
+      <c r="B254" t="n">
+        <v>21731079518</v>
+      </c>
+      <c r="C254" t="n">
+        <v>60341364451</v>
+      </c>
+      <c r="D254" t="n">
+        <v>0.360135699875442</v>
+      </c>
+      <c r="E254" t="n">
+        <v>253</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/king_index/output/index.xlsx
+++ b/king_index/output/index.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E254"/>
+  <dimension ref="A1:E255"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5262,6 +5262,25 @@
         <v>253</v>
       </c>
     </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>2021-07-01</t>
+        </is>
+      </c>
+      <c r="B255" t="n">
+        <v>23237110584</v>
+      </c>
+      <c r="C255" t="n">
+        <v>66252494627</v>
+      </c>
+      <c r="D255" t="n">
+        <v>0.3507356321422218</v>
+      </c>
+      <c r="E255" t="n">
+        <v>254</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/king_index/output/index.xlsx
+++ b/king_index/output/index.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E255"/>
+  <dimension ref="A1:E251"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -458,17 +458,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2020-06-17</t>
+          <t>2020-06-24</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>23156031895</v>
+        <v>19322024502</v>
       </c>
       <c r="C2" t="n">
-        <v>61386131654</v>
+        <v>52926747938</v>
       </c>
       <c r="D2" t="n">
-        <v>0.3772192720257707</v>
+        <v>0.3650710700123576</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>
@@ -477,17 +477,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2020-06-18</t>
+          <t>2020-06-29</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>25733088111</v>
+        <v>20448932009</v>
       </c>
       <c r="C3" t="n">
-        <v>63354121102</v>
+        <v>54347085975</v>
       </c>
       <c r="D3" t="n">
-        <v>0.4061785983830442</v>
+        <v>0.3762654729713868</v>
       </c>
       <c r="E3" t="n">
         <v>2</v>
@@ -496,17 +496,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2020-06-19</t>
+          <t>2020-06-30</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>24126480724</v>
+        <v>20003048931</v>
       </c>
       <c r="C4" t="n">
-        <v>61888832308</v>
+        <v>53946886834</v>
       </c>
       <c r="D4" t="n">
-        <v>0.3898357720489956</v>
+        <v>0.3707915341352578</v>
       </c>
       <c r="E4" t="n">
         <v>3</v>
@@ -515,17 +515,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2020-06-22</t>
+          <t>2020-07-01</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>25010112764</v>
+        <v>25539868441</v>
       </c>
       <c r="C5" t="n">
-        <v>63846785740</v>
+        <v>66477208273</v>
       </c>
       <c r="D5" t="n">
-        <v>0.3917207808369149</v>
+        <v>0.3841898464826647</v>
       </c>
       <c r="E5" t="n">
         <v>4</v>
@@ -534,17 +534,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2020-06-23</t>
+          <t>2020-07-02</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>21417149307</v>
+        <v>35281401239</v>
       </c>
       <c r="C6" t="n">
-        <v>56906481203</v>
+        <v>86277275738</v>
       </c>
       <c r="D6" t="n">
-        <v>0.3763569430799901</v>
+        <v>0.4089304041789609</v>
       </c>
       <c r="E6" t="n">
         <v>5</v>
@@ -553,17 +553,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2020-06-24</t>
+          <t>2020-07-03</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>19322024502</v>
+        <v>39589081860</v>
       </c>
       <c r="C7" t="n">
-        <v>52926747938</v>
+        <v>96590527098</v>
       </c>
       <c r="D7" t="n">
-        <v>0.3650710700123576</v>
+        <v>0.4098650566409398</v>
       </c>
       <c r="E7" t="n">
         <v>6</v>
@@ -572,17 +572,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2020-06-29</t>
+          <t>2020-07-06</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>20448932009</v>
+        <v>51680326902</v>
       </c>
       <c r="C8" t="n">
-        <v>54347085975</v>
+        <v>132721246132</v>
       </c>
       <c r="D8" t="n">
-        <v>0.3762654729713868</v>
+        <v>0.3893900065600689</v>
       </c>
       <c r="E8" t="n">
         <v>7</v>
@@ -591,17 +591,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2020-06-30</t>
+          <t>2020-07-07</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>20003048931</v>
+        <v>54130474812</v>
       </c>
       <c r="C9" t="n">
-        <v>53946886834</v>
+        <v>140540263998</v>
       </c>
       <c r="D9" t="n">
-        <v>0.3707915341352578</v>
+        <v>0.3851599055824338</v>
       </c>
       <c r="E9" t="n">
         <v>8</v>
@@ -610,17 +610,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2020-07-01</t>
+          <t>2020-07-08</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>25539868441</v>
+        <v>48763694238</v>
       </c>
       <c r="C10" t="n">
-        <v>66477208273</v>
+        <v>124820435614</v>
       </c>
       <c r="D10" t="n">
-        <v>0.3841898464826647</v>
+        <v>0.3906707583427999</v>
       </c>
       <c r="E10" t="n">
         <v>9</v>
@@ -629,17 +629,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2020-07-02</t>
+          <t>2020-07-09</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>35281401239</v>
+        <v>50352644938</v>
       </c>
       <c r="C11" t="n">
-        <v>86277275738</v>
+        <v>137276438768</v>
       </c>
       <c r="D11" t="n">
-        <v>0.4089304041789609</v>
+        <v>0.3667974299879457</v>
       </c>
       <c r="E11" t="n">
         <v>10</v>
@@ -648,17 +648,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2020-07-03</t>
+          <t>2020-07-10</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>39589081860</v>
+        <v>45792064703</v>
       </c>
       <c r="C12" t="n">
-        <v>96590527098</v>
+        <v>124540979573</v>
       </c>
       <c r="D12" t="n">
-        <v>0.4098650566409398</v>
+        <v>0.3676867233580644</v>
       </c>
       <c r="E12" t="n">
         <v>11</v>
@@ -667,17 +667,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2020-07-06</t>
+          <t>2020-07-13</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>51680326902</v>
+        <v>45569190970</v>
       </c>
       <c r="C13" t="n">
-        <v>132721246132</v>
+        <v>125874117474</v>
       </c>
       <c r="D13" t="n">
-        <v>0.3893900065600689</v>
+        <v>0.3620219301987366</v>
       </c>
       <c r="E13" t="n">
         <v>12</v>
@@ -686,17 +686,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2020-07-07</t>
+          <t>2020-07-14</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>54130474812</v>
+        <v>44404671526</v>
       </c>
       <c r="C14" t="n">
-        <v>140540263998</v>
+        <v>127205292718</v>
       </c>
       <c r="D14" t="n">
-        <v>0.3851599055824338</v>
+        <v>0.3490788046409375</v>
       </c>
       <c r="E14" t="n">
         <v>13</v>
@@ -705,17 +705,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2020-07-08</t>
+          <t>2020-07-15</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>48763694238</v>
+        <v>40948010990</v>
       </c>
       <c r="C15" t="n">
-        <v>124820435614</v>
+        <v>115744357395</v>
       </c>
       <c r="D15" t="n">
-        <v>0.3906707583427999</v>
+        <v>0.3537797600815822</v>
       </c>
       <c r="E15" t="n">
         <v>14</v>
@@ -724,17 +724,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2020-07-09</t>
+          <t>2020-07-16</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>50352644938</v>
+        <v>41327517137</v>
       </c>
       <c r="C16" t="n">
-        <v>137276438768</v>
+        <v>110570972319</v>
       </c>
       <c r="D16" t="n">
-        <v>0.3667974299879457</v>
+        <v>0.373764617152584</v>
       </c>
       <c r="E16" t="n">
         <v>15</v>
@@ -743,17 +743,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2020-07-10</t>
+          <t>2020-07-17</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>45792064703</v>
+        <v>30786629717</v>
       </c>
       <c r="C17" t="n">
-        <v>124540979573</v>
+        <v>83073812068</v>
       </c>
       <c r="D17" t="n">
-        <v>0.3676867233580644</v>
+        <v>0.3705936798927636</v>
       </c>
       <c r="E17" t="n">
         <v>16</v>
@@ -762,17 +762,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2020-07-13</t>
+          <t>2020-07-20</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>45569190970</v>
+        <v>33302406491</v>
       </c>
       <c r="C18" t="n">
-        <v>125874117474</v>
+        <v>90725025902</v>
       </c>
       <c r="D18" t="n">
-        <v>0.3620219301987366</v>
+        <v>0.3670696829226903</v>
       </c>
       <c r="E18" t="n">
         <v>17</v>
@@ -781,17 +781,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2020-07-14</t>
+          <t>2020-07-21</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>44404671526</v>
+        <v>29750727633</v>
       </c>
       <c r="C19" t="n">
-        <v>127205292718</v>
+        <v>82804408460</v>
       </c>
       <c r="D19" t="n">
-        <v>0.3490788046409375</v>
+        <v>0.3592891753749025</v>
       </c>
       <c r="E19" t="n">
         <v>18</v>
@@ -800,17 +800,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2020-07-15</t>
+          <t>2020-07-22</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>40948010990</v>
+        <v>32546369994</v>
       </c>
       <c r="C20" t="n">
-        <v>115744357395</v>
+        <v>88951002081</v>
       </c>
       <c r="D20" t="n">
-        <v>0.3537797600815822</v>
+        <v>0.3658909875389917</v>
       </c>
       <c r="E20" t="n">
         <v>19</v>
@@ -819,17 +819,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2020-07-16</t>
+          <t>2020-07-23</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>41327517137</v>
+        <v>33380341470</v>
       </c>
       <c r="C21" t="n">
-        <v>110570972319</v>
+        <v>92918126099</v>
       </c>
       <c r="D21" t="n">
-        <v>0.373764617152584</v>
+        <v>0.3592446691664313</v>
       </c>
       <c r="E21" t="n">
         <v>20</v>
@@ -838,17 +838,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2020-07-17</t>
+          <t>2020-07-24</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>30786629717</v>
+        <v>34826858650</v>
       </c>
       <c r="C22" t="n">
-        <v>83073812068</v>
+        <v>98778010270</v>
       </c>
       <c r="D22" t="n">
-        <v>0.3705936798927636</v>
+        <v>0.3525770417404056</v>
       </c>
       <c r="E22" t="n">
         <v>21</v>
@@ -857,17 +857,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2020-07-20</t>
+          <t>2020-07-27</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>33302406491</v>
+        <v>25272101520</v>
       </c>
       <c r="C23" t="n">
-        <v>90725025902</v>
+        <v>69273127708</v>
       </c>
       <c r="D23" t="n">
-        <v>0.3670696829226903</v>
+        <v>0.3648182542951854</v>
       </c>
       <c r="E23" t="n">
         <v>22</v>
@@ -876,17 +876,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2020-07-21</t>
+          <t>2020-07-28</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>29750727633</v>
+        <v>25533477451</v>
       </c>
       <c r="C24" t="n">
-        <v>82804408460</v>
+        <v>67557159363</v>
       </c>
       <c r="D24" t="n">
-        <v>0.3592891753749025</v>
+        <v>0.3779536868002814</v>
       </c>
       <c r="E24" t="n">
         <v>23</v>
@@ -895,17 +895,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2020-07-22</t>
+          <t>2020-07-29</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>32546369994</v>
+        <v>27398207256</v>
       </c>
       <c r="C25" t="n">
-        <v>88951002081</v>
+        <v>75808503607</v>
       </c>
       <c r="D25" t="n">
-        <v>0.3658909875389917</v>
+        <v>0.3614133764997586</v>
       </c>
       <c r="E25" t="n">
         <v>24</v>
@@ -914,17 +914,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2020-07-23</t>
+          <t>2020-07-30</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>33380341470</v>
+        <v>29316097538</v>
       </c>
       <c r="C26" t="n">
-        <v>92918126099</v>
+        <v>80705680370</v>
       </c>
       <c r="D26" t="n">
-        <v>0.3592446691664313</v>
+        <v>0.3632470156201968</v>
       </c>
       <c r="E26" t="n">
         <v>25</v>
@@ -933,17 +933,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2020-07-24</t>
+          <t>2020-07-31</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>34826858650</v>
+        <v>30421341838</v>
       </c>
       <c r="C27" t="n">
-        <v>98778010270</v>
+        <v>83388719271</v>
       </c>
       <c r="D27" t="n">
-        <v>0.3525770417404056</v>
+        <v>0.3648136355126825</v>
       </c>
       <c r="E27" t="n">
         <v>26</v>
@@ -952,17 +952,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2020-07-27</t>
+          <t>2020-08-03</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>25272101520</v>
+        <v>32534419194</v>
       </c>
       <c r="C28" t="n">
-        <v>69273127708</v>
+        <v>97147468049</v>
       </c>
       <c r="D28" t="n">
-        <v>0.3648182542951854</v>
+        <v>0.3348972427937086</v>
       </c>
       <c r="E28" t="n">
         <v>27</v>
@@ -971,17 +971,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2020-07-28</t>
+          <t>2020-08-04</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>25533477451</v>
+        <v>35518548960</v>
       </c>
       <c r="C29" t="n">
-        <v>67557159363</v>
+        <v>100401661483</v>
       </c>
       <c r="D29" t="n">
-        <v>0.3779536868002814</v>
+        <v>0.3537645536474912</v>
       </c>
       <c r="E29" t="n">
         <v>28</v>
@@ -990,17 +990,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2020-07-29</t>
+          <t>2020-08-05</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>27398207256</v>
+        <v>31118752071</v>
       </c>
       <c r="C30" t="n">
-        <v>75808503607</v>
+        <v>88411991123</v>
       </c>
       <c r="D30" t="n">
-        <v>0.3614133764997586</v>
+        <v>0.351974338273947</v>
       </c>
       <c r="E30" t="n">
         <v>29</v>
@@ -1009,17 +1009,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2020-07-30</t>
+          <t>2020-08-06</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>29316097538</v>
+        <v>35289080996</v>
       </c>
       <c r="C31" t="n">
-        <v>80705680370</v>
+        <v>94484631872</v>
       </c>
       <c r="D31" t="n">
-        <v>0.3632470156201968</v>
+        <v>0.3734901676264849</v>
       </c>
       <c r="E31" t="n">
         <v>30</v>
@@ -1028,17 +1028,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2020-07-31</t>
+          <t>2020-08-07</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>30421341838</v>
+        <v>33926327226</v>
       </c>
       <c r="C32" t="n">
-        <v>83388719271</v>
+        <v>90977583613</v>
       </c>
       <c r="D32" t="n">
-        <v>0.3648136355126825</v>
+        <v>0.3729086427522151</v>
       </c>
       <c r="E32" t="n">
         <v>31</v>
@@ -1047,17 +1047,17 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2020-08-03</t>
+          <t>2020-08-10</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>32534419194</v>
+        <v>29708663069</v>
       </c>
       <c r="C33" t="n">
-        <v>97147468049</v>
+        <v>82942928747</v>
       </c>
       <c r="D33" t="n">
-        <v>0.3348972427937086</v>
+        <v>0.3581819875160189</v>
       </c>
       <c r="E33" t="n">
         <v>32</v>
@@ -1066,17 +1066,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2020-08-04</t>
+          <t>2020-08-11</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>35518548960</v>
+        <v>30946369948</v>
       </c>
       <c r="C34" t="n">
-        <v>100401661483</v>
+        <v>86295092754</v>
       </c>
       <c r="D34" t="n">
-        <v>0.3537645536474912</v>
+        <v>0.3586110051033644</v>
       </c>
       <c r="E34" t="n">
         <v>33</v>
@@ -1085,17 +1085,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2020-08-05</t>
+          <t>2020-08-12</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>31118752071</v>
+        <v>29856245191</v>
       </c>
       <c r="C35" t="n">
-        <v>88411991123</v>
+        <v>82452473263</v>
       </c>
       <c r="D35" t="n">
-        <v>0.351974338273947</v>
+        <v>0.3621024817019988</v>
       </c>
       <c r="E35" t="n">
         <v>34</v>
@@ -1104,17 +1104,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2020-08-06</t>
+          <t>2020-08-13</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>35289080996</v>
+        <v>27823565615</v>
       </c>
       <c r="C36" t="n">
-        <v>94484631872</v>
+        <v>72532322436</v>
       </c>
       <c r="D36" t="n">
-        <v>0.3734901676264849</v>
+        <v>0.3836022986793308</v>
       </c>
       <c r="E36" t="n">
         <v>35</v>
@@ -1123,17 +1123,17 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2020-08-07</t>
+          <t>2020-08-14</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>33926327226</v>
+        <v>27261549866</v>
       </c>
       <c r="C37" t="n">
-        <v>90977583613</v>
+        <v>69180221661</v>
       </c>
       <c r="D37" t="n">
-        <v>0.3729086427522151</v>
+        <v>0.3940656622869504</v>
       </c>
       <c r="E37" t="n">
         <v>36</v>
@@ -1142,17 +1142,17 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2020-08-10</t>
+          <t>2020-08-17</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>29708663069</v>
+        <v>37118467741</v>
       </c>
       <c r="C38" t="n">
-        <v>82942928747</v>
+        <v>91788369903</v>
       </c>
       <c r="D38" t="n">
-        <v>0.3581819875160189</v>
+        <v>0.4043918394043386</v>
       </c>
       <c r="E38" t="n">
         <v>37</v>
@@ -1161,17 +1161,17 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2020-08-11</t>
+          <t>2020-08-18</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>30946369948</v>
+        <v>31325687773</v>
       </c>
       <c r="C39" t="n">
-        <v>86295092754</v>
+        <v>85178317604</v>
       </c>
       <c r="D39" t="n">
-        <v>0.3586110051033644</v>
+        <v>0.3677659838109897</v>
       </c>
       <c r="E39" t="n">
         <v>38</v>
@@ -1180,17 +1180,17 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2020-08-12</t>
+          <t>2020-08-19</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>29856245191</v>
+        <v>33073383828</v>
       </c>
       <c r="C40" t="n">
-        <v>82452473263</v>
+        <v>88140275731</v>
       </c>
       <c r="D40" t="n">
-        <v>0.3621024817019988</v>
+        <v>0.375235765417145</v>
       </c>
       <c r="E40" t="n">
         <v>39</v>
@@ -1199,17 +1199,17 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2020-08-13</t>
+          <t>2020-08-20</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>27823565615</v>
+        <v>27646953314</v>
       </c>
       <c r="C41" t="n">
-        <v>72532322436</v>
+        <v>72119978332</v>
       </c>
       <c r="D41" t="n">
-        <v>0.3836022986793308</v>
+        <v>0.3833466669489126</v>
       </c>
       <c r="E41" t="n">
         <v>40</v>
@@ -1218,17 +1218,17 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2020-08-14</t>
+          <t>2020-08-21</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>27261549866</v>
+        <v>25486130617</v>
       </c>
       <c r="C42" t="n">
-        <v>69180221661</v>
+        <v>66786682396</v>
       </c>
       <c r="D42" t="n">
-        <v>0.3940656622869504</v>
+        <v>0.3816049802546626</v>
       </c>
       <c r="E42" t="n">
         <v>41</v>
@@ -1237,17 +1237,17 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2020-08-17</t>
+          <t>2020-08-24</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>37118467741</v>
+        <v>25209284709</v>
       </c>
       <c r="C43" t="n">
-        <v>91788369903</v>
+        <v>67412296336</v>
       </c>
       <c r="D43" t="n">
-        <v>0.4043918394043386</v>
+        <v>0.3739567716748666</v>
       </c>
       <c r="E43" t="n">
         <v>42</v>
@@ -1256,17 +1256,17 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2020-08-18</t>
+          <t>2020-08-25</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>31325687773</v>
+        <v>26619247474</v>
       </c>
       <c r="C44" t="n">
-        <v>85178317604</v>
+        <v>73103731924</v>
       </c>
       <c r="D44" t="n">
-        <v>0.3677659838109897</v>
+        <v>0.3641298025889275</v>
       </c>
       <c r="E44" t="n">
         <v>43</v>
@@ -1275,17 +1275,17 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2020-08-19</t>
+          <t>2020-08-26</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>33073383828</v>
+        <v>26322908958</v>
       </c>
       <c r="C45" t="n">
-        <v>88140275731</v>
+        <v>75716936591</v>
       </c>
       <c r="D45" t="n">
-        <v>0.375235765417145</v>
+        <v>0.3476488899727732</v>
       </c>
       <c r="E45" t="n">
         <v>44</v>
@@ -1294,17 +1294,17 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2020-08-20</t>
+          <t>2020-08-27</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>27646953314</v>
+        <v>23276018839</v>
       </c>
       <c r="C46" t="n">
-        <v>72119978332</v>
+        <v>65005692955</v>
       </c>
       <c r="D46" t="n">
-        <v>0.3833466669489126</v>
+        <v>0.3580612371152286</v>
       </c>
       <c r="E46" t="n">
         <v>45</v>
@@ -1313,17 +1313,17 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2020-08-21</t>
+          <t>2020-08-28</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>25486130617</v>
+        <v>25701039669</v>
       </c>
       <c r="C47" t="n">
-        <v>66786682396</v>
+        <v>70850828969</v>
       </c>
       <c r="D47" t="n">
-        <v>0.3816049802546626</v>
+        <v>0.3627486091975749</v>
       </c>
       <c r="E47" t="n">
         <v>46</v>
@@ -1332,17 +1332,17 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2020-08-24</t>
+          <t>2020-08-31</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>25209284709</v>
+        <v>28573296373</v>
       </c>
       <c r="C48" t="n">
-        <v>67412296336</v>
+        <v>77184652221</v>
       </c>
       <c r="D48" t="n">
-        <v>0.3739567716748666</v>
+        <v>0.3701940159189566</v>
       </c>
       <c r="E48" t="n">
         <v>47</v>
@@ -1351,17 +1351,17 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2020-08-25</t>
+          <t>2020-09-01</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>26619247474</v>
+        <v>23964180511</v>
       </c>
       <c r="C49" t="n">
-        <v>73103731924</v>
+        <v>64392996012</v>
       </c>
       <c r="D49" t="n">
-        <v>0.3641298025889275</v>
+        <v>0.3721550788929613</v>
       </c>
       <c r="E49" t="n">
         <v>48</v>
@@ -1370,17 +1370,17 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2020-08-26</t>
+          <t>2020-09-02</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>26322908958</v>
+        <v>30082062270</v>
       </c>
       <c r="C50" t="n">
-        <v>75716936591</v>
+        <v>77531927895</v>
       </c>
       <c r="D50" t="n">
-        <v>0.3476488899727732</v>
+        <v>0.3879957984630482</v>
       </c>
       <c r="E50" t="n">
         <v>49</v>
@@ -1389,17 +1389,17 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2020-08-27</t>
+          <t>2020-09-03</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>23276018839</v>
+        <v>27715216294</v>
       </c>
       <c r="C51" t="n">
-        <v>65005692955</v>
+        <v>73519808249</v>
       </c>
       <c r="D51" t="n">
-        <v>0.3580612371152286</v>
+        <v>0.3769761776327399</v>
       </c>
       <c r="E51" t="n">
         <v>50</v>
@@ -1408,17 +1408,17 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2020-08-28</t>
+          <t>2020-09-04</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>25701039669</v>
+        <v>24329945914</v>
       </c>
       <c r="C52" t="n">
-        <v>70850828969</v>
+        <v>65573685675</v>
       </c>
       <c r="D52" t="n">
-        <v>0.3627486091975749</v>
+        <v>0.37103215510236</v>
       </c>
       <c r="E52" t="n">
         <v>51</v>
@@ -1427,17 +1427,17 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2020-08-31</t>
+          <t>2020-09-07</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>28573296373</v>
+        <v>29997390344</v>
       </c>
       <c r="C53" t="n">
-        <v>77184652221</v>
+        <v>79881522723</v>
       </c>
       <c r="D53" t="n">
-        <v>0.3701940159189566</v>
+        <v>0.375523516846568</v>
       </c>
       <c r="E53" t="n">
         <v>52</v>
@@ -1446,17 +1446,17 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2020-09-01</t>
+          <t>2020-09-08</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>23964180511</v>
+        <v>32724062545</v>
       </c>
       <c r="C54" t="n">
-        <v>64392996012</v>
+        <v>80161481426</v>
       </c>
       <c r="D54" t="n">
-        <v>0.3721550788929613</v>
+        <v>0.4082267688030289</v>
       </c>
       <c r="E54" t="n">
         <v>53</v>
@@ -1465,17 +1465,17 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2020-09-02</t>
+          <t>2020-09-09</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>30082062270</v>
+        <v>41720230941</v>
       </c>
       <c r="C55" t="n">
-        <v>77531927895</v>
+        <v>98517765305</v>
       </c>
       <c r="D55" t="n">
-        <v>0.3879957984630482</v>
+        <v>0.4234792660170358</v>
       </c>
       <c r="E55" t="n">
         <v>54</v>
@@ -1484,17 +1484,17 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2020-09-03</t>
+          <t>2020-09-10</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>27715216294</v>
+        <v>32362586075</v>
       </c>
       <c r="C56" t="n">
-        <v>73519808249</v>
+        <v>83938666669</v>
       </c>
       <c r="D56" t="n">
-        <v>0.3769761776327399</v>
+        <v>0.3855503948212232</v>
       </c>
       <c r="E56" t="n">
         <v>55</v>
@@ -1503,17 +1503,17 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2020-09-04</t>
+          <t>2020-09-11</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>24329945914</v>
+        <v>23586290440</v>
       </c>
       <c r="C57" t="n">
-        <v>65573685675</v>
+        <v>60330240577</v>
       </c>
       <c r="D57" t="n">
-        <v>0.37103215510236</v>
+        <v>0.3909530314220547</v>
       </c>
       <c r="E57" t="n">
         <v>56</v>
@@ -1522,17 +1522,17 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2020-09-07</t>
+          <t>2020-09-14</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>29997390344</v>
+        <v>24462170352</v>
       </c>
       <c r="C58" t="n">
-        <v>79881522723</v>
+        <v>63101019998</v>
       </c>
       <c r="D58" t="n">
-        <v>0.375523516846568</v>
+        <v>0.3876667976646865</v>
       </c>
       <c r="E58" t="n">
         <v>57</v>
@@ -1541,17 +1541,17 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2020-09-08</t>
+          <t>2020-09-15</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>32724062545</v>
+        <v>23106120892</v>
       </c>
       <c r="C59" t="n">
-        <v>80161481426</v>
+        <v>58614407766</v>
       </c>
       <c r="D59" t="n">
-        <v>0.4082267688030289</v>
+        <v>0.3942054824514151</v>
       </c>
       <c r="E59" t="n">
         <v>58</v>
@@ -1560,17 +1560,17 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2020-09-09</t>
+          <t>2020-09-16</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>41720230941</v>
+        <v>21724638649</v>
       </c>
       <c r="C60" t="n">
-        <v>98517765305</v>
+        <v>55182289033</v>
       </c>
       <c r="D60" t="n">
-        <v>0.4234792660170358</v>
+        <v>0.3936886096915674</v>
       </c>
       <c r="E60" t="n">
         <v>59</v>
@@ -1579,17 +1579,17 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2020-09-10</t>
+          <t>2020-09-17</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>32362586075</v>
+        <v>20554994106</v>
       </c>
       <c r="C61" t="n">
-        <v>83938666669</v>
+        <v>55472969929</v>
       </c>
       <c r="D61" t="n">
-        <v>0.3855503948212232</v>
+        <v>0.3705407179804577</v>
       </c>
       <c r="E61" t="n">
         <v>60</v>
@@ -1598,17 +1598,17 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2020-09-11</t>
+          <t>2020-09-18</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>23586290440</v>
+        <v>25018086444</v>
       </c>
       <c r="C62" t="n">
-        <v>60330240577</v>
+        <v>64587549837</v>
       </c>
       <c r="D62" t="n">
-        <v>0.3909530314220547</v>
+        <v>0.3873515330297914</v>
       </c>
       <c r="E62" t="n">
         <v>61</v>
@@ -1617,17 +1617,17 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2020-09-14</t>
+          <t>2020-09-21</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>24462170352</v>
+        <v>22182279260</v>
       </c>
       <c r="C63" t="n">
-        <v>63101019998</v>
+        <v>58098440053</v>
       </c>
       <c r="D63" t="n">
-        <v>0.3876667976646865</v>
+        <v>0.3818050749686968</v>
       </c>
       <c r="E63" t="n">
         <v>62</v>
@@ -1636,17 +1636,17 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2020-09-15</t>
+          <t>2020-09-22</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>23106120892</v>
+        <v>22099090990</v>
       </c>
       <c r="C64" t="n">
-        <v>58614407766</v>
+        <v>56264182474</v>
       </c>
       <c r="D64" t="n">
-        <v>0.3942054824514151</v>
+        <v>0.3927736975510506</v>
       </c>
       <c r="E64" t="n">
         <v>63</v>
@@ -1655,17 +1655,17 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2020-09-16</t>
+          <t>2020-09-23</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>21724638649</v>
+        <v>19077501915</v>
       </c>
       <c r="C65" t="n">
-        <v>55182289033</v>
+        <v>48597940983</v>
       </c>
       <c r="D65" t="n">
-        <v>0.3936886096915674</v>
+        <v>0.3925578230088695</v>
       </c>
       <c r="E65" t="n">
         <v>64</v>
@@ -1674,17 +1674,17 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2020-09-17</t>
+          <t>2020-09-24</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>20554994106</v>
+        <v>20859996043</v>
       </c>
       <c r="C66" t="n">
-        <v>55472969929</v>
+        <v>54861814882</v>
       </c>
       <c r="D66" t="n">
-        <v>0.3705407179804577</v>
+        <v>0.3802279616134993</v>
       </c>
       <c r="E66" t="n">
         <v>65</v>
@@ -1693,17 +1693,17 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2020-09-18</t>
+          <t>2020-09-25</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>25018086444</v>
+        <v>16281719043</v>
       </c>
       <c r="C67" t="n">
-        <v>64587549837</v>
+        <v>43622575116</v>
       </c>
       <c r="D67" t="n">
-        <v>0.3873515330297914</v>
+        <v>0.373240667239476</v>
       </c>
       <c r="E67" t="n">
         <v>66</v>
@@ -1712,17 +1712,17 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2020-09-21</t>
+          <t>2020-09-28</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>22182279260</v>
+        <v>14676583271</v>
       </c>
       <c r="C68" t="n">
-        <v>58098440053</v>
+        <v>40556797589</v>
       </c>
       <c r="D68" t="n">
-        <v>0.3818050749686968</v>
+        <v>0.3618772719614492</v>
       </c>
       <c r="E68" t="n">
         <v>67</v>
@@ -1731,17 +1731,17 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2020-09-22</t>
+          <t>2020-09-29</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>22099090990</v>
+        <v>14442107257</v>
       </c>
       <c r="C69" t="n">
-        <v>56264182474</v>
+        <v>40163621965</v>
       </c>
       <c r="D69" t="n">
-        <v>0.3927736975510506</v>
+        <v>0.3595817944304267</v>
       </c>
       <c r="E69" t="n">
         <v>68</v>
@@ -1750,17 +1750,17 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2020-09-23</t>
+          <t>2020-09-30</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>19077501915</v>
+        <v>15066784297</v>
       </c>
       <c r="C70" t="n">
-        <v>48597940983</v>
+        <v>40300843448</v>
       </c>
       <c r="D70" t="n">
-        <v>0.3925578230088695</v>
+        <v>0.3738577907541961</v>
       </c>
       <c r="E70" t="n">
         <v>69</v>
@@ -1769,17 +1769,17 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2020-09-24</t>
+          <t>2020-10-09</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>20859996043</v>
+        <v>18363804782</v>
       </c>
       <c r="C71" t="n">
-        <v>54861814882</v>
+        <v>50410563994</v>
       </c>
       <c r="D71" t="n">
-        <v>0.3802279616134993</v>
+        <v>0.3642848507742486</v>
       </c>
       <c r="E71" t="n">
         <v>70</v>
@@ -1788,17 +1788,17 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2020-09-25</t>
+          <t>2020-10-12</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>16281719043</v>
+        <v>24824121596</v>
       </c>
       <c r="C72" t="n">
-        <v>43622575116</v>
+        <v>69075123930</v>
       </c>
       <c r="D72" t="n">
-        <v>0.373240667239476</v>
+        <v>0.3593786038104905</v>
       </c>
       <c r="E72" t="n">
         <v>71</v>
@@ -1807,17 +1807,17 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2020-09-28</t>
+          <t>2020-10-13</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>14676583271</v>
+        <v>21950874234</v>
       </c>
       <c r="C73" t="n">
-        <v>40556797589</v>
+        <v>58435290007</v>
       </c>
       <c r="D73" t="n">
-        <v>0.3618772719614492</v>
+        <v>0.3756441395494142</v>
       </c>
       <c r="E73" t="n">
         <v>72</v>
@@ -1826,17 +1826,17 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2020-09-29</t>
+          <t>2020-10-14</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>14442107257</v>
+        <v>21810988673</v>
       </c>
       <c r="C74" t="n">
-        <v>40163621965</v>
+        <v>58022364557</v>
       </c>
       <c r="D74" t="n">
-        <v>0.3595817944304267</v>
+        <v>0.3759065808421738</v>
       </c>
       <c r="E74" t="n">
         <v>73</v>
@@ -1845,17 +1845,17 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2020-09-30</t>
+          <t>2020-10-15</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>15066784297</v>
+        <v>20410751440</v>
       </c>
       <c r="C75" t="n">
-        <v>40300843448</v>
+        <v>54415224691</v>
       </c>
       <c r="D75" t="n">
-        <v>0.3738577907541961</v>
+        <v>0.3750926612157467</v>
       </c>
       <c r="E75" t="n">
         <v>74</v>
@@ -1864,17 +1864,17 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2020-10-09</t>
+          <t>2020-10-16</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>18363804782</v>
+        <v>19779199722</v>
       </c>
       <c r="C76" t="n">
-        <v>50410563994</v>
+        <v>51552706029</v>
       </c>
       <c r="D76" t="n">
-        <v>0.3642848507742486</v>
+        <v>0.3836694762613156</v>
       </c>
       <c r="E76" t="n">
         <v>75</v>
@@ -1883,17 +1883,17 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2020-10-12</t>
+          <t>2020-10-19</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>24824121596</v>
+        <v>20562725471</v>
       </c>
       <c r="C77" t="n">
-        <v>69075123930</v>
+        <v>53895497648</v>
       </c>
       <c r="D77" t="n">
-        <v>0.3593786038104905</v>
+        <v>0.3815295593947087</v>
       </c>
       <c r="E77" t="n">
         <v>76</v>
@@ -1902,17 +1902,17 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2020-10-13</t>
+          <t>2020-10-20</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>21950874234</v>
+        <v>18296672779</v>
       </c>
       <c r="C78" t="n">
-        <v>58435290007</v>
+        <v>47922773316</v>
       </c>
       <c r="D78" t="n">
-        <v>0.3756441395494142</v>
+        <v>0.3817949486844761</v>
       </c>
       <c r="E78" t="n">
         <v>77</v>
@@ -1921,17 +1921,17 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2020-10-14</t>
+          <t>2020-10-21</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>21810988673</v>
+        <v>18370049664</v>
       </c>
       <c r="C79" t="n">
-        <v>58022364557</v>
+        <v>49307563396</v>
       </c>
       <c r="D79" t="n">
-        <v>0.3759065808421738</v>
+        <v>0.3725604836009853</v>
       </c>
       <c r="E79" t="n">
         <v>78</v>
@@ -1940,17 +1940,17 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2020-10-15</t>
+          <t>2020-10-22</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>20410751440</v>
+        <v>17665602844</v>
       </c>
       <c r="C80" t="n">
-        <v>54415224691</v>
+        <v>46460364776</v>
       </c>
       <c r="D80" t="n">
-        <v>0.3750926612157467</v>
+        <v>0.3802295339085566</v>
       </c>
       <c r="E80" t="n">
         <v>79</v>
@@ -1959,17 +1959,17 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2020-10-16</t>
+          <t>2020-10-23</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>19779199722</v>
+        <v>17466910909</v>
       </c>
       <c r="C81" t="n">
-        <v>51552706029</v>
+        <v>47398504650</v>
       </c>
       <c r="D81" t="n">
-        <v>0.3836694762613156</v>
+        <v>0.3685118557637873</v>
       </c>
       <c r="E81" t="n">
         <v>80</v>
@@ -1978,17 +1978,17 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2020-10-19</t>
+          <t>2020-10-26</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>20562725471</v>
+        <v>16145407434</v>
       </c>
       <c r="C82" t="n">
-        <v>53895497648</v>
+        <v>44150494774</v>
       </c>
       <c r="D82" t="n">
-        <v>0.3815295593947087</v>
+        <v>0.3656902944496094</v>
       </c>
       <c r="E82" t="n">
         <v>81</v>
@@ -1997,17 +1997,17 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2020-10-20</t>
+          <t>2020-10-27</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>18296672779</v>
+        <v>15491813981</v>
       </c>
       <c r="C83" t="n">
-        <v>47922773316</v>
+        <v>43505082864</v>
       </c>
       <c r="D83" t="n">
-        <v>0.3817949486844761</v>
+        <v>0.356092046288672</v>
       </c>
       <c r="E83" t="n">
         <v>82</v>
@@ -2016,17 +2016,17 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2020-10-21</t>
+          <t>2020-10-28</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>18370049664</v>
+        <v>17543172634</v>
       </c>
       <c r="C84" t="n">
-        <v>49307563396</v>
+        <v>49485508785</v>
       </c>
       <c r="D84" t="n">
-        <v>0.3725604836009853</v>
+        <v>0.3545113117906887</v>
       </c>
       <c r="E84" t="n">
         <v>83</v>
@@ -2035,17 +2035,17 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2020-10-22</t>
+          <t>2020-10-29</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>17665602844</v>
+        <v>18553392322</v>
       </c>
       <c r="C85" t="n">
-        <v>46460364776</v>
+        <v>51689467398</v>
       </c>
       <c r="D85" t="n">
-        <v>0.3802295339085566</v>
+        <v>0.3589395142948963</v>
       </c>
       <c r="E85" t="n">
         <v>84</v>
@@ -2054,17 +2054,17 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2020-10-23</t>
+          <t>2020-10-30</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>17466910909</v>
+        <v>20650226596</v>
       </c>
       <c r="C86" t="n">
-        <v>47398504650</v>
+        <v>60348197366</v>
       </c>
       <c r="D86" t="n">
-        <v>0.3685118557637873</v>
+        <v>0.3421846467220954</v>
       </c>
       <c r="E86" t="n">
         <v>85</v>
@@ -2073,17 +2073,17 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2020-10-26</t>
+          <t>2020-11-02</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>16145407434</v>
+        <v>19992661394</v>
       </c>
       <c r="C87" t="n">
-        <v>44150494774</v>
+        <v>56353918211</v>
       </c>
       <c r="D87" t="n">
-        <v>0.3656902944496094</v>
+        <v>0.3547696775784711</v>
       </c>
       <c r="E87" t="n">
         <v>86</v>
@@ -2092,17 +2092,17 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2020-10-27</t>
+          <t>2020-11-03</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>15491813981</v>
+        <v>20249408150</v>
       </c>
       <c r="C88" t="n">
-        <v>43505082864</v>
+        <v>55344378404</v>
       </c>
       <c r="D88" t="n">
-        <v>0.356092046288672</v>
+        <v>0.365880126111173</v>
       </c>
       <c r="E88" t="n">
         <v>87</v>
@@ -2111,17 +2111,17 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2020-10-28</t>
+          <t>2020-11-04</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>17543172634</v>
+        <v>18257580496</v>
       </c>
       <c r="C89" t="n">
-        <v>49485508785</v>
+        <v>49909415865</v>
       </c>
       <c r="D89" t="n">
-        <v>0.3545113117906887</v>
+        <v>0.3658143494483073</v>
       </c>
       <c r="E89" t="n">
         <v>88</v>
@@ -2130,17 +2130,17 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2020-10-29</t>
+          <t>2020-11-05</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>18553392322</v>
+        <v>21285267389</v>
       </c>
       <c r="C90" t="n">
-        <v>51689467398</v>
+        <v>58980118835</v>
       </c>
       <c r="D90" t="n">
-        <v>0.3589395142948963</v>
+        <v>0.3608888522002924</v>
       </c>
       <c r="E90" t="n">
         <v>89</v>
@@ -2149,17 +2149,17 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2020-10-30</t>
+          <t>2020-11-06</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>20650226596</v>
+        <v>23071856412</v>
       </c>
       <c r="C91" t="n">
-        <v>60348197366</v>
+        <v>59902082650</v>
       </c>
       <c r="D91" t="n">
-        <v>0.3421846467220954</v>
+        <v>0.3851595034984981</v>
       </c>
       <c r="E91" t="n">
         <v>90</v>
@@ -2168,17 +2168,17 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2020-11-02</t>
+          <t>2020-11-09</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>19992661394</v>
+        <v>27202863336</v>
       </c>
       <c r="C92" t="n">
-        <v>56353918211</v>
+        <v>74478178320</v>
       </c>
       <c r="D92" t="n">
-        <v>0.3547696775784711</v>
+        <v>0.3652460888492902</v>
       </c>
       <c r="E92" t="n">
         <v>91</v>
@@ -2187,17 +2187,17 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2020-11-03</t>
+          <t>2020-11-10</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>20249408150</v>
+        <v>25309810082</v>
       </c>
       <c r="C93" t="n">
-        <v>55344378404</v>
+        <v>67090114044</v>
       </c>
       <c r="D93" t="n">
-        <v>0.365880126111173</v>
+        <v>0.3772509622714452</v>
       </c>
       <c r="E93" t="n">
         <v>92</v>
@@ -2206,17 +2206,17 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2020-11-04</t>
+          <t>2020-11-11</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>18257580496</v>
+        <v>23822441228</v>
       </c>
       <c r="C94" t="n">
-        <v>49909415865</v>
+        <v>61988411650</v>
       </c>
       <c r="D94" t="n">
-        <v>0.3658143494483073</v>
+        <v>0.3843047529997488</v>
       </c>
       <c r="E94" t="n">
         <v>93</v>
@@ -2225,17 +2225,17 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2020-11-05</t>
+          <t>2020-11-12</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>21285267389</v>
+        <v>19076439758</v>
       </c>
       <c r="C95" t="n">
-        <v>58980118835</v>
+        <v>51703999860</v>
       </c>
       <c r="D95" t="n">
-        <v>0.3608888522002924</v>
+        <v>0.3689548160616911</v>
       </c>
       <c r="E95" t="n">
         <v>94</v>
@@ -2244,17 +2244,17 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2020-11-06</t>
+          <t>2020-11-13</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>23071856412</v>
+        <v>20119982649</v>
       </c>
       <c r="C96" t="n">
-        <v>59902082650</v>
+        <v>52210418675</v>
       </c>
       <c r="D96" t="n">
-        <v>0.3851595034984981</v>
+        <v>0.3853633653896379</v>
       </c>
       <c r="E96" t="n">
         <v>95</v>
@@ -2263,17 +2263,17 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2020-11-09</t>
+          <t>2020-11-16</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>27202863336</v>
+        <v>23217241543</v>
       </c>
       <c r="C97" t="n">
-        <v>74478178320</v>
+        <v>61350411349</v>
       </c>
       <c r="D97" t="n">
-        <v>0.3652460888492902</v>
+        <v>0.3784366075546849</v>
       </c>
       <c r="E97" t="n">
         <v>96</v>
@@ -2282,17 +2282,17 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2020-11-10</t>
+          <t>2020-11-17</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>25309810082</v>
+        <v>24335506367</v>
       </c>
       <c r="C98" t="n">
-        <v>67090114044</v>
+        <v>64241703103</v>
       </c>
       <c r="D98" t="n">
-        <v>0.3772509622714452</v>
+        <v>0.3788116626980203</v>
       </c>
       <c r="E98" t="n">
         <v>97</v>
@@ -2301,17 +2301,17 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2020-11-11</t>
+          <t>2020-11-18</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>23822441228</v>
+        <v>25490702717</v>
       </c>
       <c r="C99" t="n">
-        <v>61988411650</v>
+        <v>63205463709</v>
       </c>
       <c r="D99" t="n">
-        <v>0.3843047529997488</v>
+        <v>0.4032990381078449</v>
       </c>
       <c r="E99" t="n">
         <v>98</v>
@@ -2320,17 +2320,17 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2020-11-12</t>
+          <t>2020-11-19</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>19076439758</v>
+        <v>23177522765</v>
       </c>
       <c r="C100" t="n">
-        <v>51703999860</v>
+        <v>59756276020</v>
       </c>
       <c r="D100" t="n">
-        <v>0.3689548160616911</v>
+        <v>0.3878675899623104</v>
       </c>
       <c r="E100" t="n">
         <v>99</v>
@@ -2339,17 +2339,17 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2020-11-13</t>
+          <t>2020-11-20</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>20119982649</v>
+        <v>22935620159</v>
       </c>
       <c r="C101" t="n">
-        <v>52210418675</v>
+        <v>58875754449</v>
       </c>
       <c r="D101" t="n">
-        <v>0.3853633653896379</v>
+        <v>0.3895596816320637</v>
       </c>
       <c r="E101" t="n">
         <v>100</v>
@@ -2358,17 +2358,17 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2020-11-16</t>
+          <t>2020-11-23</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>23217241543</v>
+        <v>32096579820</v>
       </c>
       <c r="C102" t="n">
-        <v>61350411349</v>
+        <v>77198006469</v>
       </c>
       <c r="D102" t="n">
-        <v>0.3784366075546849</v>
+        <v>0.4157695423506675</v>
       </c>
       <c r="E102" t="n">
         <v>101</v>
@@ -2377,17 +2377,17 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2020-11-17</t>
+          <t>2020-11-24</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>24335506367</v>
+        <v>26709718473</v>
       </c>
       <c r="C103" t="n">
-        <v>64241703103</v>
+        <v>65410116144</v>
       </c>
       <c r="D103" t="n">
-        <v>0.3788116626980203</v>
+        <v>0.408342318399171</v>
       </c>
       <c r="E103" t="n">
         <v>102</v>
@@ -2396,17 +2396,17 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2020-11-18</t>
+          <t>2020-11-25</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>25490702717</v>
+        <v>27089790866</v>
       </c>
       <c r="C104" t="n">
-        <v>63205463709</v>
+        <v>68837443765</v>
       </c>
       <c r="D104" t="n">
-        <v>0.4032990381078449</v>
+        <v>0.3935327836762824</v>
       </c>
       <c r="E104" t="n">
         <v>103</v>
@@ -2415,17 +2415,17 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2020-11-19</t>
+          <t>2020-11-26</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>23177522765</v>
+        <v>21689088930</v>
       </c>
       <c r="C105" t="n">
-        <v>59756276020</v>
+        <v>57127013421</v>
       </c>
       <c r="D105" t="n">
-        <v>0.3878675899623104</v>
+        <v>0.3796643239540867</v>
       </c>
       <c r="E105" t="n">
         <v>104</v>
@@ -2434,17 +2434,17 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2020-11-20</t>
+          <t>2020-11-27</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>22935620159</v>
+        <v>23626364341</v>
       </c>
       <c r="C106" t="n">
-        <v>58875754449</v>
+        <v>58765160877</v>
       </c>
       <c r="D106" t="n">
-        <v>0.3895596816320637</v>
+        <v>0.4020471311301572</v>
       </c>
       <c r="E106" t="n">
         <v>105</v>
@@ -2453,17 +2453,17 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2020-11-23</t>
+          <t>2020-11-30</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>32096579820</v>
+        <v>33970232252</v>
       </c>
       <c r="C107" t="n">
-        <v>77198006469</v>
+        <v>75092505579</v>
       </c>
       <c r="D107" t="n">
-        <v>0.4157695423506675</v>
+        <v>0.4523784629381171</v>
       </c>
       <c r="E107" t="n">
         <v>106</v>
@@ -2472,17 +2472,17 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2020-11-24</t>
+          <t>2020-12-01</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>26709718473</v>
+        <v>28738868941</v>
       </c>
       <c r="C108" t="n">
-        <v>65410116144</v>
+        <v>67936162045</v>
       </c>
       <c r="D108" t="n">
-        <v>0.408342318399171</v>
+        <v>0.4230275611089682</v>
       </c>
       <c r="E108" t="n">
         <v>107</v>
@@ -2491,17 +2491,17 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2020-11-25</t>
+          <t>2020-12-02</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>27089790866</v>
+        <v>28928357564</v>
       </c>
       <c r="C109" t="n">
-        <v>68837443765</v>
+        <v>69689843826</v>
       </c>
       <c r="D109" t="n">
-        <v>0.3935327836762824</v>
+        <v>0.4151014835996427</v>
       </c>
       <c r="E109" t="n">
         <v>108</v>
@@ -2510,17 +2510,17 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2020-11-26</t>
+          <t>2020-12-03</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>21689088930</v>
+        <v>28497726227</v>
       </c>
       <c r="C110" t="n">
-        <v>57127013421</v>
+        <v>66950741850</v>
       </c>
       <c r="D110" t="n">
-        <v>0.3796643239540867</v>
+        <v>0.4256521352795137</v>
       </c>
       <c r="E110" t="n">
         <v>109</v>
@@ -2529,17 +2529,17 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2020-11-27</t>
+          <t>2020-12-04</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>23626364341</v>
+        <v>23614518756</v>
       </c>
       <c r="C111" t="n">
-        <v>58765160877</v>
+        <v>57124426015</v>
       </c>
       <c r="D111" t="n">
-        <v>0.4020471311301572</v>
+        <v>0.4133874141649876</v>
       </c>
       <c r="E111" t="n">
         <v>110</v>
@@ -2548,17 +2548,17 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2020-11-30</t>
+          <t>2020-12-07</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>33970232252</v>
+        <v>22345056458</v>
       </c>
       <c r="C112" t="n">
-        <v>75092505579</v>
+        <v>56856559648</v>
       </c>
       <c r="D112" t="n">
-        <v>0.4523784629381171</v>
+        <v>0.3930075367967857</v>
       </c>
       <c r="E112" t="n">
         <v>111</v>
@@ -2567,17 +2567,17 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2020-12-01</t>
+          <t>2020-12-08</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>28738868941</v>
+        <v>20555717183</v>
       </c>
       <c r="C113" t="n">
-        <v>67936162045</v>
+        <v>51665831943</v>
       </c>
       <c r="D113" t="n">
-        <v>0.4230275611089682</v>
+        <v>0.3978590184259099</v>
       </c>
       <c r="E113" t="n">
         <v>112</v>
@@ -2586,17 +2586,17 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2020-12-02</t>
+          <t>2020-12-09</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>28928357564</v>
+        <v>22167887887</v>
       </c>
       <c r="C114" t="n">
-        <v>69689843826</v>
+        <v>59426788696</v>
       </c>
       <c r="D114" t="n">
-        <v>0.4151014835996427</v>
+        <v>0.3730285343265085</v>
       </c>
       <c r="E114" t="n">
         <v>113</v>
@@ -2605,17 +2605,17 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2020-12-03</t>
+          <t>2020-12-10</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>28497726227</v>
+        <v>21008686040</v>
       </c>
       <c r="C115" t="n">
-        <v>66950741850</v>
+        <v>53530291688</v>
       </c>
       <c r="D115" t="n">
-        <v>0.4256521352795137</v>
+        <v>0.3924635076238444</v>
       </c>
       <c r="E115" t="n">
         <v>114</v>
@@ -2624,17 +2624,17 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2020-12-04</t>
+          <t>2020-12-11</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>23614518756</v>
+        <v>24084146686</v>
       </c>
       <c r="C116" t="n">
-        <v>57124426015</v>
+        <v>64194443337</v>
       </c>
       <c r="D116" t="n">
-        <v>0.4133874141649876</v>
+        <v>0.3751749440300626</v>
       </c>
       <c r="E116" t="n">
         <v>115</v>
@@ -2643,17 +2643,17 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2020-12-07</t>
+          <t>2020-12-14</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>22345056458</v>
+        <v>20561369384</v>
       </c>
       <c r="C117" t="n">
-        <v>56856559648</v>
+        <v>52737085483</v>
       </c>
       <c r="D117" t="n">
-        <v>0.3930075367967857</v>
+        <v>0.3898844465082932</v>
       </c>
       <c r="E117" t="n">
         <v>116</v>
@@ -2662,17 +2662,17 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2020-12-08</t>
+          <t>2020-12-15</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>20555717183</v>
+        <v>20518702233</v>
       </c>
       <c r="C118" t="n">
-        <v>51665831943</v>
+        <v>50712282528</v>
       </c>
       <c r="D118" t="n">
-        <v>0.3978590184259099</v>
+        <v>0.4046101104139991</v>
       </c>
       <c r="E118" t="n">
         <v>117</v>
@@ -2681,17 +2681,17 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2020-12-09</t>
+          <t>2020-12-16</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>22167887887</v>
+        <v>20098821894</v>
       </c>
       <c r="C119" t="n">
-        <v>59426788696</v>
+        <v>51594471274</v>
       </c>
       <c r="D119" t="n">
-        <v>0.3730285343265085</v>
+        <v>0.3895537912824469</v>
       </c>
       <c r="E119" t="n">
         <v>118</v>
@@ -2700,17 +2700,17 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2020-12-10</t>
+          <t>2020-12-17</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>21008686040</v>
+        <v>23623180829</v>
       </c>
       <c r="C120" t="n">
-        <v>53530291688</v>
+        <v>60346809075</v>
       </c>
       <c r="D120" t="n">
-        <v>0.3924635076238444</v>
+        <v>0.3914569998165226</v>
       </c>
       <c r="E120" t="n">
         <v>119</v>
@@ -2719,17 +2719,17 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2020-12-11</t>
+          <t>2020-12-18</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>24084146686</v>
+        <v>24395319589</v>
       </c>
       <c r="C121" t="n">
-        <v>64194443337</v>
+        <v>59011526731</v>
       </c>
       <c r="D121" t="n">
-        <v>0.3751749440300626</v>
+        <v>0.4133992279204094</v>
       </c>
       <c r="E121" t="n">
         <v>120</v>
@@ -2738,17 +2738,17 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2020-12-14</t>
+          <t>2020-12-21</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>20561369384</v>
+        <v>25669905456</v>
       </c>
       <c r="C122" t="n">
-        <v>52737085483</v>
+        <v>62473191028</v>
       </c>
       <c r="D122" t="n">
-        <v>0.3898844465082932</v>
+        <v>0.410894737944392</v>
       </c>
       <c r="E122" t="n">
         <v>121</v>
@@ -2757,17 +2757,17 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2020-12-15</t>
+          <t>2020-12-22</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>20518702233</v>
+        <v>27752409533</v>
       </c>
       <c r="C123" t="n">
-        <v>50712282528</v>
+        <v>70592976908</v>
       </c>
       <c r="D123" t="n">
-        <v>0.4046101104139991</v>
+        <v>0.3931327271998773</v>
       </c>
       <c r="E123" t="n">
         <v>122</v>
@@ -2776,17 +2776,17 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2020-12-16</t>
+          <t>2020-12-23</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>20098821894</v>
+        <v>26781996550</v>
       </c>
       <c r="C124" t="n">
-        <v>51594471274</v>
+        <v>66516491988</v>
       </c>
       <c r="D124" t="n">
-        <v>0.3895537912824469</v>
+        <v>0.4026369363380084</v>
       </c>
       <c r="E124" t="n">
         <v>123</v>
@@ -2795,17 +2795,17 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2020-12-17</t>
+          <t>2020-12-24</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>23623180829</v>
+        <v>23869444669</v>
       </c>
       <c r="C125" t="n">
-        <v>60346809075</v>
+        <v>63015856260</v>
       </c>
       <c r="D125" t="n">
-        <v>0.3914569998165226</v>
+        <v>0.3787847390427572</v>
       </c>
       <c r="E125" t="n">
         <v>124</v>
@@ -2814,17 +2814,17 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2020-12-18</t>
+          <t>2020-12-25</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>24395319589</v>
+        <v>25870374333</v>
       </c>
       <c r="C126" t="n">
-        <v>59011526731</v>
+        <v>63035613181</v>
       </c>
       <c r="D126" t="n">
-        <v>0.4133992279204094</v>
+        <v>0.4104088629822002</v>
       </c>
       <c r="E126" t="n">
         <v>125</v>
@@ -2833,17 +2833,17 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2020-12-21</t>
+          <t>2020-12-28</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>25669905456</v>
+        <v>27591719605</v>
       </c>
       <c r="C127" t="n">
-        <v>62473191028</v>
+        <v>68634054637</v>
       </c>
       <c r="D127" t="n">
-        <v>0.410894737944392</v>
+        <v>0.4020120878903394</v>
       </c>
       <c r="E127" t="n">
         <v>126</v>
@@ -2852,17 +2852,17 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2020-12-22</t>
+          <t>2020-12-29</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>27752409533</v>
+        <v>28714767727</v>
       </c>
       <c r="C128" t="n">
-        <v>70592976908</v>
+        <v>68080937199</v>
       </c>
       <c r="D128" t="n">
-        <v>0.3931327271998773</v>
+        <v>0.4217739782733451</v>
       </c>
       <c r="E128" t="n">
         <v>127</v>
@@ -2871,17 +2871,17 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2020-12-23</t>
+          <t>2020-12-30</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>26781996550</v>
+        <v>27431057672</v>
       </c>
       <c r="C129" t="n">
-        <v>66516491988</v>
+        <v>63970764234</v>
       </c>
       <c r="D129" t="n">
-        <v>0.4026369363380084</v>
+        <v>0.4288061585704895</v>
       </c>
       <c r="E129" t="n">
         <v>128</v>
@@ -2890,17 +2890,17 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2020-12-24</t>
+          <t>2020-12-31</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>23869444669</v>
+        <v>29516497306</v>
       </c>
       <c r="C130" t="n">
-        <v>63015856260</v>
+        <v>70483427194</v>
       </c>
       <c r="D130" t="n">
-        <v>0.3787847390427572</v>
+        <v>0.4187721636287379</v>
       </c>
       <c r="E130" t="n">
         <v>129</v>
@@ -2909,17 +2909,17 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2020-12-25</t>
+          <t>2021-01-04</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>25870374333</v>
+        <v>32842910849</v>
       </c>
       <c r="C131" t="n">
-        <v>63035613181</v>
+        <v>81262611004</v>
       </c>
       <c r="D131" t="n">
-        <v>0.4104088629822002</v>
+        <v>0.4041577109475767</v>
       </c>
       <c r="E131" t="n">
         <v>130</v>
@@ -2928,17 +2928,17 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>2020-12-28</t>
+          <t>2021-01-05</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>27591719605</v>
+        <v>34955476638</v>
       </c>
       <c r="C132" t="n">
-        <v>68634054637</v>
+        <v>86306603527</v>
       </c>
       <c r="D132" t="n">
-        <v>0.4020120878903394</v>
+        <v>0.4050150881799513</v>
       </c>
       <c r="E132" t="n">
         <v>131</v>
@@ -2947,17 +2947,17 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>2020-12-29</t>
+          <t>2021-01-06</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>28714767727</v>
+        <v>31318863380</v>
       </c>
       <c r="C133" t="n">
-        <v>68080937199</v>
+        <v>79924024318</v>
       </c>
       <c r="D133" t="n">
-        <v>0.4217739782733451</v>
+        <v>0.3918579381762507</v>
       </c>
       <c r="E133" t="n">
         <v>132</v>
@@ -2966,17 +2966,17 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2020-12-30</t>
+          <t>2021-01-07</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>27431057672</v>
+        <v>34820241307</v>
       </c>
       <c r="C134" t="n">
-        <v>63970764234</v>
+        <v>87045282583</v>
       </c>
       <c r="D134" t="n">
-        <v>0.4288061585704895</v>
+        <v>0.4000244501911746</v>
       </c>
       <c r="E134" t="n">
         <v>133</v>
@@ -2985,17 +2985,17 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>2020-12-31</t>
+          <t>2021-01-08</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>29516497306</v>
+        <v>31741361539</v>
       </c>
       <c r="C135" t="n">
-        <v>70483427194</v>
+        <v>76243328872</v>
       </c>
       <c r="D135" t="n">
-        <v>0.4187721636287379</v>
+        <v>0.4163165749529185</v>
       </c>
       <c r="E135" t="n">
         <v>134</v>
@@ -3004,17 +3004,17 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>2021-01-04</t>
+          <t>2021-01-11</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>32842910849</v>
+        <v>33861909952</v>
       </c>
       <c r="C136" t="n">
-        <v>81262611004</v>
+        <v>79843929989</v>
       </c>
       <c r="D136" t="n">
-        <v>0.4041577109475767</v>
+        <v>0.4241012429706943</v>
       </c>
       <c r="E136" t="n">
         <v>135</v>
@@ -3023,17 +3023,17 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>2021-01-05</t>
+          <t>2021-01-12</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>34955476638</v>
+        <v>31336739617</v>
       </c>
       <c r="C137" t="n">
-        <v>86306603527</v>
+        <v>70684174141</v>
       </c>
       <c r="D137" t="n">
-        <v>0.4050150881799513</v>
+        <v>0.4433345936035105</v>
       </c>
       <c r="E137" t="n">
         <v>136</v>
@@ -3042,17 +3042,17 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>2021-01-06</t>
+          <t>2021-01-13</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>31318863380</v>
+        <v>36176556832</v>
       </c>
       <c r="C138" t="n">
-        <v>79924024318</v>
+        <v>81782457644</v>
       </c>
       <c r="D138" t="n">
-        <v>0.3918579381762507</v>
+        <v>0.4423510600461162</v>
       </c>
       <c r="E138" t="n">
         <v>137</v>
@@ -3061,17 +3061,17 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>2021-01-07</t>
+          <t>2021-01-14</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>34820241307</v>
+        <v>32971296424</v>
       </c>
       <c r="C139" t="n">
-        <v>87045282583</v>
+        <v>74034016193</v>
       </c>
       <c r="D139" t="n">
-        <v>0.4000244501911746</v>
+        <v>0.4453533405245341</v>
       </c>
       <c r="E139" t="n">
         <v>138</v>
@@ -3080,17 +3080,17 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>2021-01-08</t>
+          <t>2021-01-15</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>31741361539</v>
+        <v>31268748151</v>
       </c>
       <c r="C140" t="n">
-        <v>76243328872</v>
+        <v>68522530970</v>
       </c>
       <c r="D140" t="n">
-        <v>0.4163165749529185</v>
+        <v>0.4563279801309417</v>
       </c>
       <c r="E140" t="n">
         <v>139</v>
@@ -3099,17 +3099,17 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>2021-01-11</t>
+          <t>2021-01-18</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>33861909952</v>
+        <v>28025154838</v>
       </c>
       <c r="C141" t="n">
-        <v>79843929989</v>
+        <v>66132336803</v>
       </c>
       <c r="D141" t="n">
-        <v>0.4241012429706943</v>
+        <v>0.4237738479056539</v>
       </c>
       <c r="E141" t="n">
         <v>140</v>
@@ -3118,17 +3118,17 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>2021-01-12</t>
+          <t>2021-01-19</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>31336739617</v>
+        <v>30160755219</v>
       </c>
       <c r="C142" t="n">
-        <v>70684174141</v>
+        <v>71588657610</v>
       </c>
       <c r="D142" t="n">
-        <v>0.4433345936035105</v>
+        <v>0.4213063385447102</v>
       </c>
       <c r="E142" t="n">
         <v>141</v>
@@ -3137,17 +3137,17 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>2021-01-13</t>
+          <t>2021-01-20</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>36176556832</v>
+        <v>25498108632</v>
       </c>
       <c r="C143" t="n">
-        <v>81782457644</v>
+        <v>61023142374</v>
       </c>
       <c r="D143" t="n">
-        <v>0.4423510600461162</v>
+        <v>0.4178432581483041</v>
       </c>
       <c r="E143" t="n">
         <v>142</v>
@@ -3156,17 +3156,17 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>2021-01-14</t>
+          <t>2021-01-21</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>32971296424</v>
+        <v>31550851527</v>
       </c>
       <c r="C144" t="n">
-        <v>74034016193</v>
+        <v>73606094304</v>
       </c>
       <c r="D144" t="n">
-        <v>0.4453533405245341</v>
+        <v>0.4286445548474839</v>
       </c>
       <c r="E144" t="n">
         <v>143</v>
@@ -3175,17 +3175,17 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>2021-01-15</t>
+          <t>2021-01-22</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>31268748151</v>
+        <v>29587073243</v>
       </c>
       <c r="C145" t="n">
-        <v>68522530970</v>
+        <v>71863919964</v>
       </c>
       <c r="D145" t="n">
-        <v>0.4563279801309417</v>
+        <v>0.4117097043665521</v>
       </c>
       <c r="E145" t="n">
         <v>144</v>
@@ -3194,17 +3194,17 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>2021-01-18</t>
+          <t>2021-01-25</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>28025154838</v>
+        <v>29768085597</v>
       </c>
       <c r="C146" t="n">
-        <v>66132336803</v>
+        <v>72841620023</v>
       </c>
       <c r="D146" t="n">
-        <v>0.4237738479056539</v>
+        <v>0.4086686373477226</v>
       </c>
       <c r="E146" t="n">
         <v>145</v>
@@ -3213,17 +3213,17 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>2021-01-19</t>
+          <t>2021-01-26</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>30160755219</v>
+        <v>25588114580</v>
       </c>
       <c r="C147" t="n">
-        <v>71588657610</v>
+        <v>62625061804</v>
       </c>
       <c r="D147" t="n">
-        <v>0.4213063385447102</v>
+        <v>0.4085922447483418</v>
       </c>
       <c r="E147" t="n">
         <v>146</v>
@@ -3232,17 +3232,17 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>2021-01-20</t>
+          <t>2021-01-27</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>25498108632</v>
+        <v>25604690493</v>
       </c>
       <c r="C148" t="n">
-        <v>61023142374</v>
+        <v>60015878129</v>
       </c>
       <c r="D148" t="n">
-        <v>0.4178432581483041</v>
+        <v>0.4266319396004584</v>
       </c>
       <c r="E148" t="n">
         <v>147</v>
@@ -3251,17 +3251,17 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>2021-01-21</t>
+          <t>2021-01-28</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>31550851527</v>
+        <v>26286085867</v>
       </c>
       <c r="C149" t="n">
-        <v>73606094304</v>
+        <v>62311898539</v>
       </c>
       <c r="D149" t="n">
-        <v>0.4286445548474839</v>
+        <v>0.4218469743872106</v>
       </c>
       <c r="E149" t="n">
         <v>148</v>
@@ -3270,17 +3270,17 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>2021-01-22</t>
+          <t>2021-01-29</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>29587073243</v>
+        <v>27002904913</v>
       </c>
       <c r="C150" t="n">
-        <v>71863919964</v>
+        <v>66018503681</v>
       </c>
       <c r="D150" t="n">
-        <v>0.4117097043665521</v>
+        <v>0.4090202504963981</v>
       </c>
       <c r="E150" t="n">
         <v>149</v>
@@ -3289,17 +3289,17 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>2021-01-25</t>
+          <t>2021-02-01</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>29768085597</v>
+        <v>25457673045</v>
       </c>
       <c r="C151" t="n">
-        <v>72841620023</v>
+        <v>61214730247</v>
       </c>
       <c r="D151" t="n">
-        <v>0.4086686373477226</v>
+        <v>0.4158749526834291</v>
       </c>
       <c r="E151" t="n">
         <v>150</v>
@@ -3308,17 +3308,17 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>2021-01-26</t>
+          <t>2021-02-02</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>25588114580</v>
+        <v>24585679056</v>
       </c>
       <c r="C152" t="n">
-        <v>62625061804</v>
+        <v>59083806830</v>
       </c>
       <c r="D152" t="n">
-        <v>0.4085922447483418</v>
+        <v>0.4161153516519274</v>
       </c>
       <c r="E152" t="n">
         <v>151</v>
@@ -3327,17 +3327,17 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>2021-01-27</t>
+          <t>2021-02-03</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>25604690493</v>
+        <v>27946762653</v>
       </c>
       <c r="C153" t="n">
-        <v>60015878129</v>
+        <v>64252239936</v>
       </c>
       <c r="D153" t="n">
-        <v>0.4266319396004584</v>
+        <v>0.4349539048107436</v>
       </c>
       <c r="E153" t="n">
         <v>152</v>
@@ -3346,17 +3346,17 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>2021-01-28</t>
+          <t>2021-02-04</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>26286085867</v>
+        <v>26745949814</v>
       </c>
       <c r="C154" t="n">
-        <v>62311898539</v>
+        <v>65026335158</v>
       </c>
       <c r="D154" t="n">
-        <v>0.4218469743872106</v>
+        <v>0.411309506356357</v>
       </c>
       <c r="E154" t="n">
         <v>153</v>
@@ -3365,17 +3365,17 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>2021-01-29</t>
+          <t>2021-02-05</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>27002904913</v>
+        <v>27228530445</v>
       </c>
       <c r="C155" t="n">
-        <v>66018503681</v>
+        <v>60817228192</v>
       </c>
       <c r="D155" t="n">
-        <v>0.4090202504963981</v>
+        <v>0.44771080916479</v>
       </c>
       <c r="E155" t="n">
         <v>154</v>
@@ -3384,17 +3384,17 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>2021-02-01</t>
+          <t>2021-02-08</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>25457673045</v>
+        <v>22845413099</v>
       </c>
       <c r="C156" t="n">
-        <v>61214730247</v>
+        <v>53099229697</v>
       </c>
       <c r="D156" t="n">
-        <v>0.4158749526834291</v>
+        <v>0.4302400096830542</v>
       </c>
       <c r="E156" t="n">
         <v>155</v>
@@ -3403,17 +3403,17 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>2021-02-02</t>
+          <t>2021-02-09</t>
         </is>
       </c>
       <c r="B157" t="n">
-        <v>24585679056</v>
+        <v>23052987297</v>
       </c>
       <c r="C157" t="n">
-        <v>59083806830</v>
+        <v>54414450658</v>
       </c>
       <c r="D157" t="n">
-        <v>0.4161153516519274</v>
+        <v>0.4236556101960896</v>
       </c>
       <c r="E157" t="n">
         <v>156</v>
@@ -3422,17 +3422,17 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>2021-02-03</t>
+          <t>2021-02-10</t>
         </is>
       </c>
       <c r="B158" t="n">
-        <v>27946762653</v>
+        <v>23672043794</v>
       </c>
       <c r="C158" t="n">
-        <v>64252239936</v>
+        <v>53724833418</v>
       </c>
       <c r="D158" t="n">
-        <v>0.4349539048107436</v>
+        <v>0.4406164205260971</v>
       </c>
       <c r="E158" t="n">
         <v>157</v>
@@ -3441,17 +3441,17 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>2021-02-04</t>
+          <t>2021-02-18</t>
         </is>
       </c>
       <c r="B159" t="n">
-        <v>26745949814</v>
+        <v>30305438799</v>
       </c>
       <c r="C159" t="n">
-        <v>65026335158</v>
+        <v>70581483088</v>
       </c>
       <c r="D159" t="n">
-        <v>0.411309506356357</v>
+        <v>0.4293681213982937</v>
       </c>
       <c r="E159" t="n">
         <v>158</v>
@@ -3460,17 +3460,17 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>2021-02-05</t>
+          <t>2021-02-19</t>
         </is>
       </c>
       <c r="B160" t="n">
-        <v>27228530445</v>
+        <v>31871390359</v>
       </c>
       <c r="C160" t="n">
-        <v>60817228192</v>
+        <v>74891926971</v>
       </c>
       <c r="D160" t="n">
-        <v>0.44771080916479</v>
+        <v>0.4255650995779744</v>
       </c>
       <c r="E160" t="n">
         <v>159</v>
@@ -3479,17 +3479,17 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>2021-02-08</t>
+          <t>2021-02-22</t>
         </is>
       </c>
       <c r="B161" t="n">
-        <v>22845413099</v>
+        <v>41800730539</v>
       </c>
       <c r="C161" t="n">
-        <v>53099229697</v>
+        <v>98345390597</v>
       </c>
       <c r="D161" t="n">
-        <v>0.4302400096830542</v>
+        <v>0.4250400581588124</v>
       </c>
       <c r="E161" t="n">
         <v>160</v>
@@ -3498,17 +3498,17 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>2021-02-09</t>
+          <t>2021-02-23</t>
         </is>
       </c>
       <c r="B162" t="n">
-        <v>23052987297</v>
+        <v>36659765914</v>
       </c>
       <c r="C162" t="n">
-        <v>54414450658</v>
+        <v>79667225639</v>
       </c>
       <c r="D162" t="n">
-        <v>0.4236556101960896</v>
+        <v>0.4601611970287279</v>
       </c>
       <c r="E162" t="n">
         <v>161</v>
@@ -3517,17 +3517,17 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>2021-02-10</t>
+          <t>2021-02-24</t>
         </is>
       </c>
       <c r="B163" t="n">
-        <v>23672043794</v>
+        <v>33328852498</v>
       </c>
       <c r="C163" t="n">
-        <v>53724833418</v>
+        <v>74974298826</v>
       </c>
       <c r="D163" t="n">
-        <v>0.4406164205260971</v>
+        <v>0.4445370349557979</v>
       </c>
       <c r="E163" t="n">
         <v>162</v>
@@ -3536,17 +3536,17 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>2021-02-18</t>
+          <t>2021-02-25</t>
         </is>
       </c>
       <c r="B164" t="n">
-        <v>30305438799</v>
+        <v>33009105938</v>
       </c>
       <c r="C164" t="n">
-        <v>70581483088</v>
+        <v>72321851390</v>
       </c>
       <c r="D164" t="n">
-        <v>0.4293681213982937</v>
+        <v>0.4564195371603028</v>
       </c>
       <c r="E164" t="n">
         <v>163</v>
@@ -3555,17 +3555,17 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>2021-02-19</t>
+          <t>2021-02-26</t>
         </is>
       </c>
       <c r="B165" t="n">
-        <v>31871390359</v>
+        <v>29437488128</v>
       </c>
       <c r="C165" t="n">
-        <v>74891926971</v>
+        <v>67566280430</v>
       </c>
       <c r="D165" t="n">
-        <v>0.4255650995779744</v>
+        <v>0.4356831238993216</v>
       </c>
       <c r="E165" t="n">
         <v>164</v>
@@ -3574,17 +3574,17 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>2021-02-22</t>
+          <t>2021-03-01</t>
         </is>
       </c>
       <c r="B166" t="n">
-        <v>41800730539</v>
+        <v>28022529242</v>
       </c>
       <c r="C166" t="n">
-        <v>98345390597</v>
+        <v>65847760652</v>
       </c>
       <c r="D166" t="n">
-        <v>0.4250400581588124</v>
+        <v>0.425565409734991</v>
       </c>
       <c r="E166" t="n">
         <v>165</v>
@@ -3593,17 +3593,17 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>2021-02-23</t>
+          <t>2021-03-02</t>
         </is>
       </c>
       <c r="B167" t="n">
-        <v>36659765914</v>
+        <v>30548474585</v>
       </c>
       <c r="C167" t="n">
-        <v>79667225639</v>
+        <v>69441386639</v>
       </c>
       <c r="D167" t="n">
-        <v>0.4601611970287279</v>
+        <v>0.4399174046424243</v>
       </c>
       <c r="E167" t="n">
         <v>166</v>
@@ -3612,17 +3612,17 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>2021-02-24</t>
+          <t>2021-03-03</t>
         </is>
       </c>
       <c r="B168" t="n">
-        <v>33328852498</v>
+        <v>31581683271</v>
       </c>
       <c r="C168" t="n">
-        <v>74974298826</v>
+        <v>69999474895</v>
       </c>
       <c r="D168" t="n">
-        <v>0.4445370349557979</v>
+        <v>0.4511702883253464</v>
       </c>
       <c r="E168" t="n">
         <v>167</v>
@@ -3631,17 +3631,17 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>2021-02-25</t>
+          <t>2021-03-04</t>
         </is>
       </c>
       <c r="B169" t="n">
-        <v>33009105938</v>
+        <v>36100282673</v>
       </c>
       <c r="C169" t="n">
-        <v>72321851390</v>
+        <v>78562142790</v>
       </c>
       <c r="D169" t="n">
-        <v>0.4564195371603028</v>
+        <v>0.4595124495203449</v>
       </c>
       <c r="E169" t="n">
         <v>168</v>
@@ -3650,17 +3650,17 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>2021-02-26</t>
+          <t>2021-03-05</t>
         </is>
       </c>
       <c r="B170" t="n">
-        <v>29437488128</v>
+        <v>32337135967</v>
       </c>
       <c r="C170" t="n">
-        <v>67566280430</v>
+        <v>73514786011</v>
       </c>
       <c r="D170" t="n">
-        <v>0.4356831238993216</v>
+        <v>0.4398725443091326</v>
       </c>
       <c r="E170" t="n">
         <v>169</v>
@@ -3669,17 +3669,17 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>2021-03-01</t>
+          <t>2021-03-08</t>
         </is>
       </c>
       <c r="B171" t="n">
-        <v>28022529242</v>
+        <v>34237890063</v>
       </c>
       <c r="C171" t="n">
-        <v>65847760652</v>
+        <v>78814375242</v>
       </c>
       <c r="D171" t="n">
-        <v>0.425565409734991</v>
+        <v>0.4344117422471771</v>
       </c>
       <c r="E171" t="n">
         <v>170</v>
@@ -3688,17 +3688,17 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>2021-03-02</t>
+          <t>2021-03-09</t>
         </is>
       </c>
       <c r="B172" t="n">
-        <v>30548474585</v>
+        <v>35838361211</v>
       </c>
       <c r="C172" t="n">
-        <v>69441386639</v>
+        <v>82850202998</v>
       </c>
       <c r="D172" t="n">
-        <v>0.4399174046424243</v>
+        <v>0.4325681762284292</v>
       </c>
       <c r="E172" t="n">
         <v>171</v>
@@ -3707,17 +3707,17 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>2021-03-03</t>
+          <t>2021-03-10</t>
         </is>
       </c>
       <c r="B173" t="n">
-        <v>31581683271</v>
+        <v>26975456721</v>
       </c>
       <c r="C173" t="n">
-        <v>69999474895</v>
+        <v>62127335207</v>
       </c>
       <c r="D173" t="n">
-        <v>0.4511702883253464</v>
+        <v>0.4341962620981791</v>
       </c>
       <c r="E173" t="n">
         <v>172</v>
@@ -3726,17 +3726,17 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>2021-03-04</t>
+          <t>2021-03-11</t>
         </is>
       </c>
       <c r="B174" t="n">
-        <v>36100282673</v>
+        <v>30680047969</v>
       </c>
       <c r="C174" t="n">
-        <v>78562142790</v>
+        <v>66598157167</v>
       </c>
       <c r="D174" t="n">
-        <v>0.4595124495203449</v>
+        <v>0.4606741278451207</v>
       </c>
       <c r="E174" t="n">
         <v>173</v>
@@ -3745,17 +3745,17 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>2021-03-05</t>
+          <t>2021-03-12</t>
         </is>
       </c>
       <c r="B175" t="n">
-        <v>32337135967</v>
+        <v>33862968625</v>
       </c>
       <c r="C175" t="n">
-        <v>73514786011</v>
+        <v>72238010975</v>
       </c>
       <c r="D175" t="n">
-        <v>0.4398725443091326</v>
+        <v>0.4687693939513262</v>
       </c>
       <c r="E175" t="n">
         <v>174</v>
@@ -3764,17 +3764,17 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>2021-03-08</t>
+          <t>2021-03-15</t>
         </is>
       </c>
       <c r="B176" t="n">
-        <v>34237890063</v>
+        <v>34591765793</v>
       </c>
       <c r="C176" t="n">
-        <v>78814375242</v>
+        <v>71723136959</v>
       </c>
       <c r="D176" t="n">
-        <v>0.4344117422471771</v>
+        <v>0.4822957731585852</v>
       </c>
       <c r="E176" t="n">
         <v>175</v>
@@ -3783,17 +3783,17 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>2021-03-09</t>
+          <t>2021-03-16</t>
         </is>
       </c>
       <c r="B177" t="n">
-        <v>35838361211</v>
+        <v>29977825317</v>
       </c>
       <c r="C177" t="n">
-        <v>82850202998</v>
+        <v>67049266583</v>
       </c>
       <c r="D177" t="n">
-        <v>0.4325681762284292</v>
+        <v>0.447101465008429</v>
       </c>
       <c r="E177" t="n">
         <v>176</v>
@@ -3802,17 +3802,17 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>2021-03-10</t>
+          <t>2021-03-17</t>
         </is>
       </c>
       <c r="B178" t="n">
-        <v>26975456721</v>
+        <v>27491185060</v>
       </c>
       <c r="C178" t="n">
-        <v>62127335207</v>
+        <v>62515062852</v>
       </c>
       <c r="D178" t="n">
-        <v>0.4341962620981791</v>
+        <v>0.4397529780156095</v>
       </c>
       <c r="E178" t="n">
         <v>177</v>
@@ -3821,17 +3821,17 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>2021-03-11</t>
+          <t>2021-03-18</t>
         </is>
       </c>
       <c r="B179" t="n">
-        <v>30680047969</v>
+        <v>26739276351</v>
       </c>
       <c r="C179" t="n">
-        <v>66598157167</v>
+        <v>62832911819</v>
       </c>
       <c r="D179" t="n">
-        <v>0.4606741278451207</v>
+        <v>0.4255616296762858</v>
       </c>
       <c r="E179" t="n">
         <v>178</v>
@@ -3840,17 +3840,17 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>2021-03-12</t>
+          <t>2021-03-19</t>
         </is>
       </c>
       <c r="B180" t="n">
-        <v>33862968625</v>
+        <v>28358235249</v>
       </c>
       <c r="C180" t="n">
-        <v>72238010975</v>
+        <v>65875538395</v>
       </c>
       <c r="D180" t="n">
-        <v>0.4687693939513262</v>
+        <v>0.4304820262562349</v>
       </c>
       <c r="E180" t="n">
         <v>179</v>
@@ -3859,17 +3859,17 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>2021-03-15</t>
+          <t>2021-03-22</t>
         </is>
       </c>
       <c r="B181" t="n">
-        <v>34591765793</v>
+        <v>29121013208</v>
       </c>
       <c r="C181" t="n">
-        <v>71723136959</v>
+        <v>67358226346</v>
       </c>
       <c r="D181" t="n">
-        <v>0.4822957731585852</v>
+        <v>0.4323304633707791</v>
       </c>
       <c r="E181" t="n">
         <v>180</v>
@@ -3878,17 +3878,17 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>2021-03-16</t>
+          <t>2021-03-23</t>
         </is>
       </c>
       <c r="B182" t="n">
-        <v>29977825317</v>
+        <v>29320271653</v>
       </c>
       <c r="C182" t="n">
-        <v>67049266583</v>
+        <v>70323191299</v>
       </c>
       <c r="D182" t="n">
-        <v>0.447101465008429</v>
+        <v>0.4169360222623591</v>
       </c>
       <c r="E182" t="n">
         <v>181</v>
@@ -3897,17 +3897,17 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>2021-03-17</t>
+          <t>2021-03-24</t>
         </is>
       </c>
       <c r="B183" t="n">
-        <v>27491185060</v>
+        <v>28494202046</v>
       </c>
       <c r="C183" t="n">
-        <v>62515062852</v>
+        <v>67303523996</v>
       </c>
       <c r="D183" t="n">
-        <v>0.4397529780156095</v>
+        <v>0.423368649280437</v>
       </c>
       <c r="E183" t="n">
         <v>182</v>
@@ -3916,17 +3916,17 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>2021-03-18</t>
+          <t>2021-03-25</t>
         </is>
       </c>
       <c r="B184" t="n">
-        <v>26739276351</v>
+        <v>25857769578</v>
       </c>
       <c r="C184" t="n">
-        <v>62832911819</v>
+        <v>60650502617</v>
       </c>
       <c r="D184" t="n">
-        <v>0.4255616296762858</v>
+        <v>0.426340565407816</v>
       </c>
       <c r="E184" t="n">
         <v>183</v>
@@ -3935,17 +3935,17 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>2021-03-19</t>
+          <t>2021-03-26</t>
         </is>
       </c>
       <c r="B185" t="n">
-        <v>28358235249</v>
+        <v>25857588064</v>
       </c>
       <c r="C185" t="n">
-        <v>65875538395</v>
+        <v>61284664475</v>
       </c>
       <c r="D185" t="n">
-        <v>0.4304820262562349</v>
+        <v>0.4219259138564452</v>
       </c>
       <c r="E185" t="n">
         <v>184</v>
@@ -3954,17 +3954,17 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>2021-03-22</t>
+          <t>2021-03-29</t>
         </is>
       </c>
       <c r="B186" t="n">
-        <v>29121013208</v>
+        <v>26030305012</v>
       </c>
       <c r="C186" t="n">
-        <v>67358226346</v>
+        <v>62965892538</v>
       </c>
       <c r="D186" t="n">
-        <v>0.4323304633707791</v>
+        <v>0.4134032563151658</v>
       </c>
       <c r="E186" t="n">
         <v>185</v>
@@ -3973,17 +3973,17 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>2021-03-23</t>
+          <t>2021-03-30</t>
         </is>
       </c>
       <c r="B187" t="n">
-        <v>29320271653</v>
+        <v>25780001010</v>
       </c>
       <c r="C187" t="n">
-        <v>70323191299</v>
+        <v>62868502600</v>
       </c>
       <c r="D187" t="n">
-        <v>0.4169360222623591</v>
+        <v>0.4100622719460158</v>
       </c>
       <c r="E187" t="n">
         <v>186</v>
@@ -3992,17 +3992,17 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>2021-03-24</t>
+          <t>2021-03-31</t>
         </is>
       </c>
       <c r="B188" t="n">
-        <v>28494202046</v>
+        <v>25340940136</v>
       </c>
       <c r="C188" t="n">
-        <v>67303523996</v>
+        <v>58944651908</v>
       </c>
       <c r="D188" t="n">
-        <v>0.423368649280437</v>
+        <v>0.4299107606157687</v>
       </c>
       <c r="E188" t="n">
         <v>187</v>
@@ -4011,17 +4011,17 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>2021-03-25</t>
+          <t>2021-04-01</t>
         </is>
       </c>
       <c r="B189" t="n">
-        <v>25857769578</v>
+        <v>24459982838</v>
       </c>
       <c r="C189" t="n">
-        <v>60650502617</v>
+        <v>57742915146</v>
       </c>
       <c r="D189" t="n">
-        <v>0.426340565407816</v>
+        <v>0.4236014544148696</v>
       </c>
       <c r="E189" t="n">
         <v>188</v>
@@ -4030,17 +4030,17 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>2021-03-26</t>
+          <t>2021-04-02</t>
         </is>
       </c>
       <c r="B190" t="n">
-        <v>25857588064</v>
+        <v>23776468616</v>
       </c>
       <c r="C190" t="n">
-        <v>61284664475</v>
+        <v>57637646459</v>
       </c>
       <c r="D190" t="n">
-        <v>0.4219259138564452</v>
+        <v>0.4125162992717471</v>
       </c>
       <c r="E190" t="n">
         <v>189</v>
@@ -4049,17 +4049,17 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>2021-03-29</t>
+          <t>2021-04-06</t>
         </is>
       </c>
       <c r="B191" t="n">
-        <v>26030305012</v>
+        <v>21609152872</v>
       </c>
       <c r="C191" t="n">
-        <v>62965892538</v>
+        <v>54009467026</v>
       </c>
       <c r="D191" t="n">
-        <v>0.4134032563151658</v>
+        <v>0.4000993540928189</v>
       </c>
       <c r="E191" t="n">
         <v>190</v>
@@ -4068,17 +4068,17 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>2021-03-30</t>
+          <t>2021-04-07</t>
         </is>
       </c>
       <c r="B192" t="n">
-        <v>25780001010</v>
+        <v>28192988226</v>
       </c>
       <c r="C192" t="n">
-        <v>62868502600</v>
+        <v>64777711487</v>
       </c>
       <c r="D192" t="n">
-        <v>0.4100622719460158</v>
+        <v>0.4352266787266473</v>
       </c>
       <c r="E192" t="n">
         <v>191</v>
@@ -4087,17 +4087,17 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>2021-03-31</t>
+          <t>2021-04-08</t>
         </is>
       </c>
       <c r="B193" t="n">
-        <v>25340940136</v>
+        <v>31610774016</v>
       </c>
       <c r="C193" t="n">
-        <v>58944651908</v>
+        <v>70183037971</v>
       </c>
       <c r="D193" t="n">
-        <v>0.4299107606157687</v>
+        <v>0.4504047549076137</v>
       </c>
       <c r="E193" t="n">
         <v>192</v>
@@ -4106,17 +4106,17 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>2021-04-01</t>
+          <t>2021-04-09</t>
         </is>
       </c>
       <c r="B194" t="n">
-        <v>24459982838</v>
+        <v>27363203695</v>
       </c>
       <c r="C194" t="n">
-        <v>57742915146</v>
+        <v>60908586933</v>
       </c>
       <c r="D194" t="n">
-        <v>0.4236014544148696</v>
+        <v>0.4492503450309851</v>
       </c>
       <c r="E194" t="n">
         <v>193</v>
@@ -4125,17 +4125,17 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>2021-04-02</t>
+          <t>2021-04-12</t>
         </is>
       </c>
       <c r="B195" t="n">
-        <v>23776468616</v>
+        <v>29441281600</v>
       </c>
       <c r="C195" t="n">
-        <v>57637646459</v>
+        <v>66662877908</v>
       </c>
       <c r="D195" t="n">
-        <v>0.4125162992717471</v>
+        <v>0.4416443232563598</v>
       </c>
       <c r="E195" t="n">
         <v>194</v>
@@ -4144,17 +4144,17 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>2021-04-06</t>
+          <t>2021-04-13</t>
         </is>
       </c>
       <c r="B196" t="n">
-        <v>21609152872</v>
+        <v>26500289609</v>
       </c>
       <c r="C196" t="n">
-        <v>54009467026</v>
+        <v>60099497250</v>
       </c>
       <c r="D196" t="n">
-        <v>0.4000993540928189</v>
+        <v>0.4409402877159675</v>
       </c>
       <c r="E196" t="n">
         <v>195</v>
@@ -4163,17 +4163,17 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>2021-04-07</t>
+          <t>2021-04-14</t>
         </is>
       </c>
       <c r="B197" t="n">
-        <v>28192988226</v>
+        <v>24875678254</v>
       </c>
       <c r="C197" t="n">
-        <v>64777711487</v>
+        <v>56149660115</v>
       </c>
       <c r="D197" t="n">
-        <v>0.4352266787266473</v>
+        <v>0.4430245562137362</v>
       </c>
       <c r="E197" t="n">
         <v>196</v>
@@ -4182,17 +4182,17 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>2021-04-08</t>
+          <t>2021-04-15</t>
         </is>
       </c>
       <c r="B198" t="n">
-        <v>31610774016</v>
+        <v>23587218127</v>
       </c>
       <c r="C198" t="n">
-        <v>70183037971</v>
+        <v>56730832399</v>
       </c>
       <c r="D198" t="n">
-        <v>0.4504047549076137</v>
+        <v>0.4157742294543835</v>
       </c>
       <c r="E198" t="n">
         <v>197</v>
@@ -4201,17 +4201,17 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>2021-04-09</t>
+          <t>2021-04-16</t>
         </is>
       </c>
       <c r="B199" t="n">
-        <v>27363203695</v>
+        <v>23064238930</v>
       </c>
       <c r="C199" t="n">
-        <v>60908586933</v>
+        <v>60757105467</v>
       </c>
       <c r="D199" t="n">
-        <v>0.4492503450309851</v>
+        <v>0.3796138534368998</v>
       </c>
       <c r="E199" t="n">
         <v>198</v>
@@ -4220,17 +4220,17 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>2021-04-12</t>
+          <t>2021-04-19</t>
         </is>
       </c>
       <c r="B200" t="n">
-        <v>29441281600</v>
+        <v>26349229565</v>
       </c>
       <c r="C200" t="n">
-        <v>66662877908</v>
+        <v>68717257011</v>
       </c>
       <c r="D200" t="n">
-        <v>0.4416443232563598</v>
+        <v>0.3834441406877186</v>
       </c>
       <c r="E200" t="n">
         <v>199</v>
@@ -4239,17 +4239,17 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>2021-04-13</t>
+          <t>2021-04-20</t>
         </is>
       </c>
       <c r="B201" t="n">
-        <v>26500289609</v>
+        <v>26332452757</v>
       </c>
       <c r="C201" t="n">
-        <v>60099497250</v>
+        <v>66152179163</v>
       </c>
       <c r="D201" t="n">
-        <v>0.4409402877159675</v>
+        <v>0.3980587350284626</v>
       </c>
       <c r="E201" t="n">
         <v>200</v>
@@ -4258,17 +4258,17 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>2021-04-14</t>
+          <t>2021-04-21</t>
         </is>
       </c>
       <c r="B202" t="n">
-        <v>24875678254</v>
+        <v>23796108657</v>
       </c>
       <c r="C202" t="n">
-        <v>56149660115</v>
+        <v>58645267418</v>
       </c>
       <c r="D202" t="n">
-        <v>0.4430245562137362</v>
+        <v>0.4057634947316526</v>
       </c>
       <c r="E202" t="n">
         <v>201</v>
@@ -4277,17 +4277,17 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>2021-04-15</t>
+          <t>2021-04-22</t>
         </is>
       </c>
       <c r="B203" t="n">
-        <v>23587218127</v>
+        <v>23283868400</v>
       </c>
       <c r="C203" t="n">
-        <v>56730832399</v>
+        <v>57343158813</v>
       </c>
       <c r="D203" t="n">
-        <v>0.4157742294543835</v>
+        <v>0.406044398006226</v>
       </c>
       <c r="E203" t="n">
         <v>202</v>
@@ -4296,17 +4296,17 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>2021-04-16</t>
+          <t>2021-04-23</t>
         </is>
       </c>
       <c r="B204" t="n">
-        <v>23064238930</v>
+        <v>23110619160</v>
       </c>
       <c r="C204" t="n">
-        <v>60757105467</v>
+        <v>58758936747</v>
       </c>
       <c r="D204" t="n">
-        <v>0.3796138534368998</v>
+        <v>0.3933124123655954</v>
       </c>
       <c r="E204" t="n">
         <v>203</v>
@@ -4315,17 +4315,17 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>2021-04-19</t>
+          <t>2021-04-26</t>
         </is>
       </c>
       <c r="B205" t="n">
-        <v>26349229565</v>
+        <v>26080656908</v>
       </c>
       <c r="C205" t="n">
-        <v>68717257011</v>
+        <v>64990659217</v>
       </c>
       <c r="D205" t="n">
-        <v>0.3834441406877186</v>
+        <v>0.4012985438556365</v>
       </c>
       <c r="E205" t="n">
         <v>204</v>
@@ -4334,17 +4334,17 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>2021-04-20</t>
+          <t>2021-04-27</t>
         </is>
       </c>
       <c r="B206" t="n">
-        <v>26332452757</v>
+        <v>22805398723</v>
       </c>
       <c r="C206" t="n">
-        <v>66152179163</v>
+        <v>58465572266</v>
       </c>
       <c r="D206" t="n">
-        <v>0.3980587350284626</v>
+        <v>0.3900654323409783</v>
       </c>
       <c r="E206" t="n">
         <v>205</v>
@@ -4353,17 +4353,17 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>2021-04-21</t>
+          <t>2021-04-28</t>
         </is>
       </c>
       <c r="B207" t="n">
-        <v>23796108657</v>
+        <v>21764975470</v>
       </c>
       <c r="C207" t="n">
-        <v>58645267418</v>
+        <v>56258757783</v>
       </c>
       <c r="D207" t="n">
-        <v>0.4057634947316526</v>
+        <v>0.3868726635229197</v>
       </c>
       <c r="E207" t="n">
         <v>206</v>
@@ -4372,17 +4372,17 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>2021-04-22</t>
+          <t>2021-04-29</t>
         </is>
       </c>
       <c r="B208" t="n">
-        <v>23283868400</v>
+        <v>23871290845</v>
       </c>
       <c r="C208" t="n">
-        <v>57343158813</v>
+        <v>59672070298</v>
       </c>
       <c r="D208" t="n">
-        <v>0.406044398006226</v>
+        <v>0.400041270996426</v>
       </c>
       <c r="E208" t="n">
         <v>207</v>
@@ -4391,17 +4391,17 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>2021-04-23</t>
+          <t>2021-04-30</t>
         </is>
       </c>
       <c r="B209" t="n">
-        <v>23110619160</v>
+        <v>26727927563</v>
       </c>
       <c r="C209" t="n">
-        <v>58758936747</v>
+        <v>64623812735</v>
       </c>
       <c r="D209" t="n">
-        <v>0.3933124123655954</v>
+        <v>0.413592550978105</v>
       </c>
       <c r="E209" t="n">
         <v>208</v>
@@ -4410,17 +4410,17 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>2021-04-26</t>
+          <t>2021-05-06</t>
         </is>
       </c>
       <c r="B210" t="n">
-        <v>26080656908</v>
+        <v>28245158344</v>
       </c>
       <c r="C210" t="n">
-        <v>64990659217</v>
+        <v>64995398044</v>
       </c>
       <c r="D210" t="n">
-        <v>0.4012985438556365</v>
+        <v>0.4345716649797089</v>
       </c>
       <c r="E210" t="n">
         <v>209</v>
@@ -4429,17 +4429,17 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>2021-04-27</t>
+          <t>2021-05-07</t>
         </is>
       </c>
       <c r="B211" t="n">
-        <v>22805398723</v>
+        <v>33809492530</v>
       </c>
       <c r="C211" t="n">
-        <v>58465572266</v>
+        <v>72689004129</v>
       </c>
       <c r="D211" t="n">
-        <v>0.3900654323409783</v>
+        <v>0.4651252680529072</v>
       </c>
       <c r="E211" t="n">
         <v>210</v>
@@ -4448,17 +4448,17 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>2021-04-28</t>
+          <t>2021-05-10</t>
         </is>
       </c>
       <c r="B212" t="n">
-        <v>21764975470</v>
+        <v>34980447442</v>
       </c>
       <c r="C212" t="n">
-        <v>56258757783</v>
+        <v>74391256531</v>
       </c>
       <c r="D212" t="n">
-        <v>0.3868726635229197</v>
+        <v>0.4702225647636843</v>
       </c>
       <c r="E212" t="n">
         <v>211</v>
@@ -4467,17 +4467,17 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>2021-04-29</t>
+          <t>2021-05-11</t>
         </is>
       </c>
       <c r="B213" t="n">
-        <v>23871290845</v>
+        <v>33682768573</v>
       </c>
       <c r="C213" t="n">
-        <v>59672070298</v>
+        <v>73459473614</v>
       </c>
       <c r="D213" t="n">
-        <v>0.400041270996426</v>
+        <v>0.4585217796412401</v>
       </c>
       <c r="E213" t="n">
         <v>212</v>
@@ -4486,17 +4486,17 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>2021-04-30</t>
+          <t>2021-05-12</t>
         </is>
       </c>
       <c r="B214" t="n">
-        <v>26727927563</v>
+        <v>28011409229</v>
       </c>
       <c r="C214" t="n">
-        <v>64623812735</v>
+        <v>66061705250</v>
       </c>
       <c r="D214" t="n">
-        <v>0.413592550978105</v>
+        <v>0.4240188642269418</v>
       </c>
       <c r="E214" t="n">
         <v>213</v>
@@ -4505,17 +4505,17 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>2021-05-06</t>
+          <t>2021-05-13</t>
         </is>
       </c>
       <c r="B215" t="n">
-        <v>28245158344</v>
+        <v>29021959092</v>
       </c>
       <c r="C215" t="n">
-        <v>64995398044</v>
+        <v>69247970457</v>
       </c>
       <c r="D215" t="n">
-        <v>0.4345716649797089</v>
+        <v>0.4191019448002651</v>
       </c>
       <c r="E215" t="n">
         <v>214</v>
@@ -4524,17 +4524,17 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>2021-05-07</t>
+          <t>2021-05-14</t>
         </is>
       </c>
       <c r="B216" t="n">
-        <v>33809492530</v>
+        <v>29087549466</v>
       </c>
       <c r="C216" t="n">
-        <v>72689004129</v>
+        <v>72865719627</v>
       </c>
       <c r="D216" t="n">
-        <v>0.4651252680529072</v>
+        <v>0.3991938817718307</v>
       </c>
       <c r="E216" t="n">
         <v>215</v>
@@ -4543,17 +4543,17 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>2021-05-10</t>
+          <t>2021-05-17</t>
         </is>
       </c>
       <c r="B217" t="n">
-        <v>34980447442</v>
+        <v>26738086558</v>
       </c>
       <c r="C217" t="n">
-        <v>74391256531</v>
+        <v>68865623007</v>
       </c>
       <c r="D217" t="n">
-        <v>0.4702225647636843</v>
+        <v>0.3882646433806625</v>
       </c>
       <c r="E217" t="n">
         <v>216</v>
@@ -4562,17 +4562,17 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>2021-05-11</t>
+          <t>2021-05-18</t>
         </is>
       </c>
       <c r="B218" t="n">
-        <v>33682768573</v>
+        <v>23944078372</v>
       </c>
       <c r="C218" t="n">
-        <v>73459473614</v>
+        <v>58781317109</v>
       </c>
       <c r="D218" t="n">
-        <v>0.4585217796412401</v>
+        <v>0.4073416444139855</v>
       </c>
       <c r="E218" t="n">
         <v>217</v>
@@ -4581,17 +4581,17 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>2021-05-12</t>
+          <t>2021-05-19</t>
         </is>
       </c>
       <c r="B219" t="n">
-        <v>28011409229</v>
+        <v>25053218592</v>
       </c>
       <c r="C219" t="n">
-        <v>66061705250</v>
+        <v>60763325645</v>
       </c>
       <c r="D219" t="n">
-        <v>0.4240188642269418</v>
+        <v>0.4123082192434532</v>
       </c>
       <c r="E219" t="n">
         <v>218</v>
@@ -4600,17 +4600,17 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>2021-05-13</t>
+          <t>2021-05-20</t>
         </is>
       </c>
       <c r="B220" t="n">
-        <v>29021959092</v>
+        <v>28722723747</v>
       </c>
       <c r="C220" t="n">
-        <v>69247970457</v>
+        <v>68566840023</v>
       </c>
       <c r="D220" t="n">
-        <v>0.4191019448002651</v>
+        <v>0.4189010859675796</v>
       </c>
       <c r="E220" t="n">
         <v>219</v>
@@ -4619,17 +4619,17 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>2021-05-14</t>
+          <t>2021-05-21</t>
         </is>
       </c>
       <c r="B221" t="n">
-        <v>29087549466</v>
+        <v>25545536529</v>
       </c>
       <c r="C221" t="n">
-        <v>72865719627</v>
+        <v>61418379955</v>
       </c>
       <c r="D221" t="n">
-        <v>0.3991938817718307</v>
+        <v>0.4159265768279251</v>
       </c>
       <c r="E221" t="n">
         <v>220</v>
@@ -4638,17 +4638,17 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>2021-05-17</t>
+          <t>2021-05-24</t>
         </is>
       </c>
       <c r="B222" t="n">
-        <v>26738086558</v>
+        <v>25923087661</v>
       </c>
       <c r="C222" t="n">
-        <v>68865623007</v>
+        <v>63386616118</v>
       </c>
       <c r="D222" t="n">
-        <v>0.3882646433806625</v>
+        <v>0.4089678428761964</v>
       </c>
       <c r="E222" t="n">
         <v>221</v>
@@ -4657,17 +4657,17 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>2021-05-18</t>
+          <t>2021-05-25</t>
         </is>
       </c>
       <c r="B223" t="n">
-        <v>23944078372</v>
+        <v>29902389375</v>
       </c>
       <c r="C223" t="n">
-        <v>58781317109</v>
+        <v>71817033145</v>
       </c>
       <c r="D223" t="n">
-        <v>0.4073416444139855</v>
+        <v>0.4163690431854305</v>
       </c>
       <c r="E223" t="n">
         <v>222</v>
@@ -4676,17 +4676,17 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>2021-05-19</t>
+          <t>2021-05-26</t>
         </is>
       </c>
       <c r="B224" t="n">
-        <v>25053218592</v>
+        <v>29496722494</v>
       </c>
       <c r="C224" t="n">
-        <v>60763325645</v>
+        <v>72933630614</v>
       </c>
       <c r="D224" t="n">
-        <v>0.4123082192434532</v>
+        <v>0.4044323893611015</v>
       </c>
       <c r="E224" t="n">
         <v>223</v>
@@ -4695,17 +4695,17 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>2021-05-20</t>
+          <t>2021-05-27</t>
         </is>
       </c>
       <c r="B225" t="n">
-        <v>28722723747</v>
+        <v>26896810605</v>
       </c>
       <c r="C225" t="n">
-        <v>68566840023</v>
+        <v>68968444971</v>
       </c>
       <c r="D225" t="n">
-        <v>0.4189010859675796</v>
+        <v>0.3899871980049663</v>
       </c>
       <c r="E225" t="n">
         <v>224</v>
@@ -4714,17 +4714,17 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>2021-05-21</t>
+          <t>2021-05-27</t>
         </is>
       </c>
       <c r="B226" t="n">
-        <v>25545536529</v>
+        <v>26896810605</v>
       </c>
       <c r="C226" t="n">
-        <v>61418379955</v>
+        <v>68968444971</v>
       </c>
       <c r="D226" t="n">
-        <v>0.4159265768279251</v>
+        <v>0.3899871980049663</v>
       </c>
       <c r="E226" t="n">
         <v>225</v>
@@ -4733,17 +4733,17 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>2021-05-24</t>
+          <t>2021-05-28</t>
         </is>
       </c>
       <c r="B227" t="n">
-        <v>25923087661</v>
+        <v>29791926043</v>
       </c>
       <c r="C227" t="n">
-        <v>63386616118</v>
+        <v>73972884560</v>
       </c>
       <c r="D227" t="n">
-        <v>0.4089678428761964</v>
+        <v>0.4027411695543051</v>
       </c>
       <c r="E227" t="n">
         <v>226</v>
@@ -4752,17 +4752,17 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>2021-05-25</t>
+          <t>2021-05-31</t>
         </is>
       </c>
       <c r="B228" t="n">
-        <v>29902389375</v>
+        <v>27775314244</v>
       </c>
       <c r="C228" t="n">
-        <v>71817033145</v>
+        <v>70615016083</v>
       </c>
       <c r="D228" t="n">
-        <v>0.4163690431854305</v>
+        <v>0.3933343895490053</v>
       </c>
       <c r="E228" t="n">
         <v>227</v>
@@ -4771,17 +4771,17 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>2021-05-26</t>
+          <t>2021-06-01</t>
         </is>
       </c>
       <c r="B229" t="n">
-        <v>29496722494</v>
+        <v>28722955321</v>
       </c>
       <c r="C229" t="n">
-        <v>72933630614</v>
+        <v>75176823860</v>
       </c>
       <c r="D229" t="n">
-        <v>0.4044323893611015</v>
+        <v>0.3820719451315218</v>
       </c>
       <c r="E229" t="n">
         <v>228</v>
@@ -4790,17 +4790,17 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>2021-05-27</t>
+          <t>2021-06-02</t>
         </is>
       </c>
       <c r="B230" t="n">
-        <v>26896810605</v>
+        <v>29120888356</v>
       </c>
       <c r="C230" t="n">
-        <v>68968444971</v>
+        <v>75272955834</v>
       </c>
       <c r="D230" t="n">
-        <v>0.3899871980049663</v>
+        <v>0.3868705305026218</v>
       </c>
       <c r="E230" t="n">
         <v>229</v>
@@ -4809,17 +4809,17 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>2021-05-27</t>
+          <t>2021-06-03</t>
         </is>
       </c>
       <c r="B231" t="n">
-        <v>26896810605</v>
+        <v>29199450254</v>
       </c>
       <c r="C231" t="n">
-        <v>68968444971</v>
+        <v>72798616374</v>
       </c>
       <c r="D231" t="n">
-        <v>0.3899871980049663</v>
+        <v>0.4010989728704318</v>
       </c>
       <c r="E231" t="n">
         <v>230</v>
@@ -4828,17 +4828,17 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>2021-05-28</t>
+          <t>2021-06-04</t>
         </is>
       </c>
       <c r="B232" t="n">
-        <v>29791926043</v>
+        <v>27330244158</v>
       </c>
       <c r="C232" t="n">
-        <v>73972884560</v>
+        <v>68930352581</v>
       </c>
       <c r="D232" t="n">
-        <v>0.4027411695543051</v>
+        <v>0.3964907059757783</v>
       </c>
       <c r="E232" t="n">
         <v>231</v>
@@ -4847,17 +4847,17 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>2021-05-31</t>
+          <t>2021-06-07</t>
         </is>
       </c>
       <c r="B233" t="n">
-        <v>27775314244</v>
+        <v>25294989410</v>
       </c>
       <c r="C233" t="n">
-        <v>70615016083</v>
+        <v>66558910303</v>
       </c>
       <c r="D233" t="n">
-        <v>0.3933343895490053</v>
+        <v>0.3800391156472988</v>
       </c>
       <c r="E233" t="n">
         <v>232</v>
@@ -4866,17 +4866,17 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>2021-06-01</t>
+          <t>2021-06-08</t>
         </is>
       </c>
       <c r="B234" t="n">
-        <v>28722955321</v>
+        <v>25589368881</v>
       </c>
       <c r="C234" t="n">
-        <v>75176823860</v>
+        <v>68255065080</v>
       </c>
       <c r="D234" t="n">
-        <v>0.3820719451315218</v>
+        <v>0.3749079844991337</v>
       </c>
       <c r="E234" t="n">
         <v>233</v>
@@ -4885,17 +4885,17 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>2021-06-02</t>
+          <t>2021-06-09</t>
         </is>
       </c>
       <c r="B235" t="n">
-        <v>29120888356</v>
+        <v>25270907666</v>
       </c>
       <c r="C235" t="n">
-        <v>75272955834</v>
+        <v>66612688195</v>
       </c>
       <c r="D235" t="n">
-        <v>0.3868705305026218</v>
+        <v>0.3793707828157707</v>
       </c>
       <c r="E235" t="n">
         <v>234</v>
@@ -4904,17 +4904,17 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>2021-06-03</t>
+          <t>2021-06-10</t>
         </is>
       </c>
       <c r="B236" t="n">
-        <v>29199450254</v>
+        <v>27144684274</v>
       </c>
       <c r="C236" t="n">
-        <v>72798616374</v>
+        <v>72726642476</v>
       </c>
       <c r="D236" t="n">
-        <v>0.4010989728704318</v>
+        <v>0.3732426432714507</v>
       </c>
       <c r="E236" t="n">
         <v>235</v>
@@ -4923,17 +4923,17 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>2021-06-04</t>
+          <t>2021-06-11</t>
         </is>
       </c>
       <c r="B237" t="n">
-        <v>27330244158</v>
+        <v>31253551848</v>
       </c>
       <c r="C237" t="n">
-        <v>68930352581</v>
+        <v>80603106508</v>
       </c>
       <c r="D237" t="n">
-        <v>0.3964907059757783</v>
+        <v>0.3877462445556987</v>
       </c>
       <c r="E237" t="n">
         <v>236</v>
@@ -4942,17 +4942,17 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>2021-06-07</t>
+          <t>2021-06-15</t>
         </is>
       </c>
       <c r="B238" t="n">
-        <v>25294989410</v>
+        <v>26600340763</v>
       </c>
       <c r="C238" t="n">
-        <v>66558910303</v>
+        <v>71269245087</v>
       </c>
       <c r="D238" t="n">
-        <v>0.3800391156472988</v>
+        <v>0.3732373021564681</v>
       </c>
       <c r="E238" t="n">
         <v>237</v>
@@ -4961,17 +4961,17 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>2021-06-08</t>
+          <t>2021-06-16</t>
         </is>
       </c>
       <c r="B239" t="n">
-        <v>25589368881</v>
+        <v>25225237352</v>
       </c>
       <c r="C239" t="n">
-        <v>68255065080</v>
+        <v>65304111913</v>
       </c>
       <c r="D239" t="n">
-        <v>0.3749079844991337</v>
+        <v>0.3862733388918263</v>
       </c>
       <c r="E239" t="n">
         <v>238</v>
@@ -4980,17 +4980,17 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>2021-06-09</t>
+          <t>2021-06-17</t>
         </is>
       </c>
       <c r="B240" t="n">
-        <v>25270907666</v>
+        <v>23865594042</v>
       </c>
       <c r="C240" t="n">
-        <v>66612688195</v>
+        <v>62073104309</v>
       </c>
       <c r="D240" t="n">
-        <v>0.3793707828157707</v>
+        <v>0.3844756003050377</v>
       </c>
       <c r="E240" t="n">
         <v>239</v>
@@ -4999,17 +4999,17 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>2021-06-10</t>
+          <t>2021-06-18</t>
         </is>
       </c>
       <c r="B241" t="n">
-        <v>27144684274</v>
+        <v>26773348572</v>
       </c>
       <c r="C241" t="n">
-        <v>72726642476</v>
+        <v>68507417006</v>
       </c>
       <c r="D241" t="n">
-        <v>0.3732426432714507</v>
+        <v>0.3908094881121433</v>
       </c>
       <c r="E241" t="n">
         <v>240</v>
@@ -5018,17 +5018,17 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>2021-06-11</t>
+          <t>2021-06-21</t>
         </is>
       </c>
       <c r="B242" t="n">
-        <v>31253551848</v>
+        <v>25810884254</v>
       </c>
       <c r="C242" t="n">
-        <v>80603106508</v>
+        <v>68094480065</v>
       </c>
       <c r="D242" t="n">
-        <v>0.3877462445556987</v>
+        <v>0.3790451770740016</v>
       </c>
       <c r="E242" t="n">
         <v>241</v>
@@ -5037,17 +5037,17 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>2021-06-15</t>
+          <t>2021-06-22</t>
         </is>
       </c>
       <c r="B243" t="n">
-        <v>26600340763</v>
+        <v>27325435943</v>
       </c>
       <c r="C243" t="n">
-        <v>71269245087</v>
+        <v>71331165214</v>
       </c>
       <c r="D243" t="n">
-        <v>0.3732373021564681</v>
+        <v>0.3830785023772036</v>
       </c>
       <c r="E243" t="n">
         <v>242</v>
@@ -5056,17 +5056,17 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>2021-06-16</t>
+          <t>2021-06-23</t>
         </is>
       </c>
       <c r="B244" t="n">
-        <v>25225237352</v>
+        <v>26948115800</v>
       </c>
       <c r="C244" t="n">
-        <v>65304111913</v>
+        <v>71129212592</v>
       </c>
       <c r="D244" t="n">
-        <v>0.3862733388918263</v>
+        <v>0.3788614384721994</v>
       </c>
       <c r="E244" t="n">
         <v>243</v>
@@ -5075,17 +5075,17 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>2021-06-17</t>
+          <t>2021-06-24</t>
         </is>
       </c>
       <c r="B245" t="n">
-        <v>23865594042</v>
+        <v>25431794302</v>
       </c>
       <c r="C245" t="n">
-        <v>62073104309</v>
+        <v>68625630748</v>
       </c>
       <c r="D245" t="n">
-        <v>0.3844756003050377</v>
+        <v>0.3705874033477087</v>
       </c>
       <c r="E245" t="n">
         <v>244</v>
@@ -5094,17 +5094,17 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>2021-06-18</t>
+          <t>2021-06-25</t>
         </is>
       </c>
       <c r="B246" t="n">
-        <v>26773348572</v>
+        <v>27857858703</v>
       </c>
       <c r="C246" t="n">
-        <v>68507417006</v>
+        <v>71470857871</v>
       </c>
       <c r="D246" t="n">
-        <v>0.3908094881121433</v>
+        <v>0.3897792685416135</v>
       </c>
       <c r="E246" t="n">
         <v>245</v>
@@ -5113,17 +5113,17 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>2021-06-21</t>
+          <t>2021-06-28</t>
         </is>
       </c>
       <c r="B247" t="n">
-        <v>25810884254</v>
+        <v>25041439447</v>
       </c>
       <c r="C247" t="n">
-        <v>68094480065</v>
+        <v>67772533030</v>
       </c>
       <c r="D247" t="n">
-        <v>0.3790451770740016</v>
+        <v>0.369492452582748</v>
       </c>
       <c r="E247" t="n">
         <v>246</v>
@@ -5132,17 +5132,17 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>2021-06-22</t>
+          <t>2021-06-29</t>
         </is>
       </c>
       <c r="B248" t="n">
-        <v>27325435943</v>
+        <v>23759674387</v>
       </c>
       <c r="C248" t="n">
-        <v>71331165214</v>
+        <v>65504552666</v>
       </c>
       <c r="D248" t="n">
-        <v>0.3830785023772036</v>
+        <v>0.3627179092138493</v>
       </c>
       <c r="E248" t="n">
         <v>247</v>
@@ -5151,17 +5151,17 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>2021-06-23</t>
+          <t>2021-06-30</t>
         </is>
       </c>
       <c r="B249" t="n">
-        <v>26948115800</v>
+        <v>21731079518</v>
       </c>
       <c r="C249" t="n">
-        <v>71129212592</v>
+        <v>60341364451</v>
       </c>
       <c r="D249" t="n">
-        <v>0.3788614384721994</v>
+        <v>0.360135699875442</v>
       </c>
       <c r="E249" t="n">
         <v>248</v>
@@ -5170,17 +5170,17 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>2021-06-24</t>
+          <t>2021-07-01</t>
         </is>
       </c>
       <c r="B250" t="n">
-        <v>25431794302</v>
+        <v>23237110584</v>
       </c>
       <c r="C250" t="n">
-        <v>68625630748</v>
+        <v>66252494627</v>
       </c>
       <c r="D250" t="n">
-        <v>0.3705874033477087</v>
+        <v>0.3507356321422218</v>
       </c>
       <c r="E250" t="n">
         <v>249</v>
@@ -5189,96 +5189,20 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>2021-06-25</t>
+          <t>2021-07-02</t>
         </is>
       </c>
       <c r="B251" t="n">
-        <v>27857858703</v>
+        <v>23485251132</v>
       </c>
       <c r="C251" t="n">
-        <v>71470857871</v>
+        <v>63093845574</v>
       </c>
       <c r="D251" t="n">
-        <v>0.3897792685416135</v>
+        <v>0.3722272896562499</v>
       </c>
       <c r="E251" t="n">
         <v>250</v>
-      </c>
-    </row>
-    <row r="252">
-      <c r="A252" t="inlineStr">
-        <is>
-          <t>2021-06-28</t>
-        </is>
-      </c>
-      <c r="B252" t="n">
-        <v>25041439447</v>
-      </c>
-      <c r="C252" t="n">
-        <v>67772533030</v>
-      </c>
-      <c r="D252" t="n">
-        <v>0.369492452582748</v>
-      </c>
-      <c r="E252" t="n">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="253">
-      <c r="A253" t="inlineStr">
-        <is>
-          <t>2021-06-29</t>
-        </is>
-      </c>
-      <c r="B253" t="n">
-        <v>23759674387</v>
-      </c>
-      <c r="C253" t="n">
-        <v>65504552666</v>
-      </c>
-      <c r="D253" t="n">
-        <v>0.3627179092138493</v>
-      </c>
-      <c r="E253" t="n">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="254">
-      <c r="A254" t="inlineStr">
-        <is>
-          <t>2021-06-30</t>
-        </is>
-      </c>
-      <c r="B254" t="n">
-        <v>21731079518</v>
-      </c>
-      <c r="C254" t="n">
-        <v>60341364451</v>
-      </c>
-      <c r="D254" t="n">
-        <v>0.360135699875442</v>
-      </c>
-      <c r="E254" t="n">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="255">
-      <c r="A255" t="inlineStr">
-        <is>
-          <t>2021-07-01</t>
-        </is>
-      </c>
-      <c r="B255" t="n">
-        <v>23237110584</v>
-      </c>
-      <c r="C255" t="n">
-        <v>66252494627</v>
-      </c>
-      <c r="D255" t="n">
-        <v>0.3507356321422218</v>
-      </c>
-      <c r="E255" t="n">
-        <v>254</v>
       </c>
     </row>
   </sheetData>

--- a/king_index/output/index.xlsx
+++ b/king_index/output/index.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E251"/>
+  <dimension ref="A1:E252"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5205,6 +5205,25 @@
         <v>250</v>
       </c>
     </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>2021-07-05</t>
+        </is>
+      </c>
+      <c r="B252" t="n">
+        <v>24607854588</v>
+      </c>
+      <c r="C252" t="n">
+        <v>63949188580</v>
+      </c>
+      <c r="D252" t="n">
+        <v>0.3848032341679479</v>
+      </c>
+      <c r="E252" t="n">
+        <v>251</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/king_index/output/index.xlsx
+++ b/king_index/output/index.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E252"/>
+  <dimension ref="A1:E253"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5224,6 +5224,25 @@
         <v>251</v>
       </c>
     </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>2021-07-06</t>
+        </is>
+      </c>
+      <c r="B253" t="n">
+        <v>26803155256</v>
+      </c>
+      <c r="C253" t="n">
+        <v>68805538123</v>
+      </c>
+      <c r="D253" t="n">
+        <v>0.3895493878426679</v>
+      </c>
+      <c r="E253" t="n">
+        <v>252</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/king_index/output/index.xlsx
+++ b/king_index/output/index.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E253"/>
+  <dimension ref="A1:E254"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5243,6 +5243,25 @@
         <v>252</v>
       </c>
     </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>2021-07-07</t>
+        </is>
+      </c>
+      <c r="B254" t="n">
+        <v>28008698287</v>
+      </c>
+      <c r="C254" t="n">
+        <v>67984401713</v>
+      </c>
+      <c r="D254" t="n">
+        <v>0.4119871261828604</v>
+      </c>
+      <c r="E254" t="n">
+        <v>253</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/king_index/output/index.xlsx
+++ b/king_index/output/index.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E254"/>
+  <dimension ref="A1:E255"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5262,6 +5262,25 @@
         <v>253</v>
       </c>
     </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>2021-07-08</t>
+        </is>
+      </c>
+      <c r="B255" t="n">
+        <v>30540652959</v>
+      </c>
+      <c r="C255" t="n">
+        <v>76367311906</v>
+      </c>
+      <c r="D255" t="n">
+        <v>0.3999178731941263</v>
+      </c>
+      <c r="E255" t="n">
+        <v>254</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/king_index/output/index.xlsx
+++ b/king_index/output/index.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E255"/>
+  <dimension ref="A1:E239"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -458,17 +458,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2020-06-24</t>
+          <t>2020-07-21</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>19322024502</v>
+        <v>29750727633</v>
       </c>
       <c r="C2" t="n">
-        <v>52926747938</v>
+        <v>82804408460</v>
       </c>
       <c r="D2" t="n">
-        <v>0.3650710700123576</v>
+        <v>0.3592891753749025</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>
@@ -477,17 +477,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2020-06-29</t>
+          <t>2020-07-22</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>20448932009</v>
+        <v>32546369994</v>
       </c>
       <c r="C3" t="n">
-        <v>54347085975</v>
+        <v>88951002081</v>
       </c>
       <c r="D3" t="n">
-        <v>0.3762654729713868</v>
+        <v>0.3658909875389917</v>
       </c>
       <c r="E3" t="n">
         <v>2</v>
@@ -496,17 +496,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2020-06-30</t>
+          <t>2020-07-23</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>20003048931</v>
+        <v>33380341470</v>
       </c>
       <c r="C4" t="n">
-        <v>53946886834</v>
+        <v>92918126099</v>
       </c>
       <c r="D4" t="n">
-        <v>0.3707915341352578</v>
+        <v>0.3592446691664313</v>
       </c>
       <c r="E4" t="n">
         <v>3</v>
@@ -515,17 +515,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2020-07-01</t>
+          <t>2020-07-24</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>25539868441</v>
+        <v>34826858650</v>
       </c>
       <c r="C5" t="n">
-        <v>66477208273</v>
+        <v>98778010270</v>
       </c>
       <c r="D5" t="n">
-        <v>0.3841898464826647</v>
+        <v>0.3525770417404056</v>
       </c>
       <c r="E5" t="n">
         <v>4</v>
@@ -534,17 +534,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2020-07-02</t>
+          <t>2020-07-27</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>35281401239</v>
+        <v>25272101520</v>
       </c>
       <c r="C6" t="n">
-        <v>86277275738</v>
+        <v>69273127708</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4089304041789609</v>
+        <v>0.3648182542951854</v>
       </c>
       <c r="E6" t="n">
         <v>5</v>
@@ -553,17 +553,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2020-07-03</t>
+          <t>2020-07-28</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>39589081860</v>
+        <v>25533477451</v>
       </c>
       <c r="C7" t="n">
-        <v>96590527098</v>
+        <v>67557159363</v>
       </c>
       <c r="D7" t="n">
-        <v>0.4098650566409398</v>
+        <v>0.3779536868002814</v>
       </c>
       <c r="E7" t="n">
         <v>6</v>
@@ -572,17 +572,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2020-07-06</t>
+          <t>2020-07-29</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>51680326902</v>
+        <v>27398207256</v>
       </c>
       <c r="C8" t="n">
-        <v>132721246132</v>
+        <v>75808503607</v>
       </c>
       <c r="D8" t="n">
-        <v>0.3893900065600689</v>
+        <v>0.3614133764997586</v>
       </c>
       <c r="E8" t="n">
         <v>7</v>
@@ -591,17 +591,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2020-07-07</t>
+          <t>2020-07-30</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>54130474812</v>
+        <v>29316097538</v>
       </c>
       <c r="C9" t="n">
-        <v>140540263998</v>
+        <v>80705680370</v>
       </c>
       <c r="D9" t="n">
-        <v>0.3851599055824338</v>
+        <v>0.3632470156201968</v>
       </c>
       <c r="E9" t="n">
         <v>8</v>
@@ -610,17 +610,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2020-07-08</t>
+          <t>2020-07-31</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>48763694238</v>
+        <v>30421341838</v>
       </c>
       <c r="C10" t="n">
-        <v>124820435614</v>
+        <v>83388719271</v>
       </c>
       <c r="D10" t="n">
-        <v>0.3906707583427999</v>
+        <v>0.3648136355126825</v>
       </c>
       <c r="E10" t="n">
         <v>9</v>
@@ -629,17 +629,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2020-07-09</t>
+          <t>2020-08-03</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>50352644938</v>
+        <v>32534419194</v>
       </c>
       <c r="C11" t="n">
-        <v>137276438768</v>
+        <v>97147468049</v>
       </c>
       <c r="D11" t="n">
-        <v>0.3667974299879457</v>
+        <v>0.3348972427937086</v>
       </c>
       <c r="E11" t="n">
         <v>10</v>
@@ -648,17 +648,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2020-07-10</t>
+          <t>2020-08-04</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>45792064703</v>
+        <v>35518548960</v>
       </c>
       <c r="C12" t="n">
-        <v>124540979573</v>
+        <v>100401661483</v>
       </c>
       <c r="D12" t="n">
-        <v>0.3676867233580644</v>
+        <v>0.3537645536474912</v>
       </c>
       <c r="E12" t="n">
         <v>11</v>
@@ -667,17 +667,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2020-07-13</t>
+          <t>2020-08-05</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>45569190970</v>
+        <v>31118752071</v>
       </c>
       <c r="C13" t="n">
-        <v>125874117474</v>
+        <v>88411991123</v>
       </c>
       <c r="D13" t="n">
-        <v>0.3620219301987366</v>
+        <v>0.351974338273947</v>
       </c>
       <c r="E13" t="n">
         <v>12</v>
@@ -686,17 +686,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2020-07-14</t>
+          <t>2020-08-06</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>44404671526</v>
+        <v>35289080996</v>
       </c>
       <c r="C14" t="n">
-        <v>127205292718</v>
+        <v>94484631872</v>
       </c>
       <c r="D14" t="n">
-        <v>0.3490788046409375</v>
+        <v>0.3734901676264849</v>
       </c>
       <c r="E14" t="n">
         <v>13</v>
@@ -705,17 +705,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2020-07-15</t>
+          <t>2020-08-07</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>40948010990</v>
+        <v>33926327226</v>
       </c>
       <c r="C15" t="n">
-        <v>115744357395</v>
+        <v>90977583613</v>
       </c>
       <c r="D15" t="n">
-        <v>0.3537797600815822</v>
+        <v>0.3729086427522151</v>
       </c>
       <c r="E15" t="n">
         <v>14</v>
@@ -724,17 +724,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2020-07-16</t>
+          <t>2020-08-10</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>41327517137</v>
+        <v>29708663069</v>
       </c>
       <c r="C16" t="n">
-        <v>110570972319</v>
+        <v>82942928747</v>
       </c>
       <c r="D16" t="n">
-        <v>0.373764617152584</v>
+        <v>0.3581819875160189</v>
       </c>
       <c r="E16" t="n">
         <v>15</v>
@@ -743,17 +743,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2020-07-17</t>
+          <t>2020-08-11</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>30786629717</v>
+        <v>30946369948</v>
       </c>
       <c r="C17" t="n">
-        <v>83073812068</v>
+        <v>86295092754</v>
       </c>
       <c r="D17" t="n">
-        <v>0.3705936798927636</v>
+        <v>0.3586110051033644</v>
       </c>
       <c r="E17" t="n">
         <v>16</v>
@@ -762,17 +762,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2020-07-20</t>
+          <t>2020-08-12</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>33302406491</v>
+        <v>29856245191</v>
       </c>
       <c r="C18" t="n">
-        <v>90725025902</v>
+        <v>82452473263</v>
       </c>
       <c r="D18" t="n">
-        <v>0.3670696829226903</v>
+        <v>0.3621024817019988</v>
       </c>
       <c r="E18" t="n">
         <v>17</v>
@@ -781,17 +781,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2020-07-21</t>
+          <t>2020-08-13</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>29750727633</v>
+        <v>27823565615</v>
       </c>
       <c r="C19" t="n">
-        <v>82804408460</v>
+        <v>72532322436</v>
       </c>
       <c r="D19" t="n">
-        <v>0.3592891753749025</v>
+        <v>0.3836022986793308</v>
       </c>
       <c r="E19" t="n">
         <v>18</v>
@@ -800,17 +800,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2020-07-22</t>
+          <t>2020-08-14</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>32546369994</v>
+        <v>27261549866</v>
       </c>
       <c r="C20" t="n">
-        <v>88951002081</v>
+        <v>69180221661</v>
       </c>
       <c r="D20" t="n">
-        <v>0.3658909875389917</v>
+        <v>0.3940656622869504</v>
       </c>
       <c r="E20" t="n">
         <v>19</v>
@@ -819,17 +819,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2020-07-23</t>
+          <t>2020-08-17</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>33380341470</v>
+        <v>37118467741</v>
       </c>
       <c r="C21" t="n">
-        <v>92918126099</v>
+        <v>91788369903</v>
       </c>
       <c r="D21" t="n">
-        <v>0.3592446691664313</v>
+        <v>0.4043918394043386</v>
       </c>
       <c r="E21" t="n">
         <v>20</v>
@@ -838,17 +838,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2020-07-24</t>
+          <t>2020-08-18</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>34826858650</v>
+        <v>31325687773</v>
       </c>
       <c r="C22" t="n">
-        <v>98778010270</v>
+        <v>85178317604</v>
       </c>
       <c r="D22" t="n">
-        <v>0.3525770417404056</v>
+        <v>0.3677659838109897</v>
       </c>
       <c r="E22" t="n">
         <v>21</v>
@@ -857,17 +857,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2020-07-27</t>
+          <t>2020-08-19</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>25272101520</v>
+        <v>33073383828</v>
       </c>
       <c r="C23" t="n">
-        <v>69273127708</v>
+        <v>88140275731</v>
       </c>
       <c r="D23" t="n">
-        <v>0.3648182542951854</v>
+        <v>0.375235765417145</v>
       </c>
       <c r="E23" t="n">
         <v>22</v>
@@ -876,17 +876,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2020-07-28</t>
+          <t>2020-08-20</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>25533477451</v>
+        <v>27646953314</v>
       </c>
       <c r="C24" t="n">
-        <v>67557159363</v>
+        <v>72119978332</v>
       </c>
       <c r="D24" t="n">
-        <v>0.3779536868002814</v>
+        <v>0.3833466669489126</v>
       </c>
       <c r="E24" t="n">
         <v>23</v>
@@ -895,17 +895,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2020-07-29</t>
+          <t>2020-08-21</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>27398207256</v>
+        <v>25486130617</v>
       </c>
       <c r="C25" t="n">
-        <v>75808503607</v>
+        <v>66786682396</v>
       </c>
       <c r="D25" t="n">
-        <v>0.3614133764997586</v>
+        <v>0.3816049802546626</v>
       </c>
       <c r="E25" t="n">
         <v>24</v>
@@ -914,17 +914,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2020-07-30</t>
+          <t>2020-08-24</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>29316097538</v>
+        <v>25209284709</v>
       </c>
       <c r="C26" t="n">
-        <v>80705680370</v>
+        <v>67412296336</v>
       </c>
       <c r="D26" t="n">
-        <v>0.3632470156201968</v>
+        <v>0.3739567716748666</v>
       </c>
       <c r="E26" t="n">
         <v>25</v>
@@ -933,17 +933,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2020-07-31</t>
+          <t>2020-08-25</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>30421341838</v>
+        <v>26619247474</v>
       </c>
       <c r="C27" t="n">
-        <v>83388719271</v>
+        <v>73103731924</v>
       </c>
       <c r="D27" t="n">
-        <v>0.3648136355126825</v>
+        <v>0.3641298025889275</v>
       </c>
       <c r="E27" t="n">
         <v>26</v>
@@ -952,17 +952,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2020-08-03</t>
+          <t>2020-08-26</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>32534419194</v>
+        <v>26322908958</v>
       </c>
       <c r="C28" t="n">
-        <v>97147468049</v>
+        <v>75716936591</v>
       </c>
       <c r="D28" t="n">
-        <v>0.3348972427937086</v>
+        <v>0.3476488899727732</v>
       </c>
       <c r="E28" t="n">
         <v>27</v>
@@ -971,17 +971,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2020-08-04</t>
+          <t>2020-08-27</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>35518548960</v>
+        <v>23276018839</v>
       </c>
       <c r="C29" t="n">
-        <v>100401661483</v>
+        <v>65005692955</v>
       </c>
       <c r="D29" t="n">
-        <v>0.3537645536474912</v>
+        <v>0.3580612371152286</v>
       </c>
       <c r="E29" t="n">
         <v>28</v>
@@ -990,17 +990,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2020-08-05</t>
+          <t>2020-08-28</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>31118752071</v>
+        <v>25701039669</v>
       </c>
       <c r="C30" t="n">
-        <v>88411991123</v>
+        <v>70850828969</v>
       </c>
       <c r="D30" t="n">
-        <v>0.351974338273947</v>
+        <v>0.3627486091975749</v>
       </c>
       <c r="E30" t="n">
         <v>29</v>
@@ -1009,17 +1009,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2020-08-06</t>
+          <t>2020-08-31</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>35289080996</v>
+        <v>28573296373</v>
       </c>
       <c r="C31" t="n">
-        <v>94484631872</v>
+        <v>77184652221</v>
       </c>
       <c r="D31" t="n">
-        <v>0.3734901676264849</v>
+        <v>0.3701940159189566</v>
       </c>
       <c r="E31" t="n">
         <v>30</v>
@@ -1028,17 +1028,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2020-08-07</t>
+          <t>2020-09-01</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>33926327226</v>
+        <v>23964180511</v>
       </c>
       <c r="C32" t="n">
-        <v>90977583613</v>
+        <v>64392996012</v>
       </c>
       <c r="D32" t="n">
-        <v>0.3729086427522151</v>
+        <v>0.3721550788929613</v>
       </c>
       <c r="E32" t="n">
         <v>31</v>
@@ -1047,17 +1047,17 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2020-08-10</t>
+          <t>2020-09-02</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>29708663069</v>
+        <v>30082062270</v>
       </c>
       <c r="C33" t="n">
-        <v>82942928747</v>
+        <v>77531927895</v>
       </c>
       <c r="D33" t="n">
-        <v>0.3581819875160189</v>
+        <v>0.3879957984630482</v>
       </c>
       <c r="E33" t="n">
         <v>32</v>
@@ -1066,17 +1066,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2020-08-11</t>
+          <t>2020-09-03</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>30946369948</v>
+        <v>27715216294</v>
       </c>
       <c r="C34" t="n">
-        <v>86295092754</v>
+        <v>73519808249</v>
       </c>
       <c r="D34" t="n">
-        <v>0.3586110051033644</v>
+        <v>0.3769761776327399</v>
       </c>
       <c r="E34" t="n">
         <v>33</v>
@@ -1085,17 +1085,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2020-08-12</t>
+          <t>2020-09-04</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>29856245191</v>
+        <v>24329945914</v>
       </c>
       <c r="C35" t="n">
-        <v>82452473263</v>
+        <v>65573685675</v>
       </c>
       <c r="D35" t="n">
-        <v>0.3621024817019988</v>
+        <v>0.37103215510236</v>
       </c>
       <c r="E35" t="n">
         <v>34</v>
@@ -1104,17 +1104,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2020-08-13</t>
+          <t>2020-09-07</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>27823565615</v>
+        <v>29997390344</v>
       </c>
       <c r="C36" t="n">
-        <v>72532322436</v>
+        <v>79881522723</v>
       </c>
       <c r="D36" t="n">
-        <v>0.3836022986793308</v>
+        <v>0.375523516846568</v>
       </c>
       <c r="E36" t="n">
         <v>35</v>
@@ -1123,17 +1123,17 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2020-08-14</t>
+          <t>2020-09-08</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>27261549866</v>
+        <v>32724062545</v>
       </c>
       <c r="C37" t="n">
-        <v>69180221661</v>
+        <v>80161481426</v>
       </c>
       <c r="D37" t="n">
-        <v>0.3940656622869504</v>
+        <v>0.4082267688030289</v>
       </c>
       <c r="E37" t="n">
         <v>36</v>
@@ -1142,17 +1142,17 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2020-08-17</t>
+          <t>2020-09-09</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>37118467741</v>
+        <v>41720230941</v>
       </c>
       <c r="C38" t="n">
-        <v>91788369903</v>
+        <v>98517765305</v>
       </c>
       <c r="D38" t="n">
-        <v>0.4043918394043386</v>
+        <v>0.4234792660170358</v>
       </c>
       <c r="E38" t="n">
         <v>37</v>
@@ -1161,17 +1161,17 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2020-08-18</t>
+          <t>2020-09-10</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>31325687773</v>
+        <v>32362586075</v>
       </c>
       <c r="C39" t="n">
-        <v>85178317604</v>
+        <v>83938666669</v>
       </c>
       <c r="D39" t="n">
-        <v>0.3677659838109897</v>
+        <v>0.3855503948212232</v>
       </c>
       <c r="E39" t="n">
         <v>38</v>
@@ -1180,17 +1180,17 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2020-08-19</t>
+          <t>2020-09-11</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>33073383828</v>
+        <v>23586290440</v>
       </c>
       <c r="C40" t="n">
-        <v>88140275731</v>
+        <v>60330240577</v>
       </c>
       <c r="D40" t="n">
-        <v>0.375235765417145</v>
+        <v>0.3909530314220547</v>
       </c>
       <c r="E40" t="n">
         <v>39</v>
@@ -1199,17 +1199,17 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2020-08-20</t>
+          <t>2020-09-14</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>27646953314</v>
+        <v>24462170352</v>
       </c>
       <c r="C41" t="n">
-        <v>72119978332</v>
+        <v>63101019998</v>
       </c>
       <c r="D41" t="n">
-        <v>0.3833466669489126</v>
+        <v>0.3876667976646865</v>
       </c>
       <c r="E41" t="n">
         <v>40</v>
@@ -1218,17 +1218,17 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2020-08-21</t>
+          <t>2020-09-15</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>25486130617</v>
+        <v>23106120892</v>
       </c>
       <c r="C42" t="n">
-        <v>66786682396</v>
+        <v>58614407766</v>
       </c>
       <c r="D42" t="n">
-        <v>0.3816049802546626</v>
+        <v>0.3942054824514151</v>
       </c>
       <c r="E42" t="n">
         <v>41</v>
@@ -1237,17 +1237,17 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2020-08-24</t>
+          <t>2020-09-16</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>25209284709</v>
+        <v>21724638649</v>
       </c>
       <c r="C43" t="n">
-        <v>67412296336</v>
+        <v>55182289033</v>
       </c>
       <c r="D43" t="n">
-        <v>0.3739567716748666</v>
+        <v>0.3936886096915674</v>
       </c>
       <c r="E43" t="n">
         <v>42</v>
@@ -1256,17 +1256,17 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2020-08-25</t>
+          <t>2020-09-17</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>26619247474</v>
+        <v>20554994106</v>
       </c>
       <c r="C44" t="n">
-        <v>73103731924</v>
+        <v>55472969929</v>
       </c>
       <c r="D44" t="n">
-        <v>0.3641298025889275</v>
+        <v>0.3705407179804577</v>
       </c>
       <c r="E44" t="n">
         <v>43</v>
@@ -1275,17 +1275,17 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2020-08-26</t>
+          <t>2020-09-18</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>26322908958</v>
+        <v>25018086444</v>
       </c>
       <c r="C45" t="n">
-        <v>75716936591</v>
+        <v>64587549837</v>
       </c>
       <c r="D45" t="n">
-        <v>0.3476488899727732</v>
+        <v>0.3873515330297914</v>
       </c>
       <c r="E45" t="n">
         <v>44</v>
@@ -1294,17 +1294,17 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2020-08-27</t>
+          <t>2020-09-21</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>23276018839</v>
+        <v>22182279260</v>
       </c>
       <c r="C46" t="n">
-        <v>65005692955</v>
+        <v>58098440053</v>
       </c>
       <c r="D46" t="n">
-        <v>0.3580612371152286</v>
+        <v>0.3818050749686968</v>
       </c>
       <c r="E46" t="n">
         <v>45</v>
@@ -1313,17 +1313,17 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2020-08-28</t>
+          <t>2020-09-22</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>25701039669</v>
+        <v>22099090990</v>
       </c>
       <c r="C47" t="n">
-        <v>70850828969</v>
+        <v>56264182474</v>
       </c>
       <c r="D47" t="n">
-        <v>0.3627486091975749</v>
+        <v>0.3927736975510506</v>
       </c>
       <c r="E47" t="n">
         <v>46</v>
@@ -1332,17 +1332,17 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2020-08-31</t>
+          <t>2020-09-23</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>28573296373</v>
+        <v>19077501915</v>
       </c>
       <c r="C48" t="n">
-        <v>77184652221</v>
+        <v>48597940983</v>
       </c>
       <c r="D48" t="n">
-        <v>0.3701940159189566</v>
+        <v>0.3925578230088695</v>
       </c>
       <c r="E48" t="n">
         <v>47</v>
@@ -1351,17 +1351,17 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2020-09-01</t>
+          <t>2020-09-24</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>23964180511</v>
+        <v>20859996043</v>
       </c>
       <c r="C49" t="n">
-        <v>64392996012</v>
+        <v>54861814882</v>
       </c>
       <c r="D49" t="n">
-        <v>0.3721550788929613</v>
+        <v>0.3802279616134993</v>
       </c>
       <c r="E49" t="n">
         <v>48</v>
@@ -1370,17 +1370,17 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2020-09-02</t>
+          <t>2020-09-25</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>30082062270</v>
+        <v>16281719043</v>
       </c>
       <c r="C50" t="n">
-        <v>77531927895</v>
+        <v>43622575116</v>
       </c>
       <c r="D50" t="n">
-        <v>0.3879957984630482</v>
+        <v>0.373240667239476</v>
       </c>
       <c r="E50" t="n">
         <v>49</v>
@@ -1389,17 +1389,17 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2020-09-03</t>
+          <t>2020-09-28</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>27715216294</v>
+        <v>14676583271</v>
       </c>
       <c r="C51" t="n">
-        <v>73519808249</v>
+        <v>40556797589</v>
       </c>
       <c r="D51" t="n">
-        <v>0.3769761776327399</v>
+        <v>0.3618772719614492</v>
       </c>
       <c r="E51" t="n">
         <v>50</v>
@@ -1408,17 +1408,17 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2020-09-04</t>
+          <t>2020-09-29</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>24329945914</v>
+        <v>14442107257</v>
       </c>
       <c r="C52" t="n">
-        <v>65573685675</v>
+        <v>40163621965</v>
       </c>
       <c r="D52" t="n">
-        <v>0.37103215510236</v>
+        <v>0.3595817944304267</v>
       </c>
       <c r="E52" t="n">
         <v>51</v>
@@ -1427,17 +1427,17 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2020-09-07</t>
+          <t>2020-09-30</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>29997390344</v>
+        <v>15066784297</v>
       </c>
       <c r="C53" t="n">
-        <v>79881522723</v>
+        <v>40300843448</v>
       </c>
       <c r="D53" t="n">
-        <v>0.375523516846568</v>
+        <v>0.3738577907541961</v>
       </c>
       <c r="E53" t="n">
         <v>52</v>
@@ -1446,17 +1446,17 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2020-09-08</t>
+          <t>2020-10-09</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>32724062545</v>
+        <v>18363804782</v>
       </c>
       <c r="C54" t="n">
-        <v>80161481426</v>
+        <v>50410563994</v>
       </c>
       <c r="D54" t="n">
-        <v>0.4082267688030289</v>
+        <v>0.3642848507742486</v>
       </c>
       <c r="E54" t="n">
         <v>53</v>
@@ -1465,17 +1465,17 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2020-09-09</t>
+          <t>2020-10-12</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>41720230941</v>
+        <v>24824121596</v>
       </c>
       <c r="C55" t="n">
-        <v>98517765305</v>
+        <v>69075123930</v>
       </c>
       <c r="D55" t="n">
-        <v>0.4234792660170358</v>
+        <v>0.3593786038104905</v>
       </c>
       <c r="E55" t="n">
         <v>54</v>
@@ -1484,17 +1484,17 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2020-09-10</t>
+          <t>2020-10-13</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>32362586075</v>
+        <v>21950874234</v>
       </c>
       <c r="C56" t="n">
-        <v>83938666669</v>
+        <v>58435290007</v>
       </c>
       <c r="D56" t="n">
-        <v>0.3855503948212232</v>
+        <v>0.3756441395494142</v>
       </c>
       <c r="E56" t="n">
         <v>55</v>
@@ -1503,17 +1503,17 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2020-09-11</t>
+          <t>2020-10-14</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>23586290440</v>
+        <v>21810988673</v>
       </c>
       <c r="C57" t="n">
-        <v>60330240577</v>
+        <v>58022364557</v>
       </c>
       <c r="D57" t="n">
-        <v>0.3909530314220547</v>
+        <v>0.3759065808421738</v>
       </c>
       <c r="E57" t="n">
         <v>56</v>
@@ -1522,17 +1522,17 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2020-09-14</t>
+          <t>2020-10-15</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>24462170352</v>
+        <v>20410751440</v>
       </c>
       <c r="C58" t="n">
-        <v>63101019998</v>
+        <v>54415224691</v>
       </c>
       <c r="D58" t="n">
-        <v>0.3876667976646865</v>
+        <v>0.3750926612157467</v>
       </c>
       <c r="E58" t="n">
         <v>57</v>
@@ -1541,17 +1541,17 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2020-09-15</t>
+          <t>2020-10-16</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>23106120892</v>
+        <v>19779199722</v>
       </c>
       <c r="C59" t="n">
-        <v>58614407766</v>
+        <v>51552706029</v>
       </c>
       <c r="D59" t="n">
-        <v>0.3942054824514151</v>
+        <v>0.3836694762613156</v>
       </c>
       <c r="E59" t="n">
         <v>58</v>
@@ -1560,17 +1560,17 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2020-09-16</t>
+          <t>2020-10-19</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>21724638649</v>
+        <v>20562725471</v>
       </c>
       <c r="C60" t="n">
-        <v>55182289033</v>
+        <v>53895497648</v>
       </c>
       <c r="D60" t="n">
-        <v>0.3936886096915674</v>
+        <v>0.3815295593947087</v>
       </c>
       <c r="E60" t="n">
         <v>59</v>
@@ -1579,17 +1579,17 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2020-09-17</t>
+          <t>2020-10-20</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>20554994106</v>
+        <v>18296672779</v>
       </c>
       <c r="C61" t="n">
-        <v>55472969929</v>
+        <v>47922773316</v>
       </c>
       <c r="D61" t="n">
-        <v>0.3705407179804577</v>
+        <v>0.3817949486844761</v>
       </c>
       <c r="E61" t="n">
         <v>60</v>
@@ -1598,17 +1598,17 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2020-09-18</t>
+          <t>2020-10-21</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>25018086444</v>
+        <v>18370049664</v>
       </c>
       <c r="C62" t="n">
-        <v>64587549837</v>
+        <v>49307563396</v>
       </c>
       <c r="D62" t="n">
-        <v>0.3873515330297914</v>
+        <v>0.3725604836009853</v>
       </c>
       <c r="E62" t="n">
         <v>61</v>
@@ -1617,17 +1617,17 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2020-09-21</t>
+          <t>2020-10-22</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>22182279260</v>
+        <v>17665602844</v>
       </c>
       <c r="C63" t="n">
-        <v>58098440053</v>
+        <v>46460364776</v>
       </c>
       <c r="D63" t="n">
-        <v>0.3818050749686968</v>
+        <v>0.3802295339085566</v>
       </c>
       <c r="E63" t="n">
         <v>62</v>
@@ -1636,17 +1636,17 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2020-09-22</t>
+          <t>2020-10-23</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>22099090990</v>
+        <v>17466910909</v>
       </c>
       <c r="C64" t="n">
-        <v>56264182474</v>
+        <v>47398504650</v>
       </c>
       <c r="D64" t="n">
-        <v>0.3927736975510506</v>
+        <v>0.3685118557637873</v>
       </c>
       <c r="E64" t="n">
         <v>63</v>
@@ -1655,17 +1655,17 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2020-09-23</t>
+          <t>2020-10-26</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>19077501915</v>
+        <v>16145407434</v>
       </c>
       <c r="C65" t="n">
-        <v>48597940983</v>
+        <v>44150494774</v>
       </c>
       <c r="D65" t="n">
-        <v>0.3925578230088695</v>
+        <v>0.3656902944496094</v>
       </c>
       <c r="E65" t="n">
         <v>64</v>
@@ -1674,17 +1674,17 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2020-09-24</t>
+          <t>2020-10-27</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>20859996043</v>
+        <v>15491813981</v>
       </c>
       <c r="C66" t="n">
-        <v>54861814882</v>
+        <v>43505082864</v>
       </c>
       <c r="D66" t="n">
-        <v>0.3802279616134993</v>
+        <v>0.356092046288672</v>
       </c>
       <c r="E66" t="n">
         <v>65</v>
@@ -1693,17 +1693,17 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2020-09-25</t>
+          <t>2020-10-28</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>16281719043</v>
+        <v>17543172634</v>
       </c>
       <c r="C67" t="n">
-        <v>43622575116</v>
+        <v>49485508785</v>
       </c>
       <c r="D67" t="n">
-        <v>0.373240667239476</v>
+        <v>0.3545113117906887</v>
       </c>
       <c r="E67" t="n">
         <v>66</v>
@@ -1712,17 +1712,17 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2020-09-28</t>
+          <t>2020-10-29</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>14676583271</v>
+        <v>18553392322</v>
       </c>
       <c r="C68" t="n">
-        <v>40556797589</v>
+        <v>51689467398</v>
       </c>
       <c r="D68" t="n">
-        <v>0.3618772719614492</v>
+        <v>0.3589395142948963</v>
       </c>
       <c r="E68" t="n">
         <v>67</v>
@@ -1731,17 +1731,17 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2020-09-29</t>
+          <t>2020-10-30</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>14442107257</v>
+        <v>20650226596</v>
       </c>
       <c r="C69" t="n">
-        <v>40163621965</v>
+        <v>60348197366</v>
       </c>
       <c r="D69" t="n">
-        <v>0.3595817944304267</v>
+        <v>0.3421846467220954</v>
       </c>
       <c r="E69" t="n">
         <v>68</v>
@@ -1750,17 +1750,17 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2020-09-30</t>
+          <t>2020-11-02</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>15066784297</v>
+        <v>19992661394</v>
       </c>
       <c r="C70" t="n">
-        <v>40300843448</v>
+        <v>56353918211</v>
       </c>
       <c r="D70" t="n">
-        <v>0.3738577907541961</v>
+        <v>0.3547696775784711</v>
       </c>
       <c r="E70" t="n">
         <v>69</v>
@@ -1769,17 +1769,17 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2020-10-09</t>
+          <t>2020-11-03</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>18363804782</v>
+        <v>20249408150</v>
       </c>
       <c r="C71" t="n">
-        <v>50410563994</v>
+        <v>55344378404</v>
       </c>
       <c r="D71" t="n">
-        <v>0.3642848507742486</v>
+        <v>0.365880126111173</v>
       </c>
       <c r="E71" t="n">
         <v>70</v>
@@ -1788,17 +1788,17 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2020-10-12</t>
+          <t>2020-11-04</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>24824121596</v>
+        <v>18257580496</v>
       </c>
       <c r="C72" t="n">
-        <v>69075123930</v>
+        <v>49909415865</v>
       </c>
       <c r="D72" t="n">
-        <v>0.3593786038104905</v>
+        <v>0.3658143494483073</v>
       </c>
       <c r="E72" t="n">
         <v>71</v>
@@ -1807,17 +1807,17 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2020-10-13</t>
+          <t>2020-11-05</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>21950874234</v>
+        <v>21285267389</v>
       </c>
       <c r="C73" t="n">
-        <v>58435290007</v>
+        <v>58980118835</v>
       </c>
       <c r="D73" t="n">
-        <v>0.3756441395494142</v>
+        <v>0.3608888522002924</v>
       </c>
       <c r="E73" t="n">
         <v>72</v>
@@ -1826,17 +1826,17 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2020-10-14</t>
+          <t>2020-11-06</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>21810988673</v>
+        <v>23071856412</v>
       </c>
       <c r="C74" t="n">
-        <v>58022364557</v>
+        <v>59902082650</v>
       </c>
       <c r="D74" t="n">
-        <v>0.3759065808421738</v>
+        <v>0.3851595034984981</v>
       </c>
       <c r="E74" t="n">
         <v>73</v>
@@ -1845,17 +1845,17 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2020-10-15</t>
+          <t>2020-11-09</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>20410751440</v>
+        <v>27202863336</v>
       </c>
       <c r="C75" t="n">
-        <v>54415224691</v>
+        <v>74478178320</v>
       </c>
       <c r="D75" t="n">
-        <v>0.3750926612157467</v>
+        <v>0.3652460888492902</v>
       </c>
       <c r="E75" t="n">
         <v>74</v>
@@ -1864,17 +1864,17 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2020-10-16</t>
+          <t>2020-11-10</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>19779199722</v>
+        <v>25309810082</v>
       </c>
       <c r="C76" t="n">
-        <v>51552706029</v>
+        <v>67090114044</v>
       </c>
       <c r="D76" t="n">
-        <v>0.3836694762613156</v>
+        <v>0.3772509622714452</v>
       </c>
       <c r="E76" t="n">
         <v>75</v>
@@ -1883,17 +1883,17 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2020-10-19</t>
+          <t>2020-11-11</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>20562725471</v>
+        <v>23822441228</v>
       </c>
       <c r="C77" t="n">
-        <v>53895497648</v>
+        <v>61988411650</v>
       </c>
       <c r="D77" t="n">
-        <v>0.3815295593947087</v>
+        <v>0.3843047529997488</v>
       </c>
       <c r="E77" t="n">
         <v>76</v>
@@ -1902,17 +1902,17 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2020-10-20</t>
+          <t>2020-11-12</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>18296672779</v>
+        <v>19076439758</v>
       </c>
       <c r="C78" t="n">
-        <v>47922773316</v>
+        <v>51703999860</v>
       </c>
       <c r="D78" t="n">
-        <v>0.3817949486844761</v>
+        <v>0.3689548160616911</v>
       </c>
       <c r="E78" t="n">
         <v>77</v>
@@ -1921,17 +1921,17 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2020-10-21</t>
+          <t>2020-11-13</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>18370049664</v>
+        <v>20119982649</v>
       </c>
       <c r="C79" t="n">
-        <v>49307563396</v>
+        <v>52210418675</v>
       </c>
       <c r="D79" t="n">
-        <v>0.3725604836009853</v>
+        <v>0.3853633653896379</v>
       </c>
       <c r="E79" t="n">
         <v>78</v>
@@ -1940,17 +1940,17 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2020-10-22</t>
+          <t>2020-11-16</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>17665602844</v>
+        <v>23217241543</v>
       </c>
       <c r="C80" t="n">
-        <v>46460364776</v>
+        <v>61350411349</v>
       </c>
       <c r="D80" t="n">
-        <v>0.3802295339085566</v>
+        <v>0.3784366075546849</v>
       </c>
       <c r="E80" t="n">
         <v>79</v>
@@ -1959,17 +1959,17 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2020-10-23</t>
+          <t>2020-11-17</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>17466910909</v>
+        <v>24335506367</v>
       </c>
       <c r="C81" t="n">
-        <v>47398504650</v>
+        <v>64241703103</v>
       </c>
       <c r="D81" t="n">
-        <v>0.3685118557637873</v>
+        <v>0.3788116626980203</v>
       </c>
       <c r="E81" t="n">
         <v>80</v>
@@ -1978,17 +1978,17 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2020-10-26</t>
+          <t>2020-11-18</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>16145407434</v>
+        <v>25490702717</v>
       </c>
       <c r="C82" t="n">
-        <v>44150494774</v>
+        <v>63205463709</v>
       </c>
       <c r="D82" t="n">
-        <v>0.3656902944496094</v>
+        <v>0.4032990381078449</v>
       </c>
       <c r="E82" t="n">
         <v>81</v>
@@ -1997,17 +1997,17 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2020-10-27</t>
+          <t>2020-11-19</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>15491813981</v>
+        <v>23177522765</v>
       </c>
       <c r="C83" t="n">
-        <v>43505082864</v>
+        <v>59756276020</v>
       </c>
       <c r="D83" t="n">
-        <v>0.356092046288672</v>
+        <v>0.3878675899623104</v>
       </c>
       <c r="E83" t="n">
         <v>82</v>
@@ -2016,17 +2016,17 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2020-10-28</t>
+          <t>2020-11-20</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>17543172634</v>
+        <v>22935620159</v>
       </c>
       <c r="C84" t="n">
-        <v>49485508785</v>
+        <v>58875754449</v>
       </c>
       <c r="D84" t="n">
-        <v>0.3545113117906887</v>
+        <v>0.3895596816320637</v>
       </c>
       <c r="E84" t="n">
         <v>83</v>
@@ -2035,17 +2035,17 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2020-10-29</t>
+          <t>2020-11-23</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>18553392322</v>
+        <v>32096579820</v>
       </c>
       <c r="C85" t="n">
-        <v>51689467398</v>
+        <v>77198006469</v>
       </c>
       <c r="D85" t="n">
-        <v>0.3589395142948963</v>
+        <v>0.4157695423506675</v>
       </c>
       <c r="E85" t="n">
         <v>84</v>
@@ -2054,17 +2054,17 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2020-10-30</t>
+          <t>2020-11-24</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>20650226596</v>
+        <v>26709718473</v>
       </c>
       <c r="C86" t="n">
-        <v>60348197366</v>
+        <v>65410116144</v>
       </c>
       <c r="D86" t="n">
-        <v>0.3421846467220954</v>
+        <v>0.408342318399171</v>
       </c>
       <c r="E86" t="n">
         <v>85</v>
@@ -2073,17 +2073,17 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2020-11-02</t>
+          <t>2020-11-25</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>19992661394</v>
+        <v>27089790866</v>
       </c>
       <c r="C87" t="n">
-        <v>56353918211</v>
+        <v>68837443765</v>
       </c>
       <c r="D87" t="n">
-        <v>0.3547696775784711</v>
+        <v>0.3935327836762824</v>
       </c>
       <c r="E87" t="n">
         <v>86</v>
@@ -2092,17 +2092,17 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2020-11-03</t>
+          <t>2020-11-26</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>20249408150</v>
+        <v>21689088930</v>
       </c>
       <c r="C88" t="n">
-        <v>55344378404</v>
+        <v>57127013421</v>
       </c>
       <c r="D88" t="n">
-        <v>0.365880126111173</v>
+        <v>0.3796643239540867</v>
       </c>
       <c r="E88" t="n">
         <v>87</v>
@@ -2111,17 +2111,17 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2020-11-04</t>
+          <t>2020-11-27</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>18257580496</v>
+        <v>23626364341</v>
       </c>
       <c r="C89" t="n">
-        <v>49909415865</v>
+        <v>58765160877</v>
       </c>
       <c r="D89" t="n">
-        <v>0.3658143494483073</v>
+        <v>0.4020471311301572</v>
       </c>
       <c r="E89" t="n">
         <v>88</v>
@@ -2130,17 +2130,17 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2020-11-05</t>
+          <t>2020-11-30</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>21285267389</v>
+        <v>33970232252</v>
       </c>
       <c r="C90" t="n">
-        <v>58980118835</v>
+        <v>75092505579</v>
       </c>
       <c r="D90" t="n">
-        <v>0.3608888522002924</v>
+        <v>0.4523784629381171</v>
       </c>
       <c r="E90" t="n">
         <v>89</v>
@@ -2149,17 +2149,17 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2020-11-06</t>
+          <t>2020-12-01</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>23071856412</v>
+        <v>28738868941</v>
       </c>
       <c r="C91" t="n">
-        <v>59902082650</v>
+        <v>67936162045</v>
       </c>
       <c r="D91" t="n">
-        <v>0.3851595034984981</v>
+        <v>0.4230275611089682</v>
       </c>
       <c r="E91" t="n">
         <v>90</v>
@@ -2168,17 +2168,17 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2020-11-09</t>
+          <t>2020-12-02</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>27202863336</v>
+        <v>28928357564</v>
       </c>
       <c r="C92" t="n">
-        <v>74478178320</v>
+        <v>69689843826</v>
       </c>
       <c r="D92" t="n">
-        <v>0.3652460888492902</v>
+        <v>0.4151014835996427</v>
       </c>
       <c r="E92" t="n">
         <v>91</v>
@@ -2187,17 +2187,17 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2020-11-10</t>
+          <t>2020-12-03</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>25309810082</v>
+        <v>28497726227</v>
       </c>
       <c r="C93" t="n">
-        <v>67090114044</v>
+        <v>66950741850</v>
       </c>
       <c r="D93" t="n">
-        <v>0.3772509622714452</v>
+        <v>0.4256521352795137</v>
       </c>
       <c r="E93" t="n">
         <v>92</v>
@@ -2206,17 +2206,17 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2020-11-11</t>
+          <t>2020-12-04</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>23822441228</v>
+        <v>23614518756</v>
       </c>
       <c r="C94" t="n">
-        <v>61988411650</v>
+        <v>57124426015</v>
       </c>
       <c r="D94" t="n">
-        <v>0.3843047529997488</v>
+        <v>0.4133874141649876</v>
       </c>
       <c r="E94" t="n">
         <v>93</v>
@@ -2225,17 +2225,17 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2020-11-12</t>
+          <t>2020-12-07</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>19076439758</v>
+        <v>22345056458</v>
       </c>
       <c r="C95" t="n">
-        <v>51703999860</v>
+        <v>56856559648</v>
       </c>
       <c r="D95" t="n">
-        <v>0.3689548160616911</v>
+        <v>0.3930075367967857</v>
       </c>
       <c r="E95" t="n">
         <v>94</v>
@@ -2244,17 +2244,17 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2020-11-13</t>
+          <t>2020-12-08</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>20119982649</v>
+        <v>20555717183</v>
       </c>
       <c r="C96" t="n">
-        <v>52210418675</v>
+        <v>51665831943</v>
       </c>
       <c r="D96" t="n">
-        <v>0.3853633653896379</v>
+        <v>0.3978590184259099</v>
       </c>
       <c r="E96" t="n">
         <v>95</v>
@@ -2263,17 +2263,17 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2020-11-16</t>
+          <t>2020-12-09</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>23217241543</v>
+        <v>22167887887</v>
       </c>
       <c r="C97" t="n">
-        <v>61350411349</v>
+        <v>59426788696</v>
       </c>
       <c r="D97" t="n">
-        <v>0.3784366075546849</v>
+        <v>0.3730285343265085</v>
       </c>
       <c r="E97" t="n">
         <v>96</v>
@@ -2282,17 +2282,17 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2020-11-17</t>
+          <t>2020-12-10</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>24335506367</v>
+        <v>21008686040</v>
       </c>
       <c r="C98" t="n">
-        <v>64241703103</v>
+        <v>53530291688</v>
       </c>
       <c r="D98" t="n">
-        <v>0.3788116626980203</v>
+        <v>0.3924635076238444</v>
       </c>
       <c r="E98" t="n">
         <v>97</v>
@@ -2301,17 +2301,17 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2020-11-18</t>
+          <t>2020-12-11</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>25490702717</v>
+        <v>24084146686</v>
       </c>
       <c r="C99" t="n">
-        <v>63205463709</v>
+        <v>64194443337</v>
       </c>
       <c r="D99" t="n">
-        <v>0.4032990381078449</v>
+        <v>0.3751749440300626</v>
       </c>
       <c r="E99" t="n">
         <v>98</v>
@@ -2320,17 +2320,17 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2020-11-19</t>
+          <t>2020-12-14</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>23177522765</v>
+        <v>20561369384</v>
       </c>
       <c r="C100" t="n">
-        <v>59756276020</v>
+        <v>52737085483</v>
       </c>
       <c r="D100" t="n">
-        <v>0.3878675899623104</v>
+        <v>0.3898844465082932</v>
       </c>
       <c r="E100" t="n">
         <v>99</v>
@@ -2339,17 +2339,17 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2020-11-20</t>
+          <t>2020-12-15</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>22935620159</v>
+        <v>20518702233</v>
       </c>
       <c r="C101" t="n">
-        <v>58875754449</v>
+        <v>50712282528</v>
       </c>
       <c r="D101" t="n">
-        <v>0.3895596816320637</v>
+        <v>0.4046101104139991</v>
       </c>
       <c r="E101" t="n">
         <v>100</v>
@@ -2358,17 +2358,17 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2020-11-23</t>
+          <t>2020-12-16</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>32096579820</v>
+        <v>20098821894</v>
       </c>
       <c r="C102" t="n">
-        <v>77198006469</v>
+        <v>51594471274</v>
       </c>
       <c r="D102" t="n">
-        <v>0.4157695423506675</v>
+        <v>0.3895537912824469</v>
       </c>
       <c r="E102" t="n">
         <v>101</v>
@@ -2377,17 +2377,17 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2020-11-24</t>
+          <t>2020-12-17</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>26709718473</v>
+        <v>23623180829</v>
       </c>
       <c r="C103" t="n">
-        <v>65410116144</v>
+        <v>60346809075</v>
       </c>
       <c r="D103" t="n">
-        <v>0.408342318399171</v>
+        <v>0.3914569998165226</v>
       </c>
       <c r="E103" t="n">
         <v>102</v>
@@ -2396,17 +2396,17 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2020-11-25</t>
+          <t>2020-12-18</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>27089790866</v>
+        <v>24395319589</v>
       </c>
       <c r="C104" t="n">
-        <v>68837443765</v>
+        <v>59011526731</v>
       </c>
       <c r="D104" t="n">
-        <v>0.3935327836762824</v>
+        <v>0.4133992279204094</v>
       </c>
       <c r="E104" t="n">
         <v>103</v>
@@ -2415,17 +2415,17 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2020-11-26</t>
+          <t>2020-12-21</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>21689088930</v>
+        <v>25669905456</v>
       </c>
       <c r="C105" t="n">
-        <v>57127013421</v>
+        <v>62473191028</v>
       </c>
       <c r="D105" t="n">
-        <v>0.3796643239540867</v>
+        <v>0.410894737944392</v>
       </c>
       <c r="E105" t="n">
         <v>104</v>
@@ -2434,17 +2434,17 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2020-11-27</t>
+          <t>2020-12-22</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>23626364341</v>
+        <v>27752409533</v>
       </c>
       <c r="C106" t="n">
-        <v>58765160877</v>
+        <v>70592976908</v>
       </c>
       <c r="D106" t="n">
-        <v>0.4020471311301572</v>
+        <v>0.3931327271998773</v>
       </c>
       <c r="E106" t="n">
         <v>105</v>
@@ -2453,17 +2453,17 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2020-11-30</t>
+          <t>2020-12-23</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>33970232252</v>
+        <v>26781996550</v>
       </c>
       <c r="C107" t="n">
-        <v>75092505579</v>
+        <v>66516491988</v>
       </c>
       <c r="D107" t="n">
-        <v>0.4523784629381171</v>
+        <v>0.4026369363380084</v>
       </c>
       <c r="E107" t="n">
         <v>106</v>
@@ -2472,17 +2472,17 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2020-12-01</t>
+          <t>2020-12-24</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>28738868941</v>
+        <v>23869444669</v>
       </c>
       <c r="C108" t="n">
-        <v>67936162045</v>
+        <v>63015856260</v>
       </c>
       <c r="D108" t="n">
-        <v>0.4230275611089682</v>
+        <v>0.3787847390427572</v>
       </c>
       <c r="E108" t="n">
         <v>107</v>
@@ -2491,17 +2491,17 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2020-12-02</t>
+          <t>2020-12-25</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>28928357564</v>
+        <v>25870374333</v>
       </c>
       <c r="C109" t="n">
-        <v>69689843826</v>
+        <v>63035613181</v>
       </c>
       <c r="D109" t="n">
-        <v>0.4151014835996427</v>
+        <v>0.4104088629822002</v>
       </c>
       <c r="E109" t="n">
         <v>108</v>
@@ -2510,17 +2510,17 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2020-12-03</t>
+          <t>2020-12-28</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>28497726227</v>
+        <v>27591719605</v>
       </c>
       <c r="C110" t="n">
-        <v>66950741850</v>
+        <v>68634054637</v>
       </c>
       <c r="D110" t="n">
-        <v>0.4256521352795137</v>
+        <v>0.4020120878903394</v>
       </c>
       <c r="E110" t="n">
         <v>109</v>
@@ -2529,17 +2529,17 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2020-12-04</t>
+          <t>2020-12-29</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>23614518756</v>
+        <v>28714767727</v>
       </c>
       <c r="C111" t="n">
-        <v>57124426015</v>
+        <v>68080937199</v>
       </c>
       <c r="D111" t="n">
-        <v>0.4133874141649876</v>
+        <v>0.4217739782733451</v>
       </c>
       <c r="E111" t="n">
         <v>110</v>
@@ -2548,17 +2548,17 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2020-12-07</t>
+          <t>2020-12-30</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>22345056458</v>
+        <v>27431057672</v>
       </c>
       <c r="C112" t="n">
-        <v>56856559648</v>
+        <v>63970764234</v>
       </c>
       <c r="D112" t="n">
-        <v>0.3930075367967857</v>
+        <v>0.4288061585704895</v>
       </c>
       <c r="E112" t="n">
         <v>111</v>
@@ -2567,17 +2567,17 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2020-12-08</t>
+          <t>2020-12-31</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>20555717183</v>
+        <v>29516497306</v>
       </c>
       <c r="C113" t="n">
-        <v>51665831943</v>
+        <v>70483427194</v>
       </c>
       <c r="D113" t="n">
-        <v>0.3978590184259099</v>
+        <v>0.4187721636287379</v>
       </c>
       <c r="E113" t="n">
         <v>112</v>
@@ -2586,17 +2586,17 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2020-12-09</t>
+          <t>2021-01-04</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>22167887887</v>
+        <v>32842910849</v>
       </c>
       <c r="C114" t="n">
-        <v>59426788696</v>
+        <v>81262611004</v>
       </c>
       <c r="D114" t="n">
-        <v>0.3730285343265085</v>
+        <v>0.4041577109475767</v>
       </c>
       <c r="E114" t="n">
         <v>113</v>
@@ -2605,17 +2605,17 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2020-12-10</t>
+          <t>2021-01-05</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>21008686040</v>
+        <v>34955476638</v>
       </c>
       <c r="C115" t="n">
-        <v>53530291688</v>
+        <v>86306603527</v>
       </c>
       <c r="D115" t="n">
-        <v>0.3924635076238444</v>
+        <v>0.4050150881799513</v>
       </c>
       <c r="E115" t="n">
         <v>114</v>
@@ -2624,17 +2624,17 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2020-12-11</t>
+          <t>2021-01-06</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>24084146686</v>
+        <v>31318863380</v>
       </c>
       <c r="C116" t="n">
-        <v>64194443337</v>
+        <v>79924024318</v>
       </c>
       <c r="D116" t="n">
-        <v>0.3751749440300626</v>
+        <v>0.3918579381762507</v>
       </c>
       <c r="E116" t="n">
         <v>115</v>
@@ -2643,17 +2643,17 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2020-12-14</t>
+          <t>2021-01-07</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>20561369384</v>
+        <v>34820241307</v>
       </c>
       <c r="C117" t="n">
-        <v>52737085483</v>
+        <v>87045282583</v>
       </c>
       <c r="D117" t="n">
-        <v>0.3898844465082932</v>
+        <v>0.4000244501911746</v>
       </c>
       <c r="E117" t="n">
         <v>116</v>
@@ -2662,17 +2662,17 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2020-12-15</t>
+          <t>2021-01-08</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>20518702233</v>
+        <v>31741361539</v>
       </c>
       <c r="C118" t="n">
-        <v>50712282528</v>
+        <v>76243328872</v>
       </c>
       <c r="D118" t="n">
-        <v>0.4046101104139991</v>
+        <v>0.4163165749529185</v>
       </c>
       <c r="E118" t="n">
         <v>117</v>
@@ -2681,17 +2681,17 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2020-12-16</t>
+          <t>2021-01-11</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>20098821894</v>
+        <v>33861909952</v>
       </c>
       <c r="C119" t="n">
-        <v>51594471274</v>
+        <v>79843929989</v>
       </c>
       <c r="D119" t="n">
-        <v>0.3895537912824469</v>
+        <v>0.4241012429706943</v>
       </c>
       <c r="E119" t="n">
         <v>118</v>
@@ -2700,17 +2700,17 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2020-12-17</t>
+          <t>2021-01-12</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>23623180829</v>
+        <v>31336739617</v>
       </c>
       <c r="C120" t="n">
-        <v>60346809075</v>
+        <v>70684174141</v>
       </c>
       <c r="D120" t="n">
-        <v>0.3914569998165226</v>
+        <v>0.4433345936035105</v>
       </c>
       <c r="E120" t="n">
         <v>119</v>
@@ -2719,17 +2719,17 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2020-12-18</t>
+          <t>2021-01-13</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>24395319589</v>
+        <v>36176556832</v>
       </c>
       <c r="C121" t="n">
-        <v>59011526731</v>
+        <v>81782457644</v>
       </c>
       <c r="D121" t="n">
-        <v>0.4133992279204094</v>
+        <v>0.4423510600461162</v>
       </c>
       <c r="E121" t="n">
         <v>120</v>
@@ -2738,17 +2738,17 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2020-12-21</t>
+          <t>2021-01-14</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>25669905456</v>
+        <v>32971296424</v>
       </c>
       <c r="C122" t="n">
-        <v>62473191028</v>
+        <v>74034016193</v>
       </c>
       <c r="D122" t="n">
-        <v>0.410894737944392</v>
+        <v>0.4453533405245341</v>
       </c>
       <c r="E122" t="n">
         <v>121</v>
@@ -2757,17 +2757,17 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2020-12-22</t>
+          <t>2021-01-15</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>27752409533</v>
+        <v>31268748151</v>
       </c>
       <c r="C123" t="n">
-        <v>70592976908</v>
+        <v>68522530970</v>
       </c>
       <c r="D123" t="n">
-        <v>0.3931327271998773</v>
+        <v>0.4563279801309417</v>
       </c>
       <c r="E123" t="n">
         <v>122</v>
@@ -2776,17 +2776,17 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2020-12-23</t>
+          <t>2021-01-18</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>26781996550</v>
+        <v>28025154838</v>
       </c>
       <c r="C124" t="n">
-        <v>66516491988</v>
+        <v>66132336803</v>
       </c>
       <c r="D124" t="n">
-        <v>0.4026369363380084</v>
+        <v>0.4237738479056539</v>
       </c>
       <c r="E124" t="n">
         <v>123</v>
@@ -2795,17 +2795,17 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2020-12-24</t>
+          <t>2021-01-19</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>23869444669</v>
+        <v>30160755219</v>
       </c>
       <c r="C125" t="n">
-        <v>63015856260</v>
+        <v>71588657610</v>
       </c>
       <c r="D125" t="n">
-        <v>0.3787847390427572</v>
+        <v>0.4213063385447102</v>
       </c>
       <c r="E125" t="n">
         <v>124</v>
@@ -2814,17 +2814,17 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2020-12-25</t>
+          <t>2021-01-20</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>25870374333</v>
+        <v>25498108632</v>
       </c>
       <c r="C126" t="n">
-        <v>63035613181</v>
+        <v>61023142374</v>
       </c>
       <c r="D126" t="n">
-        <v>0.4104088629822002</v>
+        <v>0.4178432581483041</v>
       </c>
       <c r="E126" t="n">
         <v>125</v>
@@ -2833,17 +2833,17 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2020-12-28</t>
+          <t>2021-01-21</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>27591719605</v>
+        <v>31550851527</v>
       </c>
       <c r="C127" t="n">
-        <v>68634054637</v>
+        <v>73606094304</v>
       </c>
       <c r="D127" t="n">
-        <v>0.4020120878903394</v>
+        <v>0.4286445548474839</v>
       </c>
       <c r="E127" t="n">
         <v>126</v>
@@ -2852,17 +2852,17 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2020-12-29</t>
+          <t>2021-01-22</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>28714767727</v>
+        <v>29587073243</v>
       </c>
       <c r="C128" t="n">
-        <v>68080937199</v>
+        <v>71863919964</v>
       </c>
       <c r="D128" t="n">
-        <v>0.4217739782733451</v>
+        <v>0.4117097043665521</v>
       </c>
       <c r="E128" t="n">
         <v>127</v>
@@ -2871,17 +2871,17 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2020-12-30</t>
+          <t>2021-01-25</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>27431057672</v>
+        <v>29768085597</v>
       </c>
       <c r="C129" t="n">
-        <v>63970764234</v>
+        <v>72841620023</v>
       </c>
       <c r="D129" t="n">
-        <v>0.4288061585704895</v>
+        <v>0.4086686373477226</v>
       </c>
       <c r="E129" t="n">
         <v>128</v>
@@ -2890,17 +2890,17 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2020-12-31</t>
+          <t>2021-01-26</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>29516497306</v>
+        <v>25588114580</v>
       </c>
       <c r="C130" t="n">
-        <v>70483427194</v>
+        <v>62625061804</v>
       </c>
       <c r="D130" t="n">
-        <v>0.4187721636287379</v>
+        <v>0.4085922447483418</v>
       </c>
       <c r="E130" t="n">
         <v>129</v>
@@ -2909,17 +2909,17 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2021-01-04</t>
+          <t>2021-01-27</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>32842910849</v>
+        <v>25604690493</v>
       </c>
       <c r="C131" t="n">
-        <v>81262611004</v>
+        <v>60015878129</v>
       </c>
       <c r="D131" t="n">
-        <v>0.4041577109475767</v>
+        <v>0.4266319396004584</v>
       </c>
       <c r="E131" t="n">
         <v>130</v>
@@ -2928,17 +2928,17 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>2021-01-05</t>
+          <t>2021-01-28</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>34955476638</v>
+        <v>26286085867</v>
       </c>
       <c r="C132" t="n">
-        <v>86306603527</v>
+        <v>62311898539</v>
       </c>
       <c r="D132" t="n">
-        <v>0.4050150881799513</v>
+        <v>0.4218469743872106</v>
       </c>
       <c r="E132" t="n">
         <v>131</v>
@@ -2947,17 +2947,17 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>2021-01-06</t>
+          <t>2021-01-29</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>31318863380</v>
+        <v>27002904913</v>
       </c>
       <c r="C133" t="n">
-        <v>79924024318</v>
+        <v>66018503681</v>
       </c>
       <c r="D133" t="n">
-        <v>0.3918579381762507</v>
+        <v>0.4090202504963981</v>
       </c>
       <c r="E133" t="n">
         <v>132</v>
@@ -2966,17 +2966,17 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2021-01-07</t>
+          <t>2021-02-01</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>34820241307</v>
+        <v>25457673045</v>
       </c>
       <c r="C134" t="n">
-        <v>87045282583</v>
+        <v>61214730247</v>
       </c>
       <c r="D134" t="n">
-        <v>0.4000244501911746</v>
+        <v>0.4158749526834291</v>
       </c>
       <c r="E134" t="n">
         <v>133</v>
@@ -2985,17 +2985,17 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>2021-01-08</t>
+          <t>2021-02-02</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>31741361539</v>
+        <v>24585679056</v>
       </c>
       <c r="C135" t="n">
-        <v>76243328872</v>
+        <v>59083806830</v>
       </c>
       <c r="D135" t="n">
-        <v>0.4163165749529185</v>
+        <v>0.4161153516519274</v>
       </c>
       <c r="E135" t="n">
         <v>134</v>
@@ -3004,17 +3004,17 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>2021-01-11</t>
+          <t>2021-02-03</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>33861909952</v>
+        <v>27946762653</v>
       </c>
       <c r="C136" t="n">
-        <v>79843929989</v>
+        <v>64252239936</v>
       </c>
       <c r="D136" t="n">
-        <v>0.4241012429706943</v>
+        <v>0.4349539048107436</v>
       </c>
       <c r="E136" t="n">
         <v>135</v>
@@ -3023,17 +3023,17 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>2021-01-12</t>
+          <t>2021-02-04</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>31336739617</v>
+        <v>26745949814</v>
       </c>
       <c r="C137" t="n">
-        <v>70684174141</v>
+        <v>65026335158</v>
       </c>
       <c r="D137" t="n">
-        <v>0.4433345936035105</v>
+        <v>0.411309506356357</v>
       </c>
       <c r="E137" t="n">
         <v>136</v>
@@ -3042,17 +3042,17 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>2021-01-13</t>
+          <t>2021-02-05</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>36176556832</v>
+        <v>27228530445</v>
       </c>
       <c r="C138" t="n">
-        <v>81782457644</v>
+        <v>60817228192</v>
       </c>
       <c r="D138" t="n">
-        <v>0.4423510600461162</v>
+        <v>0.44771080916479</v>
       </c>
       <c r="E138" t="n">
         <v>137</v>
@@ -3061,17 +3061,17 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>2021-01-14</t>
+          <t>2021-02-08</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>32971296424</v>
+        <v>22845413099</v>
       </c>
       <c r="C139" t="n">
-        <v>74034016193</v>
+        <v>53099229697</v>
       </c>
       <c r="D139" t="n">
-        <v>0.4453533405245341</v>
+        <v>0.4302400096830542</v>
       </c>
       <c r="E139" t="n">
         <v>138</v>
@@ -3080,17 +3080,17 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>2021-01-15</t>
+          <t>2021-02-09</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>31268748151</v>
+        <v>23052987297</v>
       </c>
       <c r="C140" t="n">
-        <v>68522530970</v>
+        <v>54414450658</v>
       </c>
       <c r="D140" t="n">
-        <v>0.4563279801309417</v>
+        <v>0.4236556101960896</v>
       </c>
       <c r="E140" t="n">
         <v>139</v>
@@ -3099,17 +3099,17 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>2021-01-18</t>
+          <t>2021-02-10</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>28025154838</v>
+        <v>23672043794</v>
       </c>
       <c r="C141" t="n">
-        <v>66132336803</v>
+        <v>53724833418</v>
       </c>
       <c r="D141" t="n">
-        <v>0.4237738479056539</v>
+        <v>0.4406164205260971</v>
       </c>
       <c r="E141" t="n">
         <v>140</v>
@@ -3118,17 +3118,17 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>2021-01-19</t>
+          <t>2021-02-18</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>30160755219</v>
+        <v>30305438799</v>
       </c>
       <c r="C142" t="n">
-        <v>71588657610</v>
+        <v>70581483088</v>
       </c>
       <c r="D142" t="n">
-        <v>0.4213063385447102</v>
+        <v>0.4293681213982937</v>
       </c>
       <c r="E142" t="n">
         <v>141</v>
@@ -3137,17 +3137,17 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>2021-01-20</t>
+          <t>2021-02-19</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>25498108632</v>
+        <v>31871390359</v>
       </c>
       <c r="C143" t="n">
-        <v>61023142374</v>
+        <v>74891926971</v>
       </c>
       <c r="D143" t="n">
-        <v>0.4178432581483041</v>
+        <v>0.4255650995779744</v>
       </c>
       <c r="E143" t="n">
         <v>142</v>
@@ -3156,17 +3156,17 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>2021-01-21</t>
+          <t>2021-02-22</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>31550851527</v>
+        <v>41800730539</v>
       </c>
       <c r="C144" t="n">
-        <v>73606094304</v>
+        <v>98345390597</v>
       </c>
       <c r="D144" t="n">
-        <v>0.4286445548474839</v>
+        <v>0.4250400581588124</v>
       </c>
       <c r="E144" t="n">
         <v>143</v>
@@ -3175,17 +3175,17 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>2021-01-22</t>
+          <t>2021-02-23</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>29587073243</v>
+        <v>36659765914</v>
       </c>
       <c r="C145" t="n">
-        <v>71863919964</v>
+        <v>79667225639</v>
       </c>
       <c r="D145" t="n">
-        <v>0.4117097043665521</v>
+        <v>0.4601611970287279</v>
       </c>
       <c r="E145" t="n">
         <v>144</v>
@@ -3194,17 +3194,17 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>2021-01-25</t>
+          <t>2021-02-24</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>29768085597</v>
+        <v>33328852498</v>
       </c>
       <c r="C146" t="n">
-        <v>72841620023</v>
+        <v>74974298826</v>
       </c>
       <c r="D146" t="n">
-        <v>0.4086686373477226</v>
+        <v>0.4445370349557979</v>
       </c>
       <c r="E146" t="n">
         <v>145</v>
@@ -3213,17 +3213,17 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>2021-01-26</t>
+          <t>2021-02-25</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>25588114580</v>
+        <v>33009105938</v>
       </c>
       <c r="C147" t="n">
-        <v>62625061804</v>
+        <v>72321851390</v>
       </c>
       <c r="D147" t="n">
-        <v>0.4085922447483418</v>
+        <v>0.4564195371603028</v>
       </c>
       <c r="E147" t="n">
         <v>146</v>
@@ -3232,17 +3232,17 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>2021-01-27</t>
+          <t>2021-02-26</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>25604690493</v>
+        <v>29437488128</v>
       </c>
       <c r="C148" t="n">
-        <v>60015878129</v>
+        <v>67566280430</v>
       </c>
       <c r="D148" t="n">
-        <v>0.4266319396004584</v>
+        <v>0.4356831238993216</v>
       </c>
       <c r="E148" t="n">
         <v>147</v>
@@ -3251,17 +3251,17 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>2021-01-28</t>
+          <t>2021-03-01</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>26286085867</v>
+        <v>28022529242</v>
       </c>
       <c r="C149" t="n">
-        <v>62311898539</v>
+        <v>65847760652</v>
       </c>
       <c r="D149" t="n">
-        <v>0.4218469743872106</v>
+        <v>0.425565409734991</v>
       </c>
       <c r="E149" t="n">
         <v>148</v>
@@ -3270,17 +3270,17 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>2021-01-29</t>
+          <t>2021-03-02</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>27002904913</v>
+        <v>30548474585</v>
       </c>
       <c r="C150" t="n">
-        <v>66018503681</v>
+        <v>69441386639</v>
       </c>
       <c r="D150" t="n">
-        <v>0.4090202504963981</v>
+        <v>0.4399174046424243</v>
       </c>
       <c r="E150" t="n">
         <v>149</v>
@@ -3289,17 +3289,17 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>2021-02-01</t>
+          <t>2021-03-03</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>25457673045</v>
+        <v>31581683271</v>
       </c>
       <c r="C151" t="n">
-        <v>61214730247</v>
+        <v>69999474895</v>
       </c>
       <c r="D151" t="n">
-        <v>0.4158749526834291</v>
+        <v>0.4511702883253464</v>
       </c>
       <c r="E151" t="n">
         <v>150</v>
@@ -3308,17 +3308,17 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>2021-02-02</t>
+          <t>2021-03-04</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>24585679056</v>
+        <v>36100282673</v>
       </c>
       <c r="C152" t="n">
-        <v>59083806830</v>
+        <v>78562142790</v>
       </c>
       <c r="D152" t="n">
-        <v>0.4161153516519274</v>
+        <v>0.4595124495203449</v>
       </c>
       <c r="E152" t="n">
         <v>151</v>
@@ -3327,17 +3327,17 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>2021-02-03</t>
+          <t>2021-03-05</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>27946762653</v>
+        <v>32337135967</v>
       </c>
       <c r="C153" t="n">
-        <v>64252239936</v>
+        <v>73514786011</v>
       </c>
       <c r="D153" t="n">
-        <v>0.4349539048107436</v>
+        <v>0.4398725443091326</v>
       </c>
       <c r="E153" t="n">
         <v>152</v>
@@ -3346,17 +3346,17 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>2021-02-04</t>
+          <t>2021-03-08</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>26745949814</v>
+        <v>34237890063</v>
       </c>
       <c r="C154" t="n">
-        <v>65026335158</v>
+        <v>78814375242</v>
       </c>
       <c r="D154" t="n">
-        <v>0.411309506356357</v>
+        <v>0.4344117422471771</v>
       </c>
       <c r="E154" t="n">
         <v>153</v>
@@ -3365,17 +3365,17 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>2021-02-05</t>
+          <t>2021-03-09</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>27228530445</v>
+        <v>35838361211</v>
       </c>
       <c r="C155" t="n">
-        <v>60817228192</v>
+        <v>82850202998</v>
       </c>
       <c r="D155" t="n">
-        <v>0.44771080916479</v>
+        <v>0.4325681762284292</v>
       </c>
       <c r="E155" t="n">
         <v>154</v>
@@ -3384,17 +3384,17 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>2021-02-08</t>
+          <t>2021-03-10</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>22845413099</v>
+        <v>26975456721</v>
       </c>
       <c r="C156" t="n">
-        <v>53099229697</v>
+        <v>62127335207</v>
       </c>
       <c r="D156" t="n">
-        <v>0.4302400096830542</v>
+        <v>0.4341962620981791</v>
       </c>
       <c r="E156" t="n">
         <v>155</v>
@@ -3403,17 +3403,17 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>2021-02-09</t>
+          <t>2021-03-11</t>
         </is>
       </c>
       <c r="B157" t="n">
-        <v>23052987297</v>
+        <v>30680047969</v>
       </c>
       <c r="C157" t="n">
-        <v>54414450658</v>
+        <v>66598157167</v>
       </c>
       <c r="D157" t="n">
-        <v>0.4236556101960896</v>
+        <v>0.4606741278451207</v>
       </c>
       <c r="E157" t="n">
         <v>156</v>
@@ -3422,17 +3422,17 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>2021-02-10</t>
+          <t>2021-03-12</t>
         </is>
       </c>
       <c r="B158" t="n">
-        <v>23672043794</v>
+        <v>33862968625</v>
       </c>
       <c r="C158" t="n">
-        <v>53724833418</v>
+        <v>72238010975</v>
       </c>
       <c r="D158" t="n">
-        <v>0.4406164205260971</v>
+        <v>0.4687693939513262</v>
       </c>
       <c r="E158" t="n">
         <v>157</v>
@@ -3441,17 +3441,17 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>2021-02-18</t>
+          <t>2021-03-15</t>
         </is>
       </c>
       <c r="B159" t="n">
-        <v>30305438799</v>
+        <v>34591765793</v>
       </c>
       <c r="C159" t="n">
-        <v>70581483088</v>
+        <v>71723136959</v>
       </c>
       <c r="D159" t="n">
-        <v>0.4293681213982937</v>
+        <v>0.4822957731585852</v>
       </c>
       <c r="E159" t="n">
         <v>158</v>
@@ -3460,17 +3460,17 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>2021-02-19</t>
+          <t>2021-03-16</t>
         </is>
       </c>
       <c r="B160" t="n">
-        <v>31871390359</v>
+        <v>29977825317</v>
       </c>
       <c r="C160" t="n">
-        <v>74891926971</v>
+        <v>67049266583</v>
       </c>
       <c r="D160" t="n">
-        <v>0.4255650995779744</v>
+        <v>0.447101465008429</v>
       </c>
       <c r="E160" t="n">
         <v>159</v>
@@ -3479,17 +3479,17 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>2021-02-22</t>
+          <t>2021-03-17</t>
         </is>
       </c>
       <c r="B161" t="n">
-        <v>41800730539</v>
+        <v>27491185060</v>
       </c>
       <c r="C161" t="n">
-        <v>98345390597</v>
+        <v>62515062852</v>
       </c>
       <c r="D161" t="n">
-        <v>0.4250400581588124</v>
+        <v>0.4397529780156095</v>
       </c>
       <c r="E161" t="n">
         <v>160</v>
@@ -3498,17 +3498,17 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>2021-02-23</t>
+          <t>2021-03-18</t>
         </is>
       </c>
       <c r="B162" t="n">
-        <v>36659765914</v>
+        <v>26739276351</v>
       </c>
       <c r="C162" t="n">
-        <v>79667225639</v>
+        <v>62832911819</v>
       </c>
       <c r="D162" t="n">
-        <v>0.4601611970287279</v>
+        <v>0.4255616296762858</v>
       </c>
       <c r="E162" t="n">
         <v>161</v>
@@ -3517,17 +3517,17 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>2021-02-24</t>
+          <t>2021-03-19</t>
         </is>
       </c>
       <c r="B163" t="n">
-        <v>33328852498</v>
+        <v>28358235249</v>
       </c>
       <c r="C163" t="n">
-        <v>74974298826</v>
+        <v>65875538395</v>
       </c>
       <c r="D163" t="n">
-        <v>0.4445370349557979</v>
+        <v>0.4304820262562349</v>
       </c>
       <c r="E163" t="n">
         <v>162</v>
@@ -3536,17 +3536,17 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>2021-02-25</t>
+          <t>2021-03-22</t>
         </is>
       </c>
       <c r="B164" t="n">
-        <v>33009105938</v>
+        <v>29121013208</v>
       </c>
       <c r="C164" t="n">
-        <v>72321851390</v>
+        <v>67358226346</v>
       </c>
       <c r="D164" t="n">
-        <v>0.4564195371603028</v>
+        <v>0.4323304633707791</v>
       </c>
       <c r="E164" t="n">
         <v>163</v>
@@ -3555,17 +3555,17 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>2021-02-26</t>
+          <t>2021-03-23</t>
         </is>
       </c>
       <c r="B165" t="n">
-        <v>29437488128</v>
+        <v>29320271653</v>
       </c>
       <c r="C165" t="n">
-        <v>67566280430</v>
+        <v>70323191299</v>
       </c>
       <c r="D165" t="n">
-        <v>0.4356831238993216</v>
+        <v>0.4169360222623591</v>
       </c>
       <c r="E165" t="n">
         <v>164</v>
@@ -3574,17 +3574,17 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>2021-03-01</t>
+          <t>2021-03-24</t>
         </is>
       </c>
       <c r="B166" t="n">
-        <v>28022529242</v>
+        <v>28494202046</v>
       </c>
       <c r="C166" t="n">
-        <v>65847760652</v>
+        <v>67303523996</v>
       </c>
       <c r="D166" t="n">
-        <v>0.425565409734991</v>
+        <v>0.423368649280437</v>
       </c>
       <c r="E166" t="n">
         <v>165</v>
@@ -3593,17 +3593,17 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>2021-03-02</t>
+          <t>2021-03-25</t>
         </is>
       </c>
       <c r="B167" t="n">
-        <v>30548474585</v>
+        <v>25857769578</v>
       </c>
       <c r="C167" t="n">
-        <v>69441386639</v>
+        <v>60650502617</v>
       </c>
       <c r="D167" t="n">
-        <v>0.4399174046424243</v>
+        <v>0.426340565407816</v>
       </c>
       <c r="E167" t="n">
         <v>166</v>
@@ -3612,17 +3612,17 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>2021-03-03</t>
+          <t>2021-03-26</t>
         </is>
       </c>
       <c r="B168" t="n">
-        <v>31581683271</v>
+        <v>25857588064</v>
       </c>
       <c r="C168" t="n">
-        <v>69999474895</v>
+        <v>61284664475</v>
       </c>
       <c r="D168" t="n">
-        <v>0.4511702883253464</v>
+        <v>0.4219259138564452</v>
       </c>
       <c r="E168" t="n">
         <v>167</v>
@@ -3631,17 +3631,17 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>2021-03-04</t>
+          <t>2021-03-29</t>
         </is>
       </c>
       <c r="B169" t="n">
-        <v>36100282673</v>
+        <v>26030305012</v>
       </c>
       <c r="C169" t="n">
-        <v>78562142790</v>
+        <v>62965892538</v>
       </c>
       <c r="D169" t="n">
-        <v>0.4595124495203449</v>
+        <v>0.4134032563151658</v>
       </c>
       <c r="E169" t="n">
         <v>168</v>
@@ -3650,17 +3650,17 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>2021-03-05</t>
+          <t>2021-03-30</t>
         </is>
       </c>
       <c r="B170" t="n">
-        <v>32337135967</v>
+        <v>25780001010</v>
       </c>
       <c r="C170" t="n">
-        <v>73514786011</v>
+        <v>62868502600</v>
       </c>
       <c r="D170" t="n">
-        <v>0.4398725443091326</v>
+        <v>0.4100622719460158</v>
       </c>
       <c r="E170" t="n">
         <v>169</v>
@@ -3669,17 +3669,17 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>2021-03-08</t>
+          <t>2021-03-31</t>
         </is>
       </c>
       <c r="B171" t="n">
-        <v>34237890063</v>
+        <v>25340940136</v>
       </c>
       <c r="C171" t="n">
-        <v>78814375242</v>
+        <v>58944651908</v>
       </c>
       <c r="D171" t="n">
-        <v>0.4344117422471771</v>
+        <v>0.4299107606157687</v>
       </c>
       <c r="E171" t="n">
         <v>170</v>
@@ -3688,17 +3688,17 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>2021-03-09</t>
+          <t>2021-04-01</t>
         </is>
       </c>
       <c r="B172" t="n">
-        <v>35838361211</v>
+        <v>24459982838</v>
       </c>
       <c r="C172" t="n">
-        <v>82850202998</v>
+        <v>57742915146</v>
       </c>
       <c r="D172" t="n">
-        <v>0.4325681762284292</v>
+        <v>0.4236014544148696</v>
       </c>
       <c r="E172" t="n">
         <v>171</v>
@@ -3707,17 +3707,17 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>2021-03-10</t>
+          <t>2021-04-02</t>
         </is>
       </c>
       <c r="B173" t="n">
-        <v>26975456721</v>
+        <v>23776468616</v>
       </c>
       <c r="C173" t="n">
-        <v>62127335207</v>
+        <v>57637646459</v>
       </c>
       <c r="D173" t="n">
-        <v>0.4341962620981791</v>
+        <v>0.4125162992717471</v>
       </c>
       <c r="E173" t="n">
         <v>172</v>
@@ -3726,17 +3726,17 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>2021-03-11</t>
+          <t>2021-04-06</t>
         </is>
       </c>
       <c r="B174" t="n">
-        <v>30680047969</v>
+        <v>21609152872</v>
       </c>
       <c r="C174" t="n">
-        <v>66598157167</v>
+        <v>54009467026</v>
       </c>
       <c r="D174" t="n">
-        <v>0.4606741278451207</v>
+        <v>0.4000993540928189</v>
       </c>
       <c r="E174" t="n">
         <v>173</v>
@@ -3745,17 +3745,17 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>2021-03-12</t>
+          <t>2021-04-07</t>
         </is>
       </c>
       <c r="B175" t="n">
-        <v>33862968625</v>
+        <v>28192988226</v>
       </c>
       <c r="C175" t="n">
-        <v>72238010975</v>
+        <v>64777711487</v>
       </c>
       <c r="D175" t="n">
-        <v>0.4687693939513262</v>
+        <v>0.4352266787266473</v>
       </c>
       <c r="E175" t="n">
         <v>174</v>
@@ -3764,17 +3764,17 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>2021-03-15</t>
+          <t>2021-04-08</t>
         </is>
       </c>
       <c r="B176" t="n">
-        <v>34591765793</v>
+        <v>31610774016</v>
       </c>
       <c r="C176" t="n">
-        <v>71723136959</v>
+        <v>70183037971</v>
       </c>
       <c r="D176" t="n">
-        <v>0.4822957731585852</v>
+        <v>0.4504047549076137</v>
       </c>
       <c r="E176" t="n">
         <v>175</v>
@@ -3783,17 +3783,17 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>2021-03-16</t>
+          <t>2021-04-09</t>
         </is>
       </c>
       <c r="B177" t="n">
-        <v>29977825317</v>
+        <v>27363203695</v>
       </c>
       <c r="C177" t="n">
-        <v>67049266583</v>
+        <v>60908586933</v>
       </c>
       <c r="D177" t="n">
-        <v>0.447101465008429</v>
+        <v>0.4492503450309851</v>
       </c>
       <c r="E177" t="n">
         <v>176</v>
@@ -3802,17 +3802,17 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>2021-03-17</t>
+          <t>2021-04-12</t>
         </is>
       </c>
       <c r="B178" t="n">
-        <v>27491185060</v>
+        <v>29441281600</v>
       </c>
       <c r="C178" t="n">
-        <v>62515062852</v>
+        <v>66662877908</v>
       </c>
       <c r="D178" t="n">
-        <v>0.4397529780156095</v>
+        <v>0.4416443232563598</v>
       </c>
       <c r="E178" t="n">
         <v>177</v>
@@ -3821,17 +3821,17 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>2021-03-18</t>
+          <t>2021-04-13</t>
         </is>
       </c>
       <c r="B179" t="n">
-        <v>26739276351</v>
+        <v>26500289609</v>
       </c>
       <c r="C179" t="n">
-        <v>62832911819</v>
+        <v>60099497250</v>
       </c>
       <c r="D179" t="n">
-        <v>0.4255616296762858</v>
+        <v>0.4409402877159675</v>
       </c>
       <c r="E179" t="n">
         <v>178</v>
@@ -3840,17 +3840,17 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>2021-03-19</t>
+          <t>2021-04-14</t>
         </is>
       </c>
       <c r="B180" t="n">
-        <v>28358235249</v>
+        <v>24875678254</v>
       </c>
       <c r="C180" t="n">
-        <v>65875538395</v>
+        <v>56149660115</v>
       </c>
       <c r="D180" t="n">
-        <v>0.4304820262562349</v>
+        <v>0.4430245562137362</v>
       </c>
       <c r="E180" t="n">
         <v>179</v>
@@ -3859,17 +3859,17 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>2021-03-22</t>
+          <t>2021-04-15</t>
         </is>
       </c>
       <c r="B181" t="n">
-        <v>29121013208</v>
+        <v>23587218127</v>
       </c>
       <c r="C181" t="n">
-        <v>67358226346</v>
+        <v>56730832399</v>
       </c>
       <c r="D181" t="n">
-        <v>0.4323304633707791</v>
+        <v>0.4157742294543835</v>
       </c>
       <c r="E181" t="n">
         <v>180</v>
@@ -3878,17 +3878,17 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>2021-03-23</t>
+          <t>2021-04-16</t>
         </is>
       </c>
       <c r="B182" t="n">
-        <v>29320271653</v>
+        <v>23064238930</v>
       </c>
       <c r="C182" t="n">
-        <v>70323191299</v>
+        <v>60757105467</v>
       </c>
       <c r="D182" t="n">
-        <v>0.4169360222623591</v>
+        <v>0.3796138534368998</v>
       </c>
       <c r="E182" t="n">
         <v>181</v>
@@ -3897,17 +3897,17 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>2021-03-24</t>
+          <t>2021-04-19</t>
         </is>
       </c>
       <c r="B183" t="n">
-        <v>28494202046</v>
+        <v>26349229565</v>
       </c>
       <c r="C183" t="n">
-        <v>67303523996</v>
+        <v>68717257011</v>
       </c>
       <c r="D183" t="n">
-        <v>0.423368649280437</v>
+        <v>0.3834441406877186</v>
       </c>
       <c r="E183" t="n">
         <v>182</v>
@@ -3916,17 +3916,17 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>2021-03-25</t>
+          <t>2021-04-20</t>
         </is>
       </c>
       <c r="B184" t="n">
-        <v>25857769578</v>
+        <v>26332452757</v>
       </c>
       <c r="C184" t="n">
-        <v>60650502617</v>
+        <v>66152179163</v>
       </c>
       <c r="D184" t="n">
-        <v>0.426340565407816</v>
+        <v>0.3980587350284626</v>
       </c>
       <c r="E184" t="n">
         <v>183</v>
@@ -3935,17 +3935,17 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>2021-03-26</t>
+          <t>2021-04-21</t>
         </is>
       </c>
       <c r="B185" t="n">
-        <v>25857588064</v>
+        <v>23796108657</v>
       </c>
       <c r="C185" t="n">
-        <v>61284664475</v>
+        <v>58645267418</v>
       </c>
       <c r="D185" t="n">
-        <v>0.4219259138564452</v>
+        <v>0.4057634947316526</v>
       </c>
       <c r="E185" t="n">
         <v>184</v>
@@ -3954,17 +3954,17 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>2021-03-29</t>
+          <t>2021-04-22</t>
         </is>
       </c>
       <c r="B186" t="n">
-        <v>26030305012</v>
+        <v>23283868400</v>
       </c>
       <c r="C186" t="n">
-        <v>62965892538</v>
+        <v>57343158813</v>
       </c>
       <c r="D186" t="n">
-        <v>0.4134032563151658</v>
+        <v>0.406044398006226</v>
       </c>
       <c r="E186" t="n">
         <v>185</v>
@@ -3973,17 +3973,17 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>2021-03-30</t>
+          <t>2021-04-23</t>
         </is>
       </c>
       <c r="B187" t="n">
-        <v>25780001010</v>
+        <v>23110619160</v>
       </c>
       <c r="C187" t="n">
-        <v>62868502600</v>
+        <v>58758936747</v>
       </c>
       <c r="D187" t="n">
-        <v>0.4100622719460158</v>
+        <v>0.3933124123655954</v>
       </c>
       <c r="E187" t="n">
         <v>186</v>
@@ -3992,17 +3992,17 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>2021-03-31</t>
+          <t>2021-04-26</t>
         </is>
       </c>
       <c r="B188" t="n">
-        <v>25340940136</v>
+        <v>26080656908</v>
       </c>
       <c r="C188" t="n">
-        <v>58944651908</v>
+        <v>64990659217</v>
       </c>
       <c r="D188" t="n">
-        <v>0.4299107606157687</v>
+        <v>0.4012985438556365</v>
       </c>
       <c r="E188" t="n">
         <v>187</v>
@@ -4011,17 +4011,17 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>2021-04-01</t>
+          <t>2021-04-27</t>
         </is>
       </c>
       <c r="B189" t="n">
-        <v>24459982838</v>
+        <v>22805398723</v>
       </c>
       <c r="C189" t="n">
-        <v>57742915146</v>
+        <v>58465572266</v>
       </c>
       <c r="D189" t="n">
-        <v>0.4236014544148696</v>
+        <v>0.3900654323409783</v>
       </c>
       <c r="E189" t="n">
         <v>188</v>
@@ -4030,17 +4030,17 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>2021-04-02</t>
+          <t>2021-04-28</t>
         </is>
       </c>
       <c r="B190" t="n">
-        <v>23776468616</v>
+        <v>21764975470</v>
       </c>
       <c r="C190" t="n">
-        <v>57637646459</v>
+        <v>56258757783</v>
       </c>
       <c r="D190" t="n">
-        <v>0.4125162992717471</v>
+        <v>0.3868726635229197</v>
       </c>
       <c r="E190" t="n">
         <v>189</v>
@@ -4049,17 +4049,17 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>2021-04-06</t>
+          <t>2021-04-29</t>
         </is>
       </c>
       <c r="B191" t="n">
-        <v>21609152872</v>
+        <v>23871290845</v>
       </c>
       <c r="C191" t="n">
-        <v>54009467026</v>
+        <v>59672070298</v>
       </c>
       <c r="D191" t="n">
-        <v>0.4000993540928189</v>
+        <v>0.400041270996426</v>
       </c>
       <c r="E191" t="n">
         <v>190</v>
@@ -4068,17 +4068,17 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>2021-04-07</t>
+          <t>2021-04-30</t>
         </is>
       </c>
       <c r="B192" t="n">
-        <v>28192988226</v>
+        <v>26727927563</v>
       </c>
       <c r="C192" t="n">
-        <v>64777711487</v>
+        <v>64623812735</v>
       </c>
       <c r="D192" t="n">
-        <v>0.4352266787266473</v>
+        <v>0.413592550978105</v>
       </c>
       <c r="E192" t="n">
         <v>191</v>
@@ -4087,17 +4087,17 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>2021-04-08</t>
+          <t>2021-05-06</t>
         </is>
       </c>
       <c r="B193" t="n">
-        <v>31610774016</v>
+        <v>28245158344</v>
       </c>
       <c r="C193" t="n">
-        <v>70183037971</v>
+        <v>64995398044</v>
       </c>
       <c r="D193" t="n">
-        <v>0.4504047549076137</v>
+        <v>0.4345716649797089</v>
       </c>
       <c r="E193" t="n">
         <v>192</v>
@@ -4106,17 +4106,17 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>2021-04-09</t>
+          <t>2021-05-07</t>
         </is>
       </c>
       <c r="B194" t="n">
-        <v>27363203695</v>
+        <v>33809492530</v>
       </c>
       <c r="C194" t="n">
-        <v>60908586933</v>
+        <v>72689004129</v>
       </c>
       <c r="D194" t="n">
-        <v>0.4492503450309851</v>
+        <v>0.4651252680529072</v>
       </c>
       <c r="E194" t="n">
         <v>193</v>
@@ -4125,17 +4125,17 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>2021-04-12</t>
+          <t>2021-05-10</t>
         </is>
       </c>
       <c r="B195" t="n">
-        <v>29441281600</v>
+        <v>34980447442</v>
       </c>
       <c r="C195" t="n">
-        <v>66662877908</v>
+        <v>74391256531</v>
       </c>
       <c r="D195" t="n">
-        <v>0.4416443232563598</v>
+        <v>0.4702225647636843</v>
       </c>
       <c r="E195" t="n">
         <v>194</v>
@@ -4144,17 +4144,17 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>2021-04-13</t>
+          <t>2021-05-11</t>
         </is>
       </c>
       <c r="B196" t="n">
-        <v>26500289609</v>
+        <v>33682768573</v>
       </c>
       <c r="C196" t="n">
-        <v>60099497250</v>
+        <v>73459473614</v>
       </c>
       <c r="D196" t="n">
-        <v>0.4409402877159675</v>
+        <v>0.4585217796412401</v>
       </c>
       <c r="E196" t="n">
         <v>195</v>
@@ -4163,17 +4163,17 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>2021-04-14</t>
+          <t>2021-05-12</t>
         </is>
       </c>
       <c r="B197" t="n">
-        <v>24875678254</v>
+        <v>28011409229</v>
       </c>
       <c r="C197" t="n">
-        <v>56149660115</v>
+        <v>66061705250</v>
       </c>
       <c r="D197" t="n">
-        <v>0.4430245562137362</v>
+        <v>0.4240188642269418</v>
       </c>
       <c r="E197" t="n">
         <v>196</v>
@@ -4182,17 +4182,17 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>2021-04-15</t>
+          <t>2021-05-13</t>
         </is>
       </c>
       <c r="B198" t="n">
-        <v>23587218127</v>
+        <v>29021959092</v>
       </c>
       <c r="C198" t="n">
-        <v>56730832399</v>
+        <v>69247970457</v>
       </c>
       <c r="D198" t="n">
-        <v>0.4157742294543835</v>
+        <v>0.4191019448002651</v>
       </c>
       <c r="E198" t="n">
         <v>197</v>
@@ -4201,17 +4201,17 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>2021-04-16</t>
+          <t>2021-05-14</t>
         </is>
       </c>
       <c r="B199" t="n">
-        <v>23064238930</v>
+        <v>29087549466</v>
       </c>
       <c r="C199" t="n">
-        <v>60757105467</v>
+        <v>72865719627</v>
       </c>
       <c r="D199" t="n">
-        <v>0.3796138534368998</v>
+        <v>0.3991938817718307</v>
       </c>
       <c r="E199" t="n">
         <v>198</v>
@@ -4220,17 +4220,17 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>2021-04-19</t>
+          <t>2021-05-17</t>
         </is>
       </c>
       <c r="B200" t="n">
-        <v>26349229565</v>
+        <v>26738086558</v>
       </c>
       <c r="C200" t="n">
-        <v>68717257011</v>
+        <v>68865623007</v>
       </c>
       <c r="D200" t="n">
-        <v>0.3834441406877186</v>
+        <v>0.3882646433806625</v>
       </c>
       <c r="E200" t="n">
         <v>199</v>
@@ -4239,17 +4239,17 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>2021-04-20</t>
+          <t>2021-05-18</t>
         </is>
       </c>
       <c r="B201" t="n">
-        <v>26332452757</v>
+        <v>23944078372</v>
       </c>
       <c r="C201" t="n">
-        <v>66152179163</v>
+        <v>58781317109</v>
       </c>
       <c r="D201" t="n">
-        <v>0.3980587350284626</v>
+        <v>0.4073416444139855</v>
       </c>
       <c r="E201" t="n">
         <v>200</v>
@@ -4258,17 +4258,17 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>2021-04-21</t>
+          <t>2021-05-19</t>
         </is>
       </c>
       <c r="B202" t="n">
-        <v>23796108657</v>
+        <v>25053218592</v>
       </c>
       <c r="C202" t="n">
-        <v>58645267418</v>
+        <v>60763325645</v>
       </c>
       <c r="D202" t="n">
-        <v>0.4057634947316526</v>
+        <v>0.4123082192434532</v>
       </c>
       <c r="E202" t="n">
         <v>201</v>
@@ -4277,17 +4277,17 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>2021-04-22</t>
+          <t>2021-05-20</t>
         </is>
       </c>
       <c r="B203" t="n">
-        <v>23283868400</v>
+        <v>28722723747</v>
       </c>
       <c r="C203" t="n">
-        <v>57343158813</v>
+        <v>68566840023</v>
       </c>
       <c r="D203" t="n">
-        <v>0.406044398006226</v>
+        <v>0.4189010859675796</v>
       </c>
       <c r="E203" t="n">
         <v>202</v>
@@ -4296,17 +4296,17 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>2021-04-23</t>
+          <t>2021-05-21</t>
         </is>
       </c>
       <c r="B204" t="n">
-        <v>23110619160</v>
+        <v>25545536529</v>
       </c>
       <c r="C204" t="n">
-        <v>58758936747</v>
+        <v>61418379955</v>
       </c>
       <c r="D204" t="n">
-        <v>0.3933124123655954</v>
+        <v>0.4159265768279251</v>
       </c>
       <c r="E204" t="n">
         <v>203</v>
@@ -4315,17 +4315,17 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>2021-04-26</t>
+          <t>2021-05-24</t>
         </is>
       </c>
       <c r="B205" t="n">
-        <v>26080656908</v>
+        <v>25923087661</v>
       </c>
       <c r="C205" t="n">
-        <v>64990659217</v>
+        <v>63386616118</v>
       </c>
       <c r="D205" t="n">
-        <v>0.4012985438556365</v>
+        <v>0.4089678428761964</v>
       </c>
       <c r="E205" t="n">
         <v>204</v>
@@ -4334,17 +4334,17 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>2021-04-27</t>
+          <t>2021-05-25</t>
         </is>
       </c>
       <c r="B206" t="n">
-        <v>22805398723</v>
+        <v>29902389375</v>
       </c>
       <c r="C206" t="n">
-        <v>58465572266</v>
+        <v>71817033145</v>
       </c>
       <c r="D206" t="n">
-        <v>0.3900654323409783</v>
+        <v>0.4163690431854305</v>
       </c>
       <c r="E206" t="n">
         <v>205</v>
@@ -4353,17 +4353,17 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>2021-04-28</t>
+          <t>2021-05-26</t>
         </is>
       </c>
       <c r="B207" t="n">
-        <v>21764975470</v>
+        <v>29496722494</v>
       </c>
       <c r="C207" t="n">
-        <v>56258757783</v>
+        <v>72933630614</v>
       </c>
       <c r="D207" t="n">
-        <v>0.3868726635229197</v>
+        <v>0.4044323893611015</v>
       </c>
       <c r="E207" t="n">
         <v>206</v>
@@ -4372,17 +4372,17 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>2021-04-29</t>
+          <t>2021-05-27</t>
         </is>
       </c>
       <c r="B208" t="n">
-        <v>23871290845</v>
+        <v>26896810605</v>
       </c>
       <c r="C208" t="n">
-        <v>59672070298</v>
+        <v>68968444971</v>
       </c>
       <c r="D208" t="n">
-        <v>0.400041270996426</v>
+        <v>0.3899871980049663</v>
       </c>
       <c r="E208" t="n">
         <v>207</v>
@@ -4391,17 +4391,17 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>2021-04-30</t>
+          <t>2021-05-27</t>
         </is>
       </c>
       <c r="B209" t="n">
-        <v>26727927563</v>
+        <v>26896810605</v>
       </c>
       <c r="C209" t="n">
-        <v>64623812735</v>
+        <v>68968444971</v>
       </c>
       <c r="D209" t="n">
-        <v>0.413592550978105</v>
+        <v>0.3899871980049663</v>
       </c>
       <c r="E209" t="n">
         <v>208</v>
@@ -4410,17 +4410,17 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>2021-05-06</t>
+          <t>2021-05-28</t>
         </is>
       </c>
       <c r="B210" t="n">
-        <v>28245158344</v>
+        <v>29791926043</v>
       </c>
       <c r="C210" t="n">
-        <v>64995398044</v>
+        <v>73972884560</v>
       </c>
       <c r="D210" t="n">
-        <v>0.4345716649797089</v>
+        <v>0.4027411695543051</v>
       </c>
       <c r="E210" t="n">
         <v>209</v>
@@ -4429,17 +4429,17 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>2021-05-07</t>
+          <t>2021-05-31</t>
         </is>
       </c>
       <c r="B211" t="n">
-        <v>33809492530</v>
+        <v>27775314244</v>
       </c>
       <c r="C211" t="n">
-        <v>72689004129</v>
+        <v>70615016083</v>
       </c>
       <c r="D211" t="n">
-        <v>0.4651252680529072</v>
+        <v>0.3933343895490053</v>
       </c>
       <c r="E211" t="n">
         <v>210</v>
@@ -4448,17 +4448,17 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>2021-05-10</t>
+          <t>2021-06-01</t>
         </is>
       </c>
       <c r="B212" t="n">
-        <v>34980447442</v>
+        <v>28722955321</v>
       </c>
       <c r="C212" t="n">
-        <v>74391256531</v>
+        <v>75176823860</v>
       </c>
       <c r="D212" t="n">
-        <v>0.4702225647636843</v>
+        <v>0.3820719451315218</v>
       </c>
       <c r="E212" t="n">
         <v>211</v>
@@ -4467,17 +4467,17 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>2021-05-11</t>
+          <t>2021-06-02</t>
         </is>
       </c>
       <c r="B213" t="n">
-        <v>33682768573</v>
+        <v>29120888356</v>
       </c>
       <c r="C213" t="n">
-        <v>73459473614</v>
+        <v>75272955834</v>
       </c>
       <c r="D213" t="n">
-        <v>0.4585217796412401</v>
+        <v>0.3868705305026218</v>
       </c>
       <c r="E213" t="n">
         <v>212</v>
@@ -4486,17 +4486,17 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>2021-05-12</t>
+          <t>2021-06-03</t>
         </is>
       </c>
       <c r="B214" t="n">
-        <v>28011409229</v>
+        <v>29199450254</v>
       </c>
       <c r="C214" t="n">
-        <v>66061705250</v>
+        <v>72798616374</v>
       </c>
       <c r="D214" t="n">
-        <v>0.4240188642269418</v>
+        <v>0.4010989728704318</v>
       </c>
       <c r="E214" t="n">
         <v>213</v>
@@ -4505,17 +4505,17 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>2021-05-13</t>
+          <t>2021-06-04</t>
         </is>
       </c>
       <c r="B215" t="n">
-        <v>29021959092</v>
+        <v>27330244158</v>
       </c>
       <c r="C215" t="n">
-        <v>69247970457</v>
+        <v>68930352581</v>
       </c>
       <c r="D215" t="n">
-        <v>0.4191019448002651</v>
+        <v>0.3964907059757783</v>
       </c>
       <c r="E215" t="n">
         <v>214</v>
@@ -4524,17 +4524,17 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>2021-05-14</t>
+          <t>2021-06-07</t>
         </is>
       </c>
       <c r="B216" t="n">
-        <v>29087549466</v>
+        <v>25294989410</v>
       </c>
       <c r="C216" t="n">
-        <v>72865719627</v>
+        <v>66558910303</v>
       </c>
       <c r="D216" t="n">
-        <v>0.3991938817718307</v>
+        <v>0.3800391156472988</v>
       </c>
       <c r="E216" t="n">
         <v>215</v>
@@ -4543,17 +4543,17 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>2021-05-17</t>
+          <t>2021-06-08</t>
         </is>
       </c>
       <c r="B217" t="n">
-        <v>26738086558</v>
+        <v>25589368881</v>
       </c>
       <c r="C217" t="n">
-        <v>68865623007</v>
+        <v>68255065080</v>
       </c>
       <c r="D217" t="n">
-        <v>0.3882646433806625</v>
+        <v>0.3749079844991337</v>
       </c>
       <c r="E217" t="n">
         <v>216</v>
@@ -4562,17 +4562,17 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>2021-05-18</t>
+          <t>2021-06-09</t>
         </is>
       </c>
       <c r="B218" t="n">
-        <v>23944078372</v>
+        <v>25270907666</v>
       </c>
       <c r="C218" t="n">
-        <v>58781317109</v>
+        <v>66612688195</v>
       </c>
       <c r="D218" t="n">
-        <v>0.4073416444139855</v>
+        <v>0.3793707828157707</v>
       </c>
       <c r="E218" t="n">
         <v>217</v>
@@ -4581,17 +4581,17 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>2021-05-19</t>
+          <t>2021-06-10</t>
         </is>
       </c>
       <c r="B219" t="n">
-        <v>25053218592</v>
+        <v>27144684274</v>
       </c>
       <c r="C219" t="n">
-        <v>60763325645</v>
+        <v>72726642476</v>
       </c>
       <c r="D219" t="n">
-        <v>0.4123082192434532</v>
+        <v>0.3732426432714507</v>
       </c>
       <c r="E219" t="n">
         <v>218</v>
@@ -4600,17 +4600,17 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>2021-05-20</t>
+          <t>2021-06-11</t>
         </is>
       </c>
       <c r="B220" t="n">
-        <v>28722723747</v>
+        <v>31253551848</v>
       </c>
       <c r="C220" t="n">
-        <v>68566840023</v>
+        <v>80603106508</v>
       </c>
       <c r="D220" t="n">
-        <v>0.4189010859675796</v>
+        <v>0.3877462445556987</v>
       </c>
       <c r="E220" t="n">
         <v>219</v>
@@ -4619,17 +4619,17 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>2021-05-21</t>
+          <t>2021-06-15</t>
         </is>
       </c>
       <c r="B221" t="n">
-        <v>25545536529</v>
+        <v>26600340763</v>
       </c>
       <c r="C221" t="n">
-        <v>61418379955</v>
+        <v>71269245087</v>
       </c>
       <c r="D221" t="n">
-        <v>0.4159265768279251</v>
+        <v>0.3732373021564681</v>
       </c>
       <c r="E221" t="n">
         <v>220</v>
@@ -4638,17 +4638,17 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>2021-05-24</t>
+          <t>2021-06-16</t>
         </is>
       </c>
       <c r="B222" t="n">
-        <v>25923087661</v>
+        <v>25225237352</v>
       </c>
       <c r="C222" t="n">
-        <v>63386616118</v>
+        <v>65304111913</v>
       </c>
       <c r="D222" t="n">
-        <v>0.4089678428761964</v>
+        <v>0.3862733388918263</v>
       </c>
       <c r="E222" t="n">
         <v>221</v>
@@ -4657,17 +4657,17 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>2021-05-25</t>
+          <t>2021-06-17</t>
         </is>
       </c>
       <c r="B223" t="n">
-        <v>29902389375</v>
+        <v>23865594042</v>
       </c>
       <c r="C223" t="n">
-        <v>71817033145</v>
+        <v>62073104309</v>
       </c>
       <c r="D223" t="n">
-        <v>0.4163690431854305</v>
+        <v>0.3844756003050377</v>
       </c>
       <c r="E223" t="n">
         <v>222</v>
@@ -4676,17 +4676,17 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>2021-05-26</t>
+          <t>2021-06-18</t>
         </is>
       </c>
       <c r="B224" t="n">
-        <v>29496722494</v>
+        <v>26773348572</v>
       </c>
       <c r="C224" t="n">
-        <v>72933630614</v>
+        <v>68507417006</v>
       </c>
       <c r="D224" t="n">
-        <v>0.4044323893611015</v>
+        <v>0.3908094881121433</v>
       </c>
       <c r="E224" t="n">
         <v>223</v>
@@ -4695,17 +4695,17 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>2021-05-27</t>
+          <t>2021-06-21</t>
         </is>
       </c>
       <c r="B225" t="n">
-        <v>26896810605</v>
+        <v>25810884254</v>
       </c>
       <c r="C225" t="n">
-        <v>68968444971</v>
+        <v>68094480065</v>
       </c>
       <c r="D225" t="n">
-        <v>0.3899871980049663</v>
+        <v>0.3790451770740016</v>
       </c>
       <c r="E225" t="n">
         <v>224</v>
@@ -4714,17 +4714,17 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>2021-05-27</t>
+          <t>2021-06-22</t>
         </is>
       </c>
       <c r="B226" t="n">
-        <v>26896810605</v>
+        <v>27325435943</v>
       </c>
       <c r="C226" t="n">
-        <v>68968444971</v>
+        <v>71331165214</v>
       </c>
       <c r="D226" t="n">
-        <v>0.3899871980049663</v>
+        <v>0.3830785023772036</v>
       </c>
       <c r="E226" t="n">
         <v>225</v>
@@ -4733,17 +4733,17 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>2021-05-28</t>
+          <t>2021-06-23</t>
         </is>
       </c>
       <c r="B227" t="n">
-        <v>29791926043</v>
+        <v>26948115800</v>
       </c>
       <c r="C227" t="n">
-        <v>73972884560</v>
+        <v>71129212592</v>
       </c>
       <c r="D227" t="n">
-        <v>0.4027411695543051</v>
+        <v>0.3788614384721994</v>
       </c>
       <c r="E227" t="n">
         <v>226</v>
@@ -4752,17 +4752,17 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>2021-05-31</t>
+          <t>2021-06-24</t>
         </is>
       </c>
       <c r="B228" t="n">
-        <v>27775314244</v>
+        <v>25431794302</v>
       </c>
       <c r="C228" t="n">
-        <v>70615016083</v>
+        <v>68625630748</v>
       </c>
       <c r="D228" t="n">
-        <v>0.3933343895490053</v>
+        <v>0.3705874033477087</v>
       </c>
       <c r="E228" t="n">
         <v>227</v>
@@ -4771,17 +4771,17 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>2021-06-01</t>
+          <t>2021-06-25</t>
         </is>
       </c>
       <c r="B229" t="n">
-        <v>28722955321</v>
+        <v>27857858703</v>
       </c>
       <c r="C229" t="n">
-        <v>75176823860</v>
+        <v>71470857871</v>
       </c>
       <c r="D229" t="n">
-        <v>0.3820719451315218</v>
+        <v>0.3897792685416135</v>
       </c>
       <c r="E229" t="n">
         <v>228</v>
@@ -4790,17 +4790,17 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>2021-06-02</t>
+          <t>2021-06-28</t>
         </is>
       </c>
       <c r="B230" t="n">
-        <v>29120888356</v>
+        <v>25041439447</v>
       </c>
       <c r="C230" t="n">
-        <v>75272955834</v>
+        <v>67772533030</v>
       </c>
       <c r="D230" t="n">
-        <v>0.3868705305026218</v>
+        <v>0.369492452582748</v>
       </c>
       <c r="E230" t="n">
         <v>229</v>
@@ -4809,17 +4809,17 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>2021-06-03</t>
+          <t>2021-06-29</t>
         </is>
       </c>
       <c r="B231" t="n">
-        <v>29199450254</v>
+        <v>23759674387</v>
       </c>
       <c r="C231" t="n">
-        <v>72798616374</v>
+        <v>65504552666</v>
       </c>
       <c r="D231" t="n">
-        <v>0.4010989728704318</v>
+        <v>0.3627179092138493</v>
       </c>
       <c r="E231" t="n">
         <v>230</v>
@@ -4828,17 +4828,17 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>2021-06-04</t>
+          <t>2021-06-30</t>
         </is>
       </c>
       <c r="B232" t="n">
-        <v>27330244158</v>
+        <v>21731079518</v>
       </c>
       <c r="C232" t="n">
-        <v>68930352581</v>
+        <v>60341364451</v>
       </c>
       <c r="D232" t="n">
-        <v>0.3964907059757783</v>
+        <v>0.360135699875442</v>
       </c>
       <c r="E232" t="n">
         <v>231</v>
@@ -4847,17 +4847,17 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>2021-06-07</t>
+          <t>2021-07-01</t>
         </is>
       </c>
       <c r="B233" t="n">
-        <v>25294989410</v>
+        <v>23237110584</v>
       </c>
       <c r="C233" t="n">
-        <v>66558910303</v>
+        <v>66252494627</v>
       </c>
       <c r="D233" t="n">
-        <v>0.3800391156472988</v>
+        <v>0.3507356321422218</v>
       </c>
       <c r="E233" t="n">
         <v>232</v>
@@ -4866,17 +4866,17 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>2021-06-08</t>
+          <t>2021-07-02</t>
         </is>
       </c>
       <c r="B234" t="n">
-        <v>25589368881</v>
+        <v>23485251132</v>
       </c>
       <c r="C234" t="n">
-        <v>68255065080</v>
+        <v>63093845574</v>
       </c>
       <c r="D234" t="n">
-        <v>0.3749079844991337</v>
+        <v>0.3722272896562499</v>
       </c>
       <c r="E234" t="n">
         <v>233</v>
@@ -4885,17 +4885,17 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>2021-06-09</t>
+          <t>2021-07-05</t>
         </is>
       </c>
       <c r="B235" t="n">
-        <v>25270907666</v>
+        <v>24607854588</v>
       </c>
       <c r="C235" t="n">
-        <v>66612688195</v>
+        <v>63949188580</v>
       </c>
       <c r="D235" t="n">
-        <v>0.3793707828157707</v>
+        <v>0.3848032341679479</v>
       </c>
       <c r="E235" t="n">
         <v>234</v>
@@ -4904,17 +4904,17 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>2021-06-10</t>
+          <t>2021-07-06</t>
         </is>
       </c>
       <c r="B236" t="n">
-        <v>27144684274</v>
+        <v>26803155256</v>
       </c>
       <c r="C236" t="n">
-        <v>72726642476</v>
+        <v>68805538123</v>
       </c>
       <c r="D236" t="n">
-        <v>0.3732426432714507</v>
+        <v>0.3895493878426679</v>
       </c>
       <c r="E236" t="n">
         <v>235</v>
@@ -4923,17 +4923,17 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>2021-06-11</t>
+          <t>2021-07-07</t>
         </is>
       </c>
       <c r="B237" t="n">
-        <v>31253551848</v>
+        <v>28008698287</v>
       </c>
       <c r="C237" t="n">
-        <v>80603106508</v>
+        <v>67984401713</v>
       </c>
       <c r="D237" t="n">
-        <v>0.3877462445556987</v>
+        <v>0.4119871261828604</v>
       </c>
       <c r="E237" t="n">
         <v>236</v>
@@ -4942,17 +4942,17 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>2021-06-15</t>
+          <t>2021-07-08</t>
         </is>
       </c>
       <c r="B238" t="n">
-        <v>26600340763</v>
+        <v>30540652959</v>
       </c>
       <c r="C238" t="n">
-        <v>71269245087</v>
+        <v>76367311906</v>
       </c>
       <c r="D238" t="n">
-        <v>0.3732373021564681</v>
+        <v>0.3999178731941263</v>
       </c>
       <c r="E238" t="n">
         <v>237</v>
@@ -4961,324 +4961,20 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>2021-06-16</t>
+          <t>2021-07-09</t>
         </is>
       </c>
       <c r="B239" t="n">
-        <v>25225237352</v>
+        <v>30301028805</v>
       </c>
       <c r="C239" t="n">
-        <v>65304111913</v>
+        <v>74948316753</v>
       </c>
       <c r="D239" t="n">
-        <v>0.3862733388918263</v>
+        <v>0.4042923192639563</v>
       </c>
       <c r="E239" t="n">
         <v>238</v>
-      </c>
-    </row>
-    <row r="240">
-      <c r="A240" t="inlineStr">
-        <is>
-          <t>2021-06-17</t>
-        </is>
-      </c>
-      <c r="B240" t="n">
-        <v>23865594042</v>
-      </c>
-      <c r="C240" t="n">
-        <v>62073104309</v>
-      </c>
-      <c r="D240" t="n">
-        <v>0.3844756003050377</v>
-      </c>
-      <c r="E240" t="n">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="241">
-      <c r="A241" t="inlineStr">
-        <is>
-          <t>2021-06-18</t>
-        </is>
-      </c>
-      <c r="B241" t="n">
-        <v>26773348572</v>
-      </c>
-      <c r="C241" t="n">
-        <v>68507417006</v>
-      </c>
-      <c r="D241" t="n">
-        <v>0.3908094881121433</v>
-      </c>
-      <c r="E241" t="n">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="242">
-      <c r="A242" t="inlineStr">
-        <is>
-          <t>2021-06-21</t>
-        </is>
-      </c>
-      <c r="B242" t="n">
-        <v>25810884254</v>
-      </c>
-      <c r="C242" t="n">
-        <v>68094480065</v>
-      </c>
-      <c r="D242" t="n">
-        <v>0.3790451770740016</v>
-      </c>
-      <c r="E242" t="n">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="243">
-      <c r="A243" t="inlineStr">
-        <is>
-          <t>2021-06-22</t>
-        </is>
-      </c>
-      <c r="B243" t="n">
-        <v>27325435943</v>
-      </c>
-      <c r="C243" t="n">
-        <v>71331165214</v>
-      </c>
-      <c r="D243" t="n">
-        <v>0.3830785023772036</v>
-      </c>
-      <c r="E243" t="n">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="244">
-      <c r="A244" t="inlineStr">
-        <is>
-          <t>2021-06-23</t>
-        </is>
-      </c>
-      <c r="B244" t="n">
-        <v>26948115800</v>
-      </c>
-      <c r="C244" t="n">
-        <v>71129212592</v>
-      </c>
-      <c r="D244" t="n">
-        <v>0.3788614384721994</v>
-      </c>
-      <c r="E244" t="n">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="245">
-      <c r="A245" t="inlineStr">
-        <is>
-          <t>2021-06-24</t>
-        </is>
-      </c>
-      <c r="B245" t="n">
-        <v>25431794302</v>
-      </c>
-      <c r="C245" t="n">
-        <v>68625630748</v>
-      </c>
-      <c r="D245" t="n">
-        <v>0.3705874033477087</v>
-      </c>
-      <c r="E245" t="n">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="246">
-      <c r="A246" t="inlineStr">
-        <is>
-          <t>2021-06-25</t>
-        </is>
-      </c>
-      <c r="B246" t="n">
-        <v>27857858703</v>
-      </c>
-      <c r="C246" t="n">
-        <v>71470857871</v>
-      </c>
-      <c r="D246" t="n">
-        <v>0.3897792685416135</v>
-      </c>
-      <c r="E246" t="n">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="247">
-      <c r="A247" t="inlineStr">
-        <is>
-          <t>2021-06-28</t>
-        </is>
-      </c>
-      <c r="B247" t="n">
-        <v>25041439447</v>
-      </c>
-      <c r="C247" t="n">
-        <v>67772533030</v>
-      </c>
-      <c r="D247" t="n">
-        <v>0.369492452582748</v>
-      </c>
-      <c r="E247" t="n">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="248">
-      <c r="A248" t="inlineStr">
-        <is>
-          <t>2021-06-29</t>
-        </is>
-      </c>
-      <c r="B248" t="n">
-        <v>23759674387</v>
-      </c>
-      <c r="C248" t="n">
-        <v>65504552666</v>
-      </c>
-      <c r="D248" t="n">
-        <v>0.3627179092138493</v>
-      </c>
-      <c r="E248" t="n">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="249">
-      <c r="A249" t="inlineStr">
-        <is>
-          <t>2021-06-30</t>
-        </is>
-      </c>
-      <c r="B249" t="n">
-        <v>21731079518</v>
-      </c>
-      <c r="C249" t="n">
-        <v>60341364451</v>
-      </c>
-      <c r="D249" t="n">
-        <v>0.360135699875442</v>
-      </c>
-      <c r="E249" t="n">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="250">
-      <c r="A250" t="inlineStr">
-        <is>
-          <t>2021-07-01</t>
-        </is>
-      </c>
-      <c r="B250" t="n">
-        <v>23237110584</v>
-      </c>
-      <c r="C250" t="n">
-        <v>66252494627</v>
-      </c>
-      <c r="D250" t="n">
-        <v>0.3507356321422218</v>
-      </c>
-      <c r="E250" t="n">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="251">
-      <c r="A251" t="inlineStr">
-        <is>
-          <t>2021-07-02</t>
-        </is>
-      </c>
-      <c r="B251" t="n">
-        <v>23485251132</v>
-      </c>
-      <c r="C251" t="n">
-        <v>63093845574</v>
-      </c>
-      <c r="D251" t="n">
-        <v>0.3722272896562499</v>
-      </c>
-      <c r="E251" t="n">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="252">
-      <c r="A252" t="inlineStr">
-        <is>
-          <t>2021-07-05</t>
-        </is>
-      </c>
-      <c r="B252" t="n">
-        <v>24607854588</v>
-      </c>
-      <c r="C252" t="n">
-        <v>63949188580</v>
-      </c>
-      <c r="D252" t="n">
-        <v>0.3848032341679479</v>
-      </c>
-      <c r="E252" t="n">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="253">
-      <c r="A253" t="inlineStr">
-        <is>
-          <t>2021-07-06</t>
-        </is>
-      </c>
-      <c r="B253" t="n">
-        <v>26803155256</v>
-      </c>
-      <c r="C253" t="n">
-        <v>68805538123</v>
-      </c>
-      <c r="D253" t="n">
-        <v>0.3895493878426679</v>
-      </c>
-      <c r="E253" t="n">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="254">
-      <c r="A254" t="inlineStr">
-        <is>
-          <t>2021-07-07</t>
-        </is>
-      </c>
-      <c r="B254" t="n">
-        <v>28008698287</v>
-      </c>
-      <c r="C254" t="n">
-        <v>67984401713</v>
-      </c>
-      <c r="D254" t="n">
-        <v>0.4119871261828604</v>
-      </c>
-      <c r="E254" t="n">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="255">
-      <c r="A255" t="inlineStr">
-        <is>
-          <t>2021-07-08</t>
-        </is>
-      </c>
-      <c r="B255" t="n">
-        <v>30540652959</v>
-      </c>
-      <c r="C255" t="n">
-        <v>76367311906</v>
-      </c>
-      <c r="D255" t="n">
-        <v>0.3999178731941263</v>
-      </c>
-      <c r="E255" t="n">
-        <v>254</v>
       </c>
     </row>
   </sheetData>

--- a/king_index/output/index.xlsx
+++ b/king_index/output/index.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E239"/>
+  <dimension ref="A1:E240"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4977,6 +4977,25 @@
         <v>238</v>
       </c>
     </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>2021-07-12</t>
+        </is>
+      </c>
+      <c r="B240" t="n">
+        <v>35708190055</v>
+      </c>
+      <c r="C240" t="n">
+        <v>86869304227</v>
+      </c>
+      <c r="D240" t="n">
+        <v>0.4110564758489395</v>
+      </c>
+      <c r="E240" t="n">
+        <v>239</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
